--- a/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
+++ b/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlando.carvajal.DESMEX\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlando.carvajal.DESMEX\Desktop\ClaudeCode\Pipeline1\pipeline-web\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60E2C570-AF39-4810-A3D9-501EDB80B233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{00CE5536-C96A-4F7B-8FCF-AD2730557073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Copia seguridad 27-01-2026" sheetId="9" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$K$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$K$190</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Copia seguridad 27-01-2026'!$A$1:$K$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Daniela Lara'!$A$1:$K$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Josué Morales'!$A$1:$K$148</definedName>
@@ -50,11 +50,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={03062533-0299-4130-ab8c-647f611c95d2}</author>
-    <author>tc={e2a6f111-ee8c-4824-bd8b-79fcbb8902d5}</author>
+    <author>tc={59db04cf-5a89-4e3c-8c22-99dd66220e49}</author>
+    <author>tc={936ca761-2c3d-4692-a7d7-4892c3141580}</author>
   </authors>
   <commentList>
-    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{03062533-0299-4130-AB8C-647F611C95D2}">
+    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{59DB04CF-5A89-4E3C-8C22-99DD66220E49}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -62,7 +62,7 @@
     ya lo tiene en seguimiento Josué</t>
       </text>
     </comment>
-    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{E2A6F111-EE8C-4824-BD8B-79FCBB8902D5}">
+    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{936CA761-2C3D-4692-A7D7-4892C3141580}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4590" uniqueCount="1396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4616" uniqueCount="1404">
   <si>
     <t>ID de Prospecto</t>
   </si>
@@ -2273,6 +2273,12 @@
     <t>Punta Mita</t>
   </si>
   <si>
+    <t>Hotel Plaza Camelinas</t>
+  </si>
+  <si>
+    <t>Santiago de Querétaro</t>
+  </si>
+  <si>
     <t>PSP81</t>
   </si>
   <si>
@@ -3473,7 +3479,7 @@
     <t>Acerta</t>
   </si>
   <si>
-    <t>SFV Yy BC</t>
+    <t>SFV y BC</t>
   </si>
   <si>
     <t>Arq. Jaime Mercado</t>
@@ -3569,7 +3575,25 @@
     <t>Arq. Óscar Alvarado</t>
   </si>
   <si>
-    <t>Parque Nesin</t>
+    <t>Parque Industrial Nesin</t>
+  </si>
+  <si>
+    <t>Lic. Fernanda López</t>
+  </si>
+  <si>
+    <t>Mr. Pampas León</t>
+  </si>
+  <si>
+    <t>Heriberto Salgado</t>
+  </si>
+  <si>
+    <t>Truper</t>
+  </si>
+  <si>
+    <t>Mexico City</t>
+  </si>
+  <si>
+    <t>Ing. Héctor Cruz Pacheco</t>
   </si>
   <si>
     <r>
@@ -5538,7 +5562,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Anónimo" id="{A318C847-9990-4DB4-911B-AA3B918BC21D}" userId="" providerId="google-sheets"/>
+  <person displayName="Anónimo" id="{727B64BC-16E0-4E2E-A369-9A34EBDEB621}" userId="" providerId="google-sheets"/>
 </personList>
 </file>
 
@@ -5603,8 +5627,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:K187">
-  <autoFilter ref="A1:K187" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:K190">
+  <autoFilter ref="A1:K190" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID de Prospecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Nombre del Prospecto"/>
@@ -5880,10 +5904,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{A318C847-9990-4DB4-911B-AA3B918BC21D}" id="{03062533-0299-4130-AB8C-647F611C95D2}" done="1">
+  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{727B64BC-16E0-4E2E-A369-9A34EBDEB621}" id="{59DB04CF-5A89-4E3C-8C22-99DD66220E49}" done="1">
     <text>ya lo tiene en seguimiento Josué</text>
   </threadedComment>
-  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{A318C847-9990-4DB4-911B-AA3B918BC21D}" id="{E2A6F111-EE8C-4824-BD8B-79FCBB8902D5}" done="1">
+  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{727B64BC-16E0-4E2E-A369-9A34EBDEB621}" id="{936CA761-2C3D-4692-A7D7-4892C3141580}" done="1">
     <text>Ya tienen contrato con Ammper</text>
   </threadedComment>
 </ThreadedComments>
@@ -12733,15 +12757,33 @@
       <c r="A31" s="46" t="s">
         <v>538</v>
       </c>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="57"/>
+      <c r="B31" s="50" t="s">
+        <v>595</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>730</v>
+      </c>
+      <c r="D31" s="49" t="s">
+        <v>731</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="F31" s="52" t="s">
+        <v>666</v>
+      </c>
+      <c r="G31" s="53">
+        <v>46140</v>
+      </c>
+      <c r="H31" s="54">
+        <v>0</v>
+      </c>
+      <c r="I31" s="55">
+        <v>0.1</v>
+      </c>
+      <c r="J31" s="52" t="s">
+        <v>25</v>
+      </c>
       <c r="K31" s="46" t="s">
         <v>659</v>
       </c>
@@ -13615,7 +13657,7 @@
     </row>
     <row r="83" spans="1:11" ht="22.5" customHeight="1">
       <c r="A83" s="46" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B83" s="50"/>
       <c r="C83" s="50"/>
@@ -13632,7 +13674,7 @@
     </row>
     <row r="84" spans="1:11" ht="22.5" customHeight="1">
       <c r="A84" s="46" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B84" s="50"/>
       <c r="C84" s="50"/>
@@ -13649,7 +13691,7 @@
     </row>
     <row r="85" spans="1:11" ht="22.5" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B85" s="50"/>
       <c r="C85" s="50"/>
@@ -13666,7 +13708,7 @@
     </row>
     <row r="86" spans="1:11" ht="22.5" customHeight="1">
       <c r="A86" s="46" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B86" s="50"/>
       <c r="C86" s="50"/>
@@ -13683,7 +13725,7 @@
     </row>
     <row r="87" spans="1:11" ht="22.5" customHeight="1">
       <c r="A87" s="46" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B87" s="50"/>
       <c r="C87" s="50"/>
@@ -13700,7 +13742,7 @@
     </row>
     <row r="88" spans="1:11" ht="22.5" customHeight="1">
       <c r="A88" s="46" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B88" s="50"/>
       <c r="C88" s="50"/>
@@ -13717,7 +13759,7 @@
     </row>
     <row r="89" spans="1:11" ht="22.5" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B89" s="50"/>
       <c r="C89" s="50"/>
@@ -13734,7 +13776,7 @@
     </row>
     <row r="90" spans="1:11" ht="22.5" customHeight="1">
       <c r="A90" s="46" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B90" s="50"/>
       <c r="C90" s="50"/>
@@ -13751,7 +13793,7 @@
     </row>
     <row r="91" spans="1:11" ht="22.5" customHeight="1">
       <c r="A91" s="46" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B91" s="50"/>
       <c r="C91" s="50"/>
@@ -13768,7 +13810,7 @@
     </row>
     <row r="92" spans="1:11" ht="22.5" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B92" s="50"/>
       <c r="C92" s="50"/>
@@ -13785,7 +13827,7 @@
     </row>
     <row r="93" spans="1:11" ht="22.5" customHeight="1">
       <c r="A93" s="46" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B93" s="50"/>
       <c r="C93" s="50"/>
@@ -13802,7 +13844,7 @@
     </row>
     <row r="94" spans="1:11" ht="22.5" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B94" s="50"/>
       <c r="C94" s="50"/>
@@ -13819,7 +13861,7 @@
     </row>
     <row r="95" spans="1:11" ht="22.5" customHeight="1">
       <c r="A95" s="46" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B95" s="50"/>
       <c r="C95" s="50"/>
@@ -13836,7 +13878,7 @@
     </row>
     <row r="96" spans="1:11" ht="22.5" customHeight="1">
       <c r="A96" s="46" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B96" s="50"/>
       <c r="C96" s="50"/>
@@ -14219,13 +14261,14 @@
     <hyperlink ref="D28" r:id="rId26" xr:uid="{00000000-0004-0000-0300-000019000000}"/>
     <hyperlink ref="D29" r:id="rId27" xr:uid="{00000000-0004-0000-0300-00001A000000}"/>
     <hyperlink ref="D30" r:id="rId28" xr:uid="{00000000-0004-0000-0300-00001B000000}"/>
+    <hyperlink ref="D31" r:id="rId29" xr:uid="{00000000-0004-0000-0300-00001C000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
-  <legacyDrawing r:id="rId29"/>
+  <legacyDrawing r:id="rId30"/>
   <tableParts count="1">
-    <tablePart r:id="rId30"/>
+    <tablePart r:id="rId31"/>
   </tableParts>
 </worksheet>
 </file>
@@ -14236,7 +14279,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC187"/>
+  <dimension ref="A1:AC190"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -14308,10 +14351,10 @@
     <row r="2" spans="1:29" ht="22.5" customHeight="1">
       <c r="A2" s="46"/>
       <c r="B2" s="46" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="D2" s="49" t="s">
         <v>561</v>
@@ -14329,16 +14372,16 @@
       <c r="I2" s="55"/>
       <c r="J2" s="52"/>
       <c r="K2" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
       <c r="A3" s="46"/>
       <c r="B3" s="46" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D3" s="49" t="s">
         <v>561</v>
@@ -14356,22 +14399,22 @@
       <c r="I3" s="55"/>
       <c r="J3" s="52"/>
       <c r="K3" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
       <c r="A4" s="46"/>
       <c r="B4" s="46" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F4" s="52" t="s">
         <v>119</v>
@@ -14385,19 +14428,19 @@
         <v>25</v>
       </c>
       <c r="K4" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
       <c r="A5" s="46"/>
       <c r="B5" s="46" t="s">
+        <v>754</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>755</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>752</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>753</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>750</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>448</v>
@@ -14411,19 +14454,19 @@
       <c r="H5" s="54"/>
       <c r="I5" s="55"/>
       <c r="J5" s="52" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="K5" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
       <c r="A6" s="46"/>
       <c r="B6" s="50" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D6" s="49" t="s">
         <v>561</v>
@@ -14443,19 +14486,19 @@
         <v>25</v>
       </c>
       <c r="K6" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
       <c r="A7" s="46"/>
       <c r="B7" s="50" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>448</v>
@@ -14472,19 +14515,19 @@
         <v>16</v>
       </c>
       <c r="K7" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
       <c r="A8" s="46"/>
       <c r="B8" s="50" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>448</v>
@@ -14501,19 +14544,19 @@
         <v>16</v>
       </c>
       <c r="K8" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
       <c r="A9" s="46"/>
       <c r="B9" s="50" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>448</v>
@@ -14530,16 +14573,16 @@
         <v>16</v>
       </c>
       <c r="K9" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
       <c r="A10" s="46"/>
       <c r="B10" s="50" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D10" s="49" t="s">
         <v>540</v>
@@ -14559,16 +14602,16 @@
         <v>74</v>
       </c>
       <c r="K10" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
       <c r="A11" s="46"/>
       <c r="B11" s="50" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>722</v>
@@ -14585,19 +14628,19 @@
       <c r="H11" s="54"/>
       <c r="I11" s="55"/>
       <c r="J11" s="52" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="50" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D12" s="49" t="s">
         <v>540</v>
@@ -14617,16 +14660,16 @@
         <v>16</v>
       </c>
       <c r="K12" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="50" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D13" s="49" t="s">
         <v>540</v>
@@ -14646,16 +14689,16 @@
         <v>687</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
       <c r="A14" s="46"/>
       <c r="B14" s="50" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D14" s="49" t="s">
         <v>530</v>
@@ -14672,19 +14715,19 @@
       <c r="H14" s="54"/>
       <c r="I14" s="55"/>
       <c r="J14" s="52" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="K14" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
       <c r="A15" s="46"/>
       <c r="B15" s="50" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D15" s="49" t="s">
         <v>561</v>
@@ -14704,16 +14747,16 @@
         <v>687</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
       <c r="A16" s="46"/>
       <c r="B16" s="50" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -14731,19 +14774,19 @@
         <v>687</v>
       </c>
       <c r="K16" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
       <c r="A17" s="46"/>
       <c r="B17" s="50" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>448</v>
@@ -14760,16 +14803,16 @@
         <v>687</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="22.5" customHeight="1">
       <c r="A18" s="46"/>
       <c r="B18" s="50" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D18" s="49" t="s">
         <v>540</v>
@@ -14789,16 +14832,16 @@
         <v>16</v>
       </c>
       <c r="K18" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="22.5" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="50" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D19" s="49" t="s">
         <v>722</v>
@@ -14818,7 +14861,7 @@
         <v>74</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="22.5" customHeight="1">
@@ -14826,13 +14869,13 @@
         <v>175</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C20" s="50" t="s">
         <v>483</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>448</v>
@@ -14849,7 +14892,7 @@
         <v>16</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="22.5" customHeight="1">
@@ -14857,7 +14900,7 @@
         <v>170</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C21" s="50" t="s">
         <v>483</v>
@@ -14880,7 +14923,7 @@
         <v>16</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="22.5" customHeight="1">
@@ -14888,10 +14931,10 @@
         <v>172</v>
       </c>
       <c r="B22" s="50" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D22" s="49" t="s">
         <v>561</v>
@@ -14911,7 +14954,7 @@
         <v>513</v>
       </c>
       <c r="K22" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="22.5" customHeight="1">
@@ -14919,16 +14962,16 @@
         <v>135</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D23" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="F23" s="52" t="s">
         <v>119</v>
@@ -14942,7 +14985,7 @@
         <v>687</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="22.5" customHeight="1">
@@ -14950,13 +14993,13 @@
         <v>139</v>
       </c>
       <c r="B24" s="50" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>448</v>
@@ -14973,7 +15016,7 @@
         <v>16</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="22.5" customHeight="1">
@@ -14981,13 +15024,13 @@
         <v>142</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>448</v>
@@ -15004,7 +15047,7 @@
         <v>74</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -15012,13 +15055,13 @@
         <v>144</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>448</v>
@@ -15035,7 +15078,7 @@
         <v>74</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="22.5" customHeight="1">
@@ -15043,13 +15086,13 @@
         <v>152</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>448</v>
@@ -15066,7 +15109,7 @@
         <v>74</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="22.5" customHeight="1">
@@ -15074,13 +15117,13 @@
         <v>155</v>
       </c>
       <c r="B28" s="50" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="D28" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>448</v>
@@ -15097,24 +15140,24 @@
         <v>74</v>
       </c>
       <c r="K28" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="22.5" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="F29" s="52" t="s">
         <v>119</v>
@@ -15128,7 +15171,7 @@
         <v>687</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="22.5" customHeight="1">
@@ -15136,10 +15179,10 @@
         <v>149</v>
       </c>
       <c r="B30" s="50" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D30" s="49" t="s">
         <v>561</v>
@@ -15163,7 +15206,7 @@
         <v>513</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="22.5" customHeight="1">
@@ -15171,10 +15214,10 @@
         <v>97</v>
       </c>
       <c r="B31" s="50" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D31" s="49" t="s">
         <v>725</v>
@@ -15194,7 +15237,7 @@
         <v>25</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="22.5" customHeight="1">
@@ -15202,13 +15245,13 @@
         <v>99</v>
       </c>
       <c r="B32" s="50" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D32" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>448</v>
@@ -15225,7 +15268,7 @@
         <v>74</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="22.5" customHeight="1">
@@ -15233,10 +15276,10 @@
         <v>103</v>
       </c>
       <c r="B33" s="46" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C33" s="46" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D33" s="49" t="s">
         <v>561</v>
@@ -15256,7 +15299,7 @@
         <v>687</v>
       </c>
       <c r="K33" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="22.5" customHeight="1">
@@ -15264,13 +15307,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="50" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="D34" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>448</v>
@@ -15283,25 +15326,25 @@
       </c>
       <c r="H34" s="54"/>
       <c r="I34" s="59" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="J34" s="52" t="s">
         <v>687</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="22.5" customHeight="1">
       <c r="A35" s="46"/>
       <c r="B35" s="50" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>448</v>
@@ -15318,7 +15361,7 @@
         <v>687</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="22.5" customHeight="1">
@@ -15326,10 +15369,10 @@
         <v>68</v>
       </c>
       <c r="B36" s="50" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C36" s="50" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10" t="s">
@@ -15347,7 +15390,7 @@
         <v>74</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="22.5" customHeight="1">
@@ -15355,10 +15398,10 @@
         <v>71</v>
       </c>
       <c r="B37" s="50" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C37" s="50" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="D37" s="49" t="s">
         <v>540</v>
@@ -15378,7 +15421,7 @@
         <v>687</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="22.5" customHeight="1">
@@ -15386,13 +15429,13 @@
         <v>78</v>
       </c>
       <c r="B38" s="50" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D38" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>448</v>
@@ -15409,7 +15452,7 @@
         <v>16</v>
       </c>
       <c r="K38" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="22.5" customHeight="1">
@@ -15417,16 +15460,16 @@
         <v>81</v>
       </c>
       <c r="B39" s="50" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F39" s="52" t="s">
         <v>119</v>
@@ -15440,19 +15483,19 @@
         <v>16</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="22.5" customHeight="1">
       <c r="A40" s="46"/>
       <c r="B40" s="50" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>448</v>
@@ -15469,7 +15512,7 @@
         <v>74</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="22.5" customHeight="1">
@@ -15477,10 +15520,10 @@
         <v>54</v>
       </c>
       <c r="B41" s="50" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D41" s="49" t="s">
         <v>722</v>
@@ -15500,7 +15543,7 @@
         <v>25</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="22.5" customHeight="1">
@@ -15508,14 +15551,14 @@
         <v>60</v>
       </c>
       <c r="B42" s="46" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F42" s="52" t="s">
         <v>119</v>
@@ -15529,7 +15572,7 @@
         <v>687</v>
       </c>
       <c r="K42" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="22.5" customHeight="1">
@@ -15537,10 +15580,10 @@
         <v>63</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D43" s="49" t="s">
         <v>722</v>
@@ -15560,7 +15603,7 @@
         <v>687</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="22.5" customHeight="1">
@@ -15568,13 +15611,13 @@
         <v>65</v>
       </c>
       <c r="B44" s="50" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>448</v>
@@ -15591,7 +15634,7 @@
         <v>25</v>
       </c>
       <c r="K44" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="22.5" customHeight="1">
@@ -15599,13 +15642,13 @@
         <v>85</v>
       </c>
       <c r="B45" s="50" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>448</v>
@@ -15618,24 +15661,24 @@
       </c>
       <c r="H45" s="54"/>
       <c r="I45" s="59" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="J45" s="52" t="s">
         <v>513</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="22.5" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B46" s="50" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D46" s="49" t="s">
         <v>540</v>
@@ -15655,18 +15698,18 @@
         <v>687</v>
       </c>
       <c r="K46" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="22.5" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B47" s="50" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D47" s="49" t="s">
         <v>526</v>
@@ -15686,21 +15729,21 @@
         <v>25</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="22.5" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B48" s="50" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D48" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>448</v>
@@ -15717,21 +15760,21 @@
         <v>74</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="22.5" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B49" s="50" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>448</v>
@@ -15748,21 +15791,21 @@
         <v>74</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="22.5" customHeight="1">
       <c r="A50" s="8" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B50" s="50" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C50" s="50" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>448</v>
@@ -15779,7 +15822,7 @@
         <v>74</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="22.5" customHeight="1">
@@ -15787,13 +15830,13 @@
         <v>11</v>
       </c>
       <c r="B51" s="50" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="D51" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>448</v>
@@ -15810,7 +15853,7 @@
         <v>687</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="22.5" customHeight="1">
@@ -15818,10 +15861,10 @@
         <v>18</v>
       </c>
       <c r="B52" s="50" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C52" s="50" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D52" s="49" t="s">
         <v>540</v>
@@ -15841,7 +15884,7 @@
         <v>25</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="22.5" customHeight="1">
@@ -15850,7 +15893,7 @@
       </c>
       <c r="B53" s="46"/>
       <c r="C53" s="46" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D53" s="49" t="s">
         <v>722</v>
@@ -15870,7 +15913,7 @@
         <v>687</v>
       </c>
       <c r="K53" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="22.5" customHeight="1">
@@ -15878,13 +15921,13 @@
         <v>26</v>
       </c>
       <c r="B54" s="50" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>448</v>
@@ -15901,7 +15944,7 @@
         <v>687</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="22.5" customHeight="1">
@@ -15909,13 +15952,13 @@
         <v>29</v>
       </c>
       <c r="B55" s="50" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D55" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>448</v>
@@ -15932,7 +15975,7 @@
         <v>74</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="22.5" customHeight="1">
@@ -15940,7 +15983,7 @@
         <v>34</v>
       </c>
       <c r="B56" s="50" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C56" s="50" t="s">
         <v>711</v>
@@ -15963,7 +16006,7 @@
         <v>687</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="22.5" customHeight="1">
@@ -15971,13 +16014,13 @@
         <v>48</v>
       </c>
       <c r="B57" s="50" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C57" s="50" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>448</v>
@@ -15991,10 +16034,10 @@
       <c r="H57" s="54"/>
       <c r="I57" s="55"/>
       <c r="J57" s="52" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="22.5" customHeight="1">
@@ -16002,10 +16045,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="50" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C58" s="50" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="D58" s="49" t="s">
         <v>561</v>
@@ -16025,7 +16068,7 @@
         <v>513</v>
       </c>
       <c r="K58" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="22.5" customHeight="1">
@@ -16033,13 +16076,13 @@
         <v>638</v>
       </c>
       <c r="B59" s="50" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>448</v>
@@ -16056,7 +16099,7 @@
         <v>74</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="22.5" customHeight="1">
@@ -16064,10 +16107,10 @@
         <v>639</v>
       </c>
       <c r="B60" s="50" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D60" s="49" t="s">
         <v>540</v>
@@ -16084,10 +16127,10 @@
       <c r="H60" s="54"/>
       <c r="I60" s="55"/>
       <c r="J60" s="52" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="22.5" customHeight="1">
@@ -16095,13 +16138,13 @@
         <v>640</v>
       </c>
       <c r="B61" s="50" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>448</v>
@@ -16118,7 +16161,7 @@
         <v>74</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="22.5" customHeight="1">
@@ -16126,13 +16169,13 @@
         <v>649</v>
       </c>
       <c r="B62" s="50" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>448</v>
@@ -16149,16 +16192,16 @@
         <v>25</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="22.5" customHeight="1">
       <c r="A63" s="46"/>
       <c r="B63" s="50" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D63" s="49" t="s">
         <v>526</v>
@@ -16178,7 +16221,7 @@
         <v>687</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="22.5" customHeight="1">
@@ -16186,13 +16229,13 @@
         <v>609</v>
       </c>
       <c r="B64" s="50" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C64" s="50" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>448</v>
@@ -16209,7 +16252,7 @@
         <v>74</v>
       </c>
       <c r="K64" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="22.5" customHeight="1">
@@ -16217,13 +16260,13 @@
         <v>621</v>
       </c>
       <c r="B65" s="50" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>448</v>
@@ -16240,7 +16283,7 @@
         <v>74</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="22.5" customHeight="1">
@@ -16248,10 +16291,10 @@
         <v>624</v>
       </c>
       <c r="B66" s="50" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C66" s="50" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D66" s="49" t="s">
         <v>540</v>
@@ -16271,7 +16314,7 @@
         <v>74</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="22.5" customHeight="1">
@@ -16279,16 +16322,16 @@
         <v>597</v>
       </c>
       <c r="B67" s="50" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C67" s="50" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F67" s="52" t="s">
         <v>119</v>
@@ -16302,7 +16345,7 @@
         <v>74</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="22.5" customHeight="1">
@@ -16310,16 +16353,16 @@
         <v>600</v>
       </c>
       <c r="B68" s="50" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="F68" s="52" t="s">
         <v>119</v>
@@ -16333,7 +16376,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="22.5" customHeight="1">
@@ -16341,13 +16384,13 @@
         <v>603</v>
       </c>
       <c r="B69" s="50" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D69" s="49" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>448</v>
@@ -16364,7 +16407,7 @@
         <v>74</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="22.5" customHeight="1">
@@ -16372,13 +16415,13 @@
         <v>146</v>
       </c>
       <c r="B70" s="50" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>448</v>
@@ -16395,7 +16438,7 @@
         <v>687</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="22.5" customHeight="1">
@@ -16403,10 +16446,10 @@
         <v>527</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C71" s="46" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D71" s="49" t="s">
         <v>561</v>
@@ -16426,7 +16469,7 @@
         <v>513</v>
       </c>
       <c r="K71" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="22.5" customHeight="1">
@@ -16434,16 +16477,16 @@
         <v>520</v>
       </c>
       <c r="B72" s="50" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F72" s="52" t="s">
         <v>119</v>
@@ -16457,7 +16500,7 @@
         <v>16</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="22.5" customHeight="1">
@@ -16465,10 +16508,10 @@
         <v>576</v>
       </c>
       <c r="B73" s="50" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="D73" s="10"/>
       <c r="E73" s="10" t="s">
@@ -16486,7 +16529,7 @@
         <v>25</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="22.5" customHeight="1">
@@ -16494,10 +16537,10 @@
         <v>579</v>
       </c>
       <c r="B74" s="50" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D74" s="49" t="s">
         <v>722</v>
@@ -16517,7 +16560,7 @@
         <v>25</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="22.5" customHeight="1">
@@ -16525,13 +16568,13 @@
         <v>650</v>
       </c>
       <c r="B75" s="50" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>448</v>
@@ -16548,7 +16591,7 @@
         <v>25</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="22.5" customHeight="1">
@@ -16556,13 +16599,13 @@
         <v>503</v>
       </c>
       <c r="B76" s="46" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C76" s="46" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D76" s="49" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>448</v>
@@ -16581,7 +16624,7 @@
         <v>25</v>
       </c>
       <c r="K76" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="22.5" customHeight="1">
@@ -16589,16 +16632,16 @@
         <v>506</v>
       </c>
       <c r="B77" s="46" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C77" s="46" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D77" s="49" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="F77" s="52" t="s">
         <v>698</v>
@@ -16612,7 +16655,7 @@
         <v>25</v>
       </c>
       <c r="K77" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="22.5" customHeight="1">
@@ -16620,10 +16663,10 @@
         <v>488</v>
       </c>
       <c r="B78" s="50" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D78" s="10"/>
       <c r="E78" s="10" t="s">
@@ -16643,7 +16686,7 @@
         <v>25</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="22.5" customHeight="1">
@@ -16651,10 +16694,10 @@
         <v>494</v>
       </c>
       <c r="B79" s="46" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C79" s="46" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D79" s="49" t="s">
         <v>657</v>
@@ -16676,21 +16719,21 @@
         <v>25</v>
       </c>
       <c r="K79" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="22.5" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B80" s="50" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D80" s="49" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>448</v>
@@ -16707,7 +16750,7 @@
         <v>16</v>
       </c>
       <c r="K80" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="22.5" customHeight="1">
@@ -16716,7 +16759,7 @@
       </c>
       <c r="B81" s="46"/>
       <c r="C81" s="46" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="D81" s="49" t="s">
         <v>540</v>
@@ -16736,7 +16779,7 @@
         <v>551</v>
       </c>
       <c r="K81" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="22.5" customHeight="1">
@@ -16744,16 +16787,16 @@
         <v>582</v>
       </c>
       <c r="B82" s="50" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C82" s="50" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D82" s="49" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F82" s="52" t="s">
         <v>119</v>
@@ -16767,7 +16810,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="22.5" customHeight="1">
@@ -16775,10 +16818,10 @@
         <v>113</v>
       </c>
       <c r="B83" s="50" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C83" s="50" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="D83" s="49" t="s">
         <v>722</v>
@@ -16798,13 +16841,13 @@
         <v>687</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22.5" customHeight="1">
       <c r="A84" s="46"/>
       <c r="B84" s="46" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C84" s="46" t="s">
         <v>410</v>
@@ -16825,7 +16868,7 @@
         <v>74</v>
       </c>
       <c r="K84" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="22.5" customHeight="1">
@@ -16833,13 +16876,13 @@
         <v>116</v>
       </c>
       <c r="B85" s="50" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="D85" s="49" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>448</v>
@@ -16856,16 +16899,16 @@
         <v>687</v>
       </c>
       <c r="K85" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="22.5" customHeight="1">
       <c r="A86" s="46"/>
       <c r="B86" s="50" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="D86" s="10"/>
       <c r="E86" s="10" t="s">
@@ -16883,16 +16926,16 @@
         <v>25</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="22.5" customHeight="1">
       <c r="A87" s="46"/>
       <c r="B87" s="50" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C87" s="50" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="D87" s="49" t="s">
         <v>677</v>
@@ -16909,22 +16952,22 @@
       <c r="H87" s="54"/>
       <c r="I87" s="55"/>
       <c r="J87" s="52" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="22.5" customHeight="1">
       <c r="A88" s="46"/>
       <c r="B88" s="50" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>448</v>
@@ -16941,7 +16984,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="22.5" customHeight="1">
@@ -16949,13 +16992,13 @@
         <v>565</v>
       </c>
       <c r="B89" s="50" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="D89" s="49" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>448</v>
@@ -16972,7 +17015,7 @@
         <v>25</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="22.5" customHeight="1">
@@ -16980,10 +17023,10 @@
         <v>568</v>
       </c>
       <c r="B90" s="50" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="D90" s="49" t="s">
         <v>722</v>
@@ -17003,7 +17046,7 @@
         <v>25</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="22.5" customHeight="1">
@@ -17011,10 +17054,10 @@
         <v>571</v>
       </c>
       <c r="B91" s="50" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="D91" s="10"/>
       <c r="E91" s="10" t="s">
@@ -17032,7 +17075,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22.5" customHeight="1">
@@ -17040,13 +17083,13 @@
         <v>574</v>
       </c>
       <c r="B92" s="50" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="D92" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>448</v>
@@ -17063,7 +17106,7 @@
         <v>25</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="22.5" customHeight="1">
@@ -17071,10 +17114,10 @@
         <v>562</v>
       </c>
       <c r="B93" s="50" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D93" s="49" t="s">
         <v>540</v>
@@ -17094,7 +17137,7 @@
         <v>25</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="22.5" customHeight="1">
@@ -17102,10 +17145,10 @@
         <v>88</v>
       </c>
       <c r="B94" s="50" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D94" s="49" t="s">
         <v>540</v>
@@ -17125,7 +17168,7 @@
         <v>513</v>
       </c>
       <c r="K94" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="22.5" customHeight="1">
@@ -17133,16 +17176,16 @@
         <v>523</v>
       </c>
       <c r="B95" s="46" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C95" s="46" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="D95" s="49" t="s">
         <v>722</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="F95" s="52" t="s">
         <v>449</v>
@@ -17156,19 +17199,19 @@
         <v>74</v>
       </c>
       <c r="K95" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="22.5" customHeight="1">
       <c r="A96" s="46"/>
       <c r="B96" s="46" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C96" s="46" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D96" s="49" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>448</v>
@@ -17185,7 +17228,7 @@
         <v>25</v>
       </c>
       <c r="K96" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="22.5" customHeight="1">
@@ -17193,13 +17236,13 @@
         <v>643</v>
       </c>
       <c r="B97" s="50" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="D97" s="49" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>448</v>
@@ -17216,7 +17259,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="22.5" customHeight="1">
@@ -17224,10 +17267,10 @@
         <v>644</v>
       </c>
       <c r="B98" s="50" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C98" s="50" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="D98" s="49" t="s">
         <v>526</v>
@@ -17247,7 +17290,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="22.5" customHeight="1">
@@ -17255,13 +17298,13 @@
         <v>132</v>
       </c>
       <c r="B99" s="50" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C99" s="50" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="D99" s="49" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>448</v>
@@ -17278,7 +17321,7 @@
         <v>513</v>
       </c>
       <c r="K99" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="22.5" customHeight="1">
@@ -17286,10 +17329,10 @@
         <v>606</v>
       </c>
       <c r="B100" s="50" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C100" s="50" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D100" s="49" t="s">
         <v>561</v>
@@ -17309,7 +17352,7 @@
         <v>25</v>
       </c>
       <c r="K100" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="22.5" customHeight="1">
@@ -17317,10 +17360,10 @@
         <v>538</v>
       </c>
       <c r="B101" s="50" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C101" s="50" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="D101" s="49" t="s">
         <v>722</v>
@@ -17340,7 +17383,7 @@
         <v>25</v>
       </c>
       <c r="K101" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="22.5" customHeight="1">
@@ -17348,10 +17391,10 @@
         <v>645</v>
       </c>
       <c r="B102" s="50" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C102" s="50" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="D102" s="49" t="s">
         <v>526</v>
@@ -17371,7 +17414,7 @@
         <v>16</v>
       </c>
       <c r="K102" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="22.5" customHeight="1">
@@ -17379,10 +17422,10 @@
         <v>120</v>
       </c>
       <c r="B103" s="50" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C103" s="50" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="D103" s="49" t="s">
         <v>540</v>
@@ -17402,7 +17445,7 @@
         <v>16</v>
       </c>
       <c r="K103" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="22.5" customHeight="1">
@@ -17410,13 +17453,13 @@
         <v>126</v>
       </c>
       <c r="B104" s="50" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C104" s="50" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>448</v>
@@ -17433,7 +17476,7 @@
         <v>16</v>
       </c>
       <c r="K104" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="22.5" customHeight="1">
@@ -17441,11 +17484,11 @@
         <v>41</v>
       </c>
       <c r="B105" s="50" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C105" s="50"/>
       <c r="D105" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>448</v>
@@ -17462,7 +17505,7 @@
         <v>16</v>
       </c>
       <c r="K105" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="22.5" customHeight="1">
@@ -17470,10 +17513,10 @@
         <v>646</v>
       </c>
       <c r="B106" s="50" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C106" s="50" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D106" s="49" t="s">
         <v>722</v>
@@ -17490,21 +17533,21 @@
       <c r="H106" s="54"/>
       <c r="I106" s="55"/>
       <c r="J106" s="52" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="K106" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="22.5" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B107" s="50" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C107" s="50" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="D107" s="49" t="s">
         <v>722</v>
@@ -17524,19 +17567,19 @@
         <v>74</v>
       </c>
       <c r="K107" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="22.5" customHeight="1">
       <c r="A108" s="46"/>
       <c r="B108" s="50" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="D108" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>448</v>
@@ -17553,7 +17596,7 @@
         <v>687</v>
       </c>
       <c r="K108" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="22.5" customHeight="1">
@@ -17561,13 +17604,13 @@
         <v>459</v>
       </c>
       <c r="B109" s="46" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C109" s="46" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>448</v>
@@ -17588,7 +17631,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="22.5" customHeight="1">
@@ -17596,10 +17639,10 @@
         <v>462</v>
       </c>
       <c r="B110" s="46" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C110" s="46" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D110" s="49" t="s">
         <v>540</v>
@@ -17621,7 +17664,7 @@
         <v>25</v>
       </c>
       <c r="K110" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="22.5" customHeight="1">
@@ -17629,19 +17672,19 @@
         <v>552</v>
       </c>
       <c r="B111" s="46" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C111" s="46" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D111" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F111" s="52" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G111" s="53">
         <v>45952</v>
@@ -17652,7 +17695,7 @@
         <v>25</v>
       </c>
       <c r="K111" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="22.5" customHeight="1">
@@ -17660,13 +17703,13 @@
         <v>534</v>
       </c>
       <c r="B112" s="50" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C112" s="50" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>448</v>
@@ -17683,7 +17726,7 @@
         <v>25</v>
       </c>
       <c r="K112" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="22.5" customHeight="1">
@@ -17691,10 +17734,10 @@
         <v>594</v>
       </c>
       <c r="B113" s="50" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="C113" s="50" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="D113" s="49" t="s">
         <v>540</v>
@@ -17714,7 +17757,7 @@
         <v>25</v>
       </c>
       <c r="K113" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="22.5" customHeight="1">
@@ -17722,10 +17765,10 @@
         <v>642</v>
       </c>
       <c r="B114" s="50" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C114" s="50" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="D114" s="49" t="s">
         <v>722</v>
@@ -17745,7 +17788,7 @@
         <v>25</v>
       </c>
       <c r="K114" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="22.5" customHeight="1">
@@ -17753,16 +17796,16 @@
         <v>531</v>
       </c>
       <c r="B115" s="46" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C115" s="46" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D115" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F115" s="52" t="s">
         <v>119</v>
@@ -17776,21 +17819,21 @@
         <v>25</v>
       </c>
       <c r="K115" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="22.5" customHeight="1">
       <c r="A116" s="8" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B116" s="50" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C116" s="50" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>448</v>
@@ -17804,10 +17847,10 @@
       <c r="H116" s="54"/>
       <c r="I116" s="55"/>
       <c r="J116" s="52" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="K116" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="22.5" customHeight="1">
@@ -17815,16 +17858,16 @@
         <v>94</v>
       </c>
       <c r="B117" s="50" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C117" s="50" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D117" s="49" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="F117" s="52" t="s">
         <v>119</v>
@@ -17838,7 +17881,7 @@
         <v>25</v>
       </c>
       <c r="K117" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="22.5" customHeight="1">
@@ -17846,19 +17889,19 @@
         <v>454</v>
       </c>
       <c r="B118" s="46" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C118" s="46" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F118" s="52" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G118" s="53">
         <v>45940</v>
@@ -17871,7 +17914,7 @@
         <v>25</v>
       </c>
       <c r="K118" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="22.5" customHeight="1">
@@ -17879,13 +17922,13 @@
         <v>585</v>
       </c>
       <c r="B119" s="50" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C119" s="50" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D119" s="49" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>448</v>
@@ -17902,7 +17945,7 @@
         <v>25</v>
       </c>
       <c r="K119" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="22.5" customHeight="1">
@@ -17910,13 +17953,13 @@
         <v>591</v>
       </c>
       <c r="B120" s="50" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C120" s="50" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>448</v>
@@ -17933,7 +17976,7 @@
         <v>25</v>
       </c>
       <c r="K120" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="22.5" customHeight="1">
@@ -17941,10 +17984,10 @@
         <v>91</v>
       </c>
       <c r="B121" s="50" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="C121" s="50" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D121" s="49" t="s">
         <v>540</v>
@@ -17964,7 +18007,7 @@
         <v>16</v>
       </c>
       <c r="K121" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="22.5" customHeight="1">
@@ -17972,19 +18015,19 @@
         <v>457</v>
       </c>
       <c r="B122" s="46" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C122" s="46" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F122" s="52" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G122" s="53">
         <v>45933</v>
@@ -17997,7 +18040,7 @@
         <v>25</v>
       </c>
       <c r="K122" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="22.5" customHeight="1">
@@ -18005,13 +18048,13 @@
         <v>652</v>
       </c>
       <c r="B123" s="50" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C123" s="50" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="D123" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>448</v>
@@ -18028,7 +18071,7 @@
         <v>16</v>
       </c>
       <c r="K123" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="22.5" customHeight="1">
@@ -18036,10 +18079,10 @@
         <v>37</v>
       </c>
       <c r="B124" s="46" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C124" s="46" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="D124" s="49" t="s">
         <v>540</v>
@@ -18056,24 +18099,24 @@
       <c r="H124" s="54"/>
       <c r="I124" s="55"/>
       <c r="J124" s="52" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="K124" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="22.5" customHeight="1">
       <c r="A125" s="8" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B125" s="46" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="C125" s="46" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="D125" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>448</v>
@@ -18090,18 +18133,18 @@
         <v>513</v>
       </c>
       <c r="K125" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="22.5" customHeight="1">
       <c r="A126" s="8" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B126" s="50" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="D126" s="49" t="s">
         <v>540</v>
@@ -18121,21 +18164,21 @@
         <v>16</v>
       </c>
       <c r="K126" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="22.5" customHeight="1">
       <c r="A127" s="8" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B127" s="50" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="C127" s="50" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="D127" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>448</v>
@@ -18152,7 +18195,7 @@
         <v>16</v>
       </c>
       <c r="K127" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="22.5" customHeight="1">
@@ -18160,13 +18203,13 @@
         <v>168</v>
       </c>
       <c r="B128" s="50" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="C128" s="50" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="D128" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>448</v>
@@ -18183,21 +18226,21 @@
         <v>74</v>
       </c>
       <c r="K128" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="22.5" customHeight="1">
       <c r="A129" s="8" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B129" s="50" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="C129" s="50" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>448</v>
@@ -18214,7 +18257,7 @@
         <v>25</v>
       </c>
       <c r="K129" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="22.5" customHeight="1">
@@ -18222,13 +18265,13 @@
         <v>641</v>
       </c>
       <c r="B130" s="50" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C130" s="50" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="E130" s="10" t="s">
         <v>448</v>
@@ -18245,7 +18288,7 @@
         <v>25</v>
       </c>
       <c r="K130" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="22.5" customHeight="1">
@@ -18253,10 +18296,10 @@
         <v>630</v>
       </c>
       <c r="B131" s="50" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="C131" s="50" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="D131" s="49" t="s">
         <v>717</v>
@@ -18276,7 +18319,7 @@
         <v>25</v>
       </c>
       <c r="K131" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="22.5" customHeight="1">
@@ -18284,13 +18327,13 @@
         <v>627</v>
       </c>
       <c r="B132" s="50" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="D132" s="49" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>448</v>
@@ -18307,7 +18350,7 @@
         <v>513</v>
       </c>
       <c r="K132" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="22.5" customHeight="1">
@@ -18315,10 +18358,10 @@
         <v>555</v>
       </c>
       <c r="B133" s="50" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="D133" s="49" t="s">
         <v>540</v>
@@ -18340,7 +18383,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="22.5" customHeight="1">
@@ -18348,13 +18391,13 @@
         <v>160</v>
       </c>
       <c r="B134" s="50" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="D134" s="49" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>448</v>
@@ -18371,7 +18414,7 @@
         <v>16</v>
       </c>
       <c r="K134" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="22.5" customHeight="1">
@@ -18379,10 +18422,10 @@
         <v>451</v>
       </c>
       <c r="B135" s="46" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C135" s="46" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D135" s="49" t="s">
         <v>540</v>
@@ -18406,7 +18449,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="22.5" customHeight="1">
@@ -18414,13 +18457,13 @@
         <v>547</v>
       </c>
       <c r="B136" s="50" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D136" s="49" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>448</v>
@@ -18437,7 +18480,7 @@
         <v>25</v>
       </c>
       <c r="K136" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="22.5" customHeight="1">
@@ -18446,10 +18489,10 @@
       </c>
       <c r="B137" s="50"/>
       <c r="C137" s="50" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>448</v>
@@ -18466,7 +18509,7 @@
         <v>25</v>
       </c>
       <c r="K137" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="22.5" customHeight="1">
@@ -18474,13 +18517,13 @@
         <v>541</v>
       </c>
       <c r="B138" s="50" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="D138" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>448</v>
@@ -18497,7 +18540,7 @@
         <v>138</v>
       </c>
       <c r="K138" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="22.5" customHeight="1">
@@ -18505,10 +18548,10 @@
         <v>477</v>
       </c>
       <c r="B139" s="46" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C139" s="46" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D139" s="49" t="s">
         <v>540</v>
@@ -18517,7 +18560,7 @@
         <v>448</v>
       </c>
       <c r="F139" s="52" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G139" s="53">
         <v>45822</v>
@@ -18530,7 +18573,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="22.5" customHeight="1">
@@ -18538,13 +18581,13 @@
         <v>654</v>
       </c>
       <c r="B140" s="50" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C140" s="50" t="s">
         <v>410</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="E140" s="10" t="s">
         <v>448</v>
@@ -18561,7 +18604,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="22.5" customHeight="1">
@@ -18569,13 +18612,13 @@
         <v>491</v>
       </c>
       <c r="B141" s="46" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C141" s="46" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D141" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>448</v>
@@ -18596,7 +18639,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="22.5" customHeight="1">
@@ -18604,13 +18647,13 @@
         <v>471</v>
       </c>
       <c r="B142" s="46" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C142" s="46" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E142" s="10" t="s">
         <v>448</v>
@@ -18629,7 +18672,7 @@
         <v>25</v>
       </c>
       <c r="K142" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="22.5" customHeight="1">
@@ -18637,10 +18680,10 @@
         <v>667</v>
       </c>
       <c r="B143" s="46" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="C143" s="46" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="D143" s="10" t="s">
         <v>717</v>
@@ -18662,7 +18705,7 @@
         <v>25</v>
       </c>
       <c r="K143" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="22.5" customHeight="1">
@@ -18670,10 +18713,10 @@
         <v>123</v>
       </c>
       <c r="B144" s="50" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="D144" s="49" t="s">
         <v>540</v>
@@ -18693,7 +18736,7 @@
         <v>16</v>
       </c>
       <c r="K144" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="22.5" customHeight="1">
@@ -18701,10 +18744,10 @@
         <v>544</v>
       </c>
       <c r="B145" s="50" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D145" s="49" t="s">
         <v>540</v>
@@ -18724,25 +18767,25 @@
         <v>25</v>
       </c>
       <c r="K145" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="22.5" customHeight="1">
       <c r="A146" s="46"/>
       <c r="B146" s="50" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="D146" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F146" s="52" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G146" s="53">
         <v>45736</v>
@@ -18753,7 +18796,7 @@
         <v>25</v>
       </c>
       <c r="K146" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="22.5" customHeight="1">
@@ -18761,10 +18804,10 @@
         <v>474</v>
       </c>
       <c r="B147" s="46" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="C147" s="46" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="D147" s="49" t="s">
         <v>540</v>
@@ -18773,7 +18816,7 @@
         <v>448</v>
       </c>
       <c r="F147" s="52" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G147" s="53">
         <v>45700</v>
@@ -18786,7 +18829,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="22.5" customHeight="1">
@@ -18794,13 +18837,13 @@
         <v>636</v>
       </c>
       <c r="B148" s="50" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="C148" s="50" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="D148" s="49" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E148" s="10" t="s">
         <v>448</v>
@@ -18817,7 +18860,7 @@
         <v>16</v>
       </c>
       <c r="K148" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="22.5" customHeight="1">
@@ -18825,13 +18868,13 @@
         <v>637</v>
       </c>
       <c r="B149" s="50" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="D149" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>448</v>
@@ -18845,10 +18888,10 @@
       <c r="H149" s="54"/>
       <c r="I149" s="55"/>
       <c r="J149" s="52" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="K149" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="22.5" customHeight="1">
@@ -18856,13 +18899,13 @@
         <v>497</v>
       </c>
       <c r="B150" s="46" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C150" s="46" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="D150" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>448</v>
@@ -18883,7 +18926,7 @@
         <v>25</v>
       </c>
       <c r="K150" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="151" spans="1:11" ht="22.5" customHeight="1">
@@ -18891,16 +18934,16 @@
         <v>500</v>
       </c>
       <c r="B151" s="46" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C151" s="46" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="D151" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="F151" s="52" t="s">
         <v>24</v>
@@ -18916,7 +18959,7 @@
         <v>25</v>
       </c>
       <c r="K151" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="22.5" customHeight="1">
@@ -18924,13 +18967,13 @@
         <v>651</v>
       </c>
       <c r="B152" s="50" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C152" s="50" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D152" s="49" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>448</v>
@@ -18947,7 +18990,7 @@
         <v>25</v>
       </c>
       <c r="K152" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="22.5" customHeight="1">
@@ -18955,16 +18998,16 @@
         <v>588</v>
       </c>
       <c r="B153" s="50" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="C153" s="50" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="D153" s="49" t="s">
         <v>526</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F153" s="52" t="s">
         <v>119</v>
@@ -18978,7 +19021,7 @@
         <v>25</v>
       </c>
       <c r="K153" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="22.5" customHeight="1">
@@ -18986,10 +19029,10 @@
         <v>481</v>
       </c>
       <c r="B154" s="46" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C154" s="46" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="D154" s="49" t="s">
         <v>526</v>
@@ -18998,7 +19041,7 @@
         <v>448</v>
       </c>
       <c r="F154" s="52" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G154" s="53">
         <v>45519</v>
@@ -19011,7 +19054,7 @@
         <v>25</v>
       </c>
       <c r="K154" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="22.5" customHeight="1">
@@ -19019,13 +19062,13 @@
         <v>517</v>
       </c>
       <c r="B155" s="46" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C155" s="46" t="s">
         <v>483</v>
       </c>
       <c r="D155" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>448</v>
@@ -19046,24 +19089,24 @@
         <v>138</v>
       </c>
       <c r="K155" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="22.5" customHeight="1">
       <c r="A156" s="8" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B156" s="50" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D156" s="49" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="E156" s="10" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F156" s="52" t="s">
         <v>119</v>
@@ -19077,7 +19120,7 @@
         <v>25</v>
       </c>
       <c r="K156" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="22.5" customHeight="1">
@@ -19085,19 +19128,19 @@
         <v>514</v>
       </c>
       <c r="B157" s="46" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="C157" s="46" t="s">
         <v>483</v>
       </c>
       <c r="D157" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F157" s="52" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G157" s="53">
         <v>45513</v>
@@ -19110,7 +19153,7 @@
         <v>16</v>
       </c>
       <c r="K157" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="22.5" customHeight="1">
@@ -19118,13 +19161,13 @@
         <v>166</v>
       </c>
       <c r="B158" s="50" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C158" s="50" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="E158" s="10" t="s">
         <v>448</v>
@@ -19141,7 +19184,7 @@
         <v>74</v>
       </c>
       <c r="K158" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="22.5" customHeight="1">
@@ -19149,13 +19192,13 @@
         <v>618</v>
       </c>
       <c r="B159" s="50" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C159" s="50" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="D159" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>448</v>
@@ -19172,7 +19215,7 @@
         <v>513</v>
       </c>
       <c r="K159" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="22.5" customHeight="1">
@@ -19180,10 +19223,10 @@
         <v>633</v>
       </c>
       <c r="B160" s="50" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C160" s="50" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="D160" s="49" t="s">
         <v>526</v>
@@ -19203,7 +19246,7 @@
         <v>16</v>
       </c>
       <c r="K160" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="22.5" customHeight="1">
@@ -19211,10 +19254,10 @@
         <v>75</v>
       </c>
       <c r="B161" s="50" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="C161" s="50" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="D161" s="49" t="s">
         <v>540</v>
@@ -19234,7 +19277,7 @@
         <v>25</v>
       </c>
       <c r="K161" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="162" spans="1:11" ht="22.5" customHeight="1">
@@ -19242,19 +19285,19 @@
         <v>465</v>
       </c>
       <c r="B162" s="46" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C162" s="46" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="E162" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F162" s="52" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G162" s="53">
         <v>45384</v>
@@ -19269,16 +19312,16 @@
         <v>138</v>
       </c>
       <c r="K162" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="22.5" customHeight="1">
       <c r="A163" s="46"/>
       <c r="B163" s="50" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C163" s="50" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D163" s="49" t="s">
         <v>540</v>
@@ -19298,7 +19341,7 @@
         <v>16</v>
       </c>
       <c r="K163" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="22.5" customHeight="1">
@@ -19306,19 +19349,19 @@
         <v>484</v>
       </c>
       <c r="B164" s="46" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="C164" s="46" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E164" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F164" s="52" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G164" s="53">
         <v>45203</v>
@@ -19333,7 +19376,7 @@
         <v>25</v>
       </c>
       <c r="K164" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="22.5" customHeight="1">
@@ -19341,13 +19384,13 @@
         <v>558</v>
       </c>
       <c r="B165" s="50" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="C165" s="50" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>448</v>
@@ -19366,7 +19409,7 @@
         <v>25</v>
       </c>
       <c r="K165" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="22.5" customHeight="1">
@@ -19374,13 +19417,13 @@
         <v>615</v>
       </c>
       <c r="B166" s="50" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C166" s="50" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="D166" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E166" s="10" t="s">
         <v>448</v>
@@ -19397,7 +19440,7 @@
         <v>513</v>
       </c>
       <c r="K166" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="167" spans="1:11" ht="22.5" customHeight="1">
@@ -19405,13 +19448,13 @@
         <v>648</v>
       </c>
       <c r="B167" s="50" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="C167" s="50" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>448</v>
@@ -19428,7 +19471,7 @@
         <v>25</v>
       </c>
       <c r="K167" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="22.5" customHeight="1">
@@ -19436,13 +19479,13 @@
         <v>612</v>
       </c>
       <c r="B168" s="50" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C168" s="50" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="D168" s="49" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="E168" s="10" t="s">
         <v>448</v>
@@ -19459,7 +19502,7 @@
         <v>16</v>
       </c>
       <c r="K168" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="169" spans="1:11" ht="22.5" customHeight="1">
@@ -19467,19 +19510,19 @@
         <v>647</v>
       </c>
       <c r="B169" s="50" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="C169" s="50" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D169" s="10" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F169" s="52" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="G169" s="53">
         <v>44725</v>
@@ -19490,7 +19533,7 @@
         <v>25</v>
       </c>
       <c r="K169" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="22.5" customHeight="1">
@@ -19498,13 +19541,13 @@
         <v>51</v>
       </c>
       <c r="B170" s="50" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="C170" s="50" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="D170" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E170" s="10" t="s">
         <v>448</v>
@@ -19521,7 +19564,7 @@
         <v>25</v>
       </c>
       <c r="K170" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="171" spans="1:11" ht="22.5" customHeight="1">
@@ -19529,13 +19572,13 @@
         <v>45</v>
       </c>
       <c r="B171" s="50" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="C171" s="50" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="D171" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>448</v>
@@ -19552,7 +19595,7 @@
         <v>74</v>
       </c>
       <c r="K171" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="172" spans="1:11" ht="22.5" customHeight="1">
@@ -19560,13 +19603,13 @@
         <v>445</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="D172" s="61" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="E172" s="62"/>
       <c r="F172" s="63" t="s">
@@ -19580,10 +19623,10 @@
       </c>
       <c r="I172" s="66"/>
       <c r="J172" s="63" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K172" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="173" spans="1:11" ht="22.5" customHeight="1">
@@ -19591,13 +19634,13 @@
         <v>468</v>
       </c>
       <c r="B173" s="46" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C173" s="46" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D173" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>448</v>
@@ -19618,24 +19661,24 @@
         <v>138</v>
       </c>
       <c r="K173" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="174" spans="1:11" ht="22.5" customHeight="1">
       <c r="A174" s="8" t="s">
         <v>653</v>
       </c>
-      <c r="B174" s="50" t="s">
-        <v>1128</v>
+      <c r="B174" s="1" t="s">
+        <v>1130</v>
       </c>
       <c r="C174" s="50" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D174" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F174" s="52" t="s">
         <v>119</v>
@@ -19649,7 +19692,7 @@
         <v>25</v>
       </c>
       <c r="K174" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="175" spans="1:11" ht="22.5" customHeight="1">
@@ -19657,13 +19700,13 @@
         <v>158</v>
       </c>
       <c r="B175" s="50" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C175" s="50" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="D175" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>448</v>
@@ -19680,19 +19723,19 @@
         <v>16</v>
       </c>
       <c r="K175" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="176" spans="1:11" ht="22.5" customHeight="1">
       <c r="A176" s="46"/>
       <c r="B176" s="50" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="C176" s="50" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D176" s="49" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E176" s="10" t="s">
         <v>448</v>
@@ -19713,7 +19756,7 @@
         <v>138</v>
       </c>
       <c r="K176" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="177" spans="1:11" ht="22.5" customHeight="1">
@@ -19721,16 +19764,16 @@
         <v>510</v>
       </c>
       <c r="B177" s="50" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C177" s="50" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="D177" s="49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="F177" s="52" t="s">
         <v>24</v>
@@ -19744,7 +19787,7 @@
         <v>25</v>
       </c>
       <c r="K177" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="178" spans="1:11" ht="22.5" customHeight="1">
@@ -19752,16 +19795,16 @@
         <v>110</v>
       </c>
       <c r="B178" s="50" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="C178" s="50" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D178" s="10" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="E178" s="10" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="F178" s="52" t="s">
         <v>119</v>
@@ -19773,19 +19816,19 @@
         <v>513</v>
       </c>
       <c r="K178" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="179" spans="1:11" ht="22.5" customHeight="1">
       <c r="A179" s="46"/>
       <c r="B179" s="50" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="C179" s="50" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="D179" s="10" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>448</v>
@@ -19806,19 +19849,19 @@
         <v>513</v>
       </c>
       <c r="K179" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="180" spans="1:11" ht="22.5" customHeight="1">
       <c r="A180" s="46"/>
       <c r="B180" s="50" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="C180" s="50" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="D180" s="10" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="E180" s="10" t="s">
         <v>448</v>
@@ -19837,22 +19880,22 @@
         <v>25</v>
       </c>
       <c r="K180" s="50" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="181" spans="1:11" ht="22.5" customHeight="1">
       <c r="A181" s="46"/>
       <c r="B181" s="46" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="C181" s="46" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D181" s="10" t="s">
         <v>1149</v>
       </c>
-      <c r="D181" s="10" t="s">
-        <v>1147</v>
-      </c>
       <c r="E181" s="10" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="F181" s="52" t="s">
         <v>119</v>
@@ -19862,22 +19905,22 @@
       <c r="I181" s="55"/>
       <c r="J181" s="52"/>
       <c r="K181" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="182" spans="1:11" ht="22.5" customHeight="1">
       <c r="A182" s="46"/>
       <c r="B182" s="46" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="C182" s="46" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D182" s="10" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E182" s="10" t="s">
         <v>1152</v>
-      </c>
-      <c r="D182" s="10" t="s">
-        <v>1147</v>
-      </c>
-      <c r="E182" s="10" t="s">
-        <v>1150</v>
       </c>
       <c r="F182" s="52" t="s">
         <v>106</v>
@@ -19895,16 +19938,16 @@
         <v>74</v>
       </c>
       <c r="K182" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="183" spans="1:11" ht="22.5" customHeight="1">
       <c r="A183" s="46"/>
       <c r="B183" s="46" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C183" s="46" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="D183" s="49" t="s">
         <v>561</v>
@@ -19928,19 +19971,19 @@
         <v>25</v>
       </c>
       <c r="K183" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="184" spans="1:11" ht="22.5" customHeight="1">
       <c r="A184" s="46"/>
       <c r="B184" s="46" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="C184" s="46" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="D184" s="10" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="E184" s="10" t="s">
         <v>448</v>
@@ -19961,16 +20004,16 @@
         <v>25</v>
       </c>
       <c r="K184" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="185" spans="1:11" ht="22.5" customHeight="1">
       <c r="A185" s="46"/>
       <c r="B185" s="46" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="C185" s="46" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D185" s="49" t="s">
         <v>677</v>
@@ -19994,19 +20037,19 @@
         <v>25</v>
       </c>
       <c r="K185" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="186" spans="1:11" ht="22.5" customHeight="1">
       <c r="A186" s="46"/>
       <c r="B186" s="46" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="C186" s="46" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D186" s="49" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="E186" s="10" t="s">
         <v>448</v>
@@ -20027,16 +20070,16 @@
         <v>25</v>
       </c>
       <c r="K186" s="46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="187" spans="1:11" ht="22.5" customHeight="1">
       <c r="A187" s="46"/>
       <c r="B187" s="46" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="C187" s="46" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="D187" s="49" t="s">
         <v>561</v>
@@ -20047,29 +20090,114 @@
       <c r="F187" s="52" t="s">
         <v>449</v>
       </c>
-      <c r="G187" s="53"/>
+      <c r="G187" s="53">
+        <v>46074</v>
+      </c>
       <c r="H187" s="54"/>
       <c r="I187" s="55"/>
-      <c r="J187" s="52"/>
+      <c r="J187" s="52" t="s">
+        <v>25</v>
+      </c>
       <c r="K187" s="46" t="s">
-        <v>745</v>
-      </c>
+        <v>747</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" ht="22.5" customHeight="1">
+      <c r="A188" s="46"/>
+      <c r="B188" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C188" s="46" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D188" s="49" t="s">
+        <v>561</v>
+      </c>
+      <c r="E188" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F188" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="G188" s="53">
+        <v>46097</v>
+      </c>
+      <c r="H188" s="54"/>
+      <c r="I188" s="55"/>
+      <c r="J188" s="52" t="s">
+        <v>513</v>
+      </c>
+      <c r="K188" s="46" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" ht="22.5" customHeight="1">
+      <c r="A189" s="46"/>
+      <c r="B189" s="9" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C189" s="46" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D189" s="49" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E189" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F189" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="G189" s="53">
+        <v>46140</v>
+      </c>
+      <c r="H189" s="54"/>
+      <c r="I189" s="55"/>
+      <c r="J189" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="K189" s="46" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" ht="22.5" customHeight="1">
+      <c r="A190" s="46"/>
+      <c r="B190" s="9" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C190" s="46" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D190" s="49" t="s">
+        <v>942</v>
+      </c>
+      <c r="E190" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F190" s="52" t="s">
+        <v>449</v>
+      </c>
+      <c r="G190" s="53"/>
+      <c r="H190" s="54"/>
+      <c r="I190" s="55"/>
+      <c r="J190" s="52"/>
+      <c r="K190" s="46"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="F2:F187" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F190" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"1. Prospección,2. Contacto Inicial,3. Calificación,4. Levantamiento de Requerimientos,5. Visita Técnica / Diagnóstico en Sitio,6. Diseño de Solución / Pre-Ingeniería,7. Estimación / Cotización,8. Propuesta Enviada,9. Aclaraciones / Ajustes de Propuesta,10"&amp;". Negociación,11. Aprobación Interna (Go/No-Go),12. Cierre de Venta (Contrato / OC),13. Kickoff / Inicio de Proyecto,14. Descartado / No Califica,15. En Pausa / Seguimiento Posterior"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G187" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G190" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G2))), AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I187" xr:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I190" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>AND(ISNUMBER(H2),(NOT(OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J187" xr:uid="{00000000-0002-0000-0400-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J190" xr:uid="{00000000-0002-0000-0400-000003000000}">
       <formula1>"Referido (Cliente),Referido (Proveedor/Subcontratista),Referido (Empleado/Interno),Cliente Recurrente (Recompra/Ampliación),Sitio Web (Formulario),Landing Page (Campaña),Chat Web / WhatsApp,SEO (Búsqueda Orgánica),Google Ads (Search),Remarketing (Display/"&amp;"Redes),LinkedIn (Orgánico),Email Outbound (Prospección),Llamada en Frío (Prospección),Visita en Frío (Prospección),Feria / Expo Industrial,Congreso / Cámara / Networking,Webinar / Evento Virtual,Licitación Pública,Licitación Privada (RFP/RFQ),Portal de Co"&amp;"mpras (Cliente),Alianza (Integrador/EPC/Constructor),Partner Tecnológico (Marca/Distribuidor),Directorio B2B / Clúster,Redes Sociales (Facebook/Instagram),YouTube / Contenido Técnico,PR / Medio Especializado,Reactivación de Base de Datos,Otros"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C187 E2:E187 K2:K187" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C190 E2:E190 K2:K190" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -20224,12 +20352,15 @@
     <hyperlink ref="D185" r:id="rId150" xr:uid="{00000000-0004-0000-0400-000095000000}"/>
     <hyperlink ref="D186" r:id="rId151" xr:uid="{00000000-0004-0000-0400-000096000000}"/>
     <hyperlink ref="D187" r:id="rId152" xr:uid="{00000000-0004-0000-0400-000097000000}"/>
+    <hyperlink ref="D188" r:id="rId153" xr:uid="{00000000-0004-0000-0400-000098000000}"/>
+    <hyperlink ref="D189" r:id="rId154" xr:uid="{00000000-0004-0000-0400-000099000000}"/>
+    <hyperlink ref="D190" r:id="rId155" xr:uid="{00000000-0004-0000-0400-00009A000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
   <tableParts count="1">
-    <tablePart r:id="rId153"/>
+    <tablePart r:id="rId156"/>
   </tableParts>
 </worksheet>
 </file>
@@ -20314,10 +20445,10 @@
         <v>481</v>
       </c>
       <c r="B2" s="67" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="D2" s="68"/>
       <c r="E2" s="68"/>
@@ -20337,7 +20468,7 @@
         <v>25</v>
       </c>
       <c r="K2" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="21" customHeight="1">
@@ -20345,10 +20476,10 @@
         <v>484</v>
       </c>
       <c r="B3" s="75" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="C3" s="74" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="D3" s="68"/>
       <c r="E3" s="68"/>
@@ -20366,7 +20497,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -20374,10 +20505,10 @@
         <v>488</v>
       </c>
       <c r="B4" s="79" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="C4" s="80" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="D4" s="81"/>
       <c r="E4" s="68"/>
@@ -20395,7 +20526,7 @@
         <v>25</v>
       </c>
       <c r="K4" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -20403,10 +20534,10 @@
         <v>491</v>
       </c>
       <c r="B5" s="79" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="C5" s="80" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="D5" s="81"/>
       <c r="E5" s="68"/>
@@ -20421,10 +20552,10 @@
       </c>
       <c r="I5" s="85"/>
       <c r="J5" s="88" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K5" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -20432,10 +20563,10 @@
         <v>494</v>
       </c>
       <c r="B6" s="79" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="C6" s="80" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="D6" s="81"/>
       <c r="E6" s="68"/>
@@ -20453,7 +20584,7 @@
         <v>74</v>
       </c>
       <c r="K6" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -20461,10 +20592,10 @@
         <v>497</v>
       </c>
       <c r="B7" s="75" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="C7" s="74" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="D7" s="68"/>
       <c r="E7" s="68"/>
@@ -20480,7 +20611,7 @@
         <v>25</v>
       </c>
       <c r="K7" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -20488,10 +20619,10 @@
         <v>500</v>
       </c>
       <c r="B8" s="75" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="C8" s="74" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="D8" s="68"/>
       <c r="E8" s="68"/>
@@ -20509,7 +20640,7 @@
         <v>74</v>
       </c>
       <c r="K8" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -20517,10 +20648,10 @@
         <v>503</v>
       </c>
       <c r="B9" s="79" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="C9" s="80" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="D9" s="81"/>
       <c r="E9" s="68"/>
@@ -20538,7 +20669,7 @@
         <v>74</v>
       </c>
       <c r="K9" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -20546,10 +20677,10 @@
         <v>506</v>
       </c>
       <c r="B10" s="74" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="C10" s="74" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="D10" s="68"/>
       <c r="E10" s="68"/>
@@ -20567,7 +20698,7 @@
         <v>25</v>
       </c>
       <c r="K10" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -20575,10 +20706,10 @@
         <v>514</v>
       </c>
       <c r="B11" s="79" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="C11" s="80" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="D11" s="81"/>
       <c r="E11" s="68"/>
@@ -20596,7 +20727,7 @@
         <v>74</v>
       </c>
       <c r="K11" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -20604,10 +20735,10 @@
         <v>517</v>
       </c>
       <c r="B12" s="79" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="C12" s="80" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="D12" s="81"/>
       <c r="E12" s="68"/>
@@ -20625,7 +20756,7 @@
         <v>74</v>
       </c>
       <c r="K12" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -20633,10 +20764,10 @@
         <v>520</v>
       </c>
       <c r="B13" s="75" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="C13" s="74" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="D13" s="68"/>
       <c r="E13" s="68"/>
@@ -20654,7 +20785,7 @@
         <v>25</v>
       </c>
       <c r="K13" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -20662,10 +20793,10 @@
         <v>523</v>
       </c>
       <c r="B14" s="79" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="C14" s="80" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="D14" s="81"/>
       <c r="E14" s="68"/>
@@ -20681,7 +20812,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -20689,10 +20820,10 @@
         <v>527</v>
       </c>
       <c r="B15" s="97" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="C15" s="80" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="D15" s="81"/>
       <c r="E15" s="68"/>
@@ -20710,7 +20841,7 @@
         <v>74</v>
       </c>
       <c r="K15" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
@@ -20718,10 +20849,10 @@
         <v>531</v>
       </c>
       <c r="B16" s="75" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="C16" s="74" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="D16" s="68"/>
       <c r="E16" s="68"/>
@@ -20737,7 +20868,7 @@
         <v>25</v>
       </c>
       <c r="K16" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
@@ -20745,10 +20876,10 @@
         <v>534</v>
       </c>
       <c r="B17" s="74" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="C17" s="74" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="D17" s="68"/>
       <c r="E17" s="68"/>
@@ -20768,7 +20899,7 @@
         <v>25</v>
       </c>
       <c r="K17" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="22.5" customHeight="1">
@@ -20776,10 +20907,10 @@
         <v>538</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="68"/>
@@ -20799,7 +20930,7 @@
         <v>74</v>
       </c>
       <c r="K18" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="22.5" customHeight="1">
@@ -20807,10 +20938,10 @@
         <v>541</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="11"/>
@@ -20830,7 +20961,7 @@
         <v>513</v>
       </c>
       <c r="K19" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="22.5" customHeight="1">
@@ -20838,10 +20969,10 @@
         <v>544</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="C20" s="74" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -20859,7 +20990,7 @@
         <v>25</v>
       </c>
       <c r="K20" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="22.5" customHeight="1">
@@ -20867,10 +20998,10 @@
         <v>547</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="C21" s="74" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -20885,10 +21016,10 @@
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="14" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="K21" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="22.5" customHeight="1">
@@ -20896,10 +21027,10 @@
         <v>552</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="C22" s="74" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="11"/>
@@ -20917,7 +21048,7 @@
         <v>551</v>
       </c>
       <c r="K22" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="22.5" customHeight="1">
@@ -20925,10 +21056,10 @@
         <v>555</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="C23" s="74" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="11"/>
@@ -20946,7 +21077,7 @@
         <v>551</v>
       </c>
       <c r="K23" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="22.5" customHeight="1">
@@ -20954,10 +21085,10 @@
         <v>558</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="C24" s="74" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -20975,7 +21106,7 @@
         <v>551</v>
       </c>
       <c r="K24" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="22.5" customHeight="1">
@@ -20983,10 +21114,10 @@
         <v>558</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="11"/>
@@ -21006,7 +21137,7 @@
         <v>513</v>
       </c>
       <c r="K25" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -21014,10 +21145,10 @@
         <v>558</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="11"/>
@@ -21037,7 +21168,7 @@
         <v>551</v>
       </c>
       <c r="K26" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="22.5" customHeight="1">
@@ -21045,10 +21176,10 @@
         <v>562</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -21066,7 +21197,7 @@
         <v>513</v>
       </c>
       <c r="K27" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="22.5" customHeight="1">
@@ -21074,10 +21205,10 @@
         <v>565</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -21095,7 +21226,7 @@
         <v>513</v>
       </c>
       <c r="K28" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="22.5" customHeight="1">
@@ -21104,7 +21235,7 @@
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="11"/>
@@ -21235,10 +21366,10 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="D2" s="99"/>
       <c r="E2" s="99" t="s">
@@ -21253,10 +21384,10 @@
       <c r="H2" s="65"/>
       <c r="I2" s="66"/>
       <c r="J2" s="63" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -21264,10 +21395,10 @@
         <v>451</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
@@ -21286,10 +21417,10 @@
         <v>0.8</v>
       </c>
       <c r="J3" s="52" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -21297,14 +21428,14 @@
         <v>454</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="F4" s="52" t="s">
         <v>449</v>
@@ -21315,10 +21446,10 @@
       <c r="H4" s="60"/>
       <c r="I4" s="55"/>
       <c r="J4" s="52" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -21326,10 +21457,10 @@
         <v>457</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
@@ -21351,7 +21482,7 @@
         <v>687</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -21359,10 +21490,10 @@
         <v>667</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
@@ -21380,7 +21511,7 @@
         <v>687</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -21388,10 +21519,10 @@
         <v>459</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
@@ -21406,10 +21537,10 @@
       <c r="H7" s="60"/>
       <c r="I7" s="55"/>
       <c r="J7" s="52" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -21417,10 +21548,10 @@
         <v>462</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
@@ -21438,7 +21569,7 @@
         <v>25</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -21446,14 +21577,14 @@
         <v>465</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="F9" s="52" t="s">
         <v>449</v>
@@ -21467,7 +21598,7 @@
         <v>658</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -21475,10 +21606,10 @@
         <v>468</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
@@ -21496,7 +21627,7 @@
         <v>658</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -21504,14 +21635,14 @@
         <v>471</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="F11" s="52" t="s">
         <v>32</v>
@@ -21525,7 +21656,7 @@
         <v>658</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -21533,17 +21664,17 @@
         <v>474</v>
       </c>
       <c r="B12" s="50" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G12" s="53"/>
       <c r="H12" s="60"/>
@@ -21552,7 +21683,7 @@
         <v>658</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -21560,10 +21691,10 @@
         <v>477</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
@@ -21585,7 +21716,7 @@
         <v>658</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -21593,10 +21724,10 @@
         <v>481</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10" t="s">
@@ -21613,10 +21744,10 @@
         <v>0.8</v>
       </c>
       <c r="J14" s="52" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -21624,10 +21755,10 @@
         <v>484</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10" t="s">
@@ -21647,10 +21778,10 @@
         <v>488</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -21670,7 +21801,7 @@
         <v>658</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
     </row>
   </sheetData>
@@ -21778,13 +21909,13 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="D2" s="61" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="E2" s="62"/>
       <c r="F2" s="63" t="s">
@@ -21800,10 +21931,10 @@
         <v>0.75</v>
       </c>
       <c r="J2" s="63" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K2" s="102" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -21811,10 +21942,10 @@
         <v>471</v>
       </c>
       <c r="B3" s="79" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="C3" s="80" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="D3" s="81"/>
       <c r="E3" s="81"/>
@@ -21830,7 +21961,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -22118,10 +22249,10 @@
         <v>474</v>
       </c>
       <c r="B14" s="105" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="C14" s="106" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="D14" s="107"/>
       <c r="E14" s="107"/>
@@ -22139,7 +22270,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="113" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -22429,10 +22560,10 @@
         <v>477</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="C25" s="116" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="D25" s="117"/>
       <c r="E25" s="117"/>
@@ -22450,7 +22581,7 @@
         <v>25</v>
       </c>
       <c r="K25" s="123" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -22748,10 +22879,10 @@
         <v>481</v>
       </c>
       <c r="B36" s="124" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="C36" s="125" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="D36" s="126"/>
       <c r="E36" s="126"/>
@@ -22767,7 +22898,7 @@
         <v>25</v>
       </c>
       <c r="K36" s="132" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="22.5" customHeight="1">
@@ -22899,7 +23030,7 @@
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="D42" s="17"/>
       <c r="E42" s="18"/>
@@ -22974,10 +23105,10 @@
         <v>484</v>
       </c>
       <c r="B46" s="105" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="C46" s="106" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="D46" s="107"/>
       <c r="E46" s="107"/>
@@ -22995,7 +23126,7 @@
         <v>74</v>
       </c>
       <c r="K46" s="113" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="22.5" customHeight="1">
@@ -23195,10 +23326,10 @@
         <v>488</v>
       </c>
       <c r="B57" s="133" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="C57" s="134" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="D57" s="135"/>
       <c r="E57" s="135"/>
@@ -23216,7 +23347,7 @@
         <v>25</v>
       </c>
       <c r="K57" s="141" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="22.5" customHeight="1">
@@ -23434,10 +23565,10 @@
         <v>491</v>
       </c>
       <c r="B68" s="105" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="C68" s="106" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="D68" s="107"/>
       <c r="E68" s="107"/>
@@ -23453,7 +23584,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="113" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="22.5" customHeight="1">
@@ -23669,10 +23800,10 @@
         <v>494</v>
       </c>
       <c r="B79" s="124" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="C79" s="125" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="D79" s="126"/>
       <c r="E79" s="126"/>
@@ -23687,10 +23818,10 @@
       </c>
       <c r="I79" s="130"/>
       <c r="J79" s="146" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K79" s="132" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="22.5" customHeight="1">
@@ -23740,10 +23871,10 @@
         <v>497</v>
       </c>
       <c r="B82" s="115" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="C82" s="116" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="D82" s="117"/>
       <c r="E82" s="117"/>
@@ -23761,7 +23892,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="123" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="22.5" customHeight="1">
@@ -23769,10 +23900,10 @@
         <v>500</v>
       </c>
       <c r="B83" s="124" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="C83" s="125" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="D83" s="126"/>
       <c r="E83" s="126"/>
@@ -23790,7 +23921,7 @@
         <v>74</v>
       </c>
       <c r="K83" s="132" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22.5" customHeight="1">
@@ -23798,13 +23929,13 @@
         <v>451</v>
       </c>
       <c r="B84" s="149" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="C84" s="149" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="D84" s="150" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E84" s="151"/>
       <c r="F84" s="152" t="s">
@@ -23823,7 +23954,7 @@
         <v>25</v>
       </c>
       <c r="K84" s="156" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="22.5" customHeight="1">
@@ -23831,10 +23962,10 @@
         <v>503</v>
       </c>
       <c r="B85" s="105" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="C85" s="106" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="D85" s="107"/>
       <c r="E85" s="107"/>
@@ -23852,7 +23983,7 @@
         <v>74</v>
       </c>
       <c r="K85" s="113" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="22.5" customHeight="1">
@@ -23860,10 +23991,10 @@
         <v>506</v>
       </c>
       <c r="B86" s="133" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
       <c r="C86" s="134" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="D86" s="135"/>
       <c r="E86" s="135"/>
@@ -23881,7 +24012,7 @@
         <v>74</v>
       </c>
       <c r="K86" s="141" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="22.5" customHeight="1">
@@ -23889,10 +24020,10 @@
         <v>510</v>
       </c>
       <c r="B87" s="106" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="C87" s="106" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="D87" s="107"/>
       <c r="E87" s="107"/>
@@ -23905,10 +24036,10 @@
       </c>
       <c r="I87" s="111"/>
       <c r="J87" s="158" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K87" s="113" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="22.5" customHeight="1">
@@ -23916,10 +24047,10 @@
         <v>514</v>
       </c>
       <c r="B88" s="133" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="C88" s="134" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="D88" s="135"/>
       <c r="E88" s="135"/>
@@ -23937,7 +24068,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="141" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="22.5" customHeight="1">
@@ -23945,10 +24076,10 @@
         <v>517</v>
       </c>
       <c r="B89" s="115" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="C89" s="116" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="D89" s="68"/>
       <c r="E89" s="68"/>
@@ -23966,7 +24097,7 @@
         <v>74</v>
       </c>
       <c r="K89" s="123" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="22.5" customHeight="1">
@@ -23974,10 +24105,10 @@
         <v>520</v>
       </c>
       <c r="B90" s="133" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="C90" s="134" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="D90" s="81"/>
       <c r="E90" s="81"/>
@@ -23993,7 +24124,7 @@
         <v>74</v>
       </c>
       <c r="K90" s="141" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="22.5" customHeight="1">
@@ -24001,10 +24132,10 @@
         <v>523</v>
       </c>
       <c r="B91" s="75" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="C91" s="74" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="D91" s="68"/>
       <c r="E91" s="68"/>
@@ -24020,7 +24151,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="123" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22.5" customHeight="1">
@@ -24028,10 +24159,10 @@
         <v>527</v>
       </c>
       <c r="B92" s="79" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="C92" s="80" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
       <c r="D92" s="81"/>
       <c r="E92" s="81"/>
@@ -24049,7 +24180,7 @@
         <v>74</v>
       </c>
       <c r="K92" s="141" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="22.5" customHeight="1">
@@ -24057,10 +24188,10 @@
         <v>531</v>
       </c>
       <c r="B93" s="75" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="C93" s="74" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="D93" s="68"/>
       <c r="E93" s="68"/>
@@ -24076,7 +24207,7 @@
         <v>74</v>
       </c>
       <c r="K93" s="123" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="22.5" customHeight="1">
@@ -24084,10 +24215,10 @@
         <v>534</v>
       </c>
       <c r="B94" s="79" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="C94" s="80" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="D94" s="81"/>
       <c r="E94" s="81"/>
@@ -24103,7 +24234,7 @@
         <v>74</v>
       </c>
       <c r="K94" s="141" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="22.5" customHeight="1">
@@ -24111,13 +24242,13 @@
         <v>454</v>
       </c>
       <c r="B95" s="102" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="C95" s="102" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="D95" s="61" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E95" s="62"/>
       <c r="F95" s="63" t="s">
@@ -24136,7 +24267,7 @@
         <v>16</v>
       </c>
       <c r="K95" s="156" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="22.5" customHeight="1">
@@ -24144,10 +24275,10 @@
         <v>538</v>
       </c>
       <c r="B96" s="75" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="C96" s="74" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="D96" s="68"/>
       <c r="E96" s="68"/>
@@ -24163,7 +24294,7 @@
         <v>74</v>
       </c>
       <c r="K96" s="123" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="22.5" customHeight="1">
@@ -24171,10 +24302,10 @@
         <v>541</v>
       </c>
       <c r="B97" s="79" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="C97" s="80" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="D97" s="81"/>
       <c r="E97" s="81"/>
@@ -24190,7 +24321,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="22.5" customHeight="1">
@@ -24198,10 +24329,10 @@
         <v>544</v>
       </c>
       <c r="B98" s="75" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="C98" s="74" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="D98" s="68"/>
       <c r="E98" s="68"/>
@@ -24219,7 +24350,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="22.5" customHeight="1">
@@ -24227,10 +24358,10 @@
         <v>547</v>
       </c>
       <c r="B99" s="79" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="C99" s="80" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="D99" s="81"/>
       <c r="E99" s="81"/>
@@ -24248,7 +24379,7 @@
         <v>74</v>
       </c>
       <c r="K99" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="22.5" customHeight="1">
@@ -24256,10 +24387,10 @@
         <v>552</v>
       </c>
       <c r="B100" s="75" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="C100" s="74" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="D100" s="68"/>
       <c r="E100" s="68"/>
@@ -24275,7 +24406,7 @@
         <v>74</v>
       </c>
       <c r="K100" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="22.5" customHeight="1">
@@ -24283,10 +24414,10 @@
         <v>555</v>
       </c>
       <c r="B101" s="79" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="C101" s="80" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="D101" s="81"/>
       <c r="E101" s="81"/>
@@ -24302,7 +24433,7 @@
         <v>74</v>
       </c>
       <c r="K101" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="22.5" customHeight="1">
@@ -24310,10 +24441,10 @@
         <v>558</v>
       </c>
       <c r="B102" s="75" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="C102" s="74" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
       <c r="D102" s="68"/>
       <c r="E102" s="68"/>
@@ -24329,7 +24460,7 @@
         <v>74</v>
       </c>
       <c r="K102" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="22.5" customHeight="1">
@@ -24337,10 +24468,10 @@
         <v>562</v>
       </c>
       <c r="B103" s="79" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="C103" s="80" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="D103" s="81"/>
       <c r="E103" s="81"/>
@@ -24356,7 +24487,7 @@
         <v>74</v>
       </c>
       <c r="K103" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="22.5" customHeight="1">
@@ -24364,10 +24495,10 @@
         <v>565</v>
       </c>
       <c r="B104" s="74" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="C104" s="74" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="D104" s="68"/>
       <c r="E104" s="68"/>
@@ -24385,7 +24516,7 @@
         <v>25</v>
       </c>
       <c r="K104" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="22.5" customHeight="1">
@@ -24393,10 +24524,10 @@
         <v>568</v>
       </c>
       <c r="B105" s="79" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="C105" s="80" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="D105" s="81"/>
       <c r="E105" s="81"/>
@@ -24414,7 +24545,7 @@
         <v>74</v>
       </c>
       <c r="K105" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="22.5" customHeight="1">
@@ -24422,10 +24553,10 @@
         <v>457</v>
       </c>
       <c r="B106" s="102" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="C106" s="102" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="D106" s="61" t="s">
         <v>540</v>
@@ -24444,10 +24575,10 @@
         <v>0.9</v>
       </c>
       <c r="J106" s="63" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="K106" s="102" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="22.5" customHeight="1">
@@ -24455,10 +24586,10 @@
         <v>571</v>
       </c>
       <c r="B107" s="75" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="C107" s="74" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="D107" s="68"/>
       <c r="E107" s="68"/>
@@ -24474,7 +24605,7 @@
         <v>25</v>
       </c>
       <c r="K107" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="22.5" customHeight="1">
@@ -24482,10 +24613,10 @@
         <v>574</v>
       </c>
       <c r="B108" s="79" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="C108" s="80" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="D108" s="81"/>
       <c r="E108" s="81"/>
@@ -24501,7 +24632,7 @@
         <v>74</v>
       </c>
       <c r="K108" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="22.5" customHeight="1">
@@ -24509,10 +24640,10 @@
         <v>576</v>
       </c>
       <c r="B109" s="75" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="C109" s="74" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="D109" s="68"/>
       <c r="E109" s="68"/>
@@ -24530,7 +24661,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="22.5" customHeight="1">
@@ -24538,10 +24669,10 @@
         <v>579</v>
       </c>
       <c r="B110" s="79" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="C110" s="80" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="D110" s="81"/>
       <c r="E110" s="81"/>
@@ -24557,7 +24688,7 @@
         <v>74</v>
       </c>
       <c r="K110" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="22.5" customHeight="1">
@@ -24565,10 +24696,10 @@
         <v>582</v>
       </c>
       <c r="B111" s="75" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="C111" s="74" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="D111" s="68"/>
       <c r="E111" s="68"/>
@@ -24584,7 +24715,7 @@
         <v>74</v>
       </c>
       <c r="K111" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="22.5" customHeight="1">
@@ -24592,10 +24723,10 @@
         <v>585</v>
       </c>
       <c r="B112" s="79" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="C112" s="80" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="D112" s="81"/>
       <c r="E112" s="81"/>
@@ -24611,7 +24742,7 @@
         <v>74</v>
       </c>
       <c r="K112" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="22.5" customHeight="1">
@@ -24619,10 +24750,10 @@
         <v>588</v>
       </c>
       <c r="B113" s="75" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="C113" s="74" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
       <c r="D113" s="68"/>
       <c r="E113" s="68"/>
@@ -24638,7 +24769,7 @@
         <v>74</v>
       </c>
       <c r="K113" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="22.5" customHeight="1">
@@ -24646,10 +24777,10 @@
         <v>591</v>
       </c>
       <c r="B114" s="79" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="C114" s="80" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="D114" s="81"/>
       <c r="E114" s="81"/>
@@ -24665,7 +24796,7 @@
         <v>74</v>
       </c>
       <c r="K114" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="22.5" customHeight="1">
@@ -24673,7 +24804,7 @@
         <v>594</v>
       </c>
       <c r="B115" s="75" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
       <c r="C115" s="74" t="s">
         <v>391</v>
@@ -24692,7 +24823,7 @@
         <v>74</v>
       </c>
       <c r="K115" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="22.5" customHeight="1">
@@ -24700,10 +24831,10 @@
         <v>597</v>
       </c>
       <c r="B116" s="79" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
       <c r="C116" s="80" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="D116" s="81"/>
       <c r="E116" s="81"/>
@@ -24719,7 +24850,7 @@
         <v>74</v>
       </c>
       <c r="K116" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="22.5" customHeight="1">
@@ -24727,17 +24858,17 @@
         <v>667</v>
       </c>
       <c r="B117" s="102" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
       <c r="C117" s="102" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="D117" s="61" t="s">
         <v>540</v>
       </c>
       <c r="E117" s="62"/>
       <c r="F117" s="63" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="G117" s="101">
         <v>45976</v>
@@ -24749,10 +24880,10 @@
         <v>0.85</v>
       </c>
       <c r="J117" s="63" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="K117" s="102" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="22.5" customHeight="1">
@@ -24760,10 +24891,10 @@
         <v>600</v>
       </c>
       <c r="B118" s="75" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
       <c r="C118" s="74" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="D118" s="68"/>
       <c r="E118" s="68"/>
@@ -24779,7 +24910,7 @@
         <v>74</v>
       </c>
       <c r="K118" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="22.5" customHeight="1">
@@ -24787,10 +24918,10 @@
         <v>603</v>
       </c>
       <c r="B119" s="79" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="C119" s="80" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="D119" s="81"/>
       <c r="E119" s="81"/>
@@ -24808,7 +24939,7 @@
         <v>74</v>
       </c>
       <c r="K119" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="22.5" customHeight="1">
@@ -24816,10 +24947,10 @@
         <v>606</v>
       </c>
       <c r="B120" s="75" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="C120" s="74" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
       <c r="D120" s="68"/>
       <c r="E120" s="68"/>
@@ -24837,7 +24968,7 @@
         <v>74</v>
       </c>
       <c r="K120" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="22.5" customHeight="1">
@@ -24845,10 +24976,10 @@
         <v>609</v>
       </c>
       <c r="B121" s="79" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
       <c r="C121" s="80" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
       <c r="D121" s="81"/>
       <c r="E121" s="81"/>
@@ -24864,7 +24995,7 @@
         <v>74</v>
       </c>
       <c r="K121" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="22.5" customHeight="1">
@@ -24872,10 +25003,10 @@
         <v>612</v>
       </c>
       <c r="B122" s="75" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
       <c r="C122" s="74" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
       <c r="D122" s="68"/>
       <c r="E122" s="68"/>
@@ -24891,7 +25022,7 @@
         <v>74</v>
       </c>
       <c r="K122" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="22.5" customHeight="1">
@@ -24899,10 +25030,10 @@
         <v>615</v>
       </c>
       <c r="B123" s="79" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="C123" s="80" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
       <c r="D123" s="81"/>
       <c r="E123" s="81"/>
@@ -24918,7 +25049,7 @@
         <v>74</v>
       </c>
       <c r="K123" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="22.5" customHeight="1">
@@ -24926,10 +25057,10 @@
         <v>618</v>
       </c>
       <c r="B124" s="75" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
       <c r="C124" s="74" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
       <c r="D124" s="68"/>
       <c r="E124" s="68"/>
@@ -24947,7 +25078,7 @@
         <v>25</v>
       </c>
       <c r="K124" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="22.5" customHeight="1">
@@ -24955,10 +25086,10 @@
         <v>621</v>
       </c>
       <c r="B125" s="79" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
       <c r="C125" s="80" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
       <c r="D125" s="81"/>
       <c r="E125" s="81"/>
@@ -24974,7 +25105,7 @@
         <v>25</v>
       </c>
       <c r="K125" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="22.5" customHeight="1">
@@ -24982,10 +25113,10 @@
         <v>624</v>
       </c>
       <c r="B126" s="75" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="C126" s="74" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="D126" s="68"/>
       <c r="E126" s="68"/>
@@ -25001,7 +25132,7 @@
         <v>74</v>
       </c>
       <c r="K126" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="22.5" customHeight="1">
@@ -25009,10 +25140,10 @@
         <v>627</v>
       </c>
       <c r="B127" s="79" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="C127" s="80" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
       <c r="D127" s="81"/>
       <c r="E127" s="81"/>
@@ -25028,7 +25159,7 @@
         <v>74</v>
       </c>
       <c r="K127" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="22.5" customHeight="1">
@@ -25036,10 +25167,10 @@
         <v>459</v>
       </c>
       <c r="B128" s="102" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
       <c r="C128" s="102" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
       <c r="D128" s="61" t="s">
         <v>540</v>
@@ -25058,10 +25189,10 @@
         <v>0.5</v>
       </c>
       <c r="J128" s="63" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="K128" s="102" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="22.5" customHeight="1">
@@ -25069,10 +25200,10 @@
         <v>630</v>
       </c>
       <c r="B129" s="75" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="C129" s="74" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
       <c r="D129" s="68"/>
       <c r="E129" s="68"/>
@@ -25088,7 +25219,7 @@
         <v>74</v>
       </c>
       <c r="K129" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="22.5" customHeight="1">
@@ -25096,10 +25227,10 @@
         <v>633</v>
       </c>
       <c r="B130" s="79" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="C130" s="80" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="D130" s="81"/>
       <c r="E130" s="81"/>
@@ -25117,7 +25248,7 @@
         <v>74</v>
       </c>
       <c r="K130" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="22.5" customHeight="1">
@@ -25125,10 +25256,10 @@
         <v>636</v>
       </c>
       <c r="B131" s="75" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="C131" s="74" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
       <c r="D131" s="68"/>
       <c r="E131" s="68"/>
@@ -25144,7 +25275,7 @@
         <v>74</v>
       </c>
       <c r="K131" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="22.5" customHeight="1">
@@ -25152,10 +25283,10 @@
         <v>637</v>
       </c>
       <c r="B132" s="79" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="C132" s="80" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="D132" s="81"/>
       <c r="E132" s="81"/>
@@ -25173,7 +25304,7 @@
         <v>74</v>
       </c>
       <c r="K132" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="22.5" customHeight="1">
@@ -25181,10 +25312,10 @@
         <v>638</v>
       </c>
       <c r="B133" s="75" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="C133" s="74" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="D133" s="68"/>
       <c r="E133" s="68"/>
@@ -25202,7 +25333,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="22.5" customHeight="1">
@@ -25210,10 +25341,10 @@
         <v>639</v>
       </c>
       <c r="B134" s="79" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
       <c r="C134" s="80" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
       <c r="D134" s="81"/>
       <c r="E134" s="81"/>
@@ -25229,7 +25360,7 @@
         <v>25</v>
       </c>
       <c r="K134" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="22.5" customHeight="1">
@@ -25237,10 +25368,10 @@
         <v>640</v>
       </c>
       <c r="B135" s="75" t="s">
-        <v>1350</v>
+        <v>1358</v>
       </c>
       <c r="C135" s="74" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
       <c r="D135" s="68"/>
       <c r="E135" s="68"/>
@@ -25258,7 +25389,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="22.5" customHeight="1">
@@ -25266,10 +25397,10 @@
         <v>641</v>
       </c>
       <c r="B136" s="79" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="C136" s="80" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="D136" s="81"/>
       <c r="E136" s="81"/>
@@ -25285,7 +25416,7 @@
         <v>74</v>
       </c>
       <c r="K136" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="22.5" customHeight="1">
@@ -25293,10 +25424,10 @@
         <v>642</v>
       </c>
       <c r="B137" s="75" t="s">
-        <v>1352</v>
+        <v>1360</v>
       </c>
       <c r="C137" s="74" t="s">
-        <v>1353</v>
+        <v>1361</v>
       </c>
       <c r="D137" s="68"/>
       <c r="E137" s="68"/>
@@ -25312,7 +25443,7 @@
         <v>74</v>
       </c>
       <c r="K137" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="22.5" customHeight="1">
@@ -25320,10 +25451,10 @@
         <v>643</v>
       </c>
       <c r="B138" s="79" t="s">
-        <v>1354</v>
+        <v>1362</v>
       </c>
       <c r="C138" s="80" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="D138" s="81"/>
       <c r="E138" s="81"/>
@@ -25341,7 +25472,7 @@
         <v>74</v>
       </c>
       <c r="K138" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="22.5" customHeight="1">
@@ -25349,13 +25480,13 @@
         <v>462</v>
       </c>
       <c r="B139" s="102" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="C139" s="102" t="s">
-        <v>1356</v>
+        <v>1364</v>
       </c>
       <c r="D139" s="61" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E139" s="62"/>
       <c r="F139" s="63" t="s">
@@ -25374,7 +25505,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="102" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="22.5" customHeight="1">
@@ -25382,10 +25513,10 @@
         <v>644</v>
       </c>
       <c r="B140" s="79" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
       <c r="C140" s="80" t="s">
-        <v>1358</v>
+        <v>1366</v>
       </c>
       <c r="D140" s="81"/>
       <c r="E140" s="81"/>
@@ -25403,7 +25534,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="22.5" customHeight="1">
@@ -25411,10 +25542,10 @@
         <v>645</v>
       </c>
       <c r="B141" s="75" t="s">
-        <v>1359</v>
+        <v>1367</v>
       </c>
       <c r="C141" s="74" t="s">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="D141" s="68"/>
       <c r="E141" s="68"/>
@@ -25430,7 +25561,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="22.5" customHeight="1">
@@ -25438,10 +25569,10 @@
         <v>646</v>
       </c>
       <c r="B142" s="79" t="s">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="C142" s="80" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D142" s="81"/>
       <c r="E142" s="81"/>
@@ -25457,7 +25588,7 @@
         <v>74</v>
       </c>
       <c r="K142" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="22.5" customHeight="1">
@@ -25465,10 +25596,10 @@
         <v>647</v>
       </c>
       <c r="B143" s="75" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
       <c r="C143" s="74" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="D143" s="68"/>
       <c r="E143" s="68"/>
@@ -25484,7 +25615,7 @@
         <v>74</v>
       </c>
       <c r="K143" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="22.5" customHeight="1">
@@ -25492,10 +25623,10 @@
         <v>648</v>
       </c>
       <c r="B144" s="79" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="C144" s="80" t="s">
-        <v>1365</v>
+        <v>1373</v>
       </c>
       <c r="D144" s="81"/>
       <c r="E144" s="81"/>
@@ -25511,7 +25642,7 @@
         <v>74</v>
       </c>
       <c r="K144" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="22.5" customHeight="1">
@@ -25519,10 +25650,10 @@
         <v>649</v>
       </c>
       <c r="B145" s="75" t="s">
-        <v>1366</v>
+        <v>1374</v>
       </c>
       <c r="C145" s="74" t="s">
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="D145" s="68"/>
       <c r="E145" s="68"/>
@@ -25538,7 +25669,7 @@
         <v>25</v>
       </c>
       <c r="K145" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="22.5" customHeight="1">
@@ -25546,10 +25677,10 @@
         <v>650</v>
       </c>
       <c r="B146" s="79" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="C146" s="80" t="s">
-        <v>1369</v>
+        <v>1377</v>
       </c>
       <c r="D146" s="81"/>
       <c r="E146" s="81"/>
@@ -25565,7 +25696,7 @@
         <v>74</v>
       </c>
       <c r="K146" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="22.5" customHeight="1">
@@ -25573,10 +25704,10 @@
         <v>651</v>
       </c>
       <c r="B147" s="75" t="s">
-        <v>1370</v>
+        <v>1378</v>
       </c>
       <c r="C147" s="74" t="s">
-        <v>1371</v>
+        <v>1379</v>
       </c>
       <c r="D147" s="68"/>
       <c r="E147" s="68"/>
@@ -25592,7 +25723,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="22.5" customHeight="1">
@@ -25600,10 +25731,10 @@
         <v>652</v>
       </c>
       <c r="B148" s="79" t="s">
-        <v>1372</v>
+        <v>1380</v>
       </c>
       <c r="C148" s="80" t="s">
-        <v>1373</v>
+        <v>1381</v>
       </c>
       <c r="D148" s="81"/>
       <c r="E148" s="81"/>
@@ -25619,7 +25750,7 @@
         <v>74</v>
       </c>
       <c r="K148" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="22.5" customHeight="1">
@@ -25627,10 +25758,10 @@
         <v>653</v>
       </c>
       <c r="B149" s="75" t="s">
-        <v>1374</v>
+        <v>1382</v>
       </c>
       <c r="C149" s="74" t="s">
-        <v>1375</v>
+        <v>1383</v>
       </c>
       <c r="D149" s="68"/>
       <c r="E149" s="68"/>
@@ -25646,7 +25777,7 @@
         <v>74</v>
       </c>
       <c r="K149" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="22.5" customHeight="1">
@@ -25654,11 +25785,11 @@
         <v>465</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="164" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E150" s="165"/>
       <c r="F150" s="166"/>
@@ -25673,10 +25804,10 @@
         <v>654</v>
       </c>
       <c r="B151" s="80" t="s">
-        <v>1377</v>
+        <v>1385</v>
       </c>
       <c r="C151" s="80" t="s">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="D151" s="81"/>
       <c r="E151" s="81"/>
@@ -25689,21 +25820,21 @@
       </c>
       <c r="I151" s="85"/>
       <c r="J151" s="88" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="K151" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="22.5" customHeight="1">
       <c r="A152" s="8" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B152" s="75" t="s">
-        <v>1379</v>
+        <v>1387</v>
       </c>
       <c r="C152" s="74" t="s">
-        <v>1380</v>
+        <v>1388</v>
       </c>
       <c r="D152" s="68"/>
       <c r="E152" s="68"/>
@@ -25719,18 +25850,18 @@
         <v>25</v>
       </c>
       <c r="K152" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="22.5" customHeight="1">
       <c r="A153" s="8" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B153" s="79" t="s">
-        <v>1381</v>
+        <v>1389</v>
       </c>
       <c r="C153" s="80" t="s">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="D153" s="81"/>
       <c r="E153" s="81"/>
@@ -25746,18 +25877,18 @@
         <v>74</v>
       </c>
       <c r="K153" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="22.5" customHeight="1">
       <c r="A154" s="8" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B154" s="75" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="C154" s="74" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="D154" s="68"/>
       <c r="E154" s="68"/>
@@ -25773,18 +25904,18 @@
         <v>25</v>
       </c>
       <c r="K154" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="22.5" customHeight="1">
       <c r="A155" s="8" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B155" s="79" t="s">
-        <v>1383</v>
+        <v>1391</v>
       </c>
       <c r="C155" s="80" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="D155" s="81"/>
       <c r="E155" s="81"/>
@@ -25802,18 +25933,18 @@
         <v>25</v>
       </c>
       <c r="K155" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="22.5" customHeight="1">
       <c r="A156" s="8" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B156" s="74" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="C156" s="74" t="s">
-        <v>1386</v>
+        <v>1394</v>
       </c>
       <c r="D156" s="68"/>
       <c r="E156" s="68"/>
@@ -25829,18 +25960,18 @@
         <v>513</v>
       </c>
       <c r="K156" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="22.5" customHeight="1">
       <c r="A157" s="8" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B157" s="79" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="C157" s="80" t="s">
-        <v>1388</v>
+        <v>1396</v>
       </c>
       <c r="D157" s="81"/>
       <c r="E157" s="81"/>
@@ -25858,18 +25989,18 @@
         <v>74</v>
       </c>
       <c r="K157" s="80" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="22.5" customHeight="1">
       <c r="A158" s="8" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B158" s="74" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="C158" s="74" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="D158" s="68"/>
       <c r="E158" s="68"/>
@@ -25887,18 +26018,18 @@
         <v>25</v>
       </c>
       <c r="K158" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="22.5" customHeight="1">
       <c r="A159" s="8" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B159" s="75" t="s">
-        <v>1389</v>
+        <v>1397</v>
       </c>
       <c r="C159" s="74" t="s">
-        <v>1390</v>
+        <v>1398</v>
       </c>
       <c r="D159" s="10"/>
       <c r="E159" s="11"/>
@@ -25914,18 +26045,18 @@
         <v>25</v>
       </c>
       <c r="K159" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="22.5" customHeight="1">
       <c r="A160" s="8" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B160" s="75" t="s">
-        <v>1391</v>
+        <v>1399</v>
       </c>
       <c r="C160" s="74" t="s">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="D160" s="10"/>
       <c r="E160" s="11"/>
@@ -25941,7 +26072,7 @@
         <v>25</v>
       </c>
       <c r="K160" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="22.5" customHeight="1">
@@ -25951,7 +26082,7 @@
       <c r="B161" s="9"/>
       <c r="C161" s="5"/>
       <c r="D161" s="61" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E161" s="165"/>
       <c r="F161" s="100"/>
@@ -25963,13 +26094,13 @@
     </row>
     <row r="162" spans="1:11" ht="22.5" customHeight="1">
       <c r="A162" s="8" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>1393</v>
+        <v>1401</v>
       </c>
       <c r="D162" s="10"/>
       <c r="E162" s="11"/>
@@ -25987,18 +26118,18 @@
         <v>74</v>
       </c>
       <c r="K162" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="22.5" customHeight="1">
       <c r="A163" s="8" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="D163" s="10"/>
       <c r="E163" s="11"/>
@@ -26016,18 +26147,18 @@
         <v>25</v>
       </c>
       <c r="K163" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="22.5" customHeight="1">
       <c r="A164" s="8" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="D164" s="10"/>
       <c r="E164" s="11"/>
@@ -26042,21 +26173,21 @@
       </c>
       <c r="I164" s="13"/>
       <c r="J164" s="14" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="K164" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="22.5" customHeight="1">
       <c r="A165" s="8" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="D165" s="10"/>
       <c r="E165" s="11"/>
@@ -26074,7 +26205,7 @@
         <v>551</v>
       </c>
       <c r="K165" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="22.5" customHeight="1">
@@ -26111,10 +26242,10 @@
         <v>11</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="D167" s="10"/>
       <c r="E167" s="11"/>
@@ -26132,7 +26263,7 @@
         <v>551</v>
       </c>
       <c r="K167" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="22.5" customHeight="1">
@@ -26169,10 +26300,10 @@
         <v>18</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="D169" s="10"/>
       <c r="E169" s="11"/>
@@ -26190,7 +26321,7 @@
         <v>551</v>
       </c>
       <c r="K169" s="74" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="22.5" customHeight="1">
@@ -27742,10 +27873,10 @@
     <row r="248" spans="1:11" ht="22.5" customHeight="1">
       <c r="A248" s="46"/>
       <c r="B248" s="9" t="s">
-        <v>1394</v>
+        <v>1402</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>1395</v>
+        <v>1403</v>
       </c>
       <c r="D248" s="10"/>
       <c r="E248" s="48" t="s">

--- a/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
+++ b/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlando.carvajal.DESMEX\Desktop\ClaudeCode\Pipeline1\pipeline-web\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE80FB11-7C38-4D02-8E4D-7E7614A5B598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C47B8120-0DB9-4D28-84F8-D6A16FA8F8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Copia seguridad 27-01-2026" sheetId="9" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$L$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$L$206</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Copia seguridad 27-01-2026'!$A$1:$K$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Daniela Lara'!$A$1:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Josué Morales'!$A$1:$K$148</definedName>
@@ -50,11 +50,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={40381c86-9cae-4e66-824a-2c6e73c456bf}</author>
-    <author>tc={66a576bc-44b9-4f3d-a3c4-84053b265c54}</author>
+    <author>tc={42a397a7-ff4f-4940-ba5e-aafcf05f7117}</author>
+    <author>tc={10ae3357-a4da-46ce-9112-d132a03a00ab}</author>
   </authors>
   <commentList>
-    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{40381C86-9CAE-4E66-824A-2C6E73C456BF}">
+    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{42A397A7-FF4F-4940-BA5E-AAFCF05F7117}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -62,7 +62,7 @@
     ya lo tiene en seguimiento Josué</t>
       </text>
     </comment>
-    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{66A576BC-44B9-4F3D-A3C4-84053B265C54}">
+    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{10AE3357-A4DA-46CE-9112-D132A03A00AB}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4702" uniqueCount="1434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4728" uniqueCount="1444">
   <si>
     <t>ID de Prospecto</t>
   </si>
@@ -2291,6 +2291,21 @@
     <t>GAFF Internacional</t>
   </si>
   <si>
+    <t>Jorge Hernández</t>
+  </si>
+  <si>
+    <t>Solar Joms</t>
+  </si>
+  <si>
+    <t>Componentes</t>
+  </si>
+  <si>
+    <t>Jorge Martínez</t>
+  </si>
+  <si>
+    <t>Gasosur</t>
+  </si>
+  <si>
     <t>PSP81</t>
   </si>
   <si>
@@ -3521,9 +3536,6 @@
     <t>Mazatlán y Centro</t>
   </si>
   <si>
-    <t>Componentes</t>
-  </si>
-  <si>
     <t>Sr. Cástulo Bojórquez</t>
   </si>
   <si>
@@ -3681,6 +3693,24 @@
   </si>
   <si>
     <t>Coca-Cola Planta</t>
+  </si>
+  <si>
+    <t>Ing. Ramiro Bonilla</t>
+  </si>
+  <si>
+    <t>Betone</t>
+  </si>
+  <si>
+    <t>Alberto Nava</t>
+  </si>
+  <si>
+    <t>Casa LEY</t>
+  </si>
+  <si>
+    <t>Arq. Salvador Martí Pozos</t>
+  </si>
+  <si>
+    <t>Proyectos varios</t>
   </si>
   <si>
     <r>
@@ -5658,7 +5688,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Anónimo" id="{0156BE3D-9F93-4E40-AE82-B4E60A322BF8}" userId="" providerId="google-sheets"/>
+  <person displayName="Anónimo" id="{0610D5FF-B13C-4B87-BA08-09B6E665D0BD}" userId="" providerId="google-sheets"/>
 </personList>
 </file>
 
@@ -5724,8 +5754,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:L203">
-  <autoFilter ref="A1:L203" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:L206">
+  <autoFilter ref="A1:L206" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID de Prospecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Nombre del Prospecto"/>
@@ -6002,10 +6032,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{0156BE3D-9F93-4E40-AE82-B4E60A322BF8}" id="{40381C86-9CAE-4E66-824A-2C6E73C456BF}" done="1">
+  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{0610D5FF-B13C-4B87-BA08-09B6E665D0BD}" id="{42A397A7-FF4F-4940-BA5E-AAFCF05F7117}" done="1">
     <text>ya lo tiene en seguimiento Josué</text>
   </threadedComment>
-  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{0156BE3D-9F93-4E40-AE82-B4E60A322BF8}" id="{66A576BC-44B9-4F3D-A3C4-84053B265C54}" done="1">
+  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{0610D5FF-B13C-4B87-BA08-09B6E665D0BD}" id="{10AE3357-A4DA-46CE-9112-D132A03A00AB}" done="1">
     <text>Ya tienen contrato con Ammper</text>
   </threadedComment>
 </ThreadedComments>
@@ -12958,15 +12988,33 @@
       <c r="A33" s="46" t="s">
         <v>544</v>
       </c>
-      <c r="B33" s="51"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="53"/>
+      <c r="B33" s="51" t="s">
+        <v>736</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>737</v>
+      </c>
+      <c r="D33" s="49" t="s">
+        <v>561</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="F33" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="54">
+        <v>46148</v>
+      </c>
+      <c r="H33" s="55">
+        <v>719200</v>
+      </c>
+      <c r="I33" s="56">
+        <v>0.9</v>
+      </c>
+      <c r="J33" s="53" t="s">
+        <v>74</v>
+      </c>
       <c r="K33" s="46" t="s">
         <v>660</v>
       </c>
@@ -12976,15 +13024,33 @@
       <c r="A34" s="46" t="s">
         <v>547</v>
       </c>
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="55"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="53"/>
+      <c r="B34" s="51" t="s">
+        <v>739</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>740</v>
+      </c>
+      <c r="D34" s="49" t="s">
+        <v>540</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>667</v>
+      </c>
+      <c r="G34" s="54">
+        <v>46148</v>
+      </c>
+      <c r="H34" s="55">
+        <v>0</v>
+      </c>
+      <c r="I34" s="56">
+        <v>0.1</v>
+      </c>
+      <c r="J34" s="53" t="s">
+        <v>74</v>
+      </c>
       <c r="K34" s="46" t="s">
         <v>660</v>
       </c>
@@ -13856,7 +13922,7 @@
     </row>
     <row r="83" spans="1:12" ht="22.5" customHeight="1">
       <c r="A83" s="46" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="B83" s="51"/>
       <c r="C83" s="51"/>
@@ -13874,7 +13940,7 @@
     </row>
     <row r="84" spans="1:12" ht="22.5" customHeight="1">
       <c r="A84" s="46" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B84" s="51"/>
       <c r="C84" s="51"/>
@@ -13892,7 +13958,7 @@
     </row>
     <row r="85" spans="1:12" ht="22.5" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B85" s="51"/>
       <c r="C85" s="51"/>
@@ -13910,7 +13976,7 @@
     </row>
     <row r="86" spans="1:12" ht="22.5" customHeight="1">
       <c r="A86" s="46" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="B86" s="51"/>
       <c r="C86" s="51"/>
@@ -13928,7 +13994,7 @@
     </row>
     <row r="87" spans="1:12" ht="22.5" customHeight="1">
       <c r="A87" s="46" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="B87" s="51"/>
       <c r="C87" s="51"/>
@@ -13946,7 +14012,7 @@
     </row>
     <row r="88" spans="1:12" ht="22.5" customHeight="1">
       <c r="A88" s="46" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="B88" s="51"/>
       <c r="C88" s="51"/>
@@ -13964,7 +14030,7 @@
     </row>
     <row r="89" spans="1:12" ht="22.5" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="B89" s="51"/>
       <c r="C89" s="51"/>
@@ -13982,7 +14048,7 @@
     </row>
     <row r="90" spans="1:12" ht="22.5" customHeight="1">
       <c r="A90" s="46" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="B90" s="51"/>
       <c r="C90" s="51"/>
@@ -14000,7 +14066,7 @@
     </row>
     <row r="91" spans="1:12" ht="22.5" customHeight="1">
       <c r="A91" s="46" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="B91" s="51"/>
       <c r="C91" s="51"/>
@@ -14018,7 +14084,7 @@
     </row>
     <row r="92" spans="1:12" ht="22.5" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="B92" s="51"/>
       <c r="C92" s="51"/>
@@ -14036,7 +14102,7 @@
     </row>
     <row r="93" spans="1:12" ht="22.5" customHeight="1">
       <c r="A93" s="46" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="B93" s="51"/>
       <c r="C93" s="51"/>
@@ -14054,7 +14120,7 @@
     </row>
     <row r="94" spans="1:12" ht="22.5" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="B94" s="51"/>
       <c r="C94" s="51"/>
@@ -14072,7 +14138,7 @@
     </row>
     <row r="95" spans="1:12" ht="22.5" customHeight="1">
       <c r="A95" s="46" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B95" s="51"/>
       <c r="C95" s="51"/>
@@ -14090,7 +14156,7 @@
     </row>
     <row r="96" spans="1:12" ht="22.5" customHeight="1">
       <c r="A96" s="46" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="B96" s="51"/>
       <c r="C96" s="51"/>
@@ -14495,13 +14561,15 @@
     <hyperlink ref="D30" r:id="rId28" xr:uid="{00000000-0004-0000-0300-00001B000000}"/>
     <hyperlink ref="D31" r:id="rId29" xr:uid="{00000000-0004-0000-0300-00001C000000}"/>
     <hyperlink ref="D32" r:id="rId30" xr:uid="{00000000-0004-0000-0300-00001D000000}"/>
+    <hyperlink ref="D33" r:id="rId31" xr:uid="{00000000-0004-0000-0300-00001E000000}"/>
+    <hyperlink ref="D34" r:id="rId32" xr:uid="{00000000-0004-0000-0300-00001F000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
-  <legacyDrawing r:id="rId31"/>
+  <legacyDrawing r:id="rId33"/>
   <tableParts count="1">
-    <tablePart r:id="rId32"/>
+    <tablePart r:id="rId34"/>
   </tableParts>
 </worksheet>
 </file>
@@ -14512,7 +14580,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC203"/>
+  <dimension ref="A1:AC206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -14586,10 +14654,10 @@
     <row r="2" spans="1:29" ht="22.5" customHeight="1">
       <c r="A2" s="46"/>
       <c r="B2" s="46" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="D2" s="49" t="s">
         <v>561</v>
@@ -14607,17 +14675,17 @@
       <c r="I2" s="56"/>
       <c r="J2" s="53"/>
       <c r="K2" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L2" s="57"/>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
       <c r="A3" s="46"/>
       <c r="B3" s="46" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="D3" s="49" t="s">
         <v>561</v>
@@ -14635,23 +14703,23 @@
       <c r="I3" s="56"/>
       <c r="J3" s="53"/>
       <c r="K3" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L3" s="57"/>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
       <c r="A4" s="46"/>
       <c r="B4" s="46" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>733</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>119</v>
@@ -14665,17 +14733,17 @@
         <v>25</v>
       </c>
       <c r="K4" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L4" s="57"/>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
       <c r="A5" s="46"/>
       <c r="B5" s="46" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>733</v>
@@ -14692,20 +14760,20 @@
       <c r="H5" s="55"/>
       <c r="I5" s="56"/>
       <c r="J5" s="53" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="K5" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L5" s="57"/>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
       <c r="A6" s="46"/>
       <c r="B6" s="51" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="D6" s="49" t="s">
         <v>561</v>
@@ -14725,17 +14793,17 @@
         <v>25</v>
       </c>
       <c r="K6" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L6" s="57"/>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
       <c r="A7" s="46"/>
       <c r="B7" s="51" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="D7" s="49" t="s">
         <v>733</v>
@@ -14755,17 +14823,17 @@
         <v>16</v>
       </c>
       <c r="K7" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L7" s="57"/>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
       <c r="A8" s="46"/>
       <c r="B8" s="51" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="D8" s="49" t="s">
         <v>733</v>
@@ -14785,17 +14853,17 @@
         <v>16</v>
       </c>
       <c r="K8" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L8" s="57"/>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
       <c r="A9" s="46"/>
       <c r="B9" s="51" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="D9" s="49" t="s">
         <v>733</v>
@@ -14815,17 +14883,17 @@
         <v>16</v>
       </c>
       <c r="K9" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L9" s="57"/>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
       <c r="A10" s="46"/>
       <c r="B10" s="51" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="D10" s="49" t="s">
         <v>540</v>
@@ -14845,17 +14913,17 @@
         <v>74</v>
       </c>
       <c r="K10" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L10" s="57"/>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
       <c r="A11" s="46"/>
       <c r="B11" s="51" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>723</v>
@@ -14872,20 +14940,20 @@
       <c r="H11" s="55"/>
       <c r="I11" s="56"/>
       <c r="J11" s="53" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L11" s="57"/>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="51" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="D12" s="49" t="s">
         <v>540</v>
@@ -14905,17 +14973,17 @@
         <v>16</v>
       </c>
       <c r="K12" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L12" s="57"/>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="51" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="D13" s="49" t="s">
         <v>540</v>
@@ -14935,17 +15003,17 @@
         <v>688</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L13" s="57"/>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
       <c r="A14" s="46"/>
       <c r="B14" s="51" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="D14" s="49" t="s">
         <v>530</v>
@@ -14962,20 +15030,20 @@
       <c r="H14" s="55"/>
       <c r="I14" s="56"/>
       <c r="J14" s="53" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="K14" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L14" s="57"/>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
       <c r="A15" s="46"/>
       <c r="B15" s="51" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="D15" s="49" t="s">
         <v>561</v>
@@ -14995,17 +15063,17 @@
         <v>688</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L15" s="57"/>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
       <c r="A16" s="46"/>
       <c r="B16" s="51" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -15023,17 +15091,17 @@
         <v>688</v>
       </c>
       <c r="K16" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L16" s="57"/>
     </row>
     <row r="17" spans="1:12" ht="22.5" customHeight="1">
       <c r="A17" s="46"/>
       <c r="B17" s="51" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="D17" s="49" t="s">
         <v>733</v>
@@ -15053,17 +15121,17 @@
         <v>688</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L17" s="57"/>
     </row>
     <row r="18" spans="1:12" ht="22.5" customHeight="1">
       <c r="A18" s="46"/>
       <c r="B18" s="51" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="D18" s="49" t="s">
         <v>540</v>
@@ -15083,17 +15151,17 @@
         <v>16</v>
       </c>
       <c r="K18" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L18" s="57"/>
     </row>
     <row r="19" spans="1:12" ht="22.5" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="51" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="D19" s="49" t="s">
         <v>723</v>
@@ -15113,7 +15181,7 @@
         <v>74</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L19" s="57"/>
     </row>
@@ -15122,7 +15190,7 @@
         <v>175</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="C20" s="51" t="s">
         <v>483</v>
@@ -15145,7 +15213,7 @@
         <v>16</v>
       </c>
       <c r="K20" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L20" s="57"/>
     </row>
@@ -15154,7 +15222,7 @@
         <v>170</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="C21" s="51" t="s">
         <v>483</v>
@@ -15177,7 +15245,7 @@
         <v>16</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L21" s="57"/>
     </row>
@@ -15186,10 +15254,10 @@
         <v>172</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="D22" s="49" t="s">
         <v>561</v>
@@ -15209,7 +15277,7 @@
         <v>513</v>
       </c>
       <c r="K22" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L22" s="57"/>
     </row>
@@ -15218,16 +15286,16 @@
         <v>135</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="D23" s="49" t="s">
         <v>733</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="F23" s="53" t="s">
         <v>119</v>
@@ -15241,7 +15309,7 @@
         <v>688</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L23" s="57"/>
     </row>
@@ -15250,13 +15318,13 @@
         <v>139</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>448</v>
@@ -15273,7 +15341,7 @@
         <v>16</v>
       </c>
       <c r="K24" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L24" s="57"/>
     </row>
@@ -15282,13 +15350,13 @@
         <v>142</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>448</v>
@@ -15305,7 +15373,7 @@
         <v>74</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L25" s="57"/>
     </row>
@@ -15314,10 +15382,10 @@
         <v>144</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>733</v>
@@ -15337,7 +15405,7 @@
         <v>74</v>
       </c>
       <c r="K26" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L26" s="57"/>
     </row>
@@ -15346,13 +15414,13 @@
         <v>152</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>448</v>
@@ -15369,7 +15437,7 @@
         <v>74</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L27" s="57"/>
     </row>
@@ -15378,10 +15446,10 @@
         <v>155</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="D28" s="49" t="s">
         <v>733</v>
@@ -15401,25 +15469,25 @@
         <v>74</v>
       </c>
       <c r="K28" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L28" s="57"/>
     </row>
     <row r="29" spans="1:12" ht="22.5" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="D29" s="49" t="s">
         <v>733</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="F29" s="53" t="s">
         <v>119</v>
@@ -15433,7 +15501,7 @@
         <v>688</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L29" s="57"/>
     </row>
@@ -15442,10 +15510,10 @@
         <v>149</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="C30" s="51" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="D30" s="49" t="s">
         <v>561</v>
@@ -15469,7 +15537,7 @@
         <v>513</v>
       </c>
       <c r="K30" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L30" s="57"/>
     </row>
@@ -15478,10 +15546,10 @@
         <v>97</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="D31" s="49" t="s">
         <v>726</v>
@@ -15501,7 +15569,7 @@
         <v>25</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L31" s="57"/>
     </row>
@@ -15510,10 +15578,10 @@
         <v>99</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D32" s="49" t="s">
         <v>733</v>
@@ -15533,7 +15601,7 @@
         <v>74</v>
       </c>
       <c r="K32" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L32" s="57"/>
     </row>
@@ -15542,10 +15610,10 @@
         <v>103</v>
       </c>
       <c r="B33" s="46" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="C33" s="46" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="D33" s="49" t="s">
         <v>561</v>
@@ -15565,7 +15633,7 @@
         <v>688</v>
       </c>
       <c r="K33" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L33" s="57"/>
     </row>
@@ -15574,10 +15642,10 @@
         <v>129</v>
       </c>
       <c r="B34" s="51" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="C34" s="51" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="D34" s="49" t="s">
         <v>733</v>
@@ -15593,26 +15661,26 @@
       </c>
       <c r="H34" s="55"/>
       <c r="I34" s="60" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="J34" s="53" t="s">
         <v>688</v>
       </c>
       <c r="K34" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L34" s="57"/>
     </row>
     <row r="35" spans="1:12" ht="22.5" customHeight="1">
       <c r="A35" s="46"/>
       <c r="B35" s="51" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="C35" s="51" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>448</v>
@@ -15629,7 +15697,7 @@
         <v>688</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L35" s="57"/>
     </row>
@@ -15638,10 +15706,10 @@
         <v>68</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10" t="s">
@@ -15659,7 +15727,7 @@
         <v>74</v>
       </c>
       <c r="K36" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L36" s="57"/>
     </row>
@@ -15668,10 +15736,10 @@
         <v>71</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="C37" s="51" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="D37" s="49" t="s">
         <v>540</v>
@@ -15691,7 +15759,7 @@
         <v>688</v>
       </c>
       <c r="K37" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L37" s="57"/>
     </row>
@@ -15700,10 +15768,10 @@
         <v>78</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C38" s="51" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="D38" s="49" t="s">
         <v>733</v>
@@ -15723,7 +15791,7 @@
         <v>16</v>
       </c>
       <c r="K38" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L38" s="57"/>
     </row>
@@ -15732,16 +15800,16 @@
         <v>81</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="F39" s="53" t="s">
         <v>119</v>
@@ -15755,20 +15823,20 @@
         <v>16</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L39" s="57"/>
     </row>
     <row r="40" spans="1:12" ht="22.5" customHeight="1">
       <c r="A40" s="46"/>
       <c r="B40" s="51" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C40" s="51" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>448</v>
@@ -15785,7 +15853,7 @@
         <v>74</v>
       </c>
       <c r="K40" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L40" s="57"/>
     </row>
@@ -15794,10 +15862,10 @@
         <v>54</v>
       </c>
       <c r="B41" s="51" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C41" s="51" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="D41" s="49" t="s">
         <v>723</v>
@@ -15817,7 +15885,7 @@
         <v>25</v>
       </c>
       <c r="K41" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L41" s="57"/>
     </row>
@@ -15826,14 +15894,14 @@
         <v>60</v>
       </c>
       <c r="B42" s="46" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="F42" s="53" t="s">
         <v>119</v>
@@ -15847,7 +15915,7 @@
         <v>688</v>
       </c>
       <c r="K42" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L42" s="57"/>
     </row>
@@ -15856,10 +15924,10 @@
         <v>63</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="C43" s="51" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="D43" s="49" t="s">
         <v>723</v>
@@ -15879,7 +15947,7 @@
         <v>688</v>
       </c>
       <c r="K43" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L43" s="57"/>
     </row>
@@ -15888,13 +15956,13 @@
         <v>65</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="C44" s="51" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>448</v>
@@ -15911,7 +15979,7 @@
         <v>25</v>
       </c>
       <c r="K44" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L44" s="57"/>
     </row>
@@ -15920,13 +15988,13 @@
         <v>85</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="C45" s="51" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>448</v>
@@ -15939,25 +16007,25 @@
       </c>
       <c r="H45" s="55"/>
       <c r="I45" s="60" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="J45" s="53" t="s">
         <v>513</v>
       </c>
       <c r="K45" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L45" s="57"/>
     </row>
     <row r="46" spans="1:12" ht="22.5" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="D46" s="49" t="s">
         <v>540</v>
@@ -15977,19 +16045,19 @@
         <v>688</v>
       </c>
       <c r="K46" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L46" s="57"/>
     </row>
     <row r="47" spans="1:12" ht="22.5" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B47" s="51" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="D47" s="49" t="s">
         <v>526</v>
@@ -16009,19 +16077,19 @@
         <v>25</v>
       </c>
       <c r="K47" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L47" s="57"/>
     </row>
     <row r="48" spans="1:12" ht="22.5" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="B48" s="51" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C48" s="51" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="D48" s="49" t="s">
         <v>733</v>
@@ -16041,22 +16109,22 @@
         <v>74</v>
       </c>
       <c r="K48" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L48" s="57"/>
     </row>
     <row r="49" spans="1:12" ht="22.5" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>448</v>
@@ -16073,19 +16141,19 @@
         <v>74</v>
       </c>
       <c r="K49" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L49" s="57"/>
     </row>
     <row r="50" spans="1:12" ht="22.5" customHeight="1">
       <c r="A50" s="8" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="B50" s="51" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="C50" s="51" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="D50" s="49" t="s">
         <v>733</v>
@@ -16105,7 +16173,7 @@
         <v>74</v>
       </c>
       <c r="K50" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L50" s="57"/>
     </row>
@@ -16114,10 +16182,10 @@
         <v>11</v>
       </c>
       <c r="B51" s="51" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="C51" s="51" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="D51" s="49" t="s">
         <v>733</v>
@@ -16137,7 +16205,7 @@
         <v>688</v>
       </c>
       <c r="K51" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L51" s="57"/>
     </row>
@@ -16146,10 +16214,10 @@
         <v>18</v>
       </c>
       <c r="B52" s="51" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="C52" s="51" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="D52" s="49" t="s">
         <v>540</v>
@@ -16169,7 +16237,7 @@
         <v>25</v>
       </c>
       <c r="K52" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L52" s="57"/>
     </row>
@@ -16179,7 +16247,7 @@
       </c>
       <c r="B53" s="46"/>
       <c r="C53" s="46" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="D53" s="49" t="s">
         <v>723</v>
@@ -16199,7 +16267,7 @@
         <v>688</v>
       </c>
       <c r="K53" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L53" s="57"/>
     </row>
@@ -16208,10 +16276,10 @@
         <v>26</v>
       </c>
       <c r="B54" s="51" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="C54" s="51" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="D54" s="49" t="s">
         <v>733</v>
@@ -16231,7 +16299,7 @@
         <v>688</v>
       </c>
       <c r="K54" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L54" s="57"/>
     </row>
@@ -16240,10 +16308,10 @@
         <v>29</v>
       </c>
       <c r="B55" s="51" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="C55" s="51" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="D55" s="49" t="s">
         <v>733</v>
@@ -16263,7 +16331,7 @@
         <v>74</v>
       </c>
       <c r="K55" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L55" s="57"/>
     </row>
@@ -16272,7 +16340,7 @@
         <v>34</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C56" s="51" t="s">
         <v>712</v>
@@ -16295,7 +16363,7 @@
         <v>688</v>
       </c>
       <c r="K56" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L56" s="57"/>
     </row>
@@ -16304,13 +16372,13 @@
         <v>48</v>
       </c>
       <c r="B57" s="51" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="C57" s="51" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>448</v>
@@ -16324,10 +16392,10 @@
       <c r="H57" s="55"/>
       <c r="I57" s="56"/>
       <c r="J57" s="53" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="K57" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L57" s="57"/>
     </row>
@@ -16336,10 +16404,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="51" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C58" s="51" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="D58" s="49" t="s">
         <v>561</v>
@@ -16359,7 +16427,7 @@
         <v>513</v>
       </c>
       <c r="K58" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L58" s="57"/>
     </row>
@@ -16368,13 +16436,13 @@
         <v>638</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="C59" s="51" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>448</v>
@@ -16391,7 +16459,7 @@
         <v>74</v>
       </c>
       <c r="K59" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L59" s="57"/>
     </row>
@@ -16400,10 +16468,10 @@
         <v>639</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="D60" s="49" t="s">
         <v>540</v>
@@ -16420,10 +16488,10 @@
       <c r="H60" s="55"/>
       <c r="I60" s="56"/>
       <c r="J60" s="53" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="K60" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L60" s="57"/>
     </row>
@@ -16432,13 +16500,13 @@
         <v>640</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="C61" s="51" t="s">
+        <v>888</v>
+      </c>
+      <c r="D61" s="49" t="s">
         <v>883</v>
-      </c>
-      <c r="D61" s="49" t="s">
-        <v>878</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>448</v>
@@ -16455,7 +16523,7 @@
         <v>74</v>
       </c>
       <c r="K61" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L61" s="57"/>
     </row>
@@ -16464,13 +16532,13 @@
         <v>649</v>
       </c>
       <c r="B62" s="51" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="C62" s="51" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>448</v>
@@ -16487,17 +16555,17 @@
         <v>25</v>
       </c>
       <c r="K62" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L62" s="57"/>
     </row>
     <row r="63" spans="1:12" ht="22.5" customHeight="1">
       <c r="A63" s="46"/>
       <c r="B63" s="51" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="C63" s="51" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="D63" s="49" t="s">
         <v>526</v>
@@ -16517,7 +16585,7 @@
         <v>688</v>
       </c>
       <c r="K63" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L63" s="57"/>
     </row>
@@ -16526,13 +16594,13 @@
         <v>609</v>
       </c>
       <c r="B64" s="51" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="C64" s="51" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>448</v>
@@ -16549,7 +16617,7 @@
         <v>74</v>
       </c>
       <c r="K64" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L64" s="57"/>
     </row>
@@ -16558,13 +16626,13 @@
         <v>621</v>
       </c>
       <c r="B65" s="51" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="C65" s="51" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>448</v>
@@ -16581,7 +16649,7 @@
         <v>74</v>
       </c>
       <c r="K65" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L65" s="57"/>
     </row>
@@ -16590,10 +16658,10 @@
         <v>624</v>
       </c>
       <c r="B66" s="51" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C66" s="51" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="D66" s="49" t="s">
         <v>540</v>
@@ -16613,7 +16681,7 @@
         <v>74</v>
       </c>
       <c r="K66" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L66" s="57"/>
     </row>
@@ -16622,16 +16690,16 @@
         <v>597</v>
       </c>
       <c r="B67" s="51" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="F67" s="53" t="s">
         <v>119</v>
@@ -16645,7 +16713,7 @@
         <v>74</v>
       </c>
       <c r="K67" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L67" s="57"/>
     </row>
@@ -16654,16 +16722,16 @@
         <v>600</v>
       </c>
       <c r="B68" s="51" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="C68" s="51" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="F68" s="53" t="s">
         <v>119</v>
@@ -16677,7 +16745,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L68" s="57"/>
     </row>
@@ -16686,13 +16754,13 @@
         <v>603</v>
       </c>
       <c r="B69" s="51" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="C69" s="51" t="s">
+        <v>907</v>
+      </c>
+      <c r="D69" s="49" t="s">
         <v>902</v>
-      </c>
-      <c r="D69" s="49" t="s">
-        <v>897</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>448</v>
@@ -16709,7 +16777,7 @@
         <v>74</v>
       </c>
       <c r="K69" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L69" s="57"/>
     </row>
@@ -16718,13 +16786,13 @@
         <v>146</v>
       </c>
       <c r="B70" s="51" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="C70" s="51" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>448</v>
@@ -16741,7 +16809,7 @@
         <v>688</v>
       </c>
       <c r="K70" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L70" s="57"/>
     </row>
@@ -16750,10 +16818,10 @@
         <v>527</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="C71" s="46" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="D71" s="49" t="s">
         <v>561</v>
@@ -16773,7 +16841,7 @@
         <v>513</v>
       </c>
       <c r="K71" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L71" s="57"/>
     </row>
@@ -16782,16 +16850,16 @@
         <v>520</v>
       </c>
       <c r="B72" s="51" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="C72" s="51" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="F72" s="53" t="s">
         <v>119</v>
@@ -16805,7 +16873,7 @@
         <v>16</v>
       </c>
       <c r="K72" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L72" s="57"/>
     </row>
@@ -16814,10 +16882,10 @@
         <v>576</v>
       </c>
       <c r="B73" s="51" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="C73" s="51" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="D73" s="10"/>
       <c r="E73" s="10" t="s">
@@ -16835,7 +16903,7 @@
         <v>25</v>
       </c>
       <c r="K73" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L73" s="57"/>
     </row>
@@ -16844,10 +16912,10 @@
         <v>579</v>
       </c>
       <c r="B74" s="51" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="D74" s="49" t="s">
         <v>723</v>
@@ -16867,7 +16935,7 @@
         <v>25</v>
       </c>
       <c r="K74" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L74" s="57"/>
     </row>
@@ -16876,13 +16944,13 @@
         <v>650</v>
       </c>
       <c r="B75" s="51" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="C75" s="51" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>448</v>
@@ -16899,7 +16967,7 @@
         <v>25</v>
       </c>
       <c r="K75" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L75" s="57"/>
     </row>
@@ -16908,13 +16976,13 @@
         <v>503</v>
       </c>
       <c r="B76" s="46" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="C76" s="46" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="D76" s="49" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>448</v>
@@ -16933,7 +17001,7 @@
         <v>25</v>
       </c>
       <c r="K76" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L76" s="57"/>
     </row>
@@ -16942,16 +17010,16 @@
         <v>506</v>
       </c>
       <c r="B77" s="46" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="C77" s="46" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="D77" s="49" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="F77" s="53" t="s">
         <v>699</v>
@@ -16965,7 +17033,7 @@
         <v>25</v>
       </c>
       <c r="K77" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L77" s="57"/>
     </row>
@@ -16974,10 +17042,10 @@
         <v>488</v>
       </c>
       <c r="B78" s="51" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="C78" s="51" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="D78" s="10"/>
       <c r="E78" s="10" t="s">
@@ -16997,7 +17065,7 @@
         <v>25</v>
       </c>
       <c r="K78" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L78" s="57"/>
     </row>
@@ -17006,10 +17074,10 @@
         <v>494</v>
       </c>
       <c r="B79" s="46" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="C79" s="46" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="D79" s="49" t="s">
         <v>658</v>
@@ -17031,22 +17099,22 @@
         <v>25</v>
       </c>
       <c r="K79" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L79" s="57"/>
     </row>
     <row r="80" spans="1:12" ht="22.5" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="B80" s="51" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="C80" s="51" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="D80" s="49" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>448</v>
@@ -17063,7 +17131,7 @@
         <v>16</v>
       </c>
       <c r="K80" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L80" s="57"/>
     </row>
@@ -17073,7 +17141,7 @@
       </c>
       <c r="B81" s="46"/>
       <c r="C81" s="46" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="D81" s="49" t="s">
         <v>540</v>
@@ -17093,7 +17161,7 @@
         <v>551</v>
       </c>
       <c r="K81" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L81" s="57"/>
     </row>
@@ -17102,16 +17170,16 @@
         <v>582</v>
       </c>
       <c r="B82" s="51" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="C82" s="51" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="D82" s="49" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="F82" s="53" t="s">
         <v>119</v>
@@ -17125,7 +17193,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L82" s="57"/>
     </row>
@@ -17134,10 +17202,10 @@
         <v>113</v>
       </c>
       <c r="B83" s="51" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="C83" s="51" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="D83" s="49" t="s">
         <v>723</v>
@@ -17157,14 +17225,14 @@
         <v>688</v>
       </c>
       <c r="K83" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L83" s="57"/>
     </row>
     <row r="84" spans="1:12" ht="22.5" customHeight="1">
       <c r="A84" s="46"/>
       <c r="B84" s="46" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="C84" s="46" t="s">
         <v>410</v>
@@ -17185,7 +17253,7 @@
         <v>74</v>
       </c>
       <c r="K84" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L84" s="57"/>
     </row>
@@ -17194,13 +17262,13 @@
         <v>116</v>
       </c>
       <c r="B85" s="51" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="C85" s="51" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="D85" s="49" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>448</v>
@@ -17217,17 +17285,17 @@
         <v>688</v>
       </c>
       <c r="K85" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L85" s="57"/>
     </row>
     <row r="86" spans="1:12" ht="22.5" customHeight="1">
       <c r="A86" s="46"/>
       <c r="B86" s="51" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="C86" s="51" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="D86" s="10"/>
       <c r="E86" s="10" t="s">
@@ -17245,17 +17313,17 @@
         <v>25</v>
       </c>
       <c r="K86" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L86" s="57"/>
     </row>
     <row r="87" spans="1:12" ht="22.5" customHeight="1">
       <c r="A87" s="46"/>
       <c r="B87" s="51" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="C87" s="51" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="D87" s="49" t="s">
         <v>678</v>
@@ -17272,23 +17340,23 @@
       <c r="H87" s="55"/>
       <c r="I87" s="56"/>
       <c r="J87" s="53" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="K87" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L87" s="57"/>
     </row>
     <row r="88" spans="1:12" ht="22.5" customHeight="1">
       <c r="A88" s="46"/>
       <c r="B88" s="51" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>448</v>
@@ -17305,7 +17373,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L88" s="57"/>
     </row>
@@ -17314,13 +17382,13 @@
         <v>565</v>
       </c>
       <c r="B89" s="51" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="D89" s="49" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>448</v>
@@ -17337,7 +17405,7 @@
         <v>25</v>
       </c>
       <c r="K89" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L89" s="57"/>
     </row>
@@ -17346,10 +17414,10 @@
         <v>568</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="C90" s="51" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="D90" s="49" t="s">
         <v>723</v>
@@ -17369,7 +17437,7 @@
         <v>25</v>
       </c>
       <c r="K90" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L90" s="57"/>
     </row>
@@ -17378,10 +17446,10 @@
         <v>571</v>
       </c>
       <c r="B91" s="51" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="C91" s="51" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="D91" s="10"/>
       <c r="E91" s="10" t="s">
@@ -17399,7 +17467,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L91" s="57"/>
     </row>
@@ -17408,13 +17476,13 @@
         <v>574</v>
       </c>
       <c r="B92" s="51" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="C92" s="51" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="D92" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>448</v>
@@ -17431,7 +17499,7 @@
         <v>25</v>
       </c>
       <c r="K92" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L92" s="57"/>
     </row>
@@ -17440,10 +17508,10 @@
         <v>562</v>
       </c>
       <c r="B93" s="51" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="C93" s="51" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="D93" s="49" t="s">
         <v>540</v>
@@ -17463,7 +17531,7 @@
         <v>25</v>
       </c>
       <c r="K93" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L93" s="57"/>
     </row>
@@ -17472,10 +17540,10 @@
         <v>88</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="C94" s="51" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="D94" s="49" t="s">
         <v>540</v>
@@ -17495,7 +17563,7 @@
         <v>513</v>
       </c>
       <c r="K94" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L94" s="57"/>
     </row>
@@ -17504,16 +17572,16 @@
         <v>523</v>
       </c>
       <c r="B95" s="46" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="C95" s="46" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="D95" s="49" t="s">
         <v>723</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="F95" s="53" t="s">
         <v>449</v>
@@ -17527,20 +17595,20 @@
         <v>74</v>
       </c>
       <c r="K95" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L95" s="57"/>
     </row>
     <row r="96" spans="1:12" ht="22.5" customHeight="1">
       <c r="A96" s="46"/>
       <c r="B96" s="46" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="C96" s="46" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="D96" s="49" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>448</v>
@@ -17557,7 +17625,7 @@
         <v>25</v>
       </c>
       <c r="K96" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L96" s="57"/>
     </row>
@@ -17566,13 +17634,13 @@
         <v>643</v>
       </c>
       <c r="B97" s="51" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="C97" s="51" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="D97" s="49" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>448</v>
@@ -17589,7 +17657,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L97" s="57"/>
     </row>
@@ -17598,10 +17666,10 @@
         <v>644</v>
       </c>
       <c r="B98" s="51" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="C98" s="51" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="D98" s="49" t="s">
         <v>526</v>
@@ -17621,7 +17689,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L98" s="57"/>
     </row>
@@ -17630,13 +17698,13 @@
         <v>132</v>
       </c>
       <c r="B99" s="51" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="C99" s="51" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="D99" s="49" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>448</v>
@@ -17653,7 +17721,7 @@
         <v>513</v>
       </c>
       <c r="K99" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L99" s="57"/>
     </row>
@@ -17662,10 +17730,10 @@
         <v>606</v>
       </c>
       <c r="B100" s="51" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="C100" s="51" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="D100" s="49" t="s">
         <v>561</v>
@@ -17685,7 +17753,7 @@
         <v>25</v>
       </c>
       <c r="K100" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L100" s="57"/>
     </row>
@@ -17694,10 +17762,10 @@
         <v>538</v>
       </c>
       <c r="B101" s="51" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="C101" s="51" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="D101" s="49" t="s">
         <v>723</v>
@@ -17717,7 +17785,7 @@
         <v>25</v>
       </c>
       <c r="K101" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L101" s="57"/>
     </row>
@@ -17726,10 +17794,10 @@
         <v>645</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="D102" s="49" t="s">
         <v>526</v>
@@ -17749,7 +17817,7 @@
         <v>16</v>
       </c>
       <c r="K102" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L102" s="57"/>
     </row>
@@ -17758,10 +17826,10 @@
         <v>120</v>
       </c>
       <c r="B103" s="51" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="C103" s="51" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="D103" s="49" t="s">
         <v>540</v>
@@ -17781,7 +17849,7 @@
         <v>16</v>
       </c>
       <c r="K103" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L103" s="57"/>
     </row>
@@ -17790,13 +17858,13 @@
         <v>126</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="C104" s="51" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>448</v>
@@ -17813,7 +17881,7 @@
         <v>16</v>
       </c>
       <c r="K104" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L104" s="57"/>
     </row>
@@ -17822,7 +17890,7 @@
         <v>41</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="C105" s="51"/>
       <c r="D105" s="49" t="s">
@@ -17843,7 +17911,7 @@
         <v>16</v>
       </c>
       <c r="K105" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L105" s="57"/>
     </row>
@@ -17852,10 +17920,10 @@
         <v>646</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="C106" s="51" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="D106" s="49" t="s">
         <v>723</v>
@@ -17872,22 +17940,22 @@
       <c r="H106" s="55"/>
       <c r="I106" s="56"/>
       <c r="J106" s="53" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="K106" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L106" s="57"/>
     </row>
     <row r="107" spans="1:12" ht="22.5" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="B107" s="51" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="C107" s="51" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="D107" s="49" t="s">
         <v>723</v>
@@ -17907,17 +17975,17 @@
         <v>74</v>
       </c>
       <c r="K107" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L107" s="57"/>
     </row>
     <row r="108" spans="1:12" ht="22.5" customHeight="1">
       <c r="A108" s="46"/>
       <c r="B108" s="51" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="C108" s="51" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="D108" s="49" t="s">
         <v>733</v>
@@ -17937,7 +18005,7 @@
         <v>688</v>
       </c>
       <c r="K108" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L108" s="57"/>
     </row>
@@ -17946,13 +18014,13 @@
         <v>459</v>
       </c>
       <c r="B109" s="46" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="C109" s="46" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>448</v>
@@ -17973,7 +18041,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L109" s="57"/>
     </row>
@@ -17982,10 +18050,10 @@
         <v>462</v>
       </c>
       <c r="B110" s="46" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="C110" s="46" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="D110" s="49" t="s">
         <v>540</v>
@@ -18007,7 +18075,7 @@
         <v>25</v>
       </c>
       <c r="K110" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L110" s="57"/>
     </row>
@@ -18016,19 +18084,19 @@
         <v>552</v>
       </c>
       <c r="B111" s="46" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="C111" s="46" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="D111" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F111" s="53" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G111" s="54">
         <v>45952</v>
@@ -18039,7 +18107,7 @@
         <v>25</v>
       </c>
       <c r="K111" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L111" s="57"/>
     </row>
@@ -18048,13 +18116,13 @@
         <v>534</v>
       </c>
       <c r="B112" s="51" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="C112" s="51" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>448</v>
@@ -18071,7 +18139,7 @@
         <v>25</v>
       </c>
       <c r="K112" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L112" s="57"/>
     </row>
@@ -18080,10 +18148,10 @@
         <v>594</v>
       </c>
       <c r="B113" s="51" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="C113" s="51" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="D113" s="49" t="s">
         <v>540</v>
@@ -18103,7 +18171,7 @@
         <v>25</v>
       </c>
       <c r="K113" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L113" s="57"/>
     </row>
@@ -18112,10 +18180,10 @@
         <v>642</v>
       </c>
       <c r="B114" s="51" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="C114" s="51" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="D114" s="49" t="s">
         <v>723</v>
@@ -18135,7 +18203,7 @@
         <v>25</v>
       </c>
       <c r="K114" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L114" s="57"/>
     </row>
@@ -18144,16 +18212,16 @@
         <v>531</v>
       </c>
       <c r="B115" s="46" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="C115" s="46" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="D115" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="F115" s="53" t="s">
         <v>119</v>
@@ -18167,22 +18235,22 @@
         <v>25</v>
       </c>
       <c r="K115" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L115" s="57"/>
     </row>
     <row r="116" spans="1:12" ht="22.5" customHeight="1">
       <c r="A116" s="8" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="B116" s="51" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>448</v>
@@ -18196,10 +18264,10 @@
       <c r="H116" s="55"/>
       <c r="I116" s="56"/>
       <c r="J116" s="53" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="K116" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L116" s="57"/>
     </row>
@@ -18208,16 +18276,16 @@
         <v>94</v>
       </c>
       <c r="B117" s="51" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="C117" s="51" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="D117" s="49" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="F117" s="53" t="s">
         <v>119</v>
@@ -18231,7 +18299,7 @@
         <v>25</v>
       </c>
       <c r="K117" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L117" s="57"/>
     </row>
@@ -18240,19 +18308,19 @@
         <v>454</v>
       </c>
       <c r="B118" s="46" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="C118" s="46" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F118" s="53" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G118" s="54">
         <v>45940</v>
@@ -18265,7 +18333,7 @@
         <v>25</v>
       </c>
       <c r="K118" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L118" s="57"/>
     </row>
@@ -18274,13 +18342,13 @@
         <v>585</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="C119" s="51" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="D119" s="49" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>448</v>
@@ -18297,7 +18365,7 @@
         <v>25</v>
       </c>
       <c r="K119" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L119" s="57"/>
     </row>
@@ -18306,13 +18374,13 @@
         <v>591</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="C120" s="51" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>448</v>
@@ -18329,7 +18397,7 @@
         <v>25</v>
       </c>
       <c r="K120" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L120" s="57"/>
     </row>
@@ -18338,10 +18406,10 @@
         <v>91</v>
       </c>
       <c r="B121" s="51" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="C121" s="51" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="D121" s="49" t="s">
         <v>540</v>
@@ -18361,7 +18429,7 @@
         <v>16</v>
       </c>
       <c r="K121" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L121" s="57"/>
     </row>
@@ -18370,19 +18438,19 @@
         <v>457</v>
       </c>
       <c r="B122" s="46" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="C122" s="46" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F122" s="53" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G122" s="54">
         <v>45933</v>
@@ -18395,7 +18463,7 @@
         <v>25</v>
       </c>
       <c r="K122" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L122" s="57"/>
     </row>
@@ -18404,10 +18472,10 @@
         <v>652</v>
       </c>
       <c r="B123" s="51" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="D123" s="49" t="s">
         <v>733</v>
@@ -18427,7 +18495,7 @@
         <v>16</v>
       </c>
       <c r="K123" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L123" s="57"/>
     </row>
@@ -18436,10 +18504,10 @@
         <v>37</v>
       </c>
       <c r="B124" s="46" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="C124" s="46" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="D124" s="49" t="s">
         <v>540</v>
@@ -18456,22 +18524,22 @@
       <c r="H124" s="55"/>
       <c r="I124" s="56"/>
       <c r="J124" s="53" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="K124" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L124" s="57"/>
     </row>
     <row r="125" spans="1:12" ht="22.5" customHeight="1">
       <c r="A125" s="8" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B125" s="46" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="C125" s="46" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="D125" s="49" t="s">
         <v>733</v>
@@ -18491,19 +18559,19 @@
         <v>513</v>
       </c>
       <c r="K125" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L125" s="57"/>
     </row>
     <row r="126" spans="1:12" ht="22.5" customHeight="1">
       <c r="A126" s="8" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="B126" s="51" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="C126" s="51" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="D126" s="49" t="s">
         <v>540</v>
@@ -18523,19 +18591,19 @@
         <v>16</v>
       </c>
       <c r="K126" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L126" s="57"/>
     </row>
     <row r="127" spans="1:12" ht="22.5" customHeight="1">
       <c r="A127" s="8" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="B127" s="51" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="C127" s="51" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="D127" s="49" t="s">
         <v>733</v>
@@ -18555,7 +18623,7 @@
         <v>16</v>
       </c>
       <c r="K127" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L127" s="57"/>
     </row>
@@ -18564,10 +18632,10 @@
         <v>168</v>
       </c>
       <c r="B128" s="51" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="C128" s="51" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="D128" s="49" t="s">
         <v>733</v>
@@ -18587,22 +18655,22 @@
         <v>74</v>
       </c>
       <c r="K128" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L128" s="57"/>
     </row>
     <row r="129" spans="1:12" ht="22.5" customHeight="1">
       <c r="A129" s="8" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B129" s="51" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="C129" s="51" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>448</v>
@@ -18619,7 +18687,7 @@
         <v>25</v>
       </c>
       <c r="K129" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L129" s="57"/>
     </row>
@@ -18628,13 +18696,13 @@
         <v>641</v>
       </c>
       <c r="B130" s="51" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="E130" s="10" t="s">
         <v>448</v>
@@ -18651,7 +18719,7 @@
         <v>25</v>
       </c>
       <c r="K130" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L130" s="57"/>
     </row>
@@ -18660,10 +18728,10 @@
         <v>630</v>
       </c>
       <c r="B131" s="51" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="C131" s="51" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="D131" s="49" t="s">
         <v>718</v>
@@ -18683,7 +18751,7 @@
         <v>25</v>
       </c>
       <c r="K131" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L131" s="57"/>
     </row>
@@ -18692,13 +18760,13 @@
         <v>627</v>
       </c>
       <c r="B132" s="51" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="C132" s="51" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="D132" s="49" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>448</v>
@@ -18715,7 +18783,7 @@
         <v>513</v>
       </c>
       <c r="K132" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L132" s="57"/>
     </row>
@@ -18724,10 +18792,10 @@
         <v>555</v>
       </c>
       <c r="B133" s="51" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="C133" s="51" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="D133" s="49" t="s">
         <v>540</v>
@@ -18749,7 +18817,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L133" s="57"/>
     </row>
@@ -18758,13 +18826,13 @@
         <v>160</v>
       </c>
       <c r="B134" s="51" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="C134" s="51" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="D134" s="49" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>448</v>
@@ -18781,7 +18849,7 @@
         <v>16</v>
       </c>
       <c r="K134" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L134" s="57"/>
     </row>
@@ -18790,10 +18858,10 @@
         <v>451</v>
       </c>
       <c r="B135" s="46" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="C135" s="46" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="D135" s="49" t="s">
         <v>540</v>
@@ -18817,7 +18885,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L135" s="57"/>
     </row>
@@ -18826,13 +18894,13 @@
         <v>547</v>
       </c>
       <c r="B136" s="51" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="C136" s="51" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="D136" s="49" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>448</v>
@@ -18849,7 +18917,7 @@
         <v>25</v>
       </c>
       <c r="K136" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L136" s="57"/>
     </row>
@@ -18859,10 +18927,10 @@
       </c>
       <c r="B137" s="51"/>
       <c r="C137" s="51" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>448</v>
@@ -18879,7 +18947,7 @@
         <v>25</v>
       </c>
       <c r="K137" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L137" s="57"/>
     </row>
@@ -18888,13 +18956,13 @@
         <v>541</v>
       </c>
       <c r="B138" s="51" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="C138" s="51" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="D138" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>448</v>
@@ -18911,7 +18979,7 @@
         <v>138</v>
       </c>
       <c r="K138" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L138" s="57"/>
     </row>
@@ -18920,10 +18988,10 @@
         <v>477</v>
       </c>
       <c r="B139" s="46" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="C139" s="46" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="D139" s="49" t="s">
         <v>540</v>
@@ -18932,7 +19000,7 @@
         <v>448</v>
       </c>
       <c r="F139" s="53" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G139" s="54">
         <v>45822</v>
@@ -18945,7 +19013,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L139" s="57"/>
     </row>
@@ -18954,13 +19022,13 @@
         <v>654</v>
       </c>
       <c r="B140" s="51" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="C140" s="51" t="s">
         <v>410</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="E140" s="10" t="s">
         <v>448</v>
@@ -18977,7 +19045,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L140" s="57"/>
     </row>
@@ -18986,13 +19054,13 @@
         <v>491</v>
       </c>
       <c r="B141" s="46" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="C141" s="46" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="D141" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>448</v>
@@ -19013,7 +19081,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L141" s="57"/>
     </row>
@@ -19022,13 +19090,13 @@
         <v>471</v>
       </c>
       <c r="B142" s="46" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="C142" s="46" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="E142" s="10" t="s">
         <v>448</v>
@@ -19047,7 +19115,7 @@
         <v>25</v>
       </c>
       <c r="K142" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L142" s="57"/>
     </row>
@@ -19056,10 +19124,10 @@
         <v>668</v>
       </c>
       <c r="B143" s="46" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="C143" s="46" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="D143" s="10" t="s">
         <v>718</v>
@@ -19081,7 +19149,7 @@
         <v>25</v>
       </c>
       <c r="K143" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L143" s="57"/>
     </row>
@@ -19090,10 +19158,10 @@
         <v>123</v>
       </c>
       <c r="B144" s="51" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="D144" s="49" t="s">
         <v>540</v>
@@ -19113,7 +19181,7 @@
         <v>16</v>
       </c>
       <c r="K144" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L144" s="57"/>
     </row>
@@ -19122,10 +19190,10 @@
         <v>544</v>
       </c>
       <c r="B145" s="51" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="C145" s="51" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="D145" s="49" t="s">
         <v>540</v>
@@ -19145,17 +19213,17 @@
         <v>25</v>
       </c>
       <c r="K145" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L145" s="57"/>
     </row>
     <row r="146" spans="1:12" ht="22.5" customHeight="1">
       <c r="A146" s="46"/>
       <c r="B146" s="51" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="C146" s="51" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="D146" s="49" t="s">
         <v>733</v>
@@ -19164,7 +19232,7 @@
         <v>448</v>
       </c>
       <c r="F146" s="53" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G146" s="54">
         <v>45736</v>
@@ -19175,7 +19243,7 @@
         <v>25</v>
       </c>
       <c r="K146" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L146" s="57"/>
     </row>
@@ -19184,10 +19252,10 @@
         <v>474</v>
       </c>
       <c r="B147" s="46" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="C147" s="46" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="D147" s="49" t="s">
         <v>540</v>
@@ -19196,7 +19264,7 @@
         <v>448</v>
       </c>
       <c r="F147" s="53" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G147" s="54">
         <v>45700</v>
@@ -19209,7 +19277,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L147" s="57"/>
     </row>
@@ -19218,13 +19286,13 @@
         <v>636</v>
       </c>
       <c r="B148" s="51" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="C148" s="51" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="D148" s="49" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="E148" s="10" t="s">
         <v>448</v>
@@ -19241,7 +19309,7 @@
         <v>16</v>
       </c>
       <c r="K148" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L148" s="57"/>
     </row>
@@ -19250,13 +19318,13 @@
         <v>637</v>
       </c>
       <c r="B149" s="51" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="C149" s="51" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="D149" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>448</v>
@@ -19270,10 +19338,10 @@
       <c r="H149" s="55"/>
       <c r="I149" s="56"/>
       <c r="J149" s="53" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="K149" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L149" s="57"/>
     </row>
@@ -19282,13 +19350,13 @@
         <v>497</v>
       </c>
       <c r="B150" s="46" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="C150" s="46" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="D150" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>448</v>
@@ -19309,7 +19377,7 @@
         <v>25</v>
       </c>
       <c r="K150" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L150" s="57"/>
     </row>
@@ -19318,16 +19386,16 @@
         <v>500</v>
       </c>
       <c r="B151" s="46" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="C151" s="46" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="D151" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="F151" s="53" t="s">
         <v>24</v>
@@ -19343,7 +19411,7 @@
         <v>25</v>
       </c>
       <c r="K151" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L151" s="57"/>
     </row>
@@ -19352,13 +19420,13 @@
         <v>651</v>
       </c>
       <c r="B152" s="51" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="C152" s="51" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="D152" s="49" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>448</v>
@@ -19375,7 +19443,7 @@
         <v>25</v>
       </c>
       <c r="K152" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L152" s="57"/>
     </row>
@@ -19384,16 +19452,16 @@
         <v>588</v>
       </c>
       <c r="B153" s="51" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="C153" s="51" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="D153" s="49" t="s">
         <v>526</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="F153" s="53" t="s">
         <v>119</v>
@@ -19407,7 +19475,7 @@
         <v>25</v>
       </c>
       <c r="K153" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L153" s="57"/>
     </row>
@@ -19416,10 +19484,10 @@
         <v>481</v>
       </c>
       <c r="B154" s="46" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="C154" s="46" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="D154" s="49" t="s">
         <v>526</v>
@@ -19428,7 +19496,7 @@
         <v>448</v>
       </c>
       <c r="F154" s="53" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G154" s="54">
         <v>45519</v>
@@ -19441,7 +19509,7 @@
         <v>25</v>
       </c>
       <c r="K154" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L154" s="57"/>
     </row>
@@ -19450,13 +19518,13 @@
         <v>517</v>
       </c>
       <c r="B155" s="46" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="C155" s="46" t="s">
         <v>483</v>
       </c>
       <c r="D155" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>448</v>
@@ -19477,25 +19545,25 @@
         <v>138</v>
       </c>
       <c r="K155" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L155" s="57"/>
     </row>
     <row r="156" spans="1:12" ht="22.5" customHeight="1">
       <c r="A156" s="8" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="B156" s="51" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="C156" s="51" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="D156" s="49" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="E156" s="10" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="F156" s="53" t="s">
         <v>119</v>
@@ -19509,7 +19577,7 @@
         <v>25</v>
       </c>
       <c r="K156" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L156" s="57"/>
     </row>
@@ -19518,19 +19586,19 @@
         <v>514</v>
       </c>
       <c r="B157" s="46" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="C157" s="46" t="s">
         <v>483</v>
       </c>
       <c r="D157" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F157" s="53" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G157" s="54">
         <v>45513</v>
@@ -19543,7 +19611,7 @@
         <v>16</v>
       </c>
       <c r="K157" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L157" s="57"/>
     </row>
@@ -19552,13 +19620,13 @@
         <v>166</v>
       </c>
       <c r="B158" s="51" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="E158" s="10" t="s">
         <v>448</v>
@@ -19575,7 +19643,7 @@
         <v>74</v>
       </c>
       <c r="K158" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L158" s="57"/>
     </row>
@@ -19584,13 +19652,13 @@
         <v>618</v>
       </c>
       <c r="B159" s="51" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="C159" s="51" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="D159" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>448</v>
@@ -19607,7 +19675,7 @@
         <v>513</v>
       </c>
       <c r="K159" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L159" s="57"/>
     </row>
@@ -19616,10 +19684,10 @@
         <v>633</v>
       </c>
       <c r="B160" s="51" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="C160" s="51" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="D160" s="49" t="s">
         <v>526</v>
@@ -19639,7 +19707,7 @@
         <v>16</v>
       </c>
       <c r="K160" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L160" s="57"/>
     </row>
@@ -19648,10 +19716,10 @@
         <v>75</v>
       </c>
       <c r="B161" s="51" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="C161" s="51" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="D161" s="49" t="s">
         <v>540</v>
@@ -19671,7 +19739,7 @@
         <v>25</v>
       </c>
       <c r="K161" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L161" s="57"/>
     </row>
@@ -19680,19 +19748,19 @@
         <v>465</v>
       </c>
       <c r="B162" s="46" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="C162" s="46" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="E162" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F162" s="53" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G162" s="54">
         <v>45384</v>
@@ -19707,17 +19775,17 @@
         <v>138</v>
       </c>
       <c r="K162" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L162" s="57"/>
     </row>
     <row r="163" spans="1:12" ht="22.5" customHeight="1">
       <c r="A163" s="46"/>
       <c r="B163" s="51" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="C163" s="51" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="D163" s="49" t="s">
         <v>540</v>
@@ -19737,7 +19805,7 @@
         <v>16</v>
       </c>
       <c r="K163" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L163" s="57"/>
     </row>
@@ -19746,19 +19814,19 @@
         <v>484</v>
       </c>
       <c r="B164" s="46" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="C164" s="46" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="E164" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F164" s="53" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G164" s="54">
         <v>45203</v>
@@ -19773,7 +19841,7 @@
         <v>25</v>
       </c>
       <c r="K164" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L164" s="57"/>
     </row>
@@ -19782,13 +19850,13 @@
         <v>558</v>
       </c>
       <c r="B165" s="51" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>448</v>
@@ -19807,7 +19875,7 @@
         <v>25</v>
       </c>
       <c r="K165" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L165" s="57"/>
     </row>
@@ -19816,13 +19884,13 @@
         <v>615</v>
       </c>
       <c r="B166" s="51" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="C166" s="51" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="D166" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E166" s="10" t="s">
         <v>448</v>
@@ -19839,7 +19907,7 @@
         <v>513</v>
       </c>
       <c r="K166" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L166" s="57"/>
     </row>
@@ -19848,13 +19916,13 @@
         <v>648</v>
       </c>
       <c r="B167" s="51" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="C167" s="51" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>448</v>
@@ -19871,7 +19939,7 @@
         <v>25</v>
       </c>
       <c r="K167" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L167" s="57"/>
     </row>
@@ -19880,13 +19948,13 @@
         <v>612</v>
       </c>
       <c r="B168" s="51" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="C168" s="51" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="D168" s="49" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="E168" s="10" t="s">
         <v>448</v>
@@ -19903,7 +19971,7 @@
         <v>16</v>
       </c>
       <c r="K168" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L168" s="57"/>
     </row>
@@ -19912,19 +19980,19 @@
         <v>647</v>
       </c>
       <c r="B169" s="51" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="C169" s="51" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="D169" s="10" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F169" s="53" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="G169" s="54">
         <v>44725</v>
@@ -19935,7 +20003,7 @@
         <v>25</v>
       </c>
       <c r="K169" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L169" s="57"/>
     </row>
@@ -19944,10 +20012,10 @@
         <v>51</v>
       </c>
       <c r="B170" s="51" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="C170" s="51" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="D170" s="49" t="s">
         <v>733</v>
@@ -19967,7 +20035,7 @@
         <v>25</v>
       </c>
       <c r="K170" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L170" s="57"/>
     </row>
@@ -19976,10 +20044,10 @@
         <v>45</v>
       </c>
       <c r="B171" s="51" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="C171" s="51" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="D171" s="49" t="s">
         <v>733</v>
@@ -19999,7 +20067,7 @@
         <v>74</v>
       </c>
       <c r="K171" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L171" s="57"/>
     </row>
@@ -20008,13 +20076,13 @@
         <v>445</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="D172" s="62" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="E172" s="63"/>
       <c r="F172" s="64" t="s">
@@ -20028,10 +20096,10 @@
       </c>
       <c r="I172" s="67"/>
       <c r="J172" s="64" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K172" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L172" s="57"/>
     </row>
@@ -20040,13 +20108,13 @@
         <v>468</v>
       </c>
       <c r="B173" s="46" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="C173" s="46" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="D173" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>448</v>
@@ -20067,7 +20135,7 @@
         <v>138</v>
       </c>
       <c r="K173" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L173" s="57"/>
     </row>
@@ -20076,16 +20144,16 @@
         <v>653</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="C174" s="51" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="D174" s="49" t="s">
         <v>733</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="F174" s="53" t="s">
         <v>119</v>
@@ -20099,7 +20167,7 @@
         <v>25</v>
       </c>
       <c r="K174" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L174" s="57"/>
     </row>
@@ -20108,10 +20176,10 @@
         <v>158</v>
       </c>
       <c r="B175" s="51" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="C175" s="51" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="D175" s="49" t="s">
         <v>733</v>
@@ -20131,17 +20199,17 @@
         <v>16</v>
       </c>
       <c r="K175" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L175" s="57"/>
     </row>
     <row r="176" spans="1:12" ht="22.5" customHeight="1">
       <c r="A176" s="46"/>
       <c r="B176" s="51" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="C176" s="51" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="D176" s="49" t="s">
         <v>733</v>
@@ -20165,7 +20233,7 @@
         <v>138</v>
       </c>
       <c r="K176" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L176" s="57"/>
     </row>
@@ -20174,16 +20242,16 @@
         <v>510</v>
       </c>
       <c r="B177" s="51" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="C177" s="51" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="D177" s="49" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="F177" s="53" t="s">
         <v>24</v>
@@ -20197,7 +20265,7 @@
         <v>25</v>
       </c>
       <c r="K177" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L177" s="57"/>
     </row>
@@ -20206,16 +20274,16 @@
         <v>110</v>
       </c>
       <c r="B178" s="51" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="C178" s="51" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="D178" s="10" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="E178" s="10" t="s">
-        <v>1146</v>
+        <v>738</v>
       </c>
       <c r="F178" s="53" t="s">
         <v>119</v>
@@ -20227,20 +20295,20 @@
         <v>513</v>
       </c>
       <c r="K178" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L178" s="57"/>
     </row>
     <row r="179" spans="1:12" ht="22.5" customHeight="1">
       <c r="A179" s="46"/>
       <c r="B179" s="51" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="D179" s="10" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>448</v>
@@ -20261,20 +20329,20 @@
         <v>513</v>
       </c>
       <c r="K179" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L179" s="57"/>
     </row>
     <row r="180" spans="1:12" ht="22.5" customHeight="1">
       <c r="A180" s="46"/>
       <c r="B180" s="51" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="C180" s="51" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="D180" s="10" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="E180" s="10" t="s">
         <v>448</v>
@@ -20293,23 +20361,23 @@
         <v>25</v>
       </c>
       <c r="K180" s="51" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L180" s="57"/>
     </row>
     <row r="181" spans="1:12" ht="22.5" customHeight="1">
       <c r="A181" s="46"/>
       <c r="B181" s="46" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="C181" s="46" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="D181" s="10" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="F181" s="53" t="s">
         <v>119</v>
@@ -20319,23 +20387,23 @@
       <c r="I181" s="56"/>
       <c r="J181" s="53"/>
       <c r="K181" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L181" s="57"/>
     </row>
     <row r="182" spans="1:12" ht="22.5" customHeight="1">
       <c r="A182" s="46"/>
       <c r="B182" s="46" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C182" s="46" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D182" s="10" t="s">
         <v>1156</v>
       </c>
-      <c r="C182" s="46" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D182" s="10" t="s">
-        <v>1152</v>
-      </c>
       <c r="E182" s="10" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="F182" s="53" t="s">
         <v>106</v>
@@ -20353,17 +20421,17 @@
         <v>74</v>
       </c>
       <c r="K182" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L182" s="57"/>
     </row>
     <row r="183" spans="1:12" ht="22.5" customHeight="1">
       <c r="A183" s="46"/>
       <c r="B183" s="46" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="C183" s="46" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="D183" s="49" t="s">
         <v>561</v>
@@ -20387,17 +20455,17 @@
         <v>25</v>
       </c>
       <c r="K183" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L183" s="57"/>
     </row>
     <row r="184" spans="1:12" ht="22.5" customHeight="1">
       <c r="A184" s="46"/>
       <c r="B184" s="46" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="C184" s="46" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="D184" s="49" t="s">
         <v>561</v>
@@ -20421,17 +20489,17 @@
         <v>25</v>
       </c>
       <c r="K184" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L184" s="57"/>
     </row>
     <row r="185" spans="1:12" ht="22.5" customHeight="1">
       <c r="A185" s="46"/>
       <c r="B185" s="46" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="C185" s="46" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="D185" s="49" t="s">
         <v>678</v>
@@ -20455,20 +20523,20 @@
         <v>25</v>
       </c>
       <c r="K185" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L185" s="57"/>
     </row>
     <row r="186" spans="1:12" ht="22.5" customHeight="1">
       <c r="A186" s="46"/>
       <c r="B186" s="46" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="C186" s="46" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="D186" s="49" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="E186" s="10" t="s">
         <v>448</v>
@@ -20489,17 +20557,17 @@
         <v>25</v>
       </c>
       <c r="K186" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L186" s="57"/>
     </row>
     <row r="187" spans="1:12" ht="22.5" customHeight="1">
       <c r="A187" s="46"/>
       <c r="B187" s="46" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="C187" s="46" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="D187" s="49" t="s">
         <v>561</v>
@@ -20519,17 +20587,17 @@
         <v>25</v>
       </c>
       <c r="K187" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L187" s="57"/>
     </row>
     <row r="188" spans="1:12" ht="22.5" customHeight="1">
       <c r="A188" s="46"/>
       <c r="B188" s="1" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="C188" s="46" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="D188" s="49" t="s">
         <v>561</v>
@@ -20549,20 +20617,20 @@
         <v>513</v>
       </c>
       <c r="K188" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L188" s="57"/>
     </row>
     <row r="189" spans="1:12" ht="22.5" customHeight="1">
       <c r="A189" s="46"/>
       <c r="B189" s="9" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="C189" s="46" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="D189" s="49" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>448</v>
@@ -20579,20 +20647,20 @@
         <v>74</v>
       </c>
       <c r="K189" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L189" s="57"/>
     </row>
     <row r="190" spans="1:12" ht="22.5" customHeight="1">
       <c r="A190" s="46"/>
       <c r="B190" s="9" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="C190" s="46" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="D190" s="49" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="E190" s="10" t="s">
         <v>448</v>
@@ -20609,20 +20677,20 @@
         <v>25</v>
       </c>
       <c r="K190" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L190" s="57"/>
     </row>
     <row r="191" spans="1:12" ht="22.5" customHeight="1">
       <c r="A191" s="46"/>
       <c r="B191" s="9" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="C191" s="46" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="D191" s="49" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>448</v>
@@ -20636,23 +20704,23 @@
       <c r="H191" s="55"/>
       <c r="I191" s="56"/>
       <c r="J191" s="53" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="K191" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L191" s="57"/>
     </row>
     <row r="192" spans="1:12" ht="22.5" customHeight="1">
       <c r="A192" s="46"/>
       <c r="B192" s="9" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="C192" s="46" t="s">
         <v>410</v>
       </c>
       <c r="D192" s="49" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="E192" s="10" t="s">
         <v>448</v>
@@ -20669,17 +20737,17 @@
         <v>74</v>
       </c>
       <c r="K192" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L192" s="57"/>
     </row>
     <row r="193" spans="1:12" ht="22.5" customHeight="1">
       <c r="A193" s="46"/>
       <c r="B193" s="9" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="C193" s="46" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="D193" s="49" t="s">
         <v>733</v>
@@ -20699,17 +20767,17 @@
         <v>16</v>
       </c>
       <c r="K193" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L193" s="57"/>
     </row>
     <row r="194" spans="1:12" ht="22.5" customHeight="1">
       <c r="A194" s="46"/>
       <c r="B194" s="9" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="C194" s="46" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="D194" s="49" t="s">
         <v>733</v>
@@ -20729,17 +20797,17 @@
         <v>74</v>
       </c>
       <c r="K194" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L194" s="57"/>
     </row>
     <row r="195" spans="1:12" ht="22.5" customHeight="1">
       <c r="A195" s="46"/>
       <c r="B195" s="9" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="C195" s="46" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="D195" s="10"/>
       <c r="E195" s="10" t="s">
@@ -20757,17 +20825,17 @@
         <v>25</v>
       </c>
       <c r="K195" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L195" s="57"/>
     </row>
     <row r="196" spans="1:12" ht="22.5" customHeight="1">
       <c r="A196" s="46"/>
       <c r="B196" s="9" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="C196" s="46" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="D196" s="49" t="s">
         <v>718</v>
@@ -20784,23 +20852,23 @@
       <c r="H196" s="55"/>
       <c r="I196" s="56"/>
       <c r="J196" s="53" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="K196" s="46" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="L196" s="57"/>
     </row>
     <row r="197" spans="1:12" ht="22.5" customHeight="1">
       <c r="A197" s="46"/>
       <c r="B197" s="9" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="C197" s="51" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="D197" s="49" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>448</v>
@@ -20818,13 +20886,13 @@
     <row r="198" spans="1:12" ht="22.5" customHeight="1">
       <c r="A198" s="46"/>
       <c r="B198" s="9" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="C198" s="46" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="D198" s="49" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="E198" s="10" t="s">
         <v>448</v>
@@ -20842,13 +20910,13 @@
     <row r="199" spans="1:12" ht="22.5" customHeight="1">
       <c r="A199" s="46"/>
       <c r="B199" s="9" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="C199" s="46" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="D199" s="49" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>448</v>
@@ -20866,10 +20934,10 @@
     <row r="200" spans="1:12" ht="22.5" customHeight="1">
       <c r="A200" s="46"/>
       <c r="B200" s="9" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="C200" s="46" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="D200" s="10"/>
       <c r="E200" s="10" t="s">
@@ -20888,7 +20956,7 @@
     <row r="201" spans="1:12" ht="22.5" customHeight="1">
       <c r="A201" s="46"/>
       <c r="B201" s="9" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="C201" s="46"/>
       <c r="D201" s="10"/>
@@ -20908,16 +20976,16 @@
     <row r="202" spans="1:12" ht="22.5" customHeight="1">
       <c r="A202" s="46"/>
       <c r="B202" s="9" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="C202" s="46" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="D202" s="10" t="s">
         <v>537</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="F202" s="53" t="s">
         <v>119</v>
@@ -20932,13 +21000,13 @@
     <row r="203" spans="1:12" ht="22.5" customHeight="1">
       <c r="A203" s="46"/>
       <c r="B203" s="9" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="C203" s="46" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D203" s="49" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>448</v>
@@ -20953,21 +21021,91 @@
       <c r="K203" s="46"/>
       <c r="L203" s="46"/>
     </row>
+    <row r="204" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A204" s="46"/>
+      <c r="B204" s="9" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C204" s="46" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D204" s="49" t="s">
+        <v>537</v>
+      </c>
+      <c r="E204" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F204" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="G204" s="54"/>
+      <c r="H204" s="55"/>
+      <c r="I204" s="56"/>
+      <c r="J204" s="53"/>
+      <c r="K204" s="46"/>
+      <c r="L204" s="46"/>
+    </row>
+    <row r="205" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A205" s="46"/>
+      <c r="B205" s="9" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C205" s="46" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D205" s="10"/>
+      <c r="E205" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F205" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="G205" s="54"/>
+      <c r="H205" s="55"/>
+      <c r="I205" s="56"/>
+      <c r="J205" s="53"/>
+      <c r="K205" s="46"/>
+      <c r="L205" s="46"/>
+    </row>
+    <row r="206" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A206" s="46"/>
+      <c r="B206" s="9" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C206" s="46" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D206" s="49" t="s">
+        <v>733</v>
+      </c>
+      <c r="E206" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F206" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="G206" s="54"/>
+      <c r="H206" s="55"/>
+      <c r="I206" s="56"/>
+      <c r="J206" s="53"/>
+      <c r="K206" s="46"/>
+      <c r="L206" s="46"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="F2:F203" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F206" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"1. Prospección,2. Contacto Inicial,3. Calificación,4. Levantamiento de Requerimientos,5. Visita Técnica / Diagnóstico en Sitio,6. Diseño de Solución / Pre-Ingeniería,7. Estimación / Cotización,8. Propuesta Enviada,9. Aclaraciones / Ajustes de Propuesta,10"&amp;". Negociación,11. Aprobación Interna (Go/No-Go),12. Cierre de Venta (Contrato / OC),13. Kickoff / Inicio de Proyecto,14. Descartado / No Califica,15. En Pausa / Seguimiento Posterior"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G203" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G206" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G2))), AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I203" xr:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I206" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>AND(ISNUMBER(H2),(NOT(OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J203" xr:uid="{00000000-0002-0000-0400-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J206" xr:uid="{00000000-0002-0000-0400-000003000000}">
       <formula1>"Referido (Cliente),Referido (Proveedor/Subcontratista),Referido (Empleado/Interno),Cliente Recurrente (Recompra/Ampliación),Sitio Web (Formulario),Landing Page (Campaña),Chat Web / WhatsApp,SEO (Búsqueda Orgánica),Google Ads (Search),Remarketing (Display/"&amp;"Redes),LinkedIn (Orgánico),Email Outbound (Prospección),Llamada en Frío (Prospección),Visita en Frío (Prospección),Feria / Expo Industrial,Congreso / Cámara / Networking,Webinar / Evento Virtual,Licitación Pública,Licitación Privada (RFP/RFQ),Portal de Co"&amp;"mpras (Cliente),Alianza (Integrador/EPC/Constructor),Partner Tecnológico (Marca/Distribuidor),Directorio B2B / Clúster,Redes Sociales (Facebook/Instagram),YouTube / Contenido Técnico,PR / Medio Especializado,Reactivación de Base de Datos,Otros"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C203 E2:E203 K2:K203" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C206 E2:E206 K2:K206" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -21135,12 +21273,14 @@
     <hyperlink ref="D198" r:id="rId163" xr:uid="{00000000-0004-0000-0400-0000A2000000}"/>
     <hyperlink ref="D199" r:id="rId164" xr:uid="{00000000-0004-0000-0400-0000A3000000}"/>
     <hyperlink ref="D203" r:id="rId165" xr:uid="{00000000-0004-0000-0400-0000A4000000}"/>
+    <hyperlink ref="D204" r:id="rId166" xr:uid="{00000000-0004-0000-0400-0000A5000000}"/>
+    <hyperlink ref="D206" r:id="rId167" xr:uid="{00000000-0004-0000-0400-0000A6000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
   <tableParts count="1">
-    <tablePart r:id="rId166"/>
+    <tablePart r:id="rId168"/>
   </tableParts>
 </worksheet>
 </file>
@@ -21225,10 +21365,10 @@
         <v>481</v>
       </c>
       <c r="B2" s="69" t="s">
-        <v>1200</v>
+        <v>1210</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1201</v>
+        <v>1211</v>
       </c>
       <c r="D2" s="70"/>
       <c r="E2" s="70"/>
@@ -21248,7 +21388,7 @@
         <v>25</v>
       </c>
       <c r="K2" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="21" customHeight="1">
@@ -21256,10 +21396,10 @@
         <v>484</v>
       </c>
       <c r="B3" s="77" t="s">
-        <v>1203</v>
+        <v>1213</v>
       </c>
       <c r="C3" s="76" t="s">
-        <v>1204</v>
+        <v>1214</v>
       </c>
       <c r="D3" s="70"/>
       <c r="E3" s="70"/>
@@ -21277,7 +21417,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -21285,10 +21425,10 @@
         <v>488</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>1205</v>
+        <v>1215</v>
       </c>
       <c r="C4" s="82" t="s">
-        <v>1206</v>
+        <v>1216</v>
       </c>
       <c r="D4" s="83"/>
       <c r="E4" s="70"/>
@@ -21306,7 +21446,7 @@
         <v>25</v>
       </c>
       <c r="K4" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -21314,10 +21454,10 @@
         <v>491</v>
       </c>
       <c r="B5" s="81" t="s">
-        <v>1207</v>
+        <v>1217</v>
       </c>
       <c r="C5" s="82" t="s">
-        <v>1208</v>
+        <v>1218</v>
       </c>
       <c r="D5" s="83"/>
       <c r="E5" s="70"/>
@@ -21332,10 +21472,10 @@
       </c>
       <c r="I5" s="87"/>
       <c r="J5" s="90" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K5" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -21343,10 +21483,10 @@
         <v>494</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>1209</v>
+        <v>1219</v>
       </c>
       <c r="C6" s="82" t="s">
-        <v>1210</v>
+        <v>1220</v>
       </c>
       <c r="D6" s="83"/>
       <c r="E6" s="70"/>
@@ -21364,7 +21504,7 @@
         <v>74</v>
       </c>
       <c r="K6" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -21372,10 +21512,10 @@
         <v>497</v>
       </c>
       <c r="B7" s="77" t="s">
-        <v>1211</v>
+        <v>1221</v>
       </c>
       <c r="C7" s="76" t="s">
-        <v>1212</v>
+        <v>1222</v>
       </c>
       <c r="D7" s="70"/>
       <c r="E7" s="70"/>
@@ -21391,7 +21531,7 @@
         <v>25</v>
       </c>
       <c r="K7" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -21399,10 +21539,10 @@
         <v>500</v>
       </c>
       <c r="B8" s="77" t="s">
-        <v>1213</v>
+        <v>1223</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>1214</v>
+        <v>1224</v>
       </c>
       <c r="D8" s="70"/>
       <c r="E8" s="70"/>
@@ -21420,7 +21560,7 @@
         <v>74</v>
       </c>
       <c r="K8" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -21428,10 +21568,10 @@
         <v>503</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>1215</v>
+        <v>1225</v>
       </c>
       <c r="C9" s="82" t="s">
-        <v>1216</v>
+        <v>1226</v>
       </c>
       <c r="D9" s="83"/>
       <c r="E9" s="70"/>
@@ -21449,7 +21589,7 @@
         <v>74</v>
       </c>
       <c r="K9" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -21457,10 +21597,10 @@
         <v>506</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>1217</v>
+        <v>1227</v>
       </c>
       <c r="C10" s="76" t="s">
-        <v>1218</v>
+        <v>1228</v>
       </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
@@ -21478,7 +21618,7 @@
         <v>25</v>
       </c>
       <c r="K10" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -21486,10 +21626,10 @@
         <v>514</v>
       </c>
       <c r="B11" s="81" t="s">
-        <v>1219</v>
+        <v>1229</v>
       </c>
       <c r="C11" s="82" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="D11" s="83"/>
       <c r="E11" s="70"/>
@@ -21507,7 +21647,7 @@
         <v>74</v>
       </c>
       <c r="K11" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -21515,10 +21655,10 @@
         <v>517</v>
       </c>
       <c r="B12" s="81" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="C12" s="82" t="s">
-        <v>1222</v>
+        <v>1232</v>
       </c>
       <c r="D12" s="83"/>
       <c r="E12" s="70"/>
@@ -21536,7 +21676,7 @@
         <v>74</v>
       </c>
       <c r="K12" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -21544,10 +21684,10 @@
         <v>520</v>
       </c>
       <c r="B13" s="77" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>1224</v>
+        <v>1234</v>
       </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
@@ -21565,7 +21705,7 @@
         <v>25</v>
       </c>
       <c r="K13" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -21573,10 +21713,10 @@
         <v>523</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>1225</v>
+        <v>1235</v>
       </c>
       <c r="C14" s="82" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="D14" s="83"/>
       <c r="E14" s="70"/>
@@ -21592,7 +21732,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -21600,10 +21740,10 @@
         <v>527</v>
       </c>
       <c r="B15" s="99" t="s">
-        <v>1227</v>
+        <v>1237</v>
       </c>
       <c r="C15" s="82" t="s">
-        <v>1228</v>
+        <v>1238</v>
       </c>
       <c r="D15" s="83"/>
       <c r="E15" s="70"/>
@@ -21621,7 +21761,7 @@
         <v>74</v>
       </c>
       <c r="K15" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
@@ -21629,10 +21769,10 @@
         <v>531</v>
       </c>
       <c r="B16" s="77" t="s">
-        <v>1229</v>
+        <v>1239</v>
       </c>
       <c r="C16" s="76" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
@@ -21648,7 +21788,7 @@
         <v>25</v>
       </c>
       <c r="K16" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
@@ -21656,10 +21796,10 @@
         <v>534</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>1231</v>
+        <v>1241</v>
       </c>
       <c r="C17" s="76" t="s">
-        <v>1232</v>
+        <v>1242</v>
       </c>
       <c r="D17" s="70"/>
       <c r="E17" s="70"/>
@@ -21679,7 +21819,7 @@
         <v>25</v>
       </c>
       <c r="K17" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="22.5" customHeight="1">
@@ -21687,10 +21827,10 @@
         <v>538</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1233</v>
+        <v>1243</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1234</v>
+        <v>1244</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="70"/>
@@ -21710,7 +21850,7 @@
         <v>74</v>
       </c>
       <c r="K18" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="22.5" customHeight="1">
@@ -21718,10 +21858,10 @@
         <v>541</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1235</v>
+        <v>1245</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1236</v>
+        <v>1246</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="11"/>
@@ -21741,7 +21881,7 @@
         <v>513</v>
       </c>
       <c r="K19" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="22.5" customHeight="1">
@@ -21749,10 +21889,10 @@
         <v>544</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1237</v>
+        <v>1247</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>1238</v>
+        <v>1248</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -21770,7 +21910,7 @@
         <v>25</v>
       </c>
       <c r="K20" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="22.5" customHeight="1">
@@ -21778,10 +21918,10 @@
         <v>547</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1239</v>
+        <v>1249</v>
       </c>
       <c r="C21" s="76" t="s">
-        <v>1240</v>
+        <v>1250</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -21796,10 +21936,10 @@
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="14" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="K21" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="22.5" customHeight="1">
@@ -21807,10 +21947,10 @@
         <v>552</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1241</v>
+        <v>1251</v>
       </c>
       <c r="C22" s="76" t="s">
-        <v>1242</v>
+        <v>1252</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="11"/>
@@ -21828,7 +21968,7 @@
         <v>551</v>
       </c>
       <c r="K22" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="22.5" customHeight="1">
@@ -21836,10 +21976,10 @@
         <v>555</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1243</v>
+        <v>1253</v>
       </c>
       <c r="C23" s="76" t="s">
-        <v>1244</v>
+        <v>1254</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="11"/>
@@ -21857,7 +21997,7 @@
         <v>551</v>
       </c>
       <c r="K23" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="22.5" customHeight="1">
@@ -21865,10 +22005,10 @@
         <v>558</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1245</v>
+        <v>1255</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>1244</v>
+        <v>1254</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -21886,7 +22026,7 @@
         <v>551</v>
       </c>
       <c r="K24" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="22.5" customHeight="1">
@@ -21894,10 +22034,10 @@
         <v>558</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1246</v>
+        <v>1256</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="11"/>
@@ -21917,7 +22057,7 @@
         <v>513</v>
       </c>
       <c r="K25" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -21925,10 +22065,10 @@
         <v>558</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1248</v>
+        <v>1258</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>1249</v>
+        <v>1259</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="11"/>
@@ -21948,7 +22088,7 @@
         <v>551</v>
       </c>
       <c r="K26" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="22.5" customHeight="1">
@@ -21956,10 +22096,10 @@
         <v>562</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1250</v>
+        <v>1260</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1251</v>
+        <v>1261</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -21977,7 +22117,7 @@
         <v>513</v>
       </c>
       <c r="K27" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="22.5" customHeight="1">
@@ -21985,10 +22125,10 @@
         <v>565</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1252</v>
+        <v>1262</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>1251</v>
+        <v>1261</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -22006,7 +22146,7 @@
         <v>513</v>
       </c>
       <c r="K28" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="22.5" customHeight="1">
@@ -22014,10 +22154,10 @@
         <v>568</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1253</v>
+        <v>1263</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1254</v>
+        <v>1264</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="11"/>
@@ -22033,7 +22173,7 @@
       <c r="I29" s="45"/>
       <c r="J29" s="14"/>
       <c r="K29" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
   </sheetData>
@@ -22156,10 +22296,10 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1255</v>
+        <v>1265</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1256</v>
+        <v>1266</v>
       </c>
       <c r="D2" s="101"/>
       <c r="E2" s="101" t="s">
@@ -22174,10 +22314,10 @@
       <c r="H2" s="66"/>
       <c r="I2" s="67"/>
       <c r="J2" s="64" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -22185,10 +22325,10 @@
         <v>451</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>1258</v>
+        <v>1268</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>1259</v>
+        <v>1269</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
@@ -22207,10 +22347,10 @@
         <v>0.8</v>
       </c>
       <c r="J3" s="53" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -22218,14 +22358,14 @@
         <v>454</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>1260</v>
+        <v>1270</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>1261</v>
+        <v>1271</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>1262</v>
+        <v>1272</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>449</v>
@@ -22236,10 +22376,10 @@
       <c r="H4" s="61"/>
       <c r="I4" s="56"/>
       <c r="J4" s="53" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -22247,10 +22387,10 @@
         <v>457</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>1263</v>
+        <v>1273</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>1264</v>
+        <v>1274</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
@@ -22272,7 +22412,7 @@
         <v>688</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -22280,10 +22420,10 @@
         <v>668</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>1265</v>
+        <v>1275</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
@@ -22301,7 +22441,7 @@
         <v>688</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -22309,10 +22449,10 @@
         <v>459</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
@@ -22327,10 +22467,10 @@
       <c r="H7" s="61"/>
       <c r="I7" s="56"/>
       <c r="J7" s="53" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -22338,10 +22478,10 @@
         <v>462</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>1269</v>
+        <v>1279</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>1270</v>
+        <v>1280</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
@@ -22359,7 +22499,7 @@
         <v>25</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -22367,14 +22507,14 @@
         <v>465</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>1271</v>
+        <v>1281</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>1272</v>
+        <v>1282</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>1273</v>
+        <v>1283</v>
       </c>
       <c r="F9" s="53" t="s">
         <v>40</v>
@@ -22388,7 +22528,7 @@
         <v>659</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -22396,10 +22536,10 @@
         <v>468</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>1274</v>
+        <v>1284</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>1275</v>
+        <v>1285</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
@@ -22417,7 +22557,7 @@
         <v>659</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -22425,14 +22565,14 @@
         <v>471</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>1276</v>
+        <v>1286</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>1277</v>
+        <v>1287</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10" t="s">
-        <v>1273</v>
+        <v>1283</v>
       </c>
       <c r="F11" s="53" t="s">
         <v>32</v>
@@ -22446,7 +22586,7 @@
         <v>659</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -22454,17 +22594,17 @@
         <v>474</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>1278</v>
+        <v>1288</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>1279</v>
+        <v>1289</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G12" s="54"/>
       <c r="H12" s="61"/>
@@ -22473,7 +22613,7 @@
         <v>659</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -22481,10 +22621,10 @@
         <v>477</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>1280</v>
+        <v>1290</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>1281</v>
+        <v>1291</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
@@ -22506,7 +22646,7 @@
         <v>659</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -22514,10 +22654,10 @@
         <v>481</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>1280</v>
+        <v>1290</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>1282</v>
+        <v>1292</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10" t="s">
@@ -22534,10 +22674,10 @@
         <v>0.8</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -22545,10 +22685,10 @@
         <v>484</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>1283</v>
+        <v>1293</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>1284</v>
+        <v>1294</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10" t="s">
@@ -22568,10 +22708,10 @@
         <v>488</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>1285</v>
+        <v>1295</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>1286</v>
+        <v>1296</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -22591,7 +22731,7 @@
         <v>659</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
     </row>
   </sheetData>
@@ -22699,13 +22839,13 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="D2" s="62" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="E2" s="63"/>
       <c r="F2" s="64" t="s">
@@ -22721,10 +22861,10 @@
         <v>0.75</v>
       </c>
       <c r="J2" s="64" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K2" s="104" t="s">
-        <v>1287</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -22732,10 +22872,10 @@
         <v>471</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>1288</v>
+        <v>1298</v>
       </c>
       <c r="C3" s="82" t="s">
-        <v>1289</v>
+        <v>1299</v>
       </c>
       <c r="D3" s="83"/>
       <c r="E3" s="83"/>
@@ -22751,7 +22891,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -23039,10 +23179,10 @@
         <v>474</v>
       </c>
       <c r="B14" s="107" t="s">
-        <v>1290</v>
+        <v>1300</v>
       </c>
       <c r="C14" s="108" t="s">
-        <v>1291</v>
+        <v>1301</v>
       </c>
       <c r="D14" s="109"/>
       <c r="E14" s="109"/>
@@ -23060,7 +23200,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -23350,10 +23490,10 @@
         <v>477</v>
       </c>
       <c r="B25" s="117" t="s">
-        <v>1292</v>
+        <v>1302</v>
       </c>
       <c r="C25" s="118" t="s">
-        <v>1293</v>
+        <v>1303</v>
       </c>
       <c r="D25" s="119"/>
       <c r="E25" s="119"/>
@@ -23371,7 +23511,7 @@
         <v>25</v>
       </c>
       <c r="K25" s="125" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -23669,10 +23809,10 @@
         <v>481</v>
       </c>
       <c r="B36" s="126" t="s">
-        <v>1294</v>
+        <v>1304</v>
       </c>
       <c r="C36" s="127" t="s">
-        <v>1295</v>
+        <v>1305</v>
       </c>
       <c r="D36" s="128"/>
       <c r="E36" s="128"/>
@@ -23688,7 +23828,7 @@
         <v>25</v>
       </c>
       <c r="K36" s="134" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="22.5" customHeight="1">
@@ -23820,7 +23960,7 @@
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16" t="s">
-        <v>1296</v>
+        <v>1306</v>
       </c>
       <c r="D42" s="17"/>
       <c r="E42" s="18"/>
@@ -23895,10 +24035,10 @@
         <v>484</v>
       </c>
       <c r="B46" s="107" t="s">
-        <v>1203</v>
+        <v>1213</v>
       </c>
       <c r="C46" s="108" t="s">
-        <v>1204</v>
+        <v>1214</v>
       </c>
       <c r="D46" s="109"/>
       <c r="E46" s="109"/>
@@ -23916,7 +24056,7 @@
         <v>74</v>
       </c>
       <c r="K46" s="115" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="22.5" customHeight="1">
@@ -24116,10 +24256,10 @@
         <v>488</v>
       </c>
       <c r="B57" s="135" t="s">
-        <v>1205</v>
+        <v>1215</v>
       </c>
       <c r="C57" s="136" t="s">
-        <v>1206</v>
+        <v>1216</v>
       </c>
       <c r="D57" s="137"/>
       <c r="E57" s="137"/>
@@ -24137,7 +24277,7 @@
         <v>25</v>
       </c>
       <c r="K57" s="143" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="22.5" customHeight="1">
@@ -24355,10 +24495,10 @@
         <v>491</v>
       </c>
       <c r="B68" s="107" t="s">
-        <v>1297</v>
+        <v>1307</v>
       </c>
       <c r="C68" s="108" t="s">
-        <v>1298</v>
+        <v>1308</v>
       </c>
       <c r="D68" s="109"/>
       <c r="E68" s="109"/>
@@ -24374,7 +24514,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="115" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="22.5" customHeight="1">
@@ -24590,10 +24730,10 @@
         <v>494</v>
       </c>
       <c r="B79" s="126" t="s">
-        <v>1207</v>
+        <v>1217</v>
       </c>
       <c r="C79" s="127" t="s">
-        <v>1208</v>
+        <v>1218</v>
       </c>
       <c r="D79" s="128"/>
       <c r="E79" s="128"/>
@@ -24608,10 +24748,10 @@
       </c>
       <c r="I79" s="132"/>
       <c r="J79" s="148" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K79" s="134" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="22.5" customHeight="1">
@@ -24661,10 +24801,10 @@
         <v>497</v>
       </c>
       <c r="B82" s="117" t="s">
-        <v>1299</v>
+        <v>1309</v>
       </c>
       <c r="C82" s="118" t="s">
-        <v>1300</v>
+        <v>1310</v>
       </c>
       <c r="D82" s="119"/>
       <c r="E82" s="119"/>
@@ -24682,7 +24822,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="125" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="22.5" customHeight="1">
@@ -24690,10 +24830,10 @@
         <v>500</v>
       </c>
       <c r="B83" s="126" t="s">
-        <v>1209</v>
+        <v>1219</v>
       </c>
       <c r="C83" s="127" t="s">
-        <v>1210</v>
+        <v>1220</v>
       </c>
       <c r="D83" s="128"/>
       <c r="E83" s="128"/>
@@ -24711,7 +24851,7 @@
         <v>74</v>
       </c>
       <c r="K83" s="134" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22.5" customHeight="1">
@@ -24719,13 +24859,13 @@
         <v>451</v>
       </c>
       <c r="B84" s="151" t="s">
-        <v>1301</v>
+        <v>1311</v>
       </c>
       <c r="C84" s="151" t="s">
-        <v>1302</v>
+        <v>1312</v>
       </c>
       <c r="D84" s="152" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="E84" s="153"/>
       <c r="F84" s="154" t="s">
@@ -24744,7 +24884,7 @@
         <v>25</v>
       </c>
       <c r="K84" s="158" t="s">
-        <v>1303</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="22.5" customHeight="1">
@@ -24752,10 +24892,10 @@
         <v>503</v>
       </c>
       <c r="B85" s="107" t="s">
-        <v>1304</v>
+        <v>1314</v>
       </c>
       <c r="C85" s="108" t="s">
-        <v>1305</v>
+        <v>1315</v>
       </c>
       <c r="D85" s="109"/>
       <c r="E85" s="109"/>
@@ -24773,7 +24913,7 @@
         <v>74</v>
       </c>
       <c r="K85" s="115" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="22.5" customHeight="1">
@@ -24781,10 +24921,10 @@
         <v>506</v>
       </c>
       <c r="B86" s="135" t="s">
-        <v>1306</v>
+        <v>1316</v>
       </c>
       <c r="C86" s="136" t="s">
-        <v>1307</v>
+        <v>1317</v>
       </c>
       <c r="D86" s="137"/>
       <c r="E86" s="137"/>
@@ -24802,7 +24942,7 @@
         <v>74</v>
       </c>
       <c r="K86" s="143" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="22.5" customHeight="1">
@@ -24810,10 +24950,10 @@
         <v>510</v>
       </c>
       <c r="B87" s="108" t="s">
-        <v>1308</v>
+        <v>1318</v>
       </c>
       <c r="C87" s="108" t="s">
-        <v>1309</v>
+        <v>1319</v>
       </c>
       <c r="D87" s="109"/>
       <c r="E87" s="109"/>
@@ -24826,10 +24966,10 @@
       </c>
       <c r="I87" s="113"/>
       <c r="J87" s="160" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K87" s="115" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="22.5" customHeight="1">
@@ -24837,10 +24977,10 @@
         <v>514</v>
       </c>
       <c r="B88" s="135" t="s">
-        <v>1310</v>
+        <v>1320</v>
       </c>
       <c r="C88" s="136" t="s">
-        <v>1311</v>
+        <v>1321</v>
       </c>
       <c r="D88" s="137"/>
       <c r="E88" s="137"/>
@@ -24858,7 +24998,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="143" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="22.5" customHeight="1">
@@ -24866,10 +25006,10 @@
         <v>517</v>
       </c>
       <c r="B89" s="117" t="s">
-        <v>1312</v>
+        <v>1322</v>
       </c>
       <c r="C89" s="118" t="s">
-        <v>1313</v>
+        <v>1323</v>
       </c>
       <c r="D89" s="70"/>
       <c r="E89" s="70"/>
@@ -24887,7 +25027,7 @@
         <v>74</v>
       </c>
       <c r="K89" s="125" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="22.5" customHeight="1">
@@ -24895,10 +25035,10 @@
         <v>520</v>
       </c>
       <c r="B90" s="135" t="s">
-        <v>1314</v>
+        <v>1324</v>
       </c>
       <c r="C90" s="136" t="s">
-        <v>1315</v>
+        <v>1325</v>
       </c>
       <c r="D90" s="83"/>
       <c r="E90" s="83"/>
@@ -24914,7 +25054,7 @@
         <v>74</v>
       </c>
       <c r="K90" s="143" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="22.5" customHeight="1">
@@ -24922,10 +25062,10 @@
         <v>523</v>
       </c>
       <c r="B91" s="77" t="s">
-        <v>1211</v>
+        <v>1221</v>
       </c>
       <c r="C91" s="76" t="s">
-        <v>1212</v>
+        <v>1222</v>
       </c>
       <c r="D91" s="70"/>
       <c r="E91" s="70"/>
@@ -24941,7 +25081,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="125" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22.5" customHeight="1">
@@ -24949,10 +25089,10 @@
         <v>527</v>
       </c>
       <c r="B92" s="81" t="s">
-        <v>1316</v>
+        <v>1326</v>
       </c>
       <c r="C92" s="82" t="s">
-        <v>1317</v>
+        <v>1327</v>
       </c>
       <c r="D92" s="83"/>
       <c r="E92" s="83"/>
@@ -24970,7 +25110,7 @@
         <v>74</v>
       </c>
       <c r="K92" s="143" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="22.5" customHeight="1">
@@ -24978,10 +25118,10 @@
         <v>531</v>
       </c>
       <c r="B93" s="77" t="s">
-        <v>1318</v>
+        <v>1328</v>
       </c>
       <c r="C93" s="76" t="s">
-        <v>1319</v>
+        <v>1329</v>
       </c>
       <c r="D93" s="70"/>
       <c r="E93" s="70"/>
@@ -24997,7 +25137,7 @@
         <v>74</v>
       </c>
       <c r="K93" s="125" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="22.5" customHeight="1">
@@ -25005,10 +25145,10 @@
         <v>534</v>
       </c>
       <c r="B94" s="81" t="s">
-        <v>1320</v>
+        <v>1330</v>
       </c>
       <c r="C94" s="82" t="s">
-        <v>1321</v>
+        <v>1331</v>
       </c>
       <c r="D94" s="83"/>
       <c r="E94" s="83"/>
@@ -25024,7 +25164,7 @@
         <v>74</v>
       </c>
       <c r="K94" s="143" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="22.5" customHeight="1">
@@ -25032,13 +25172,13 @@
         <v>454</v>
       </c>
       <c r="B95" s="104" t="s">
-        <v>1322</v>
+        <v>1332</v>
       </c>
       <c r="C95" s="104" t="s">
-        <v>1323</v>
+        <v>1333</v>
       </c>
       <c r="D95" s="62" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E95" s="63"/>
       <c r="F95" s="64" t="s">
@@ -25057,7 +25197,7 @@
         <v>16</v>
       </c>
       <c r="K95" s="158" t="s">
-        <v>1287</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="22.5" customHeight="1">
@@ -25065,10 +25205,10 @@
         <v>538</v>
       </c>
       <c r="B96" s="77" t="s">
-        <v>1324</v>
+        <v>1334</v>
       </c>
       <c r="C96" s="76" t="s">
-        <v>1325</v>
+        <v>1335</v>
       </c>
       <c r="D96" s="70"/>
       <c r="E96" s="70"/>
@@ -25084,7 +25224,7 @@
         <v>74</v>
       </c>
       <c r="K96" s="125" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="22.5" customHeight="1">
@@ -25092,10 +25232,10 @@
         <v>541</v>
       </c>
       <c r="B97" s="81" t="s">
-        <v>1326</v>
+        <v>1336</v>
       </c>
       <c r="C97" s="82" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="D97" s="83"/>
       <c r="E97" s="83"/>
@@ -25111,7 +25251,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="22.5" customHeight="1">
@@ -25119,10 +25259,10 @@
         <v>544</v>
       </c>
       <c r="B98" s="77" t="s">
-        <v>1213</v>
+        <v>1223</v>
       </c>
       <c r="C98" s="76" t="s">
-        <v>1214</v>
+        <v>1224</v>
       </c>
       <c r="D98" s="70"/>
       <c r="E98" s="70"/>
@@ -25140,7 +25280,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="22.5" customHeight="1">
@@ -25148,10 +25288,10 @@
         <v>547</v>
       </c>
       <c r="B99" s="81" t="s">
-        <v>1215</v>
+        <v>1225</v>
       </c>
       <c r="C99" s="82" t="s">
-        <v>1216</v>
+        <v>1226</v>
       </c>
       <c r="D99" s="83"/>
       <c r="E99" s="83"/>
@@ -25169,7 +25309,7 @@
         <v>74</v>
       </c>
       <c r="K99" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="22.5" customHeight="1">
@@ -25177,10 +25317,10 @@
         <v>552</v>
       </c>
       <c r="B100" s="77" t="s">
-        <v>1327</v>
+        <v>1337</v>
       </c>
       <c r="C100" s="76" t="s">
-        <v>1328</v>
+        <v>1338</v>
       </c>
       <c r="D100" s="70"/>
       <c r="E100" s="70"/>
@@ -25196,7 +25336,7 @@
         <v>74</v>
       </c>
       <c r="K100" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="22.5" customHeight="1">
@@ -25204,10 +25344,10 @@
         <v>555</v>
       </c>
       <c r="B101" s="81" t="s">
-        <v>1329</v>
+        <v>1339</v>
       </c>
       <c r="C101" s="82" t="s">
-        <v>1330</v>
+        <v>1340</v>
       </c>
       <c r="D101" s="83"/>
       <c r="E101" s="83"/>
@@ -25223,7 +25363,7 @@
         <v>74</v>
       </c>
       <c r="K101" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="22.5" customHeight="1">
@@ -25231,10 +25371,10 @@
         <v>558</v>
       </c>
       <c r="B102" s="77" t="s">
-        <v>1331</v>
+        <v>1341</v>
       </c>
       <c r="C102" s="76" t="s">
-        <v>1332</v>
+        <v>1342</v>
       </c>
       <c r="D102" s="70"/>
       <c r="E102" s="70"/>
@@ -25250,7 +25390,7 @@
         <v>74</v>
       </c>
       <c r="K102" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="22.5" customHeight="1">
@@ -25258,10 +25398,10 @@
         <v>562</v>
       </c>
       <c r="B103" s="81" t="s">
-        <v>1333</v>
+        <v>1343</v>
       </c>
       <c r="C103" s="82" t="s">
-        <v>1334</v>
+        <v>1344</v>
       </c>
       <c r="D103" s="83"/>
       <c r="E103" s="83"/>
@@ -25277,7 +25417,7 @@
         <v>74</v>
       </c>
       <c r="K103" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="22.5" customHeight="1">
@@ -25285,10 +25425,10 @@
         <v>565</v>
       </c>
       <c r="B104" s="76" t="s">
-        <v>1217</v>
+        <v>1227</v>
       </c>
       <c r="C104" s="76" t="s">
-        <v>1218</v>
+        <v>1228</v>
       </c>
       <c r="D104" s="70"/>
       <c r="E104" s="70"/>
@@ -25306,7 +25446,7 @@
         <v>25</v>
       </c>
       <c r="K104" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="22.5" customHeight="1">
@@ -25314,10 +25454,10 @@
         <v>568</v>
       </c>
       <c r="B105" s="81" t="s">
-        <v>1335</v>
+        <v>1345</v>
       </c>
       <c r="C105" s="82" t="s">
-        <v>1201</v>
+        <v>1211</v>
       </c>
       <c r="D105" s="83"/>
       <c r="E105" s="83"/>
@@ -25335,7 +25475,7 @@
         <v>74</v>
       </c>
       <c r="K105" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="22.5" customHeight="1">
@@ -25343,10 +25483,10 @@
         <v>457</v>
       </c>
       <c r="B106" s="104" t="s">
-        <v>1336</v>
+        <v>1346</v>
       </c>
       <c r="C106" s="104" t="s">
-        <v>1337</v>
+        <v>1347</v>
       </c>
       <c r="D106" s="62" t="s">
         <v>540</v>
@@ -25365,10 +25505,10 @@
         <v>0.9</v>
       </c>
       <c r="J106" s="64" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="K106" s="104" t="s">
-        <v>1338</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="22.5" customHeight="1">
@@ -25376,10 +25516,10 @@
         <v>571</v>
       </c>
       <c r="B107" s="77" t="s">
-        <v>1339</v>
+        <v>1349</v>
       </c>
       <c r="C107" s="76" t="s">
-        <v>1340</v>
+        <v>1350</v>
       </c>
       <c r="D107" s="70"/>
       <c r="E107" s="70"/>
@@ -25395,7 +25535,7 @@
         <v>25</v>
       </c>
       <c r="K107" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="22.5" customHeight="1">
@@ -25403,10 +25543,10 @@
         <v>574</v>
       </c>
       <c r="B108" s="81" t="s">
-        <v>1341</v>
+        <v>1351</v>
       </c>
       <c r="C108" s="82" t="s">
-        <v>1342</v>
+        <v>1352</v>
       </c>
       <c r="D108" s="83"/>
       <c r="E108" s="83"/>
@@ -25422,7 +25562,7 @@
         <v>74</v>
       </c>
       <c r="K108" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="22.5" customHeight="1">
@@ -25430,10 +25570,10 @@
         <v>576</v>
       </c>
       <c r="B109" s="77" t="s">
-        <v>1343</v>
+        <v>1353</v>
       </c>
       <c r="C109" s="76" t="s">
-        <v>1344</v>
+        <v>1354</v>
       </c>
       <c r="D109" s="70"/>
       <c r="E109" s="70"/>
@@ -25451,7 +25591,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="22.5" customHeight="1">
@@ -25459,10 +25599,10 @@
         <v>579</v>
       </c>
       <c r="B110" s="81" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="C110" s="82" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="D110" s="83"/>
       <c r="E110" s="83"/>
@@ -25478,7 +25618,7 @@
         <v>74</v>
       </c>
       <c r="K110" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="22.5" customHeight="1">
@@ -25486,10 +25626,10 @@
         <v>582</v>
       </c>
       <c r="B111" s="77" t="s">
-        <v>1347</v>
+        <v>1357</v>
       </c>
       <c r="C111" s="76" t="s">
-        <v>1348</v>
+        <v>1358</v>
       </c>
       <c r="D111" s="70"/>
       <c r="E111" s="70"/>
@@ -25505,7 +25645,7 @@
         <v>74</v>
       </c>
       <c r="K111" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="22.5" customHeight="1">
@@ -25513,10 +25653,10 @@
         <v>585</v>
       </c>
       <c r="B112" s="81" t="s">
-        <v>1349</v>
+        <v>1359</v>
       </c>
       <c r="C112" s="82" t="s">
-        <v>1350</v>
+        <v>1360</v>
       </c>
       <c r="D112" s="83"/>
       <c r="E112" s="83"/>
@@ -25532,7 +25672,7 @@
         <v>74</v>
       </c>
       <c r="K112" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="22.5" customHeight="1">
@@ -25540,10 +25680,10 @@
         <v>588</v>
       </c>
       <c r="B113" s="77" t="s">
-        <v>1351</v>
+        <v>1361</v>
       </c>
       <c r="C113" s="76" t="s">
-        <v>1352</v>
+        <v>1362</v>
       </c>
       <c r="D113" s="70"/>
       <c r="E113" s="70"/>
@@ -25559,7 +25699,7 @@
         <v>74</v>
       </c>
       <c r="K113" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="22.5" customHeight="1">
@@ -25567,10 +25707,10 @@
         <v>591</v>
       </c>
       <c r="B114" s="81" t="s">
-        <v>1353</v>
+        <v>1363</v>
       </c>
       <c r="C114" s="82" t="s">
-        <v>1354</v>
+        <v>1364</v>
       </c>
       <c r="D114" s="83"/>
       <c r="E114" s="83"/>
@@ -25586,7 +25726,7 @@
         <v>74</v>
       </c>
       <c r="K114" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="22.5" customHeight="1">
@@ -25594,7 +25734,7 @@
         <v>594</v>
       </c>
       <c r="B115" s="77" t="s">
-        <v>1355</v>
+        <v>1365</v>
       </c>
       <c r="C115" s="76" t="s">
         <v>391</v>
@@ -25613,7 +25753,7 @@
         <v>74</v>
       </c>
       <c r="K115" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="22.5" customHeight="1">
@@ -25621,10 +25761,10 @@
         <v>597</v>
       </c>
       <c r="B116" s="81" t="s">
-        <v>1356</v>
+        <v>1366</v>
       </c>
       <c r="C116" s="82" t="s">
-        <v>1357</v>
+        <v>1367</v>
       </c>
       <c r="D116" s="83"/>
       <c r="E116" s="83"/>
@@ -25640,7 +25780,7 @@
         <v>74</v>
       </c>
       <c r="K116" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="22.5" customHeight="1">
@@ -25648,17 +25788,17 @@
         <v>668</v>
       </c>
       <c r="B117" s="104" t="s">
-        <v>1358</v>
+        <v>1368</v>
       </c>
       <c r="C117" s="104" t="s">
-        <v>1359</v>
+        <v>1369</v>
       </c>
       <c r="D117" s="62" t="s">
         <v>540</v>
       </c>
       <c r="E117" s="63"/>
       <c r="F117" s="64" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="G117" s="103">
         <v>45976</v>
@@ -25670,10 +25810,10 @@
         <v>0.85</v>
       </c>
       <c r="J117" s="64" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="K117" s="104" t="s">
-        <v>1303</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="22.5" customHeight="1">
@@ -25681,10 +25821,10 @@
         <v>600</v>
       </c>
       <c r="B118" s="77" t="s">
-        <v>1360</v>
+        <v>1370</v>
       </c>
       <c r="C118" s="76" t="s">
-        <v>1361</v>
+        <v>1371</v>
       </c>
       <c r="D118" s="70"/>
       <c r="E118" s="70"/>
@@ -25700,7 +25840,7 @@
         <v>74</v>
       </c>
       <c r="K118" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="22.5" customHeight="1">
@@ -25708,10 +25848,10 @@
         <v>603</v>
       </c>
       <c r="B119" s="81" t="s">
-        <v>1219</v>
+        <v>1229</v>
       </c>
       <c r="C119" s="82" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="D119" s="83"/>
       <c r="E119" s="83"/>
@@ -25729,7 +25869,7 @@
         <v>74</v>
       </c>
       <c r="K119" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="22.5" customHeight="1">
@@ -25737,10 +25877,10 @@
         <v>606</v>
       </c>
       <c r="B120" s="77" t="s">
-        <v>1362</v>
+        <v>1372</v>
       </c>
       <c r="C120" s="76" t="s">
-        <v>1363</v>
+        <v>1373</v>
       </c>
       <c r="D120" s="70"/>
       <c r="E120" s="70"/>
@@ -25758,7 +25898,7 @@
         <v>74</v>
       </c>
       <c r="K120" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="22.5" customHeight="1">
@@ -25766,10 +25906,10 @@
         <v>609</v>
       </c>
       <c r="B121" s="81" t="s">
-        <v>1364</v>
+        <v>1374</v>
       </c>
       <c r="C121" s="82" t="s">
-        <v>1365</v>
+        <v>1375</v>
       </c>
       <c r="D121" s="83"/>
       <c r="E121" s="83"/>
@@ -25785,7 +25925,7 @@
         <v>74</v>
       </c>
       <c r="K121" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="22.5" customHeight="1">
@@ -25793,10 +25933,10 @@
         <v>612</v>
       </c>
       <c r="B122" s="77" t="s">
-        <v>1366</v>
+        <v>1376</v>
       </c>
       <c r="C122" s="76" t="s">
-        <v>1367</v>
+        <v>1377</v>
       </c>
       <c r="D122" s="70"/>
       <c r="E122" s="70"/>
@@ -25812,7 +25952,7 @@
         <v>74</v>
       </c>
       <c r="K122" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="22.5" customHeight="1">
@@ -25820,10 +25960,10 @@
         <v>615</v>
       </c>
       <c r="B123" s="81" t="s">
-        <v>1368</v>
+        <v>1378</v>
       </c>
       <c r="C123" s="82" t="s">
-        <v>1369</v>
+        <v>1379</v>
       </c>
       <c r="D123" s="83"/>
       <c r="E123" s="83"/>
@@ -25839,7 +25979,7 @@
         <v>74</v>
       </c>
       <c r="K123" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="22.5" customHeight="1">
@@ -25847,10 +25987,10 @@
         <v>618</v>
       </c>
       <c r="B124" s="77" t="s">
-        <v>1370</v>
+        <v>1380</v>
       </c>
       <c r="C124" s="76" t="s">
-        <v>1371</v>
+        <v>1381</v>
       </c>
       <c r="D124" s="70"/>
       <c r="E124" s="70"/>
@@ -25868,7 +26008,7 @@
         <v>25</v>
       </c>
       <c r="K124" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="22.5" customHeight="1">
@@ -25876,10 +26016,10 @@
         <v>621</v>
       </c>
       <c r="B125" s="81" t="s">
-        <v>1372</v>
+        <v>1382</v>
       </c>
       <c r="C125" s="82" t="s">
-        <v>1373</v>
+        <v>1383</v>
       </c>
       <c r="D125" s="83"/>
       <c r="E125" s="83"/>
@@ -25895,7 +26035,7 @@
         <v>25</v>
       </c>
       <c r="K125" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="22.5" customHeight="1">
@@ -25903,10 +26043,10 @@
         <v>624</v>
       </c>
       <c r="B126" s="77" t="s">
-        <v>1374</v>
+        <v>1384</v>
       </c>
       <c r="C126" s="76" t="s">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="D126" s="70"/>
       <c r="E126" s="70"/>
@@ -25922,7 +26062,7 @@
         <v>74</v>
       </c>
       <c r="K126" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="22.5" customHeight="1">
@@ -25930,10 +26070,10 @@
         <v>627</v>
       </c>
       <c r="B127" s="81" t="s">
-        <v>1376</v>
+        <v>1386</v>
       </c>
       <c r="C127" s="82" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="D127" s="83"/>
       <c r="E127" s="83"/>
@@ -25949,7 +26089,7 @@
         <v>74</v>
       </c>
       <c r="K127" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="22.5" customHeight="1">
@@ -25957,10 +26097,10 @@
         <v>459</v>
       </c>
       <c r="B128" s="104" t="s">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="C128" s="104" t="s">
-        <v>1379</v>
+        <v>1389</v>
       </c>
       <c r="D128" s="62" t="s">
         <v>540</v>
@@ -25979,10 +26119,10 @@
         <v>0.5</v>
       </c>
       <c r="J128" s="64" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="K128" s="104" t="s">
-        <v>1338</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="22.5" customHeight="1">
@@ -25990,10 +26130,10 @@
         <v>630</v>
       </c>
       <c r="B129" s="77" t="s">
-        <v>1380</v>
+        <v>1390</v>
       </c>
       <c r="C129" s="76" t="s">
-        <v>1381</v>
+        <v>1391</v>
       </c>
       <c r="D129" s="70"/>
       <c r="E129" s="70"/>
@@ -26009,7 +26149,7 @@
         <v>74</v>
       </c>
       <c r="K129" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="22.5" customHeight="1">
@@ -26017,10 +26157,10 @@
         <v>633</v>
       </c>
       <c r="B130" s="81" t="s">
-        <v>1382</v>
+        <v>1392</v>
       </c>
       <c r="C130" s="82" t="s">
-        <v>1383</v>
+        <v>1393</v>
       </c>
       <c r="D130" s="83"/>
       <c r="E130" s="83"/>
@@ -26038,7 +26178,7 @@
         <v>74</v>
       </c>
       <c r="K130" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="22.5" customHeight="1">
@@ -26046,10 +26186,10 @@
         <v>636</v>
       </c>
       <c r="B131" s="77" t="s">
-        <v>1384</v>
+        <v>1394</v>
       </c>
       <c r="C131" s="76" t="s">
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="D131" s="70"/>
       <c r="E131" s="70"/>
@@ -26065,7 +26205,7 @@
         <v>74</v>
       </c>
       <c r="K131" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="22.5" customHeight="1">
@@ -26073,10 +26213,10 @@
         <v>637</v>
       </c>
       <c r="B132" s="81" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="C132" s="82" t="s">
-        <v>1222</v>
+        <v>1232</v>
       </c>
       <c r="D132" s="83"/>
       <c r="E132" s="83"/>
@@ -26094,7 +26234,7 @@
         <v>74</v>
       </c>
       <c r="K132" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="22.5" customHeight="1">
@@ -26102,10 +26242,10 @@
         <v>638</v>
       </c>
       <c r="B133" s="77" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
       <c r="C133" s="76" t="s">
-        <v>1224</v>
+        <v>1234</v>
       </c>
       <c r="D133" s="70"/>
       <c r="E133" s="70"/>
@@ -26123,7 +26263,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="22.5" customHeight="1">
@@ -26131,10 +26271,10 @@
         <v>639</v>
       </c>
       <c r="B134" s="81" t="s">
-        <v>1386</v>
+        <v>1396</v>
       </c>
       <c r="C134" s="82" t="s">
-        <v>1387</v>
+        <v>1397</v>
       </c>
       <c r="D134" s="83"/>
       <c r="E134" s="83"/>
@@ -26150,7 +26290,7 @@
         <v>25</v>
       </c>
       <c r="K134" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="22.5" customHeight="1">
@@ -26158,10 +26298,10 @@
         <v>640</v>
       </c>
       <c r="B135" s="77" t="s">
-        <v>1388</v>
+        <v>1398</v>
       </c>
       <c r="C135" s="76" t="s">
-        <v>1389</v>
+        <v>1399</v>
       </c>
       <c r="D135" s="70"/>
       <c r="E135" s="70"/>
@@ -26179,7 +26319,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="22.5" customHeight="1">
@@ -26187,10 +26327,10 @@
         <v>641</v>
       </c>
       <c r="B136" s="81" t="s">
-        <v>1225</v>
+        <v>1235</v>
       </c>
       <c r="C136" s="82" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="D136" s="83"/>
       <c r="E136" s="83"/>
@@ -26206,7 +26346,7 @@
         <v>74</v>
       </c>
       <c r="K136" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="22.5" customHeight="1">
@@ -26214,10 +26354,10 @@
         <v>642</v>
       </c>
       <c r="B137" s="77" t="s">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="C137" s="76" t="s">
-        <v>1391</v>
+        <v>1401</v>
       </c>
       <c r="D137" s="70"/>
       <c r="E137" s="70"/>
@@ -26233,7 +26373,7 @@
         <v>74</v>
       </c>
       <c r="K137" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="22.5" customHeight="1">
@@ -26241,10 +26381,10 @@
         <v>643</v>
       </c>
       <c r="B138" s="81" t="s">
-        <v>1392</v>
+        <v>1402</v>
       </c>
       <c r="C138" s="82" t="s">
-        <v>1228</v>
+        <v>1238</v>
       </c>
       <c r="D138" s="83"/>
       <c r="E138" s="83"/>
@@ -26262,7 +26402,7 @@
         <v>74</v>
       </c>
       <c r="K138" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="22.5" customHeight="1">
@@ -26270,13 +26410,13 @@
         <v>462</v>
       </c>
       <c r="B139" s="104" t="s">
-        <v>1393</v>
+        <v>1403</v>
       </c>
       <c r="C139" s="104" t="s">
-        <v>1394</v>
+        <v>1404</v>
       </c>
       <c r="D139" s="62" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="E139" s="63"/>
       <c r="F139" s="64" t="s">
@@ -26295,7 +26435,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="104" t="s">
-        <v>1287</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="22.5" customHeight="1">
@@ -26303,10 +26443,10 @@
         <v>644</v>
       </c>
       <c r="B140" s="81" t="s">
-        <v>1395</v>
+        <v>1405</v>
       </c>
       <c r="C140" s="82" t="s">
-        <v>1396</v>
+        <v>1406</v>
       </c>
       <c r="D140" s="83"/>
       <c r="E140" s="83"/>
@@ -26324,7 +26464,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="22.5" customHeight="1">
@@ -26332,10 +26472,10 @@
         <v>645</v>
       </c>
       <c r="B141" s="77" t="s">
-        <v>1397</v>
+        <v>1407</v>
       </c>
       <c r="C141" s="76" t="s">
-        <v>1398</v>
+        <v>1408</v>
       </c>
       <c r="D141" s="70"/>
       <c r="E141" s="70"/>
@@ -26351,7 +26491,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="22.5" customHeight="1">
@@ -26359,10 +26499,10 @@
         <v>646</v>
       </c>
       <c r="B142" s="81" t="s">
-        <v>1399</v>
+        <v>1409</v>
       </c>
       <c r="C142" s="82" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="D142" s="83"/>
       <c r="E142" s="83"/>
@@ -26378,7 +26518,7 @@
         <v>74</v>
       </c>
       <c r="K142" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="22.5" customHeight="1">
@@ -26386,10 +26526,10 @@
         <v>647</v>
       </c>
       <c r="B143" s="77" t="s">
-        <v>1400</v>
+        <v>1410</v>
       </c>
       <c r="C143" s="76" t="s">
-        <v>1401</v>
+        <v>1411</v>
       </c>
       <c r="D143" s="70"/>
       <c r="E143" s="70"/>
@@ -26405,7 +26545,7 @@
         <v>74</v>
       </c>
       <c r="K143" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="22.5" customHeight="1">
@@ -26413,10 +26553,10 @@
         <v>648</v>
       </c>
       <c r="B144" s="81" t="s">
-        <v>1402</v>
+        <v>1412</v>
       </c>
       <c r="C144" s="82" t="s">
-        <v>1403</v>
+        <v>1413</v>
       </c>
       <c r="D144" s="83"/>
       <c r="E144" s="83"/>
@@ -26432,7 +26572,7 @@
         <v>74</v>
       </c>
       <c r="K144" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="22.5" customHeight="1">
@@ -26440,10 +26580,10 @@
         <v>649</v>
       </c>
       <c r="B145" s="77" t="s">
-        <v>1404</v>
+        <v>1414</v>
       </c>
       <c r="C145" s="76" t="s">
-        <v>1405</v>
+        <v>1415</v>
       </c>
       <c r="D145" s="70"/>
       <c r="E145" s="70"/>
@@ -26459,7 +26599,7 @@
         <v>25</v>
       </c>
       <c r="K145" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="22.5" customHeight="1">
@@ -26467,10 +26607,10 @@
         <v>650</v>
       </c>
       <c r="B146" s="81" t="s">
-        <v>1406</v>
+        <v>1416</v>
       </c>
       <c r="C146" s="82" t="s">
-        <v>1407</v>
+        <v>1417</v>
       </c>
       <c r="D146" s="83"/>
       <c r="E146" s="83"/>
@@ -26486,7 +26626,7 @@
         <v>74</v>
       </c>
       <c r="K146" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="22.5" customHeight="1">
@@ -26494,10 +26634,10 @@
         <v>651</v>
       </c>
       <c r="B147" s="77" t="s">
-        <v>1408</v>
+        <v>1418</v>
       </c>
       <c r="C147" s="76" t="s">
-        <v>1409</v>
+        <v>1419</v>
       </c>
       <c r="D147" s="70"/>
       <c r="E147" s="70"/>
@@ -26513,7 +26653,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="22.5" customHeight="1">
@@ -26521,10 +26661,10 @@
         <v>652</v>
       </c>
       <c r="B148" s="81" t="s">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="C148" s="82" t="s">
-        <v>1411</v>
+        <v>1421</v>
       </c>
       <c r="D148" s="83"/>
       <c r="E148" s="83"/>
@@ -26540,7 +26680,7 @@
         <v>74</v>
       </c>
       <c r="K148" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="22.5" customHeight="1">
@@ -26548,10 +26688,10 @@
         <v>653</v>
       </c>
       <c r="B149" s="77" t="s">
-        <v>1412</v>
+        <v>1422</v>
       </c>
       <c r="C149" s="76" t="s">
-        <v>1413</v>
+        <v>1423</v>
       </c>
       <c r="D149" s="70"/>
       <c r="E149" s="70"/>
@@ -26567,7 +26707,7 @@
         <v>74</v>
       </c>
       <c r="K149" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="22.5" customHeight="1">
@@ -26575,11 +26715,11 @@
         <v>465</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1414</v>
+        <v>1424</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="166" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="E150" s="167"/>
       <c r="F150" s="168"/>
@@ -26594,10 +26734,10 @@
         <v>654</v>
       </c>
       <c r="B151" s="82" t="s">
-        <v>1415</v>
+        <v>1425</v>
       </c>
       <c r="C151" s="82" t="s">
-        <v>1416</v>
+        <v>1426</v>
       </c>
       <c r="D151" s="83"/>
       <c r="E151" s="83"/>
@@ -26610,21 +26750,21 @@
       </c>
       <c r="I151" s="87"/>
       <c r="J151" s="90" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K151" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="22.5" customHeight="1">
       <c r="A152" s="8" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="B152" s="77" t="s">
-        <v>1417</v>
+        <v>1427</v>
       </c>
       <c r="C152" s="76" t="s">
-        <v>1418</v>
+        <v>1428</v>
       </c>
       <c r="D152" s="70"/>
       <c r="E152" s="70"/>
@@ -26640,18 +26780,18 @@
         <v>25</v>
       </c>
       <c r="K152" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="22.5" customHeight="1">
       <c r="A153" s="8" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B153" s="81" t="s">
-        <v>1419</v>
+        <v>1429</v>
       </c>
       <c r="C153" s="82" t="s">
-        <v>1420</v>
+        <v>1430</v>
       </c>
       <c r="D153" s="83"/>
       <c r="E153" s="83"/>
@@ -26667,18 +26807,18 @@
         <v>74</v>
       </c>
       <c r="K153" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="22.5" customHeight="1">
       <c r="A154" s="8" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B154" s="77" t="s">
-        <v>1229</v>
+        <v>1239</v>
       </c>
       <c r="C154" s="76" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="D154" s="70"/>
       <c r="E154" s="70"/>
@@ -26694,18 +26834,18 @@
         <v>25</v>
       </c>
       <c r="K154" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="22.5" customHeight="1">
       <c r="A155" s="8" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="B155" s="81" t="s">
-        <v>1421</v>
+        <v>1431</v>
       </c>
       <c r="C155" s="82" t="s">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="D155" s="83"/>
       <c r="E155" s="83"/>
@@ -26723,18 +26863,18 @@
         <v>25</v>
       </c>
       <c r="K155" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="22.5" customHeight="1">
       <c r="A156" s="8" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="B156" s="76" t="s">
-        <v>1423</v>
+        <v>1433</v>
       </c>
       <c r="C156" s="76" t="s">
-        <v>1424</v>
+        <v>1434</v>
       </c>
       <c r="D156" s="70"/>
       <c r="E156" s="70"/>
@@ -26750,18 +26890,18 @@
         <v>513</v>
       </c>
       <c r="K156" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="22.5" customHeight="1">
       <c r="A157" s="8" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="B157" s="81" t="s">
-        <v>1425</v>
+        <v>1435</v>
       </c>
       <c r="C157" s="82" t="s">
-        <v>1426</v>
+        <v>1436</v>
       </c>
       <c r="D157" s="83"/>
       <c r="E157" s="83"/>
@@ -26779,18 +26919,18 @@
         <v>74</v>
       </c>
       <c r="K157" s="82" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="22.5" customHeight="1">
       <c r="A158" s="8" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="B158" s="76" t="s">
-        <v>1231</v>
+        <v>1241</v>
       </c>
       <c r="C158" s="76" t="s">
-        <v>1232</v>
+        <v>1242</v>
       </c>
       <c r="D158" s="70"/>
       <c r="E158" s="70"/>
@@ -26808,18 +26948,18 @@
         <v>25</v>
       </c>
       <c r="K158" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="22.5" customHeight="1">
       <c r="A159" s="8" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="B159" s="77" t="s">
-        <v>1427</v>
+        <v>1437</v>
       </c>
       <c r="C159" s="76" t="s">
-        <v>1428</v>
+        <v>1438</v>
       </c>
       <c r="D159" s="10"/>
       <c r="E159" s="11"/>
@@ -26835,18 +26975,18 @@
         <v>25</v>
       </c>
       <c r="K159" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="22.5" customHeight="1">
       <c r="A160" s="8" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="B160" s="77" t="s">
-        <v>1429</v>
+        <v>1439</v>
       </c>
       <c r="C160" s="76" t="s">
-        <v>1430</v>
+        <v>1440</v>
       </c>
       <c r="D160" s="10"/>
       <c r="E160" s="11"/>
@@ -26862,7 +27002,7 @@
         <v>25</v>
       </c>
       <c r="K160" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="22.5" customHeight="1">
@@ -26872,7 +27012,7 @@
       <c r="B161" s="9"/>
       <c r="C161" s="5"/>
       <c r="D161" s="62" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="E161" s="167"/>
       <c r="F161" s="102"/>
@@ -26884,13 +27024,13 @@
     </row>
     <row r="162" spans="1:11" ht="22.5" customHeight="1">
       <c r="A162" s="8" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>1233</v>
+        <v>1243</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>1431</v>
+        <v>1441</v>
       </c>
       <c r="D162" s="10"/>
       <c r="E162" s="11"/>
@@ -26908,18 +27048,18 @@
         <v>74</v>
       </c>
       <c r="K162" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="22.5" customHeight="1">
       <c r="A163" s="8" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>1237</v>
+        <v>1247</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>1238</v>
+        <v>1248</v>
       </c>
       <c r="D163" s="10"/>
       <c r="E163" s="11"/>
@@ -26937,18 +27077,18 @@
         <v>25</v>
       </c>
       <c r="K163" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="22.5" customHeight="1">
       <c r="A164" s="8" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>1239</v>
+        <v>1249</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>1240</v>
+        <v>1250</v>
       </c>
       <c r="D164" s="10"/>
       <c r="E164" s="11"/>
@@ -26963,21 +27103,21 @@
       </c>
       <c r="I164" s="13"/>
       <c r="J164" s="14" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="K164" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="22.5" customHeight="1">
       <c r="A165" s="8" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>1241</v>
+        <v>1251</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>1242</v>
+        <v>1252</v>
       </c>
       <c r="D165" s="10"/>
       <c r="E165" s="11"/>
@@ -26995,7 +27135,7 @@
         <v>551</v>
       </c>
       <c r="K165" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="22.5" customHeight="1">
@@ -27032,10 +27172,10 @@
         <v>11</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>1243</v>
+        <v>1253</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>1244</v>
+        <v>1254</v>
       </c>
       <c r="D167" s="10"/>
       <c r="E167" s="11"/>
@@ -27053,7 +27193,7 @@
         <v>551</v>
       </c>
       <c r="K167" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="22.5" customHeight="1">
@@ -27090,10 +27230,10 @@
         <v>18</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>1245</v>
+        <v>1255</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>1244</v>
+        <v>1254</v>
       </c>
       <c r="D169" s="10"/>
       <c r="E169" s="11"/>
@@ -27111,7 +27251,7 @@
         <v>551</v>
       </c>
       <c r="K169" s="76" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="22.5" customHeight="1">
@@ -28663,10 +28803,10 @@
     <row r="248" spans="1:11" ht="22.5" customHeight="1">
       <c r="A248" s="46"/>
       <c r="B248" s="9" t="s">
-        <v>1432</v>
+        <v>1442</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>1433</v>
+        <v>1443</v>
       </c>
       <c r="D248" s="10"/>
       <c r="E248" s="48" t="s">

--- a/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
+++ b/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlando.carvajal.DESMEX\Desktop\ClaudeCode\Pipeline1\pipeline-web\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C47B8120-0DB9-4D28-84F8-D6A16FA8F8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38E98AEC-00CE-4B50-9567-294C54201CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Copia seguridad 27-01-2026" sheetId="9" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$L$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$L$210</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Copia seguridad 27-01-2026'!$A$1:$K$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Daniela Lara'!$A$1:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Josué Morales'!$A$1:$K$148</definedName>
@@ -50,11 +50,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={42a397a7-ff4f-4940-ba5e-aafcf05f7117}</author>
-    <author>tc={10ae3357-a4da-46ce-9112-d132a03a00ab}</author>
+    <author>tc={5de07d34-5d4a-43f1-b491-846ecd35ea4b}</author>
+    <author>tc={bce944ed-64d8-421b-abdb-8ef4241df362}</author>
   </authors>
   <commentList>
-    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{42A397A7-FF4F-4940-BA5E-AAFCF05F7117}">
+    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{5DE07D34-5D4A-43F1-B491-846ECD35EA4B}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -62,7 +62,7 @@
     ya lo tiene en seguimiento Josué</t>
       </text>
     </comment>
-    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{10AE3357-A4DA-46CE-9112-D132A03A00AB}">
+    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{BCE944ED-64D8-421B-ABDB-8EF4241DF362}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4728" uniqueCount="1444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4751" uniqueCount="1456">
   <si>
     <t>ID de Prospecto</t>
   </si>
@@ -2306,6 +2306,18 @@
     <t>Gasosur</t>
   </si>
   <si>
+    <t>Luis Eduardo Hernández</t>
+  </si>
+  <si>
+    <t>Ceypabasa</t>
+  </si>
+  <si>
+    <t>BESS</t>
+  </si>
+  <si>
+    <t>Congreso / Cámara / Networking</t>
+  </si>
+  <si>
     <t>PSP81</t>
   </si>
   <si>
@@ -2741,9 +2753,6 @@
     <t>Grupo Urbitec</t>
   </si>
   <si>
-    <t>Congreso / Cámara / Networking</t>
-  </si>
-  <si>
     <t>Arq. Salvador Miranda</t>
   </si>
   <si>
@@ -3711,6 +3720,33 @@
   </si>
   <si>
     <t>Proyectos varios</t>
+  </si>
+  <si>
+    <t>Ing. Omar Zárate</t>
+  </si>
+  <si>
+    <t>La Corona</t>
+  </si>
+  <si>
+    <t>SFV  y/o  BC</t>
+  </si>
+  <si>
+    <t>Lic. Luis Rodríguez</t>
+  </si>
+  <si>
+    <t>Tire Direct</t>
+  </si>
+  <si>
+    <t>Delia Villagomez / Jessica Domínguez</t>
+  </si>
+  <si>
+    <t>Kolben Schmidt Pistons</t>
+  </si>
+  <si>
+    <t>Arq. Edmundo Villarreal M,</t>
+  </si>
+  <si>
+    <t>Own Studio</t>
   </si>
   <si>
     <r>
@@ -5688,7 +5724,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Anónimo" id="{0610D5FF-B13C-4B87-BA08-09B6E665D0BD}" userId="" providerId="google-sheets"/>
+  <person displayName="Anónimo" id="{9483496C-DE73-4697-AA81-E4E84C32D530}" userId="" providerId="google-sheets"/>
 </personList>
 </file>
 
@@ -5754,8 +5790,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:L206">
-  <autoFilter ref="A1:L206" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:L210">
+  <autoFilter ref="A1:L210" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID de Prospecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Nombre del Prospecto"/>
@@ -6032,10 +6068,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{0610D5FF-B13C-4B87-BA08-09B6E665D0BD}" id="{42A397A7-FF4F-4940-BA5E-AAFCF05F7117}" done="1">
+  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{9483496C-DE73-4697-AA81-E4E84C32D530}" id="{5DE07D34-5D4A-43F1-B491-846ECD35EA4B}" done="1">
     <text>ya lo tiene en seguimiento Josué</text>
   </threadedComment>
-  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{0610D5FF-B13C-4B87-BA08-09B6E665D0BD}" id="{10AE3357-A4DA-46CE-9112-D132A03A00AB}" done="1">
+  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{9483496C-DE73-4697-AA81-E4E84C32D530}" id="{BCE944ED-64D8-421B-ABDB-8EF4241DF362}" done="1">
     <text>Ya tienen contrato con Ammper</text>
   </threadedComment>
 </ThreadedComments>
@@ -12103,7 +12139,7 @@
         <v>448</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="G8" s="54">
         <v>46078</v>
@@ -13060,15 +13096,33 @@
       <c r="A35" s="46" t="s">
         <v>552</v>
       </c>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="53"/>
+      <c r="B35" s="51" t="s">
+        <v>741</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>742</v>
+      </c>
+      <c r="D35" s="49" t="s">
+        <v>561</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="F35" s="53" t="s">
+        <v>667</v>
+      </c>
+      <c r="G35" s="54">
+        <v>46149</v>
+      </c>
+      <c r="H35" s="55">
+        <v>0</v>
+      </c>
+      <c r="I35" s="56">
+        <v>0.1</v>
+      </c>
+      <c r="J35" s="53" t="s">
+        <v>744</v>
+      </c>
       <c r="K35" s="46" t="s">
         <v>660</v>
       </c>
@@ -13922,7 +13976,7 @@
     </row>
     <row r="83" spans="1:12" ht="22.5" customHeight="1">
       <c r="A83" s="46" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B83" s="51"/>
       <c r="C83" s="51"/>
@@ -13940,7 +13994,7 @@
     </row>
     <row r="84" spans="1:12" ht="22.5" customHeight="1">
       <c r="A84" s="46" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B84" s="51"/>
       <c r="C84" s="51"/>
@@ -13958,7 +14012,7 @@
     </row>
     <row r="85" spans="1:12" ht="22.5" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B85" s="51"/>
       <c r="C85" s="51"/>
@@ -13976,7 +14030,7 @@
     </row>
     <row r="86" spans="1:12" ht="22.5" customHeight="1">
       <c r="A86" s="46" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B86" s="51"/>
       <c r="C86" s="51"/>
@@ -13994,7 +14048,7 @@
     </row>
     <row r="87" spans="1:12" ht="22.5" customHeight="1">
       <c r="A87" s="46" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B87" s="51"/>
       <c r="C87" s="51"/>
@@ -14012,7 +14066,7 @@
     </row>
     <row r="88" spans="1:12" ht="22.5" customHeight="1">
       <c r="A88" s="46" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B88" s="51"/>
       <c r="C88" s="51"/>
@@ -14030,7 +14084,7 @@
     </row>
     <row r="89" spans="1:12" ht="22.5" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B89" s="51"/>
       <c r="C89" s="51"/>
@@ -14048,7 +14102,7 @@
     </row>
     <row r="90" spans="1:12" ht="22.5" customHeight="1">
       <c r="A90" s="46" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B90" s="51"/>
       <c r="C90" s="51"/>
@@ -14066,7 +14120,7 @@
     </row>
     <row r="91" spans="1:12" ht="22.5" customHeight="1">
       <c r="A91" s="46" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B91" s="51"/>
       <c r="C91" s="51"/>
@@ -14084,7 +14138,7 @@
     </row>
     <row r="92" spans="1:12" ht="22.5" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B92" s="51"/>
       <c r="C92" s="51"/>
@@ -14102,7 +14156,7 @@
     </row>
     <row r="93" spans="1:12" ht="22.5" customHeight="1">
       <c r="A93" s="46" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B93" s="51"/>
       <c r="C93" s="51"/>
@@ -14120,7 +14174,7 @@
     </row>
     <row r="94" spans="1:12" ht="22.5" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B94" s="51"/>
       <c r="C94" s="51"/>
@@ -14138,7 +14192,7 @@
     </row>
     <row r="95" spans="1:12" ht="22.5" customHeight="1">
       <c r="A95" s="46" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B95" s="51"/>
       <c r="C95" s="51"/>
@@ -14156,7 +14210,7 @@
     </row>
     <row r="96" spans="1:12" ht="22.5" customHeight="1">
       <c r="A96" s="46" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B96" s="51"/>
       <c r="C96" s="51"/>
@@ -14563,13 +14617,14 @@
     <hyperlink ref="D32" r:id="rId30" xr:uid="{00000000-0004-0000-0300-00001D000000}"/>
     <hyperlink ref="D33" r:id="rId31" xr:uid="{00000000-0004-0000-0300-00001E000000}"/>
     <hyperlink ref="D34" r:id="rId32" xr:uid="{00000000-0004-0000-0300-00001F000000}"/>
+    <hyperlink ref="D35" r:id="rId33" xr:uid="{00000000-0004-0000-0300-000020000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
-  <legacyDrawing r:id="rId33"/>
+  <legacyDrawing r:id="rId34"/>
   <tableParts count="1">
-    <tablePart r:id="rId34"/>
+    <tablePart r:id="rId35"/>
   </tableParts>
 </worksheet>
 </file>
@@ -14580,7 +14635,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC206"/>
+  <dimension ref="A1:AC210"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -14654,10 +14709,10 @@
     <row r="2" spans="1:29" ht="22.5" customHeight="1">
       <c r="A2" s="46"/>
       <c r="B2" s="46" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="D2" s="49" t="s">
         <v>561</v>
@@ -14675,17 +14730,17 @@
       <c r="I2" s="56"/>
       <c r="J2" s="53"/>
       <c r="K2" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L2" s="57"/>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
       <c r="A3" s="46"/>
       <c r="B3" s="46" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="D3" s="49" t="s">
         <v>561</v>
@@ -14703,23 +14758,23 @@
       <c r="I3" s="56"/>
       <c r="J3" s="53"/>
       <c r="K3" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L3" s="57"/>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
       <c r="A4" s="46"/>
       <c r="B4" s="46" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>733</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>119</v>
@@ -14733,17 +14788,17 @@
         <v>25</v>
       </c>
       <c r="K4" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L4" s="57"/>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
       <c r="A5" s="46"/>
       <c r="B5" s="46" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>733</v>
@@ -14760,20 +14815,20 @@
       <c r="H5" s="55"/>
       <c r="I5" s="56"/>
       <c r="J5" s="53" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="K5" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L5" s="57"/>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
       <c r="A6" s="46"/>
       <c r="B6" s="51" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="D6" s="49" t="s">
         <v>561</v>
@@ -14793,17 +14848,17 @@
         <v>25</v>
       </c>
       <c r="K6" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L6" s="57"/>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
       <c r="A7" s="46"/>
       <c r="B7" s="51" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="D7" s="49" t="s">
         <v>733</v>
@@ -14823,17 +14878,17 @@
         <v>16</v>
       </c>
       <c r="K7" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L7" s="57"/>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
       <c r="A8" s="46"/>
       <c r="B8" s="51" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="D8" s="49" t="s">
         <v>733</v>
@@ -14853,17 +14908,17 @@
         <v>16</v>
       </c>
       <c r="K8" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L8" s="57"/>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
       <c r="A9" s="46"/>
       <c r="B9" s="51" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D9" s="49" t="s">
         <v>733</v>
@@ -14883,17 +14938,17 @@
         <v>16</v>
       </c>
       <c r="K9" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L9" s="57"/>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
       <c r="A10" s="46"/>
       <c r="B10" s="51" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="D10" s="49" t="s">
         <v>540</v>
@@ -14913,17 +14968,17 @@
         <v>74</v>
       </c>
       <c r="K10" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L10" s="57"/>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
       <c r="A11" s="46"/>
       <c r="B11" s="51" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>723</v>
@@ -14940,20 +14995,20 @@
       <c r="H11" s="55"/>
       <c r="I11" s="56"/>
       <c r="J11" s="53" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L11" s="57"/>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="51" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="D12" s="49" t="s">
         <v>540</v>
@@ -14973,17 +15028,17 @@
         <v>16</v>
       </c>
       <c r="K12" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L12" s="57"/>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="51" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="D13" s="49" t="s">
         <v>540</v>
@@ -15003,17 +15058,17 @@
         <v>688</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L13" s="57"/>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
       <c r="A14" s="46"/>
       <c r="B14" s="51" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D14" s="49" t="s">
         <v>530</v>
@@ -15030,20 +15085,20 @@
       <c r="H14" s="55"/>
       <c r="I14" s="56"/>
       <c r="J14" s="53" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="K14" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L14" s="57"/>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
       <c r="A15" s="46"/>
       <c r="B15" s="51" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="D15" s="49" t="s">
         <v>561</v>
@@ -15063,17 +15118,17 @@
         <v>688</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L15" s="57"/>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
       <c r="A16" s="46"/>
       <c r="B16" s="51" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -15091,17 +15146,17 @@
         <v>688</v>
       </c>
       <c r="K16" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L16" s="57"/>
     </row>
     <row r="17" spans="1:12" ht="22.5" customHeight="1">
       <c r="A17" s="46"/>
       <c r="B17" s="51" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="D17" s="49" t="s">
         <v>733</v>
@@ -15121,17 +15176,17 @@
         <v>688</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L17" s="57"/>
     </row>
     <row r="18" spans="1:12" ht="22.5" customHeight="1">
       <c r="A18" s="46"/>
       <c r="B18" s="51" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D18" s="49" t="s">
         <v>540</v>
@@ -15151,17 +15206,17 @@
         <v>16</v>
       </c>
       <c r="K18" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L18" s="57"/>
     </row>
     <row r="19" spans="1:12" ht="22.5" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="51" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D19" s="49" t="s">
         <v>723</v>
@@ -15181,7 +15236,7 @@
         <v>74</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L19" s="57"/>
     </row>
@@ -15190,7 +15245,7 @@
         <v>175</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="C20" s="51" t="s">
         <v>483</v>
@@ -15213,7 +15268,7 @@
         <v>16</v>
       </c>
       <c r="K20" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L20" s="57"/>
     </row>
@@ -15222,7 +15277,7 @@
         <v>170</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C21" s="51" t="s">
         <v>483</v>
@@ -15245,7 +15300,7 @@
         <v>16</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L21" s="57"/>
     </row>
@@ -15254,10 +15309,10 @@
         <v>172</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D22" s="49" t="s">
         <v>561</v>
@@ -15277,7 +15332,7 @@
         <v>513</v>
       </c>
       <c r="K22" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L22" s="57"/>
     </row>
@@ -15286,16 +15341,16 @@
         <v>135</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="D23" s="49" t="s">
         <v>733</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="F23" s="53" t="s">
         <v>119</v>
@@ -15309,7 +15364,7 @@
         <v>688</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L23" s="57"/>
     </row>
@@ -15318,13 +15373,13 @@
         <v>139</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>448</v>
@@ -15341,7 +15396,7 @@
         <v>16</v>
       </c>
       <c r="K24" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L24" s="57"/>
     </row>
@@ -15350,13 +15405,13 @@
         <v>142</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>448</v>
@@ -15373,7 +15428,7 @@
         <v>74</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L25" s="57"/>
     </row>
@@ -15382,10 +15437,10 @@
         <v>144</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>733</v>
@@ -15405,7 +15460,7 @@
         <v>74</v>
       </c>
       <c r="K26" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L26" s="57"/>
     </row>
@@ -15414,13 +15469,13 @@
         <v>152</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>448</v>
@@ -15437,7 +15492,7 @@
         <v>74</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L27" s="57"/>
     </row>
@@ -15446,10 +15501,10 @@
         <v>155</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="D28" s="49" t="s">
         <v>733</v>
@@ -15469,25 +15524,25 @@
         <v>74</v>
       </c>
       <c r="K28" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L28" s="57"/>
     </row>
     <row r="29" spans="1:12" ht="22.5" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D29" s="49" t="s">
         <v>733</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="F29" s="53" t="s">
         <v>119</v>
@@ -15501,7 +15556,7 @@
         <v>688</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L29" s="57"/>
     </row>
@@ -15510,10 +15565,10 @@
         <v>149</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C30" s="51" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="D30" s="49" t="s">
         <v>561</v>
@@ -15537,7 +15592,7 @@
         <v>513</v>
       </c>
       <c r="K30" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L30" s="57"/>
     </row>
@@ -15546,10 +15601,10 @@
         <v>97</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="D31" s="49" t="s">
         <v>726</v>
@@ -15569,7 +15624,7 @@
         <v>25</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L31" s="57"/>
     </row>
@@ -15578,10 +15633,10 @@
         <v>99</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="D32" s="49" t="s">
         <v>733</v>
@@ -15601,7 +15656,7 @@
         <v>74</v>
       </c>
       <c r="K32" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L32" s="57"/>
     </row>
@@ -15610,10 +15665,10 @@
         <v>103</v>
       </c>
       <c r="B33" s="46" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="C33" s="46" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="D33" s="49" t="s">
         <v>561</v>
@@ -15633,7 +15688,7 @@
         <v>688</v>
       </c>
       <c r="K33" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L33" s="57"/>
     </row>
@@ -15642,10 +15697,10 @@
         <v>129</v>
       </c>
       <c r="B34" s="51" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="C34" s="51" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="D34" s="49" t="s">
         <v>733</v>
@@ -15661,26 +15716,26 @@
       </c>
       <c r="H34" s="55"/>
       <c r="I34" s="60" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="J34" s="53" t="s">
         <v>688</v>
       </c>
       <c r="K34" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L34" s="57"/>
     </row>
     <row r="35" spans="1:12" ht="22.5" customHeight="1">
       <c r="A35" s="46"/>
       <c r="B35" s="51" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C35" s="51" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>448</v>
@@ -15697,7 +15752,7 @@
         <v>688</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L35" s="57"/>
     </row>
@@ -15706,10 +15761,10 @@
         <v>68</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10" t="s">
@@ -15727,7 +15782,7 @@
         <v>74</v>
       </c>
       <c r="K36" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L36" s="57"/>
     </row>
@@ -15736,10 +15791,10 @@
         <v>71</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C37" s="51" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="D37" s="49" t="s">
         <v>540</v>
@@ -15759,7 +15814,7 @@
         <v>688</v>
       </c>
       <c r="K37" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L37" s="57"/>
     </row>
@@ -15768,10 +15823,10 @@
         <v>78</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C38" s="51" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="D38" s="49" t="s">
         <v>733</v>
@@ -15791,7 +15846,7 @@
         <v>16</v>
       </c>
       <c r="K38" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L38" s="57"/>
     </row>
@@ -15800,16 +15855,16 @@
         <v>81</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="F39" s="53" t="s">
         <v>119</v>
@@ -15823,20 +15878,20 @@
         <v>16</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L39" s="57"/>
     </row>
     <row r="40" spans="1:12" ht="22.5" customHeight="1">
       <c r="A40" s="46"/>
       <c r="B40" s="51" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="C40" s="51" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>448</v>
@@ -15853,7 +15908,7 @@
         <v>74</v>
       </c>
       <c r="K40" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L40" s="57"/>
     </row>
@@ -15862,10 +15917,10 @@
         <v>54</v>
       </c>
       <c r="B41" s="51" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C41" s="51" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="D41" s="49" t="s">
         <v>723</v>
@@ -15885,7 +15940,7 @@
         <v>25</v>
       </c>
       <c r="K41" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L41" s="57"/>
     </row>
@@ -15894,14 +15949,14 @@
         <v>60</v>
       </c>
       <c r="B42" s="46" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="F42" s="53" t="s">
         <v>119</v>
@@ -15915,7 +15970,7 @@
         <v>688</v>
       </c>
       <c r="K42" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L42" s="57"/>
     </row>
@@ -15924,10 +15979,10 @@
         <v>63</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C43" s="51" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D43" s="49" t="s">
         <v>723</v>
@@ -15947,7 +16002,7 @@
         <v>688</v>
       </c>
       <c r="K43" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L43" s="57"/>
     </row>
@@ -15956,13 +16011,13 @@
         <v>65</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C44" s="51" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>448</v>
@@ -15979,7 +16034,7 @@
         <v>25</v>
       </c>
       <c r="K44" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L44" s="57"/>
     </row>
@@ -15988,13 +16043,13 @@
         <v>85</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="C45" s="51" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>448</v>
@@ -16007,25 +16062,25 @@
       </c>
       <c r="H45" s="55"/>
       <c r="I45" s="60" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="J45" s="53" t="s">
         <v>513</v>
       </c>
       <c r="K45" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L45" s="57"/>
     </row>
     <row r="46" spans="1:12" ht="22.5" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="D46" s="49" t="s">
         <v>540</v>
@@ -16045,19 +16100,19 @@
         <v>688</v>
       </c>
       <c r="K46" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L46" s="57"/>
     </row>
     <row r="47" spans="1:12" ht="22.5" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B47" s="51" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="D47" s="49" t="s">
         <v>526</v>
@@ -16077,19 +16132,19 @@
         <v>25</v>
       </c>
       <c r="K47" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L47" s="57"/>
     </row>
     <row r="48" spans="1:12" ht="22.5" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B48" s="51" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C48" s="51" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="D48" s="49" t="s">
         <v>733</v>
@@ -16109,22 +16164,22 @@
         <v>74</v>
       </c>
       <c r="K48" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L48" s="57"/>
     </row>
     <row r="49" spans="1:12" ht="22.5" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>448</v>
@@ -16141,19 +16196,19 @@
         <v>74</v>
       </c>
       <c r="K49" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L49" s="57"/>
     </row>
     <row r="50" spans="1:12" ht="22.5" customHeight="1">
       <c r="A50" s="8" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B50" s="51" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C50" s="51" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="D50" s="49" t="s">
         <v>733</v>
@@ -16173,7 +16228,7 @@
         <v>74</v>
       </c>
       <c r="K50" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L50" s="57"/>
     </row>
@@ -16182,10 +16237,10 @@
         <v>11</v>
       </c>
       <c r="B51" s="51" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="C51" s="51" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="D51" s="49" t="s">
         <v>733</v>
@@ -16205,7 +16260,7 @@
         <v>688</v>
       </c>
       <c r="K51" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L51" s="57"/>
     </row>
@@ -16214,10 +16269,10 @@
         <v>18</v>
       </c>
       <c r="B52" s="51" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="C52" s="51" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D52" s="49" t="s">
         <v>540</v>
@@ -16237,7 +16292,7 @@
         <v>25</v>
       </c>
       <c r="K52" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L52" s="57"/>
     </row>
@@ -16247,7 +16302,7 @@
       </c>
       <c r="B53" s="46"/>
       <c r="C53" s="46" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D53" s="49" t="s">
         <v>723</v>
@@ -16267,7 +16322,7 @@
         <v>688</v>
       </c>
       <c r="K53" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L53" s="57"/>
     </row>
@@ -16276,10 +16331,10 @@
         <v>26</v>
       </c>
       <c r="B54" s="51" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C54" s="51" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D54" s="49" t="s">
         <v>733</v>
@@ -16299,7 +16354,7 @@
         <v>688</v>
       </c>
       <c r="K54" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L54" s="57"/>
     </row>
@@ -16308,10 +16363,10 @@
         <v>29</v>
       </c>
       <c r="B55" s="51" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="C55" s="51" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D55" s="49" t="s">
         <v>733</v>
@@ -16331,7 +16386,7 @@
         <v>74</v>
       </c>
       <c r="K55" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L55" s="57"/>
     </row>
@@ -16340,7 +16395,7 @@
         <v>34</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C56" s="51" t="s">
         <v>712</v>
@@ -16363,7 +16418,7 @@
         <v>688</v>
       </c>
       <c r="K56" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L56" s="57"/>
     </row>
@@ -16372,13 +16427,13 @@
         <v>48</v>
       </c>
       <c r="B57" s="51" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C57" s="51" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>448</v>
@@ -16392,10 +16447,10 @@
       <c r="H57" s="55"/>
       <c r="I57" s="56"/>
       <c r="J57" s="53" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="K57" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L57" s="57"/>
     </row>
@@ -16404,10 +16459,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="51" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C58" s="51" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="D58" s="49" t="s">
         <v>561</v>
@@ -16427,7 +16482,7 @@
         <v>513</v>
       </c>
       <c r="K58" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L58" s="57"/>
     </row>
@@ -16436,13 +16491,13 @@
         <v>638</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="C59" s="51" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>448</v>
@@ -16459,7 +16514,7 @@
         <v>74</v>
       </c>
       <c r="K59" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L59" s="57"/>
     </row>
@@ -16468,10 +16523,10 @@
         <v>639</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="D60" s="49" t="s">
         <v>540</v>
@@ -16488,10 +16543,10 @@
       <c r="H60" s="55"/>
       <c r="I60" s="56"/>
       <c r="J60" s="53" t="s">
-        <v>886</v>
+        <v>744</v>
       </c>
       <c r="K60" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L60" s="57"/>
     </row>
@@ -16500,13 +16555,13 @@
         <v>640</v>
       </c>
       <c r="B61" s="51" t="s">
+        <v>890</v>
+      </c>
+      <c r="C61" s="51" t="s">
+        <v>891</v>
+      </c>
+      <c r="D61" s="49" t="s">
         <v>887</v>
-      </c>
-      <c r="C61" s="51" t="s">
-        <v>888</v>
-      </c>
-      <c r="D61" s="49" t="s">
-        <v>883</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>448</v>
@@ -16523,7 +16578,7 @@
         <v>74</v>
       </c>
       <c r="K61" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L61" s="57"/>
     </row>
@@ -16532,13 +16587,13 @@
         <v>649</v>
       </c>
       <c r="B62" s="51" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="C62" s="51" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>448</v>
@@ -16555,17 +16610,17 @@
         <v>25</v>
       </c>
       <c r="K62" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L62" s="57"/>
     </row>
     <row r="63" spans="1:12" ht="22.5" customHeight="1">
       <c r="A63" s="46"/>
       <c r="B63" s="51" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C63" s="51" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D63" s="49" t="s">
         <v>526</v>
@@ -16585,7 +16640,7 @@
         <v>688</v>
       </c>
       <c r="K63" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L63" s="57"/>
     </row>
@@ -16594,13 +16649,13 @@
         <v>609</v>
       </c>
       <c r="B64" s="51" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="C64" s="51" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>448</v>
@@ -16617,7 +16672,7 @@
         <v>74</v>
       </c>
       <c r="K64" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L64" s="57"/>
     </row>
@@ -16626,13 +16681,13 @@
         <v>621</v>
       </c>
       <c r="B65" s="51" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C65" s="51" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>448</v>
@@ -16649,7 +16704,7 @@
         <v>74</v>
       </c>
       <c r="K65" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L65" s="57"/>
     </row>
@@ -16658,10 +16713,10 @@
         <v>624</v>
       </c>
       <c r="B66" s="51" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C66" s="51" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D66" s="49" t="s">
         <v>540</v>
@@ -16681,7 +16736,7 @@
         <v>74</v>
       </c>
       <c r="K66" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L66" s="57"/>
     </row>
@@ -16690,16 +16745,16 @@
         <v>597</v>
       </c>
       <c r="B67" s="51" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="F67" s="53" t="s">
         <v>119</v>
@@ -16713,7 +16768,7 @@
         <v>74</v>
       </c>
       <c r="K67" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L67" s="57"/>
     </row>
@@ -16722,16 +16777,16 @@
         <v>600</v>
       </c>
       <c r="B68" s="51" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C68" s="51" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="F68" s="53" t="s">
         <v>119</v>
@@ -16745,7 +16800,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L68" s="57"/>
     </row>
@@ -16754,13 +16809,13 @@
         <v>603</v>
       </c>
       <c r="B69" s="51" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C69" s="51" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D69" s="49" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>448</v>
@@ -16777,7 +16832,7 @@
         <v>74</v>
       </c>
       <c r="K69" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L69" s="57"/>
     </row>
@@ -16786,13 +16841,13 @@
         <v>146</v>
       </c>
       <c r="B70" s="51" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C70" s="51" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>448</v>
@@ -16809,7 +16864,7 @@
         <v>688</v>
       </c>
       <c r="K70" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L70" s="57"/>
     </row>
@@ -16818,10 +16873,10 @@
         <v>527</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C71" s="46" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D71" s="49" t="s">
         <v>561</v>
@@ -16841,7 +16896,7 @@
         <v>513</v>
       </c>
       <c r="K71" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L71" s="57"/>
     </row>
@@ -16850,16 +16905,16 @@
         <v>520</v>
       </c>
       <c r="B72" s="51" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C72" s="51" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="F72" s="53" t="s">
         <v>119</v>
@@ -16873,7 +16928,7 @@
         <v>16</v>
       </c>
       <c r="K72" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L72" s="57"/>
     </row>
@@ -16882,10 +16937,10 @@
         <v>576</v>
       </c>
       <c r="B73" s="51" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="C73" s="51" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="D73" s="10"/>
       <c r="E73" s="10" t="s">
@@ -16903,7 +16958,7 @@
         <v>25</v>
       </c>
       <c r="K73" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L73" s="57"/>
     </row>
@@ -16912,10 +16967,10 @@
         <v>579</v>
       </c>
       <c r="B74" s="51" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="D74" s="49" t="s">
         <v>723</v>
@@ -16935,7 +16990,7 @@
         <v>25</v>
       </c>
       <c r="K74" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L74" s="57"/>
     </row>
@@ -16944,13 +16999,13 @@
         <v>650</v>
       </c>
       <c r="B75" s="51" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="C75" s="51" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>448</v>
@@ -16967,7 +17022,7 @@
         <v>25</v>
       </c>
       <c r="K75" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L75" s="57"/>
     </row>
@@ -16976,13 +17031,13 @@
         <v>503</v>
       </c>
       <c r="B76" s="46" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C76" s="46" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="D76" s="49" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>448</v>
@@ -17001,7 +17056,7 @@
         <v>25</v>
       </c>
       <c r="K76" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L76" s="57"/>
     </row>
@@ -17010,16 +17065,16 @@
         <v>506</v>
       </c>
       <c r="B77" s="46" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C77" s="46" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="D77" s="49" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="F77" s="53" t="s">
         <v>699</v>
@@ -17033,7 +17088,7 @@
         <v>25</v>
       </c>
       <c r="K77" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L77" s="57"/>
     </row>
@@ -17042,10 +17097,10 @@
         <v>488</v>
       </c>
       <c r="B78" s="51" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C78" s="51" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="D78" s="10"/>
       <c r="E78" s="10" t="s">
@@ -17065,7 +17120,7 @@
         <v>25</v>
       </c>
       <c r="K78" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L78" s="57"/>
     </row>
@@ -17074,10 +17129,10 @@
         <v>494</v>
       </c>
       <c r="B79" s="46" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C79" s="46" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D79" s="49" t="s">
         <v>658</v>
@@ -17099,22 +17154,22 @@
         <v>25</v>
       </c>
       <c r="K79" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L79" s="57"/>
     </row>
     <row r="80" spans="1:12" ht="22.5" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B80" s="51" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C80" s="51" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D80" s="49" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>448</v>
@@ -17131,7 +17186,7 @@
         <v>16</v>
       </c>
       <c r="K80" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L80" s="57"/>
     </row>
@@ -17141,7 +17196,7 @@
       </c>
       <c r="B81" s="46"/>
       <c r="C81" s="46" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="D81" s="49" t="s">
         <v>540</v>
@@ -17161,7 +17216,7 @@
         <v>551</v>
       </c>
       <c r="K81" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L81" s="57"/>
     </row>
@@ -17170,16 +17225,16 @@
         <v>582</v>
       </c>
       <c r="B82" s="51" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C82" s="51" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="D82" s="49" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="F82" s="53" t="s">
         <v>119</v>
@@ -17193,7 +17248,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L82" s="57"/>
     </row>
@@ -17202,10 +17257,10 @@
         <v>113</v>
       </c>
       <c r="B83" s="51" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="C83" s="51" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="D83" s="49" t="s">
         <v>723</v>
@@ -17225,14 +17280,14 @@
         <v>688</v>
       </c>
       <c r="K83" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L83" s="57"/>
     </row>
     <row r="84" spans="1:12" ht="22.5" customHeight="1">
       <c r="A84" s="46"/>
       <c r="B84" s="46" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C84" s="46" t="s">
         <v>410</v>
@@ -17253,7 +17308,7 @@
         <v>74</v>
       </c>
       <c r="K84" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L84" s="57"/>
     </row>
@@ -17262,13 +17317,13 @@
         <v>116</v>
       </c>
       <c r="B85" s="51" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C85" s="51" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="D85" s="49" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>448</v>
@@ -17285,17 +17340,17 @@
         <v>688</v>
       </c>
       <c r="K85" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L85" s="57"/>
     </row>
     <row r="86" spans="1:12" ht="22.5" customHeight="1">
       <c r="A86" s="46"/>
       <c r="B86" s="51" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="C86" s="51" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="D86" s="10"/>
       <c r="E86" s="10" t="s">
@@ -17313,17 +17368,17 @@
         <v>25</v>
       </c>
       <c r="K86" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L86" s="57"/>
     </row>
     <row r="87" spans="1:12" ht="22.5" customHeight="1">
       <c r="A87" s="46"/>
       <c r="B87" s="51" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="C87" s="51" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D87" s="49" t="s">
         <v>678</v>
@@ -17340,23 +17395,23 @@
       <c r="H87" s="55"/>
       <c r="I87" s="56"/>
       <c r="J87" s="53" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="K87" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L87" s="57"/>
     </row>
     <row r="88" spans="1:12" ht="22.5" customHeight="1">
       <c r="A88" s="46"/>
       <c r="B88" s="51" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>448</v>
@@ -17373,7 +17428,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L88" s="57"/>
     </row>
@@ -17382,13 +17437,13 @@
         <v>565</v>
       </c>
       <c r="B89" s="51" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D89" s="49" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>448</v>
@@ -17405,7 +17460,7 @@
         <v>25</v>
       </c>
       <c r="K89" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L89" s="57"/>
     </row>
@@ -17414,10 +17469,10 @@
         <v>568</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="C90" s="51" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="D90" s="49" t="s">
         <v>723</v>
@@ -17437,7 +17492,7 @@
         <v>25</v>
       </c>
       <c r="K90" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L90" s="57"/>
     </row>
@@ -17446,10 +17501,10 @@
         <v>571</v>
       </c>
       <c r="B91" s="51" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="C91" s="51" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="D91" s="10"/>
       <c r="E91" s="10" t="s">
@@ -17467,7 +17522,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L91" s="57"/>
     </row>
@@ -17476,13 +17531,13 @@
         <v>574</v>
       </c>
       <c r="B92" s="51" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C92" s="51" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="D92" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>448</v>
@@ -17499,7 +17554,7 @@
         <v>25</v>
       </c>
       <c r="K92" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L92" s="57"/>
     </row>
@@ -17508,10 +17563,10 @@
         <v>562</v>
       </c>
       <c r="B93" s="51" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C93" s="51" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="D93" s="49" t="s">
         <v>540</v>
@@ -17531,7 +17586,7 @@
         <v>25</v>
       </c>
       <c r="K93" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L93" s="57"/>
     </row>
@@ -17540,10 +17595,10 @@
         <v>88</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="C94" s="51" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="D94" s="49" t="s">
         <v>540</v>
@@ -17563,7 +17618,7 @@
         <v>513</v>
       </c>
       <c r="K94" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L94" s="57"/>
     </row>
@@ -17572,16 +17627,16 @@
         <v>523</v>
       </c>
       <c r="B95" s="46" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="C95" s="46" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="D95" s="49" t="s">
         <v>723</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="F95" s="53" t="s">
         <v>449</v>
@@ -17595,20 +17650,20 @@
         <v>74</v>
       </c>
       <c r="K95" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L95" s="57"/>
     </row>
     <row r="96" spans="1:12" ht="22.5" customHeight="1">
       <c r="A96" s="46"/>
       <c r="B96" s="46" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C96" s="46" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="D96" s="49" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>448</v>
@@ -17625,7 +17680,7 @@
         <v>25</v>
       </c>
       <c r="K96" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L96" s="57"/>
     </row>
@@ -17634,13 +17689,13 @@
         <v>643</v>
       </c>
       <c r="B97" s="51" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="C97" s="51" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="D97" s="49" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>448</v>
@@ -17657,7 +17712,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L97" s="57"/>
     </row>
@@ -17666,10 +17721,10 @@
         <v>644</v>
       </c>
       <c r="B98" s="51" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="C98" s="51" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="D98" s="49" t="s">
         <v>526</v>
@@ -17689,7 +17744,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L98" s="57"/>
     </row>
@@ -17698,13 +17753,13 @@
         <v>132</v>
       </c>
       <c r="B99" s="51" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="C99" s="51" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="D99" s="49" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>448</v>
@@ -17721,7 +17776,7 @@
         <v>513</v>
       </c>
       <c r="K99" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L99" s="57"/>
     </row>
@@ -17730,10 +17785,10 @@
         <v>606</v>
       </c>
       <c r="B100" s="51" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="C100" s="51" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="D100" s="49" t="s">
         <v>561</v>
@@ -17753,7 +17808,7 @@
         <v>25</v>
       </c>
       <c r="K100" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L100" s="57"/>
     </row>
@@ -17762,10 +17817,10 @@
         <v>538</v>
       </c>
       <c r="B101" s="51" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="C101" s="51" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D101" s="49" t="s">
         <v>723</v>
@@ -17785,7 +17840,7 @@
         <v>25</v>
       </c>
       <c r="K101" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L101" s="57"/>
     </row>
@@ -17794,10 +17849,10 @@
         <v>645</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="D102" s="49" t="s">
         <v>526</v>
@@ -17817,7 +17872,7 @@
         <v>16</v>
       </c>
       <c r="K102" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L102" s="57"/>
     </row>
@@ -17826,10 +17881,10 @@
         <v>120</v>
       </c>
       <c r="B103" s="51" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C103" s="51" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="D103" s="49" t="s">
         <v>540</v>
@@ -17849,7 +17904,7 @@
         <v>16</v>
       </c>
       <c r="K103" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L103" s="57"/>
     </row>
@@ -17858,13 +17913,13 @@
         <v>126</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C104" s="51" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>448</v>
@@ -17881,7 +17936,7 @@
         <v>16</v>
       </c>
       <c r="K104" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L104" s="57"/>
     </row>
@@ -17890,7 +17945,7 @@
         <v>41</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C105" s="51"/>
       <c r="D105" s="49" t="s">
@@ -17911,7 +17966,7 @@
         <v>16</v>
       </c>
       <c r="K105" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L105" s="57"/>
     </row>
@@ -17920,10 +17975,10 @@
         <v>646</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C106" s="51" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D106" s="49" t="s">
         <v>723</v>
@@ -17940,22 +17995,22 @@
       <c r="H106" s="55"/>
       <c r="I106" s="56"/>
       <c r="J106" s="53" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="K106" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L106" s="57"/>
     </row>
     <row r="107" spans="1:12" ht="22.5" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B107" s="51" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="C107" s="51" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D107" s="49" t="s">
         <v>723</v>
@@ -17975,17 +18030,17 @@
         <v>74</v>
       </c>
       <c r="K107" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L107" s="57"/>
     </row>
     <row r="108" spans="1:12" ht="22.5" customHeight="1">
       <c r="A108" s="46"/>
       <c r="B108" s="51" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C108" s="51" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D108" s="49" t="s">
         <v>733</v>
@@ -18005,7 +18060,7 @@
         <v>688</v>
       </c>
       <c r="K108" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L108" s="57"/>
     </row>
@@ -18014,13 +18069,13 @@
         <v>459</v>
       </c>
       <c r="B109" s="46" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="C109" s="46" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>448</v>
@@ -18041,7 +18096,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L109" s="57"/>
     </row>
@@ -18050,10 +18105,10 @@
         <v>462</v>
       </c>
       <c r="B110" s="46" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="C110" s="46" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D110" s="49" t="s">
         <v>540</v>
@@ -18075,7 +18130,7 @@
         <v>25</v>
       </c>
       <c r="K110" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L110" s="57"/>
     </row>
@@ -18084,19 +18139,19 @@
         <v>552</v>
       </c>
       <c r="B111" s="46" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="C111" s="46" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="D111" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F111" s="53" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="G111" s="54">
         <v>45952</v>
@@ -18107,7 +18162,7 @@
         <v>25</v>
       </c>
       <c r="K111" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L111" s="57"/>
     </row>
@@ -18116,13 +18171,13 @@
         <v>534</v>
       </c>
       <c r="B112" s="51" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C112" s="51" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>448</v>
@@ -18139,7 +18194,7 @@
         <v>25</v>
       </c>
       <c r="K112" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L112" s="57"/>
     </row>
@@ -18148,10 +18203,10 @@
         <v>594</v>
       </c>
       <c r="B113" s="51" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C113" s="51" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="D113" s="49" t="s">
         <v>540</v>
@@ -18171,7 +18226,7 @@
         <v>25</v>
       </c>
       <c r="K113" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L113" s="57"/>
     </row>
@@ -18180,10 +18235,10 @@
         <v>642</v>
       </c>
       <c r="B114" s="51" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C114" s="51" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D114" s="49" t="s">
         <v>723</v>
@@ -18203,7 +18258,7 @@
         <v>25</v>
       </c>
       <c r="K114" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L114" s="57"/>
     </row>
@@ -18212,16 +18267,16 @@
         <v>531</v>
       </c>
       <c r="B115" s="46" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C115" s="46" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="D115" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="F115" s="53" t="s">
         <v>119</v>
@@ -18235,22 +18290,22 @@
         <v>25</v>
       </c>
       <c r="K115" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L115" s="57"/>
     </row>
     <row r="116" spans="1:12" ht="22.5" customHeight="1">
       <c r="A116" s="8" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B116" s="51" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>448</v>
@@ -18264,10 +18319,10 @@
       <c r="H116" s="55"/>
       <c r="I116" s="56"/>
       <c r="J116" s="53" t="s">
-        <v>886</v>
+        <v>744</v>
       </c>
       <c r="K116" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L116" s="57"/>
     </row>
@@ -18276,16 +18331,16 @@
         <v>94</v>
       </c>
       <c r="B117" s="51" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C117" s="51" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="D117" s="49" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="F117" s="53" t="s">
         <v>119</v>
@@ -18299,7 +18354,7 @@
         <v>25</v>
       </c>
       <c r="K117" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L117" s="57"/>
     </row>
@@ -18308,19 +18363,19 @@
         <v>454</v>
       </c>
       <c r="B118" s="46" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="C118" s="46" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F118" s="53" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="G118" s="54">
         <v>45940</v>
@@ -18333,7 +18388,7 @@
         <v>25</v>
       </c>
       <c r="K118" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L118" s="57"/>
     </row>
@@ -18342,13 +18397,13 @@
         <v>585</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C119" s="51" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="D119" s="49" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>448</v>
@@ -18365,7 +18420,7 @@
         <v>25</v>
       </c>
       <c r="K119" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L119" s="57"/>
     </row>
@@ -18374,13 +18429,13 @@
         <v>591</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="C120" s="51" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>448</v>
@@ -18397,7 +18452,7 @@
         <v>25</v>
       </c>
       <c r="K120" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L120" s="57"/>
     </row>
@@ -18406,10 +18461,10 @@
         <v>91</v>
       </c>
       <c r="B121" s="51" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="C121" s="51" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="D121" s="49" t="s">
         <v>540</v>
@@ -18429,7 +18484,7 @@
         <v>16</v>
       </c>
       <c r="K121" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L121" s="57"/>
     </row>
@@ -18438,19 +18493,19 @@
         <v>457</v>
       </c>
       <c r="B122" s="46" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="C122" s="46" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F122" s="53" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="G122" s="54">
         <v>45933</v>
@@ -18463,7 +18518,7 @@
         <v>25</v>
       </c>
       <c r="K122" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L122" s="57"/>
     </row>
@@ -18472,10 +18527,10 @@
         <v>652</v>
       </c>
       <c r="B123" s="51" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="D123" s="49" t="s">
         <v>733</v>
@@ -18495,7 +18550,7 @@
         <v>16</v>
       </c>
       <c r="K123" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L123" s="57"/>
     </row>
@@ -18504,10 +18559,10 @@
         <v>37</v>
       </c>
       <c r="B124" s="46" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="C124" s="46" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="D124" s="49" t="s">
         <v>540</v>
@@ -18524,22 +18579,22 @@
       <c r="H124" s="55"/>
       <c r="I124" s="56"/>
       <c r="J124" s="53" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="K124" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L124" s="57"/>
     </row>
     <row r="125" spans="1:12" ht="22.5" customHeight="1">
       <c r="A125" s="8" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B125" s="46" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="C125" s="46" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D125" s="49" t="s">
         <v>733</v>
@@ -18559,19 +18614,19 @@
         <v>513</v>
       </c>
       <c r="K125" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L125" s="57"/>
     </row>
     <row r="126" spans="1:12" ht="22.5" customHeight="1">
       <c r="A126" s="8" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B126" s="51" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C126" s="51" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="D126" s="49" t="s">
         <v>540</v>
@@ -18591,19 +18646,19 @@
         <v>16</v>
       </c>
       <c r="K126" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L126" s="57"/>
     </row>
     <row r="127" spans="1:12" ht="22.5" customHeight="1">
       <c r="A127" s="8" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B127" s="51" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="C127" s="51" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D127" s="49" t="s">
         <v>733</v>
@@ -18623,7 +18678,7 @@
         <v>16</v>
       </c>
       <c r="K127" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L127" s="57"/>
     </row>
@@ -18632,10 +18687,10 @@
         <v>168</v>
       </c>
       <c r="B128" s="51" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="C128" s="51" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="D128" s="49" t="s">
         <v>733</v>
@@ -18655,22 +18710,22 @@
         <v>74</v>
       </c>
       <c r="K128" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L128" s="57"/>
     </row>
     <row r="129" spans="1:12" ht="22.5" customHeight="1">
       <c r="A129" s="8" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B129" s="51" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C129" s="51" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>448</v>
@@ -18687,7 +18742,7 @@
         <v>25</v>
       </c>
       <c r="K129" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L129" s="57"/>
     </row>
@@ -18696,13 +18751,13 @@
         <v>641</v>
       </c>
       <c r="B130" s="51" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="E130" s="10" t="s">
         <v>448</v>
@@ -18719,7 +18774,7 @@
         <v>25</v>
       </c>
       <c r="K130" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L130" s="57"/>
     </row>
@@ -18728,10 +18783,10 @@
         <v>630</v>
       </c>
       <c r="B131" s="51" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="C131" s="51" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="D131" s="49" t="s">
         <v>718</v>
@@ -18751,7 +18806,7 @@
         <v>25</v>
       </c>
       <c r="K131" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L131" s="57"/>
     </row>
@@ -18760,13 +18815,13 @@
         <v>627</v>
       </c>
       <c r="B132" s="51" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="C132" s="51" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D132" s="49" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>448</v>
@@ -18783,7 +18838,7 @@
         <v>513</v>
       </c>
       <c r="K132" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L132" s="57"/>
     </row>
@@ -18792,10 +18847,10 @@
         <v>555</v>
       </c>
       <c r="B133" s="51" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="C133" s="51" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="D133" s="49" t="s">
         <v>540</v>
@@ -18817,7 +18872,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L133" s="57"/>
     </row>
@@ -18826,13 +18881,13 @@
         <v>160</v>
       </c>
       <c r="B134" s="51" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="C134" s="51" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D134" s="49" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>448</v>
@@ -18849,7 +18904,7 @@
         <v>16</v>
       </c>
       <c r="K134" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L134" s="57"/>
     </row>
@@ -18858,10 +18913,10 @@
         <v>451</v>
       </c>
       <c r="B135" s="46" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="C135" s="46" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="D135" s="49" t="s">
         <v>540</v>
@@ -18885,7 +18940,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L135" s="57"/>
     </row>
@@ -18894,13 +18949,13 @@
         <v>547</v>
       </c>
       <c r="B136" s="51" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="C136" s="51" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="D136" s="49" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>448</v>
@@ -18917,7 +18972,7 @@
         <v>25</v>
       </c>
       <c r="K136" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L136" s="57"/>
     </row>
@@ -18927,10 +18982,10 @@
       </c>
       <c r="B137" s="51"/>
       <c r="C137" s="51" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>448</v>
@@ -18947,7 +19002,7 @@
         <v>25</v>
       </c>
       <c r="K137" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L137" s="57"/>
     </row>
@@ -18956,13 +19011,13 @@
         <v>541</v>
       </c>
       <c r="B138" s="51" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="C138" s="51" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="D138" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>448</v>
@@ -18979,7 +19034,7 @@
         <v>138</v>
       </c>
       <c r="K138" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L138" s="57"/>
     </row>
@@ -18988,10 +19043,10 @@
         <v>477</v>
       </c>
       <c r="B139" s="46" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="C139" s="46" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D139" s="49" t="s">
         <v>540</v>
@@ -19000,7 +19055,7 @@
         <v>448</v>
       </c>
       <c r="F139" s="53" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="G139" s="54">
         <v>45822</v>
@@ -19013,7 +19068,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L139" s="57"/>
     </row>
@@ -19022,13 +19077,13 @@
         <v>654</v>
       </c>
       <c r="B140" s="51" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="C140" s="51" t="s">
         <v>410</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="E140" s="10" t="s">
         <v>448</v>
@@ -19045,7 +19100,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L140" s="57"/>
     </row>
@@ -19054,13 +19109,13 @@
         <v>491</v>
       </c>
       <c r="B141" s="46" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="C141" s="46" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D141" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>448</v>
@@ -19081,7 +19136,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L141" s="57"/>
     </row>
@@ -19090,13 +19145,13 @@
         <v>471</v>
       </c>
       <c r="B142" s="46" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="C142" s="46" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="E142" s="10" t="s">
         <v>448</v>
@@ -19115,7 +19170,7 @@
         <v>25</v>
       </c>
       <c r="K142" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L142" s="57"/>
     </row>
@@ -19124,10 +19179,10 @@
         <v>668</v>
       </c>
       <c r="B143" s="46" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="C143" s="46" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="D143" s="10" t="s">
         <v>718</v>
@@ -19149,7 +19204,7 @@
         <v>25</v>
       </c>
       <c r="K143" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L143" s="57"/>
     </row>
@@ -19158,10 +19213,10 @@
         <v>123</v>
       </c>
       <c r="B144" s="51" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="D144" s="49" t="s">
         <v>540</v>
@@ -19181,7 +19236,7 @@
         <v>16</v>
       </c>
       <c r="K144" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L144" s="57"/>
     </row>
@@ -19190,10 +19245,10 @@
         <v>544</v>
       </c>
       <c r="B145" s="51" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="C145" s="51" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="D145" s="49" t="s">
         <v>540</v>
@@ -19213,17 +19268,17 @@
         <v>25</v>
       </c>
       <c r="K145" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L145" s="57"/>
     </row>
     <row r="146" spans="1:12" ht="22.5" customHeight="1">
       <c r="A146" s="46"/>
       <c r="B146" s="51" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="C146" s="51" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="D146" s="49" t="s">
         <v>733</v>
@@ -19232,7 +19287,7 @@
         <v>448</v>
       </c>
       <c r="F146" s="53" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="G146" s="54">
         <v>45736</v>
@@ -19243,7 +19298,7 @@
         <v>25</v>
       </c>
       <c r="K146" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L146" s="57"/>
     </row>
@@ -19252,10 +19307,10 @@
         <v>474</v>
       </c>
       <c r="B147" s="46" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="C147" s="46" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="D147" s="49" t="s">
         <v>540</v>
@@ -19264,7 +19319,7 @@
         <v>448</v>
       </c>
       <c r="F147" s="53" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="G147" s="54">
         <v>45700</v>
@@ -19277,7 +19332,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L147" s="57"/>
     </row>
@@ -19286,13 +19341,13 @@
         <v>636</v>
       </c>
       <c r="B148" s="51" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="C148" s="51" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="D148" s="49" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="E148" s="10" t="s">
         <v>448</v>
@@ -19309,7 +19364,7 @@
         <v>16</v>
       </c>
       <c r="K148" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L148" s="57"/>
     </row>
@@ -19318,13 +19373,13 @@
         <v>637</v>
       </c>
       <c r="B149" s="51" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="C149" s="51" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D149" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>448</v>
@@ -19338,10 +19393,10 @@
       <c r="H149" s="55"/>
       <c r="I149" s="56"/>
       <c r="J149" s="53" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="K149" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L149" s="57"/>
     </row>
@@ -19350,13 +19405,13 @@
         <v>497</v>
       </c>
       <c r="B150" s="46" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="C150" s="46" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="D150" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>448</v>
@@ -19377,7 +19432,7 @@
         <v>25</v>
       </c>
       <c r="K150" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L150" s="57"/>
     </row>
@@ -19386,16 +19441,16 @@
         <v>500</v>
       </c>
       <c r="B151" s="46" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="C151" s="46" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="D151" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="F151" s="53" t="s">
         <v>24</v>
@@ -19411,7 +19466,7 @@
         <v>25</v>
       </c>
       <c r="K151" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L151" s="57"/>
     </row>
@@ -19420,13 +19475,13 @@
         <v>651</v>
       </c>
       <c r="B152" s="51" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="C152" s="51" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="D152" s="49" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>448</v>
@@ -19443,7 +19498,7 @@
         <v>25</v>
       </c>
       <c r="K152" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L152" s="57"/>
     </row>
@@ -19452,16 +19507,16 @@
         <v>588</v>
       </c>
       <c r="B153" s="51" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="C153" s="51" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D153" s="49" t="s">
         <v>526</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="F153" s="53" t="s">
         <v>119</v>
@@ -19475,7 +19530,7 @@
         <v>25</v>
       </c>
       <c r="K153" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L153" s="57"/>
     </row>
@@ -19484,10 +19539,10 @@
         <v>481</v>
       </c>
       <c r="B154" s="46" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="C154" s="46" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="D154" s="49" t="s">
         <v>526</v>
@@ -19496,7 +19551,7 @@
         <v>448</v>
       </c>
       <c r="F154" s="53" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="G154" s="54">
         <v>45519</v>
@@ -19509,7 +19564,7 @@
         <v>25</v>
       </c>
       <c r="K154" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L154" s="57"/>
     </row>
@@ -19518,13 +19573,13 @@
         <v>517</v>
       </c>
       <c r="B155" s="46" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="C155" s="46" t="s">
         <v>483</v>
       </c>
       <c r="D155" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>448</v>
@@ -19545,25 +19600,25 @@
         <v>138</v>
       </c>
       <c r="K155" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L155" s="57"/>
     </row>
     <row r="156" spans="1:12" ht="22.5" customHeight="1">
       <c r="A156" s="8" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B156" s="51" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="C156" s="51" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="D156" s="49" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="E156" s="10" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="F156" s="53" t="s">
         <v>119</v>
@@ -19577,7 +19632,7 @@
         <v>25</v>
       </c>
       <c r="K156" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L156" s="57"/>
     </row>
@@ -19586,19 +19641,19 @@
         <v>514</v>
       </c>
       <c r="B157" s="46" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="C157" s="46" t="s">
         <v>483</v>
       </c>
       <c r="D157" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F157" s="53" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="G157" s="54">
         <v>45513</v>
@@ -19611,7 +19666,7 @@
         <v>16</v>
       </c>
       <c r="K157" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L157" s="57"/>
     </row>
@@ -19620,13 +19675,13 @@
         <v>166</v>
       </c>
       <c r="B158" s="51" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="E158" s="10" t="s">
         <v>448</v>
@@ -19643,7 +19698,7 @@
         <v>74</v>
       </c>
       <c r="K158" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L158" s="57"/>
     </row>
@@ -19652,13 +19707,13 @@
         <v>618</v>
       </c>
       <c r="B159" s="51" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C159" s="51" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D159" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>448</v>
@@ -19675,7 +19730,7 @@
         <v>513</v>
       </c>
       <c r="K159" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L159" s="57"/>
     </row>
@@ -19684,10 +19739,10 @@
         <v>633</v>
       </c>
       <c r="B160" s="51" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="C160" s="51" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="D160" s="49" t="s">
         <v>526</v>
@@ -19707,7 +19762,7 @@
         <v>16</v>
       </c>
       <c r="K160" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L160" s="57"/>
     </row>
@@ -19716,10 +19771,10 @@
         <v>75</v>
       </c>
       <c r="B161" s="51" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="C161" s="51" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="D161" s="49" t="s">
         <v>540</v>
@@ -19739,7 +19794,7 @@
         <v>25</v>
       </c>
       <c r="K161" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L161" s="57"/>
     </row>
@@ -19748,19 +19803,19 @@
         <v>465</v>
       </c>
       <c r="B162" s="46" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="C162" s="46" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="E162" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F162" s="53" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="G162" s="54">
         <v>45384</v>
@@ -19775,17 +19830,17 @@
         <v>138</v>
       </c>
       <c r="K162" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L162" s="57"/>
     </row>
     <row r="163" spans="1:12" ht="22.5" customHeight="1">
       <c r="A163" s="46"/>
       <c r="B163" s="51" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="C163" s="51" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="D163" s="49" t="s">
         <v>540</v>
@@ -19805,7 +19860,7 @@
         <v>16</v>
       </c>
       <c r="K163" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L163" s="57"/>
     </row>
@@ -19814,19 +19869,19 @@
         <v>484</v>
       </c>
       <c r="B164" s="46" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="C164" s="46" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="E164" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F164" s="53" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="G164" s="54">
         <v>45203</v>
@@ -19841,7 +19896,7 @@
         <v>25</v>
       </c>
       <c r="K164" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L164" s="57"/>
     </row>
@@ -19850,13 +19905,13 @@
         <v>558</v>
       </c>
       <c r="B165" s="51" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>448</v>
@@ -19875,7 +19930,7 @@
         <v>25</v>
       </c>
       <c r="K165" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L165" s="57"/>
     </row>
@@ -19884,13 +19939,13 @@
         <v>615</v>
       </c>
       <c r="B166" s="51" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="C166" s="51" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="D166" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E166" s="10" t="s">
         <v>448</v>
@@ -19907,7 +19962,7 @@
         <v>513</v>
       </c>
       <c r="K166" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L166" s="57"/>
     </row>
@@ -19916,13 +19971,13 @@
         <v>648</v>
       </c>
       <c r="B167" s="51" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="C167" s="51" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>448</v>
@@ -19939,7 +19994,7 @@
         <v>25</v>
       </c>
       <c r="K167" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L167" s="57"/>
     </row>
@@ -19948,13 +20003,13 @@
         <v>612</v>
       </c>
       <c r="B168" s="51" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="C168" s="51" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="D168" s="49" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="E168" s="10" t="s">
         <v>448</v>
@@ -19971,7 +20026,7 @@
         <v>16</v>
       </c>
       <c r="K168" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L168" s="57"/>
     </row>
@@ -19980,19 +20035,19 @@
         <v>647</v>
       </c>
       <c r="B169" s="51" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="C169" s="51" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D169" s="10" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F169" s="53" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="G169" s="54">
         <v>44725</v>
@@ -20003,7 +20058,7 @@
         <v>25</v>
       </c>
       <c r="K169" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L169" s="57"/>
     </row>
@@ -20012,10 +20067,10 @@
         <v>51</v>
       </c>
       <c r="B170" s="51" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="C170" s="51" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="D170" s="49" t="s">
         <v>733</v>
@@ -20035,7 +20090,7 @@
         <v>25</v>
       </c>
       <c r="K170" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L170" s="57"/>
     </row>
@@ -20044,10 +20099,10 @@
         <v>45</v>
       </c>
       <c r="B171" s="51" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="C171" s="51" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="D171" s="49" t="s">
         <v>733</v>
@@ -20067,7 +20122,7 @@
         <v>74</v>
       </c>
       <c r="K171" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L171" s="57"/>
     </row>
@@ -20076,13 +20131,13 @@
         <v>445</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="D172" s="62" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="E172" s="63"/>
       <c r="F172" s="64" t="s">
@@ -20096,10 +20151,10 @@
       </c>
       <c r="I172" s="67"/>
       <c r="J172" s="64" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K172" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L172" s="57"/>
     </row>
@@ -20108,13 +20163,13 @@
         <v>468</v>
       </c>
       <c r="B173" s="46" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="C173" s="46" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="D173" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>448</v>
@@ -20135,7 +20190,7 @@
         <v>138</v>
       </c>
       <c r="K173" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L173" s="57"/>
     </row>
@@ -20144,16 +20199,16 @@
         <v>653</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="C174" s="51" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="D174" s="49" t="s">
         <v>733</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="F174" s="53" t="s">
         <v>119</v>
@@ -20167,7 +20222,7 @@
         <v>25</v>
       </c>
       <c r="K174" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L174" s="57"/>
     </row>
@@ -20176,10 +20231,10 @@
         <v>158</v>
       </c>
       <c r="B175" s="51" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="C175" s="51" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="D175" s="49" t="s">
         <v>733</v>
@@ -20199,17 +20254,17 @@
         <v>16</v>
       </c>
       <c r="K175" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L175" s="57"/>
     </row>
     <row r="176" spans="1:12" ht="22.5" customHeight="1">
       <c r="A176" s="46"/>
       <c r="B176" s="51" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="C176" s="51" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="D176" s="49" t="s">
         <v>733</v>
@@ -20233,7 +20288,7 @@
         <v>138</v>
       </c>
       <c r="K176" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L176" s="57"/>
     </row>
@@ -20242,16 +20297,16 @@
         <v>510</v>
       </c>
       <c r="B177" s="51" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="C177" s="51" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="D177" s="49" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="F177" s="53" t="s">
         <v>24</v>
@@ -20265,7 +20320,7 @@
         <v>25</v>
       </c>
       <c r="K177" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L177" s="57"/>
     </row>
@@ -20274,13 +20329,13 @@
         <v>110</v>
       </c>
       <c r="B178" s="51" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="C178" s="51" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="D178" s="10" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="E178" s="10" t="s">
         <v>738</v>
@@ -20295,20 +20350,20 @@
         <v>513</v>
       </c>
       <c r="K178" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L178" s="57"/>
     </row>
     <row r="179" spans="1:12" ht="22.5" customHeight="1">
       <c r="A179" s="46"/>
       <c r="B179" s="51" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="D179" s="10" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>448</v>
@@ -20329,20 +20384,20 @@
         <v>513</v>
       </c>
       <c r="K179" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L179" s="57"/>
     </row>
     <row r="180" spans="1:12" ht="22.5" customHeight="1">
       <c r="A180" s="46"/>
       <c r="B180" s="51" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="C180" s="51" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="D180" s="10" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="E180" s="10" t="s">
         <v>448</v>
@@ -20361,23 +20416,23 @@
         <v>25</v>
       </c>
       <c r="K180" s="51" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L180" s="57"/>
     </row>
     <row r="181" spans="1:12" ht="22.5" customHeight="1">
       <c r="A181" s="46"/>
       <c r="B181" s="46" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="C181" s="46" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="D181" s="10" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="F181" s="53" t="s">
         <v>119</v>
@@ -20387,23 +20442,23 @@
       <c r="I181" s="56"/>
       <c r="J181" s="53"/>
       <c r="K181" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L181" s="57"/>
     </row>
     <row r="182" spans="1:12" ht="22.5" customHeight="1">
       <c r="A182" s="46"/>
       <c r="B182" s="46" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="C182" s="46" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="D182" s="10" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="F182" s="53" t="s">
         <v>106</v>
@@ -20421,17 +20476,17 @@
         <v>74</v>
       </c>
       <c r="K182" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L182" s="57"/>
     </row>
     <row r="183" spans="1:12" ht="22.5" customHeight="1">
       <c r="A183" s="46"/>
       <c r="B183" s="46" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C183" s="46" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="D183" s="49" t="s">
         <v>561</v>
@@ -20455,17 +20510,17 @@
         <v>25</v>
       </c>
       <c r="K183" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L183" s="57"/>
     </row>
     <row r="184" spans="1:12" ht="22.5" customHeight="1">
       <c r="A184" s="46"/>
       <c r="B184" s="46" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="C184" s="46" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="D184" s="49" t="s">
         <v>561</v>
@@ -20489,17 +20544,17 @@
         <v>25</v>
       </c>
       <c r="K184" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L184" s="57"/>
     </row>
     <row r="185" spans="1:12" ht="22.5" customHeight="1">
       <c r="A185" s="46"/>
       <c r="B185" s="46" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="C185" s="46" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="D185" s="49" t="s">
         <v>678</v>
@@ -20523,20 +20578,20 @@
         <v>25</v>
       </c>
       <c r="K185" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L185" s="57"/>
     </row>
     <row r="186" spans="1:12" ht="22.5" customHeight="1">
       <c r="A186" s="46"/>
       <c r="B186" s="46" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="C186" s="46" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="D186" s="49" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="E186" s="10" t="s">
         <v>448</v>
@@ -20557,17 +20612,17 @@
         <v>25</v>
       </c>
       <c r="K186" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L186" s="57"/>
     </row>
     <row r="187" spans="1:12" ht="22.5" customHeight="1">
       <c r="A187" s="46"/>
       <c r="B187" s="46" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="C187" s="46" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="D187" s="49" t="s">
         <v>561</v>
@@ -20587,17 +20642,17 @@
         <v>25</v>
       </c>
       <c r="K187" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L187" s="57"/>
     </row>
     <row r="188" spans="1:12" ht="22.5" customHeight="1">
       <c r="A188" s="46"/>
       <c r="B188" s="1" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="C188" s="46" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="D188" s="49" t="s">
         <v>561</v>
@@ -20617,20 +20672,20 @@
         <v>513</v>
       </c>
       <c r="K188" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L188" s="57"/>
     </row>
     <row r="189" spans="1:12" ht="22.5" customHeight="1">
       <c r="A189" s="46"/>
       <c r="B189" s="9" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="C189" s="46" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="D189" s="49" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>448</v>
@@ -20647,20 +20702,20 @@
         <v>74</v>
       </c>
       <c r="K189" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L189" s="57"/>
     </row>
     <row r="190" spans="1:12" ht="22.5" customHeight="1">
       <c r="A190" s="46"/>
       <c r="B190" s="9" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C190" s="46" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="D190" s="49" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="E190" s="10" t="s">
         <v>448</v>
@@ -20677,20 +20732,20 @@
         <v>25</v>
       </c>
       <c r="K190" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L190" s="57"/>
     </row>
     <row r="191" spans="1:12" ht="22.5" customHeight="1">
       <c r="A191" s="46"/>
       <c r="B191" s="9" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="C191" s="46" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="D191" s="49" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>448</v>
@@ -20704,23 +20759,23 @@
       <c r="H191" s="55"/>
       <c r="I191" s="56"/>
       <c r="J191" s="53" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="K191" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L191" s="57"/>
     </row>
     <row r="192" spans="1:12" ht="22.5" customHeight="1">
       <c r="A192" s="46"/>
       <c r="B192" s="9" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="C192" s="46" t="s">
         <v>410</v>
       </c>
       <c r="D192" s="49" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="E192" s="10" t="s">
         <v>448</v>
@@ -20737,17 +20792,17 @@
         <v>74</v>
       </c>
       <c r="K192" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L192" s="57"/>
     </row>
     <row r="193" spans="1:12" ht="22.5" customHeight="1">
       <c r="A193" s="46"/>
       <c r="B193" s="9" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="C193" s="46" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="D193" s="49" t="s">
         <v>733</v>
@@ -20767,17 +20822,17 @@
         <v>16</v>
       </c>
       <c r="K193" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L193" s="57"/>
     </row>
     <row r="194" spans="1:12" ht="22.5" customHeight="1">
       <c r="A194" s="46"/>
       <c r="B194" s="9" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="C194" s="46" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="D194" s="49" t="s">
         <v>733</v>
@@ -20797,17 +20852,17 @@
         <v>74</v>
       </c>
       <c r="K194" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L194" s="57"/>
     </row>
     <row r="195" spans="1:12" ht="22.5" customHeight="1">
       <c r="A195" s="46"/>
       <c r="B195" s="9" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="C195" s="46" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="D195" s="10"/>
       <c r="E195" s="10" t="s">
@@ -20825,17 +20880,17 @@
         <v>25</v>
       </c>
       <c r="K195" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L195" s="57"/>
     </row>
     <row r="196" spans="1:12" ht="22.5" customHeight="1">
       <c r="A196" s="46"/>
       <c r="B196" s="9" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="C196" s="46" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="D196" s="49" t="s">
         <v>718</v>
@@ -20852,23 +20907,23 @@
       <c r="H196" s="55"/>
       <c r="I196" s="56"/>
       <c r="J196" s="53" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="K196" s="46" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="L196" s="57"/>
     </row>
     <row r="197" spans="1:12" ht="22.5" customHeight="1">
       <c r="A197" s="46"/>
       <c r="B197" s="9" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="C197" s="51" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="D197" s="49" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>448</v>
@@ -20886,13 +20941,13 @@
     <row r="198" spans="1:12" ht="22.5" customHeight="1">
       <c r="A198" s="46"/>
       <c r="B198" s="9" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="C198" s="46" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="D198" s="49" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="E198" s="10" t="s">
         <v>448</v>
@@ -20910,13 +20965,13 @@
     <row r="199" spans="1:12" ht="22.5" customHeight="1">
       <c r="A199" s="46"/>
       <c r="B199" s="9" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="C199" s="46" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="D199" s="49" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>448</v>
@@ -20934,10 +20989,10 @@
     <row r="200" spans="1:12" ht="22.5" customHeight="1">
       <c r="A200" s="46"/>
       <c r="B200" s="9" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="C200" s="46" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="D200" s="10"/>
       <c r="E200" s="10" t="s">
@@ -20956,7 +21011,7 @@
     <row r="201" spans="1:12" ht="22.5" customHeight="1">
       <c r="A201" s="46"/>
       <c r="B201" s="9" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="C201" s="46"/>
       <c r="D201" s="10"/>
@@ -20976,16 +21031,16 @@
     <row r="202" spans="1:12" ht="22.5" customHeight="1">
       <c r="A202" s="46"/>
       <c r="B202" s="9" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="C202" s="46" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D202" s="10" t="s">
         <v>537</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="F202" s="53" t="s">
         <v>119</v>
@@ -21000,13 +21055,13 @@
     <row r="203" spans="1:12" ht="22.5" customHeight="1">
       <c r="A203" s="46"/>
       <c r="B203" s="9" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="C203" s="46" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="D203" s="49" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>448</v>
@@ -21024,10 +21079,10 @@
     <row r="204" spans="1:12" ht="22.5" customHeight="1">
       <c r="A204" s="46"/>
       <c r="B204" s="9" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="C204" s="46" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="D204" s="49" t="s">
         <v>537</v>
@@ -21048,10 +21103,10 @@
     <row r="205" spans="1:12" ht="22.5" customHeight="1">
       <c r="A205" s="46"/>
       <c r="B205" s="9" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="C205" s="46" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="D205" s="10"/>
       <c r="E205" s="10" t="s">
@@ -21070,10 +21125,10 @@
     <row r="206" spans="1:12" ht="22.5" customHeight="1">
       <c r="A206" s="46"/>
       <c r="B206" s="9" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="C206" s="46" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="D206" s="49" t="s">
         <v>733</v>
@@ -21091,21 +21146,111 @@
       <c r="K206" s="46"/>
       <c r="L206" s="46"/>
     </row>
+    <row r="207" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A207" s="46"/>
+      <c r="B207" s="9" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C207" s="46" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D207" s="49" t="s">
+        <v>678</v>
+      </c>
+      <c r="E207" s="10" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F207" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="G207" s="54"/>
+      <c r="H207" s="55"/>
+      <c r="I207" s="56"/>
+      <c r="J207" s="53"/>
+      <c r="K207" s="46"/>
+      <c r="L207" s="46"/>
+    </row>
+    <row r="208" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A208" s="46"/>
+      <c r="B208" s="9" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C208" s="46" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D208" s="49" t="s">
+        <v>561</v>
+      </c>
+      <c r="E208" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F208" s="53"/>
+      <c r="G208" s="54"/>
+      <c r="H208" s="55"/>
+      <c r="I208" s="56"/>
+      <c r="J208" s="53"/>
+      <c r="K208" s="46"/>
+      <c r="L208" s="46"/>
+    </row>
+    <row r="209" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A209" s="46"/>
+      <c r="B209" s="9" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C209" s="46" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D209" s="49" t="s">
+        <v>526</v>
+      </c>
+      <c r="E209" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F209" s="53"/>
+      <c r="G209" s="54"/>
+      <c r="H209" s="55"/>
+      <c r="I209" s="56"/>
+      <c r="J209" s="53"/>
+      <c r="K209" s="46"/>
+      <c r="L209" s="46"/>
+    </row>
+    <row r="210" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A210" s="46"/>
+      <c r="B210" s="9" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C210" s="46" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D210" s="49" t="s">
+        <v>723</v>
+      </c>
+      <c r="E210" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F210" s="53"/>
+      <c r="G210" s="54"/>
+      <c r="H210" s="55"/>
+      <c r="I210" s="56"/>
+      <c r="J210" s="53"/>
+      <c r="K210" s="46"/>
+      <c r="L210" s="46"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="F2:F206" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F210" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"1. Prospección,2. Contacto Inicial,3. Calificación,4. Levantamiento de Requerimientos,5. Visita Técnica / Diagnóstico en Sitio,6. Diseño de Solución / Pre-Ingeniería,7. Estimación / Cotización,8. Propuesta Enviada,9. Aclaraciones / Ajustes de Propuesta,10"&amp;". Negociación,11. Aprobación Interna (Go/No-Go),12. Cierre de Venta (Contrato / OC),13. Kickoff / Inicio de Proyecto,14. Descartado / No Califica,15. En Pausa / Seguimiento Posterior"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G206" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G210" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G2))), AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I206" xr:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I210" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>AND(ISNUMBER(H2),(NOT(OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J206" xr:uid="{00000000-0002-0000-0400-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J210" xr:uid="{00000000-0002-0000-0400-000003000000}">
       <formula1>"Referido (Cliente),Referido (Proveedor/Subcontratista),Referido (Empleado/Interno),Cliente Recurrente (Recompra/Ampliación),Sitio Web (Formulario),Landing Page (Campaña),Chat Web / WhatsApp,SEO (Búsqueda Orgánica),Google Ads (Search),Remarketing (Display/"&amp;"Redes),LinkedIn (Orgánico),Email Outbound (Prospección),Llamada en Frío (Prospección),Visita en Frío (Prospección),Feria / Expo Industrial,Congreso / Cámara / Networking,Webinar / Evento Virtual,Licitación Pública,Licitación Privada (RFP/RFQ),Portal de Co"&amp;"mpras (Cliente),Alianza (Integrador/EPC/Constructor),Partner Tecnológico (Marca/Distribuidor),Directorio B2B / Clúster,Redes Sociales (Facebook/Instagram),YouTube / Contenido Técnico,PR / Medio Especializado,Reactivación de Base de Datos,Otros"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C206 E2:E206 K2:K206" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C210 E2:E210 K2:K210" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -21275,12 +21420,16 @@
     <hyperlink ref="D203" r:id="rId165" xr:uid="{00000000-0004-0000-0400-0000A4000000}"/>
     <hyperlink ref="D204" r:id="rId166" xr:uid="{00000000-0004-0000-0400-0000A5000000}"/>
     <hyperlink ref="D206" r:id="rId167" xr:uid="{00000000-0004-0000-0400-0000A6000000}"/>
+    <hyperlink ref="D207" r:id="rId168" xr:uid="{00000000-0004-0000-0400-0000A7000000}"/>
+    <hyperlink ref="D208" r:id="rId169" xr:uid="{00000000-0004-0000-0400-0000A8000000}"/>
+    <hyperlink ref="D209" r:id="rId170" xr:uid="{00000000-0004-0000-0400-0000A9000000}"/>
+    <hyperlink ref="D210" r:id="rId171" xr:uid="{00000000-0004-0000-0400-0000AA000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
   <tableParts count="1">
-    <tablePart r:id="rId168"/>
+    <tablePart r:id="rId172"/>
   </tableParts>
 </worksheet>
 </file>
@@ -21365,10 +21514,10 @@
         <v>481</v>
       </c>
       <c r="B2" s="69" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1211</v>
+        <v>1223</v>
       </c>
       <c r="D2" s="70"/>
       <c r="E2" s="70"/>
@@ -21388,7 +21537,7 @@
         <v>25</v>
       </c>
       <c r="K2" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="21" customHeight="1">
@@ -21396,10 +21545,10 @@
         <v>484</v>
       </c>
       <c r="B3" s="77" t="s">
-        <v>1213</v>
+        <v>1225</v>
       </c>
       <c r="C3" s="76" t="s">
-        <v>1214</v>
+        <v>1226</v>
       </c>
       <c r="D3" s="70"/>
       <c r="E3" s="70"/>
@@ -21417,7 +21566,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -21425,10 +21574,10 @@
         <v>488</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>1215</v>
+        <v>1227</v>
       </c>
       <c r="C4" s="82" t="s">
-        <v>1216</v>
+        <v>1228</v>
       </c>
       <c r="D4" s="83"/>
       <c r="E4" s="70"/>
@@ -21446,7 +21595,7 @@
         <v>25</v>
       </c>
       <c r="K4" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -21454,10 +21603,10 @@
         <v>491</v>
       </c>
       <c r="B5" s="81" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="C5" s="82" t="s">
-        <v>1218</v>
+        <v>1230</v>
       </c>
       <c r="D5" s="83"/>
       <c r="E5" s="70"/>
@@ -21472,10 +21621,10 @@
       </c>
       <c r="I5" s="87"/>
       <c r="J5" s="90" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K5" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -21483,10 +21632,10 @@
         <v>494</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>1219</v>
+        <v>1231</v>
       </c>
       <c r="C6" s="82" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="D6" s="83"/>
       <c r="E6" s="70"/>
@@ -21504,7 +21653,7 @@
         <v>74</v>
       </c>
       <c r="K6" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -21512,10 +21661,10 @@
         <v>497</v>
       </c>
       <c r="B7" s="77" t="s">
-        <v>1221</v>
+        <v>1233</v>
       </c>
       <c r="C7" s="76" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="D7" s="70"/>
       <c r="E7" s="70"/>
@@ -21531,7 +21680,7 @@
         <v>25</v>
       </c>
       <c r="K7" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -21539,10 +21688,10 @@
         <v>500</v>
       </c>
       <c r="B8" s="77" t="s">
-        <v>1223</v>
+        <v>1235</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>1224</v>
+        <v>1236</v>
       </c>
       <c r="D8" s="70"/>
       <c r="E8" s="70"/>
@@ -21560,7 +21709,7 @@
         <v>74</v>
       </c>
       <c r="K8" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -21568,10 +21717,10 @@
         <v>503</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>1225</v>
+        <v>1237</v>
       </c>
       <c r="C9" s="82" t="s">
-        <v>1226</v>
+        <v>1238</v>
       </c>
       <c r="D9" s="83"/>
       <c r="E9" s="70"/>
@@ -21589,7 +21738,7 @@
         <v>74</v>
       </c>
       <c r="K9" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -21597,10 +21746,10 @@
         <v>506</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>1227</v>
+        <v>1239</v>
       </c>
       <c r="C10" s="76" t="s">
-        <v>1228</v>
+        <v>1240</v>
       </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
@@ -21618,7 +21767,7 @@
         <v>25</v>
       </c>
       <c r="K10" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -21626,10 +21775,10 @@
         <v>514</v>
       </c>
       <c r="B11" s="81" t="s">
-        <v>1229</v>
+        <v>1241</v>
       </c>
       <c r="C11" s="82" t="s">
-        <v>1230</v>
+        <v>1242</v>
       </c>
       <c r="D11" s="83"/>
       <c r="E11" s="70"/>
@@ -21647,7 +21796,7 @@
         <v>74</v>
       </c>
       <c r="K11" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -21655,10 +21804,10 @@
         <v>517</v>
       </c>
       <c r="B12" s="81" t="s">
-        <v>1231</v>
+        <v>1243</v>
       </c>
       <c r="C12" s="82" t="s">
-        <v>1232</v>
+        <v>1244</v>
       </c>
       <c r="D12" s="83"/>
       <c r="E12" s="70"/>
@@ -21676,7 +21825,7 @@
         <v>74</v>
       </c>
       <c r="K12" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -21684,10 +21833,10 @@
         <v>520</v>
       </c>
       <c r="B13" s="77" t="s">
-        <v>1233</v>
+        <v>1245</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>1234</v>
+        <v>1246</v>
       </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
@@ -21705,7 +21854,7 @@
         <v>25</v>
       </c>
       <c r="K13" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -21713,10 +21862,10 @@
         <v>523</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>1235</v>
+        <v>1247</v>
       </c>
       <c r="C14" s="82" t="s">
-        <v>1236</v>
+        <v>1248</v>
       </c>
       <c r="D14" s="83"/>
       <c r="E14" s="70"/>
@@ -21732,7 +21881,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -21740,10 +21889,10 @@
         <v>527</v>
       </c>
       <c r="B15" s="99" t="s">
-        <v>1237</v>
+        <v>1249</v>
       </c>
       <c r="C15" s="82" t="s">
-        <v>1238</v>
+        <v>1250</v>
       </c>
       <c r="D15" s="83"/>
       <c r="E15" s="70"/>
@@ -21761,7 +21910,7 @@
         <v>74</v>
       </c>
       <c r="K15" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
@@ -21769,10 +21918,10 @@
         <v>531</v>
       </c>
       <c r="B16" s="77" t="s">
-        <v>1239</v>
+        <v>1251</v>
       </c>
       <c r="C16" s="76" t="s">
-        <v>1240</v>
+        <v>1252</v>
       </c>
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
@@ -21788,7 +21937,7 @@
         <v>25</v>
       </c>
       <c r="K16" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
@@ -21796,10 +21945,10 @@
         <v>534</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>1241</v>
+        <v>1253</v>
       </c>
       <c r="C17" s="76" t="s">
-        <v>1242</v>
+        <v>1254</v>
       </c>
       <c r="D17" s="70"/>
       <c r="E17" s="70"/>
@@ -21819,7 +21968,7 @@
         <v>25</v>
       </c>
       <c r="K17" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="22.5" customHeight="1">
@@ -21827,10 +21976,10 @@
         <v>538</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1243</v>
+        <v>1255</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1244</v>
+        <v>1256</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="70"/>
@@ -21850,7 +21999,7 @@
         <v>74</v>
       </c>
       <c r="K18" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="22.5" customHeight="1">
@@ -21858,10 +22007,10 @@
         <v>541</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1245</v>
+        <v>1257</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1246</v>
+        <v>1258</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="11"/>
@@ -21881,7 +22030,7 @@
         <v>513</v>
       </c>
       <c r="K19" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="22.5" customHeight="1">
@@ -21889,10 +22038,10 @@
         <v>544</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>1248</v>
+        <v>1260</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -21910,7 +22059,7 @@
         <v>25</v>
       </c>
       <c r="K20" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="22.5" customHeight="1">
@@ -21918,10 +22067,10 @@
         <v>547</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1249</v>
+        <v>1261</v>
       </c>
       <c r="C21" s="76" t="s">
-        <v>1250</v>
+        <v>1262</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -21936,10 +22085,10 @@
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="14" t="s">
-        <v>886</v>
+        <v>744</v>
       </c>
       <c r="K21" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="22.5" customHeight="1">
@@ -21947,10 +22096,10 @@
         <v>552</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1251</v>
+        <v>1263</v>
       </c>
       <c r="C22" s="76" t="s">
-        <v>1252</v>
+        <v>1264</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="11"/>
@@ -21968,7 +22117,7 @@
         <v>551</v>
       </c>
       <c r="K22" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="22.5" customHeight="1">
@@ -21976,10 +22125,10 @@
         <v>555</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1253</v>
+        <v>1265</v>
       </c>
       <c r="C23" s="76" t="s">
-        <v>1254</v>
+        <v>1266</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="11"/>
@@ -21997,7 +22146,7 @@
         <v>551</v>
       </c>
       <c r="K23" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="22.5" customHeight="1">
@@ -22005,10 +22154,10 @@
         <v>558</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1255</v>
+        <v>1267</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>1254</v>
+        <v>1266</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -22026,7 +22175,7 @@
         <v>551</v>
       </c>
       <c r="K24" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="22.5" customHeight="1">
@@ -22034,10 +22183,10 @@
         <v>558</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1256</v>
+        <v>1268</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>1257</v>
+        <v>1269</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="11"/>
@@ -22057,7 +22206,7 @@
         <v>513</v>
       </c>
       <c r="K25" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -22065,10 +22214,10 @@
         <v>558</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1258</v>
+        <v>1270</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>1259</v>
+        <v>1271</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="11"/>
@@ -22088,7 +22237,7 @@
         <v>551</v>
       </c>
       <c r="K26" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="22.5" customHeight="1">
@@ -22096,10 +22245,10 @@
         <v>562</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1260</v>
+        <v>1272</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1261</v>
+        <v>1273</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -22117,7 +22266,7 @@
         <v>513</v>
       </c>
       <c r="K27" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="22.5" customHeight="1">
@@ -22125,10 +22274,10 @@
         <v>565</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>1261</v>
+        <v>1273</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -22146,7 +22295,7 @@
         <v>513</v>
       </c>
       <c r="K28" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="22.5" customHeight="1">
@@ -22154,10 +22303,10 @@
         <v>568</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1263</v>
+        <v>1275</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1264</v>
+        <v>1276</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="11"/>
@@ -22173,7 +22322,7 @@
       <c r="I29" s="45"/>
       <c r="J29" s="14"/>
       <c r="K29" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
   </sheetData>
@@ -22296,10 +22445,10 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1265</v>
+        <v>1277</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1266</v>
+        <v>1278</v>
       </c>
       <c r="D2" s="101"/>
       <c r="E2" s="101" t="s">
@@ -22314,10 +22463,10 @@
       <c r="H2" s="66"/>
       <c r="I2" s="67"/>
       <c r="J2" s="64" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -22325,10 +22474,10 @@
         <v>451</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>1268</v>
+        <v>1280</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>1269</v>
+        <v>1281</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
@@ -22347,10 +22496,10 @@
         <v>0.8</v>
       </c>
       <c r="J3" s="53" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -22358,14 +22507,14 @@
         <v>454</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>1270</v>
+        <v>1282</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>1271</v>
+        <v>1283</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>1272</v>
+        <v>1284</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>449</v>
@@ -22376,10 +22525,10 @@
       <c r="H4" s="61"/>
       <c r="I4" s="56"/>
       <c r="J4" s="53" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -22387,10 +22536,10 @@
         <v>457</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>1273</v>
+        <v>1285</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>1274</v>
+        <v>1286</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
@@ -22412,7 +22561,7 @@
         <v>688</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -22420,10 +22569,10 @@
         <v>668</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>1275</v>
+        <v>1287</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>1276</v>
+        <v>1288</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
@@ -22441,7 +22590,7 @@
         <v>688</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -22449,10 +22598,10 @@
         <v>459</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>1277</v>
+        <v>1289</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>1278</v>
+        <v>1290</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
@@ -22467,10 +22616,10 @@
       <c r="H7" s="61"/>
       <c r="I7" s="56"/>
       <c r="J7" s="53" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -22478,10 +22627,10 @@
         <v>462</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>1279</v>
+        <v>1291</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>1280</v>
+        <v>1292</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
@@ -22499,7 +22648,7 @@
         <v>25</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -22507,14 +22656,14 @@
         <v>465</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>1281</v>
+        <v>1293</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>1282</v>
+        <v>1294</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>1283</v>
+        <v>1295</v>
       </c>
       <c r="F9" s="53" t="s">
         <v>40</v>
@@ -22528,7 +22677,7 @@
         <v>659</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -22536,10 +22685,10 @@
         <v>468</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>1284</v>
+        <v>1296</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>1285</v>
+        <v>1297</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
@@ -22557,7 +22706,7 @@
         <v>659</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -22565,14 +22714,14 @@
         <v>471</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>1286</v>
+        <v>1298</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>1287</v>
+        <v>1299</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10" t="s">
-        <v>1283</v>
+        <v>1295</v>
       </c>
       <c r="F11" s="53" t="s">
         <v>32</v>
@@ -22586,7 +22735,7 @@
         <v>659</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -22594,17 +22743,17 @@
         <v>474</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>1288</v>
+        <v>1300</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>1289</v>
+        <v>1301</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="G12" s="54"/>
       <c r="H12" s="61"/>
@@ -22613,7 +22762,7 @@
         <v>659</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -22621,10 +22770,10 @@
         <v>477</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>1290</v>
+        <v>1302</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>1291</v>
+        <v>1303</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
@@ -22646,7 +22795,7 @@
         <v>659</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -22654,10 +22803,10 @@
         <v>481</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>1290</v>
+        <v>1302</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>1292</v>
+        <v>1304</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10" t="s">
@@ -22674,10 +22823,10 @@
         <v>0.8</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -22685,10 +22834,10 @@
         <v>484</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>1293</v>
+        <v>1305</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>1294</v>
+        <v>1306</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10" t="s">
@@ -22708,10 +22857,10 @@
         <v>488</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>1295</v>
+        <v>1307</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>1296</v>
+        <v>1308</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -22731,7 +22880,7 @@
         <v>659</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
   </sheetData>
@@ -22839,13 +22988,13 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="D2" s="62" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="E2" s="63"/>
       <c r="F2" s="64" t="s">
@@ -22861,10 +23010,10 @@
         <v>0.75</v>
       </c>
       <c r="J2" s="64" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K2" s="104" t="s">
-        <v>1297</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -22872,10 +23021,10 @@
         <v>471</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>1298</v>
+        <v>1310</v>
       </c>
       <c r="C3" s="82" t="s">
-        <v>1299</v>
+        <v>1311</v>
       </c>
       <c r="D3" s="83"/>
       <c r="E3" s="83"/>
@@ -22891,7 +23040,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -23179,10 +23328,10 @@
         <v>474</v>
       </c>
       <c r="B14" s="107" t="s">
-        <v>1300</v>
+        <v>1312</v>
       </c>
       <c r="C14" s="108" t="s">
-        <v>1301</v>
+        <v>1313</v>
       </c>
       <c r="D14" s="109"/>
       <c r="E14" s="109"/>
@@ -23200,7 +23349,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -23490,10 +23639,10 @@
         <v>477</v>
       </c>
       <c r="B25" s="117" t="s">
-        <v>1302</v>
+        <v>1314</v>
       </c>
       <c r="C25" s="118" t="s">
-        <v>1303</v>
+        <v>1315</v>
       </c>
       <c r="D25" s="119"/>
       <c r="E25" s="119"/>
@@ -23511,7 +23660,7 @@
         <v>25</v>
       </c>
       <c r="K25" s="125" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -23809,10 +23958,10 @@
         <v>481</v>
       </c>
       <c r="B36" s="126" t="s">
-        <v>1304</v>
+        <v>1316</v>
       </c>
       <c r="C36" s="127" t="s">
-        <v>1305</v>
+        <v>1317</v>
       </c>
       <c r="D36" s="128"/>
       <c r="E36" s="128"/>
@@ -23828,7 +23977,7 @@
         <v>25</v>
       </c>
       <c r="K36" s="134" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="22.5" customHeight="1">
@@ -23960,7 +24109,7 @@
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16" t="s">
-        <v>1306</v>
+        <v>1318</v>
       </c>
       <c r="D42" s="17"/>
       <c r="E42" s="18"/>
@@ -24035,10 +24184,10 @@
         <v>484</v>
       </c>
       <c r="B46" s="107" t="s">
-        <v>1213</v>
+        <v>1225</v>
       </c>
       <c r="C46" s="108" t="s">
-        <v>1214</v>
+        <v>1226</v>
       </c>
       <c r="D46" s="109"/>
       <c r="E46" s="109"/>
@@ -24056,7 +24205,7 @@
         <v>74</v>
       </c>
       <c r="K46" s="115" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="22.5" customHeight="1">
@@ -24256,10 +24405,10 @@
         <v>488</v>
       </c>
       <c r="B57" s="135" t="s">
-        <v>1215</v>
+        <v>1227</v>
       </c>
       <c r="C57" s="136" t="s">
-        <v>1216</v>
+        <v>1228</v>
       </c>
       <c r="D57" s="137"/>
       <c r="E57" s="137"/>
@@ -24277,7 +24426,7 @@
         <v>25</v>
       </c>
       <c r="K57" s="143" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="22.5" customHeight="1">
@@ -24495,10 +24644,10 @@
         <v>491</v>
       </c>
       <c r="B68" s="107" t="s">
-        <v>1307</v>
+        <v>1319</v>
       </c>
       <c r="C68" s="108" t="s">
-        <v>1308</v>
+        <v>1320</v>
       </c>
       <c r="D68" s="109"/>
       <c r="E68" s="109"/>
@@ -24514,7 +24663,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="115" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="22.5" customHeight="1">
@@ -24730,10 +24879,10 @@
         <v>494</v>
       </c>
       <c r="B79" s="126" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="C79" s="127" t="s">
-        <v>1218</v>
+        <v>1230</v>
       </c>
       <c r="D79" s="128"/>
       <c r="E79" s="128"/>
@@ -24748,10 +24897,10 @@
       </c>
       <c r="I79" s="132"/>
       <c r="J79" s="148" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K79" s="134" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="22.5" customHeight="1">
@@ -24801,10 +24950,10 @@
         <v>497</v>
       </c>
       <c r="B82" s="117" t="s">
-        <v>1309</v>
+        <v>1321</v>
       </c>
       <c r="C82" s="118" t="s">
-        <v>1310</v>
+        <v>1322</v>
       </c>
       <c r="D82" s="119"/>
       <c r="E82" s="119"/>
@@ -24822,7 +24971,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="125" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="22.5" customHeight="1">
@@ -24830,10 +24979,10 @@
         <v>500</v>
       </c>
       <c r="B83" s="126" t="s">
-        <v>1219</v>
+        <v>1231</v>
       </c>
       <c r="C83" s="127" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="D83" s="128"/>
       <c r="E83" s="128"/>
@@ -24851,7 +25000,7 @@
         <v>74</v>
       </c>
       <c r="K83" s="134" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22.5" customHeight="1">
@@ -24859,13 +25008,13 @@
         <v>451</v>
       </c>
       <c r="B84" s="151" t="s">
-        <v>1311</v>
+        <v>1323</v>
       </c>
       <c r="C84" s="151" t="s">
-        <v>1312</v>
+        <v>1324</v>
       </c>
       <c r="D84" s="152" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E84" s="153"/>
       <c r="F84" s="154" t="s">
@@ -24884,7 +25033,7 @@
         <v>25</v>
       </c>
       <c r="K84" s="158" t="s">
-        <v>1313</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="22.5" customHeight="1">
@@ -24892,10 +25041,10 @@
         <v>503</v>
       </c>
       <c r="B85" s="107" t="s">
-        <v>1314</v>
+        <v>1326</v>
       </c>
       <c r="C85" s="108" t="s">
-        <v>1315</v>
+        <v>1327</v>
       </c>
       <c r="D85" s="109"/>
       <c r="E85" s="109"/>
@@ -24913,7 +25062,7 @@
         <v>74</v>
       </c>
       <c r="K85" s="115" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="22.5" customHeight="1">
@@ -24921,10 +25070,10 @@
         <v>506</v>
       </c>
       <c r="B86" s="135" t="s">
-        <v>1316</v>
+        <v>1328</v>
       </c>
       <c r="C86" s="136" t="s">
-        <v>1317</v>
+        <v>1329</v>
       </c>
       <c r="D86" s="137"/>
       <c r="E86" s="137"/>
@@ -24942,7 +25091,7 @@
         <v>74</v>
       </c>
       <c r="K86" s="143" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="22.5" customHeight="1">
@@ -24950,10 +25099,10 @@
         <v>510</v>
       </c>
       <c r="B87" s="108" t="s">
-        <v>1318</v>
+        <v>1330</v>
       </c>
       <c r="C87" s="108" t="s">
-        <v>1319</v>
+        <v>1331</v>
       </c>
       <c r="D87" s="109"/>
       <c r="E87" s="109"/>
@@ -24966,10 +25115,10 @@
       </c>
       <c r="I87" s="113"/>
       <c r="J87" s="160" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K87" s="115" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="22.5" customHeight="1">
@@ -24977,10 +25126,10 @@
         <v>514</v>
       </c>
       <c r="B88" s="135" t="s">
-        <v>1320</v>
+        <v>1332</v>
       </c>
       <c r="C88" s="136" t="s">
-        <v>1321</v>
+        <v>1333</v>
       </c>
       <c r="D88" s="137"/>
       <c r="E88" s="137"/>
@@ -24998,7 +25147,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="143" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="22.5" customHeight="1">
@@ -25006,10 +25155,10 @@
         <v>517</v>
       </c>
       <c r="B89" s="117" t="s">
-        <v>1322</v>
+        <v>1334</v>
       </c>
       <c r="C89" s="118" t="s">
-        <v>1323</v>
+        <v>1335</v>
       </c>
       <c r="D89" s="70"/>
       <c r="E89" s="70"/>
@@ -25027,7 +25176,7 @@
         <v>74</v>
       </c>
       <c r="K89" s="125" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="22.5" customHeight="1">
@@ -25035,10 +25184,10 @@
         <v>520</v>
       </c>
       <c r="B90" s="135" t="s">
-        <v>1324</v>
+        <v>1336</v>
       </c>
       <c r="C90" s="136" t="s">
-        <v>1325</v>
+        <v>1337</v>
       </c>
       <c r="D90" s="83"/>
       <c r="E90" s="83"/>
@@ -25054,7 +25203,7 @@
         <v>74</v>
       </c>
       <c r="K90" s="143" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="22.5" customHeight="1">
@@ -25062,10 +25211,10 @@
         <v>523</v>
       </c>
       <c r="B91" s="77" t="s">
-        <v>1221</v>
+        <v>1233</v>
       </c>
       <c r="C91" s="76" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="D91" s="70"/>
       <c r="E91" s="70"/>
@@ -25081,7 +25230,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="125" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22.5" customHeight="1">
@@ -25089,10 +25238,10 @@
         <v>527</v>
       </c>
       <c r="B92" s="81" t="s">
-        <v>1326</v>
+        <v>1338</v>
       </c>
       <c r="C92" s="82" t="s">
-        <v>1327</v>
+        <v>1339</v>
       </c>
       <c r="D92" s="83"/>
       <c r="E92" s="83"/>
@@ -25110,7 +25259,7 @@
         <v>74</v>
       </c>
       <c r="K92" s="143" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="22.5" customHeight="1">
@@ -25118,10 +25267,10 @@
         <v>531</v>
       </c>
       <c r="B93" s="77" t="s">
-        <v>1328</v>
+        <v>1340</v>
       </c>
       <c r="C93" s="76" t="s">
-        <v>1329</v>
+        <v>1341</v>
       </c>
       <c r="D93" s="70"/>
       <c r="E93" s="70"/>
@@ -25137,7 +25286,7 @@
         <v>74</v>
       </c>
       <c r="K93" s="125" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="22.5" customHeight="1">
@@ -25145,10 +25294,10 @@
         <v>534</v>
       </c>
       <c r="B94" s="81" t="s">
-        <v>1330</v>
+        <v>1342</v>
       </c>
       <c r="C94" s="82" t="s">
-        <v>1331</v>
+        <v>1343</v>
       </c>
       <c r="D94" s="83"/>
       <c r="E94" s="83"/>
@@ -25164,7 +25313,7 @@
         <v>74</v>
       </c>
       <c r="K94" s="143" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="22.5" customHeight="1">
@@ -25172,13 +25321,13 @@
         <v>454</v>
       </c>
       <c r="B95" s="104" t="s">
-        <v>1332</v>
+        <v>1344</v>
       </c>
       <c r="C95" s="104" t="s">
-        <v>1333</v>
+        <v>1345</v>
       </c>
       <c r="D95" s="62" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E95" s="63"/>
       <c r="F95" s="64" t="s">
@@ -25197,7 +25346,7 @@
         <v>16</v>
       </c>
       <c r="K95" s="158" t="s">
-        <v>1297</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="22.5" customHeight="1">
@@ -25205,10 +25354,10 @@
         <v>538</v>
       </c>
       <c r="B96" s="77" t="s">
-        <v>1334</v>
+        <v>1346</v>
       </c>
       <c r="C96" s="76" t="s">
-        <v>1335</v>
+        <v>1347</v>
       </c>
       <c r="D96" s="70"/>
       <c r="E96" s="70"/>
@@ -25224,7 +25373,7 @@
         <v>74</v>
       </c>
       <c r="K96" s="125" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="22.5" customHeight="1">
@@ -25232,10 +25381,10 @@
         <v>541</v>
       </c>
       <c r="B97" s="81" t="s">
-        <v>1336</v>
+        <v>1348</v>
       </c>
       <c r="C97" s="82" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="D97" s="83"/>
       <c r="E97" s="83"/>
@@ -25251,7 +25400,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="22.5" customHeight="1">
@@ -25259,10 +25408,10 @@
         <v>544</v>
       </c>
       <c r="B98" s="77" t="s">
-        <v>1223</v>
+        <v>1235</v>
       </c>
       <c r="C98" s="76" t="s">
-        <v>1224</v>
+        <v>1236</v>
       </c>
       <c r="D98" s="70"/>
       <c r="E98" s="70"/>
@@ -25280,7 +25429,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="22.5" customHeight="1">
@@ -25288,10 +25437,10 @@
         <v>547</v>
       </c>
       <c r="B99" s="81" t="s">
-        <v>1225</v>
+        <v>1237</v>
       </c>
       <c r="C99" s="82" t="s">
-        <v>1226</v>
+        <v>1238</v>
       </c>
       <c r="D99" s="83"/>
       <c r="E99" s="83"/>
@@ -25309,7 +25458,7 @@
         <v>74</v>
       </c>
       <c r="K99" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="22.5" customHeight="1">
@@ -25317,10 +25466,10 @@
         <v>552</v>
       </c>
       <c r="B100" s="77" t="s">
-        <v>1337</v>
+        <v>1349</v>
       </c>
       <c r="C100" s="76" t="s">
-        <v>1338</v>
+        <v>1350</v>
       </c>
       <c r="D100" s="70"/>
       <c r="E100" s="70"/>
@@ -25336,7 +25485,7 @@
         <v>74</v>
       </c>
       <c r="K100" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="22.5" customHeight="1">
@@ -25344,10 +25493,10 @@
         <v>555</v>
       </c>
       <c r="B101" s="81" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
       <c r="C101" s="82" t="s">
-        <v>1340</v>
+        <v>1352</v>
       </c>
       <c r="D101" s="83"/>
       <c r="E101" s="83"/>
@@ -25363,7 +25512,7 @@
         <v>74</v>
       </c>
       <c r="K101" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="22.5" customHeight="1">
@@ -25371,10 +25520,10 @@
         <v>558</v>
       </c>
       <c r="B102" s="77" t="s">
-        <v>1341</v>
+        <v>1353</v>
       </c>
       <c r="C102" s="76" t="s">
-        <v>1342</v>
+        <v>1354</v>
       </c>
       <c r="D102" s="70"/>
       <c r="E102" s="70"/>
@@ -25390,7 +25539,7 @@
         <v>74</v>
       </c>
       <c r="K102" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="22.5" customHeight="1">
@@ -25398,10 +25547,10 @@
         <v>562</v>
       </c>
       <c r="B103" s="81" t="s">
-        <v>1343</v>
+        <v>1355</v>
       </c>
       <c r="C103" s="82" t="s">
-        <v>1344</v>
+        <v>1356</v>
       </c>
       <c r="D103" s="83"/>
       <c r="E103" s="83"/>
@@ -25417,7 +25566,7 @@
         <v>74</v>
       </c>
       <c r="K103" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="22.5" customHeight="1">
@@ -25425,10 +25574,10 @@
         <v>565</v>
       </c>
       <c r="B104" s="76" t="s">
-        <v>1227</v>
+        <v>1239</v>
       </c>
       <c r="C104" s="76" t="s">
-        <v>1228</v>
+        <v>1240</v>
       </c>
       <c r="D104" s="70"/>
       <c r="E104" s="70"/>
@@ -25446,7 +25595,7 @@
         <v>25</v>
       </c>
       <c r="K104" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="22.5" customHeight="1">
@@ -25454,10 +25603,10 @@
         <v>568</v>
       </c>
       <c r="B105" s="81" t="s">
-        <v>1345</v>
+        <v>1357</v>
       </c>
       <c r="C105" s="82" t="s">
-        <v>1211</v>
+        <v>1223</v>
       </c>
       <c r="D105" s="83"/>
       <c r="E105" s="83"/>
@@ -25475,7 +25624,7 @@
         <v>74</v>
       </c>
       <c r="K105" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="22.5" customHeight="1">
@@ -25483,10 +25632,10 @@
         <v>457</v>
       </c>
       <c r="B106" s="104" t="s">
-        <v>1346</v>
+        <v>1358</v>
       </c>
       <c r="C106" s="104" t="s">
-        <v>1347</v>
+        <v>1359</v>
       </c>
       <c r="D106" s="62" t="s">
         <v>540</v>
@@ -25505,10 +25654,10 @@
         <v>0.9</v>
       </c>
       <c r="J106" s="64" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="K106" s="104" t="s">
-        <v>1348</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="22.5" customHeight="1">
@@ -25516,10 +25665,10 @@
         <v>571</v>
       </c>
       <c r="B107" s="77" t="s">
-        <v>1349</v>
+        <v>1361</v>
       </c>
       <c r="C107" s="76" t="s">
-        <v>1350</v>
+        <v>1362</v>
       </c>
       <c r="D107" s="70"/>
       <c r="E107" s="70"/>
@@ -25535,7 +25684,7 @@
         <v>25</v>
       </c>
       <c r="K107" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="22.5" customHeight="1">
@@ -25543,10 +25692,10 @@
         <v>574</v>
       </c>
       <c r="B108" s="81" t="s">
-        <v>1351</v>
+        <v>1363</v>
       </c>
       <c r="C108" s="82" t="s">
-        <v>1352</v>
+        <v>1364</v>
       </c>
       <c r="D108" s="83"/>
       <c r="E108" s="83"/>
@@ -25562,7 +25711,7 @@
         <v>74</v>
       </c>
       <c r="K108" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="22.5" customHeight="1">
@@ -25570,10 +25719,10 @@
         <v>576</v>
       </c>
       <c r="B109" s="77" t="s">
-        <v>1353</v>
+        <v>1365</v>
       </c>
       <c r="C109" s="76" t="s">
-        <v>1354</v>
+        <v>1366</v>
       </c>
       <c r="D109" s="70"/>
       <c r="E109" s="70"/>
@@ -25591,7 +25740,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="22.5" customHeight="1">
@@ -25599,10 +25748,10 @@
         <v>579</v>
       </c>
       <c r="B110" s="81" t="s">
-        <v>1355</v>
+        <v>1367</v>
       </c>
       <c r="C110" s="82" t="s">
-        <v>1356</v>
+        <v>1368</v>
       </c>
       <c r="D110" s="83"/>
       <c r="E110" s="83"/>
@@ -25618,7 +25767,7 @@
         <v>74</v>
       </c>
       <c r="K110" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="22.5" customHeight="1">
@@ -25626,10 +25775,10 @@
         <v>582</v>
       </c>
       <c r="B111" s="77" t="s">
-        <v>1357</v>
+        <v>1369</v>
       </c>
       <c r="C111" s="76" t="s">
-        <v>1358</v>
+        <v>1370</v>
       </c>
       <c r="D111" s="70"/>
       <c r="E111" s="70"/>
@@ -25645,7 +25794,7 @@
         <v>74</v>
       </c>
       <c r="K111" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="22.5" customHeight="1">
@@ -25653,10 +25802,10 @@
         <v>585</v>
       </c>
       <c r="B112" s="81" t="s">
-        <v>1359</v>
+        <v>1371</v>
       </c>
       <c r="C112" s="82" t="s">
-        <v>1360</v>
+        <v>1372</v>
       </c>
       <c r="D112" s="83"/>
       <c r="E112" s="83"/>
@@ -25672,7 +25821,7 @@
         <v>74</v>
       </c>
       <c r="K112" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="22.5" customHeight="1">
@@ -25680,10 +25829,10 @@
         <v>588</v>
       </c>
       <c r="B113" s="77" t="s">
-        <v>1361</v>
+        <v>1373</v>
       </c>
       <c r="C113" s="76" t="s">
-        <v>1362</v>
+        <v>1374</v>
       </c>
       <c r="D113" s="70"/>
       <c r="E113" s="70"/>
@@ -25699,7 +25848,7 @@
         <v>74</v>
       </c>
       <c r="K113" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="22.5" customHeight="1">
@@ -25707,10 +25856,10 @@
         <v>591</v>
       </c>
       <c r="B114" s="81" t="s">
-        <v>1363</v>
+        <v>1375</v>
       </c>
       <c r="C114" s="82" t="s">
-        <v>1364</v>
+        <v>1376</v>
       </c>
       <c r="D114" s="83"/>
       <c r="E114" s="83"/>
@@ -25726,7 +25875,7 @@
         <v>74</v>
       </c>
       <c r="K114" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="22.5" customHeight="1">
@@ -25734,7 +25883,7 @@
         <v>594</v>
       </c>
       <c r="B115" s="77" t="s">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="C115" s="76" t="s">
         <v>391</v>
@@ -25753,7 +25902,7 @@
         <v>74</v>
       </c>
       <c r="K115" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="22.5" customHeight="1">
@@ -25761,10 +25910,10 @@
         <v>597</v>
       </c>
       <c r="B116" s="81" t="s">
-        <v>1366</v>
+        <v>1378</v>
       </c>
       <c r="C116" s="82" t="s">
-        <v>1367</v>
+        <v>1379</v>
       </c>
       <c r="D116" s="83"/>
       <c r="E116" s="83"/>
@@ -25780,7 +25929,7 @@
         <v>74</v>
       </c>
       <c r="K116" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="22.5" customHeight="1">
@@ -25788,17 +25937,17 @@
         <v>668</v>
       </c>
       <c r="B117" s="104" t="s">
-        <v>1368</v>
+        <v>1380</v>
       </c>
       <c r="C117" s="104" t="s">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="D117" s="62" t="s">
         <v>540</v>
       </c>
       <c r="E117" s="63"/>
       <c r="F117" s="64" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="G117" s="103">
         <v>45976</v>
@@ -25810,10 +25959,10 @@
         <v>0.85</v>
       </c>
       <c r="J117" s="64" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="K117" s="104" t="s">
-        <v>1313</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="22.5" customHeight="1">
@@ -25821,10 +25970,10 @@
         <v>600</v>
       </c>
       <c r="B118" s="77" t="s">
-        <v>1370</v>
+        <v>1382</v>
       </c>
       <c r="C118" s="76" t="s">
-        <v>1371</v>
+        <v>1383</v>
       </c>
       <c r="D118" s="70"/>
       <c r="E118" s="70"/>
@@ -25840,7 +25989,7 @@
         <v>74</v>
       </c>
       <c r="K118" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="22.5" customHeight="1">
@@ -25848,10 +25997,10 @@
         <v>603</v>
       </c>
       <c r="B119" s="81" t="s">
-        <v>1229</v>
+        <v>1241</v>
       </c>
       <c r="C119" s="82" t="s">
-        <v>1230</v>
+        <v>1242</v>
       </c>
       <c r="D119" s="83"/>
       <c r="E119" s="83"/>
@@ -25869,7 +26018,7 @@
         <v>74</v>
       </c>
       <c r="K119" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="22.5" customHeight="1">
@@ -25877,10 +26026,10 @@
         <v>606</v>
       </c>
       <c r="B120" s="77" t="s">
-        <v>1372</v>
+        <v>1384</v>
       </c>
       <c r="C120" s="76" t="s">
-        <v>1373</v>
+        <v>1385</v>
       </c>
       <c r="D120" s="70"/>
       <c r="E120" s="70"/>
@@ -25898,7 +26047,7 @@
         <v>74</v>
       </c>
       <c r="K120" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="22.5" customHeight="1">
@@ -25906,10 +26055,10 @@
         <v>609</v>
       </c>
       <c r="B121" s="81" t="s">
-        <v>1374</v>
+        <v>1386</v>
       </c>
       <c r="C121" s="82" t="s">
-        <v>1375</v>
+        <v>1387</v>
       </c>
       <c r="D121" s="83"/>
       <c r="E121" s="83"/>
@@ -25925,7 +26074,7 @@
         <v>74</v>
       </c>
       <c r="K121" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="22.5" customHeight="1">
@@ -25933,10 +26082,10 @@
         <v>612</v>
       </c>
       <c r="B122" s="77" t="s">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="C122" s="76" t="s">
-        <v>1377</v>
+        <v>1389</v>
       </c>
       <c r="D122" s="70"/>
       <c r="E122" s="70"/>
@@ -25952,7 +26101,7 @@
         <v>74</v>
       </c>
       <c r="K122" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="22.5" customHeight="1">
@@ -25960,10 +26109,10 @@
         <v>615</v>
       </c>
       <c r="B123" s="81" t="s">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="C123" s="82" t="s">
-        <v>1379</v>
+        <v>1391</v>
       </c>
       <c r="D123" s="83"/>
       <c r="E123" s="83"/>
@@ -25979,7 +26128,7 @@
         <v>74</v>
       </c>
       <c r="K123" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="22.5" customHeight="1">
@@ -25987,10 +26136,10 @@
         <v>618</v>
       </c>
       <c r="B124" s="77" t="s">
-        <v>1380</v>
+        <v>1392</v>
       </c>
       <c r="C124" s="76" t="s">
-        <v>1381</v>
+        <v>1393</v>
       </c>
       <c r="D124" s="70"/>
       <c r="E124" s="70"/>
@@ -26008,7 +26157,7 @@
         <v>25</v>
       </c>
       <c r="K124" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="22.5" customHeight="1">
@@ -26016,10 +26165,10 @@
         <v>621</v>
       </c>
       <c r="B125" s="81" t="s">
-        <v>1382</v>
+        <v>1394</v>
       </c>
       <c r="C125" s="82" t="s">
-        <v>1383</v>
+        <v>1395</v>
       </c>
       <c r="D125" s="83"/>
       <c r="E125" s="83"/>
@@ -26035,7 +26184,7 @@
         <v>25</v>
       </c>
       <c r="K125" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="22.5" customHeight="1">
@@ -26043,10 +26192,10 @@
         <v>624</v>
       </c>
       <c r="B126" s="77" t="s">
-        <v>1384</v>
+        <v>1396</v>
       </c>
       <c r="C126" s="76" t="s">
-        <v>1385</v>
+        <v>1397</v>
       </c>
       <c r="D126" s="70"/>
       <c r="E126" s="70"/>
@@ -26062,7 +26211,7 @@
         <v>74</v>
       </c>
       <c r="K126" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="22.5" customHeight="1">
@@ -26070,10 +26219,10 @@
         <v>627</v>
       </c>
       <c r="B127" s="81" t="s">
-        <v>1386</v>
+        <v>1398</v>
       </c>
       <c r="C127" s="82" t="s">
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="D127" s="83"/>
       <c r="E127" s="83"/>
@@ -26089,7 +26238,7 @@
         <v>74</v>
       </c>
       <c r="K127" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="22.5" customHeight="1">
@@ -26097,10 +26246,10 @@
         <v>459</v>
       </c>
       <c r="B128" s="104" t="s">
-        <v>1388</v>
+        <v>1400</v>
       </c>
       <c r="C128" s="104" t="s">
-        <v>1389</v>
+        <v>1401</v>
       </c>
       <c r="D128" s="62" t="s">
         <v>540</v>
@@ -26119,10 +26268,10 @@
         <v>0.5</v>
       </c>
       <c r="J128" s="64" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="K128" s="104" t="s">
-        <v>1348</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="22.5" customHeight="1">
@@ -26130,10 +26279,10 @@
         <v>630</v>
       </c>
       <c r="B129" s="77" t="s">
-        <v>1390</v>
+        <v>1402</v>
       </c>
       <c r="C129" s="76" t="s">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="D129" s="70"/>
       <c r="E129" s="70"/>
@@ -26149,7 +26298,7 @@
         <v>74</v>
       </c>
       <c r="K129" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="22.5" customHeight="1">
@@ -26157,10 +26306,10 @@
         <v>633</v>
       </c>
       <c r="B130" s="81" t="s">
-        <v>1392</v>
+        <v>1404</v>
       </c>
       <c r="C130" s="82" t="s">
-        <v>1393</v>
+        <v>1405</v>
       </c>
       <c r="D130" s="83"/>
       <c r="E130" s="83"/>
@@ -26178,7 +26327,7 @@
         <v>74</v>
       </c>
       <c r="K130" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="22.5" customHeight="1">
@@ -26186,10 +26335,10 @@
         <v>636</v>
       </c>
       <c r="B131" s="77" t="s">
-        <v>1394</v>
+        <v>1406</v>
       </c>
       <c r="C131" s="76" t="s">
-        <v>1395</v>
+        <v>1407</v>
       </c>
       <c r="D131" s="70"/>
       <c r="E131" s="70"/>
@@ -26205,7 +26354,7 @@
         <v>74</v>
       </c>
       <c r="K131" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="22.5" customHeight="1">
@@ -26213,10 +26362,10 @@
         <v>637</v>
       </c>
       <c r="B132" s="81" t="s">
-        <v>1231</v>
+        <v>1243</v>
       </c>
       <c r="C132" s="82" t="s">
-        <v>1232</v>
+        <v>1244</v>
       </c>
       <c r="D132" s="83"/>
       <c r="E132" s="83"/>
@@ -26234,7 +26383,7 @@
         <v>74</v>
       </c>
       <c r="K132" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="22.5" customHeight="1">
@@ -26242,10 +26391,10 @@
         <v>638</v>
       </c>
       <c r="B133" s="77" t="s">
-        <v>1233</v>
+        <v>1245</v>
       </c>
       <c r="C133" s="76" t="s">
-        <v>1234</v>
+        <v>1246</v>
       </c>
       <c r="D133" s="70"/>
       <c r="E133" s="70"/>
@@ -26263,7 +26412,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="22.5" customHeight="1">
@@ -26271,10 +26420,10 @@
         <v>639</v>
       </c>
       <c r="B134" s="81" t="s">
-        <v>1396</v>
+        <v>1408</v>
       </c>
       <c r="C134" s="82" t="s">
-        <v>1397</v>
+        <v>1409</v>
       </c>
       <c r="D134" s="83"/>
       <c r="E134" s="83"/>
@@ -26290,7 +26439,7 @@
         <v>25</v>
       </c>
       <c r="K134" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="22.5" customHeight="1">
@@ -26298,10 +26447,10 @@
         <v>640</v>
       </c>
       <c r="B135" s="77" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="C135" s="76" t="s">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="D135" s="70"/>
       <c r="E135" s="70"/>
@@ -26319,7 +26468,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="22.5" customHeight="1">
@@ -26327,10 +26476,10 @@
         <v>641</v>
       </c>
       <c r="B136" s="81" t="s">
-        <v>1235</v>
+        <v>1247</v>
       </c>
       <c r="C136" s="82" t="s">
-        <v>1236</v>
+        <v>1248</v>
       </c>
       <c r="D136" s="83"/>
       <c r="E136" s="83"/>
@@ -26346,7 +26495,7 @@
         <v>74</v>
       </c>
       <c r="K136" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="22.5" customHeight="1">
@@ -26354,10 +26503,10 @@
         <v>642</v>
       </c>
       <c r="B137" s="77" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="C137" s="76" t="s">
-        <v>1401</v>
+        <v>1413</v>
       </c>
       <c r="D137" s="70"/>
       <c r="E137" s="70"/>
@@ -26373,7 +26522,7 @@
         <v>74</v>
       </c>
       <c r="K137" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="22.5" customHeight="1">
@@ -26381,10 +26530,10 @@
         <v>643</v>
       </c>
       <c r="B138" s="81" t="s">
-        <v>1402</v>
+        <v>1414</v>
       </c>
       <c r="C138" s="82" t="s">
-        <v>1238</v>
+        <v>1250</v>
       </c>
       <c r="D138" s="83"/>
       <c r="E138" s="83"/>
@@ -26402,7 +26551,7 @@
         <v>74</v>
       </c>
       <c r="K138" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="22.5" customHeight="1">
@@ -26410,13 +26559,13 @@
         <v>462</v>
       </c>
       <c r="B139" s="104" t="s">
-        <v>1403</v>
+        <v>1415</v>
       </c>
       <c r="C139" s="104" t="s">
-        <v>1404</v>
+        <v>1416</v>
       </c>
       <c r="D139" s="62" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E139" s="63"/>
       <c r="F139" s="64" t="s">
@@ -26435,7 +26584,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="104" t="s">
-        <v>1297</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="22.5" customHeight="1">
@@ -26443,10 +26592,10 @@
         <v>644</v>
       </c>
       <c r="B140" s="81" t="s">
-        <v>1405</v>
+        <v>1417</v>
       </c>
       <c r="C140" s="82" t="s">
-        <v>1406</v>
+        <v>1418</v>
       </c>
       <c r="D140" s="83"/>
       <c r="E140" s="83"/>
@@ -26464,7 +26613,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="22.5" customHeight="1">
@@ -26472,10 +26621,10 @@
         <v>645</v>
       </c>
       <c r="B141" s="77" t="s">
-        <v>1407</v>
+        <v>1419</v>
       </c>
       <c r="C141" s="76" t="s">
-        <v>1408</v>
+        <v>1420</v>
       </c>
       <c r="D141" s="70"/>
       <c r="E141" s="70"/>
@@ -26491,7 +26640,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="22.5" customHeight="1">
@@ -26499,10 +26648,10 @@
         <v>646</v>
       </c>
       <c r="B142" s="81" t="s">
-        <v>1409</v>
+        <v>1421</v>
       </c>
       <c r="C142" s="82" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="D142" s="83"/>
       <c r="E142" s="83"/>
@@ -26518,7 +26667,7 @@
         <v>74</v>
       </c>
       <c r="K142" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="22.5" customHeight="1">
@@ -26526,10 +26675,10 @@
         <v>647</v>
       </c>
       <c r="B143" s="77" t="s">
-        <v>1410</v>
+        <v>1422</v>
       </c>
       <c r="C143" s="76" t="s">
-        <v>1411</v>
+        <v>1423</v>
       </c>
       <c r="D143" s="70"/>
       <c r="E143" s="70"/>
@@ -26545,7 +26694,7 @@
         <v>74</v>
       </c>
       <c r="K143" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="22.5" customHeight="1">
@@ -26553,10 +26702,10 @@
         <v>648</v>
       </c>
       <c r="B144" s="81" t="s">
-        <v>1412</v>
+        <v>1424</v>
       </c>
       <c r="C144" s="82" t="s">
-        <v>1413</v>
+        <v>1425</v>
       </c>
       <c r="D144" s="83"/>
       <c r="E144" s="83"/>
@@ -26572,7 +26721,7 @@
         <v>74</v>
       </c>
       <c r="K144" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="22.5" customHeight="1">
@@ -26580,10 +26729,10 @@
         <v>649</v>
       </c>
       <c r="B145" s="77" t="s">
-        <v>1414</v>
+        <v>1426</v>
       </c>
       <c r="C145" s="76" t="s">
-        <v>1415</v>
+        <v>1427</v>
       </c>
       <c r="D145" s="70"/>
       <c r="E145" s="70"/>
@@ -26599,7 +26748,7 @@
         <v>25</v>
       </c>
       <c r="K145" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="22.5" customHeight="1">
@@ -26607,10 +26756,10 @@
         <v>650</v>
       </c>
       <c r="B146" s="81" t="s">
-        <v>1416</v>
+        <v>1428</v>
       </c>
       <c r="C146" s="82" t="s">
-        <v>1417</v>
+        <v>1429</v>
       </c>
       <c r="D146" s="83"/>
       <c r="E146" s="83"/>
@@ -26626,7 +26775,7 @@
         <v>74</v>
       </c>
       <c r="K146" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="22.5" customHeight="1">
@@ -26634,10 +26783,10 @@
         <v>651</v>
       </c>
       <c r="B147" s="77" t="s">
-        <v>1418</v>
+        <v>1430</v>
       </c>
       <c r="C147" s="76" t="s">
-        <v>1419</v>
+        <v>1431</v>
       </c>
       <c r="D147" s="70"/>
       <c r="E147" s="70"/>
@@ -26653,7 +26802,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="22.5" customHeight="1">
@@ -26661,10 +26810,10 @@
         <v>652</v>
       </c>
       <c r="B148" s="81" t="s">
-        <v>1420</v>
+        <v>1432</v>
       </c>
       <c r="C148" s="82" t="s">
-        <v>1421</v>
+        <v>1433</v>
       </c>
       <c r="D148" s="83"/>
       <c r="E148" s="83"/>
@@ -26680,7 +26829,7 @@
         <v>74</v>
       </c>
       <c r="K148" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="22.5" customHeight="1">
@@ -26688,10 +26837,10 @@
         <v>653</v>
       </c>
       <c r="B149" s="77" t="s">
-        <v>1422</v>
+        <v>1434</v>
       </c>
       <c r="C149" s="76" t="s">
-        <v>1423</v>
+        <v>1435</v>
       </c>
       <c r="D149" s="70"/>
       <c r="E149" s="70"/>
@@ -26707,7 +26856,7 @@
         <v>74</v>
       </c>
       <c r="K149" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="22.5" customHeight="1">
@@ -26715,11 +26864,11 @@
         <v>465</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1424</v>
+        <v>1436</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="166" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E150" s="167"/>
       <c r="F150" s="168"/>
@@ -26734,10 +26883,10 @@
         <v>654</v>
       </c>
       <c r="B151" s="82" t="s">
-        <v>1425</v>
+        <v>1437</v>
       </c>
       <c r="C151" s="82" t="s">
-        <v>1426</v>
+        <v>1438</v>
       </c>
       <c r="D151" s="83"/>
       <c r="E151" s="83"/>
@@ -26750,21 +26899,21 @@
       </c>
       <c r="I151" s="87"/>
       <c r="J151" s="90" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="K151" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="22.5" customHeight="1">
       <c r="A152" s="8" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B152" s="77" t="s">
-        <v>1427</v>
+        <v>1439</v>
       </c>
       <c r="C152" s="76" t="s">
-        <v>1428</v>
+        <v>1440</v>
       </c>
       <c r="D152" s="70"/>
       <c r="E152" s="70"/>
@@ -26780,18 +26929,18 @@
         <v>25</v>
       </c>
       <c r="K152" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="22.5" customHeight="1">
       <c r="A153" s="8" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B153" s="81" t="s">
-        <v>1429</v>
+        <v>1441</v>
       </c>
       <c r="C153" s="82" t="s">
-        <v>1430</v>
+        <v>1442</v>
       </c>
       <c r="D153" s="83"/>
       <c r="E153" s="83"/>
@@ -26807,18 +26956,18 @@
         <v>74</v>
       </c>
       <c r="K153" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="22.5" customHeight="1">
       <c r="A154" s="8" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B154" s="77" t="s">
-        <v>1239</v>
+        <v>1251</v>
       </c>
       <c r="C154" s="76" t="s">
-        <v>1240</v>
+        <v>1252</v>
       </c>
       <c r="D154" s="70"/>
       <c r="E154" s="70"/>
@@ -26834,18 +26983,18 @@
         <v>25</v>
       </c>
       <c r="K154" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="22.5" customHeight="1">
       <c r="A155" s="8" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B155" s="81" t="s">
-        <v>1431</v>
+        <v>1443</v>
       </c>
       <c r="C155" s="82" t="s">
-        <v>1432</v>
+        <v>1444</v>
       </c>
       <c r="D155" s="83"/>
       <c r="E155" s="83"/>
@@ -26863,18 +27012,18 @@
         <v>25</v>
       </c>
       <c r="K155" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="22.5" customHeight="1">
       <c r="A156" s="8" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B156" s="76" t="s">
-        <v>1433</v>
+        <v>1445</v>
       </c>
       <c r="C156" s="76" t="s">
-        <v>1434</v>
+        <v>1446</v>
       </c>
       <c r="D156" s="70"/>
       <c r="E156" s="70"/>
@@ -26890,18 +27039,18 @@
         <v>513</v>
       </c>
       <c r="K156" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="22.5" customHeight="1">
       <c r="A157" s="8" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B157" s="81" t="s">
-        <v>1435</v>
+        <v>1447</v>
       </c>
       <c r="C157" s="82" t="s">
-        <v>1436</v>
+        <v>1448</v>
       </c>
       <c r="D157" s="83"/>
       <c r="E157" s="83"/>
@@ -26919,18 +27068,18 @@
         <v>74</v>
       </c>
       <c r="K157" s="82" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="22.5" customHeight="1">
       <c r="A158" s="8" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B158" s="76" t="s">
-        <v>1241</v>
+        <v>1253</v>
       </c>
       <c r="C158" s="76" t="s">
-        <v>1242</v>
+        <v>1254</v>
       </c>
       <c r="D158" s="70"/>
       <c r="E158" s="70"/>
@@ -26948,18 +27097,18 @@
         <v>25</v>
       </c>
       <c r="K158" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="22.5" customHeight="1">
       <c r="A159" s="8" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B159" s="77" t="s">
-        <v>1437</v>
+        <v>1449</v>
       </c>
       <c r="C159" s="76" t="s">
-        <v>1438</v>
+        <v>1450</v>
       </c>
       <c r="D159" s="10"/>
       <c r="E159" s="11"/>
@@ -26975,18 +27124,18 @@
         <v>25</v>
       </c>
       <c r="K159" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="22.5" customHeight="1">
       <c r="A160" s="8" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B160" s="77" t="s">
-        <v>1439</v>
+        <v>1451</v>
       </c>
       <c r="C160" s="76" t="s">
-        <v>1440</v>
+        <v>1452</v>
       </c>
       <c r="D160" s="10"/>
       <c r="E160" s="11"/>
@@ -27002,7 +27151,7 @@
         <v>25</v>
       </c>
       <c r="K160" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="22.5" customHeight="1">
@@ -27012,7 +27161,7 @@
       <c r="B161" s="9"/>
       <c r="C161" s="5"/>
       <c r="D161" s="62" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E161" s="167"/>
       <c r="F161" s="102"/>
@@ -27024,13 +27173,13 @@
     </row>
     <row r="162" spans="1:11" ht="22.5" customHeight="1">
       <c r="A162" s="8" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>1243</v>
+        <v>1255</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>1441</v>
+        <v>1453</v>
       </c>
       <c r="D162" s="10"/>
       <c r="E162" s="11"/>
@@ -27048,18 +27197,18 @@
         <v>74</v>
       </c>
       <c r="K162" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="22.5" customHeight="1">
       <c r="A163" s="8" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>1248</v>
+        <v>1260</v>
       </c>
       <c r="D163" s="10"/>
       <c r="E163" s="11"/>
@@ -27077,18 +27226,18 @@
         <v>25</v>
       </c>
       <c r="K163" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="22.5" customHeight="1">
       <c r="A164" s="8" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>1249</v>
+        <v>1261</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>1250</v>
+        <v>1262</v>
       </c>
       <c r="D164" s="10"/>
       <c r="E164" s="11"/>
@@ -27103,21 +27252,21 @@
       </c>
       <c r="I164" s="13"/>
       <c r="J164" s="14" t="s">
-        <v>886</v>
+        <v>744</v>
       </c>
       <c r="K164" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="22.5" customHeight="1">
       <c r="A165" s="8" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>1251</v>
+        <v>1263</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>1252</v>
+        <v>1264</v>
       </c>
       <c r="D165" s="10"/>
       <c r="E165" s="11"/>
@@ -27135,7 +27284,7 @@
         <v>551</v>
       </c>
       <c r="K165" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="22.5" customHeight="1">
@@ -27172,10 +27321,10 @@
         <v>11</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>1253</v>
+        <v>1265</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>1254</v>
+        <v>1266</v>
       </c>
       <c r="D167" s="10"/>
       <c r="E167" s="11"/>
@@ -27193,7 +27342,7 @@
         <v>551</v>
       </c>
       <c r="K167" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="22.5" customHeight="1">
@@ -27230,10 +27379,10 @@
         <v>18</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>1255</v>
+        <v>1267</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>1254</v>
+        <v>1266</v>
       </c>
       <c r="D169" s="10"/>
       <c r="E169" s="11"/>
@@ -27251,7 +27400,7 @@
         <v>551</v>
       </c>
       <c r="K169" s="76" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="22.5" customHeight="1">
@@ -28803,10 +28952,10 @@
     <row r="248" spans="1:11" ht="22.5" customHeight="1">
       <c r="A248" s="46"/>
       <c r="B248" s="9" t="s">
-        <v>1442</v>
+        <v>1454</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="D248" s="10"/>
       <c r="E248" s="48" t="s">

--- a/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
+++ b/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlando.carvajal.DESMEX\Desktop\ClaudeCode\Pipeline1\pipeline-web\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38E98AEC-00CE-4B50-9567-294C54201CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06111943-CD1E-4FE6-9C9F-BA263163C4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,13 +22,13 @@
     <sheet name="Copia seguridad 27-01-2026" sheetId="9" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$L$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$L$213</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Copia seguridad 27-01-2026'!$A$1:$K$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Daniela Lara'!$A$1:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Josué Morales'!$A$1:$K$148</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Marco Flores'!$A$1:$K$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rebeca Ortiz'!$A$1:$K$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Saira Gómez'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Saira Gómez'!$A$1:$K$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,11 +50,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={5de07d34-5d4a-43f1-b491-846ecd35ea4b}</author>
-    <author>tc={bce944ed-64d8-421b-abdb-8ef4241df362}</author>
+    <author>tc={e486e15b-6e62-4266-9919-8644122bfe6b}</author>
+    <author>tc={c7ed0c02-4231-43e4-b355-89166dd53e3e}</author>
   </authors>
   <commentList>
-    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{5DE07D34-5D4A-43F1-B491-846ECD35EA4B}">
+    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{E486E15B-6E62-4266-9919-8644122BFE6B}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -62,7 +62,7 @@
     ya lo tiene en seguimiento Josué</t>
       </text>
     </comment>
-    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{BCE944ED-64D8-421B-ABDB-8EF4241DF362}">
+    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{C7ED0C02-4231-43E4-B355-89166DD53E3E}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4751" uniqueCount="1456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4782" uniqueCount="1467">
   <si>
     <t>ID de Prospecto</t>
   </si>
@@ -2315,6 +2315,9 @@
     <t>BESS</t>
   </si>
   <si>
+    <t>5. Visita Técnica / Diagnóstico en Sitio</t>
+  </si>
+  <si>
     <t>Congreso / Cámara / Networking</t>
   </si>
   <si>
@@ -3095,9 +3098,6 @@
     <t>Dirac (Proyecto Residencial)</t>
   </si>
   <si>
-    <t>5. Visita Técnica / Diagnóstico en Sitio</t>
-  </si>
-  <si>
     <t>Allan Alfaro</t>
   </si>
   <si>
@@ -3747,6 +3747,18 @@
   </si>
   <si>
     <t>Own Studio</t>
+  </si>
+  <si>
+    <t>Lic. R. Ascencio (Compras)</t>
+  </si>
+  <si>
+    <t>Grupo Aryba</t>
+  </si>
+  <si>
+    <t>Ing. Gabriela Ortíz Nava</t>
+  </si>
+  <si>
+    <t>Polesazinc</t>
   </si>
   <si>
     <r>
@@ -4016,6 +4028,27 @@
   </si>
   <si>
     <t xml:space="preserve">Hotel Mexico Plaza Bajío </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Carlos Ayala </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOTEL ARANZAZU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOTEL ARANZAZU ECO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karina Barajas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hules y recubrimientos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karla Acosta </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Vìa Corta </t>
   </si>
   <si>
     <t>Ana López</t>
@@ -5724,7 +5757,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Anónimo" id="{9483496C-DE73-4697-AA81-E4E84C32D530}" userId="" providerId="google-sheets"/>
+  <person displayName="Anónimo" id="{55861A80-B128-4B50-9A2A-1BD4FD1E5499}" userId="" providerId="google-sheets"/>
 </personList>
 </file>
 
@@ -5790,8 +5823,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:L210">
-  <autoFilter ref="A1:L210" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:L213">
+  <autoFilter ref="A1:L213" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID de Prospecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Nombre del Prospecto"/>
@@ -5831,8 +5864,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabla_8" displayName="Tabla_8" ref="A1:K16">
-  <autoFilter ref="A1:K16" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabla_8" displayName="Tabla_8" ref="A1:K21">
+  <autoFilter ref="A1:K21" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="ID de Prospecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Nombre del Prospecto"/>
@@ -6068,10 +6101,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{9483496C-DE73-4697-AA81-E4E84C32D530}" id="{5DE07D34-5D4A-43F1-B491-846ECD35EA4B}" done="1">
+  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{55861A80-B128-4B50-9A2A-1BD4FD1E5499}" id="{E486E15B-6E62-4266-9919-8644122BFE6B}" done="1">
     <text>ya lo tiene en seguimiento Josué</text>
   </threadedComment>
-  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{9483496C-DE73-4697-AA81-E4E84C32D530}" id="{BCE944ED-64D8-421B-ABDB-8EF4241DF362}" done="1">
+  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{55861A80-B128-4B50-9A2A-1BD4FD1E5499}" id="{C7ED0C02-4231-43E4-B355-89166DD53E3E}" done="1">
     <text>Ya tienen contrato con Ammper</text>
   </threadedComment>
 </ThreadedComments>
@@ -13109,7 +13142,7 @@
         <v>743</v>
       </c>
       <c r="F35" s="53" t="s">
-        <v>667</v>
+        <v>744</v>
       </c>
       <c r="G35" s="54">
         <v>46149</v>
@@ -13121,7 +13154,7 @@
         <v>0.1</v>
       </c>
       <c r="J35" s="53" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K35" s="46" t="s">
         <v>660</v>
@@ -13976,7 +14009,7 @@
     </row>
     <row r="83" spans="1:12" ht="22.5" customHeight="1">
       <c r="A83" s="46" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B83" s="51"/>
       <c r="C83" s="51"/>
@@ -13994,7 +14027,7 @@
     </row>
     <row r="84" spans="1:12" ht="22.5" customHeight="1">
       <c r="A84" s="46" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B84" s="51"/>
       <c r="C84" s="51"/>
@@ -14012,7 +14045,7 @@
     </row>
     <row r="85" spans="1:12" ht="22.5" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B85" s="51"/>
       <c r="C85" s="51"/>
@@ -14030,7 +14063,7 @@
     </row>
     <row r="86" spans="1:12" ht="22.5" customHeight="1">
       <c r="A86" s="46" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B86" s="51"/>
       <c r="C86" s="51"/>
@@ -14048,7 +14081,7 @@
     </row>
     <row r="87" spans="1:12" ht="22.5" customHeight="1">
       <c r="A87" s="46" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B87" s="51"/>
       <c r="C87" s="51"/>
@@ -14066,7 +14099,7 @@
     </row>
     <row r="88" spans="1:12" ht="22.5" customHeight="1">
       <c r="A88" s="46" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B88" s="51"/>
       <c r="C88" s="51"/>
@@ -14084,7 +14117,7 @@
     </row>
     <row r="89" spans="1:12" ht="22.5" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B89" s="51"/>
       <c r="C89" s="51"/>
@@ -14102,7 +14135,7 @@
     </row>
     <row r="90" spans="1:12" ht="22.5" customHeight="1">
       <c r="A90" s="46" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B90" s="51"/>
       <c r="C90" s="51"/>
@@ -14120,7 +14153,7 @@
     </row>
     <row r="91" spans="1:12" ht="22.5" customHeight="1">
       <c r="A91" s="46" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B91" s="51"/>
       <c r="C91" s="51"/>
@@ -14138,7 +14171,7 @@
     </row>
     <row r="92" spans="1:12" ht="22.5" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B92" s="51"/>
       <c r="C92" s="51"/>
@@ -14156,7 +14189,7 @@
     </row>
     <row r="93" spans="1:12" ht="22.5" customHeight="1">
       <c r="A93" s="46" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B93" s="51"/>
       <c r="C93" s="51"/>
@@ -14174,7 +14207,7 @@
     </row>
     <row r="94" spans="1:12" ht="22.5" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B94" s="51"/>
       <c r="C94" s="51"/>
@@ -14192,7 +14225,7 @@
     </row>
     <row r="95" spans="1:12" ht="22.5" customHeight="1">
       <c r="A95" s="46" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B95" s="51"/>
       <c r="C95" s="51"/>
@@ -14210,7 +14243,7 @@
     </row>
     <row r="96" spans="1:12" ht="22.5" customHeight="1">
       <c r="A96" s="46" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B96" s="51"/>
       <c r="C96" s="51"/>
@@ -14635,7 +14668,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC210"/>
+  <dimension ref="A1:AC213"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -14709,10 +14742,10 @@
     <row r="2" spans="1:29" ht="22.5" customHeight="1">
       <c r="A2" s="46"/>
       <c r="B2" s="46" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D2" s="49" t="s">
         <v>561</v>
@@ -14730,17 +14763,17 @@
       <c r="I2" s="56"/>
       <c r="J2" s="53"/>
       <c r="K2" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L2" s="57"/>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
       <c r="A3" s="46"/>
       <c r="B3" s="46" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D3" s="49" t="s">
         <v>561</v>
@@ -14758,23 +14791,23 @@
       <c r="I3" s="56"/>
       <c r="J3" s="53"/>
       <c r="K3" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L3" s="57"/>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
       <c r="A4" s="46"/>
       <c r="B4" s="46" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>733</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>119</v>
@@ -14788,17 +14821,17 @@
         <v>25</v>
       </c>
       <c r="K4" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L4" s="57"/>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
       <c r="A5" s="46"/>
       <c r="B5" s="46" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>733</v>
@@ -14815,20 +14848,20 @@
       <c r="H5" s="55"/>
       <c r="I5" s="56"/>
       <c r="J5" s="53" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K5" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L5" s="57"/>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
       <c r="A6" s="46"/>
       <c r="B6" s="51" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D6" s="49" t="s">
         <v>561</v>
@@ -14848,17 +14881,17 @@
         <v>25</v>
       </c>
       <c r="K6" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L6" s="57"/>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
       <c r="A7" s="46"/>
       <c r="B7" s="51" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D7" s="49" t="s">
         <v>733</v>
@@ -14878,17 +14911,17 @@
         <v>16</v>
       </c>
       <c r="K7" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L7" s="57"/>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
       <c r="A8" s="46"/>
       <c r="B8" s="51" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D8" s="49" t="s">
         <v>733</v>
@@ -14908,17 +14941,17 @@
         <v>16</v>
       </c>
       <c r="K8" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L8" s="57"/>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
       <c r="A9" s="46"/>
       <c r="B9" s="51" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D9" s="49" t="s">
         <v>733</v>
@@ -14938,17 +14971,17 @@
         <v>16</v>
       </c>
       <c r="K9" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L9" s="57"/>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
       <c r="A10" s="46"/>
       <c r="B10" s="51" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D10" s="49" t="s">
         <v>540</v>
@@ -14968,17 +15001,17 @@
         <v>74</v>
       </c>
       <c r="K10" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L10" s="57"/>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
       <c r="A11" s="46"/>
       <c r="B11" s="51" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>723</v>
@@ -14995,20 +15028,20 @@
       <c r="H11" s="55"/>
       <c r="I11" s="56"/>
       <c r="J11" s="53" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L11" s="57"/>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="51" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D12" s="49" t="s">
         <v>540</v>
@@ -15028,17 +15061,17 @@
         <v>16</v>
       </c>
       <c r="K12" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L12" s="57"/>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="51" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D13" s="49" t="s">
         <v>540</v>
@@ -15058,17 +15091,17 @@
         <v>688</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L13" s="57"/>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
       <c r="A14" s="46"/>
       <c r="B14" s="51" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D14" s="49" t="s">
         <v>530</v>
@@ -15085,20 +15118,20 @@
       <c r="H14" s="55"/>
       <c r="I14" s="56"/>
       <c r="J14" s="53" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K14" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L14" s="57"/>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
       <c r="A15" s="46"/>
       <c r="B15" s="51" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D15" s="49" t="s">
         <v>561</v>
@@ -15118,17 +15151,17 @@
         <v>688</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L15" s="57"/>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
       <c r="A16" s="46"/>
       <c r="B16" s="51" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -15146,17 +15179,17 @@
         <v>688</v>
       </c>
       <c r="K16" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L16" s="57"/>
     </row>
     <row r="17" spans="1:12" ht="22.5" customHeight="1">
       <c r="A17" s="46"/>
       <c r="B17" s="51" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D17" s="49" t="s">
         <v>733</v>
@@ -15176,17 +15209,17 @@
         <v>688</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L17" s="57"/>
     </row>
     <row r="18" spans="1:12" ht="22.5" customHeight="1">
       <c r="A18" s="46"/>
       <c r="B18" s="51" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D18" s="49" t="s">
         <v>540</v>
@@ -15206,17 +15239,17 @@
         <v>16</v>
       </c>
       <c r="K18" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L18" s="57"/>
     </row>
     <row r="19" spans="1:12" ht="22.5" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="51" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D19" s="49" t="s">
         <v>723</v>
@@ -15236,7 +15269,7 @@
         <v>74</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L19" s="57"/>
     </row>
@@ -15245,7 +15278,7 @@
         <v>175</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C20" s="51" t="s">
         <v>483</v>
@@ -15268,7 +15301,7 @@
         <v>16</v>
       </c>
       <c r="K20" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L20" s="57"/>
     </row>
@@ -15277,7 +15310,7 @@
         <v>170</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C21" s="51" t="s">
         <v>483</v>
@@ -15300,7 +15333,7 @@
         <v>16</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L21" s="57"/>
     </row>
@@ -15309,10 +15342,10 @@
         <v>172</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D22" s="49" t="s">
         <v>561</v>
@@ -15332,7 +15365,7 @@
         <v>513</v>
       </c>
       <c r="K22" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L22" s="57"/>
     </row>
@@ -15341,16 +15374,16 @@
         <v>135</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D23" s="49" t="s">
         <v>733</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F23" s="53" t="s">
         <v>119</v>
@@ -15364,7 +15397,7 @@
         <v>688</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L23" s="57"/>
     </row>
@@ -15373,13 +15406,13 @@
         <v>139</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>448</v>
@@ -15396,7 +15429,7 @@
         <v>16</v>
       </c>
       <c r="K24" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L24" s="57"/>
     </row>
@@ -15405,13 +15438,13 @@
         <v>142</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>448</v>
@@ -15428,7 +15461,7 @@
         <v>74</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L25" s="57"/>
     </row>
@@ -15437,10 +15470,10 @@
         <v>144</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>733</v>
@@ -15460,7 +15493,7 @@
         <v>74</v>
       </c>
       <c r="K26" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L26" s="57"/>
     </row>
@@ -15469,13 +15502,13 @@
         <v>152</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>448</v>
@@ -15492,7 +15525,7 @@
         <v>74</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L27" s="57"/>
     </row>
@@ -15501,10 +15534,10 @@
         <v>155</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D28" s="49" t="s">
         <v>733</v>
@@ -15524,25 +15557,25 @@
         <v>74</v>
       </c>
       <c r="K28" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L28" s="57"/>
     </row>
     <row r="29" spans="1:12" ht="22.5" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D29" s="49" t="s">
         <v>733</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F29" s="53" t="s">
         <v>119</v>
@@ -15556,7 +15589,7 @@
         <v>688</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L29" s="57"/>
     </row>
@@ -15565,10 +15598,10 @@
         <v>149</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C30" s="51" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D30" s="49" t="s">
         <v>561</v>
@@ -15592,7 +15625,7 @@
         <v>513</v>
       </c>
       <c r="K30" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L30" s="57"/>
     </row>
@@ -15601,10 +15634,10 @@
         <v>97</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D31" s="49" t="s">
         <v>726</v>
@@ -15624,7 +15657,7 @@
         <v>25</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L31" s="57"/>
     </row>
@@ -15633,10 +15666,10 @@
         <v>99</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D32" s="49" t="s">
         <v>733</v>
@@ -15656,7 +15689,7 @@
         <v>74</v>
       </c>
       <c r="K32" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L32" s="57"/>
     </row>
@@ -15665,10 +15698,10 @@
         <v>103</v>
       </c>
       <c r="B33" s="46" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C33" s="46" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D33" s="49" t="s">
         <v>561</v>
@@ -15688,7 +15721,7 @@
         <v>688</v>
       </c>
       <c r="K33" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L33" s="57"/>
     </row>
@@ -15697,10 +15730,10 @@
         <v>129</v>
       </c>
       <c r="B34" s="51" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C34" s="51" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D34" s="49" t="s">
         <v>733</v>
@@ -15716,26 +15749,26 @@
       </c>
       <c r="H34" s="55"/>
       <c r="I34" s="60" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J34" s="53" t="s">
         <v>688</v>
       </c>
       <c r="K34" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L34" s="57"/>
     </row>
     <row r="35" spans="1:12" ht="22.5" customHeight="1">
       <c r="A35" s="46"/>
       <c r="B35" s="51" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C35" s="51" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>448</v>
@@ -15752,7 +15785,7 @@
         <v>688</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L35" s="57"/>
     </row>
@@ -15761,10 +15794,10 @@
         <v>68</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10" t="s">
@@ -15782,7 +15815,7 @@
         <v>74</v>
       </c>
       <c r="K36" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L36" s="57"/>
     </row>
@@ -15791,10 +15824,10 @@
         <v>71</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C37" s="51" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D37" s="49" t="s">
         <v>540</v>
@@ -15814,7 +15847,7 @@
         <v>688</v>
       </c>
       <c r="K37" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L37" s="57"/>
     </row>
@@ -15823,10 +15856,10 @@
         <v>78</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C38" s="51" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D38" s="49" t="s">
         <v>733</v>
@@ -15846,7 +15879,7 @@
         <v>16</v>
       </c>
       <c r="K38" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L38" s="57"/>
     </row>
@@ -15855,16 +15888,16 @@
         <v>81</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F39" s="53" t="s">
         <v>119</v>
@@ -15878,20 +15911,20 @@
         <v>16</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L39" s="57"/>
     </row>
     <row r="40" spans="1:12" ht="22.5" customHeight="1">
       <c r="A40" s="46"/>
       <c r="B40" s="51" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C40" s="51" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>448</v>
@@ -15908,7 +15941,7 @@
         <v>74</v>
       </c>
       <c r="K40" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L40" s="57"/>
     </row>
@@ -15917,10 +15950,10 @@
         <v>54</v>
       </c>
       <c r="B41" s="51" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C41" s="51" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D41" s="49" t="s">
         <v>723</v>
@@ -15940,7 +15973,7 @@
         <v>25</v>
       </c>
       <c r="K41" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L41" s="57"/>
     </row>
@@ -15949,14 +15982,14 @@
         <v>60</v>
       </c>
       <c r="B42" s="46" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F42" s="53" t="s">
         <v>119</v>
@@ -15970,7 +16003,7 @@
         <v>688</v>
       </c>
       <c r="K42" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L42" s="57"/>
     </row>
@@ -15979,10 +16012,10 @@
         <v>63</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C43" s="51" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D43" s="49" t="s">
         <v>723</v>
@@ -16002,7 +16035,7 @@
         <v>688</v>
       </c>
       <c r="K43" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L43" s="57"/>
     </row>
@@ -16011,13 +16044,13 @@
         <v>65</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C44" s="51" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>448</v>
@@ -16034,7 +16067,7 @@
         <v>25</v>
       </c>
       <c r="K44" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L44" s="57"/>
     </row>
@@ -16043,13 +16076,13 @@
         <v>85</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C45" s="51" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>448</v>
@@ -16062,25 +16095,25 @@
       </c>
       <c r="H45" s="55"/>
       <c r="I45" s="60" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J45" s="53" t="s">
         <v>513</v>
       </c>
       <c r="K45" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L45" s="57"/>
     </row>
     <row r="46" spans="1:12" ht="22.5" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D46" s="49" t="s">
         <v>540</v>
@@ -16100,19 +16133,19 @@
         <v>688</v>
       </c>
       <c r="K46" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L46" s="57"/>
     </row>
     <row r="47" spans="1:12" ht="22.5" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B47" s="51" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D47" s="49" t="s">
         <v>526</v>
@@ -16132,19 +16165,19 @@
         <v>25</v>
       </c>
       <c r="K47" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L47" s="57"/>
     </row>
     <row r="48" spans="1:12" ht="22.5" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B48" s="51" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C48" s="51" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D48" s="49" t="s">
         <v>733</v>
@@ -16164,22 +16197,22 @@
         <v>74</v>
       </c>
       <c r="K48" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L48" s="57"/>
     </row>
     <row r="49" spans="1:12" ht="22.5" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>448</v>
@@ -16196,19 +16229,19 @@
         <v>74</v>
       </c>
       <c r="K49" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L49" s="57"/>
     </row>
     <row r="50" spans="1:12" ht="22.5" customHeight="1">
       <c r="A50" s="8" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B50" s="51" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C50" s="51" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D50" s="49" t="s">
         <v>733</v>
@@ -16228,7 +16261,7 @@
         <v>74</v>
       </c>
       <c r="K50" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L50" s="57"/>
     </row>
@@ -16237,10 +16270,10 @@
         <v>11</v>
       </c>
       <c r="B51" s="51" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C51" s="51" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D51" s="49" t="s">
         <v>733</v>
@@ -16260,7 +16293,7 @@
         <v>688</v>
       </c>
       <c r="K51" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L51" s="57"/>
     </row>
@@ -16269,10 +16302,10 @@
         <v>18</v>
       </c>
       <c r="B52" s="51" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C52" s="51" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D52" s="49" t="s">
         <v>540</v>
@@ -16292,7 +16325,7 @@
         <v>25</v>
       </c>
       <c r="K52" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L52" s="57"/>
     </row>
@@ -16302,7 +16335,7 @@
       </c>
       <c r="B53" s="46"/>
       <c r="C53" s="46" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D53" s="49" t="s">
         <v>723</v>
@@ -16322,7 +16355,7 @@
         <v>688</v>
       </c>
       <c r="K53" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L53" s="57"/>
     </row>
@@ -16331,10 +16364,10 @@
         <v>26</v>
       </c>
       <c r="B54" s="51" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C54" s="51" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D54" s="49" t="s">
         <v>733</v>
@@ -16354,7 +16387,7 @@
         <v>688</v>
       </c>
       <c r="K54" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L54" s="57"/>
     </row>
@@ -16363,10 +16396,10 @@
         <v>29</v>
       </c>
       <c r="B55" s="51" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C55" s="51" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D55" s="49" t="s">
         <v>733</v>
@@ -16386,7 +16419,7 @@
         <v>74</v>
       </c>
       <c r="K55" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L55" s="57"/>
     </row>
@@ -16395,7 +16428,7 @@
         <v>34</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C56" s="51" t="s">
         <v>712</v>
@@ -16418,7 +16451,7 @@
         <v>688</v>
       </c>
       <c r="K56" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L56" s="57"/>
     </row>
@@ -16427,13 +16460,13 @@
         <v>48</v>
       </c>
       <c r="B57" s="51" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C57" s="51" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>448</v>
@@ -16447,10 +16480,10 @@
       <c r="H57" s="55"/>
       <c r="I57" s="56"/>
       <c r="J57" s="53" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K57" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L57" s="57"/>
     </row>
@@ -16459,10 +16492,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="51" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C58" s="51" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D58" s="49" t="s">
         <v>561</v>
@@ -16482,7 +16515,7 @@
         <v>513</v>
       </c>
       <c r="K58" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L58" s="57"/>
     </row>
@@ -16491,13 +16524,13 @@
         <v>638</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C59" s="51" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>448</v>
@@ -16514,7 +16547,7 @@
         <v>74</v>
       </c>
       <c r="K59" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L59" s="57"/>
     </row>
@@ -16523,10 +16556,10 @@
         <v>639</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D60" s="49" t="s">
         <v>540</v>
@@ -16543,10 +16576,10 @@
       <c r="H60" s="55"/>
       <c r="I60" s="56"/>
       <c r="J60" s="53" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K60" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L60" s="57"/>
     </row>
@@ -16555,13 +16588,13 @@
         <v>640</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C61" s="51" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>448</v>
@@ -16578,7 +16611,7 @@
         <v>74</v>
       </c>
       <c r="K61" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L61" s="57"/>
     </row>
@@ -16587,13 +16620,13 @@
         <v>649</v>
       </c>
       <c r="B62" s="51" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C62" s="51" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>448</v>
@@ -16610,17 +16643,17 @@
         <v>25</v>
       </c>
       <c r="K62" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L62" s="57"/>
     </row>
     <row r="63" spans="1:12" ht="22.5" customHeight="1">
       <c r="A63" s="46"/>
       <c r="B63" s="51" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C63" s="51" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D63" s="49" t="s">
         <v>526</v>
@@ -16640,7 +16673,7 @@
         <v>688</v>
       </c>
       <c r="K63" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L63" s="57"/>
     </row>
@@ -16649,13 +16682,13 @@
         <v>609</v>
       </c>
       <c r="B64" s="51" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C64" s="51" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>448</v>
@@ -16672,7 +16705,7 @@
         <v>74</v>
       </c>
       <c r="K64" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L64" s="57"/>
     </row>
@@ -16681,13 +16714,13 @@
         <v>621</v>
       </c>
       <c r="B65" s="51" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C65" s="51" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>448</v>
@@ -16704,7 +16737,7 @@
         <v>74</v>
       </c>
       <c r="K65" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L65" s="57"/>
     </row>
@@ -16713,10 +16746,10 @@
         <v>624</v>
       </c>
       <c r="B66" s="51" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C66" s="51" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D66" s="49" t="s">
         <v>540</v>
@@ -16736,7 +16769,7 @@
         <v>74</v>
       </c>
       <c r="K66" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L66" s="57"/>
     </row>
@@ -16745,16 +16778,16 @@
         <v>597</v>
       </c>
       <c r="B67" s="51" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F67" s="53" t="s">
         <v>119</v>
@@ -16768,7 +16801,7 @@
         <v>74</v>
       </c>
       <c r="K67" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L67" s="57"/>
     </row>
@@ -16777,16 +16810,16 @@
         <v>600</v>
       </c>
       <c r="B68" s="51" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C68" s="51" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F68" s="53" t="s">
         <v>119</v>
@@ -16800,7 +16833,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L68" s="57"/>
     </row>
@@ -16809,13 +16842,13 @@
         <v>603</v>
       </c>
       <c r="B69" s="51" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C69" s="51" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D69" s="49" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>448</v>
@@ -16832,7 +16865,7 @@
         <v>74</v>
       </c>
       <c r="K69" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L69" s="57"/>
     </row>
@@ -16841,13 +16874,13 @@
         <v>146</v>
       </c>
       <c r="B70" s="51" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C70" s="51" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>448</v>
@@ -16864,7 +16897,7 @@
         <v>688</v>
       </c>
       <c r="K70" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L70" s="57"/>
     </row>
@@ -16873,10 +16906,10 @@
         <v>527</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C71" s="46" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D71" s="49" t="s">
         <v>561</v>
@@ -16896,7 +16929,7 @@
         <v>513</v>
       </c>
       <c r="K71" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L71" s="57"/>
     </row>
@@ -16905,16 +16938,16 @@
         <v>520</v>
       </c>
       <c r="B72" s="51" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C72" s="51" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F72" s="53" t="s">
         <v>119</v>
@@ -16928,7 +16961,7 @@
         <v>16</v>
       </c>
       <c r="K72" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L72" s="57"/>
     </row>
@@ -16937,10 +16970,10 @@
         <v>576</v>
       </c>
       <c r="B73" s="51" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C73" s="51" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D73" s="10"/>
       <c r="E73" s="10" t="s">
@@ -16958,7 +16991,7 @@
         <v>25</v>
       </c>
       <c r="K73" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L73" s="57"/>
     </row>
@@ -16967,10 +17000,10 @@
         <v>579</v>
       </c>
       <c r="B74" s="51" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D74" s="49" t="s">
         <v>723</v>
@@ -16990,7 +17023,7 @@
         <v>25</v>
       </c>
       <c r="K74" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L74" s="57"/>
     </row>
@@ -16999,13 +17032,13 @@
         <v>650</v>
       </c>
       <c r="B75" s="51" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C75" s="51" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>448</v>
@@ -17022,7 +17055,7 @@
         <v>25</v>
       </c>
       <c r="K75" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L75" s="57"/>
     </row>
@@ -17031,13 +17064,13 @@
         <v>503</v>
       </c>
       <c r="B76" s="46" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C76" s="46" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D76" s="49" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>448</v>
@@ -17056,7 +17089,7 @@
         <v>25</v>
       </c>
       <c r="K76" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L76" s="57"/>
     </row>
@@ -17065,16 +17098,16 @@
         <v>506</v>
       </c>
       <c r="B77" s="46" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C77" s="46" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D77" s="49" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F77" s="53" t="s">
         <v>699</v>
@@ -17088,7 +17121,7 @@
         <v>25</v>
       </c>
       <c r="K77" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L77" s="57"/>
     </row>
@@ -17097,10 +17130,10 @@
         <v>488</v>
       </c>
       <c r="B78" s="51" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C78" s="51" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D78" s="10"/>
       <c r="E78" s="10" t="s">
@@ -17120,7 +17153,7 @@
         <v>25</v>
       </c>
       <c r="K78" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L78" s="57"/>
     </row>
@@ -17129,10 +17162,10 @@
         <v>494</v>
       </c>
       <c r="B79" s="46" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C79" s="46" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D79" s="49" t="s">
         <v>658</v>
@@ -17154,22 +17187,22 @@
         <v>25</v>
       </c>
       <c r="K79" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L79" s="57"/>
     </row>
     <row r="80" spans="1:12" ht="22.5" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B80" s="51" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C80" s="51" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D80" s="49" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>448</v>
@@ -17186,7 +17219,7 @@
         <v>16</v>
       </c>
       <c r="K80" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L80" s="57"/>
     </row>
@@ -17196,7 +17229,7 @@
       </c>
       <c r="B81" s="46"/>
       <c r="C81" s="46" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D81" s="49" t="s">
         <v>540</v>
@@ -17216,7 +17249,7 @@
         <v>551</v>
       </c>
       <c r="K81" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L81" s="57"/>
     </row>
@@ -17225,16 +17258,16 @@
         <v>582</v>
       </c>
       <c r="B82" s="51" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C82" s="51" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D82" s="49" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F82" s="53" t="s">
         <v>119</v>
@@ -17248,7 +17281,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L82" s="57"/>
     </row>
@@ -17257,10 +17290,10 @@
         <v>113</v>
       </c>
       <c r="B83" s="51" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C83" s="51" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D83" s="49" t="s">
         <v>723</v>
@@ -17280,14 +17313,14 @@
         <v>688</v>
       </c>
       <c r="K83" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L83" s="57"/>
     </row>
     <row r="84" spans="1:12" ht="22.5" customHeight="1">
       <c r="A84" s="46"/>
       <c r="B84" s="46" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C84" s="46" t="s">
         <v>410</v>
@@ -17308,7 +17341,7 @@
         <v>74</v>
       </c>
       <c r="K84" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L84" s="57"/>
     </row>
@@ -17317,13 +17350,13 @@
         <v>116</v>
       </c>
       <c r="B85" s="51" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C85" s="51" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="D85" s="49" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>448</v>
@@ -17340,17 +17373,17 @@
         <v>688</v>
       </c>
       <c r="K85" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L85" s="57"/>
     </row>
     <row r="86" spans="1:12" ht="22.5" customHeight="1">
       <c r="A86" s="46"/>
       <c r="B86" s="51" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C86" s="51" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D86" s="10"/>
       <c r="E86" s="10" t="s">
@@ -17368,17 +17401,17 @@
         <v>25</v>
       </c>
       <c r="K86" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L86" s="57"/>
     </row>
     <row r="87" spans="1:12" ht="22.5" customHeight="1">
       <c r="A87" s="46"/>
       <c r="B87" s="51" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C87" s="51" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D87" s="49" t="s">
         <v>678</v>
@@ -17395,23 +17428,23 @@
       <c r="H87" s="55"/>
       <c r="I87" s="56"/>
       <c r="J87" s="53" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="K87" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L87" s="57"/>
     </row>
     <row r="88" spans="1:12" ht="22.5" customHeight="1">
       <c r="A88" s="46"/>
       <c r="B88" s="51" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>448</v>
@@ -17428,7 +17461,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L88" s="57"/>
     </row>
@@ -17437,13 +17470,13 @@
         <v>565</v>
       </c>
       <c r="B89" s="51" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D89" s="49" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>448</v>
@@ -17460,7 +17493,7 @@
         <v>25</v>
       </c>
       <c r="K89" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L89" s="57"/>
     </row>
@@ -17469,10 +17502,10 @@
         <v>568</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C90" s="51" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D90" s="49" t="s">
         <v>723</v>
@@ -17492,7 +17525,7 @@
         <v>25</v>
       </c>
       <c r="K90" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L90" s="57"/>
     </row>
@@ -17501,10 +17534,10 @@
         <v>571</v>
       </c>
       <c r="B91" s="51" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C91" s="51" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D91" s="10"/>
       <c r="E91" s="10" t="s">
@@ -17522,7 +17555,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L91" s="57"/>
     </row>
@@ -17531,13 +17564,13 @@
         <v>574</v>
       </c>
       <c r="B92" s="51" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C92" s="51" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D92" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>448</v>
@@ -17554,7 +17587,7 @@
         <v>25</v>
       </c>
       <c r="K92" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L92" s="57"/>
     </row>
@@ -17563,10 +17596,10 @@
         <v>562</v>
       </c>
       <c r="B93" s="51" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C93" s="51" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D93" s="49" t="s">
         <v>540</v>
@@ -17586,7 +17619,7 @@
         <v>25</v>
       </c>
       <c r="K93" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L93" s="57"/>
     </row>
@@ -17595,10 +17628,10 @@
         <v>88</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C94" s="51" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D94" s="49" t="s">
         <v>540</v>
@@ -17618,7 +17651,7 @@
         <v>513</v>
       </c>
       <c r="K94" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L94" s="57"/>
     </row>
@@ -17627,16 +17660,16 @@
         <v>523</v>
       </c>
       <c r="B95" s="46" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C95" s="46" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D95" s="49" t="s">
         <v>723</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F95" s="53" t="s">
         <v>449</v>
@@ -17650,20 +17683,20 @@
         <v>74</v>
       </c>
       <c r="K95" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L95" s="57"/>
     </row>
     <row r="96" spans="1:12" ht="22.5" customHeight="1">
       <c r="A96" s="46"/>
       <c r="B96" s="46" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C96" s="46" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D96" s="49" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>448</v>
@@ -17680,7 +17713,7 @@
         <v>25</v>
       </c>
       <c r="K96" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L96" s="57"/>
     </row>
@@ -17689,13 +17722,13 @@
         <v>643</v>
       </c>
       <c r="B97" s="51" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C97" s="51" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D97" s="49" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>448</v>
@@ -17712,7 +17745,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L97" s="57"/>
     </row>
@@ -17721,10 +17754,10 @@
         <v>644</v>
       </c>
       <c r="B98" s="51" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C98" s="51" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D98" s="49" t="s">
         <v>526</v>
@@ -17744,7 +17777,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L98" s="57"/>
     </row>
@@ -17753,13 +17786,13 @@
         <v>132</v>
       </c>
       <c r="B99" s="51" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C99" s="51" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D99" s="49" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>448</v>
@@ -17776,7 +17809,7 @@
         <v>513</v>
       </c>
       <c r="K99" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L99" s="57"/>
     </row>
@@ -17785,10 +17818,10 @@
         <v>606</v>
       </c>
       <c r="B100" s="51" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C100" s="51" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D100" s="49" t="s">
         <v>561</v>
@@ -17808,7 +17841,7 @@
         <v>25</v>
       </c>
       <c r="K100" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L100" s="57"/>
     </row>
@@ -17817,10 +17850,10 @@
         <v>538</v>
       </c>
       <c r="B101" s="51" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C101" s="51" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D101" s="49" t="s">
         <v>723</v>
@@ -17840,7 +17873,7 @@
         <v>25</v>
       </c>
       <c r="K101" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L101" s="57"/>
     </row>
@@ -17849,10 +17882,10 @@
         <v>645</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D102" s="49" t="s">
         <v>526</v>
@@ -17872,7 +17905,7 @@
         <v>16</v>
       </c>
       <c r="K102" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L102" s="57"/>
     </row>
@@ -17881,10 +17914,10 @@
         <v>120</v>
       </c>
       <c r="B103" s="51" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C103" s="51" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D103" s="49" t="s">
         <v>540</v>
@@ -17904,7 +17937,7 @@
         <v>16</v>
       </c>
       <c r="K103" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L103" s="57"/>
     </row>
@@ -17913,13 +17946,13 @@
         <v>126</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C104" s="51" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>448</v>
@@ -17936,7 +17969,7 @@
         <v>16</v>
       </c>
       <c r="K104" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L104" s="57"/>
     </row>
@@ -17945,7 +17978,7 @@
         <v>41</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C105" s="51"/>
       <c r="D105" s="49" t="s">
@@ -17966,7 +17999,7 @@
         <v>16</v>
       </c>
       <c r="K105" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L105" s="57"/>
     </row>
@@ -17975,10 +18008,10 @@
         <v>646</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C106" s="51" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D106" s="49" t="s">
         <v>723</v>
@@ -17995,22 +18028,22 @@
       <c r="H106" s="55"/>
       <c r="I106" s="56"/>
       <c r="J106" s="53" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="K106" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L106" s="57"/>
     </row>
     <row r="107" spans="1:12" ht="22.5" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B107" s="51" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C107" s="51" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D107" s="49" t="s">
         <v>723</v>
@@ -18030,17 +18063,17 @@
         <v>74</v>
       </c>
       <c r="K107" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L107" s="57"/>
     </row>
     <row r="108" spans="1:12" ht="22.5" customHeight="1">
       <c r="A108" s="46"/>
       <c r="B108" s="51" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C108" s="51" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D108" s="49" t="s">
         <v>733</v>
@@ -18060,7 +18093,7 @@
         <v>688</v>
       </c>
       <c r="K108" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L108" s="57"/>
     </row>
@@ -18069,13 +18102,13 @@
         <v>459</v>
       </c>
       <c r="B109" s="46" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C109" s="46" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>448</v>
@@ -18096,7 +18129,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L109" s="57"/>
     </row>
@@ -18105,10 +18138,10 @@
         <v>462</v>
       </c>
       <c r="B110" s="46" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C110" s="46" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D110" s="49" t="s">
         <v>540</v>
@@ -18130,7 +18163,7 @@
         <v>25</v>
       </c>
       <c r="K110" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L110" s="57"/>
     </row>
@@ -18139,19 +18172,19 @@
         <v>552</v>
       </c>
       <c r="B111" s="46" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C111" s="46" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D111" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F111" s="53" t="s">
-        <v>1004</v>
+        <v>744</v>
       </c>
       <c r="G111" s="54">
         <v>45952</v>
@@ -18162,7 +18195,7 @@
         <v>25</v>
       </c>
       <c r="K111" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L111" s="57"/>
     </row>
@@ -18177,7 +18210,7 @@
         <v>1006</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>448</v>
@@ -18194,7 +18227,7 @@
         <v>25</v>
       </c>
       <c r="K112" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L112" s="57"/>
     </row>
@@ -18226,7 +18259,7 @@
         <v>25</v>
       </c>
       <c r="K113" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L113" s="57"/>
     </row>
@@ -18258,7 +18291,7 @@
         <v>25</v>
       </c>
       <c r="K114" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L114" s="57"/>
     </row>
@@ -18273,10 +18306,10 @@
         <v>1012</v>
       </c>
       <c r="D115" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F115" s="53" t="s">
         <v>119</v>
@@ -18290,13 +18323,13 @@
         <v>25</v>
       </c>
       <c r="K115" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L115" s="57"/>
     </row>
     <row r="116" spans="1:12" ht="22.5" customHeight="1">
       <c r="A116" s="8" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B116" s="51" t="s">
         <v>1013</v>
@@ -18305,7 +18338,7 @@
         <v>1014</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>448</v>
@@ -18319,10 +18352,10 @@
       <c r="H116" s="55"/>
       <c r="I116" s="56"/>
       <c r="J116" s="53" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K116" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L116" s="57"/>
     </row>
@@ -18354,7 +18387,7 @@
         <v>25</v>
       </c>
       <c r="K117" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L117" s="57"/>
     </row>
@@ -18375,7 +18408,7 @@
         <v>448</v>
       </c>
       <c r="F118" s="53" t="s">
-        <v>1004</v>
+        <v>744</v>
       </c>
       <c r="G118" s="54">
         <v>45940</v>
@@ -18388,7 +18421,7 @@
         <v>25</v>
       </c>
       <c r="K118" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L118" s="57"/>
     </row>
@@ -18420,7 +18453,7 @@
         <v>25</v>
       </c>
       <c r="K119" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L119" s="57"/>
     </row>
@@ -18452,7 +18485,7 @@
         <v>25</v>
       </c>
       <c r="K120" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L120" s="57"/>
     </row>
@@ -18484,7 +18517,7 @@
         <v>16</v>
       </c>
       <c r="K121" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L121" s="57"/>
     </row>
@@ -18499,13 +18532,13 @@
         <v>1031</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F122" s="53" t="s">
-        <v>1004</v>
+        <v>744</v>
       </c>
       <c r="G122" s="54">
         <v>45933</v>
@@ -18518,7 +18551,7 @@
         <v>25</v>
       </c>
       <c r="K122" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L122" s="57"/>
     </row>
@@ -18550,7 +18583,7 @@
         <v>16</v>
       </c>
       <c r="K123" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L123" s="57"/>
     </row>
@@ -18582,13 +18615,13 @@
         <v>1036</v>
       </c>
       <c r="K124" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L124" s="57"/>
     </row>
     <row r="125" spans="1:12" ht="22.5" customHeight="1">
       <c r="A125" s="8" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B125" s="46" t="s">
         <v>1037</v>
@@ -18614,13 +18647,13 @@
         <v>513</v>
       </c>
       <c r="K125" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L125" s="57"/>
     </row>
     <row r="126" spans="1:12" ht="22.5" customHeight="1">
       <c r="A126" s="8" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B126" s="51" t="s">
         <v>1039</v>
@@ -18646,13 +18679,13 @@
         <v>16</v>
       </c>
       <c r="K126" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L126" s="57"/>
     </row>
     <row r="127" spans="1:12" ht="22.5" customHeight="1">
       <c r="A127" s="8" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B127" s="51" t="s">
         <v>1041</v>
@@ -18678,7 +18711,7 @@
         <v>16</v>
       </c>
       <c r="K127" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L127" s="57"/>
     </row>
@@ -18710,13 +18743,13 @@
         <v>74</v>
       </c>
       <c r="K128" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L128" s="57"/>
     </row>
     <row r="129" spans="1:12" ht="22.5" customHeight="1">
       <c r="A129" s="8" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B129" s="51" t="s">
         <v>1045</v>
@@ -18742,7 +18775,7 @@
         <v>25</v>
       </c>
       <c r="K129" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L129" s="57"/>
     </row>
@@ -18774,7 +18807,7 @@
         <v>25</v>
       </c>
       <c r="K130" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L130" s="57"/>
     </row>
@@ -18806,7 +18839,7 @@
         <v>25</v>
       </c>
       <c r="K131" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L131" s="57"/>
     </row>
@@ -18821,7 +18854,7 @@
         <v>1054</v>
       </c>
       <c r="D132" s="49" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>448</v>
@@ -18838,7 +18871,7 @@
         <v>513</v>
       </c>
       <c r="K132" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L132" s="57"/>
     </row>
@@ -18872,7 +18905,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L133" s="57"/>
     </row>
@@ -18904,7 +18937,7 @@
         <v>16</v>
       </c>
       <c r="K134" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L134" s="57"/>
     </row>
@@ -18940,7 +18973,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L135" s="57"/>
     </row>
@@ -18972,7 +19005,7 @@
         <v>25</v>
       </c>
       <c r="K136" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L136" s="57"/>
     </row>
@@ -19002,7 +19035,7 @@
         <v>25</v>
       </c>
       <c r="K137" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L137" s="57"/>
     </row>
@@ -19017,7 +19050,7 @@
         <v>1067</v>
       </c>
       <c r="D138" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>448</v>
@@ -19034,7 +19067,7 @@
         <v>138</v>
       </c>
       <c r="K138" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L138" s="57"/>
     </row>
@@ -19055,7 +19088,7 @@
         <v>448</v>
       </c>
       <c r="F139" s="53" t="s">
-        <v>1004</v>
+        <v>744</v>
       </c>
       <c r="G139" s="54">
         <v>45822</v>
@@ -19068,7 +19101,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L139" s="57"/>
     </row>
@@ -19100,7 +19133,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L140" s="57"/>
     </row>
@@ -19115,7 +19148,7 @@
         <v>1073</v>
       </c>
       <c r="D141" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>448</v>
@@ -19136,7 +19169,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L141" s="57"/>
     </row>
@@ -19170,7 +19203,7 @@
         <v>25</v>
       </c>
       <c r="K142" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L142" s="57"/>
     </row>
@@ -19204,7 +19237,7 @@
         <v>25</v>
       </c>
       <c r="K143" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L143" s="57"/>
     </row>
@@ -19236,7 +19269,7 @@
         <v>16</v>
       </c>
       <c r="K144" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L144" s="57"/>
     </row>
@@ -19268,7 +19301,7 @@
         <v>25</v>
       </c>
       <c r="K145" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L145" s="57"/>
     </row>
@@ -19287,7 +19320,7 @@
         <v>448</v>
       </c>
       <c r="F146" s="53" t="s">
-        <v>1004</v>
+        <v>744</v>
       </c>
       <c r="G146" s="54">
         <v>45736</v>
@@ -19298,7 +19331,7 @@
         <v>25</v>
       </c>
       <c r="K146" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L146" s="57"/>
     </row>
@@ -19319,7 +19352,7 @@
         <v>448</v>
       </c>
       <c r="F147" s="53" t="s">
-        <v>1004</v>
+        <v>744</v>
       </c>
       <c r="G147" s="54">
         <v>45700</v>
@@ -19332,7 +19365,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L147" s="57"/>
     </row>
@@ -19347,7 +19380,7 @@
         <v>1088</v>
       </c>
       <c r="D148" s="49" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E148" s="10" t="s">
         <v>448</v>
@@ -19364,7 +19397,7 @@
         <v>16</v>
       </c>
       <c r="K148" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L148" s="57"/>
     </row>
@@ -19379,7 +19412,7 @@
         <v>1090</v>
       </c>
       <c r="D149" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>448</v>
@@ -19393,10 +19426,10 @@
       <c r="H149" s="55"/>
       <c r="I149" s="56"/>
       <c r="J149" s="53" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K149" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L149" s="57"/>
     </row>
@@ -19411,7 +19444,7 @@
         <v>1092</v>
       </c>
       <c r="D150" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>448</v>
@@ -19432,7 +19465,7 @@
         <v>25</v>
       </c>
       <c r="K150" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L150" s="57"/>
     </row>
@@ -19447,10 +19480,10 @@
         <v>1092</v>
       </c>
       <c r="D151" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F151" s="53" t="s">
         <v>24</v>
@@ -19466,7 +19499,7 @@
         <v>25</v>
       </c>
       <c r="K151" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L151" s="57"/>
     </row>
@@ -19481,7 +19514,7 @@
         <v>1094</v>
       </c>
       <c r="D152" s="49" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>448</v>
@@ -19498,7 +19531,7 @@
         <v>25</v>
       </c>
       <c r="K152" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L152" s="57"/>
     </row>
@@ -19516,7 +19549,7 @@
         <v>526</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F153" s="53" t="s">
         <v>119</v>
@@ -19530,7 +19563,7 @@
         <v>25</v>
       </c>
       <c r="K153" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L153" s="57"/>
     </row>
@@ -19551,7 +19584,7 @@
         <v>448</v>
       </c>
       <c r="F154" s="53" t="s">
-        <v>1004</v>
+        <v>744</v>
       </c>
       <c r="G154" s="54">
         <v>45519</v>
@@ -19564,7 +19597,7 @@
         <v>25</v>
       </c>
       <c r="K154" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L154" s="57"/>
     </row>
@@ -19579,7 +19612,7 @@
         <v>483</v>
       </c>
       <c r="D155" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>448</v>
@@ -19600,13 +19633,13 @@
         <v>138</v>
       </c>
       <c r="K155" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L155" s="57"/>
     </row>
     <row r="156" spans="1:12" ht="22.5" customHeight="1">
       <c r="A156" s="8" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B156" s="51" t="s">
         <v>1100</v>
@@ -19618,7 +19651,7 @@
         <v>1102</v>
       </c>
       <c r="E156" s="10" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F156" s="53" t="s">
         <v>119</v>
@@ -19632,7 +19665,7 @@
         <v>25</v>
       </c>
       <c r="K156" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L156" s="57"/>
     </row>
@@ -19647,13 +19680,13 @@
         <v>483</v>
       </c>
       <c r="D157" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F157" s="53" t="s">
-        <v>1004</v>
+        <v>744</v>
       </c>
       <c r="G157" s="54">
         <v>45513</v>
@@ -19666,7 +19699,7 @@
         <v>16</v>
       </c>
       <c r="K157" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L157" s="57"/>
     </row>
@@ -19698,7 +19731,7 @@
         <v>74</v>
       </c>
       <c r="K158" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L158" s="57"/>
     </row>
@@ -19713,7 +19746,7 @@
         <v>1108</v>
       </c>
       <c r="D159" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>448</v>
@@ -19730,7 +19763,7 @@
         <v>513</v>
       </c>
       <c r="K159" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L159" s="57"/>
     </row>
@@ -19762,7 +19795,7 @@
         <v>16</v>
       </c>
       <c r="K160" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L160" s="57"/>
     </row>
@@ -19794,7 +19827,7 @@
         <v>25</v>
       </c>
       <c r="K161" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L161" s="57"/>
     </row>
@@ -19815,7 +19848,7 @@
         <v>448</v>
       </c>
       <c r="F162" s="53" t="s">
-        <v>1004</v>
+        <v>744</v>
       </c>
       <c r="G162" s="54">
         <v>45384</v>
@@ -19830,7 +19863,7 @@
         <v>138</v>
       </c>
       <c r="K162" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L162" s="57"/>
     </row>
@@ -19860,7 +19893,7 @@
         <v>16</v>
       </c>
       <c r="K163" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L163" s="57"/>
     </row>
@@ -19881,7 +19914,7 @@
         <v>448</v>
       </c>
       <c r="F164" s="53" t="s">
-        <v>1004</v>
+        <v>744</v>
       </c>
       <c r="G164" s="54">
         <v>45203</v>
@@ -19896,7 +19929,7 @@
         <v>25</v>
       </c>
       <c r="K164" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L164" s="57"/>
     </row>
@@ -19930,7 +19963,7 @@
         <v>25</v>
       </c>
       <c r="K165" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L165" s="57"/>
     </row>
@@ -19945,7 +19978,7 @@
         <v>1123</v>
       </c>
       <c r="D166" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E166" s="10" t="s">
         <v>448</v>
@@ -19962,7 +19995,7 @@
         <v>513</v>
       </c>
       <c r="K166" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L166" s="57"/>
     </row>
@@ -19977,7 +20010,7 @@
         <v>1125</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>448</v>
@@ -19994,7 +20027,7 @@
         <v>25</v>
       </c>
       <c r="K167" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L167" s="57"/>
     </row>
@@ -20026,7 +20059,7 @@
         <v>16</v>
       </c>
       <c r="K168" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L168" s="57"/>
     </row>
@@ -20038,7 +20071,7 @@
         <v>1129</v>
       </c>
       <c r="C169" s="51" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D169" s="10" t="s">
         <v>1130</v>
@@ -20058,7 +20091,7 @@
         <v>25</v>
       </c>
       <c r="K169" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L169" s="57"/>
     </row>
@@ -20090,7 +20123,7 @@
         <v>25</v>
       </c>
       <c r="K170" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L170" s="57"/>
     </row>
@@ -20122,7 +20155,7 @@
         <v>74</v>
       </c>
       <c r="K171" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L171" s="57"/>
     </row>
@@ -20151,10 +20184,10 @@
       </c>
       <c r="I172" s="67"/>
       <c r="J172" s="64" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K172" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L172" s="57"/>
     </row>
@@ -20169,7 +20202,7 @@
         <v>1140</v>
       </c>
       <c r="D173" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>448</v>
@@ -20190,7 +20223,7 @@
         <v>138</v>
       </c>
       <c r="K173" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L173" s="57"/>
     </row>
@@ -20222,7 +20255,7 @@
         <v>25</v>
       </c>
       <c r="K174" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L174" s="57"/>
     </row>
@@ -20254,7 +20287,7 @@
         <v>16</v>
       </c>
       <c r="K175" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L175" s="57"/>
     </row>
@@ -20288,7 +20321,7 @@
         <v>138</v>
       </c>
       <c r="K176" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L176" s="57"/>
     </row>
@@ -20303,7 +20336,7 @@
         <v>1149</v>
       </c>
       <c r="D177" s="49" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>1150</v>
@@ -20320,7 +20353,7 @@
         <v>25</v>
       </c>
       <c r="K177" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L177" s="57"/>
     </row>
@@ -20350,7 +20383,7 @@
         <v>513</v>
       </c>
       <c r="K178" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L178" s="57"/>
     </row>
@@ -20384,7 +20417,7 @@
         <v>513</v>
       </c>
       <c r="K179" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L179" s="57"/>
     </row>
@@ -20416,7 +20449,7 @@
         <v>25</v>
       </c>
       <c r="K180" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L180" s="57"/>
     </row>
@@ -20442,7 +20475,7 @@
       <c r="I181" s="56"/>
       <c r="J181" s="53"/>
       <c r="K181" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L181" s="57"/>
     </row>
@@ -20476,14 +20509,14 @@
         <v>74</v>
       </c>
       <c r="K182" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L182" s="57"/>
     </row>
     <row r="183" spans="1:12" ht="22.5" customHeight="1">
       <c r="A183" s="46"/>
       <c r="B183" s="46" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C183" s="46" t="s">
         <v>1165</v>
@@ -20510,7 +20543,7 @@
         <v>25</v>
       </c>
       <c r="K183" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L183" s="57"/>
     </row>
@@ -20544,7 +20577,7 @@
         <v>25</v>
       </c>
       <c r="K184" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L184" s="57"/>
     </row>
@@ -20578,7 +20611,7 @@
         <v>25</v>
       </c>
       <c r="K185" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L185" s="57"/>
     </row>
@@ -20612,7 +20645,7 @@
         <v>25</v>
       </c>
       <c r="K186" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L186" s="57"/>
     </row>
@@ -20642,7 +20675,7 @@
         <v>25</v>
       </c>
       <c r="K187" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L187" s="57"/>
     </row>
@@ -20672,7 +20705,7 @@
         <v>513</v>
       </c>
       <c r="K188" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L188" s="57"/>
     </row>
@@ -20702,7 +20735,7 @@
         <v>74</v>
       </c>
       <c r="K189" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L189" s="57"/>
     </row>
@@ -20715,7 +20748,7 @@
         <v>1014</v>
       </c>
       <c r="D190" s="49" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="E190" s="10" t="s">
         <v>448</v>
@@ -20732,7 +20765,7 @@
         <v>25</v>
       </c>
       <c r="K190" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L190" s="57"/>
     </row>
@@ -20759,10 +20792,10 @@
       <c r="H191" s="55"/>
       <c r="I191" s="56"/>
       <c r="J191" s="53" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K191" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L191" s="57"/>
     </row>
@@ -20775,7 +20808,7 @@
         <v>410</v>
       </c>
       <c r="D192" s="49" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E192" s="10" t="s">
         <v>448</v>
@@ -20792,7 +20825,7 @@
         <v>74</v>
       </c>
       <c r="K192" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L192" s="57"/>
     </row>
@@ -20822,7 +20855,7 @@
         <v>16</v>
       </c>
       <c r="K193" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L193" s="57"/>
     </row>
@@ -20852,7 +20885,7 @@
         <v>74</v>
       </c>
       <c r="K194" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L194" s="57"/>
     </row>
@@ -20880,7 +20913,7 @@
         <v>25</v>
       </c>
       <c r="K195" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L195" s="57"/>
     </row>
@@ -20910,7 +20943,7 @@
         <v>1192</v>
       </c>
       <c r="K196" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L196" s="57"/>
     </row>
@@ -20923,7 +20956,7 @@
         <v>1194</v>
       </c>
       <c r="D197" s="49" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>448</v>
@@ -21040,7 +21073,7 @@
         <v>537</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F202" s="53" t="s">
         <v>119</v>
@@ -21061,7 +21094,7 @@
         <v>1206</v>
       </c>
       <c r="D203" s="49" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>448</v>
@@ -21236,21 +21269,83 @@
       <c r="K210" s="46"/>
       <c r="L210" s="46"/>
     </row>
+    <row r="211" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A211" s="46"/>
+      <c r="B211" s="9" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C211" s="46" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D211" s="49" t="s">
+        <v>561</v>
+      </c>
+      <c r="E211" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F211" s="53"/>
+      <c r="G211" s="54"/>
+      <c r="H211" s="55"/>
+      <c r="I211" s="56"/>
+      <c r="J211" s="53"/>
+      <c r="K211" s="46"/>
+      <c r="L211" s="46"/>
+    </row>
+    <row r="212" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A212" s="46"/>
+      <c r="B212" s="9" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C212" s="46" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D212" s="10"/>
+      <c r="E212" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F212" s="53"/>
+      <c r="G212" s="54"/>
+      <c r="H212" s="55"/>
+      <c r="I212" s="56"/>
+      <c r="J212" s="53"/>
+      <c r="K212" s="46"/>
+      <c r="L212" s="46"/>
+    </row>
+    <row r="213" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A213" s="46"/>
+      <c r="B213" s="9"/>
+      <c r="C213" s="46" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D213" s="49" t="s">
+        <v>815</v>
+      </c>
+      <c r="E213" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F213" s="53"/>
+      <c r="G213" s="54"/>
+      <c r="H213" s="55"/>
+      <c r="I213" s="56"/>
+      <c r="J213" s="53"/>
+      <c r="K213" s="46"/>
+      <c r="L213" s="46"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="F2:F210" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F213" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"1. Prospección,2. Contacto Inicial,3. Calificación,4. Levantamiento de Requerimientos,5. Visita Técnica / Diagnóstico en Sitio,6. Diseño de Solución / Pre-Ingeniería,7. Estimación / Cotización,8. Propuesta Enviada,9. Aclaraciones / Ajustes de Propuesta,10"&amp;". Negociación,11. Aprobación Interna (Go/No-Go),12. Cierre de Venta (Contrato / OC),13. Kickoff / Inicio de Proyecto,14. Descartado / No Califica,15. En Pausa / Seguimiento Posterior"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G210" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G213" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G2))), AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I210" xr:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I213" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>AND(ISNUMBER(H2),(NOT(OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J210" xr:uid="{00000000-0002-0000-0400-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J213" xr:uid="{00000000-0002-0000-0400-000003000000}">
       <formula1>"Referido (Cliente),Referido (Proveedor/Subcontratista),Referido (Empleado/Interno),Cliente Recurrente (Recompra/Ampliación),Sitio Web (Formulario),Landing Page (Campaña),Chat Web / WhatsApp,SEO (Búsqueda Orgánica),Google Ads (Search),Remarketing (Display/"&amp;"Redes),LinkedIn (Orgánico),Email Outbound (Prospección),Llamada en Frío (Prospección),Visita en Frío (Prospección),Feria / Expo Industrial,Congreso / Cámara / Networking,Webinar / Evento Virtual,Licitación Pública,Licitación Privada (RFP/RFQ),Portal de Co"&amp;"mpras (Cliente),Alianza (Integrador/EPC/Constructor),Partner Tecnológico (Marca/Distribuidor),Directorio B2B / Clúster,Redes Sociales (Facebook/Instagram),YouTube / Contenido Técnico,PR / Medio Especializado,Reactivación de Base de Datos,Otros"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C210 E2:E210 K2:K210" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C213 E2:E213 K2:K213" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -21424,12 +21519,14 @@
     <hyperlink ref="D208" r:id="rId169" xr:uid="{00000000-0004-0000-0400-0000A8000000}"/>
     <hyperlink ref="D209" r:id="rId170" xr:uid="{00000000-0004-0000-0400-0000A9000000}"/>
     <hyperlink ref="D210" r:id="rId171" xr:uid="{00000000-0004-0000-0400-0000AA000000}"/>
+    <hyperlink ref="D211" r:id="rId172" xr:uid="{00000000-0004-0000-0400-0000AB000000}"/>
+    <hyperlink ref="D213" r:id="rId173" xr:uid="{00000000-0004-0000-0400-0000AC000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
   <tableParts count="1">
-    <tablePart r:id="rId172"/>
+    <tablePart r:id="rId174"/>
   </tableParts>
 </worksheet>
 </file>
@@ -21514,10 +21611,10 @@
         <v>481</v>
       </c>
       <c r="B2" s="69" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D2" s="70"/>
       <c r="E2" s="70"/>
@@ -21537,7 +21634,7 @@
         <v>25</v>
       </c>
       <c r="K2" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="21" customHeight="1">
@@ -21545,10 +21642,10 @@
         <v>484</v>
       </c>
       <c r="B3" s="77" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="C3" s="76" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="D3" s="70"/>
       <c r="E3" s="70"/>
@@ -21566,7 +21663,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -21574,10 +21671,10 @@
         <v>488</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="C4" s="82" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="D4" s="83"/>
       <c r="E4" s="70"/>
@@ -21595,7 +21692,7 @@
         <v>25</v>
       </c>
       <c r="K4" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -21603,10 +21700,10 @@
         <v>491</v>
       </c>
       <c r="B5" s="81" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="C5" s="82" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="D5" s="83"/>
       <c r="E5" s="70"/>
@@ -21621,10 +21718,10 @@
       </c>
       <c r="I5" s="87"/>
       <c r="J5" s="90" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K5" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -21632,10 +21729,10 @@
         <v>494</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="C6" s="82" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="D6" s="83"/>
       <c r="E6" s="70"/>
@@ -21653,7 +21750,7 @@
         <v>74</v>
       </c>
       <c r="K6" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -21661,10 +21758,10 @@
         <v>497</v>
       </c>
       <c r="B7" s="77" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="C7" s="76" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="D7" s="70"/>
       <c r="E7" s="70"/>
@@ -21680,7 +21777,7 @@
         <v>25</v>
       </c>
       <c r="K7" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -21688,10 +21785,10 @@
         <v>500</v>
       </c>
       <c r="B8" s="77" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="D8" s="70"/>
       <c r="E8" s="70"/>
@@ -21709,7 +21806,7 @@
         <v>74</v>
       </c>
       <c r="K8" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -21717,10 +21814,10 @@
         <v>503</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="C9" s="82" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="D9" s="83"/>
       <c r="E9" s="70"/>
@@ -21738,7 +21835,7 @@
         <v>74</v>
       </c>
       <c r="K9" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -21746,10 +21843,10 @@
         <v>506</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="C10" s="76" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
@@ -21767,7 +21864,7 @@
         <v>25</v>
       </c>
       <c r="K10" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -21775,10 +21872,10 @@
         <v>514</v>
       </c>
       <c r="B11" s="81" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="C11" s="82" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="D11" s="83"/>
       <c r="E11" s="70"/>
@@ -21796,7 +21893,7 @@
         <v>74</v>
       </c>
       <c r="K11" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -21804,10 +21901,10 @@
         <v>517</v>
       </c>
       <c r="B12" s="81" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="C12" s="82" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="D12" s="83"/>
       <c r="E12" s="70"/>
@@ -21825,7 +21922,7 @@
         <v>74</v>
       </c>
       <c r="K12" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -21833,10 +21930,10 @@
         <v>520</v>
       </c>
       <c r="B13" s="77" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
@@ -21854,7 +21951,7 @@
         <v>25</v>
       </c>
       <c r="K13" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -21862,10 +21959,10 @@
         <v>523</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="C14" s="82" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="D14" s="83"/>
       <c r="E14" s="70"/>
@@ -21881,7 +21978,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -21889,10 +21986,10 @@
         <v>527</v>
       </c>
       <c r="B15" s="99" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="C15" s="82" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="D15" s="83"/>
       <c r="E15" s="70"/>
@@ -21910,7 +22007,7 @@
         <v>74</v>
       </c>
       <c r="K15" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
@@ -21918,10 +22015,10 @@
         <v>531</v>
       </c>
       <c r="B16" s="77" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="C16" s="76" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
@@ -21937,7 +22034,7 @@
         <v>25</v>
       </c>
       <c r="K16" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
@@ -21945,10 +22042,10 @@
         <v>534</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="C17" s="76" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D17" s="70"/>
       <c r="E17" s="70"/>
@@ -21968,7 +22065,7 @@
         <v>25</v>
       </c>
       <c r="K17" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="22.5" customHeight="1">
@@ -21976,10 +22073,10 @@
         <v>538</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="70"/>
@@ -21999,7 +22096,7 @@
         <v>74</v>
       </c>
       <c r="K18" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="22.5" customHeight="1">
@@ -22007,10 +22104,10 @@
         <v>541</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="11"/>
@@ -22030,7 +22127,7 @@
         <v>513</v>
       </c>
       <c r="K19" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="22.5" customHeight="1">
@@ -22038,10 +22135,10 @@
         <v>544</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -22059,7 +22156,7 @@
         <v>25</v>
       </c>
       <c r="K20" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="22.5" customHeight="1">
@@ -22067,10 +22164,10 @@
         <v>547</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="C21" s="76" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -22085,10 +22182,10 @@
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="14" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K21" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="22.5" customHeight="1">
@@ -22096,10 +22193,10 @@
         <v>552</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="C22" s="76" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="11"/>
@@ -22117,7 +22214,7 @@
         <v>551</v>
       </c>
       <c r="K22" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="22.5" customHeight="1">
@@ -22125,10 +22222,10 @@
         <v>555</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="C23" s="76" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="11"/>
@@ -22146,7 +22243,7 @@
         <v>551</v>
       </c>
       <c r="K23" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="22.5" customHeight="1">
@@ -22154,10 +22251,10 @@
         <v>558</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -22175,7 +22272,7 @@
         <v>551</v>
       </c>
       <c r="K24" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="22.5" customHeight="1">
@@ -22183,10 +22280,10 @@
         <v>558</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="11"/>
@@ -22206,7 +22303,7 @@
         <v>513</v>
       </c>
       <c r="K25" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -22214,15 +22311,15 @@
         <v>558</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="11"/>
       <c r="F26" s="3" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="G26" s="12">
         <v>46075</v>
@@ -22237,7 +22334,7 @@
         <v>551</v>
       </c>
       <c r="K26" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="22.5" customHeight="1">
@@ -22245,10 +22342,10 @@
         <v>562</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -22266,7 +22363,7 @@
         <v>513</v>
       </c>
       <c r="K27" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="22.5" customHeight="1">
@@ -22274,10 +22371,10 @@
         <v>565</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -22295,7 +22392,7 @@
         <v>513</v>
       </c>
       <c r="K28" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="22.5" customHeight="1">
@@ -22303,10 +22400,10 @@
         <v>568</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="11"/>
@@ -22322,7 +22419,7 @@
       <c r="I29" s="45"/>
       <c r="J29" s="14"/>
       <c r="K29" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
   </sheetData>
@@ -22371,7 +22468,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -22445,10 +22542,10 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="D2" s="101"/>
       <c r="E2" s="101" t="s">
@@ -22463,10 +22560,10 @@
       <c r="H2" s="66"/>
       <c r="I2" s="67"/>
       <c r="J2" s="64" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -22474,10 +22571,10 @@
         <v>451</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
@@ -22496,10 +22593,10 @@
         <v>0.8</v>
       </c>
       <c r="J3" s="53" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -22507,14 +22604,14 @@
         <v>454</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>449</v>
@@ -22525,10 +22622,10 @@
       <c r="H4" s="61"/>
       <c r="I4" s="56"/>
       <c r="J4" s="53" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -22536,10 +22633,10 @@
         <v>457</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
@@ -22561,7 +22658,7 @@
         <v>688</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -22569,10 +22666,10 @@
         <v>668</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
@@ -22590,7 +22687,7 @@
         <v>688</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -22598,10 +22695,10 @@
         <v>459</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
@@ -22616,10 +22713,10 @@
       <c r="H7" s="61"/>
       <c r="I7" s="56"/>
       <c r="J7" s="53" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -22627,10 +22724,10 @@
         <v>462</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
@@ -22648,7 +22745,7 @@
         <v>25</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -22656,14 +22753,14 @@
         <v>465</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="F9" s="53" t="s">
         <v>40</v>
@@ -22677,7 +22774,7 @@
         <v>659</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -22685,10 +22782,10 @@
         <v>468</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
@@ -22706,7 +22803,7 @@
         <v>659</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -22714,14 +22811,14 @@
         <v>471</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="F11" s="53" t="s">
         <v>32</v>
@@ -22735,7 +22832,7 @@
         <v>659</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -22743,17 +22840,17 @@
         <v>474</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>1004</v>
+        <v>744</v>
       </c>
       <c r="G12" s="54"/>
       <c r="H12" s="61"/>
@@ -22762,7 +22859,7 @@
         <v>659</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -22770,10 +22867,10 @@
         <v>477</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
@@ -22795,7 +22892,7 @@
         <v>659</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -22803,10 +22900,10 @@
         <v>481</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10" t="s">
@@ -22823,10 +22920,10 @@
         <v>0.8</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -22834,10 +22931,10 @@
         <v>484</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10" t="s">
@@ -22857,10 +22954,10 @@
         <v>488</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -22880,24 +22977,131 @@
         <v>659</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>1279</v>
-      </c>
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="22.5" customHeight="1">
+      <c r="A17" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>699</v>
+      </c>
+      <c r="G17" s="54"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" spans="1:11" ht="22.5" customHeight="1">
+      <c r="A18" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>699</v>
+      </c>
+      <c r="G18" s="54"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" ht="22.5" customHeight="1">
+      <c r="A19" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="B19" s="51" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>699</v>
+      </c>
+      <c r="G19" s="54"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="59"/>
+    </row>
+    <row r="20" spans="1:11" ht="22.5" customHeight="1">
+      <c r="A20" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>449</v>
+      </c>
+      <c r="G20" s="54"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="59"/>
+    </row>
+    <row r="21" spans="1:11" ht="22.5" customHeight="1">
+      <c r="A21" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="51"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="F2:F16" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F21" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"1. Prospección,2. Contacto Inicial,3. Calificación,4. Levantamiento de Requerimientos,5. Visita Técnica / Diagnóstico en Sitio,6. Diseño de Solución / Pre-Ingeniería,7. Estimación / Cotización,8. Propuesta Enviada,9. Aclaraciones / Ajustes de Propuesta,10"&amp;". Negociación,11. Aprobación Interna (Go/No-Go),12. Cierre de Venta (Contrato / OC),13. Kickoff / Inicio de Proyecto,14. Descartado / No Califica,15. En Pausa / Seguimiento Posterior"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G16" xr:uid="{00000000-0002-0000-0600-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G21" xr:uid="{00000000-0002-0000-0600-000001000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G2))), AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I16" xr:uid="{00000000-0002-0000-0600-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I21" xr:uid="{00000000-0002-0000-0600-000002000000}">
       <formula1>AND(ISNUMBER(H2),(NOT(OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J16" xr:uid="{00000000-0002-0000-0600-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J21" xr:uid="{00000000-0002-0000-0600-000003000000}">
       <formula1>"Referido (Cliente),Referido (Proveedor/Subcontratista),Referido (Empleado/Interno),Cliente Recurrente (Recompra/Ampliación),Sitio Web (Formulario),Landing Page (Campaña),Chat Web / WhatsApp,SEO (Búsqueda Orgánica),Google Ads (Search),Remarketing (Display/"&amp;"Redes),LinkedIn (Orgánico),Email Outbound (Prospección),Llamada en Frío (Prospección),Visita en Frío (Prospección),Feria / Expo Industrial,Congreso / Cámara / Networking,Webinar / Evento Virtual,Licitación Pública,Licitación Privada (RFP/RFQ),Portal de Co"&amp;"mpras (Cliente),Alianza (Integrador/EPC/Constructor),Partner Tecnológico (Marca/Distribuidor),Directorio B2B / Clúster,Redes Sociales (Facebook/Instagram),YouTube / Contenido Técnico,PR / Medio Especializado,Reactivación de Base de Datos,Otros"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C16 E2:E16 K2:K16" xr:uid="{00000000-0002-0000-0600-000004000000}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C21 E2:E21 K2:K21" xr:uid="{00000000-0002-0000-0600-000004000000}"/>
   </dataValidations>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -23010,10 +23214,10 @@
         <v>0.75</v>
       </c>
       <c r="J2" s="64" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K2" s="104" t="s">
-        <v>1309</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -23021,10 +23225,10 @@
         <v>471</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>1310</v>
+        <v>1321</v>
       </c>
       <c r="C3" s="82" t="s">
-        <v>1311</v>
+        <v>1322</v>
       </c>
       <c r="D3" s="83"/>
       <c r="E3" s="83"/>
@@ -23040,7 +23244,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -23328,10 +23532,10 @@
         <v>474</v>
       </c>
       <c r="B14" s="107" t="s">
-        <v>1312</v>
+        <v>1323</v>
       </c>
       <c r="C14" s="108" t="s">
-        <v>1313</v>
+        <v>1324</v>
       </c>
       <c r="D14" s="109"/>
       <c r="E14" s="109"/>
@@ -23349,7 +23553,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -23639,10 +23843,10 @@
         <v>477</v>
       </c>
       <c r="B25" s="117" t="s">
-        <v>1314</v>
+        <v>1325</v>
       </c>
       <c r="C25" s="118" t="s">
-        <v>1315</v>
+        <v>1326</v>
       </c>
       <c r="D25" s="119"/>
       <c r="E25" s="119"/>
@@ -23660,7 +23864,7 @@
         <v>25</v>
       </c>
       <c r="K25" s="125" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -23958,10 +24162,10 @@
         <v>481</v>
       </c>
       <c r="B36" s="126" t="s">
-        <v>1316</v>
+        <v>1327</v>
       </c>
       <c r="C36" s="127" t="s">
-        <v>1317</v>
+        <v>1328</v>
       </c>
       <c r="D36" s="128"/>
       <c r="E36" s="128"/>
@@ -23977,7 +24181,7 @@
         <v>25</v>
       </c>
       <c r="K36" s="134" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="22.5" customHeight="1">
@@ -24109,7 +24313,7 @@
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16" t="s">
-        <v>1318</v>
+        <v>1329</v>
       </c>
       <c r="D42" s="17"/>
       <c r="E42" s="18"/>
@@ -24184,10 +24388,10 @@
         <v>484</v>
       </c>
       <c r="B46" s="107" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="C46" s="108" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="D46" s="109"/>
       <c r="E46" s="109"/>
@@ -24205,7 +24409,7 @@
         <v>74</v>
       </c>
       <c r="K46" s="115" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="22.5" customHeight="1">
@@ -24405,10 +24609,10 @@
         <v>488</v>
       </c>
       <c r="B57" s="135" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="C57" s="136" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="D57" s="137"/>
       <c r="E57" s="137"/>
@@ -24426,7 +24630,7 @@
         <v>25</v>
       </c>
       <c r="K57" s="143" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="22.5" customHeight="1">
@@ -24644,10 +24848,10 @@
         <v>491</v>
       </c>
       <c r="B68" s="107" t="s">
-        <v>1319</v>
+        <v>1330</v>
       </c>
       <c r="C68" s="108" t="s">
-        <v>1320</v>
+        <v>1331</v>
       </c>
       <c r="D68" s="109"/>
       <c r="E68" s="109"/>
@@ -24663,7 +24867,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="115" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="22.5" customHeight="1">
@@ -24879,10 +25083,10 @@
         <v>494</v>
       </c>
       <c r="B79" s="126" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="C79" s="127" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="D79" s="128"/>
       <c r="E79" s="128"/>
@@ -24897,10 +25101,10 @@
       </c>
       <c r="I79" s="132"/>
       <c r="J79" s="148" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K79" s="134" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="22.5" customHeight="1">
@@ -24950,10 +25154,10 @@
         <v>497</v>
       </c>
       <c r="B82" s="117" t="s">
-        <v>1321</v>
+        <v>1332</v>
       </c>
       <c r="C82" s="118" t="s">
-        <v>1322</v>
+        <v>1333</v>
       </c>
       <c r="D82" s="119"/>
       <c r="E82" s="119"/>
@@ -24971,7 +25175,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="125" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="22.5" customHeight="1">
@@ -24979,10 +25183,10 @@
         <v>500</v>
       </c>
       <c r="B83" s="126" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="C83" s="127" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="D83" s="128"/>
       <c r="E83" s="128"/>
@@ -25000,7 +25204,7 @@
         <v>74</v>
       </c>
       <c r="K83" s="134" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22.5" customHeight="1">
@@ -25008,13 +25212,13 @@
         <v>451</v>
       </c>
       <c r="B84" s="151" t="s">
-        <v>1323</v>
+        <v>1334</v>
       </c>
       <c r="C84" s="151" t="s">
-        <v>1324</v>
+        <v>1335</v>
       </c>
       <c r="D84" s="152" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E84" s="153"/>
       <c r="F84" s="154" t="s">
@@ -25033,7 +25237,7 @@
         <v>25</v>
       </c>
       <c r="K84" s="158" t="s">
-        <v>1325</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="22.5" customHeight="1">
@@ -25041,10 +25245,10 @@
         <v>503</v>
       </c>
       <c r="B85" s="107" t="s">
-        <v>1326</v>
+        <v>1337</v>
       </c>
       <c r="C85" s="108" t="s">
-        <v>1327</v>
+        <v>1338</v>
       </c>
       <c r="D85" s="109"/>
       <c r="E85" s="109"/>
@@ -25062,7 +25266,7 @@
         <v>74</v>
       </c>
       <c r="K85" s="115" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="22.5" customHeight="1">
@@ -25070,10 +25274,10 @@
         <v>506</v>
       </c>
       <c r="B86" s="135" t="s">
-        <v>1328</v>
+        <v>1339</v>
       </c>
       <c r="C86" s="136" t="s">
-        <v>1329</v>
+        <v>1340</v>
       </c>
       <c r="D86" s="137"/>
       <c r="E86" s="137"/>
@@ -25091,7 +25295,7 @@
         <v>74</v>
       </c>
       <c r="K86" s="143" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="22.5" customHeight="1">
@@ -25099,10 +25303,10 @@
         <v>510</v>
       </c>
       <c r="B87" s="108" t="s">
-        <v>1330</v>
+        <v>1341</v>
       </c>
       <c r="C87" s="108" t="s">
-        <v>1331</v>
+        <v>1342</v>
       </c>
       <c r="D87" s="109"/>
       <c r="E87" s="109"/>
@@ -25115,10 +25319,10 @@
       </c>
       <c r="I87" s="113"/>
       <c r="J87" s="160" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K87" s="115" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="22.5" customHeight="1">
@@ -25126,10 +25330,10 @@
         <v>514</v>
       </c>
       <c r="B88" s="135" t="s">
-        <v>1332</v>
+        <v>1343</v>
       </c>
       <c r="C88" s="136" t="s">
-        <v>1333</v>
+        <v>1344</v>
       </c>
       <c r="D88" s="137"/>
       <c r="E88" s="137"/>
@@ -25147,7 +25351,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="143" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="22.5" customHeight="1">
@@ -25155,10 +25359,10 @@
         <v>517</v>
       </c>
       <c r="B89" s="117" t="s">
-        <v>1334</v>
+        <v>1345</v>
       </c>
       <c r="C89" s="118" t="s">
-        <v>1335</v>
+        <v>1346</v>
       </c>
       <c r="D89" s="70"/>
       <c r="E89" s="70"/>
@@ -25176,7 +25380,7 @@
         <v>74</v>
       </c>
       <c r="K89" s="125" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="22.5" customHeight="1">
@@ -25184,10 +25388,10 @@
         <v>520</v>
       </c>
       <c r="B90" s="135" t="s">
-        <v>1336</v>
+        <v>1347</v>
       </c>
       <c r="C90" s="136" t="s">
-        <v>1337</v>
+        <v>1348</v>
       </c>
       <c r="D90" s="83"/>
       <c r="E90" s="83"/>
@@ -25203,7 +25407,7 @@
         <v>74</v>
       </c>
       <c r="K90" s="143" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="22.5" customHeight="1">
@@ -25211,10 +25415,10 @@
         <v>523</v>
       </c>
       <c r="B91" s="77" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="C91" s="76" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="D91" s="70"/>
       <c r="E91" s="70"/>
@@ -25230,7 +25434,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="125" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22.5" customHeight="1">
@@ -25238,10 +25442,10 @@
         <v>527</v>
       </c>
       <c r="B92" s="81" t="s">
-        <v>1338</v>
+        <v>1349</v>
       </c>
       <c r="C92" s="82" t="s">
-        <v>1339</v>
+        <v>1350</v>
       </c>
       <c r="D92" s="83"/>
       <c r="E92" s="83"/>
@@ -25259,7 +25463,7 @@
         <v>74</v>
       </c>
       <c r="K92" s="143" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="22.5" customHeight="1">
@@ -25267,10 +25471,10 @@
         <v>531</v>
       </c>
       <c r="B93" s="77" t="s">
-        <v>1340</v>
+        <v>1351</v>
       </c>
       <c r="C93" s="76" t="s">
-        <v>1341</v>
+        <v>1352</v>
       </c>
       <c r="D93" s="70"/>
       <c r="E93" s="70"/>
@@ -25286,7 +25490,7 @@
         <v>74</v>
       </c>
       <c r="K93" s="125" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="22.5" customHeight="1">
@@ -25294,10 +25498,10 @@
         <v>534</v>
       </c>
       <c r="B94" s="81" t="s">
-        <v>1342</v>
+        <v>1353</v>
       </c>
       <c r="C94" s="82" t="s">
-        <v>1343</v>
+        <v>1354</v>
       </c>
       <c r="D94" s="83"/>
       <c r="E94" s="83"/>
@@ -25313,7 +25517,7 @@
         <v>74</v>
       </c>
       <c r="K94" s="143" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="22.5" customHeight="1">
@@ -25321,13 +25525,13 @@
         <v>454</v>
       </c>
       <c r="B95" s="104" t="s">
-        <v>1344</v>
+        <v>1355</v>
       </c>
       <c r="C95" s="104" t="s">
-        <v>1345</v>
+        <v>1356</v>
       </c>
       <c r="D95" s="62" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E95" s="63"/>
       <c r="F95" s="64" t="s">
@@ -25346,7 +25550,7 @@
         <v>16</v>
       </c>
       <c r="K95" s="158" t="s">
-        <v>1309</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="22.5" customHeight="1">
@@ -25354,10 +25558,10 @@
         <v>538</v>
       </c>
       <c r="B96" s="77" t="s">
-        <v>1346</v>
+        <v>1357</v>
       </c>
       <c r="C96" s="76" t="s">
-        <v>1347</v>
+        <v>1358</v>
       </c>
       <c r="D96" s="70"/>
       <c r="E96" s="70"/>
@@ -25373,7 +25577,7 @@
         <v>74</v>
       </c>
       <c r="K96" s="125" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="22.5" customHeight="1">
@@ -25381,7 +25585,7 @@
         <v>541</v>
       </c>
       <c r="B97" s="81" t="s">
-        <v>1348</v>
+        <v>1359</v>
       </c>
       <c r="C97" s="82" t="s">
         <v>1078</v>
@@ -25400,7 +25604,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="22.5" customHeight="1">
@@ -25408,10 +25612,10 @@
         <v>544</v>
       </c>
       <c r="B98" s="77" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="C98" s="76" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="D98" s="70"/>
       <c r="E98" s="70"/>
@@ -25429,7 +25633,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="22.5" customHeight="1">
@@ -25437,10 +25641,10 @@
         <v>547</v>
       </c>
       <c r="B99" s="81" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="C99" s="82" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="D99" s="83"/>
       <c r="E99" s="83"/>
@@ -25458,7 +25662,7 @@
         <v>74</v>
       </c>
       <c r="K99" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="22.5" customHeight="1">
@@ -25466,10 +25670,10 @@
         <v>552</v>
       </c>
       <c r="B100" s="77" t="s">
-        <v>1349</v>
+        <v>1360</v>
       </c>
       <c r="C100" s="76" t="s">
-        <v>1350</v>
+        <v>1361</v>
       </c>
       <c r="D100" s="70"/>
       <c r="E100" s="70"/>
@@ -25485,7 +25689,7 @@
         <v>74</v>
       </c>
       <c r="K100" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="22.5" customHeight="1">
@@ -25493,10 +25697,10 @@
         <v>555</v>
       </c>
       <c r="B101" s="81" t="s">
-        <v>1351</v>
+        <v>1362</v>
       </c>
       <c r="C101" s="82" t="s">
-        <v>1352</v>
+        <v>1363</v>
       </c>
       <c r="D101" s="83"/>
       <c r="E101" s="83"/>
@@ -25512,7 +25716,7 @@
         <v>74</v>
       </c>
       <c r="K101" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="22.5" customHeight="1">
@@ -25520,10 +25724,10 @@
         <v>558</v>
       </c>
       <c r="B102" s="77" t="s">
-        <v>1353</v>
+        <v>1364</v>
       </c>
       <c r="C102" s="76" t="s">
-        <v>1354</v>
+        <v>1365</v>
       </c>
       <c r="D102" s="70"/>
       <c r="E102" s="70"/>
@@ -25539,7 +25743,7 @@
         <v>74</v>
       </c>
       <c r="K102" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="22.5" customHeight="1">
@@ -25547,10 +25751,10 @@
         <v>562</v>
       </c>
       <c r="B103" s="81" t="s">
-        <v>1355</v>
+        <v>1366</v>
       </c>
       <c r="C103" s="82" t="s">
-        <v>1356</v>
+        <v>1367</v>
       </c>
       <c r="D103" s="83"/>
       <c r="E103" s="83"/>
@@ -25566,7 +25770,7 @@
         <v>74</v>
       </c>
       <c r="K103" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="22.5" customHeight="1">
@@ -25574,10 +25778,10 @@
         <v>565</v>
       </c>
       <c r="B104" s="76" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="C104" s="76" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="D104" s="70"/>
       <c r="E104" s="70"/>
@@ -25595,7 +25799,7 @@
         <v>25</v>
       </c>
       <c r="K104" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="22.5" customHeight="1">
@@ -25603,10 +25807,10 @@
         <v>568</v>
       </c>
       <c r="B105" s="81" t="s">
-        <v>1357</v>
+        <v>1368</v>
       </c>
       <c r="C105" s="82" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D105" s="83"/>
       <c r="E105" s="83"/>
@@ -25624,7 +25828,7 @@
         <v>74</v>
       </c>
       <c r="K105" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="22.5" customHeight="1">
@@ -25632,10 +25836,10 @@
         <v>457</v>
       </c>
       <c r="B106" s="104" t="s">
-        <v>1358</v>
+        <v>1369</v>
       </c>
       <c r="C106" s="104" t="s">
-        <v>1359</v>
+        <v>1370</v>
       </c>
       <c r="D106" s="62" t="s">
         <v>540</v>
@@ -25657,7 +25861,7 @@
         <v>1192</v>
       </c>
       <c r="K106" s="104" t="s">
-        <v>1360</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="22.5" customHeight="1">
@@ -25665,10 +25869,10 @@
         <v>571</v>
       </c>
       <c r="B107" s="77" t="s">
-        <v>1361</v>
+        <v>1372</v>
       </c>
       <c r="C107" s="76" t="s">
-        <v>1362</v>
+        <v>1373</v>
       </c>
       <c r="D107" s="70"/>
       <c r="E107" s="70"/>
@@ -25684,7 +25888,7 @@
         <v>25</v>
       </c>
       <c r="K107" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="22.5" customHeight="1">
@@ -25692,10 +25896,10 @@
         <v>574</v>
       </c>
       <c r="B108" s="81" t="s">
-        <v>1363</v>
+        <v>1374</v>
       </c>
       <c r="C108" s="82" t="s">
-        <v>1364</v>
+        <v>1375</v>
       </c>
       <c r="D108" s="83"/>
       <c r="E108" s="83"/>
@@ -25711,7 +25915,7 @@
         <v>74</v>
       </c>
       <c r="K108" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="22.5" customHeight="1">
@@ -25719,10 +25923,10 @@
         <v>576</v>
       </c>
       <c r="B109" s="77" t="s">
-        <v>1365</v>
+        <v>1376</v>
       </c>
       <c r="C109" s="76" t="s">
-        <v>1366</v>
+        <v>1377</v>
       </c>
       <c r="D109" s="70"/>
       <c r="E109" s="70"/>
@@ -25740,7 +25944,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="22.5" customHeight="1">
@@ -25748,10 +25952,10 @@
         <v>579</v>
       </c>
       <c r="B110" s="81" t="s">
-        <v>1367</v>
+        <v>1378</v>
       </c>
       <c r="C110" s="82" t="s">
-        <v>1368</v>
+        <v>1379</v>
       </c>
       <c r="D110" s="83"/>
       <c r="E110" s="83"/>
@@ -25767,7 +25971,7 @@
         <v>74</v>
       </c>
       <c r="K110" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="22.5" customHeight="1">
@@ -25775,10 +25979,10 @@
         <v>582</v>
       </c>
       <c r="B111" s="77" t="s">
-        <v>1369</v>
+        <v>1380</v>
       </c>
       <c r="C111" s="76" t="s">
-        <v>1370</v>
+        <v>1381</v>
       </c>
       <c r="D111" s="70"/>
       <c r="E111" s="70"/>
@@ -25794,7 +25998,7 @@
         <v>74</v>
       </c>
       <c r="K111" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="22.5" customHeight="1">
@@ -25802,10 +26006,10 @@
         <v>585</v>
       </c>
       <c r="B112" s="81" t="s">
-        <v>1371</v>
+        <v>1382</v>
       </c>
       <c r="C112" s="82" t="s">
-        <v>1372</v>
+        <v>1383</v>
       </c>
       <c r="D112" s="83"/>
       <c r="E112" s="83"/>
@@ -25821,7 +26025,7 @@
         <v>74</v>
       </c>
       <c r="K112" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="22.5" customHeight="1">
@@ -25829,10 +26033,10 @@
         <v>588</v>
       </c>
       <c r="B113" s="77" t="s">
-        <v>1373</v>
+        <v>1384</v>
       </c>
       <c r="C113" s="76" t="s">
-        <v>1374</v>
+        <v>1385</v>
       </c>
       <c r="D113" s="70"/>
       <c r="E113" s="70"/>
@@ -25848,7 +26052,7 @@
         <v>74</v>
       </c>
       <c r="K113" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="22.5" customHeight="1">
@@ -25856,10 +26060,10 @@
         <v>591</v>
       </c>
       <c r="B114" s="81" t="s">
-        <v>1375</v>
+        <v>1386</v>
       </c>
       <c r="C114" s="82" t="s">
-        <v>1376</v>
+        <v>1387</v>
       </c>
       <c r="D114" s="83"/>
       <c r="E114" s="83"/>
@@ -25875,7 +26079,7 @@
         <v>74</v>
       </c>
       <c r="K114" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="22.5" customHeight="1">
@@ -25883,7 +26087,7 @@
         <v>594</v>
       </c>
       <c r="B115" s="77" t="s">
-        <v>1377</v>
+        <v>1388</v>
       </c>
       <c r="C115" s="76" t="s">
         <v>391</v>
@@ -25902,7 +26106,7 @@
         <v>74</v>
       </c>
       <c r="K115" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="22.5" customHeight="1">
@@ -25910,10 +26114,10 @@
         <v>597</v>
       </c>
       <c r="B116" s="81" t="s">
-        <v>1378</v>
+        <v>1389</v>
       </c>
       <c r="C116" s="82" t="s">
-        <v>1379</v>
+        <v>1390</v>
       </c>
       <c r="D116" s="83"/>
       <c r="E116" s="83"/>
@@ -25929,7 +26133,7 @@
         <v>74</v>
       </c>
       <c r="K116" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="22.5" customHeight="1">
@@ -25937,10 +26141,10 @@
         <v>668</v>
       </c>
       <c r="B117" s="104" t="s">
-        <v>1380</v>
+        <v>1391</v>
       </c>
       <c r="C117" s="104" t="s">
-        <v>1381</v>
+        <v>1392</v>
       </c>
       <c r="D117" s="62" t="s">
         <v>540</v>
@@ -25962,7 +26166,7 @@
         <v>1192</v>
       </c>
       <c r="K117" s="104" t="s">
-        <v>1325</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="22.5" customHeight="1">
@@ -25970,10 +26174,10 @@
         <v>600</v>
       </c>
       <c r="B118" s="77" t="s">
-        <v>1382</v>
+        <v>1393</v>
       </c>
       <c r="C118" s="76" t="s">
-        <v>1383</v>
+        <v>1394</v>
       </c>
       <c r="D118" s="70"/>
       <c r="E118" s="70"/>
@@ -25989,7 +26193,7 @@
         <v>74</v>
       </c>
       <c r="K118" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="22.5" customHeight="1">
@@ -25997,10 +26201,10 @@
         <v>603</v>
       </c>
       <c r="B119" s="81" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="C119" s="82" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="D119" s="83"/>
       <c r="E119" s="83"/>
@@ -26018,7 +26222,7 @@
         <v>74</v>
       </c>
       <c r="K119" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="22.5" customHeight="1">
@@ -26026,10 +26230,10 @@
         <v>606</v>
       </c>
       <c r="B120" s="77" t="s">
-        <v>1384</v>
+        <v>1395</v>
       </c>
       <c r="C120" s="76" t="s">
-        <v>1385</v>
+        <v>1396</v>
       </c>
       <c r="D120" s="70"/>
       <c r="E120" s="70"/>
@@ -26047,7 +26251,7 @@
         <v>74</v>
       </c>
       <c r="K120" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="22.5" customHeight="1">
@@ -26055,10 +26259,10 @@
         <v>609</v>
       </c>
       <c r="B121" s="81" t="s">
-        <v>1386</v>
+        <v>1397</v>
       </c>
       <c r="C121" s="82" t="s">
-        <v>1387</v>
+        <v>1398</v>
       </c>
       <c r="D121" s="83"/>
       <c r="E121" s="83"/>
@@ -26074,7 +26278,7 @@
         <v>74</v>
       </c>
       <c r="K121" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="22.5" customHeight="1">
@@ -26082,10 +26286,10 @@
         <v>612</v>
       </c>
       <c r="B122" s="77" t="s">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="C122" s="76" t="s">
-        <v>1389</v>
+        <v>1400</v>
       </c>
       <c r="D122" s="70"/>
       <c r="E122" s="70"/>
@@ -26101,7 +26305,7 @@
         <v>74</v>
       </c>
       <c r="K122" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="22.5" customHeight="1">
@@ -26109,10 +26313,10 @@
         <v>615</v>
       </c>
       <c r="B123" s="81" t="s">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="C123" s="82" t="s">
-        <v>1391</v>
+        <v>1402</v>
       </c>
       <c r="D123" s="83"/>
       <c r="E123" s="83"/>
@@ -26128,7 +26332,7 @@
         <v>74</v>
       </c>
       <c r="K123" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="22.5" customHeight="1">
@@ -26136,10 +26340,10 @@
         <v>618</v>
       </c>
       <c r="B124" s="77" t="s">
-        <v>1392</v>
+        <v>1403</v>
       </c>
       <c r="C124" s="76" t="s">
-        <v>1393</v>
+        <v>1404</v>
       </c>
       <c r="D124" s="70"/>
       <c r="E124" s="70"/>
@@ -26157,7 +26361,7 @@
         <v>25</v>
       </c>
       <c r="K124" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="22.5" customHeight="1">
@@ -26165,10 +26369,10 @@
         <v>621</v>
       </c>
       <c r="B125" s="81" t="s">
-        <v>1394</v>
+        <v>1405</v>
       </c>
       <c r="C125" s="82" t="s">
-        <v>1395</v>
+        <v>1406</v>
       </c>
       <c r="D125" s="83"/>
       <c r="E125" s="83"/>
@@ -26184,7 +26388,7 @@
         <v>25</v>
       </c>
       <c r="K125" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="22.5" customHeight="1">
@@ -26192,10 +26396,10 @@
         <v>624</v>
       </c>
       <c r="B126" s="77" t="s">
-        <v>1396</v>
+        <v>1407</v>
       </c>
       <c r="C126" s="76" t="s">
-        <v>1397</v>
+        <v>1408</v>
       </c>
       <c r="D126" s="70"/>
       <c r="E126" s="70"/>
@@ -26211,7 +26415,7 @@
         <v>74</v>
       </c>
       <c r="K126" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="22.5" customHeight="1">
@@ -26219,10 +26423,10 @@
         <v>627</v>
       </c>
       <c r="B127" s="81" t="s">
-        <v>1398</v>
+        <v>1409</v>
       </c>
       <c r="C127" s="82" t="s">
-        <v>1399</v>
+        <v>1410</v>
       </c>
       <c r="D127" s="83"/>
       <c r="E127" s="83"/>
@@ -26238,7 +26442,7 @@
         <v>74</v>
       </c>
       <c r="K127" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="22.5" customHeight="1">
@@ -26246,10 +26450,10 @@
         <v>459</v>
       </c>
       <c r="B128" s="104" t="s">
-        <v>1400</v>
+        <v>1411</v>
       </c>
       <c r="C128" s="104" t="s">
-        <v>1401</v>
+        <v>1412</v>
       </c>
       <c r="D128" s="62" t="s">
         <v>540</v>
@@ -26271,7 +26475,7 @@
         <v>1036</v>
       </c>
       <c r="K128" s="104" t="s">
-        <v>1360</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="22.5" customHeight="1">
@@ -26279,10 +26483,10 @@
         <v>630</v>
       </c>
       <c r="B129" s="77" t="s">
-        <v>1402</v>
+        <v>1413</v>
       </c>
       <c r="C129" s="76" t="s">
-        <v>1403</v>
+        <v>1414</v>
       </c>
       <c r="D129" s="70"/>
       <c r="E129" s="70"/>
@@ -26298,7 +26502,7 @@
         <v>74</v>
       </c>
       <c r="K129" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="22.5" customHeight="1">
@@ -26306,10 +26510,10 @@
         <v>633</v>
       </c>
       <c r="B130" s="81" t="s">
-        <v>1404</v>
+        <v>1415</v>
       </c>
       <c r="C130" s="82" t="s">
-        <v>1405</v>
+        <v>1416</v>
       </c>
       <c r="D130" s="83"/>
       <c r="E130" s="83"/>
@@ -26327,7 +26531,7 @@
         <v>74</v>
       </c>
       <c r="K130" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="22.5" customHeight="1">
@@ -26335,10 +26539,10 @@
         <v>636</v>
       </c>
       <c r="B131" s="77" t="s">
-        <v>1406</v>
+        <v>1417</v>
       </c>
       <c r="C131" s="76" t="s">
-        <v>1407</v>
+        <v>1418</v>
       </c>
       <c r="D131" s="70"/>
       <c r="E131" s="70"/>
@@ -26354,7 +26558,7 @@
         <v>74</v>
       </c>
       <c r="K131" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="22.5" customHeight="1">
@@ -26362,10 +26566,10 @@
         <v>637</v>
       </c>
       <c r="B132" s="81" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="C132" s="82" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="D132" s="83"/>
       <c r="E132" s="83"/>
@@ -26383,7 +26587,7 @@
         <v>74</v>
       </c>
       <c r="K132" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="22.5" customHeight="1">
@@ -26391,10 +26595,10 @@
         <v>638</v>
       </c>
       <c r="B133" s="77" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="C133" s="76" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="D133" s="70"/>
       <c r="E133" s="70"/>
@@ -26412,7 +26616,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="22.5" customHeight="1">
@@ -26420,10 +26624,10 @@
         <v>639</v>
       </c>
       <c r="B134" s="81" t="s">
-        <v>1408</v>
+        <v>1419</v>
       </c>
       <c r="C134" s="82" t="s">
-        <v>1409</v>
+        <v>1420</v>
       </c>
       <c r="D134" s="83"/>
       <c r="E134" s="83"/>
@@ -26439,7 +26643,7 @@
         <v>25</v>
       </c>
       <c r="K134" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="22.5" customHeight="1">
@@ -26447,10 +26651,10 @@
         <v>640</v>
       </c>
       <c r="B135" s="77" t="s">
-        <v>1410</v>
+        <v>1421</v>
       </c>
       <c r="C135" s="76" t="s">
-        <v>1411</v>
+        <v>1422</v>
       </c>
       <c r="D135" s="70"/>
       <c r="E135" s="70"/>
@@ -26468,7 +26672,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="22.5" customHeight="1">
@@ -26476,10 +26680,10 @@
         <v>641</v>
       </c>
       <c r="B136" s="81" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="C136" s="82" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="D136" s="83"/>
       <c r="E136" s="83"/>
@@ -26495,7 +26699,7 @@
         <v>74</v>
       </c>
       <c r="K136" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="22.5" customHeight="1">
@@ -26503,10 +26707,10 @@
         <v>642</v>
       </c>
       <c r="B137" s="77" t="s">
-        <v>1412</v>
+        <v>1423</v>
       </c>
       <c r="C137" s="76" t="s">
-        <v>1413</v>
+        <v>1424</v>
       </c>
       <c r="D137" s="70"/>
       <c r="E137" s="70"/>
@@ -26522,7 +26726,7 @@
         <v>74</v>
       </c>
       <c r="K137" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="22.5" customHeight="1">
@@ -26530,10 +26734,10 @@
         <v>643</v>
       </c>
       <c r="B138" s="81" t="s">
-        <v>1414</v>
+        <v>1425</v>
       </c>
       <c r="C138" s="82" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="D138" s="83"/>
       <c r="E138" s="83"/>
@@ -26551,7 +26755,7 @@
         <v>74</v>
       </c>
       <c r="K138" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="22.5" customHeight="1">
@@ -26559,13 +26763,13 @@
         <v>462</v>
       </c>
       <c r="B139" s="104" t="s">
-        <v>1415</v>
+        <v>1426</v>
       </c>
       <c r="C139" s="104" t="s">
-        <v>1416</v>
+        <v>1427</v>
       </c>
       <c r="D139" s="62" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E139" s="63"/>
       <c r="F139" s="64" t="s">
@@ -26584,7 +26788,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="104" t="s">
-        <v>1309</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="22.5" customHeight="1">
@@ -26592,10 +26796,10 @@
         <v>644</v>
       </c>
       <c r="B140" s="81" t="s">
-        <v>1417</v>
+        <v>1428</v>
       </c>
       <c r="C140" s="82" t="s">
-        <v>1418</v>
+        <v>1429</v>
       </c>
       <c r="D140" s="83"/>
       <c r="E140" s="83"/>
@@ -26613,7 +26817,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="22.5" customHeight="1">
@@ -26621,10 +26825,10 @@
         <v>645</v>
       </c>
       <c r="B141" s="77" t="s">
-        <v>1419</v>
+        <v>1430</v>
       </c>
       <c r="C141" s="76" t="s">
-        <v>1420</v>
+        <v>1431</v>
       </c>
       <c r="D141" s="70"/>
       <c r="E141" s="70"/>
@@ -26640,7 +26844,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="22.5" customHeight="1">
@@ -26648,7 +26852,7 @@
         <v>646</v>
       </c>
       <c r="B142" s="81" t="s">
-        <v>1421</v>
+        <v>1432</v>
       </c>
       <c r="C142" s="82" t="s">
         <v>1094</v>
@@ -26667,7 +26871,7 @@
         <v>74</v>
       </c>
       <c r="K142" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="22.5" customHeight="1">
@@ -26675,10 +26879,10 @@
         <v>647</v>
       </c>
       <c r="B143" s="77" t="s">
-        <v>1422</v>
+        <v>1433</v>
       </c>
       <c r="C143" s="76" t="s">
-        <v>1423</v>
+        <v>1434</v>
       </c>
       <c r="D143" s="70"/>
       <c r="E143" s="70"/>
@@ -26694,7 +26898,7 @@
         <v>74</v>
       </c>
       <c r="K143" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="22.5" customHeight="1">
@@ -26702,10 +26906,10 @@
         <v>648</v>
       </c>
       <c r="B144" s="81" t="s">
-        <v>1424</v>
+        <v>1435</v>
       </c>
       <c r="C144" s="82" t="s">
-        <v>1425</v>
+        <v>1436</v>
       </c>
       <c r="D144" s="83"/>
       <c r="E144" s="83"/>
@@ -26721,7 +26925,7 @@
         <v>74</v>
       </c>
       <c r="K144" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="22.5" customHeight="1">
@@ -26729,10 +26933,10 @@
         <v>649</v>
       </c>
       <c r="B145" s="77" t="s">
-        <v>1426</v>
+        <v>1437</v>
       </c>
       <c r="C145" s="76" t="s">
-        <v>1427</v>
+        <v>1438</v>
       </c>
       <c r="D145" s="70"/>
       <c r="E145" s="70"/>
@@ -26748,7 +26952,7 @@
         <v>25</v>
       </c>
       <c r="K145" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="22.5" customHeight="1">
@@ -26756,10 +26960,10 @@
         <v>650</v>
       </c>
       <c r="B146" s="81" t="s">
-        <v>1428</v>
+        <v>1439</v>
       </c>
       <c r="C146" s="82" t="s">
-        <v>1429</v>
+        <v>1440</v>
       </c>
       <c r="D146" s="83"/>
       <c r="E146" s="83"/>
@@ -26775,7 +26979,7 @@
         <v>74</v>
       </c>
       <c r="K146" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="22.5" customHeight="1">
@@ -26783,10 +26987,10 @@
         <v>651</v>
       </c>
       <c r="B147" s="77" t="s">
-        <v>1430</v>
+        <v>1441</v>
       </c>
       <c r="C147" s="76" t="s">
-        <v>1431</v>
+        <v>1442</v>
       </c>
       <c r="D147" s="70"/>
       <c r="E147" s="70"/>
@@ -26802,7 +27006,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="22.5" customHeight="1">
@@ -26810,10 +27014,10 @@
         <v>652</v>
       </c>
       <c r="B148" s="81" t="s">
-        <v>1432</v>
+        <v>1443</v>
       </c>
       <c r="C148" s="82" t="s">
-        <v>1433</v>
+        <v>1444</v>
       </c>
       <c r="D148" s="83"/>
       <c r="E148" s="83"/>
@@ -26829,7 +27033,7 @@
         <v>74</v>
       </c>
       <c r="K148" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="22.5" customHeight="1">
@@ -26837,10 +27041,10 @@
         <v>653</v>
       </c>
       <c r="B149" s="77" t="s">
-        <v>1434</v>
+        <v>1445</v>
       </c>
       <c r="C149" s="76" t="s">
-        <v>1435</v>
+        <v>1446</v>
       </c>
       <c r="D149" s="70"/>
       <c r="E149" s="70"/>
@@ -26856,7 +27060,7 @@
         <v>74</v>
       </c>
       <c r="K149" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="22.5" customHeight="1">
@@ -26864,11 +27068,11 @@
         <v>465</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1436</v>
+        <v>1447</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="166" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E150" s="167"/>
       <c r="F150" s="168"/>
@@ -26883,10 +27087,10 @@
         <v>654</v>
       </c>
       <c r="B151" s="82" t="s">
-        <v>1437</v>
+        <v>1448</v>
       </c>
       <c r="C151" s="82" t="s">
-        <v>1438</v>
+        <v>1449</v>
       </c>
       <c r="D151" s="83"/>
       <c r="E151" s="83"/>
@@ -26899,21 +27103,21 @@
       </c>
       <c r="I151" s="87"/>
       <c r="J151" s="90" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K151" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="22.5" customHeight="1">
       <c r="A152" s="8" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B152" s="77" t="s">
-        <v>1439</v>
+        <v>1450</v>
       </c>
       <c r="C152" s="76" t="s">
-        <v>1440</v>
+        <v>1451</v>
       </c>
       <c r="D152" s="70"/>
       <c r="E152" s="70"/>
@@ -26929,18 +27133,18 @@
         <v>25</v>
       </c>
       <c r="K152" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="22.5" customHeight="1">
       <c r="A153" s="8" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B153" s="81" t="s">
-        <v>1441</v>
+        <v>1452</v>
       </c>
       <c r="C153" s="82" t="s">
-        <v>1442</v>
+        <v>1453</v>
       </c>
       <c r="D153" s="83"/>
       <c r="E153" s="83"/>
@@ -26956,18 +27160,18 @@
         <v>74</v>
       </c>
       <c r="K153" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="22.5" customHeight="1">
       <c r="A154" s="8" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B154" s="77" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="C154" s="76" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="D154" s="70"/>
       <c r="E154" s="70"/>
@@ -26983,18 +27187,18 @@
         <v>25</v>
       </c>
       <c r="K154" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="22.5" customHeight="1">
       <c r="A155" s="8" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B155" s="81" t="s">
-        <v>1443</v>
+        <v>1454</v>
       </c>
       <c r="C155" s="82" t="s">
-        <v>1444</v>
+        <v>1455</v>
       </c>
       <c r="D155" s="83"/>
       <c r="E155" s="83"/>
@@ -27012,18 +27216,18 @@
         <v>25</v>
       </c>
       <c r="K155" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="22.5" customHeight="1">
       <c r="A156" s="8" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B156" s="76" t="s">
-        <v>1445</v>
+        <v>1456</v>
       </c>
       <c r="C156" s="76" t="s">
-        <v>1446</v>
+        <v>1457</v>
       </c>
       <c r="D156" s="70"/>
       <c r="E156" s="70"/>
@@ -27039,18 +27243,18 @@
         <v>513</v>
       </c>
       <c r="K156" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="22.5" customHeight="1">
       <c r="A157" s="8" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B157" s="81" t="s">
-        <v>1447</v>
+        <v>1458</v>
       </c>
       <c r="C157" s="82" t="s">
-        <v>1448</v>
+        <v>1459</v>
       </c>
       <c r="D157" s="83"/>
       <c r="E157" s="83"/>
@@ -27068,18 +27272,18 @@
         <v>74</v>
       </c>
       <c r="K157" s="82" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="22.5" customHeight="1">
       <c r="A158" s="8" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B158" s="76" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="C158" s="76" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D158" s="70"/>
       <c r="E158" s="70"/>
@@ -27097,18 +27301,18 @@
         <v>25</v>
       </c>
       <c r="K158" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="22.5" customHeight="1">
       <c r="A159" s="8" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B159" s="77" t="s">
-        <v>1449</v>
+        <v>1460</v>
       </c>
       <c r="C159" s="76" t="s">
-        <v>1450</v>
+        <v>1461</v>
       </c>
       <c r="D159" s="10"/>
       <c r="E159" s="11"/>
@@ -27124,18 +27328,18 @@
         <v>25</v>
       </c>
       <c r="K159" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="22.5" customHeight="1">
       <c r="A160" s="8" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B160" s="77" t="s">
-        <v>1451</v>
+        <v>1462</v>
       </c>
       <c r="C160" s="76" t="s">
-        <v>1452</v>
+        <v>1463</v>
       </c>
       <c r="D160" s="10"/>
       <c r="E160" s="11"/>
@@ -27151,7 +27355,7 @@
         <v>25</v>
       </c>
       <c r="K160" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="22.5" customHeight="1">
@@ -27161,7 +27365,7 @@
       <c r="B161" s="9"/>
       <c r="C161" s="5"/>
       <c r="D161" s="62" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E161" s="167"/>
       <c r="F161" s="102"/>
@@ -27173,13 +27377,13 @@
     </row>
     <row r="162" spans="1:11" ht="22.5" customHeight="1">
       <c r="A162" s="8" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>1453</v>
+        <v>1464</v>
       </c>
       <c r="D162" s="10"/>
       <c r="E162" s="11"/>
@@ -27197,18 +27401,18 @@
         <v>74</v>
       </c>
       <c r="K162" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="22.5" customHeight="1">
       <c r="A163" s="8" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="D163" s="10"/>
       <c r="E163" s="11"/>
@@ -27226,18 +27430,18 @@
         <v>25</v>
       </c>
       <c r="K163" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="22.5" customHeight="1">
       <c r="A164" s="8" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="D164" s="10"/>
       <c r="E164" s="11"/>
@@ -27252,21 +27456,21 @@
       </c>
       <c r="I164" s="13"/>
       <c r="J164" s="14" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K164" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="22.5" customHeight="1">
       <c r="A165" s="8" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="D165" s="10"/>
       <c r="E165" s="11"/>
@@ -27284,7 +27488,7 @@
         <v>551</v>
       </c>
       <c r="K165" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="22.5" customHeight="1">
@@ -27321,10 +27525,10 @@
         <v>11</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="D167" s="10"/>
       <c r="E167" s="11"/>
@@ -27342,7 +27546,7 @@
         <v>551</v>
       </c>
       <c r="K167" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="22.5" customHeight="1">
@@ -27379,10 +27583,10 @@
         <v>18</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="D169" s="10"/>
       <c r="E169" s="11"/>
@@ -27400,7 +27604,7 @@
         <v>551</v>
       </c>
       <c r="K169" s="76" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="22.5" customHeight="1">
@@ -28952,10 +29156,10 @@
     <row r="248" spans="1:11" ht="22.5" customHeight="1">
       <c r="A248" s="46"/>
       <c r="B248" s="9" t="s">
-        <v>1454</v>
+        <v>1465</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>1455</v>
+        <v>1466</v>
       </c>
       <c r="D248" s="10"/>
       <c r="E248" s="48" t="s">

--- a/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
+++ b/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlando.carvajal.DESMEX\Desktop\ClaudeCode\Pipeline1\pipeline-web\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06111943-CD1E-4FE6-9C9F-BA263163C4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46E7B812-D90F-416E-B00A-14D1BCEEBAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Copia seguridad 27-01-2026" sheetId="9" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$L$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$L$214</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Copia seguridad 27-01-2026'!$A$1:$K$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Daniela Lara'!$A$1:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Josué Morales'!$A$1:$K$148</definedName>
@@ -50,11 +50,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={e486e15b-6e62-4266-9919-8644122bfe6b}</author>
-    <author>tc={c7ed0c02-4231-43e4-b355-89166dd53e3e}</author>
+    <author>tc={b3541e79-7142-4e55-b220-7706f78da251}</author>
+    <author>tc={fd5a665c-4ee9-467e-b1ab-105dbaf1c13e}</author>
   </authors>
   <commentList>
-    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{E486E15B-6E62-4266-9919-8644122BFE6B}">
+    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{B3541E79-7142-4E55-B220-7706F78DA251}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -62,7 +62,7 @@
     ya lo tiene en seguimiento Josué</t>
       </text>
     </comment>
-    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{C7ED0C02-4231-43E4-B355-89166DD53E3E}">
+    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{FD5A665C-4EE9-467E-B1AB-105DBAF1C13E}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4782" uniqueCount="1467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4784" uniqueCount="1468">
   <si>
     <t>ID de Prospecto</t>
   </si>
@@ -3759,6 +3759,9 @@
   </si>
   <si>
     <t>Polesazinc</t>
+  </si>
+  <si>
+    <t>Arq. Alejandra Vergara</t>
   </si>
   <si>
     <r>
@@ -5757,7 +5760,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Anónimo" id="{55861A80-B128-4B50-9A2A-1BD4FD1E5499}" userId="" providerId="google-sheets"/>
+  <person displayName="Anónimo" id="{800B8EA1-66A5-4344-9FAA-9DC8A887D0FD}" userId="" providerId="google-sheets"/>
 </personList>
 </file>
 
@@ -5803,7 +5806,17 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabla_6" displayName="Tabla_6" ref="A1:L115">
-  <autoFilter ref="A1:L115" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+  <autoFilter ref="A1:L115" xr:uid="{00000000-0009-0000-0100-000004000000}">
+    <filterColumn colId="5">
+      <filters blank="1">
+        <filter val="10. Negociación"/>
+        <filter val="5. Visita Técnica / Diagnóstico en Sitio"/>
+        <filter val="6. Diseño de Solución / Pre-Ingeniería"/>
+        <filter val="7. Estimación / Cotización"/>
+        <filter val="8. Propuesta Enviada"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="ID de Prospecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Nombre del Prospecto"/>
@@ -5823,8 +5836,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:L213">
-  <autoFilter ref="A1:L213" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:L214">
+  <autoFilter ref="A1:L214" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID de Prospecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Nombre del Prospecto"/>
@@ -6101,10 +6114,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{55861A80-B128-4B50-9A2A-1BD4FD1E5499}" id="{E486E15B-6E62-4266-9919-8644122BFE6B}" done="1">
+  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{800B8EA1-66A5-4344-9FAA-9DC8A887D0FD}" id="{B3541E79-7142-4E55-B220-7706F78DA251}" done="1">
     <text>ya lo tiene en seguimiento Josué</text>
   </threadedComment>
-  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{55861A80-B128-4B50-9A2A-1BD4FD1E5499}" id="{C7ED0C02-4231-43E4-B355-89166DD53E3E}" done="1">
+  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{800B8EA1-66A5-4344-9FAA-9DC8A887D0FD}" id="{FD5A665C-4EE9-467E-B1AB-105DBAF1C13E}" done="1">
     <text>Ya tienen contrato con Ammper</text>
   </threadedComment>
 </ThreadedComments>
@@ -11939,7 +11952,7 @@
       <c r="AB1" s="7"/>
       <c r="AC1" s="7"/>
     </row>
-    <row r="2" spans="1:29" ht="22.5" customHeight="1">
+    <row r="2" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A2" s="46" t="s">
         <v>445</v>
       </c>
@@ -11975,7 +11988,7 @@
       </c>
       <c r="L2" s="57"/>
     </row>
-    <row r="3" spans="1:29" ht="22.5" customHeight="1">
+    <row r="3" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A3" s="46" t="s">
         <v>451</v>
       </c>
@@ -12011,7 +12024,7 @@
       </c>
       <c r="L3" s="57"/>
     </row>
-    <row r="4" spans="1:29" ht="22.5" customHeight="1">
+    <row r="4" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A4" s="46" t="s">
         <v>454</v>
       </c>
@@ -12047,7 +12060,7 @@
       </c>
       <c r="L4" s="57"/>
     </row>
-    <row r="5" spans="1:29" ht="22.5" customHeight="1">
+    <row r="5" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A5" s="46" t="s">
         <v>457</v>
       </c>
@@ -12083,7 +12096,7 @@
       </c>
       <c r="L5" s="57"/>
     </row>
-    <row r="6" spans="1:29" ht="22.5" customHeight="1">
+    <row r="6" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A6" s="46" t="s">
         <v>668</v>
       </c>
@@ -12119,7 +12132,7 @@
       </c>
       <c r="L6" s="57"/>
     </row>
-    <row r="7" spans="1:29" ht="22.5" customHeight="1">
+    <row r="7" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A7" s="46" t="s">
         <v>459</v>
       </c>
@@ -12191,7 +12204,7 @@
       </c>
       <c r="L8" s="57"/>
     </row>
-    <row r="9" spans="1:29" ht="22.5" customHeight="1">
+    <row r="9" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A9" s="46" t="s">
         <v>465</v>
       </c>
@@ -12227,7 +12240,7 @@
       </c>
       <c r="L9" s="57"/>
     </row>
-    <row r="10" spans="1:29" ht="22.5" customHeight="1">
+    <row r="10" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A10" s="46" t="s">
         <v>468</v>
       </c>
@@ -12263,7 +12276,7 @@
       </c>
       <c r="L10" s="57"/>
     </row>
-    <row r="11" spans="1:29" ht="22.5" customHeight="1">
+    <row r="11" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A11" s="46" t="s">
         <v>471</v>
       </c>
@@ -12299,7 +12312,7 @@
       </c>
       <c r="L11" s="57"/>
     </row>
-    <row r="12" spans="1:29" ht="22.5" customHeight="1">
+    <row r="12" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A12" s="46" t="s">
         <v>474</v>
       </c>
@@ -12335,7 +12348,7 @@
       </c>
       <c r="L12" s="57"/>
     </row>
-    <row r="13" spans="1:29" ht="22.5" customHeight="1">
+    <row r="13" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A13" s="46" t="s">
         <v>477</v>
       </c>
@@ -12371,7 +12384,7 @@
       </c>
       <c r="L13" s="57"/>
     </row>
-    <row r="14" spans="1:29" ht="22.5" customHeight="1">
+    <row r="14" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A14" s="46" t="s">
         <v>481</v>
       </c>
@@ -12443,7 +12456,7 @@
       </c>
       <c r="L15" s="57"/>
     </row>
-    <row r="16" spans="1:29" ht="22.5" customHeight="1">
+    <row r="16" spans="1:29" ht="22.5" hidden="1" customHeight="1">
       <c r="A16" s="46" t="s">
         <v>488</v>
       </c>
@@ -12587,7 +12600,7 @@
       </c>
       <c r="L19" s="57"/>
     </row>
-    <row r="20" spans="1:12" ht="22.5" customHeight="1">
+    <row r="20" spans="1:12" ht="22.5" hidden="1" customHeight="1">
       <c r="A20" s="46" t="s">
         <v>500</v>
       </c>
@@ -12659,7 +12672,7 @@
       </c>
       <c r="L21" s="57"/>
     </row>
-    <row r="22" spans="1:12" ht="22.5" customHeight="1">
+    <row r="22" spans="1:12" ht="22.5" hidden="1" customHeight="1">
       <c r="A22" s="46" t="s">
         <v>506</v>
       </c>
@@ -12695,7 +12708,7 @@
       </c>
       <c r="L22" s="57"/>
     </row>
-    <row r="23" spans="1:12" ht="22.5" customHeight="1">
+    <row r="23" spans="1:12" ht="22.5" hidden="1" customHeight="1">
       <c r="A23" s="46" t="s">
         <v>510</v>
       </c>
@@ -12767,7 +12780,7 @@
       </c>
       <c r="L24" s="57"/>
     </row>
-    <row r="25" spans="1:12" ht="22.5" customHeight="1">
+    <row r="25" spans="1:12" ht="22.5" hidden="1" customHeight="1">
       <c r="A25" s="46" t="s">
         <v>517</v>
       </c>
@@ -12803,7 +12816,7 @@
       </c>
       <c r="L25" s="57"/>
     </row>
-    <row r="26" spans="1:12" ht="22.5" customHeight="1">
+    <row r="26" spans="1:12" ht="22.5" hidden="1" customHeight="1">
       <c r="A26" s="46" t="s">
         <v>520</v>
       </c>
@@ -12837,7 +12850,7 @@
       </c>
       <c r="L26" s="57"/>
     </row>
-    <row r="27" spans="1:12" ht="22.5" customHeight="1">
+    <row r="27" spans="1:12" ht="22.5" hidden="1" customHeight="1">
       <c r="A27" s="46" t="s">
         <v>523</v>
       </c>
@@ -12873,7 +12886,7 @@
       </c>
       <c r="L27" s="57"/>
     </row>
-    <row r="28" spans="1:12" ht="22.5" customHeight="1">
+    <row r="28" spans="1:12" ht="22.5" hidden="1" customHeight="1">
       <c r="A28" s="46" t="s">
         <v>527</v>
       </c>
@@ -12909,7 +12922,7 @@
       </c>
       <c r="L28" s="57"/>
     </row>
-    <row r="29" spans="1:12" ht="22.5" customHeight="1">
+    <row r="29" spans="1:12" ht="22.5" hidden="1" customHeight="1">
       <c r="A29" s="46" t="s">
         <v>531</v>
       </c>
@@ -12945,7 +12958,7 @@
       </c>
       <c r="L29" s="57"/>
     </row>
-    <row r="30" spans="1:12" ht="22.5" customHeight="1">
+    <row r="30" spans="1:12" ht="22.5" hidden="1" customHeight="1">
       <c r="A30" s="46" t="s">
         <v>534</v>
       </c>
@@ -12981,7 +12994,7 @@
       </c>
       <c r="L30" s="57"/>
     </row>
-    <row r="31" spans="1:12" ht="22.5" customHeight="1">
+    <row r="31" spans="1:12" ht="22.5" hidden="1" customHeight="1">
       <c r="A31" s="46" t="s">
         <v>538</v>
       </c>
@@ -13017,7 +13030,7 @@
       </c>
       <c r="L31" s="57"/>
     </row>
-    <row r="32" spans="1:12" ht="22.5" customHeight="1">
+    <row r="32" spans="1:12" ht="22.5" hidden="1" customHeight="1">
       <c r="A32" s="46" t="s">
         <v>541</v>
       </c>
@@ -13089,7 +13102,7 @@
       </c>
       <c r="L33" s="57"/>
     </row>
-    <row r="34" spans="1:12" ht="22.5" customHeight="1">
+    <row r="34" spans="1:12" ht="22.5" hidden="1" customHeight="1">
       <c r="A34" s="46" t="s">
         <v>547</v>
       </c>
@@ -14668,7 +14681,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC213"/>
+  <dimension ref="A1:AC214"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -14754,7 +14767,7 @@
         <v>448</v>
       </c>
       <c r="F2" s="53" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="G2" s="54">
         <v>46111</v>
@@ -21331,21 +21344,39 @@
       <c r="K213" s="46"/>
       <c r="L213" s="46"/>
     </row>
+    <row r="214" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A214" s="46"/>
+      <c r="B214" s="9" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C214" s="46"/>
+      <c r="D214" s="10"/>
+      <c r="E214" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F214" s="53"/>
+      <c r="G214" s="54"/>
+      <c r="H214" s="55"/>
+      <c r="I214" s="56"/>
+      <c r="J214" s="53"/>
+      <c r="K214" s="46"/>
+      <c r="L214" s="46"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="F2:F213" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F214" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"1. Prospección,2. Contacto Inicial,3. Calificación,4. Levantamiento de Requerimientos,5. Visita Técnica / Diagnóstico en Sitio,6. Diseño de Solución / Pre-Ingeniería,7. Estimación / Cotización,8. Propuesta Enviada,9. Aclaraciones / Ajustes de Propuesta,10"&amp;". Negociación,11. Aprobación Interna (Go/No-Go),12. Cierre de Venta (Contrato / OC),13. Kickoff / Inicio de Proyecto,14. Descartado / No Califica,15. En Pausa / Seguimiento Posterior"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G213" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G214" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G2))), AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I213" xr:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I214" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>AND(ISNUMBER(H2),(NOT(OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J213" xr:uid="{00000000-0002-0000-0400-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J214" xr:uid="{00000000-0002-0000-0400-000003000000}">
       <formula1>"Referido (Cliente),Referido (Proveedor/Subcontratista),Referido (Empleado/Interno),Cliente Recurrente (Recompra/Ampliación),Sitio Web (Formulario),Landing Page (Campaña),Chat Web / WhatsApp,SEO (Búsqueda Orgánica),Google Ads (Search),Remarketing (Display/"&amp;"Redes),LinkedIn (Orgánico),Email Outbound (Prospección),Llamada en Frío (Prospección),Visita en Frío (Prospección),Feria / Expo Industrial,Congreso / Cámara / Networking,Webinar / Evento Virtual,Licitación Pública,Licitación Privada (RFP/RFQ),Portal de Co"&amp;"mpras (Cliente),Alianza (Integrador/EPC/Constructor),Partner Tecnológico (Marca/Distribuidor),Directorio B2B / Clúster,Redes Sociales (Facebook/Instagram),YouTube / Contenido Técnico,PR / Medio Especializado,Reactivación de Base de Datos,Otros"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C213 E2:E213 K2:K213" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C214 E2:E214 K2:K214" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -21611,10 +21642,10 @@
         <v>481</v>
       </c>
       <c r="B2" s="69" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D2" s="70"/>
       <c r="E2" s="70"/>
@@ -21634,7 +21665,7 @@
         <v>25</v>
       </c>
       <c r="K2" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="21" customHeight="1">
@@ -21642,10 +21673,10 @@
         <v>484</v>
       </c>
       <c r="B3" s="77" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="C3" s="76" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D3" s="70"/>
       <c r="E3" s="70"/>
@@ -21663,7 +21694,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -21671,10 +21702,10 @@
         <v>488</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="C4" s="82" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="D4" s="83"/>
       <c r="E4" s="70"/>
@@ -21692,7 +21723,7 @@
         <v>25</v>
       </c>
       <c r="K4" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -21700,10 +21731,10 @@
         <v>491</v>
       </c>
       <c r="B5" s="81" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C5" s="82" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="D5" s="83"/>
       <c r="E5" s="70"/>
@@ -21721,7 +21752,7 @@
         <v>782</v>
       </c>
       <c r="K5" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -21729,10 +21760,10 @@
         <v>494</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="C6" s="82" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="D6" s="83"/>
       <c r="E6" s="70"/>
@@ -21750,7 +21781,7 @@
         <v>74</v>
       </c>
       <c r="K6" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -21758,10 +21789,10 @@
         <v>497</v>
       </c>
       <c r="B7" s="77" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C7" s="76" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D7" s="70"/>
       <c r="E7" s="70"/>
@@ -21777,7 +21808,7 @@
         <v>25</v>
       </c>
       <c r="K7" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -21785,10 +21816,10 @@
         <v>500</v>
       </c>
       <c r="B8" s="77" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="D8" s="70"/>
       <c r="E8" s="70"/>
@@ -21806,7 +21837,7 @@
         <v>74</v>
       </c>
       <c r="K8" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -21814,10 +21845,10 @@
         <v>503</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="C9" s="82" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="D9" s="83"/>
       <c r="E9" s="70"/>
@@ -21835,7 +21866,7 @@
         <v>74</v>
       </c>
       <c r="K9" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -21843,10 +21874,10 @@
         <v>506</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C10" s="76" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
@@ -21864,7 +21895,7 @@
         <v>25</v>
       </c>
       <c r="K10" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -21872,10 +21903,10 @@
         <v>514</v>
       </c>
       <c r="B11" s="81" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C11" s="82" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="D11" s="83"/>
       <c r="E11" s="70"/>
@@ -21893,7 +21924,7 @@
         <v>74</v>
       </c>
       <c r="K11" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -21901,10 +21932,10 @@
         <v>517</v>
       </c>
       <c r="B12" s="81" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C12" s="82" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="D12" s="83"/>
       <c r="E12" s="70"/>
@@ -21922,7 +21953,7 @@
         <v>74</v>
       </c>
       <c r="K12" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -21930,10 +21961,10 @@
         <v>520</v>
       </c>
       <c r="B13" s="77" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
@@ -21951,7 +21982,7 @@
         <v>25</v>
       </c>
       <c r="K13" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -21959,10 +21990,10 @@
         <v>523</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C14" s="82" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="D14" s="83"/>
       <c r="E14" s="70"/>
@@ -21978,7 +22009,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -21986,10 +22017,10 @@
         <v>527</v>
       </c>
       <c r="B15" s="99" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="C15" s="82" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D15" s="83"/>
       <c r="E15" s="70"/>
@@ -22007,7 +22038,7 @@
         <v>74</v>
       </c>
       <c r="K15" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
@@ -22015,10 +22046,10 @@
         <v>531</v>
       </c>
       <c r="B16" s="77" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C16" s="76" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
@@ -22034,7 +22065,7 @@
         <v>25</v>
       </c>
       <c r="K16" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
@@ -22042,10 +22073,10 @@
         <v>534</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="C17" s="76" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="D17" s="70"/>
       <c r="E17" s="70"/>
@@ -22065,7 +22096,7 @@
         <v>25</v>
       </c>
       <c r="K17" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="22.5" customHeight="1">
@@ -22073,10 +22104,10 @@
         <v>538</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="70"/>
@@ -22096,7 +22127,7 @@
         <v>74</v>
       </c>
       <c r="K18" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="22.5" customHeight="1">
@@ -22104,10 +22135,10 @@
         <v>541</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="11"/>
@@ -22127,7 +22158,7 @@
         <v>513</v>
       </c>
       <c r="K19" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="22.5" customHeight="1">
@@ -22135,10 +22166,10 @@
         <v>544</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -22156,7 +22187,7 @@
         <v>25</v>
       </c>
       <c r="K20" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="22.5" customHeight="1">
@@ -22164,10 +22195,10 @@
         <v>547</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="C21" s="76" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -22185,7 +22216,7 @@
         <v>745</v>
       </c>
       <c r="K21" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="22.5" customHeight="1">
@@ -22193,10 +22224,10 @@
         <v>552</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C22" s="76" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="11"/>
@@ -22214,7 +22245,7 @@
         <v>551</v>
       </c>
       <c r="K22" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="22.5" customHeight="1">
@@ -22222,10 +22253,10 @@
         <v>555</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C23" s="76" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="11"/>
@@ -22243,7 +22274,7 @@
         <v>551</v>
       </c>
       <c r="K23" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="22.5" customHeight="1">
@@ -22251,10 +22282,10 @@
         <v>558</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C24" s="76" t="s">
         <v>1271</v>
-      </c>
-      <c r="C24" s="76" t="s">
-        <v>1270</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -22272,7 +22303,7 @@
         <v>551</v>
       </c>
       <c r="K24" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="22.5" customHeight="1">
@@ -22280,10 +22311,10 @@
         <v>558</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="11"/>
@@ -22303,7 +22334,7 @@
         <v>513</v>
       </c>
       <c r="K25" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -22311,10 +22342,10 @@
         <v>558</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="11"/>
@@ -22334,7 +22365,7 @@
         <v>551</v>
       </c>
       <c r="K26" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="22.5" customHeight="1">
@@ -22342,10 +22373,10 @@
         <v>562</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -22363,7 +22394,7 @@
         <v>513</v>
       </c>
       <c r="K27" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="22.5" customHeight="1">
@@ -22371,10 +22402,10 @@
         <v>565</v>
       </c>
       <c r="B28" s="9" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>1278</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>1277</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -22392,7 +22423,7 @@
         <v>513</v>
       </c>
       <c r="K28" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="22.5" customHeight="1">
@@ -22400,10 +22431,10 @@
         <v>568</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="11"/>
@@ -22419,7 +22450,7 @@
       <c r="I29" s="45"/>
       <c r="J29" s="14"/>
       <c r="K29" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
   </sheetData>
@@ -22542,10 +22573,10 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="D2" s="101"/>
       <c r="E2" s="101" t="s">
@@ -22563,7 +22594,7 @@
         <v>782</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -22571,10 +22602,10 @@
         <v>451</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
@@ -22596,7 +22627,7 @@
         <v>782</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -22604,14 +22635,14 @@
         <v>454</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>449</v>
@@ -22625,7 +22656,7 @@
         <v>782</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -22633,10 +22664,10 @@
         <v>457</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
@@ -22658,7 +22689,7 @@
         <v>688</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -22666,10 +22697,10 @@
         <v>668</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
@@ -22687,7 +22718,7 @@
         <v>688</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -22695,10 +22726,10 @@
         <v>459</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
@@ -22716,7 +22747,7 @@
         <v>782</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -22724,10 +22755,10 @@
         <v>462</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
@@ -22745,7 +22776,7 @@
         <v>25</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -22753,14 +22784,14 @@
         <v>465</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="F9" s="53" t="s">
         <v>40</v>
@@ -22774,7 +22805,7 @@
         <v>659</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -22782,10 +22813,10 @@
         <v>468</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
@@ -22803,7 +22834,7 @@
         <v>659</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -22811,14 +22842,14 @@
         <v>471</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="F11" s="53" t="s">
         <v>32</v>
@@ -22832,7 +22863,7 @@
         <v>659</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -22840,10 +22871,10 @@
         <v>474</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
@@ -22859,7 +22890,7 @@
         <v>659</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -22867,10 +22898,10 @@
         <v>477</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
@@ -22892,7 +22923,7 @@
         <v>659</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -22900,10 +22931,10 @@
         <v>481</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10" t="s">
@@ -22923,7 +22954,7 @@
         <v>782</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -22931,10 +22962,10 @@
         <v>484</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10" t="s">
@@ -22954,10 +22985,10 @@
         <v>488</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -22977,7 +23008,7 @@
         <v>659</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
@@ -22985,10 +23016,10 @@
         <v>491</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10" t="s">
@@ -23008,10 +23039,10 @@
         <v>494</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10" t="s">
@@ -23031,10 +23062,10 @@
         <v>497</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10" t="s">
@@ -23054,10 +23085,10 @@
         <v>500</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10" t="s">
@@ -23217,7 +23248,7 @@
         <v>782</v>
       </c>
       <c r="K2" s="104" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -23225,10 +23256,10 @@
         <v>471</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C3" s="82" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="D3" s="83"/>
       <c r="E3" s="83"/>
@@ -23244,7 +23275,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -23532,10 +23563,10 @@
         <v>474</v>
       </c>
       <c r="B14" s="107" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C14" s="108" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="D14" s="109"/>
       <c r="E14" s="109"/>
@@ -23553,7 +23584,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -23843,10 +23874,10 @@
         <v>477</v>
       </c>
       <c r="B25" s="117" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C25" s="118" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D25" s="119"/>
       <c r="E25" s="119"/>
@@ -23864,7 +23895,7 @@
         <v>25</v>
       </c>
       <c r="K25" s="125" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -24162,10 +24193,10 @@
         <v>481</v>
       </c>
       <c r="B36" s="126" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C36" s="127" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="D36" s="128"/>
       <c r="E36" s="128"/>
@@ -24181,7 +24212,7 @@
         <v>25</v>
       </c>
       <c r="K36" s="134" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="22.5" customHeight="1">
@@ -24313,7 +24344,7 @@
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D42" s="17"/>
       <c r="E42" s="18"/>
@@ -24388,10 +24419,10 @@
         <v>484</v>
       </c>
       <c r="B46" s="107" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="C46" s="108" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D46" s="109"/>
       <c r="E46" s="109"/>
@@ -24409,7 +24440,7 @@
         <v>74</v>
       </c>
       <c r="K46" s="115" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="22.5" customHeight="1">
@@ -24609,10 +24640,10 @@
         <v>488</v>
       </c>
       <c r="B57" s="135" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="C57" s="136" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="D57" s="137"/>
       <c r="E57" s="137"/>
@@ -24630,7 +24661,7 @@
         <v>25</v>
       </c>
       <c r="K57" s="143" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="22.5" customHeight="1">
@@ -24848,10 +24879,10 @@
         <v>491</v>
       </c>
       <c r="B68" s="107" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C68" s="108" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="D68" s="109"/>
       <c r="E68" s="109"/>
@@ -24867,7 +24898,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="115" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="22.5" customHeight="1">
@@ -25083,10 +25114,10 @@
         <v>494</v>
       </c>
       <c r="B79" s="126" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C79" s="127" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="D79" s="128"/>
       <c r="E79" s="128"/>
@@ -25104,7 +25135,7 @@
         <v>782</v>
       </c>
       <c r="K79" s="134" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="22.5" customHeight="1">
@@ -25154,10 +25185,10 @@
         <v>497</v>
       </c>
       <c r="B82" s="117" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C82" s="118" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D82" s="119"/>
       <c r="E82" s="119"/>
@@ -25175,7 +25206,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="125" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="22.5" customHeight="1">
@@ -25183,10 +25214,10 @@
         <v>500</v>
       </c>
       <c r="B83" s="126" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="C83" s="127" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="D83" s="128"/>
       <c r="E83" s="128"/>
@@ -25204,7 +25235,7 @@
         <v>74</v>
       </c>
       <c r="K83" s="134" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22.5" customHeight="1">
@@ -25212,10 +25243,10 @@
         <v>451</v>
       </c>
       <c r="B84" s="151" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="C84" s="151" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="D84" s="152" t="s">
         <v>810</v>
@@ -25237,7 +25268,7 @@
         <v>25</v>
       </c>
       <c r="K84" s="158" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="22.5" customHeight="1">
@@ -25245,10 +25276,10 @@
         <v>503</v>
       </c>
       <c r="B85" s="107" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="C85" s="108" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="D85" s="109"/>
       <c r="E85" s="109"/>
@@ -25266,7 +25297,7 @@
         <v>74</v>
       </c>
       <c r="K85" s="115" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="22.5" customHeight="1">
@@ -25274,10 +25305,10 @@
         <v>506</v>
       </c>
       <c r="B86" s="135" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C86" s="136" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="D86" s="137"/>
       <c r="E86" s="137"/>
@@ -25295,7 +25326,7 @@
         <v>74</v>
       </c>
       <c r="K86" s="143" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="22.5" customHeight="1">
@@ -25303,10 +25334,10 @@
         <v>510</v>
       </c>
       <c r="B87" s="108" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="C87" s="108" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="D87" s="109"/>
       <c r="E87" s="109"/>
@@ -25322,7 +25353,7 @@
         <v>782</v>
       </c>
       <c r="K87" s="115" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="22.5" customHeight="1">
@@ -25330,10 +25361,10 @@
         <v>514</v>
       </c>
       <c r="B88" s="135" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="C88" s="136" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="D88" s="137"/>
       <c r="E88" s="137"/>
@@ -25351,7 +25382,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="143" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="22.5" customHeight="1">
@@ -25359,10 +25390,10 @@
         <v>517</v>
       </c>
       <c r="B89" s="117" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="C89" s="118" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="D89" s="70"/>
       <c r="E89" s="70"/>
@@ -25380,7 +25411,7 @@
         <v>74</v>
       </c>
       <c r="K89" s="125" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="22.5" customHeight="1">
@@ -25388,10 +25419,10 @@
         <v>520</v>
       </c>
       <c r="B90" s="135" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C90" s="136" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="D90" s="83"/>
       <c r="E90" s="83"/>
@@ -25407,7 +25438,7 @@
         <v>74</v>
       </c>
       <c r="K90" s="143" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="22.5" customHeight="1">
@@ -25415,10 +25446,10 @@
         <v>523</v>
       </c>
       <c r="B91" s="77" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C91" s="76" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D91" s="70"/>
       <c r="E91" s="70"/>
@@ -25434,7 +25465,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="125" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22.5" customHeight="1">
@@ -25442,10 +25473,10 @@
         <v>527</v>
       </c>
       <c r="B92" s="81" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="C92" s="82" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D92" s="83"/>
       <c r="E92" s="83"/>
@@ -25463,7 +25494,7 @@
         <v>74</v>
       </c>
       <c r="K92" s="143" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="22.5" customHeight="1">
@@ -25471,10 +25502,10 @@
         <v>531</v>
       </c>
       <c r="B93" s="77" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="C93" s="76" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D93" s="70"/>
       <c r="E93" s="70"/>
@@ -25490,7 +25521,7 @@
         <v>74</v>
       </c>
       <c r="K93" s="125" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="22.5" customHeight="1">
@@ -25498,10 +25529,10 @@
         <v>534</v>
       </c>
       <c r="B94" s="81" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="C94" s="82" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D94" s="83"/>
       <c r="E94" s="83"/>
@@ -25517,7 +25548,7 @@
         <v>74</v>
       </c>
       <c r="K94" s="143" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="22.5" customHeight="1">
@@ -25525,10 +25556,10 @@
         <v>454</v>
       </c>
       <c r="B95" s="104" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="C95" s="104" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="D95" s="62" t="s">
         <v>888</v>
@@ -25550,7 +25581,7 @@
         <v>16</v>
       </c>
       <c r="K95" s="158" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="22.5" customHeight="1">
@@ -25558,10 +25589,10 @@
         <v>538</v>
       </c>
       <c r="B96" s="77" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="C96" s="76" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="D96" s="70"/>
       <c r="E96" s="70"/>
@@ -25577,7 +25608,7 @@
         <v>74</v>
       </c>
       <c r="K96" s="125" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="22.5" customHeight="1">
@@ -25585,7 +25616,7 @@
         <v>541</v>
       </c>
       <c r="B97" s="81" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="C97" s="82" t="s">
         <v>1078</v>
@@ -25604,7 +25635,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="22.5" customHeight="1">
@@ -25612,10 +25643,10 @@
         <v>544</v>
       </c>
       <c r="B98" s="77" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C98" s="76" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="D98" s="70"/>
       <c r="E98" s="70"/>
@@ -25633,7 +25664,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="22.5" customHeight="1">
@@ -25641,10 +25672,10 @@
         <v>547</v>
       </c>
       <c r="B99" s="81" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="C99" s="82" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="D99" s="83"/>
       <c r="E99" s="83"/>
@@ -25662,7 +25693,7 @@
         <v>74</v>
       </c>
       <c r="K99" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="22.5" customHeight="1">
@@ -25670,10 +25701,10 @@
         <v>552</v>
       </c>
       <c r="B100" s="77" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="C100" s="76" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D100" s="70"/>
       <c r="E100" s="70"/>
@@ -25689,7 +25720,7 @@
         <v>74</v>
       </c>
       <c r="K100" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="22.5" customHeight="1">
@@ -25697,10 +25728,10 @@
         <v>555</v>
       </c>
       <c r="B101" s="81" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="C101" s="82" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="D101" s="83"/>
       <c r="E101" s="83"/>
@@ -25716,7 +25747,7 @@
         <v>74</v>
       </c>
       <c r="K101" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="22.5" customHeight="1">
@@ -25724,10 +25755,10 @@
         <v>558</v>
       </c>
       <c r="B102" s="77" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="C102" s="76" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="D102" s="70"/>
       <c r="E102" s="70"/>
@@ -25743,7 +25774,7 @@
         <v>74</v>
       </c>
       <c r="K102" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="22.5" customHeight="1">
@@ -25751,10 +25782,10 @@
         <v>562</v>
       </c>
       <c r="B103" s="81" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="C103" s="82" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="D103" s="83"/>
       <c r="E103" s="83"/>
@@ -25770,7 +25801,7 @@
         <v>74</v>
       </c>
       <c r="K103" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="22.5" customHeight="1">
@@ -25778,10 +25809,10 @@
         <v>565</v>
       </c>
       <c r="B104" s="76" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C104" s="76" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="D104" s="70"/>
       <c r="E104" s="70"/>
@@ -25799,7 +25830,7 @@
         <v>25</v>
       </c>
       <c r="K104" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="22.5" customHeight="1">
@@ -25807,10 +25838,10 @@
         <v>568</v>
       </c>
       <c r="B105" s="81" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="C105" s="82" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D105" s="83"/>
       <c r="E105" s="83"/>
@@ -25828,7 +25859,7 @@
         <v>74</v>
       </c>
       <c r="K105" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="22.5" customHeight="1">
@@ -25836,10 +25867,10 @@
         <v>457</v>
       </c>
       <c r="B106" s="104" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="C106" s="104" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="D106" s="62" t="s">
         <v>540</v>
@@ -25861,7 +25892,7 @@
         <v>1192</v>
       </c>
       <c r="K106" s="104" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="22.5" customHeight="1">
@@ -25869,10 +25900,10 @@
         <v>571</v>
       </c>
       <c r="B107" s="77" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="C107" s="76" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="D107" s="70"/>
       <c r="E107" s="70"/>
@@ -25888,7 +25919,7 @@
         <v>25</v>
       </c>
       <c r="K107" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="22.5" customHeight="1">
@@ -25896,10 +25927,10 @@
         <v>574</v>
       </c>
       <c r="B108" s="81" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C108" s="82" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="D108" s="83"/>
       <c r="E108" s="83"/>
@@ -25915,7 +25946,7 @@
         <v>74</v>
       </c>
       <c r="K108" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="22.5" customHeight="1">
@@ -25923,10 +25954,10 @@
         <v>576</v>
       </c>
       <c r="B109" s="77" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="C109" s="76" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D109" s="70"/>
       <c r="E109" s="70"/>
@@ -25944,7 +25975,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="22.5" customHeight="1">
@@ -25952,10 +25983,10 @@
         <v>579</v>
       </c>
       <c r="B110" s="81" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="C110" s="82" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="D110" s="83"/>
       <c r="E110" s="83"/>
@@ -25971,7 +26002,7 @@
         <v>74</v>
       </c>
       <c r="K110" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="22.5" customHeight="1">
@@ -25979,10 +26010,10 @@
         <v>582</v>
       </c>
       <c r="B111" s="77" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="C111" s="76" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="D111" s="70"/>
       <c r="E111" s="70"/>
@@ -25998,7 +26029,7 @@
         <v>74</v>
       </c>
       <c r="K111" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="22.5" customHeight="1">
@@ -26006,10 +26037,10 @@
         <v>585</v>
       </c>
       <c r="B112" s="81" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="C112" s="82" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="D112" s="83"/>
       <c r="E112" s="83"/>
@@ -26025,7 +26056,7 @@
         <v>74</v>
       </c>
       <c r="K112" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="22.5" customHeight="1">
@@ -26033,10 +26064,10 @@
         <v>588</v>
       </c>
       <c r="B113" s="77" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="C113" s="76" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="D113" s="70"/>
       <c r="E113" s="70"/>
@@ -26052,7 +26083,7 @@
         <v>74</v>
       </c>
       <c r="K113" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="22.5" customHeight="1">
@@ -26060,10 +26091,10 @@
         <v>591</v>
       </c>
       <c r="B114" s="81" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="C114" s="82" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="D114" s="83"/>
       <c r="E114" s="83"/>
@@ -26079,7 +26110,7 @@
         <v>74</v>
       </c>
       <c r="K114" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="22.5" customHeight="1">
@@ -26087,7 +26118,7 @@
         <v>594</v>
       </c>
       <c r="B115" s="77" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="C115" s="76" t="s">
         <v>391</v>
@@ -26106,7 +26137,7 @@
         <v>74</v>
       </c>
       <c r="K115" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="22.5" customHeight="1">
@@ -26114,10 +26145,10 @@
         <v>597</v>
       </c>
       <c r="B116" s="81" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="C116" s="82" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="D116" s="83"/>
       <c r="E116" s="83"/>
@@ -26133,7 +26164,7 @@
         <v>74</v>
       </c>
       <c r="K116" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="22.5" customHeight="1">
@@ -26141,10 +26172,10 @@
         <v>668</v>
       </c>
       <c r="B117" s="104" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="C117" s="104" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="D117" s="62" t="s">
         <v>540</v>
@@ -26166,7 +26197,7 @@
         <v>1192</v>
       </c>
       <c r="K117" s="104" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="22.5" customHeight="1">
@@ -26174,10 +26205,10 @@
         <v>600</v>
       </c>
       <c r="B118" s="77" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="C118" s="76" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="D118" s="70"/>
       <c r="E118" s="70"/>
@@ -26193,7 +26224,7 @@
         <v>74</v>
       </c>
       <c r="K118" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="22.5" customHeight="1">
@@ -26201,10 +26232,10 @@
         <v>603</v>
       </c>
       <c r="B119" s="81" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C119" s="82" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="D119" s="83"/>
       <c r="E119" s="83"/>
@@ -26222,7 +26253,7 @@
         <v>74</v>
       </c>
       <c r="K119" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="22.5" customHeight="1">
@@ -26230,10 +26261,10 @@
         <v>606</v>
       </c>
       <c r="B120" s="77" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="C120" s="76" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="D120" s="70"/>
       <c r="E120" s="70"/>
@@ -26251,7 +26282,7 @@
         <v>74</v>
       </c>
       <c r="K120" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="22.5" customHeight="1">
@@ -26259,10 +26290,10 @@
         <v>609</v>
       </c>
       <c r="B121" s="81" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="C121" s="82" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="D121" s="83"/>
       <c r="E121" s="83"/>
@@ -26278,7 +26309,7 @@
         <v>74</v>
       </c>
       <c r="K121" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="22.5" customHeight="1">
@@ -26286,10 +26317,10 @@
         <v>612</v>
       </c>
       <c r="B122" s="77" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="C122" s="76" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="D122" s="70"/>
       <c r="E122" s="70"/>
@@ -26305,7 +26336,7 @@
         <v>74</v>
       </c>
       <c r="K122" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="22.5" customHeight="1">
@@ -26313,10 +26344,10 @@
         <v>615</v>
       </c>
       <c r="B123" s="81" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="C123" s="82" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D123" s="83"/>
       <c r="E123" s="83"/>
@@ -26332,7 +26363,7 @@
         <v>74</v>
       </c>
       <c r="K123" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="22.5" customHeight="1">
@@ -26340,10 +26371,10 @@
         <v>618</v>
       </c>
       <c r="B124" s="77" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="C124" s="76" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="D124" s="70"/>
       <c r="E124" s="70"/>
@@ -26361,7 +26392,7 @@
         <v>25</v>
       </c>
       <c r="K124" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="22.5" customHeight="1">
@@ -26369,10 +26400,10 @@
         <v>621</v>
       </c>
       <c r="B125" s="81" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="C125" s="82" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="D125" s="83"/>
       <c r="E125" s="83"/>
@@ -26388,7 +26419,7 @@
         <v>25</v>
       </c>
       <c r="K125" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="22.5" customHeight="1">
@@ -26396,10 +26427,10 @@
         <v>624</v>
       </c>
       <c r="B126" s="77" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="C126" s="76" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="D126" s="70"/>
       <c r="E126" s="70"/>
@@ -26415,7 +26446,7 @@
         <v>74</v>
       </c>
       <c r="K126" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="22.5" customHeight="1">
@@ -26423,10 +26454,10 @@
         <v>627</v>
       </c>
       <c r="B127" s="81" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="C127" s="82" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="D127" s="83"/>
       <c r="E127" s="83"/>
@@ -26442,7 +26473,7 @@
         <v>74</v>
       </c>
       <c r="K127" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="22.5" customHeight="1">
@@ -26450,10 +26481,10 @@
         <v>459</v>
       </c>
       <c r="B128" s="104" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="C128" s="104" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="D128" s="62" t="s">
         <v>540</v>
@@ -26475,7 +26506,7 @@
         <v>1036</v>
       </c>
       <c r="K128" s="104" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="22.5" customHeight="1">
@@ -26483,10 +26514,10 @@
         <v>630</v>
       </c>
       <c r="B129" s="77" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="C129" s="76" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="D129" s="70"/>
       <c r="E129" s="70"/>
@@ -26502,7 +26533,7 @@
         <v>74</v>
       </c>
       <c r="K129" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="22.5" customHeight="1">
@@ -26510,10 +26541,10 @@
         <v>633</v>
       </c>
       <c r="B130" s="81" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="C130" s="82" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="D130" s="83"/>
       <c r="E130" s="83"/>
@@ -26531,7 +26562,7 @@
         <v>74</v>
       </c>
       <c r="K130" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="22.5" customHeight="1">
@@ -26539,10 +26570,10 @@
         <v>636</v>
       </c>
       <c r="B131" s="77" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="C131" s="76" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="D131" s="70"/>
       <c r="E131" s="70"/>
@@ -26558,7 +26589,7 @@
         <v>74</v>
       </c>
       <c r="K131" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="22.5" customHeight="1">
@@ -26566,10 +26597,10 @@
         <v>637</v>
       </c>
       <c r="B132" s="81" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C132" s="82" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="D132" s="83"/>
       <c r="E132" s="83"/>
@@ -26587,7 +26618,7 @@
         <v>74</v>
       </c>
       <c r="K132" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="22.5" customHeight="1">
@@ -26595,10 +26626,10 @@
         <v>638</v>
       </c>
       <c r="B133" s="77" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C133" s="76" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D133" s="70"/>
       <c r="E133" s="70"/>
@@ -26616,7 +26647,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="22.5" customHeight="1">
@@ -26624,10 +26655,10 @@
         <v>639</v>
       </c>
       <c r="B134" s="81" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="C134" s="82" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="D134" s="83"/>
       <c r="E134" s="83"/>
@@ -26643,7 +26674,7 @@
         <v>25</v>
       </c>
       <c r="K134" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="22.5" customHeight="1">
@@ -26651,10 +26682,10 @@
         <v>640</v>
       </c>
       <c r="B135" s="77" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="C135" s="76" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D135" s="70"/>
       <c r="E135" s="70"/>
@@ -26672,7 +26703,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="22.5" customHeight="1">
@@ -26680,10 +26711,10 @@
         <v>641</v>
       </c>
       <c r="B136" s="81" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C136" s="82" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="D136" s="83"/>
       <c r="E136" s="83"/>
@@ -26699,7 +26730,7 @@
         <v>74</v>
       </c>
       <c r="K136" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="22.5" customHeight="1">
@@ -26707,10 +26738,10 @@
         <v>642</v>
       </c>
       <c r="B137" s="77" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="C137" s="76" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="D137" s="70"/>
       <c r="E137" s="70"/>
@@ -26726,7 +26757,7 @@
         <v>74</v>
       </c>
       <c r="K137" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="22.5" customHeight="1">
@@ -26734,10 +26765,10 @@
         <v>643</v>
       </c>
       <c r="B138" s="81" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C138" s="82" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D138" s="83"/>
       <c r="E138" s="83"/>
@@ -26755,7 +26786,7 @@
         <v>74</v>
       </c>
       <c r="K138" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="22.5" customHeight="1">
@@ -26763,10 +26794,10 @@
         <v>462</v>
       </c>
       <c r="B139" s="104" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C139" s="104" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="D139" s="62" t="s">
         <v>810</v>
@@ -26788,7 +26819,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="104" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="22.5" customHeight="1">
@@ -26796,10 +26827,10 @@
         <v>644</v>
       </c>
       <c r="B140" s="81" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="C140" s="82" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="D140" s="83"/>
       <c r="E140" s="83"/>
@@ -26817,7 +26848,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="22.5" customHeight="1">
@@ -26825,10 +26856,10 @@
         <v>645</v>
       </c>
       <c r="B141" s="77" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C141" s="76" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="D141" s="70"/>
       <c r="E141" s="70"/>
@@ -26844,7 +26875,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="22.5" customHeight="1">
@@ -26852,7 +26883,7 @@
         <v>646</v>
       </c>
       <c r="B142" s="81" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C142" s="82" t="s">
         <v>1094</v>
@@ -26871,7 +26902,7 @@
         <v>74</v>
       </c>
       <c r="K142" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="22.5" customHeight="1">
@@ -26879,10 +26910,10 @@
         <v>647</v>
       </c>
       <c r="B143" s="77" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="C143" s="76" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="D143" s="70"/>
       <c r="E143" s="70"/>
@@ -26898,7 +26929,7 @@
         <v>74</v>
       </c>
       <c r="K143" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="22.5" customHeight="1">
@@ -26906,10 +26937,10 @@
         <v>648</v>
       </c>
       <c r="B144" s="81" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="C144" s="82" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="D144" s="83"/>
       <c r="E144" s="83"/>
@@ -26925,7 +26956,7 @@
         <v>74</v>
       </c>
       <c r="K144" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="22.5" customHeight="1">
@@ -26933,10 +26964,10 @@
         <v>649</v>
       </c>
       <c r="B145" s="77" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="C145" s="76" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="D145" s="70"/>
       <c r="E145" s="70"/>
@@ -26952,7 +26983,7 @@
         <v>25</v>
       </c>
       <c r="K145" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="22.5" customHeight="1">
@@ -26960,10 +26991,10 @@
         <v>650</v>
       </c>
       <c r="B146" s="81" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C146" s="82" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="D146" s="83"/>
       <c r="E146" s="83"/>
@@ -26979,7 +27010,7 @@
         <v>74</v>
       </c>
       <c r="K146" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="22.5" customHeight="1">
@@ -26987,10 +27018,10 @@
         <v>651</v>
       </c>
       <c r="B147" s="77" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C147" s="76" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="D147" s="70"/>
       <c r="E147" s="70"/>
@@ -27006,7 +27037,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="22.5" customHeight="1">
@@ -27014,10 +27045,10 @@
         <v>652</v>
       </c>
       <c r="B148" s="81" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="C148" s="82" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="D148" s="83"/>
       <c r="E148" s="83"/>
@@ -27033,7 +27064,7 @@
         <v>74</v>
       </c>
       <c r="K148" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="22.5" customHeight="1">
@@ -27041,10 +27072,10 @@
         <v>653</v>
       </c>
       <c r="B149" s="77" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C149" s="76" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="D149" s="70"/>
       <c r="E149" s="70"/>
@@ -27060,7 +27091,7 @@
         <v>74</v>
       </c>
       <c r="K149" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="22.5" customHeight="1">
@@ -27068,7 +27099,7 @@
         <v>465</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="166" t="s">
@@ -27087,10 +27118,10 @@
         <v>654</v>
       </c>
       <c r="B151" s="82" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="C151" s="82" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="D151" s="83"/>
       <c r="E151" s="83"/>
@@ -27106,7 +27137,7 @@
         <v>782</v>
       </c>
       <c r="K151" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="22.5" customHeight="1">
@@ -27114,10 +27145,10 @@
         <v>746</v>
       </c>
       <c r="B152" s="77" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="C152" s="76" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="D152" s="70"/>
       <c r="E152" s="70"/>
@@ -27133,7 +27164,7 @@
         <v>25</v>
       </c>
       <c r="K152" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="22.5" customHeight="1">
@@ -27141,10 +27172,10 @@
         <v>747</v>
       </c>
       <c r="B153" s="81" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C153" s="82" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D153" s="83"/>
       <c r="E153" s="83"/>
@@ -27160,7 +27191,7 @@
         <v>74</v>
       </c>
       <c r="K153" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="22.5" customHeight="1">
@@ -27168,10 +27199,10 @@
         <v>748</v>
       </c>
       <c r="B154" s="77" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C154" s="76" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D154" s="70"/>
       <c r="E154" s="70"/>
@@ -27187,7 +27218,7 @@
         <v>25</v>
       </c>
       <c r="K154" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="22.5" customHeight="1">
@@ -27195,10 +27226,10 @@
         <v>749</v>
       </c>
       <c r="B155" s="81" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C155" s="82" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="D155" s="83"/>
       <c r="E155" s="83"/>
@@ -27216,7 +27247,7 @@
         <v>25</v>
       </c>
       <c r="K155" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="22.5" customHeight="1">
@@ -27224,10 +27255,10 @@
         <v>750</v>
       </c>
       <c r="B156" s="76" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C156" s="76" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="D156" s="70"/>
       <c r="E156" s="70"/>
@@ -27243,7 +27274,7 @@
         <v>513</v>
       </c>
       <c r="K156" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="22.5" customHeight="1">
@@ -27251,10 +27282,10 @@
         <v>751</v>
       </c>
       <c r="B157" s="81" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="C157" s="82" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="D157" s="83"/>
       <c r="E157" s="83"/>
@@ -27272,7 +27303,7 @@
         <v>74</v>
       </c>
       <c r="K157" s="82" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="22.5" customHeight="1">
@@ -27280,10 +27311,10 @@
         <v>752</v>
       </c>
       <c r="B158" s="76" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="C158" s="76" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="D158" s="70"/>
       <c r="E158" s="70"/>
@@ -27301,7 +27332,7 @@
         <v>25</v>
       </c>
       <c r="K158" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="22.5" customHeight="1">
@@ -27309,10 +27340,10 @@
         <v>753</v>
       </c>
       <c r="B159" s="77" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="C159" s="76" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="D159" s="10"/>
       <c r="E159" s="11"/>
@@ -27328,7 +27359,7 @@
         <v>25</v>
       </c>
       <c r="K159" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="22.5" customHeight="1">
@@ -27336,10 +27367,10 @@
         <v>754</v>
       </c>
       <c r="B160" s="77" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="C160" s="76" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="D160" s="10"/>
       <c r="E160" s="11"/>
@@ -27355,7 +27386,7 @@
         <v>25</v>
       </c>
       <c r="K160" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="22.5" customHeight="1">
@@ -27380,10 +27411,10 @@
         <v>755</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="D162" s="10"/>
       <c r="E162" s="11"/>
@@ -27401,7 +27432,7 @@
         <v>74</v>
       </c>
       <c r="K162" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="22.5" customHeight="1">
@@ -27409,10 +27440,10 @@
         <v>756</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="D163" s="10"/>
       <c r="E163" s="11"/>
@@ -27430,7 +27461,7 @@
         <v>25</v>
       </c>
       <c r="K163" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="22.5" customHeight="1">
@@ -27438,10 +27469,10 @@
         <v>757</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D164" s="10"/>
       <c r="E164" s="11"/>
@@ -27459,7 +27490,7 @@
         <v>745</v>
       </c>
       <c r="K164" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="22.5" customHeight="1">
@@ -27467,10 +27498,10 @@
         <v>758</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D165" s="10"/>
       <c r="E165" s="11"/>
@@ -27488,7 +27519,7 @@
         <v>551</v>
       </c>
       <c r="K165" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="22.5" customHeight="1">
@@ -27525,10 +27556,10 @@
         <v>11</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D167" s="10"/>
       <c r="E167" s="11"/>
@@ -27546,7 +27577,7 @@
         <v>551</v>
       </c>
       <c r="K167" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="22.5" customHeight="1">
@@ -27583,10 +27614,10 @@
         <v>18</v>
       </c>
       <c r="B169" s="9" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C169" s="9" t="s">
         <v>1271</v>
-      </c>
-      <c r="C169" s="9" t="s">
-        <v>1270</v>
       </c>
       <c r="D169" s="10"/>
       <c r="E169" s="11"/>
@@ -27604,7 +27635,7 @@
         <v>551</v>
       </c>
       <c r="K169" s="76" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="22.5" customHeight="1">
@@ -29156,10 +29187,10 @@
     <row r="248" spans="1:11" ht="22.5" customHeight="1">
       <c r="A248" s="46"/>
       <c r="B248" s="9" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="D248" s="10"/>
       <c r="E248" s="48" t="s">

--- a/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
+++ b/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlando.carvajal.DESMEX\Desktop\ClaudeCode\Pipeline1\pipeline-web\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46E7B812-D90F-416E-B00A-14D1BCEEBAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D685B323-FA30-41B3-9322-F069B3C2951A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Copia seguridad 27-01-2026" sheetId="9" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$L$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$L$216</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Copia seguridad 27-01-2026'!$A$1:$K$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Daniela Lara'!$A$1:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Josué Morales'!$A$1:$K$148</definedName>
@@ -50,11 +50,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={b3541e79-7142-4e55-b220-7706f78da251}</author>
-    <author>tc={fd5a665c-4ee9-467e-b1ab-105dbaf1c13e}</author>
+    <author>tc={003ccfb8-b085-4153-879b-b430b2a5a855}</author>
+    <author>tc={72def68a-07f2-4ab5-9dd8-2358d7537fb4}</author>
   </authors>
   <commentList>
-    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{B3541E79-7142-4E55-B220-7706F78DA251}">
+    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{003CCFB8-B085-4153-879B-B430B2A5A855}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -62,7 +62,7 @@
     ya lo tiene en seguimiento Josué</t>
       </text>
     </comment>
-    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{FD5A665C-4EE9-467E-B1AB-105DBAF1C13E}">
+    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{72DEF68A-07F2-4AB5-9DD8-2358D7537FB4}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4784" uniqueCount="1468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4794" uniqueCount="1473">
   <si>
     <t>ID de Prospecto</t>
   </si>
@@ -3755,6 +3755,9 @@
     <t>Grupo Aryba</t>
   </si>
   <si>
+    <t>SFV, BiPV y/o BC</t>
+  </si>
+  <si>
     <t>Ing. Gabriela Ortíz Nava</t>
   </si>
   <si>
@@ -3762,6 +3765,18 @@
   </si>
   <si>
     <t>Arq. Alejandra Vergara</t>
+  </si>
+  <si>
+    <t>Ing. Horacio Valdez</t>
+  </si>
+  <si>
+    <t>Apsa</t>
+  </si>
+  <si>
+    <t>Ing. Wálter Hernández Manríquez</t>
+  </si>
+  <si>
+    <t>Betone SA DE CV</t>
   </si>
   <si>
     <r>
@@ -5760,7 +5775,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Anónimo" id="{800B8EA1-66A5-4344-9FAA-9DC8A887D0FD}" userId="" providerId="google-sheets"/>
+  <person displayName="Anónimo" id="{987CB782-65FF-43C3-B2A1-A92D6AA16498}" userId="" providerId="google-sheets"/>
 </personList>
 </file>
 
@@ -5836,8 +5851,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:L214">
-  <autoFilter ref="A1:L214" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:L216">
+  <autoFilter ref="A1:L216" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID de Prospecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Nombre del Prospecto"/>
@@ -6114,10 +6129,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{800B8EA1-66A5-4344-9FAA-9DC8A887D0FD}" id="{B3541E79-7142-4E55-B220-7706F78DA251}" done="1">
+  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{987CB782-65FF-43C3-B2A1-A92D6AA16498}" id="{003CCFB8-B085-4153-879B-B430B2A5A855}" done="1">
     <text>ya lo tiene en seguimiento Josué</text>
   </threadedComment>
-  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{800B8EA1-66A5-4344-9FAA-9DC8A887D0FD}" id="{FD5A665C-4EE9-467E-B1AB-105DBAF1C13E}" done="1">
+  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{987CB782-65FF-43C3-B2A1-A92D6AA16498}" id="{72DEF68A-07F2-4AB5-9DD8-2358D7537FB4}" done="1">
     <text>Ya tienen contrato con Ammper</text>
   </threadedComment>
 </ThreadedComments>
@@ -14681,7 +14696,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC214"/>
+  <dimension ref="A1:AC216"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -21065,7 +21080,7 @@
         <v>448</v>
       </c>
       <c r="F201" s="53" t="s">
-        <v>119</v>
+        <v>449</v>
       </c>
       <c r="G201" s="54"/>
       <c r="H201" s="55"/>
@@ -21294,9 +21309,11 @@
         <v>561</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="F211" s="53"/>
+        <v>1224</v>
+      </c>
+      <c r="F211" s="53" t="s">
+        <v>449</v>
+      </c>
       <c r="G211" s="54"/>
       <c r="H211" s="55"/>
       <c r="I211" s="56"/>
@@ -21307,7 +21324,7 @@
     <row r="212" spans="1:12" ht="22.5" customHeight="1">
       <c r="A212" s="46"/>
       <c r="B212" s="9" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="C212" s="46" t="s">
         <v>1094</v>
@@ -21328,7 +21345,7 @@
       <c r="A213" s="46"/>
       <c r="B213" s="9"/>
       <c r="C213" s="46" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="D213" s="49" t="s">
         <v>815</v>
@@ -21347,7 +21364,7 @@
     <row r="214" spans="1:12" ht="22.5" customHeight="1">
       <c r="A214" s="46"/>
       <c r="B214" s="9" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C214" s="46"/>
       <c r="D214" s="10"/>
@@ -21362,21 +21379,67 @@
       <c r="K214" s="46"/>
       <c r="L214" s="46"/>
     </row>
+    <row r="215" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A215" s="46"/>
+      <c r="B215" s="9" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C215" s="46" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D215" s="49" t="s">
+        <v>678</v>
+      </c>
+      <c r="E215" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F215" s="53" t="s">
+        <v>449</v>
+      </c>
+      <c r="G215" s="54"/>
+      <c r="H215" s="55"/>
+      <c r="I215" s="56"/>
+      <c r="J215" s="53"/>
+      <c r="K215" s="46"/>
+      <c r="L215" s="46"/>
+    </row>
+    <row r="216" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A216" s="46"/>
+      <c r="B216" s="9" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C216" s="46" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D216" s="49" t="s">
+        <v>815</v>
+      </c>
+      <c r="E216" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F216" s="53"/>
+      <c r="G216" s="54"/>
+      <c r="H216" s="55"/>
+      <c r="I216" s="56"/>
+      <c r="J216" s="53"/>
+      <c r="K216" s="46"/>
+      <c r="L216" s="46"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="F2:F214" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F216" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"1. Prospección,2. Contacto Inicial,3. Calificación,4. Levantamiento de Requerimientos,5. Visita Técnica / Diagnóstico en Sitio,6. Diseño de Solución / Pre-Ingeniería,7. Estimación / Cotización,8. Propuesta Enviada,9. Aclaraciones / Ajustes de Propuesta,10"&amp;". Negociación,11. Aprobación Interna (Go/No-Go),12. Cierre de Venta (Contrato / OC),13. Kickoff / Inicio de Proyecto,14. Descartado / No Califica,15. En Pausa / Seguimiento Posterior"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G214" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G216" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G2))), AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I214" xr:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I216" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>AND(ISNUMBER(H2),(NOT(OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J214" xr:uid="{00000000-0002-0000-0400-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J216" xr:uid="{00000000-0002-0000-0400-000003000000}">
       <formula1>"Referido (Cliente),Referido (Proveedor/Subcontratista),Referido (Empleado/Interno),Cliente Recurrente (Recompra/Ampliación),Sitio Web (Formulario),Landing Page (Campaña),Chat Web / WhatsApp,SEO (Búsqueda Orgánica),Google Ads (Search),Remarketing (Display/"&amp;"Redes),LinkedIn (Orgánico),Email Outbound (Prospección),Llamada en Frío (Prospección),Visita en Frío (Prospección),Feria / Expo Industrial,Congreso / Cámara / Networking,Webinar / Evento Virtual,Licitación Pública,Licitación Privada (RFP/RFQ),Portal de Co"&amp;"mpras (Cliente),Alianza (Integrador/EPC/Constructor),Partner Tecnológico (Marca/Distribuidor),Directorio B2B / Clúster,Redes Sociales (Facebook/Instagram),YouTube / Contenido Técnico,PR / Medio Especializado,Reactivación de Base de Datos,Otros"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C214 E2:E214 K2:K214" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C216 E2:E216 K2:K216" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -21552,12 +21615,14 @@
     <hyperlink ref="D210" r:id="rId171" xr:uid="{00000000-0004-0000-0400-0000AA000000}"/>
     <hyperlink ref="D211" r:id="rId172" xr:uid="{00000000-0004-0000-0400-0000AB000000}"/>
     <hyperlink ref="D213" r:id="rId173" xr:uid="{00000000-0004-0000-0400-0000AC000000}"/>
+    <hyperlink ref="D215" r:id="rId174" xr:uid="{00000000-0004-0000-0400-0000AD000000}"/>
+    <hyperlink ref="D216" r:id="rId175" xr:uid="{00000000-0004-0000-0400-0000AE000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
   <tableParts count="1">
-    <tablePart r:id="rId174"/>
+    <tablePart r:id="rId176"/>
   </tableParts>
 </worksheet>
 </file>
@@ -21642,10 +21707,10 @@
         <v>481</v>
       </c>
       <c r="B2" s="69" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="D2" s="70"/>
       <c r="E2" s="70"/>
@@ -21665,7 +21730,7 @@
         <v>25</v>
       </c>
       <c r="K2" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="21" customHeight="1">
@@ -21673,10 +21738,10 @@
         <v>484</v>
       </c>
       <c r="B3" s="77" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="C3" s="76" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="D3" s="70"/>
       <c r="E3" s="70"/>
@@ -21694,7 +21759,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -21702,10 +21767,10 @@
         <v>488</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="C4" s="82" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="D4" s="83"/>
       <c r="E4" s="70"/>
@@ -21723,7 +21788,7 @@
         <v>25</v>
       </c>
       <c r="K4" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -21731,10 +21796,10 @@
         <v>491</v>
       </c>
       <c r="B5" s="81" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="C5" s="82" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="D5" s="83"/>
       <c r="E5" s="70"/>
@@ -21752,7 +21817,7 @@
         <v>782</v>
       </c>
       <c r="K5" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -21760,10 +21825,10 @@
         <v>494</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="C6" s="82" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="D6" s="83"/>
       <c r="E6" s="70"/>
@@ -21781,7 +21846,7 @@
         <v>74</v>
       </c>
       <c r="K6" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -21789,10 +21854,10 @@
         <v>497</v>
       </c>
       <c r="B7" s="77" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="C7" s="76" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="D7" s="70"/>
       <c r="E7" s="70"/>
@@ -21808,7 +21873,7 @@
         <v>25</v>
       </c>
       <c r="K7" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -21816,10 +21881,10 @@
         <v>500</v>
       </c>
       <c r="B8" s="77" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="D8" s="70"/>
       <c r="E8" s="70"/>
@@ -21837,7 +21902,7 @@
         <v>74</v>
       </c>
       <c r="K8" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -21845,10 +21910,10 @@
         <v>503</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="C9" s="82" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="D9" s="83"/>
       <c r="E9" s="70"/>
@@ -21866,7 +21931,7 @@
         <v>74</v>
       </c>
       <c r="K9" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -21874,10 +21939,10 @@
         <v>506</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="C10" s="76" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
@@ -21895,7 +21960,7 @@
         <v>25</v>
       </c>
       <c r="K10" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -21903,10 +21968,10 @@
         <v>514</v>
       </c>
       <c r="B11" s="81" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="C11" s="82" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="D11" s="83"/>
       <c r="E11" s="70"/>
@@ -21924,7 +21989,7 @@
         <v>74</v>
       </c>
       <c r="K11" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -21932,10 +21997,10 @@
         <v>517</v>
       </c>
       <c r="B12" s="81" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="C12" s="82" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="D12" s="83"/>
       <c r="E12" s="70"/>
@@ -21953,7 +22018,7 @@
         <v>74</v>
       </c>
       <c r="K12" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -21961,10 +22026,10 @@
         <v>520</v>
       </c>
       <c r="B13" s="77" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
@@ -21982,7 +22047,7 @@
         <v>25</v>
       </c>
       <c r="K13" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -21990,10 +22055,10 @@
         <v>523</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
       <c r="C14" s="82" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="D14" s="83"/>
       <c r="E14" s="70"/>
@@ -22009,7 +22074,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -22017,10 +22082,10 @@
         <v>527</v>
       </c>
       <c r="B15" s="99" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="C15" s="82" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="D15" s="83"/>
       <c r="E15" s="70"/>
@@ -22038,7 +22103,7 @@
         <v>74</v>
       </c>
       <c r="K15" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
@@ -22046,10 +22111,10 @@
         <v>531</v>
       </c>
       <c r="B16" s="77" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="C16" s="76" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
@@ -22065,7 +22130,7 @@
         <v>25</v>
       </c>
       <c r="K16" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
@@ -22073,10 +22138,10 @@
         <v>534</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="C17" s="76" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="D17" s="70"/>
       <c r="E17" s="70"/>
@@ -22096,7 +22161,7 @@
         <v>25</v>
       </c>
       <c r="K17" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="22.5" customHeight="1">
@@ -22104,10 +22169,10 @@
         <v>538</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="70"/>
@@ -22127,7 +22192,7 @@
         <v>74</v>
       </c>
       <c r="K18" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="22.5" customHeight="1">
@@ -22135,10 +22200,10 @@
         <v>541</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="11"/>
@@ -22158,7 +22223,7 @@
         <v>513</v>
       </c>
       <c r="K19" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="22.5" customHeight="1">
@@ -22166,10 +22231,10 @@
         <v>544</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -22187,7 +22252,7 @@
         <v>25</v>
       </c>
       <c r="K20" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="22.5" customHeight="1">
@@ -22195,10 +22260,10 @@
         <v>547</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="C21" s="76" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -22216,7 +22281,7 @@
         <v>745</v>
       </c>
       <c r="K21" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="22.5" customHeight="1">
@@ -22224,10 +22289,10 @@
         <v>552</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="C22" s="76" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="11"/>
@@ -22245,7 +22310,7 @@
         <v>551</v>
       </c>
       <c r="K22" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="22.5" customHeight="1">
@@ -22253,10 +22318,10 @@
         <v>555</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="C23" s="76" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="11"/>
@@ -22274,7 +22339,7 @@
         <v>551</v>
       </c>
       <c r="K23" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="22.5" customHeight="1">
@@ -22282,10 +22347,10 @@
         <v>558</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -22303,7 +22368,7 @@
         <v>551</v>
       </c>
       <c r="K24" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="22.5" customHeight="1">
@@ -22311,15 +22376,15 @@
         <v>558</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="11"/>
       <c r="F25" s="3" t="s">
-        <v>106</v>
+        <v>1131</v>
       </c>
       <c r="G25" s="12">
         <v>46068</v>
@@ -22334,7 +22399,7 @@
         <v>513</v>
       </c>
       <c r="K25" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -22342,10 +22407,10 @@
         <v>558</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="11"/>
@@ -22365,7 +22430,7 @@
         <v>551</v>
       </c>
       <c r="K26" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="22.5" customHeight="1">
@@ -22373,10 +22438,10 @@
         <v>562</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -22394,7 +22459,7 @@
         <v>513</v>
       </c>
       <c r="K27" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="22.5" customHeight="1">
@@ -22402,10 +22467,10 @@
         <v>565</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -22423,7 +22488,7 @@
         <v>513</v>
       </c>
       <c r="K28" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="22.5" customHeight="1">
@@ -22431,10 +22496,10 @@
         <v>568</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="11"/>
@@ -22450,7 +22515,7 @@
       <c r="I29" s="45"/>
       <c r="J29" s="14"/>
       <c r="K29" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
   </sheetData>
@@ -22573,10 +22638,10 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="D2" s="101"/>
       <c r="E2" s="101" t="s">
@@ -22594,7 +22659,7 @@
         <v>782</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -22602,10 +22667,10 @@
         <v>451</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
@@ -22627,7 +22692,7 @@
         <v>782</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -22635,14 +22700,14 @@
         <v>454</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>449</v>
@@ -22656,7 +22721,7 @@
         <v>782</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -22664,10 +22729,10 @@
         <v>457</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
@@ -22689,7 +22754,7 @@
         <v>688</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -22697,10 +22762,10 @@
         <v>668</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
@@ -22718,7 +22783,7 @@
         <v>688</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -22726,10 +22791,10 @@
         <v>459</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
@@ -22747,7 +22812,7 @@
         <v>782</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -22755,10 +22820,10 @@
         <v>462</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
@@ -22776,7 +22841,7 @@
         <v>25</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -22784,14 +22849,14 @@
         <v>465</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="F9" s="53" t="s">
         <v>40</v>
@@ -22805,7 +22870,7 @@
         <v>659</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -22813,10 +22878,10 @@
         <v>468</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
@@ -22834,7 +22899,7 @@
         <v>659</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -22842,14 +22907,14 @@
         <v>471</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>1303</v>
+        <v>1308</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="F11" s="53" t="s">
         <v>32</v>
@@ -22863,7 +22928,7 @@
         <v>659</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -22871,10 +22936,10 @@
         <v>474</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
@@ -22890,7 +22955,7 @@
         <v>659</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -22898,10 +22963,10 @@
         <v>477</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
@@ -22923,7 +22988,7 @@
         <v>659</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -22931,10 +22996,10 @@
         <v>481</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10" t="s">
@@ -22954,7 +23019,7 @@
         <v>782</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -22962,10 +23027,10 @@
         <v>484</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10" t="s">
@@ -22985,10 +23050,10 @@
         <v>488</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -23008,7 +23073,7 @@
         <v>659</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
@@ -23016,10 +23081,10 @@
         <v>491</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10" t="s">
@@ -23039,10 +23104,10 @@
         <v>494</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10" t="s">
@@ -23062,10 +23127,10 @@
         <v>497</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10" t="s">
@@ -23085,10 +23150,10 @@
         <v>500</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>1319</v>
+        <v>1324</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10" t="s">
@@ -23248,7 +23313,7 @@
         <v>782</v>
       </c>
       <c r="K2" s="104" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -23256,10 +23321,10 @@
         <v>471</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>1322</v>
+        <v>1327</v>
       </c>
       <c r="C3" s="82" t="s">
-        <v>1323</v>
+        <v>1328</v>
       </c>
       <c r="D3" s="83"/>
       <c r="E3" s="83"/>
@@ -23275,7 +23340,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -23563,10 +23628,10 @@
         <v>474</v>
       </c>
       <c r="B14" s="107" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
       <c r="C14" s="108" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
       <c r="D14" s="109"/>
       <c r="E14" s="109"/>
@@ -23584,7 +23649,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -23874,10 +23939,10 @@
         <v>477</v>
       </c>
       <c r="B25" s="117" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="C25" s="118" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="D25" s="119"/>
       <c r="E25" s="119"/>
@@ -23895,7 +23960,7 @@
         <v>25</v>
       </c>
       <c r="K25" s="125" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -24193,10 +24258,10 @@
         <v>481</v>
       </c>
       <c r="B36" s="126" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="C36" s="127" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="D36" s="128"/>
       <c r="E36" s="128"/>
@@ -24212,7 +24277,7 @@
         <v>25</v>
       </c>
       <c r="K36" s="134" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="22.5" customHeight="1">
@@ -24344,7 +24409,7 @@
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
       <c r="D42" s="17"/>
       <c r="E42" s="18"/>
@@ -24419,10 +24484,10 @@
         <v>484</v>
       </c>
       <c r="B46" s="107" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="C46" s="108" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="D46" s="109"/>
       <c r="E46" s="109"/>
@@ -24440,7 +24505,7 @@
         <v>74</v>
       </c>
       <c r="K46" s="115" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="22.5" customHeight="1">
@@ -24640,10 +24705,10 @@
         <v>488</v>
       </c>
       <c r="B57" s="135" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="C57" s="136" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="D57" s="137"/>
       <c r="E57" s="137"/>
@@ -24661,7 +24726,7 @@
         <v>25</v>
       </c>
       <c r="K57" s="143" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="22.5" customHeight="1">
@@ -24879,10 +24944,10 @@
         <v>491</v>
       </c>
       <c r="B68" s="107" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="C68" s="108" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="D68" s="109"/>
       <c r="E68" s="109"/>
@@ -24898,7 +24963,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="115" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="22.5" customHeight="1">
@@ -25114,10 +25179,10 @@
         <v>494</v>
       </c>
       <c r="B79" s="126" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="C79" s="127" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="D79" s="128"/>
       <c r="E79" s="128"/>
@@ -25135,7 +25200,7 @@
         <v>782</v>
       </c>
       <c r="K79" s="134" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="22.5" customHeight="1">
@@ -25185,10 +25250,10 @@
         <v>497</v>
       </c>
       <c r="B82" s="117" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
       <c r="C82" s="118" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="D82" s="119"/>
       <c r="E82" s="119"/>
@@ -25206,7 +25271,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="125" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="22.5" customHeight="1">
@@ -25214,10 +25279,10 @@
         <v>500</v>
       </c>
       <c r="B83" s="126" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="C83" s="127" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="D83" s="128"/>
       <c r="E83" s="128"/>
@@ -25235,7 +25300,7 @@
         <v>74</v>
       </c>
       <c r="K83" s="134" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22.5" customHeight="1">
@@ -25243,10 +25308,10 @@
         <v>451</v>
       </c>
       <c r="B84" s="151" t="s">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="C84" s="151" t="s">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="D84" s="152" t="s">
         <v>810</v>
@@ -25268,7 +25333,7 @@
         <v>25</v>
       </c>
       <c r="K84" s="158" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="22.5" customHeight="1">
@@ -25276,10 +25341,10 @@
         <v>503</v>
       </c>
       <c r="B85" s="107" t="s">
-        <v>1338</v>
+        <v>1343</v>
       </c>
       <c r="C85" s="108" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="D85" s="109"/>
       <c r="E85" s="109"/>
@@ -25297,7 +25362,7 @@
         <v>74</v>
       </c>
       <c r="K85" s="115" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="22.5" customHeight="1">
@@ -25305,10 +25370,10 @@
         <v>506</v>
       </c>
       <c r="B86" s="135" t="s">
-        <v>1340</v>
+        <v>1345</v>
       </c>
       <c r="C86" s="136" t="s">
-        <v>1341</v>
+        <v>1346</v>
       </c>
       <c r="D86" s="137"/>
       <c r="E86" s="137"/>
@@ -25326,7 +25391,7 @@
         <v>74</v>
       </c>
       <c r="K86" s="143" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="22.5" customHeight="1">
@@ -25334,10 +25399,10 @@
         <v>510</v>
       </c>
       <c r="B87" s="108" t="s">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="C87" s="108" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="D87" s="109"/>
       <c r="E87" s="109"/>
@@ -25353,7 +25418,7 @@
         <v>782</v>
       </c>
       <c r="K87" s="115" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="22.5" customHeight="1">
@@ -25361,10 +25426,10 @@
         <v>514</v>
       </c>
       <c r="B88" s="135" t="s">
-        <v>1344</v>
+        <v>1349</v>
       </c>
       <c r="C88" s="136" t="s">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="D88" s="137"/>
       <c r="E88" s="137"/>
@@ -25382,7 +25447,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="143" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="22.5" customHeight="1">
@@ -25390,10 +25455,10 @@
         <v>517</v>
       </c>
       <c r="B89" s="117" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="C89" s="118" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="D89" s="70"/>
       <c r="E89" s="70"/>
@@ -25411,7 +25476,7 @@
         <v>74</v>
       </c>
       <c r="K89" s="125" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="22.5" customHeight="1">
@@ -25419,10 +25484,10 @@
         <v>520</v>
       </c>
       <c r="B90" s="135" t="s">
-        <v>1348</v>
+        <v>1353</v>
       </c>
       <c r="C90" s="136" t="s">
-        <v>1349</v>
+        <v>1354</v>
       </c>
       <c r="D90" s="83"/>
       <c r="E90" s="83"/>
@@ -25438,7 +25503,7 @@
         <v>74</v>
       </c>
       <c r="K90" s="143" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="22.5" customHeight="1">
@@ -25446,10 +25511,10 @@
         <v>523</v>
       </c>
       <c r="B91" s="77" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="C91" s="76" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="D91" s="70"/>
       <c r="E91" s="70"/>
@@ -25465,7 +25530,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="125" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22.5" customHeight="1">
@@ -25473,10 +25538,10 @@
         <v>527</v>
       </c>
       <c r="B92" s="81" t="s">
-        <v>1350</v>
+        <v>1355</v>
       </c>
       <c r="C92" s="82" t="s">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="D92" s="83"/>
       <c r="E92" s="83"/>
@@ -25494,7 +25559,7 @@
         <v>74</v>
       </c>
       <c r="K92" s="143" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="22.5" customHeight="1">
@@ -25502,10 +25567,10 @@
         <v>531</v>
       </c>
       <c r="B93" s="77" t="s">
-        <v>1352</v>
+        <v>1357</v>
       </c>
       <c r="C93" s="76" t="s">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="D93" s="70"/>
       <c r="E93" s="70"/>
@@ -25521,7 +25586,7 @@
         <v>74</v>
       </c>
       <c r="K93" s="125" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="22.5" customHeight="1">
@@ -25529,10 +25594,10 @@
         <v>534</v>
       </c>
       <c r="B94" s="81" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="C94" s="82" t="s">
-        <v>1355</v>
+        <v>1360</v>
       </c>
       <c r="D94" s="83"/>
       <c r="E94" s="83"/>
@@ -25548,7 +25613,7 @@
         <v>74</v>
       </c>
       <c r="K94" s="143" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="22.5" customHeight="1">
@@ -25556,10 +25621,10 @@
         <v>454</v>
       </c>
       <c r="B95" s="104" t="s">
-        <v>1356</v>
+        <v>1361</v>
       </c>
       <c r="C95" s="104" t="s">
-        <v>1357</v>
+        <v>1362</v>
       </c>
       <c r="D95" s="62" t="s">
         <v>888</v>
@@ -25581,7 +25646,7 @@
         <v>16</v>
       </c>
       <c r="K95" s="158" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="22.5" customHeight="1">
@@ -25589,10 +25654,10 @@
         <v>538</v>
       </c>
       <c r="B96" s="77" t="s">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="C96" s="76" t="s">
-        <v>1359</v>
+        <v>1364</v>
       </c>
       <c r="D96" s="70"/>
       <c r="E96" s="70"/>
@@ -25608,7 +25673,7 @@
         <v>74</v>
       </c>
       <c r="K96" s="125" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="22.5" customHeight="1">
@@ -25616,7 +25681,7 @@
         <v>541</v>
       </c>
       <c r="B97" s="81" t="s">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="C97" s="82" t="s">
         <v>1078</v>
@@ -25635,7 +25700,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="22.5" customHeight="1">
@@ -25643,10 +25708,10 @@
         <v>544</v>
       </c>
       <c r="B98" s="77" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="C98" s="76" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="D98" s="70"/>
       <c r="E98" s="70"/>
@@ -25664,7 +25729,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="22.5" customHeight="1">
@@ -25672,10 +25737,10 @@
         <v>547</v>
       </c>
       <c r="B99" s="81" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="C99" s="82" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="D99" s="83"/>
       <c r="E99" s="83"/>
@@ -25693,7 +25758,7 @@
         <v>74</v>
       </c>
       <c r="K99" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="22.5" customHeight="1">
@@ -25701,10 +25766,10 @@
         <v>552</v>
       </c>
       <c r="B100" s="77" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="C100" s="76" t="s">
-        <v>1362</v>
+        <v>1367</v>
       </c>
       <c r="D100" s="70"/>
       <c r="E100" s="70"/>
@@ -25720,7 +25785,7 @@
         <v>74</v>
       </c>
       <c r="K100" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="22.5" customHeight="1">
@@ -25728,10 +25793,10 @@
         <v>555</v>
       </c>
       <c r="B101" s="81" t="s">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="C101" s="82" t="s">
-        <v>1364</v>
+        <v>1369</v>
       </c>
       <c r="D101" s="83"/>
       <c r="E101" s="83"/>
@@ -25747,7 +25812,7 @@
         <v>74</v>
       </c>
       <c r="K101" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="22.5" customHeight="1">
@@ -25755,10 +25820,10 @@
         <v>558</v>
       </c>
       <c r="B102" s="77" t="s">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="C102" s="76" t="s">
-        <v>1366</v>
+        <v>1371</v>
       </c>
       <c r="D102" s="70"/>
       <c r="E102" s="70"/>
@@ -25774,7 +25839,7 @@
         <v>74</v>
       </c>
       <c r="K102" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="22.5" customHeight="1">
@@ -25782,10 +25847,10 @@
         <v>562</v>
       </c>
       <c r="B103" s="81" t="s">
-        <v>1367</v>
+        <v>1372</v>
       </c>
       <c r="C103" s="82" t="s">
-        <v>1368</v>
+        <v>1373</v>
       </c>
       <c r="D103" s="83"/>
       <c r="E103" s="83"/>
@@ -25801,7 +25866,7 @@
         <v>74</v>
       </c>
       <c r="K103" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="22.5" customHeight="1">
@@ -25809,10 +25874,10 @@
         <v>565</v>
       </c>
       <c r="B104" s="76" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="C104" s="76" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="D104" s="70"/>
       <c r="E104" s="70"/>
@@ -25830,7 +25895,7 @@
         <v>25</v>
       </c>
       <c r="K104" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="22.5" customHeight="1">
@@ -25838,10 +25903,10 @@
         <v>568</v>
       </c>
       <c r="B105" s="81" t="s">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="C105" s="82" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="D105" s="83"/>
       <c r="E105" s="83"/>
@@ -25859,7 +25924,7 @@
         <v>74</v>
       </c>
       <c r="K105" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="22.5" customHeight="1">
@@ -25867,10 +25932,10 @@
         <v>457</v>
       </c>
       <c r="B106" s="104" t="s">
-        <v>1370</v>
+        <v>1375</v>
       </c>
       <c r="C106" s="104" t="s">
-        <v>1371</v>
+        <v>1376</v>
       </c>
       <c r="D106" s="62" t="s">
         <v>540</v>
@@ -25892,7 +25957,7 @@
         <v>1192</v>
       </c>
       <c r="K106" s="104" t="s">
-        <v>1372</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="22.5" customHeight="1">
@@ -25900,10 +25965,10 @@
         <v>571</v>
       </c>
       <c r="B107" s="77" t="s">
-        <v>1373</v>
+        <v>1378</v>
       </c>
       <c r="C107" s="76" t="s">
-        <v>1374</v>
+        <v>1379</v>
       </c>
       <c r="D107" s="70"/>
       <c r="E107" s="70"/>
@@ -25919,7 +25984,7 @@
         <v>25</v>
       </c>
       <c r="K107" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="22.5" customHeight="1">
@@ -25927,10 +25992,10 @@
         <v>574</v>
       </c>
       <c r="B108" s="81" t="s">
-        <v>1375</v>
+        <v>1380</v>
       </c>
       <c r="C108" s="82" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="D108" s="83"/>
       <c r="E108" s="83"/>
@@ -25946,7 +26011,7 @@
         <v>74</v>
       </c>
       <c r="K108" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="22.5" customHeight="1">
@@ -25954,10 +26019,10 @@
         <v>576</v>
       </c>
       <c r="B109" s="77" t="s">
-        <v>1377</v>
+        <v>1382</v>
       </c>
       <c r="C109" s="76" t="s">
-        <v>1378</v>
+        <v>1383</v>
       </c>
       <c r="D109" s="70"/>
       <c r="E109" s="70"/>
@@ -25975,7 +26040,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="22.5" customHeight="1">
@@ -25983,10 +26048,10 @@
         <v>579</v>
       </c>
       <c r="B110" s="81" t="s">
-        <v>1379</v>
+        <v>1384</v>
       </c>
       <c r="C110" s="82" t="s">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="D110" s="83"/>
       <c r="E110" s="83"/>
@@ -26002,7 +26067,7 @@
         <v>74</v>
       </c>
       <c r="K110" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="22.5" customHeight="1">
@@ -26010,10 +26075,10 @@
         <v>582</v>
       </c>
       <c r="B111" s="77" t="s">
-        <v>1381</v>
+        <v>1386</v>
       </c>
       <c r="C111" s="76" t="s">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="D111" s="70"/>
       <c r="E111" s="70"/>
@@ -26029,7 +26094,7 @@
         <v>74</v>
       </c>
       <c r="K111" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="22.5" customHeight="1">
@@ -26037,10 +26102,10 @@
         <v>585</v>
       </c>
       <c r="B112" s="81" t="s">
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="C112" s="82" t="s">
-        <v>1384</v>
+        <v>1389</v>
       </c>
       <c r="D112" s="83"/>
       <c r="E112" s="83"/>
@@ -26056,7 +26121,7 @@
         <v>74</v>
       </c>
       <c r="K112" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="22.5" customHeight="1">
@@ -26064,10 +26129,10 @@
         <v>588</v>
       </c>
       <c r="B113" s="77" t="s">
-        <v>1385</v>
+        <v>1390</v>
       </c>
       <c r="C113" s="76" t="s">
-        <v>1386</v>
+        <v>1391</v>
       </c>
       <c r="D113" s="70"/>
       <c r="E113" s="70"/>
@@ -26083,7 +26148,7 @@
         <v>74</v>
       </c>
       <c r="K113" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="22.5" customHeight="1">
@@ -26091,10 +26156,10 @@
         <v>591</v>
       </c>
       <c r="B114" s="81" t="s">
-        <v>1387</v>
+        <v>1392</v>
       </c>
       <c r="C114" s="82" t="s">
-        <v>1388</v>
+        <v>1393</v>
       </c>
       <c r="D114" s="83"/>
       <c r="E114" s="83"/>
@@ -26110,7 +26175,7 @@
         <v>74</v>
       </c>
       <c r="K114" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="22.5" customHeight="1">
@@ -26118,7 +26183,7 @@
         <v>594</v>
       </c>
       <c r="B115" s="77" t="s">
-        <v>1389</v>
+        <v>1394</v>
       </c>
       <c r="C115" s="76" t="s">
         <v>391</v>
@@ -26137,7 +26202,7 @@
         <v>74</v>
       </c>
       <c r="K115" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="22.5" customHeight="1">
@@ -26145,10 +26210,10 @@
         <v>597</v>
       </c>
       <c r="B116" s="81" t="s">
-        <v>1390</v>
+        <v>1395</v>
       </c>
       <c r="C116" s="82" t="s">
-        <v>1391</v>
+        <v>1396</v>
       </c>
       <c r="D116" s="83"/>
       <c r="E116" s="83"/>
@@ -26164,7 +26229,7 @@
         <v>74</v>
       </c>
       <c r="K116" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="22.5" customHeight="1">
@@ -26172,10 +26237,10 @@
         <v>668</v>
       </c>
       <c r="B117" s="104" t="s">
-        <v>1392</v>
+        <v>1397</v>
       </c>
       <c r="C117" s="104" t="s">
-        <v>1393</v>
+        <v>1398</v>
       </c>
       <c r="D117" s="62" t="s">
         <v>540</v>
@@ -26197,7 +26262,7 @@
         <v>1192</v>
       </c>
       <c r="K117" s="104" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="22.5" customHeight="1">
@@ -26205,10 +26270,10 @@
         <v>600</v>
       </c>
       <c r="B118" s="77" t="s">
-        <v>1394</v>
+        <v>1399</v>
       </c>
       <c r="C118" s="76" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="D118" s="70"/>
       <c r="E118" s="70"/>
@@ -26224,7 +26289,7 @@
         <v>74</v>
       </c>
       <c r="K118" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="22.5" customHeight="1">
@@ -26232,10 +26297,10 @@
         <v>603</v>
       </c>
       <c r="B119" s="81" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="C119" s="82" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="D119" s="83"/>
       <c r="E119" s="83"/>
@@ -26253,7 +26318,7 @@
         <v>74</v>
       </c>
       <c r="K119" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="22.5" customHeight="1">
@@ -26261,10 +26326,10 @@
         <v>606</v>
       </c>
       <c r="B120" s="77" t="s">
-        <v>1396</v>
+        <v>1401</v>
       </c>
       <c r="C120" s="76" t="s">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="D120" s="70"/>
       <c r="E120" s="70"/>
@@ -26282,7 +26347,7 @@
         <v>74</v>
       </c>
       <c r="K120" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="22.5" customHeight="1">
@@ -26290,10 +26355,10 @@
         <v>609</v>
       </c>
       <c r="B121" s="81" t="s">
-        <v>1398</v>
+        <v>1403</v>
       </c>
       <c r="C121" s="82" t="s">
-        <v>1399</v>
+        <v>1404</v>
       </c>
       <c r="D121" s="83"/>
       <c r="E121" s="83"/>
@@ -26309,7 +26374,7 @@
         <v>74</v>
       </c>
       <c r="K121" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="22.5" customHeight="1">
@@ -26317,10 +26382,10 @@
         <v>612</v>
       </c>
       <c r="B122" s="77" t="s">
-        <v>1400</v>
+        <v>1405</v>
       </c>
       <c r="C122" s="76" t="s">
-        <v>1401</v>
+        <v>1406</v>
       </c>
       <c r="D122" s="70"/>
       <c r="E122" s="70"/>
@@ -26336,7 +26401,7 @@
         <v>74</v>
       </c>
       <c r="K122" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="22.5" customHeight="1">
@@ -26344,10 +26409,10 @@
         <v>615</v>
       </c>
       <c r="B123" s="81" t="s">
-        <v>1402</v>
+        <v>1407</v>
       </c>
       <c r="C123" s="82" t="s">
-        <v>1403</v>
+        <v>1408</v>
       </c>
       <c r="D123" s="83"/>
       <c r="E123" s="83"/>
@@ -26363,7 +26428,7 @@
         <v>74</v>
       </c>
       <c r="K123" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="22.5" customHeight="1">
@@ -26371,10 +26436,10 @@
         <v>618</v>
       </c>
       <c r="B124" s="77" t="s">
-        <v>1404</v>
+        <v>1409</v>
       </c>
       <c r="C124" s="76" t="s">
-        <v>1405</v>
+        <v>1410</v>
       </c>
       <c r="D124" s="70"/>
       <c r="E124" s="70"/>
@@ -26392,7 +26457,7 @@
         <v>25</v>
       </c>
       <c r="K124" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="22.5" customHeight="1">
@@ -26400,10 +26465,10 @@
         <v>621</v>
       </c>
       <c r="B125" s="81" t="s">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="C125" s="82" t="s">
-        <v>1407</v>
+        <v>1412</v>
       </c>
       <c r="D125" s="83"/>
       <c r="E125" s="83"/>
@@ -26419,7 +26484,7 @@
         <v>25</v>
       </c>
       <c r="K125" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="22.5" customHeight="1">
@@ -26427,10 +26492,10 @@
         <v>624</v>
       </c>
       <c r="B126" s="77" t="s">
-        <v>1408</v>
+        <v>1413</v>
       </c>
       <c r="C126" s="76" t="s">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="D126" s="70"/>
       <c r="E126" s="70"/>
@@ -26446,7 +26511,7 @@
         <v>74</v>
       </c>
       <c r="K126" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="22.5" customHeight="1">
@@ -26454,10 +26519,10 @@
         <v>627</v>
       </c>
       <c r="B127" s="81" t="s">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="C127" s="82" t="s">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="D127" s="83"/>
       <c r="E127" s="83"/>
@@ -26473,7 +26538,7 @@
         <v>74</v>
       </c>
       <c r="K127" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="22.5" customHeight="1">
@@ -26481,10 +26546,10 @@
         <v>459</v>
       </c>
       <c r="B128" s="104" t="s">
-        <v>1412</v>
+        <v>1417</v>
       </c>
       <c r="C128" s="104" t="s">
-        <v>1413</v>
+        <v>1418</v>
       </c>
       <c r="D128" s="62" t="s">
         <v>540</v>
@@ -26506,7 +26571,7 @@
         <v>1036</v>
       </c>
       <c r="K128" s="104" t="s">
-        <v>1372</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="22.5" customHeight="1">
@@ -26514,10 +26579,10 @@
         <v>630</v>
       </c>
       <c r="B129" s="77" t="s">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="C129" s="76" t="s">
-        <v>1415</v>
+        <v>1420</v>
       </c>
       <c r="D129" s="70"/>
       <c r="E129" s="70"/>
@@ -26533,7 +26598,7 @@
         <v>74</v>
       </c>
       <c r="K129" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="22.5" customHeight="1">
@@ -26541,10 +26606,10 @@
         <v>633</v>
       </c>
       <c r="B130" s="81" t="s">
-        <v>1416</v>
+        <v>1421</v>
       </c>
       <c r="C130" s="82" t="s">
-        <v>1417</v>
+        <v>1422</v>
       </c>
       <c r="D130" s="83"/>
       <c r="E130" s="83"/>
@@ -26562,7 +26627,7 @@
         <v>74</v>
       </c>
       <c r="K130" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="22.5" customHeight="1">
@@ -26570,10 +26635,10 @@
         <v>636</v>
       </c>
       <c r="B131" s="77" t="s">
-        <v>1418</v>
+        <v>1423</v>
       </c>
       <c r="C131" s="76" t="s">
-        <v>1419</v>
+        <v>1424</v>
       </c>
       <c r="D131" s="70"/>
       <c r="E131" s="70"/>
@@ -26589,7 +26654,7 @@
         <v>74</v>
       </c>
       <c r="K131" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="22.5" customHeight="1">
@@ -26597,10 +26662,10 @@
         <v>637</v>
       </c>
       <c r="B132" s="81" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="C132" s="82" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="D132" s="83"/>
       <c r="E132" s="83"/>
@@ -26618,7 +26683,7 @@
         <v>74</v>
       </c>
       <c r="K132" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="22.5" customHeight="1">
@@ -26626,10 +26691,10 @@
         <v>638</v>
       </c>
       <c r="B133" s="77" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="C133" s="76" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="D133" s="70"/>
       <c r="E133" s="70"/>
@@ -26647,7 +26712,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="22.5" customHeight="1">
@@ -26655,10 +26720,10 @@
         <v>639</v>
       </c>
       <c r="B134" s="81" t="s">
-        <v>1420</v>
+        <v>1425</v>
       </c>
       <c r="C134" s="82" t="s">
-        <v>1421</v>
+        <v>1426</v>
       </c>
       <c r="D134" s="83"/>
       <c r="E134" s="83"/>
@@ -26674,7 +26739,7 @@
         <v>25</v>
       </c>
       <c r="K134" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="22.5" customHeight="1">
@@ -26682,10 +26747,10 @@
         <v>640</v>
       </c>
       <c r="B135" s="77" t="s">
-        <v>1422</v>
+        <v>1427</v>
       </c>
       <c r="C135" s="76" t="s">
-        <v>1423</v>
+        <v>1428</v>
       </c>
       <c r="D135" s="70"/>
       <c r="E135" s="70"/>
@@ -26703,7 +26768,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="22.5" customHeight="1">
@@ -26711,10 +26776,10 @@
         <v>641</v>
       </c>
       <c r="B136" s="81" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
       <c r="C136" s="82" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="D136" s="83"/>
       <c r="E136" s="83"/>
@@ -26730,7 +26795,7 @@
         <v>74</v>
       </c>
       <c r="K136" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="22.5" customHeight="1">
@@ -26738,10 +26803,10 @@
         <v>642</v>
       </c>
       <c r="B137" s="77" t="s">
-        <v>1424</v>
+        <v>1429</v>
       </c>
       <c r="C137" s="76" t="s">
-        <v>1425</v>
+        <v>1430</v>
       </c>
       <c r="D137" s="70"/>
       <c r="E137" s="70"/>
@@ -26757,7 +26822,7 @@
         <v>74</v>
       </c>
       <c r="K137" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="22.5" customHeight="1">
@@ -26765,10 +26830,10 @@
         <v>643</v>
       </c>
       <c r="B138" s="81" t="s">
-        <v>1426</v>
+        <v>1431</v>
       </c>
       <c r="C138" s="82" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="D138" s="83"/>
       <c r="E138" s="83"/>
@@ -26786,7 +26851,7 @@
         <v>74</v>
       </c>
       <c r="K138" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="22.5" customHeight="1">
@@ -26794,10 +26859,10 @@
         <v>462</v>
       </c>
       <c r="B139" s="104" t="s">
-        <v>1427</v>
+        <v>1432</v>
       </c>
       <c r="C139" s="104" t="s">
-        <v>1428</v>
+        <v>1433</v>
       </c>
       <c r="D139" s="62" t="s">
         <v>810</v>
@@ -26819,7 +26884,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="104" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="22.5" customHeight="1">
@@ -26827,10 +26892,10 @@
         <v>644</v>
       </c>
       <c r="B140" s="81" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="C140" s="82" t="s">
-        <v>1430</v>
+        <v>1435</v>
       </c>
       <c r="D140" s="83"/>
       <c r="E140" s="83"/>
@@ -26848,7 +26913,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="22.5" customHeight="1">
@@ -26856,10 +26921,10 @@
         <v>645</v>
       </c>
       <c r="B141" s="77" t="s">
-        <v>1431</v>
+        <v>1436</v>
       </c>
       <c r="C141" s="76" t="s">
-        <v>1432</v>
+        <v>1437</v>
       </c>
       <c r="D141" s="70"/>
       <c r="E141" s="70"/>
@@ -26875,7 +26940,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="22.5" customHeight="1">
@@ -26883,7 +26948,7 @@
         <v>646</v>
       </c>
       <c r="B142" s="81" t="s">
-        <v>1433</v>
+        <v>1438</v>
       </c>
       <c r="C142" s="82" t="s">
         <v>1094</v>
@@ -26902,7 +26967,7 @@
         <v>74</v>
       </c>
       <c r="K142" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="22.5" customHeight="1">
@@ -26910,10 +26975,10 @@
         <v>647</v>
       </c>
       <c r="B143" s="77" t="s">
-        <v>1434</v>
+        <v>1439</v>
       </c>
       <c r="C143" s="76" t="s">
-        <v>1435</v>
+        <v>1440</v>
       </c>
       <c r="D143" s="70"/>
       <c r="E143" s="70"/>
@@ -26929,7 +26994,7 @@
         <v>74</v>
       </c>
       <c r="K143" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="22.5" customHeight="1">
@@ -26937,10 +27002,10 @@
         <v>648</v>
       </c>
       <c r="B144" s="81" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="C144" s="82" t="s">
-        <v>1437</v>
+        <v>1442</v>
       </c>
       <c r="D144" s="83"/>
       <c r="E144" s="83"/>
@@ -26956,7 +27021,7 @@
         <v>74</v>
       </c>
       <c r="K144" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="22.5" customHeight="1">
@@ -26964,10 +27029,10 @@
         <v>649</v>
       </c>
       <c r="B145" s="77" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="C145" s="76" t="s">
-        <v>1439</v>
+        <v>1444</v>
       </c>
       <c r="D145" s="70"/>
       <c r="E145" s="70"/>
@@ -26983,7 +27048,7 @@
         <v>25</v>
       </c>
       <c r="K145" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="22.5" customHeight="1">
@@ -26991,10 +27056,10 @@
         <v>650</v>
       </c>
       <c r="B146" s="81" t="s">
-        <v>1440</v>
+        <v>1445</v>
       </c>
       <c r="C146" s="82" t="s">
-        <v>1441</v>
+        <v>1446</v>
       </c>
       <c r="D146" s="83"/>
       <c r="E146" s="83"/>
@@ -27010,7 +27075,7 @@
         <v>74</v>
       </c>
       <c r="K146" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="22.5" customHeight="1">
@@ -27018,10 +27083,10 @@
         <v>651</v>
       </c>
       <c r="B147" s="77" t="s">
-        <v>1442</v>
+        <v>1447</v>
       </c>
       <c r="C147" s="76" t="s">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="D147" s="70"/>
       <c r="E147" s="70"/>
@@ -27037,7 +27102,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="22.5" customHeight="1">
@@ -27045,10 +27110,10 @@
         <v>652</v>
       </c>
       <c r="B148" s="81" t="s">
-        <v>1444</v>
+        <v>1449</v>
       </c>
       <c r="C148" s="82" t="s">
-        <v>1445</v>
+        <v>1450</v>
       </c>
       <c r="D148" s="83"/>
       <c r="E148" s="83"/>
@@ -27064,7 +27129,7 @@
         <v>74</v>
       </c>
       <c r="K148" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="22.5" customHeight="1">
@@ -27072,10 +27137,10 @@
         <v>653</v>
       </c>
       <c r="B149" s="77" t="s">
-        <v>1446</v>
+        <v>1451</v>
       </c>
       <c r="C149" s="76" t="s">
-        <v>1447</v>
+        <v>1452</v>
       </c>
       <c r="D149" s="70"/>
       <c r="E149" s="70"/>
@@ -27091,7 +27156,7 @@
         <v>74</v>
       </c>
       <c r="K149" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="22.5" customHeight="1">
@@ -27099,7 +27164,7 @@
         <v>465</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1448</v>
+        <v>1453</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="166" t="s">
@@ -27118,10 +27183,10 @@
         <v>654</v>
       </c>
       <c r="B151" s="82" t="s">
-        <v>1449</v>
+        <v>1454</v>
       </c>
       <c r="C151" s="82" t="s">
-        <v>1450</v>
+        <v>1455</v>
       </c>
       <c r="D151" s="83"/>
       <c r="E151" s="83"/>
@@ -27137,7 +27202,7 @@
         <v>782</v>
       </c>
       <c r="K151" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="22.5" customHeight="1">
@@ -27145,10 +27210,10 @@
         <v>746</v>
       </c>
       <c r="B152" s="77" t="s">
-        <v>1451</v>
+        <v>1456</v>
       </c>
       <c r="C152" s="76" t="s">
-        <v>1452</v>
+        <v>1457</v>
       </c>
       <c r="D152" s="70"/>
       <c r="E152" s="70"/>
@@ -27164,7 +27229,7 @@
         <v>25</v>
       </c>
       <c r="K152" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="22.5" customHeight="1">
@@ -27172,10 +27237,10 @@
         <v>747</v>
       </c>
       <c r="B153" s="81" t="s">
-        <v>1453</v>
+        <v>1458</v>
       </c>
       <c r="C153" s="82" t="s">
-        <v>1454</v>
+        <v>1459</v>
       </c>
       <c r="D153" s="83"/>
       <c r="E153" s="83"/>
@@ -27191,7 +27256,7 @@
         <v>74</v>
       </c>
       <c r="K153" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="22.5" customHeight="1">
@@ -27199,10 +27264,10 @@
         <v>748</v>
       </c>
       <c r="B154" s="77" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="C154" s="76" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D154" s="70"/>
       <c r="E154" s="70"/>
@@ -27218,7 +27283,7 @@
         <v>25</v>
       </c>
       <c r="K154" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="22.5" customHeight="1">
@@ -27226,10 +27291,10 @@
         <v>749</v>
       </c>
       <c r="B155" s="81" t="s">
-        <v>1455</v>
+        <v>1460</v>
       </c>
       <c r="C155" s="82" t="s">
-        <v>1456</v>
+        <v>1461</v>
       </c>
       <c r="D155" s="83"/>
       <c r="E155" s="83"/>
@@ -27247,7 +27312,7 @@
         <v>25</v>
       </c>
       <c r="K155" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="22.5" customHeight="1">
@@ -27255,10 +27320,10 @@
         <v>750</v>
       </c>
       <c r="B156" s="76" t="s">
-        <v>1457</v>
+        <v>1462</v>
       </c>
       <c r="C156" s="76" t="s">
-        <v>1458</v>
+        <v>1463</v>
       </c>
       <c r="D156" s="70"/>
       <c r="E156" s="70"/>
@@ -27274,7 +27339,7 @@
         <v>513</v>
       </c>
       <c r="K156" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="22.5" customHeight="1">
@@ -27282,10 +27347,10 @@
         <v>751</v>
       </c>
       <c r="B157" s="81" t="s">
-        <v>1459</v>
+        <v>1464</v>
       </c>
       <c r="C157" s="82" t="s">
-        <v>1460</v>
+        <v>1465</v>
       </c>
       <c r="D157" s="83"/>
       <c r="E157" s="83"/>
@@ -27303,7 +27368,7 @@
         <v>74</v>
       </c>
       <c r="K157" s="82" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="22.5" customHeight="1">
@@ -27311,10 +27376,10 @@
         <v>752</v>
       </c>
       <c r="B158" s="76" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="C158" s="76" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="D158" s="70"/>
       <c r="E158" s="70"/>
@@ -27332,7 +27397,7 @@
         <v>25</v>
       </c>
       <c r="K158" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="22.5" customHeight="1">
@@ -27340,10 +27405,10 @@
         <v>753</v>
       </c>
       <c r="B159" s="77" t="s">
-        <v>1461</v>
+        <v>1466</v>
       </c>
       <c r="C159" s="76" t="s">
-        <v>1462</v>
+        <v>1467</v>
       </c>
       <c r="D159" s="10"/>
       <c r="E159" s="11"/>
@@ -27359,7 +27424,7 @@
         <v>25</v>
       </c>
       <c r="K159" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="22.5" customHeight="1">
@@ -27367,10 +27432,10 @@
         <v>754</v>
       </c>
       <c r="B160" s="77" t="s">
-        <v>1463</v>
+        <v>1468</v>
       </c>
       <c r="C160" s="76" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="D160" s="10"/>
       <c r="E160" s="11"/>
@@ -27386,7 +27451,7 @@
         <v>25</v>
       </c>
       <c r="K160" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="22.5" customHeight="1">
@@ -27411,10 +27476,10 @@
         <v>755</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="D162" s="10"/>
       <c r="E162" s="11"/>
@@ -27432,7 +27497,7 @@
         <v>74</v>
       </c>
       <c r="K162" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="22.5" customHeight="1">
@@ -27440,10 +27505,10 @@
         <v>756</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="D163" s="10"/>
       <c r="E163" s="11"/>
@@ -27461,7 +27526,7 @@
         <v>25</v>
       </c>
       <c r="K163" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="22.5" customHeight="1">
@@ -27469,10 +27534,10 @@
         <v>757</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="D164" s="10"/>
       <c r="E164" s="11"/>
@@ -27490,7 +27555,7 @@
         <v>745</v>
       </c>
       <c r="K164" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="22.5" customHeight="1">
@@ -27498,10 +27563,10 @@
         <v>758</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="D165" s="10"/>
       <c r="E165" s="11"/>
@@ -27519,7 +27584,7 @@
         <v>551</v>
       </c>
       <c r="K165" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="22.5" customHeight="1">
@@ -27556,10 +27621,10 @@
         <v>11</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="D167" s="10"/>
       <c r="E167" s="11"/>
@@ -27577,7 +27642,7 @@
         <v>551</v>
       </c>
       <c r="K167" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="22.5" customHeight="1">
@@ -27614,10 +27679,10 @@
         <v>18</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="D169" s="10"/>
       <c r="E169" s="11"/>
@@ -27635,7 +27700,7 @@
         <v>551</v>
       </c>
       <c r="K169" s="76" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="22.5" customHeight="1">
@@ -29187,10 +29252,10 @@
     <row r="248" spans="1:11" ht="22.5" customHeight="1">
       <c r="A248" s="46"/>
       <c r="B248" s="9" t="s">
-        <v>1466</v>
+        <v>1471</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>1467</v>
+        <v>1472</v>
       </c>
       <c r="D248" s="10"/>
       <c r="E248" s="48" t="s">

--- a/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
+++ b/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlando.carvajal.DESMEX\Desktop\ClaudeCode\Pipeline1\pipeline-web\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D685B323-FA30-41B3-9322-F069B3C2951A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3DDA241-21CC-481C-A298-5112A4DF8A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Josué Morales" sheetId="2" r:id="rId1"/>
@@ -50,11 +50,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={003ccfb8-b085-4153-879b-b430b2a5a855}</author>
-    <author>tc={72def68a-07f2-4ab5-9dd8-2358d7537fb4}</author>
+    <author>tc={9d256fd8-46be-4af9-9b5c-7e04558d4601}</author>
+    <author>tc={c75241ac-b84b-47da-aa2a-6d1cfa1e46ac}</author>
   </authors>
   <commentList>
-    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{003CCFB8-B085-4153-879B-B430B2A5A855}">
+    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{9D256FD8-46BE-4AF9-9B5C-7E04558D4601}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -62,7 +62,7 @@
     ya lo tiene en seguimiento Josué</t>
       </text>
     </comment>
-    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{72DEF68A-07F2-4AB5-9DD8-2358D7537FB4}">
+    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{C75241AC-B84B-47DA-AA2A-6D1CFA1E46AC}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4794" uniqueCount="1473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4839" uniqueCount="1481">
   <si>
     <t>ID de Prospecto</t>
   </si>
@@ -2084,27 +2084,27 @@
     <t>Standard Profil</t>
   </si>
   <si>
+    <t>PSP5</t>
+  </si>
+  <si>
+    <t>Joel Rodríguez</t>
+  </si>
+  <si>
+    <t>ZF Group</t>
+  </si>
+  <si>
+    <t>Manuel Limón</t>
+  </si>
+  <si>
+    <t>Radiall</t>
+  </si>
+  <si>
+    <t>Sonora</t>
+  </si>
+  <si>
     <t>3. Calificación</t>
   </si>
   <si>
-    <t>PSP5</t>
-  </si>
-  <si>
-    <t>Joel Rodríguez</t>
-  </si>
-  <si>
-    <t>ZF Group</t>
-  </si>
-  <si>
-    <t>Manuel Limón</t>
-  </si>
-  <si>
-    <t>Radiall</t>
-  </si>
-  <si>
-    <t>Sonora</t>
-  </si>
-  <si>
     <t>Iván Bello</t>
   </si>
   <si>
@@ -2321,6 +2321,30 @@
     <t>Congreso / Cámara / Networking</t>
   </si>
   <si>
+    <t>José</t>
+  </si>
+  <si>
+    <t>Supermercado La Noria</t>
+  </si>
+  <si>
+    <t>Eduardo Guerrero</t>
+  </si>
+  <si>
+    <t>Tortillería y Cremería</t>
+  </si>
+  <si>
+    <t>Fernando Cadena</t>
+  </si>
+  <si>
+    <t>Tortillería La Perla</t>
+  </si>
+  <si>
+    <t>Germán Mendoza</t>
+  </si>
+  <si>
+    <t>American Boa</t>
+  </si>
+  <si>
     <t>PSP81</t>
   </si>
   <si>
@@ -3761,7 +3785,7 @@
     <t>Ing. Gabriela Ortíz Nava</t>
   </si>
   <si>
-    <t>Polesazinc</t>
+    <t>Ing. Juan Gasca</t>
   </si>
   <si>
     <t>Arq. Alejandra Vergara</t>
@@ -5775,7 +5799,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Anónimo" id="{987CB782-65FF-43C3-B2A1-A92D6AA16498}" userId="" providerId="google-sheets"/>
+  <person displayName="Anónimo" id="{45B2083E-4DCC-4231-86BE-3E9E61CFA40D}" userId="" providerId="google-sheets"/>
 </personList>
 </file>
 
@@ -5821,17 +5845,7 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabla_6" displayName="Tabla_6" ref="A1:L115">
-  <autoFilter ref="A1:L115" xr:uid="{00000000-0009-0000-0100-000004000000}">
-    <filterColumn colId="5">
-      <filters blank="1">
-        <filter val="10. Negociación"/>
-        <filter val="5. Visita Técnica / Diagnóstico en Sitio"/>
-        <filter val="6. Diseño de Solución / Pre-Ingeniería"/>
-        <filter val="7. Estimación / Cotización"/>
-        <filter val="8. Propuesta Enviada"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L115" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="ID de Prospecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Nombre del Prospecto"/>
@@ -6129,10 +6143,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{987CB782-65FF-43C3-B2A1-A92D6AA16498}" id="{003CCFB8-B085-4153-879B-B430B2A5A855}" done="1">
+  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{45B2083E-4DCC-4231-86BE-3E9E61CFA40D}" id="{9D256FD8-46BE-4AF9-9B5C-7E04558D4601}" done="1">
     <text>ya lo tiene en seguimiento Josué</text>
   </threadedComment>
-  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{987CB782-65FF-43C3-B2A1-A92D6AA16498}" id="{72DEF68A-07F2-4AB5-9DD8-2358D7537FB4}" done="1">
+  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{45B2083E-4DCC-4231-86BE-3E9E61CFA40D}" id="{C75241AC-B84B-47DA-AA2A-6D1CFA1E46AC}" done="1">
     <text>Ya tienen contrato con Ammper</text>
   </threadedComment>
 </ThreadedComments>
@@ -11967,7 +11981,7 @@
       <c r="AB1" s="7"/>
       <c r="AC1" s="7"/>
     </row>
-    <row r="2" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="2" spans="1:29" ht="22.5" customHeight="1">
       <c r="A2" s="46" t="s">
         <v>445</v>
       </c>
@@ -12003,7 +12017,7 @@
       </c>
       <c r="L2" s="57"/>
     </row>
-    <row r="3" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="3" spans="1:29" ht="22.5" customHeight="1">
       <c r="A3" s="46" t="s">
         <v>451</v>
       </c>
@@ -12039,7 +12053,7 @@
       </c>
       <c r="L3" s="57"/>
     </row>
-    <row r="4" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="4" spans="1:29" ht="22.5" customHeight="1">
       <c r="A4" s="46" t="s">
         <v>454</v>
       </c>
@@ -12075,7 +12089,7 @@
       </c>
       <c r="L4" s="57"/>
     </row>
-    <row r="5" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="5" spans="1:29" ht="22.5" customHeight="1">
       <c r="A5" s="46" t="s">
         <v>457</v>
       </c>
@@ -12092,7 +12106,7 @@
         <v>448</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>667</v>
+        <v>14</v>
       </c>
       <c r="G5" s="54">
         <v>46076</v>
@@ -12111,15 +12125,15 @@
       </c>
       <c r="L5" s="57"/>
     </row>
-    <row r="6" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="6" spans="1:29" ht="22.5" customHeight="1">
       <c r="A6" s="46" t="s">
+        <v>667</v>
+      </c>
+      <c r="B6" s="51" t="s">
         <v>668</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="C6" s="51" t="s">
         <v>669</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>670</v>
       </c>
       <c r="D6" s="52" t="s">
         <v>540</v>
@@ -12147,24 +12161,24 @@
       </c>
       <c r="L6" s="57"/>
     </row>
-    <row r="7" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="7" spans="1:29" ht="22.5" customHeight="1">
       <c r="A7" s="46" t="s">
         <v>459</v>
       </c>
       <c r="B7" s="51" t="s">
+        <v>670</v>
+      </c>
+      <c r="C7" s="51" t="s">
         <v>671</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="D7" s="52" t="s">
         <v>672</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="E7" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F7" s="53" t="s">
         <v>673</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="F7" s="53" t="s">
-        <v>667</v>
       </c>
       <c r="G7" s="54">
         <v>46077</v>
@@ -12219,7 +12233,7 @@
       </c>
       <c r="L8" s="57"/>
     </row>
-    <row r="9" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="9" spans="1:29" ht="22.5" customHeight="1">
       <c r="A9" s="46" t="s">
         <v>465</v>
       </c>
@@ -12255,7 +12269,7 @@
       </c>
       <c r="L9" s="57"/>
     </row>
-    <row r="10" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="10" spans="1:29" ht="22.5" customHeight="1">
       <c r="A10" s="46" t="s">
         <v>468</v>
       </c>
@@ -12291,7 +12305,7 @@
       </c>
       <c r="L10" s="57"/>
     </row>
-    <row r="11" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="11" spans="1:29" ht="22.5" customHeight="1">
       <c r="A11" s="46" t="s">
         <v>471</v>
       </c>
@@ -12308,7 +12322,7 @@
         <v>683</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G11" s="54">
         <v>46083</v>
@@ -12327,7 +12341,7 @@
       </c>
       <c r="L11" s="57"/>
     </row>
-    <row r="12" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="12" spans="1:29" ht="22.5" customHeight="1">
       <c r="A12" s="46" t="s">
         <v>474</v>
       </c>
@@ -12344,7 +12358,7 @@
         <v>683</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G12" s="54">
         <v>46083</v>
@@ -12363,7 +12377,7 @@
       </c>
       <c r="L12" s="57"/>
     </row>
-    <row r="13" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="13" spans="1:29" ht="22.5" customHeight="1">
       <c r="A13" s="46" t="s">
         <v>477</v>
       </c>
@@ -12380,7 +12394,7 @@
         <v>448</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G13" s="54">
         <v>46085</v>
@@ -12399,7 +12413,7 @@
       </c>
       <c r="L13" s="57"/>
     </row>
-    <row r="14" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="14" spans="1:29" ht="22.5" customHeight="1">
       <c r="A14" s="46" t="s">
         <v>481</v>
       </c>
@@ -12471,7 +12485,7 @@
       </c>
       <c r="L15" s="57"/>
     </row>
-    <row r="16" spans="1:29" ht="22.5" hidden="1" customHeight="1">
+    <row r="16" spans="1:29" ht="22.5" customHeight="1">
       <c r="A16" s="46" t="s">
         <v>488</v>
       </c>
@@ -12488,7 +12502,7 @@
         <v>692</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G16" s="54">
         <v>46087</v>
@@ -12615,7 +12629,7 @@
       </c>
       <c r="L19" s="57"/>
     </row>
-    <row r="20" spans="1:12" ht="22.5" hidden="1" customHeight="1">
+    <row r="20" spans="1:12" ht="22.5" customHeight="1">
       <c r="A20" s="46" t="s">
         <v>500</v>
       </c>
@@ -12687,7 +12701,7 @@
       </c>
       <c r="L21" s="57"/>
     </row>
-    <row r="22" spans="1:12" ht="22.5" hidden="1" customHeight="1">
+    <row r="22" spans="1:12" ht="22.5" customHeight="1">
       <c r="A22" s="46" t="s">
         <v>506</v>
       </c>
@@ -12723,7 +12737,7 @@
       </c>
       <c r="L22" s="57"/>
     </row>
-    <row r="23" spans="1:12" ht="22.5" hidden="1" customHeight="1">
+    <row r="23" spans="1:12" ht="22.5" customHeight="1">
       <c r="A23" s="46" t="s">
         <v>510</v>
       </c>
@@ -12795,7 +12809,7 @@
       </c>
       <c r="L24" s="57"/>
     </row>
-    <row r="25" spans="1:12" ht="22.5" hidden="1" customHeight="1">
+    <row r="25" spans="1:12" ht="22.5" customHeight="1">
       <c r="A25" s="46" t="s">
         <v>517</v>
       </c>
@@ -12831,7 +12845,7 @@
       </c>
       <c r="L25" s="57"/>
     </row>
-    <row r="26" spans="1:12" ht="22.5" hidden="1" customHeight="1">
+    <row r="26" spans="1:12" ht="22.5" customHeight="1">
       <c r="A26" s="46" t="s">
         <v>520</v>
       </c>
@@ -12865,7 +12879,7 @@
       </c>
       <c r="L26" s="57"/>
     </row>
-    <row r="27" spans="1:12" ht="22.5" hidden="1" customHeight="1">
+    <row r="27" spans="1:12" ht="22.5" customHeight="1">
       <c r="A27" s="46" t="s">
         <v>523</v>
       </c>
@@ -12882,7 +12896,7 @@
         <v>448</v>
       </c>
       <c r="F27" s="53" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G27" s="54">
         <v>46135</v>
@@ -12901,7 +12915,7 @@
       </c>
       <c r="L27" s="57"/>
     </row>
-    <row r="28" spans="1:12" ht="22.5" hidden="1" customHeight="1">
+    <row r="28" spans="1:12" ht="22.5" customHeight="1">
       <c r="A28" s="46" t="s">
         <v>527</v>
       </c>
@@ -12918,7 +12932,7 @@
         <v>448</v>
       </c>
       <c r="F28" s="53" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G28" s="54">
         <v>46135</v>
@@ -12937,7 +12951,7 @@
       </c>
       <c r="L28" s="57"/>
     </row>
-    <row r="29" spans="1:12" ht="22.5" hidden="1" customHeight="1">
+    <row r="29" spans="1:12" ht="22.5" customHeight="1">
       <c r="A29" s="46" t="s">
         <v>531</v>
       </c>
@@ -12954,7 +12968,7 @@
         <v>706</v>
       </c>
       <c r="F29" s="53" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G29" s="54">
         <v>46140</v>
@@ -12973,7 +12987,7 @@
       </c>
       <c r="L29" s="57"/>
     </row>
-    <row r="30" spans="1:12" ht="22.5" hidden="1" customHeight="1">
+    <row r="30" spans="1:12" ht="22.5" customHeight="1">
       <c r="A30" s="46" t="s">
         <v>534</v>
       </c>
@@ -13009,7 +13023,7 @@
       </c>
       <c r="L30" s="57"/>
     </row>
-    <row r="31" spans="1:12" ht="22.5" hidden="1" customHeight="1">
+    <row r="31" spans="1:12" ht="22.5" customHeight="1">
       <c r="A31" s="46" t="s">
         <v>538</v>
       </c>
@@ -13045,7 +13059,7 @@
       </c>
       <c r="L31" s="57"/>
     </row>
-    <row r="32" spans="1:12" ht="22.5" hidden="1" customHeight="1">
+    <row r="32" spans="1:12" ht="22.5" customHeight="1">
       <c r="A32" s="46" t="s">
         <v>541</v>
       </c>
@@ -13103,7 +13117,7 @@
       <c r="G33" s="54">
         <v>46148</v>
       </c>
-      <c r="H33" s="55">
+      <c r="H33" s="58">
         <v>719200</v>
       </c>
       <c r="I33" s="56">
@@ -13117,7 +13131,7 @@
       </c>
       <c r="L33" s="57"/>
     </row>
-    <row r="34" spans="1:12" ht="22.5" hidden="1" customHeight="1">
+    <row r="34" spans="1:12" ht="22.5" customHeight="1">
       <c r="A34" s="46" t="s">
         <v>547</v>
       </c>
@@ -13134,7 +13148,7 @@
         <v>448</v>
       </c>
       <c r="F34" s="53" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G34" s="54">
         <v>46148</v>
@@ -13193,15 +13207,33 @@
       <c r="A36" s="46" t="s">
         <v>555</v>
       </c>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="53"/>
+      <c r="B36" s="51" t="s">
+        <v>746</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>747</v>
+      </c>
+      <c r="D36" s="49" t="s">
+        <v>658</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F36" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="54">
+        <v>46155</v>
+      </c>
+      <c r="H36" s="55">
+        <v>0</v>
+      </c>
+      <c r="I36" s="56">
+        <v>0.2</v>
+      </c>
+      <c r="J36" s="53" t="s">
+        <v>513</v>
+      </c>
       <c r="K36" s="46" t="s">
         <v>660</v>
       </c>
@@ -13211,15 +13243,33 @@
       <c r="A37" s="46" t="s">
         <v>558</v>
       </c>
-      <c r="B37" s="51"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="53"/>
+      <c r="B37" s="51" t="s">
+        <v>748</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>749</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>658</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F37" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="54">
+        <v>46155</v>
+      </c>
+      <c r="H37" s="55">
+        <v>0</v>
+      </c>
+      <c r="I37" s="56">
+        <v>0.2</v>
+      </c>
+      <c r="J37" s="53" t="s">
+        <v>513</v>
+      </c>
       <c r="K37" s="46" t="s">
         <v>660</v>
       </c>
@@ -13229,15 +13279,33 @@
       <c r="A38" s="46" t="s">
         <v>562</v>
       </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="53"/>
+      <c r="B38" s="51" t="s">
+        <v>750</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>751</v>
+      </c>
+      <c r="D38" s="49" t="s">
+        <v>658</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F38" s="53" t="s">
+        <v>673</v>
+      </c>
+      <c r="G38" s="54">
+        <v>46155</v>
+      </c>
+      <c r="H38" s="55">
+        <v>0</v>
+      </c>
+      <c r="I38" s="56">
+        <v>0.1</v>
+      </c>
+      <c r="J38" s="53" t="s">
+        <v>513</v>
+      </c>
       <c r="K38" s="46" t="s">
         <v>660</v>
       </c>
@@ -13247,15 +13315,33 @@
       <c r="A39" s="46" t="s">
         <v>565</v>
       </c>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="54"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="53"/>
+      <c r="B39" s="51" t="s">
+        <v>752</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>753</v>
+      </c>
+      <c r="D39" s="49" t="s">
+        <v>726</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F39" s="53" t="s">
+        <v>673</v>
+      </c>
+      <c r="G39" s="54">
+        <v>46155</v>
+      </c>
+      <c r="H39" s="55">
+        <v>0</v>
+      </c>
+      <c r="I39" s="56">
+        <v>0.1</v>
+      </c>
+      <c r="J39" s="53" t="s">
+        <v>659</v>
+      </c>
       <c r="K39" s="46" t="s">
         <v>660</v>
       </c>
@@ -14037,7 +14123,7 @@
     </row>
     <row r="83" spans="1:12" ht="22.5" customHeight="1">
       <c r="A83" s="46" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="B83" s="51"/>
       <c r="C83" s="51"/>
@@ -14055,7 +14141,7 @@
     </row>
     <row r="84" spans="1:12" ht="22.5" customHeight="1">
       <c r="A84" s="46" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="B84" s="51"/>
       <c r="C84" s="51"/>
@@ -14073,7 +14159,7 @@
     </row>
     <row r="85" spans="1:12" ht="22.5" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="B85" s="51"/>
       <c r="C85" s="51"/>
@@ -14091,7 +14177,7 @@
     </row>
     <row r="86" spans="1:12" ht="22.5" customHeight="1">
       <c r="A86" s="46" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="B86" s="51"/>
       <c r="C86" s="51"/>
@@ -14109,7 +14195,7 @@
     </row>
     <row r="87" spans="1:12" ht="22.5" customHeight="1">
       <c r="A87" s="46" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="B87" s="51"/>
       <c r="C87" s="51"/>
@@ -14127,7 +14213,7 @@
     </row>
     <row r="88" spans="1:12" ht="22.5" customHeight="1">
       <c r="A88" s="46" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="B88" s="51"/>
       <c r="C88" s="51"/>
@@ -14145,7 +14231,7 @@
     </row>
     <row r="89" spans="1:12" ht="22.5" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="B89" s="51"/>
       <c r="C89" s="51"/>
@@ -14163,7 +14249,7 @@
     </row>
     <row r="90" spans="1:12" ht="22.5" customHeight="1">
       <c r="A90" s="46" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="B90" s="51"/>
       <c r="C90" s="51"/>
@@ -14181,7 +14267,7 @@
     </row>
     <row r="91" spans="1:12" ht="22.5" customHeight="1">
       <c r="A91" s="46" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B91" s="51"/>
       <c r="C91" s="51"/>
@@ -14199,7 +14285,7 @@
     </row>
     <row r="92" spans="1:12" ht="22.5" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="B92" s="51"/>
       <c r="C92" s="51"/>
@@ -14217,7 +14303,7 @@
     </row>
     <row r="93" spans="1:12" ht="22.5" customHeight="1">
       <c r="A93" s="46" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="B93" s="51"/>
       <c r="C93" s="51"/>
@@ -14235,7 +14321,7 @@
     </row>
     <row r="94" spans="1:12" ht="22.5" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="B94" s="51"/>
       <c r="C94" s="51"/>
@@ -14253,7 +14339,7 @@
     </row>
     <row r="95" spans="1:12" ht="22.5" customHeight="1">
       <c r="A95" s="46" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="B95" s="51"/>
       <c r="C95" s="51"/>
@@ -14271,7 +14357,7 @@
     </row>
     <row r="96" spans="1:12" ht="22.5" customHeight="1">
       <c r="A96" s="46" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="B96" s="51"/>
       <c r="C96" s="51"/>
@@ -14679,13 +14765,17 @@
     <hyperlink ref="D33" r:id="rId31" xr:uid="{00000000-0004-0000-0300-00001E000000}"/>
     <hyperlink ref="D34" r:id="rId32" xr:uid="{00000000-0004-0000-0300-00001F000000}"/>
     <hyperlink ref="D35" r:id="rId33" xr:uid="{00000000-0004-0000-0300-000020000000}"/>
+    <hyperlink ref="D36" r:id="rId34" xr:uid="{00000000-0004-0000-0300-000021000000}"/>
+    <hyperlink ref="D37" r:id="rId35" xr:uid="{00000000-0004-0000-0300-000022000000}"/>
+    <hyperlink ref="D38" r:id="rId36" xr:uid="{00000000-0004-0000-0300-000023000000}"/>
+    <hyperlink ref="D39" r:id="rId37" xr:uid="{00000000-0004-0000-0300-000024000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
-  <legacyDrawing r:id="rId34"/>
+  <legacyDrawing r:id="rId38"/>
   <tableParts count="1">
-    <tablePart r:id="rId35"/>
+    <tablePart r:id="rId39"/>
   </tableParts>
 </worksheet>
 </file>
@@ -14770,10 +14860,10 @@
     <row r="2" spans="1:29" ht="22.5" customHeight="1">
       <c r="A2" s="46"/>
       <c r="B2" s="46" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="D2" s="49" t="s">
         <v>561</v>
@@ -14791,17 +14881,17 @@
       <c r="I2" s="56"/>
       <c r="J2" s="53"/>
       <c r="K2" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L2" s="57"/>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
       <c r="A3" s="46"/>
       <c r="B3" s="46" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="D3" s="49" t="s">
         <v>561</v>
@@ -14819,23 +14909,23 @@
       <c r="I3" s="56"/>
       <c r="J3" s="53"/>
       <c r="K3" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L3" s="57"/>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
       <c r="A4" s="46"/>
       <c r="B4" s="46" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>733</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>119</v>
@@ -14849,17 +14939,17 @@
         <v>25</v>
       </c>
       <c r="K4" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L4" s="57"/>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
       <c r="A5" s="46"/>
       <c r="B5" s="46" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>733</v>
@@ -14876,20 +14966,20 @@
       <c r="H5" s="55"/>
       <c r="I5" s="56"/>
       <c r="J5" s="53" t="s">
+        <v>777</v>
+      </c>
+      <c r="K5" s="46" t="s">
         <v>769</v>
-      </c>
-      <c r="K5" s="46" t="s">
-        <v>761</v>
       </c>
       <c r="L5" s="57"/>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
       <c r="A6" s="46"/>
       <c r="B6" s="51" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="D6" s="49" t="s">
         <v>561</v>
@@ -14909,17 +14999,17 @@
         <v>25</v>
       </c>
       <c r="K6" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L6" s="57"/>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
       <c r="A7" s="46"/>
       <c r="B7" s="51" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="D7" s="49" t="s">
         <v>733</v>
@@ -14939,17 +15029,17 @@
         <v>16</v>
       </c>
       <c r="K7" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L7" s="57"/>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
       <c r="A8" s="46"/>
       <c r="B8" s="51" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="D8" s="49" t="s">
         <v>733</v>
@@ -14969,17 +15059,17 @@
         <v>16</v>
       </c>
       <c r="K8" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L8" s="57"/>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
       <c r="A9" s="46"/>
       <c r="B9" s="51" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="D9" s="49" t="s">
         <v>733</v>
@@ -14999,17 +15089,17 @@
         <v>16</v>
       </c>
       <c r="K9" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L9" s="57"/>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
       <c r="A10" s="46"/>
       <c r="B10" s="51" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="D10" s="49" t="s">
         <v>540</v>
@@ -15029,17 +15119,17 @@
         <v>74</v>
       </c>
       <c r="K10" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L10" s="57"/>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
       <c r="A11" s="46"/>
       <c r="B11" s="51" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>723</v>
@@ -15056,20 +15146,20 @@
       <c r="H11" s="55"/>
       <c r="I11" s="56"/>
       <c r="J11" s="53" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L11" s="57"/>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="51" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="D12" s="49" t="s">
         <v>540</v>
@@ -15089,17 +15179,17 @@
         <v>16</v>
       </c>
       <c r="K12" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L12" s="57"/>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="51" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="D13" s="49" t="s">
         <v>540</v>
@@ -15119,17 +15209,17 @@
         <v>688</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L13" s="57"/>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
       <c r="A14" s="46"/>
       <c r="B14" s="51" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="D14" s="49" t="s">
         <v>530</v>
@@ -15146,20 +15236,20 @@
       <c r="H14" s="55"/>
       <c r="I14" s="56"/>
       <c r="J14" s="53" t="s">
+        <v>777</v>
+      </c>
+      <c r="K14" s="51" t="s">
         <v>769</v>
-      </c>
-      <c r="K14" s="51" t="s">
-        <v>761</v>
       </c>
       <c r="L14" s="57"/>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
       <c r="A15" s="46"/>
       <c r="B15" s="51" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="D15" s="49" t="s">
         <v>561</v>
@@ -15179,17 +15269,17 @@
         <v>688</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L15" s="57"/>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
       <c r="A16" s="46"/>
       <c r="B16" s="51" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -15207,17 +15297,17 @@
         <v>688</v>
       </c>
       <c r="K16" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L16" s="57"/>
     </row>
     <row r="17" spans="1:12" ht="22.5" customHeight="1">
       <c r="A17" s="46"/>
       <c r="B17" s="51" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="D17" s="49" t="s">
         <v>733</v>
@@ -15237,17 +15327,17 @@
         <v>688</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L17" s="57"/>
     </row>
     <row r="18" spans="1:12" ht="22.5" customHeight="1">
       <c r="A18" s="46"/>
       <c r="B18" s="51" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="D18" s="49" t="s">
         <v>540</v>
@@ -15267,17 +15357,17 @@
         <v>16</v>
       </c>
       <c r="K18" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L18" s="57"/>
     </row>
     <row r="19" spans="1:12" ht="22.5" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="51" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="D19" s="49" t="s">
         <v>723</v>
@@ -15297,7 +15387,7 @@
         <v>74</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L19" s="57"/>
     </row>
@@ -15306,7 +15396,7 @@
         <v>175</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="C20" s="51" t="s">
         <v>483</v>
@@ -15329,7 +15419,7 @@
         <v>16</v>
       </c>
       <c r="K20" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L20" s="57"/>
     </row>
@@ -15338,7 +15428,7 @@
         <v>170</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="C21" s="51" t="s">
         <v>483</v>
@@ -15361,7 +15451,7 @@
         <v>16</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L21" s="57"/>
     </row>
@@ -15370,10 +15460,10 @@
         <v>172</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="D22" s="49" t="s">
         <v>561</v>
@@ -15393,7 +15483,7 @@
         <v>513</v>
       </c>
       <c r="K22" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L22" s="57"/>
     </row>
@@ -15402,16 +15492,16 @@
         <v>135</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="D23" s="49" t="s">
         <v>733</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="F23" s="53" t="s">
         <v>119</v>
@@ -15425,7 +15515,7 @@
         <v>688</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L23" s="57"/>
     </row>
@@ -15434,13 +15524,13 @@
         <v>139</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>448</v>
@@ -15457,7 +15547,7 @@
         <v>16</v>
       </c>
       <c r="K24" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L24" s="57"/>
     </row>
@@ -15466,13 +15556,13 @@
         <v>142</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>448</v>
@@ -15489,7 +15579,7 @@
         <v>74</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L25" s="57"/>
     </row>
@@ -15498,10 +15588,10 @@
         <v>144</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>733</v>
@@ -15521,7 +15611,7 @@
         <v>74</v>
       </c>
       <c r="K26" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L26" s="57"/>
     </row>
@@ -15530,13 +15620,13 @@
         <v>152</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>448</v>
@@ -15553,7 +15643,7 @@
         <v>74</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L27" s="57"/>
     </row>
@@ -15562,10 +15652,10 @@
         <v>155</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="D28" s="49" t="s">
         <v>733</v>
@@ -15585,25 +15675,25 @@
         <v>74</v>
       </c>
       <c r="K28" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L28" s="57"/>
     </row>
     <row r="29" spans="1:12" ht="22.5" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="D29" s="49" t="s">
         <v>733</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="F29" s="53" t="s">
         <v>119</v>
@@ -15617,7 +15707,7 @@
         <v>688</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L29" s="57"/>
     </row>
@@ -15626,10 +15716,10 @@
         <v>149</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="C30" s="51" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="D30" s="49" t="s">
         <v>561</v>
@@ -15653,7 +15743,7 @@
         <v>513</v>
       </c>
       <c r="K30" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L30" s="57"/>
     </row>
@@ -15662,10 +15752,10 @@
         <v>97</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="D31" s="49" t="s">
         <v>726</v>
@@ -15685,7 +15775,7 @@
         <v>25</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L31" s="57"/>
     </row>
@@ -15694,10 +15784,10 @@
         <v>99</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="D32" s="49" t="s">
         <v>733</v>
@@ -15717,7 +15807,7 @@
         <v>74</v>
       </c>
       <c r="K32" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L32" s="57"/>
     </row>
@@ -15726,10 +15816,10 @@
         <v>103</v>
       </c>
       <c r="B33" s="46" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="C33" s="46" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="D33" s="49" t="s">
         <v>561</v>
@@ -15749,7 +15839,7 @@
         <v>688</v>
       </c>
       <c r="K33" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L33" s="57"/>
     </row>
@@ -15758,10 +15848,10 @@
         <v>129</v>
       </c>
       <c r="B34" s="51" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C34" s="51" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="D34" s="49" t="s">
         <v>733</v>
@@ -15777,26 +15867,26 @@
       </c>
       <c r="H34" s="55"/>
       <c r="I34" s="60" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="J34" s="53" t="s">
         <v>688</v>
       </c>
       <c r="K34" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L34" s="57"/>
     </row>
     <row r="35" spans="1:12" ht="22.5" customHeight="1">
       <c r="A35" s="46"/>
       <c r="B35" s="51" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="C35" s="51" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>448</v>
@@ -15813,7 +15903,7 @@
         <v>688</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L35" s="57"/>
     </row>
@@ -15822,10 +15912,10 @@
         <v>68</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10" t="s">
@@ -15843,7 +15933,7 @@
         <v>74</v>
       </c>
       <c r="K36" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L36" s="57"/>
     </row>
@@ -15852,10 +15942,10 @@
         <v>71</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="C37" s="51" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="D37" s="49" t="s">
         <v>540</v>
@@ -15875,7 +15965,7 @@
         <v>688</v>
       </c>
       <c r="K37" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L37" s="57"/>
     </row>
@@ -15884,10 +15974,10 @@
         <v>78</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C38" s="51" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D38" s="49" t="s">
         <v>733</v>
@@ -15907,7 +15997,7 @@
         <v>16</v>
       </c>
       <c r="K38" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L38" s="57"/>
     </row>
@@ -15916,16 +16006,16 @@
         <v>81</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="F39" s="53" t="s">
         <v>119</v>
@@ -15939,20 +16029,20 @@
         <v>16</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L39" s="57"/>
     </row>
     <row r="40" spans="1:12" ht="22.5" customHeight="1">
       <c r="A40" s="46"/>
       <c r="B40" s="51" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="C40" s="51" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>448</v>
@@ -15969,7 +16059,7 @@
         <v>74</v>
       </c>
       <c r="K40" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L40" s="57"/>
     </row>
@@ -15978,10 +16068,10 @@
         <v>54</v>
       </c>
       <c r="B41" s="51" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="C41" s="51" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="D41" s="49" t="s">
         <v>723</v>
@@ -16001,7 +16091,7 @@
         <v>25</v>
       </c>
       <c r="K41" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L41" s="57"/>
     </row>
@@ -16010,14 +16100,14 @@
         <v>60</v>
       </c>
       <c r="B42" s="46" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="F42" s="53" t="s">
         <v>119</v>
@@ -16031,7 +16121,7 @@
         <v>688</v>
       </c>
       <c r="K42" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L42" s="57"/>
     </row>
@@ -16040,10 +16130,10 @@
         <v>63</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="C43" s="51" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="D43" s="49" t="s">
         <v>723</v>
@@ -16063,7 +16153,7 @@
         <v>688</v>
       </c>
       <c r="K43" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L43" s="57"/>
     </row>
@@ -16072,13 +16162,13 @@
         <v>65</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="C44" s="51" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>448</v>
@@ -16095,7 +16185,7 @@
         <v>25</v>
       </c>
       <c r="K44" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L44" s="57"/>
     </row>
@@ -16104,13 +16194,13 @@
         <v>85</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="C45" s="51" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>448</v>
@@ -16123,25 +16213,25 @@
       </c>
       <c r="H45" s="55"/>
       <c r="I45" s="60" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="J45" s="53" t="s">
         <v>513</v>
       </c>
       <c r="K45" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L45" s="57"/>
     </row>
     <row r="46" spans="1:12" ht="22.5" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="D46" s="49" t="s">
         <v>540</v>
@@ -16161,19 +16251,19 @@
         <v>688</v>
       </c>
       <c r="K46" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L46" s="57"/>
     </row>
     <row r="47" spans="1:12" ht="22.5" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="B47" s="51" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="D47" s="49" t="s">
         <v>526</v>
@@ -16193,19 +16283,19 @@
         <v>25</v>
       </c>
       <c r="K47" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L47" s="57"/>
     </row>
     <row r="48" spans="1:12" ht="22.5" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="B48" s="51" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="C48" s="51" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="D48" s="49" t="s">
         <v>733</v>
@@ -16225,22 +16315,22 @@
         <v>74</v>
       </c>
       <c r="K48" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L48" s="57"/>
     </row>
     <row r="49" spans="1:12" ht="22.5" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>448</v>
@@ -16257,19 +16347,19 @@
         <v>74</v>
       </c>
       <c r="K49" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L49" s="57"/>
     </row>
     <row r="50" spans="1:12" ht="22.5" customHeight="1">
       <c r="A50" s="8" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="B50" s="51" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="C50" s="51" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="D50" s="49" t="s">
         <v>733</v>
@@ -16289,7 +16379,7 @@
         <v>74</v>
       </c>
       <c r="K50" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L50" s="57"/>
     </row>
@@ -16298,10 +16388,10 @@
         <v>11</v>
       </c>
       <c r="B51" s="51" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="C51" s="51" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="D51" s="49" t="s">
         <v>733</v>
@@ -16321,7 +16411,7 @@
         <v>688</v>
       </c>
       <c r="K51" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L51" s="57"/>
     </row>
@@ -16330,10 +16420,10 @@
         <v>18</v>
       </c>
       <c r="B52" s="51" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="C52" s="51" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="D52" s="49" t="s">
         <v>540</v>
@@ -16353,7 +16443,7 @@
         <v>25</v>
       </c>
       <c r="K52" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L52" s="57"/>
     </row>
@@ -16363,7 +16453,7 @@
       </c>
       <c r="B53" s="46"/>
       <c r="C53" s="46" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="D53" s="49" t="s">
         <v>723</v>
@@ -16383,7 +16473,7 @@
         <v>688</v>
       </c>
       <c r="K53" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L53" s="57"/>
     </row>
@@ -16392,10 +16482,10 @@
         <v>26</v>
       </c>
       <c r="B54" s="51" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="C54" s="51" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="D54" s="49" t="s">
         <v>733</v>
@@ -16415,7 +16505,7 @@
         <v>688</v>
       </c>
       <c r="K54" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L54" s="57"/>
     </row>
@@ -16424,10 +16514,10 @@
         <v>29</v>
       </c>
       <c r="B55" s="51" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="C55" s="51" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="D55" s="49" t="s">
         <v>733</v>
@@ -16447,7 +16537,7 @@
         <v>74</v>
       </c>
       <c r="K55" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L55" s="57"/>
     </row>
@@ -16456,7 +16546,7 @@
         <v>34</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="C56" s="51" t="s">
         <v>712</v>
@@ -16479,7 +16569,7 @@
         <v>688</v>
       </c>
       <c r="K56" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L56" s="57"/>
     </row>
@@ -16488,13 +16578,13 @@
         <v>48</v>
       </c>
       <c r="B57" s="51" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="C57" s="51" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>448</v>
@@ -16508,10 +16598,10 @@
       <c r="H57" s="55"/>
       <c r="I57" s="56"/>
       <c r="J57" s="53" t="s">
+        <v>777</v>
+      </c>
+      <c r="K57" s="51" t="s">
         <v>769</v>
-      </c>
-      <c r="K57" s="51" t="s">
-        <v>761</v>
       </c>
       <c r="L57" s="57"/>
     </row>
@@ -16520,10 +16610,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="51" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="C58" s="51" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="D58" s="49" t="s">
         <v>561</v>
@@ -16543,7 +16633,7 @@
         <v>513</v>
       </c>
       <c r="K58" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L58" s="57"/>
     </row>
@@ -16552,13 +16642,13 @@
         <v>638</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="C59" s="51" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>448</v>
@@ -16575,7 +16665,7 @@
         <v>74</v>
       </c>
       <c r="K59" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L59" s="57"/>
     </row>
@@ -16584,10 +16674,10 @@
         <v>639</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="D60" s="49" t="s">
         <v>540</v>
@@ -16607,7 +16697,7 @@
         <v>745</v>
       </c>
       <c r="K60" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L60" s="57"/>
     </row>
@@ -16616,13 +16706,13 @@
         <v>640</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="C61" s="51" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>448</v>
@@ -16639,7 +16729,7 @@
         <v>74</v>
       </c>
       <c r="K61" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L61" s="57"/>
     </row>
@@ -16648,13 +16738,13 @@
         <v>649</v>
       </c>
       <c r="B62" s="51" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="C62" s="51" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>448</v>
@@ -16671,17 +16761,17 @@
         <v>25</v>
       </c>
       <c r="K62" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L62" s="57"/>
     </row>
     <row r="63" spans="1:12" ht="22.5" customHeight="1">
       <c r="A63" s="46"/>
       <c r="B63" s="51" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="C63" s="51" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="D63" s="49" t="s">
         <v>526</v>
@@ -16701,7 +16791,7 @@
         <v>688</v>
       </c>
       <c r="K63" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L63" s="57"/>
     </row>
@@ -16710,13 +16800,13 @@
         <v>609</v>
       </c>
       <c r="B64" s="51" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="C64" s="51" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>448</v>
@@ -16733,7 +16823,7 @@
         <v>74</v>
       </c>
       <c r="K64" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L64" s="57"/>
     </row>
@@ -16742,13 +16832,13 @@
         <v>621</v>
       </c>
       <c r="B65" s="51" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="C65" s="51" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>448</v>
@@ -16765,7 +16855,7 @@
         <v>74</v>
       </c>
       <c r="K65" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L65" s="57"/>
     </row>
@@ -16774,10 +16864,10 @@
         <v>624</v>
       </c>
       <c r="B66" s="51" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="C66" s="51" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="D66" s="49" t="s">
         <v>540</v>
@@ -16797,7 +16887,7 @@
         <v>74</v>
       </c>
       <c r="K66" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L66" s="57"/>
     </row>
@@ -16806,16 +16896,16 @@
         <v>597</v>
       </c>
       <c r="B67" s="51" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="F67" s="53" t="s">
         <v>119</v>
@@ -16829,7 +16919,7 @@
         <v>74</v>
       </c>
       <c r="K67" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L67" s="57"/>
     </row>
@@ -16838,16 +16928,16 @@
         <v>600</v>
       </c>
       <c r="B68" s="51" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="C68" s="51" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="F68" s="53" t="s">
         <v>119</v>
@@ -16861,7 +16951,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L68" s="57"/>
     </row>
@@ -16870,13 +16960,13 @@
         <v>603</v>
       </c>
       <c r="B69" s="51" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="C69" s="51" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="D69" s="49" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>448</v>
@@ -16893,7 +16983,7 @@
         <v>74</v>
       </c>
       <c r="K69" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L69" s="57"/>
     </row>
@@ -16902,13 +16992,13 @@
         <v>146</v>
       </c>
       <c r="B70" s="51" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="C70" s="51" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>448</v>
@@ -16925,7 +17015,7 @@
         <v>688</v>
       </c>
       <c r="K70" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L70" s="57"/>
     </row>
@@ -16934,10 +17024,10 @@
         <v>527</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="C71" s="46" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="D71" s="49" t="s">
         <v>561</v>
@@ -16957,7 +17047,7 @@
         <v>513</v>
       </c>
       <c r="K71" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L71" s="57"/>
     </row>
@@ -16966,16 +17056,16 @@
         <v>520</v>
       </c>
       <c r="B72" s="51" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="C72" s="51" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="F72" s="53" t="s">
         <v>119</v>
@@ -16989,7 +17079,7 @@
         <v>16</v>
       </c>
       <c r="K72" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L72" s="57"/>
     </row>
@@ -16998,10 +17088,10 @@
         <v>576</v>
       </c>
       <c r="B73" s="51" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="C73" s="51" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="D73" s="10"/>
       <c r="E73" s="10" t="s">
@@ -17019,7 +17109,7 @@
         <v>25</v>
       </c>
       <c r="K73" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L73" s="57"/>
     </row>
@@ -17028,10 +17118,10 @@
         <v>579</v>
       </c>
       <c r="B74" s="51" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="D74" s="49" t="s">
         <v>723</v>
@@ -17051,7 +17141,7 @@
         <v>25</v>
       </c>
       <c r="K74" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L74" s="57"/>
     </row>
@@ -17060,13 +17150,13 @@
         <v>650</v>
       </c>
       <c r="B75" s="51" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="C75" s="51" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>448</v>
@@ -17083,7 +17173,7 @@
         <v>25</v>
       </c>
       <c r="K75" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L75" s="57"/>
     </row>
@@ -17092,13 +17182,13 @@
         <v>503</v>
       </c>
       <c r="B76" s="46" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="C76" s="46" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="D76" s="49" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>448</v>
@@ -17117,7 +17207,7 @@
         <v>25</v>
       </c>
       <c r="K76" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L76" s="57"/>
     </row>
@@ -17126,16 +17216,16 @@
         <v>506</v>
       </c>
       <c r="B77" s="46" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="C77" s="46" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="D77" s="49" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="F77" s="53" t="s">
         <v>699</v>
@@ -17149,7 +17239,7 @@
         <v>25</v>
       </c>
       <c r="K77" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L77" s="57"/>
     </row>
@@ -17158,10 +17248,10 @@
         <v>488</v>
       </c>
       <c r="B78" s="51" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="C78" s="51" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="D78" s="10"/>
       <c r="E78" s="10" t="s">
@@ -17181,7 +17271,7 @@
         <v>25</v>
       </c>
       <c r="K78" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L78" s="57"/>
     </row>
@@ -17190,10 +17280,10 @@
         <v>494</v>
       </c>
       <c r="B79" s="46" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="C79" s="46" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="D79" s="49" t="s">
         <v>658</v>
@@ -17215,22 +17305,22 @@
         <v>25</v>
       </c>
       <c r="K79" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L79" s="57"/>
     </row>
     <row r="80" spans="1:12" ht="22.5" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="B80" s="51" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="C80" s="51" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="D80" s="49" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>448</v>
@@ -17247,7 +17337,7 @@
         <v>16</v>
       </c>
       <c r="K80" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L80" s="57"/>
     </row>
@@ -17257,7 +17347,7 @@
       </c>
       <c r="B81" s="46"/>
       <c r="C81" s="46" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="D81" s="49" t="s">
         <v>540</v>
@@ -17277,7 +17367,7 @@
         <v>551</v>
       </c>
       <c r="K81" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L81" s="57"/>
     </row>
@@ -17286,16 +17376,16 @@
         <v>582</v>
       </c>
       <c r="B82" s="51" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="C82" s="51" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D82" s="49" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="F82" s="53" t="s">
         <v>119</v>
@@ -17309,7 +17399,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L82" s="57"/>
     </row>
@@ -17318,10 +17408,10 @@
         <v>113</v>
       </c>
       <c r="B83" s="51" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="C83" s="51" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="D83" s="49" t="s">
         <v>723</v>
@@ -17341,14 +17431,14 @@
         <v>688</v>
       </c>
       <c r="K83" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L83" s="57"/>
     </row>
     <row r="84" spans="1:12" ht="22.5" customHeight="1">
       <c r="A84" s="46"/>
       <c r="B84" s="46" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="C84" s="46" t="s">
         <v>410</v>
@@ -17369,7 +17459,7 @@
         <v>74</v>
       </c>
       <c r="K84" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L84" s="57"/>
     </row>
@@ -17378,13 +17468,13 @@
         <v>116</v>
       </c>
       <c r="B85" s="51" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="C85" s="51" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="D85" s="49" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>448</v>
@@ -17401,17 +17491,17 @@
         <v>688</v>
       </c>
       <c r="K85" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L85" s="57"/>
     </row>
     <row r="86" spans="1:12" ht="22.5" customHeight="1">
       <c r="A86" s="46"/>
       <c r="B86" s="51" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="C86" s="51" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="D86" s="10"/>
       <c r="E86" s="10" t="s">
@@ -17429,17 +17519,17 @@
         <v>25</v>
       </c>
       <c r="K86" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L86" s="57"/>
     </row>
     <row r="87" spans="1:12" ht="22.5" customHeight="1">
       <c r="A87" s="46"/>
       <c r="B87" s="51" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="C87" s="51" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="D87" s="49" t="s">
         <v>678</v>
@@ -17456,23 +17546,23 @@
       <c r="H87" s="55"/>
       <c r="I87" s="56"/>
       <c r="J87" s="53" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="K87" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L87" s="57"/>
     </row>
     <row r="88" spans="1:12" ht="22.5" customHeight="1">
       <c r="A88" s="46"/>
       <c r="B88" s="51" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>448</v>
@@ -17489,7 +17579,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L88" s="57"/>
     </row>
@@ -17498,13 +17588,13 @@
         <v>565</v>
       </c>
       <c r="B89" s="51" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="D89" s="49" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>448</v>
@@ -17521,7 +17611,7 @@
         <v>25</v>
       </c>
       <c r="K89" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L89" s="57"/>
     </row>
@@ -17530,10 +17620,10 @@
         <v>568</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="C90" s="51" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="D90" s="49" t="s">
         <v>723</v>
@@ -17553,7 +17643,7 @@
         <v>25</v>
       </c>
       <c r="K90" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L90" s="57"/>
     </row>
@@ -17562,10 +17652,10 @@
         <v>571</v>
       </c>
       <c r="B91" s="51" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="C91" s="51" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="D91" s="10"/>
       <c r="E91" s="10" t="s">
@@ -17583,7 +17673,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L91" s="57"/>
     </row>
@@ -17592,13 +17682,13 @@
         <v>574</v>
       </c>
       <c r="B92" s="51" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="C92" s="51" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="D92" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>448</v>
@@ -17615,7 +17705,7 @@
         <v>25</v>
       </c>
       <c r="K92" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L92" s="57"/>
     </row>
@@ -17624,10 +17714,10 @@
         <v>562</v>
       </c>
       <c r="B93" s="51" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="C93" s="51" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="D93" s="49" t="s">
         <v>540</v>
@@ -17647,7 +17737,7 @@
         <v>25</v>
       </c>
       <c r="K93" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L93" s="57"/>
     </row>
@@ -17656,10 +17746,10 @@
         <v>88</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="C94" s="51" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="D94" s="49" t="s">
         <v>540</v>
@@ -17679,7 +17769,7 @@
         <v>513</v>
       </c>
       <c r="K94" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L94" s="57"/>
     </row>
@@ -17688,16 +17778,16 @@
         <v>523</v>
       </c>
       <c r="B95" s="46" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="C95" s="46" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="D95" s="49" t="s">
         <v>723</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="F95" s="53" t="s">
         <v>449</v>
@@ -17711,20 +17801,20 @@
         <v>74</v>
       </c>
       <c r="K95" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L95" s="57"/>
     </row>
     <row r="96" spans="1:12" ht="22.5" customHeight="1">
       <c r="A96" s="46"/>
       <c r="B96" s="46" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="C96" s="46" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="D96" s="49" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>448</v>
@@ -17741,7 +17831,7 @@
         <v>25</v>
       </c>
       <c r="K96" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L96" s="57"/>
     </row>
@@ -17750,13 +17840,13 @@
         <v>643</v>
       </c>
       <c r="B97" s="51" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="C97" s="51" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="D97" s="49" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>448</v>
@@ -17773,7 +17863,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L97" s="57"/>
     </row>
@@ -17782,10 +17872,10 @@
         <v>644</v>
       </c>
       <c r="B98" s="51" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="C98" s="51" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="D98" s="49" t="s">
         <v>526</v>
@@ -17805,7 +17895,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L98" s="57"/>
     </row>
@@ -17814,13 +17904,13 @@
         <v>132</v>
       </c>
       <c r="B99" s="51" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="C99" s="51" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="D99" s="49" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>448</v>
@@ -17837,7 +17927,7 @@
         <v>513</v>
       </c>
       <c r="K99" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L99" s="57"/>
     </row>
@@ -17846,10 +17936,10 @@
         <v>606</v>
       </c>
       <c r="B100" s="51" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="C100" s="51" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="D100" s="49" t="s">
         <v>561</v>
@@ -17869,7 +17959,7 @@
         <v>25</v>
       </c>
       <c r="K100" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L100" s="57"/>
     </row>
@@ -17878,10 +17968,10 @@
         <v>538</v>
       </c>
       <c r="B101" s="51" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="C101" s="51" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="D101" s="49" t="s">
         <v>723</v>
@@ -17901,7 +17991,7 @@
         <v>25</v>
       </c>
       <c r="K101" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L101" s="57"/>
     </row>
@@ -17910,10 +18000,10 @@
         <v>645</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="D102" s="49" t="s">
         <v>526</v>
@@ -17933,7 +18023,7 @@
         <v>16</v>
       </c>
       <c r="K102" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L102" s="57"/>
     </row>
@@ -17942,10 +18032,10 @@
         <v>120</v>
       </c>
       <c r="B103" s="51" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="C103" s="51" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="D103" s="49" t="s">
         <v>540</v>
@@ -17965,7 +18055,7 @@
         <v>16</v>
       </c>
       <c r="K103" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L103" s="57"/>
     </row>
@@ -17974,13 +18064,13 @@
         <v>126</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="C104" s="51" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>448</v>
@@ -17997,7 +18087,7 @@
         <v>16</v>
       </c>
       <c r="K104" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L104" s="57"/>
     </row>
@@ -18006,7 +18096,7 @@
         <v>41</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="C105" s="51"/>
       <c r="D105" s="49" t="s">
@@ -18027,7 +18117,7 @@
         <v>16</v>
       </c>
       <c r="K105" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L105" s="57"/>
     </row>
@@ -18036,10 +18126,10 @@
         <v>646</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="C106" s="51" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="D106" s="49" t="s">
         <v>723</v>
@@ -18056,22 +18146,22 @@
       <c r="H106" s="55"/>
       <c r="I106" s="56"/>
       <c r="J106" s="53" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="K106" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L106" s="57"/>
     </row>
     <row r="107" spans="1:12" ht="22.5" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="B107" s="51" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="C107" s="51" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="D107" s="49" t="s">
         <v>723</v>
@@ -18091,17 +18181,17 @@
         <v>74</v>
       </c>
       <c r="K107" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L107" s="57"/>
     </row>
     <row r="108" spans="1:12" ht="22.5" customHeight="1">
       <c r="A108" s="46"/>
       <c r="B108" s="51" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="C108" s="51" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="D108" s="49" t="s">
         <v>733</v>
@@ -18121,7 +18211,7 @@
         <v>688</v>
       </c>
       <c r="K108" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L108" s="57"/>
     </row>
@@ -18130,13 +18220,13 @@
         <v>459</v>
       </c>
       <c r="B109" s="46" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="C109" s="46" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>448</v>
@@ -18157,7 +18247,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L109" s="57"/>
     </row>
@@ -18166,10 +18256,10 @@
         <v>462</v>
       </c>
       <c r="B110" s="46" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="C110" s="46" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="D110" s="49" t="s">
         <v>540</v>
@@ -18191,7 +18281,7 @@
         <v>25</v>
       </c>
       <c r="K110" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L110" s="57"/>
     </row>
@@ -18200,13 +18290,13 @@
         <v>552</v>
       </c>
       <c r="B111" s="46" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="C111" s="46" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="D111" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>448</v>
@@ -18223,7 +18313,7 @@
         <v>25</v>
       </c>
       <c r="K111" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L111" s="57"/>
     </row>
@@ -18232,13 +18322,13 @@
         <v>534</v>
       </c>
       <c r="B112" s="51" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="C112" s="51" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>448</v>
@@ -18255,7 +18345,7 @@
         <v>25</v>
       </c>
       <c r="K112" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L112" s="57"/>
     </row>
@@ -18264,10 +18354,10 @@
         <v>594</v>
       </c>
       <c r="B113" s="51" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="C113" s="51" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="D113" s="49" t="s">
         <v>540</v>
@@ -18287,7 +18377,7 @@
         <v>25</v>
       </c>
       <c r="K113" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L113" s="57"/>
     </row>
@@ -18296,10 +18386,10 @@
         <v>642</v>
       </c>
       <c r="B114" s="51" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="C114" s="51" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="D114" s="49" t="s">
         <v>723</v>
@@ -18319,7 +18409,7 @@
         <v>25</v>
       </c>
       <c r="K114" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L114" s="57"/>
     </row>
@@ -18328,16 +18418,16 @@
         <v>531</v>
       </c>
       <c r="B115" s="46" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="C115" s="46" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="D115" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="F115" s="53" t="s">
         <v>119</v>
@@ -18351,22 +18441,22 @@
         <v>25</v>
       </c>
       <c r="K115" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L115" s="57"/>
     </row>
     <row r="116" spans="1:12" ht="22.5" customHeight="1">
       <c r="A116" s="8" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="B116" s="51" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>448</v>
@@ -18383,7 +18473,7 @@
         <v>745</v>
       </c>
       <c r="K116" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L116" s="57"/>
     </row>
@@ -18392,16 +18482,16 @@
         <v>94</v>
       </c>
       <c r="B117" s="51" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="C117" s="51" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="D117" s="49" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="F117" s="53" t="s">
         <v>119</v>
@@ -18415,7 +18505,7 @@
         <v>25</v>
       </c>
       <c r="K117" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L117" s="57"/>
     </row>
@@ -18424,13 +18514,13 @@
         <v>454</v>
       </c>
       <c r="B118" s="46" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="C118" s="46" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>448</v>
@@ -18449,7 +18539,7 @@
         <v>25</v>
       </c>
       <c r="K118" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L118" s="57"/>
     </row>
@@ -18458,13 +18548,13 @@
         <v>585</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="C119" s="51" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="D119" s="49" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>448</v>
@@ -18481,7 +18571,7 @@
         <v>25</v>
       </c>
       <c r="K119" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L119" s="57"/>
     </row>
@@ -18490,13 +18580,13 @@
         <v>591</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="C120" s="51" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>448</v>
@@ -18513,7 +18603,7 @@
         <v>25</v>
       </c>
       <c r="K120" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L120" s="57"/>
     </row>
@@ -18522,10 +18612,10 @@
         <v>91</v>
       </c>
       <c r="B121" s="51" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="C121" s="51" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="D121" s="49" t="s">
         <v>540</v>
@@ -18545,7 +18635,7 @@
         <v>16</v>
       </c>
       <c r="K121" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L121" s="57"/>
     </row>
@@ -18554,13 +18644,13 @@
         <v>457</v>
       </c>
       <c r="B122" s="46" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="C122" s="46" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>448</v>
@@ -18579,7 +18669,7 @@
         <v>25</v>
       </c>
       <c r="K122" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L122" s="57"/>
     </row>
@@ -18588,10 +18678,10 @@
         <v>652</v>
       </c>
       <c r="B123" s="51" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="D123" s="49" t="s">
         <v>733</v>
@@ -18611,7 +18701,7 @@
         <v>16</v>
       </c>
       <c r="K123" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L123" s="57"/>
     </row>
@@ -18620,10 +18710,10 @@
         <v>37</v>
       </c>
       <c r="B124" s="46" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="C124" s="46" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="D124" s="49" t="s">
         <v>540</v>
@@ -18640,22 +18730,22 @@
       <c r="H124" s="55"/>
       <c r="I124" s="56"/>
       <c r="J124" s="53" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="K124" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L124" s="57"/>
     </row>
     <row r="125" spans="1:12" ht="22.5" customHeight="1">
       <c r="A125" s="8" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="B125" s="46" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="C125" s="46" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="D125" s="49" t="s">
         <v>733</v>
@@ -18675,19 +18765,19 @@
         <v>513</v>
       </c>
       <c r="K125" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L125" s="57"/>
     </row>
     <row r="126" spans="1:12" ht="22.5" customHeight="1">
       <c r="A126" s="8" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="B126" s="51" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="C126" s="51" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
       <c r="D126" s="49" t="s">
         <v>540</v>
@@ -18707,19 +18797,19 @@
         <v>16</v>
       </c>
       <c r="K126" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L126" s="57"/>
     </row>
     <row r="127" spans="1:12" ht="22.5" customHeight="1">
       <c r="A127" s="8" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="B127" s="51" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="C127" s="51" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="D127" s="49" t="s">
         <v>733</v>
@@ -18739,7 +18829,7 @@
         <v>16</v>
       </c>
       <c r="K127" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L127" s="57"/>
     </row>
@@ -18748,10 +18838,10 @@
         <v>168</v>
       </c>
       <c r="B128" s="51" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="C128" s="51" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="D128" s="49" t="s">
         <v>733</v>
@@ -18771,22 +18861,22 @@
         <v>74</v>
       </c>
       <c r="K128" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L128" s="57"/>
     </row>
     <row r="129" spans="1:12" ht="22.5" customHeight="1">
       <c r="A129" s="8" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="B129" s="51" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="C129" s="51" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>448</v>
@@ -18803,7 +18893,7 @@
         <v>25</v>
       </c>
       <c r="K129" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L129" s="57"/>
     </row>
@@ -18812,13 +18902,13 @@
         <v>641</v>
       </c>
       <c r="B130" s="51" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="E130" s="10" t="s">
         <v>448</v>
@@ -18835,7 +18925,7 @@
         <v>25</v>
       </c>
       <c r="K130" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L130" s="57"/>
     </row>
@@ -18844,10 +18934,10 @@
         <v>630</v>
       </c>
       <c r="B131" s="51" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="C131" s="51" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="D131" s="49" t="s">
         <v>718</v>
@@ -18867,7 +18957,7 @@
         <v>25</v>
       </c>
       <c r="K131" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L131" s="57"/>
     </row>
@@ -18876,13 +18966,13 @@
         <v>627</v>
       </c>
       <c r="B132" s="51" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="C132" s="51" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="D132" s="49" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>448</v>
@@ -18899,7 +18989,7 @@
         <v>513</v>
       </c>
       <c r="K132" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L132" s="57"/>
     </row>
@@ -18908,10 +18998,10 @@
         <v>555</v>
       </c>
       <c r="B133" s="51" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="C133" s="51" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="D133" s="49" t="s">
         <v>540</v>
@@ -18933,7 +19023,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L133" s="57"/>
     </row>
@@ -18942,13 +19032,13 @@
         <v>160</v>
       </c>
       <c r="B134" s="51" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="C134" s="51" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="D134" s="49" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>448</v>
@@ -18965,7 +19055,7 @@
         <v>16</v>
       </c>
       <c r="K134" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L134" s="57"/>
     </row>
@@ -18974,10 +19064,10 @@
         <v>451</v>
       </c>
       <c r="B135" s="46" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="C135" s="46" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="D135" s="49" t="s">
         <v>540</v>
@@ -19001,7 +19091,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L135" s="57"/>
     </row>
@@ -19010,13 +19100,13 @@
         <v>547</v>
       </c>
       <c r="B136" s="51" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="C136" s="51" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="D136" s="49" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>448</v>
@@ -19033,7 +19123,7 @@
         <v>25</v>
       </c>
       <c r="K136" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L136" s="57"/>
     </row>
@@ -19043,10 +19133,10 @@
       </c>
       <c r="B137" s="51"/>
       <c r="C137" s="51" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>448</v>
@@ -19063,7 +19153,7 @@
         <v>25</v>
       </c>
       <c r="K137" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L137" s="57"/>
     </row>
@@ -19072,13 +19162,13 @@
         <v>541</v>
       </c>
       <c r="B138" s="51" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="C138" s="51" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="D138" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>448</v>
@@ -19095,7 +19185,7 @@
         <v>138</v>
       </c>
       <c r="K138" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L138" s="57"/>
     </row>
@@ -19104,10 +19194,10 @@
         <v>477</v>
       </c>
       <c r="B139" s="46" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="C139" s="46" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="D139" s="49" t="s">
         <v>540</v>
@@ -19129,7 +19219,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L139" s="57"/>
     </row>
@@ -19138,13 +19228,13 @@
         <v>654</v>
       </c>
       <c r="B140" s="51" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="C140" s="51" t="s">
         <v>410</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="E140" s="10" t="s">
         <v>448</v>
@@ -19161,7 +19251,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L140" s="57"/>
     </row>
@@ -19170,13 +19260,13 @@
         <v>491</v>
       </c>
       <c r="B141" s="46" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="C141" s="46" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="D141" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>448</v>
@@ -19197,7 +19287,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L141" s="57"/>
     </row>
@@ -19206,13 +19296,13 @@
         <v>471</v>
       </c>
       <c r="B142" s="46" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="C142" s="46" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="E142" s="10" t="s">
         <v>448</v>
@@ -19231,19 +19321,19 @@
         <v>25</v>
       </c>
       <c r="K142" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L142" s="57"/>
     </row>
     <row r="143" spans="1:12" ht="22.5" customHeight="1">
       <c r="A143" s="8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B143" s="46" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="C143" s="46" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="D143" s="10" t="s">
         <v>718</v>
@@ -19265,7 +19355,7 @@
         <v>25</v>
       </c>
       <c r="K143" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L143" s="57"/>
     </row>
@@ -19274,10 +19364,10 @@
         <v>123</v>
       </c>
       <c r="B144" s="51" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="D144" s="49" t="s">
         <v>540</v>
@@ -19297,7 +19387,7 @@
         <v>16</v>
       </c>
       <c r="K144" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L144" s="57"/>
     </row>
@@ -19306,10 +19396,10 @@
         <v>544</v>
       </c>
       <c r="B145" s="51" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="C145" s="51" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="D145" s="49" t="s">
         <v>540</v>
@@ -19329,17 +19419,17 @@
         <v>25</v>
       </c>
       <c r="K145" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L145" s="57"/>
     </row>
     <row r="146" spans="1:12" ht="22.5" customHeight="1">
       <c r="A146" s="46"/>
       <c r="B146" s="51" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="C146" s="51" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="D146" s="49" t="s">
         <v>733</v>
@@ -19359,7 +19449,7 @@
         <v>25</v>
       </c>
       <c r="K146" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L146" s="57"/>
     </row>
@@ -19368,10 +19458,10 @@
         <v>474</v>
       </c>
       <c r="B147" s="46" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="C147" s="46" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="D147" s="49" t="s">
         <v>540</v>
@@ -19393,7 +19483,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L147" s="57"/>
     </row>
@@ -19402,13 +19492,13 @@
         <v>636</v>
       </c>
       <c r="B148" s="51" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="C148" s="51" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="D148" s="49" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="E148" s="10" t="s">
         <v>448</v>
@@ -19425,7 +19515,7 @@
         <v>16</v>
       </c>
       <c r="K148" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L148" s="57"/>
     </row>
@@ -19434,13 +19524,13 @@
         <v>637</v>
       </c>
       <c r="B149" s="51" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="C149" s="51" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="D149" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>448</v>
@@ -19454,10 +19544,10 @@
       <c r="H149" s="55"/>
       <c r="I149" s="56"/>
       <c r="J149" s="53" t="s">
+        <v>777</v>
+      </c>
+      <c r="K149" s="51" t="s">
         <v>769</v>
-      </c>
-      <c r="K149" s="51" t="s">
-        <v>761</v>
       </c>
       <c r="L149" s="57"/>
     </row>
@@ -19466,13 +19556,13 @@
         <v>497</v>
       </c>
       <c r="B150" s="46" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="C150" s="46" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="D150" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>448</v>
@@ -19493,7 +19583,7 @@
         <v>25</v>
       </c>
       <c r="K150" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L150" s="57"/>
     </row>
@@ -19502,16 +19592,16 @@
         <v>500</v>
       </c>
       <c r="B151" s="46" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="C151" s="46" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="D151" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="F151" s="53" t="s">
         <v>24</v>
@@ -19527,7 +19617,7 @@
         <v>25</v>
       </c>
       <c r="K151" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L151" s="57"/>
     </row>
@@ -19536,13 +19626,13 @@
         <v>651</v>
       </c>
       <c r="B152" s="51" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="C152" s="51" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="D152" s="49" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>448</v>
@@ -19559,7 +19649,7 @@
         <v>25</v>
       </c>
       <c r="K152" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L152" s="57"/>
     </row>
@@ -19568,16 +19658,16 @@
         <v>588</v>
       </c>
       <c r="B153" s="51" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="C153" s="51" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="D153" s="49" t="s">
         <v>526</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="F153" s="53" t="s">
         <v>119</v>
@@ -19591,7 +19681,7 @@
         <v>25</v>
       </c>
       <c r="K153" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L153" s="57"/>
     </row>
@@ -19600,10 +19690,10 @@
         <v>481</v>
       </c>
       <c r="B154" s="46" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="C154" s="46" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="D154" s="49" t="s">
         <v>526</v>
@@ -19625,7 +19715,7 @@
         <v>25</v>
       </c>
       <c r="K154" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L154" s="57"/>
     </row>
@@ -19634,13 +19724,13 @@
         <v>517</v>
       </c>
       <c r="B155" s="46" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="C155" s="46" t="s">
         <v>483</v>
       </c>
       <c r="D155" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>448</v>
@@ -19661,25 +19751,25 @@
         <v>138</v>
       </c>
       <c r="K155" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L155" s="57"/>
     </row>
     <row r="156" spans="1:12" ht="22.5" customHeight="1">
       <c r="A156" s="8" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="B156" s="51" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="C156" s="51" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="D156" s="49" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="E156" s="10" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="F156" s="53" t="s">
         <v>119</v>
@@ -19693,7 +19783,7 @@
         <v>25</v>
       </c>
       <c r="K156" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L156" s="57"/>
     </row>
@@ -19702,13 +19792,13 @@
         <v>514</v>
       </c>
       <c r="B157" s="46" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="C157" s="46" t="s">
         <v>483</v>
       </c>
       <c r="D157" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>448</v>
@@ -19727,7 +19817,7 @@
         <v>16</v>
       </c>
       <c r="K157" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L157" s="57"/>
     </row>
@@ -19736,13 +19826,13 @@
         <v>166</v>
       </c>
       <c r="B158" s="51" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="E158" s="10" t="s">
         <v>448</v>
@@ -19759,7 +19849,7 @@
         <v>74</v>
       </c>
       <c r="K158" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L158" s="57"/>
     </row>
@@ -19768,13 +19858,13 @@
         <v>618</v>
       </c>
       <c r="B159" s="51" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="C159" s="51" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="D159" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>448</v>
@@ -19791,7 +19881,7 @@
         <v>513</v>
       </c>
       <c r="K159" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L159" s="57"/>
     </row>
@@ -19800,10 +19890,10 @@
         <v>633</v>
       </c>
       <c r="B160" s="51" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="C160" s="51" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="D160" s="49" t="s">
         <v>526</v>
@@ -19823,7 +19913,7 @@
         <v>16</v>
       </c>
       <c r="K160" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L160" s="57"/>
     </row>
@@ -19832,10 +19922,10 @@
         <v>75</v>
       </c>
       <c r="B161" s="51" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="C161" s="51" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="D161" s="49" t="s">
         <v>540</v>
@@ -19855,7 +19945,7 @@
         <v>25</v>
       </c>
       <c r="K161" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L161" s="57"/>
     </row>
@@ -19864,13 +19954,13 @@
         <v>465</v>
       </c>
       <c r="B162" s="46" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="C162" s="46" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="E162" s="10" t="s">
         <v>448</v>
@@ -19891,17 +19981,17 @@
         <v>138</v>
       </c>
       <c r="K162" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L162" s="57"/>
     </row>
     <row r="163" spans="1:12" ht="22.5" customHeight="1">
       <c r="A163" s="46"/>
       <c r="B163" s="51" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="C163" s="51" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="D163" s="49" t="s">
         <v>540</v>
@@ -19921,7 +20011,7 @@
         <v>16</v>
       </c>
       <c r="K163" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L163" s="57"/>
     </row>
@@ -19930,13 +20020,13 @@
         <v>484</v>
       </c>
       <c r="B164" s="46" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="C164" s="46" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="E164" s="10" t="s">
         <v>448</v>
@@ -19957,7 +20047,7 @@
         <v>25</v>
       </c>
       <c r="K164" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L164" s="57"/>
     </row>
@@ -19966,13 +20056,13 @@
         <v>558</v>
       </c>
       <c r="B165" s="51" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>448</v>
@@ -19991,7 +20081,7 @@
         <v>25</v>
       </c>
       <c r="K165" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L165" s="57"/>
     </row>
@@ -20000,13 +20090,13 @@
         <v>615</v>
       </c>
       <c r="B166" s="51" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="C166" s="51" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="D166" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E166" s="10" t="s">
         <v>448</v>
@@ -20023,7 +20113,7 @@
         <v>513</v>
       </c>
       <c r="K166" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L166" s="57"/>
     </row>
@@ -20032,13 +20122,13 @@
         <v>648</v>
       </c>
       <c r="B167" s="51" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="C167" s="51" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>448</v>
@@ -20055,7 +20145,7 @@
         <v>25</v>
       </c>
       <c r="K167" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L167" s="57"/>
     </row>
@@ -20064,13 +20154,13 @@
         <v>612</v>
       </c>
       <c r="B168" s="51" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="C168" s="51" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="D168" s="49" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="E168" s="10" t="s">
         <v>448</v>
@@ -20087,7 +20177,7 @@
         <v>16</v>
       </c>
       <c r="K168" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L168" s="57"/>
     </row>
@@ -20096,19 +20186,19 @@
         <v>647</v>
       </c>
       <c r="B169" s="51" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="C169" s="51" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="D169" s="10" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F169" s="53" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="G169" s="54">
         <v>44725</v>
@@ -20119,7 +20209,7 @@
         <v>25</v>
       </c>
       <c r="K169" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L169" s="57"/>
     </row>
@@ -20128,10 +20218,10 @@
         <v>51</v>
       </c>
       <c r="B170" s="51" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="C170" s="51" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="D170" s="49" t="s">
         <v>733</v>
@@ -20151,7 +20241,7 @@
         <v>25</v>
       </c>
       <c r="K170" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L170" s="57"/>
     </row>
@@ -20160,10 +20250,10 @@
         <v>45</v>
       </c>
       <c r="B171" s="51" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="C171" s="51" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="D171" s="49" t="s">
         <v>733</v>
@@ -20183,7 +20273,7 @@
         <v>74</v>
       </c>
       <c r="K171" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L171" s="57"/>
     </row>
@@ -20192,13 +20282,13 @@
         <v>445</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="D172" s="62" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="E172" s="63"/>
       <c r="F172" s="64" t="s">
@@ -20212,10 +20302,10 @@
       </c>
       <c r="I172" s="67"/>
       <c r="J172" s="64" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="K172" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L172" s="57"/>
     </row>
@@ -20224,13 +20314,13 @@
         <v>468</v>
       </c>
       <c r="B173" s="46" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="C173" s="46" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="D173" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>448</v>
@@ -20251,7 +20341,7 @@
         <v>138</v>
       </c>
       <c r="K173" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L173" s="57"/>
     </row>
@@ -20260,16 +20350,16 @@
         <v>653</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="C174" s="51" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="D174" s="49" t="s">
         <v>733</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="F174" s="53" t="s">
         <v>119</v>
@@ -20283,7 +20373,7 @@
         <v>25</v>
       </c>
       <c r="K174" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L174" s="57"/>
     </row>
@@ -20292,10 +20382,10 @@
         <v>158</v>
       </c>
       <c r="B175" s="51" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="C175" s="51" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="D175" s="49" t="s">
         <v>733</v>
@@ -20315,17 +20405,17 @@
         <v>16</v>
       </c>
       <c r="K175" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L175" s="57"/>
     </row>
     <row r="176" spans="1:12" ht="22.5" customHeight="1">
       <c r="A176" s="46"/>
       <c r="B176" s="51" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="C176" s="51" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="D176" s="49" t="s">
         <v>733</v>
@@ -20349,7 +20439,7 @@
         <v>138</v>
       </c>
       <c r="K176" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L176" s="57"/>
     </row>
@@ -20358,16 +20448,16 @@
         <v>510</v>
       </c>
       <c r="B177" s="51" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="C177" s="51" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="D177" s="49" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="F177" s="53" t="s">
         <v>24</v>
@@ -20381,7 +20471,7 @@
         <v>25</v>
       </c>
       <c r="K177" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L177" s="57"/>
     </row>
@@ -20390,13 +20480,13 @@
         <v>110</v>
       </c>
       <c r="B178" s="51" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="C178" s="51" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="D178" s="10" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="E178" s="10" t="s">
         <v>738</v>
@@ -20411,20 +20501,20 @@
         <v>513</v>
       </c>
       <c r="K178" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L178" s="57"/>
     </row>
     <row r="179" spans="1:12" ht="22.5" customHeight="1">
       <c r="A179" s="46"/>
       <c r="B179" s="51" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="D179" s="10" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>448</v>
@@ -20445,20 +20535,20 @@
         <v>513</v>
       </c>
       <c r="K179" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L179" s="57"/>
     </row>
     <row r="180" spans="1:12" ht="22.5" customHeight="1">
       <c r="A180" s="46"/>
       <c r="B180" s="51" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="C180" s="51" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="D180" s="10" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="E180" s="10" t="s">
         <v>448</v>
@@ -20477,23 +20567,23 @@
         <v>25</v>
       </c>
       <c r="K180" s="51" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L180" s="57"/>
     </row>
     <row r="181" spans="1:12" ht="22.5" customHeight="1">
       <c r="A181" s="46"/>
       <c r="B181" s="46" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="C181" s="46" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="D181" s="10" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
       <c r="F181" s="53" t="s">
         <v>119</v>
@@ -20503,23 +20593,23 @@
       <c r="I181" s="56"/>
       <c r="J181" s="53"/>
       <c r="K181" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L181" s="57"/>
     </row>
     <row r="182" spans="1:12" ht="22.5" customHeight="1">
       <c r="A182" s="46"/>
       <c r="B182" s="46" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="C182" s="46" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="D182" s="10" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
       <c r="F182" s="53" t="s">
         <v>106</v>
@@ -20537,17 +20627,17 @@
         <v>74</v>
       </c>
       <c r="K182" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L182" s="57"/>
     </row>
     <row r="183" spans="1:12" ht="22.5" customHeight="1">
       <c r="A183" s="46"/>
       <c r="B183" s="46" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="C183" s="46" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="D183" s="49" t="s">
         <v>561</v>
@@ -20571,17 +20661,17 @@
         <v>25</v>
       </c>
       <c r="K183" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L183" s="57"/>
     </row>
     <row r="184" spans="1:12" ht="22.5" customHeight="1">
       <c r="A184" s="46"/>
       <c r="B184" s="46" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="C184" s="46" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="D184" s="49" t="s">
         <v>561</v>
@@ -20605,17 +20695,17 @@
         <v>25</v>
       </c>
       <c r="K184" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L184" s="57"/>
     </row>
     <row r="185" spans="1:12" ht="22.5" customHeight="1">
       <c r="A185" s="46"/>
       <c r="B185" s="46" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="C185" s="46" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="D185" s="49" t="s">
         <v>678</v>
@@ -20639,20 +20729,20 @@
         <v>25</v>
       </c>
       <c r="K185" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L185" s="57"/>
     </row>
     <row r="186" spans="1:12" ht="22.5" customHeight="1">
       <c r="A186" s="46"/>
       <c r="B186" s="46" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="C186" s="46" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="D186" s="49" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="E186" s="10" t="s">
         <v>448</v>
@@ -20673,17 +20763,17 @@
         <v>25</v>
       </c>
       <c r="K186" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L186" s="57"/>
     </row>
     <row r="187" spans="1:12" ht="22.5" customHeight="1">
       <c r="A187" s="46"/>
       <c r="B187" s="46" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="C187" s="46" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="D187" s="49" t="s">
         <v>561</v>
@@ -20703,17 +20793,17 @@
         <v>25</v>
       </c>
       <c r="K187" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L187" s="57"/>
     </row>
     <row r="188" spans="1:12" ht="22.5" customHeight="1">
       <c r="A188" s="46"/>
       <c r="B188" s="1" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="C188" s="46" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="D188" s="49" t="s">
         <v>561</v>
@@ -20733,20 +20823,20 @@
         <v>513</v>
       </c>
       <c r="K188" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L188" s="57"/>
     </row>
     <row r="189" spans="1:12" ht="22.5" customHeight="1">
       <c r="A189" s="46"/>
       <c r="B189" s="9" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="C189" s="46" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="D189" s="49" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>448</v>
@@ -20763,20 +20853,20 @@
         <v>74</v>
       </c>
       <c r="K189" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L189" s="57"/>
     </row>
     <row r="190" spans="1:12" ht="22.5" customHeight="1">
       <c r="A190" s="46"/>
       <c r="B190" s="9" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="C190" s="46" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="D190" s="49" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="E190" s="10" t="s">
         <v>448</v>
@@ -20793,20 +20883,20 @@
         <v>25</v>
       </c>
       <c r="K190" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L190" s="57"/>
     </row>
     <row r="191" spans="1:12" ht="22.5" customHeight="1">
       <c r="A191" s="46"/>
       <c r="B191" s="9" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="C191" s="46" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="D191" s="49" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>448</v>
@@ -20820,23 +20910,23 @@
       <c r="H191" s="55"/>
       <c r="I191" s="56"/>
       <c r="J191" s="53" t="s">
+        <v>777</v>
+      </c>
+      <c r="K191" s="46" t="s">
         <v>769</v>
-      </c>
-      <c r="K191" s="46" t="s">
-        <v>761</v>
       </c>
       <c r="L191" s="57"/>
     </row>
     <row r="192" spans="1:12" ht="22.5" customHeight="1">
       <c r="A192" s="46"/>
       <c r="B192" s="9" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="C192" s="46" t="s">
         <v>410</v>
       </c>
       <c r="D192" s="49" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E192" s="10" t="s">
         <v>448</v>
@@ -20853,17 +20943,17 @@
         <v>74</v>
       </c>
       <c r="K192" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L192" s="57"/>
     </row>
     <row r="193" spans="1:12" ht="22.5" customHeight="1">
       <c r="A193" s="46"/>
       <c r="B193" s="9" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="C193" s="46" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="D193" s="49" t="s">
         <v>733</v>
@@ -20883,17 +20973,17 @@
         <v>16</v>
       </c>
       <c r="K193" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L193" s="57"/>
     </row>
     <row r="194" spans="1:12" ht="22.5" customHeight="1">
       <c r="A194" s="46"/>
       <c r="B194" s="9" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="C194" s="46" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="D194" s="49" t="s">
         <v>733</v>
@@ -20913,17 +21003,17 @@
         <v>74</v>
       </c>
       <c r="K194" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L194" s="57"/>
     </row>
     <row r="195" spans="1:12" ht="22.5" customHeight="1">
       <c r="A195" s="46"/>
       <c r="B195" s="9" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="C195" s="46" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="D195" s="10"/>
       <c r="E195" s="10" t="s">
@@ -20941,17 +21031,17 @@
         <v>25</v>
       </c>
       <c r="K195" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L195" s="57"/>
     </row>
     <row r="196" spans="1:12" ht="22.5" customHeight="1">
       <c r="A196" s="46"/>
       <c r="B196" s="9" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="C196" s="46" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="D196" s="49" t="s">
         <v>718</v>
@@ -20968,23 +21058,23 @@
       <c r="H196" s="55"/>
       <c r="I196" s="56"/>
       <c r="J196" s="53" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="K196" s="46" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L196" s="57"/>
     </row>
     <row r="197" spans="1:12" ht="22.5" customHeight="1">
       <c r="A197" s="46"/>
       <c r="B197" s="9" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="C197" s="51" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="D197" s="49" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>448</v>
@@ -20996,19 +21086,21 @@
       <c r="H197" s="55"/>
       <c r="I197" s="56"/>
       <c r="J197" s="68"/>
-      <c r="K197" s="51"/>
+      <c r="K197" s="51" t="s">
+        <v>769</v>
+      </c>
       <c r="L197" s="57"/>
     </row>
     <row r="198" spans="1:12" ht="22.5" customHeight="1">
       <c r="A198" s="46"/>
       <c r="B198" s="9" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="C198" s="46" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="D198" s="49" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="E198" s="10" t="s">
         <v>448</v>
@@ -21020,19 +21112,21 @@
       <c r="H198" s="55"/>
       <c r="I198" s="56"/>
       <c r="J198" s="53"/>
-      <c r="K198" s="46"/>
+      <c r="K198" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L198" s="57"/>
     </row>
     <row r="199" spans="1:12" ht="22.5" customHeight="1">
       <c r="A199" s="46"/>
       <c r="B199" s="9" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="C199" s="46" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="D199" s="49" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>448</v>
@@ -21044,16 +21138,18 @@
       <c r="H199" s="55"/>
       <c r="I199" s="56"/>
       <c r="J199" s="53"/>
-      <c r="K199" s="46"/>
+      <c r="K199" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L199" s="46"/>
     </row>
     <row r="200" spans="1:12" ht="22.5" customHeight="1">
       <c r="A200" s="46"/>
       <c r="B200" s="9" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="C200" s="46" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="D200" s="10"/>
       <c r="E200" s="10" t="s">
@@ -21066,13 +21162,15 @@
       <c r="H200" s="55"/>
       <c r="I200" s="56"/>
       <c r="J200" s="53"/>
-      <c r="K200" s="46"/>
+      <c r="K200" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L200" s="46"/>
     </row>
     <row r="201" spans="1:12" ht="22.5" customHeight="1">
       <c r="A201" s="46"/>
       <c r="B201" s="9" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="C201" s="46"/>
       <c r="D201" s="10"/>
@@ -21086,22 +21184,24 @@
       <c r="H201" s="55"/>
       <c r="I201" s="56"/>
       <c r="J201" s="53"/>
-      <c r="K201" s="46"/>
+      <c r="K201" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L201" s="46"/>
     </row>
     <row r="202" spans="1:12" ht="22.5" customHeight="1">
       <c r="A202" s="46"/>
       <c r="B202" s="9" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="C202" s="46" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="D202" s="10" t="s">
         <v>537</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="F202" s="53" t="s">
         <v>119</v>
@@ -21110,19 +21210,21 @@
       <c r="H202" s="55"/>
       <c r="I202" s="56"/>
       <c r="J202" s="53"/>
-      <c r="K202" s="46"/>
+      <c r="K202" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L202" s="46"/>
     </row>
     <row r="203" spans="1:12" ht="22.5" customHeight="1">
       <c r="A203" s="46"/>
       <c r="B203" s="9" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="C203" s="46" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="D203" s="49" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>448</v>
@@ -21134,16 +21236,18 @@
       <c r="H203" s="55"/>
       <c r="I203" s="56"/>
       <c r="J203" s="53"/>
-      <c r="K203" s="46"/>
+      <c r="K203" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L203" s="46"/>
     </row>
     <row r="204" spans="1:12" ht="22.5" customHeight="1">
       <c r="A204" s="46"/>
       <c r="B204" s="9" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="C204" s="46" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="D204" s="49" t="s">
         <v>537</v>
@@ -21158,16 +21262,18 @@
       <c r="H204" s="55"/>
       <c r="I204" s="56"/>
       <c r="J204" s="53"/>
-      <c r="K204" s="46"/>
+      <c r="K204" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L204" s="46"/>
     </row>
     <row r="205" spans="1:12" ht="22.5" customHeight="1">
       <c r="A205" s="46"/>
       <c r="B205" s="9" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="C205" s="46" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="D205" s="10"/>
       <c r="E205" s="10" t="s">
@@ -21180,16 +21286,18 @@
       <c r="H205" s="55"/>
       <c r="I205" s="56"/>
       <c r="J205" s="53"/>
-      <c r="K205" s="46"/>
+      <c r="K205" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L205" s="46"/>
     </row>
     <row r="206" spans="1:12" ht="22.5" customHeight="1">
       <c r="A206" s="46"/>
       <c r="B206" s="9" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="C206" s="46" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="D206" s="49" t="s">
         <v>733</v>
@@ -21204,22 +21312,24 @@
       <c r="H206" s="55"/>
       <c r="I206" s="56"/>
       <c r="J206" s="53"/>
-      <c r="K206" s="46"/>
+      <c r="K206" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L206" s="46"/>
     </row>
     <row r="207" spans="1:12" ht="22.5" customHeight="1">
       <c r="A207" s="46"/>
       <c r="B207" s="9" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="C207" s="46" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="D207" s="49" t="s">
         <v>678</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="F207" s="53" t="s">
         <v>119</v>
@@ -21228,16 +21338,18 @@
       <c r="H207" s="55"/>
       <c r="I207" s="56"/>
       <c r="J207" s="53"/>
-      <c r="K207" s="46"/>
+      <c r="K207" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L207" s="46"/>
     </row>
     <row r="208" spans="1:12" ht="22.5" customHeight="1">
       <c r="A208" s="46"/>
       <c r="B208" s="9" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="C208" s="46" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="D208" s="49" t="s">
         <v>561</v>
@@ -21250,16 +21362,18 @@
       <c r="H208" s="55"/>
       <c r="I208" s="56"/>
       <c r="J208" s="53"/>
-      <c r="K208" s="46"/>
+      <c r="K208" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L208" s="46"/>
     </row>
     <row r="209" spans="1:12" ht="22.5" customHeight="1">
       <c r="A209" s="46"/>
       <c r="B209" s="9" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="C209" s="46" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="D209" s="49" t="s">
         <v>526</v>
@@ -21272,16 +21386,18 @@
       <c r="H209" s="55"/>
       <c r="I209" s="56"/>
       <c r="J209" s="53"/>
-      <c r="K209" s="46"/>
+      <c r="K209" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L209" s="46"/>
     </row>
     <row r="210" spans="1:12" ht="22.5" customHeight="1">
       <c r="A210" s="46"/>
       <c r="B210" s="9" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="C210" s="46" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="D210" s="49" t="s">
         <v>723</v>
@@ -21294,22 +21410,24 @@
       <c r="H210" s="55"/>
       <c r="I210" s="56"/>
       <c r="J210" s="53"/>
-      <c r="K210" s="46"/>
+      <c r="K210" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L210" s="46"/>
     </row>
     <row r="211" spans="1:12" ht="22.5" customHeight="1">
       <c r="A211" s="46"/>
       <c r="B211" s="9" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="C211" s="46" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="D211" s="49" t="s">
         <v>561</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="F211" s="53" t="s">
         <v>449</v>
@@ -21318,16 +21436,18 @@
       <c r="H211" s="55"/>
       <c r="I211" s="56"/>
       <c r="J211" s="53"/>
-      <c r="K211" s="46"/>
+      <c r="K211" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L211" s="46"/>
     </row>
     <row r="212" spans="1:12" ht="22.5" customHeight="1">
       <c r="A212" s="46"/>
       <c r="B212" s="9" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="C212" s="46" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="D212" s="10"/>
       <c r="E212" s="10" t="s">
@@ -21338,33 +21458,41 @@
       <c r="H212" s="55"/>
       <c r="I212" s="56"/>
       <c r="J212" s="53"/>
-      <c r="K212" s="46"/>
+      <c r="K212" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L212" s="46"/>
     </row>
     <row r="213" spans="1:12" ht="22.5" customHeight="1">
       <c r="A213" s="46"/>
-      <c r="B213" s="9"/>
-      <c r="C213" s="46" t="s">
-        <v>1226</v>
-      </c>
+      <c r="B213" s="9" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C213" s="46"/>
       <c r="D213" s="49" t="s">
-        <v>815</v>
+        <v>561</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="F213" s="53"/>
-      <c r="G213" s="54"/>
+      <c r="F213" s="53" t="s">
+        <v>480</v>
+      </c>
+      <c r="G213" s="54">
+        <v>46100</v>
+      </c>
       <c r="H213" s="55"/>
       <c r="I213" s="56"/>
       <c r="J213" s="53"/>
-      <c r="K213" s="46"/>
+      <c r="K213" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L213" s="46"/>
     </row>
     <row r="214" spans="1:12" ht="22.5" customHeight="1">
       <c r="A214" s="46"/>
       <c r="B214" s="9" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="C214" s="46"/>
       <c r="D214" s="10"/>
@@ -21376,16 +21504,18 @@
       <c r="H214" s="55"/>
       <c r="I214" s="56"/>
       <c r="J214" s="53"/>
-      <c r="K214" s="46"/>
+      <c r="K214" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L214" s="46"/>
     </row>
     <row r="215" spans="1:12" ht="22.5" customHeight="1">
       <c r="A215" s="46"/>
       <c r="B215" s="9" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="C215" s="46" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="D215" s="49" t="s">
         <v>678</v>
@@ -21400,19 +21530,21 @@
       <c r="H215" s="55"/>
       <c r="I215" s="56"/>
       <c r="J215" s="53"/>
-      <c r="K215" s="46"/>
+      <c r="K215" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L215" s="46"/>
     </row>
     <row r="216" spans="1:12" ht="22.5" customHeight="1">
       <c r="A216" s="46"/>
       <c r="B216" s="9" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="C216" s="46" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="D216" s="49" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="E216" s="10" t="s">
         <v>448</v>
@@ -21422,7 +21554,9 @@
       <c r="H216" s="55"/>
       <c r="I216" s="56"/>
       <c r="J216" s="53"/>
-      <c r="K216" s="46"/>
+      <c r="K216" s="46" t="s">
+        <v>769</v>
+      </c>
       <c r="L216" s="46"/>
     </row>
   </sheetData>
@@ -21707,10 +21841,10 @@
         <v>481</v>
       </c>
       <c r="B2" s="69" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="D2" s="70"/>
       <c r="E2" s="70"/>
@@ -21730,7 +21864,7 @@
         <v>25</v>
       </c>
       <c r="K2" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="21" customHeight="1">
@@ -21738,15 +21872,15 @@
         <v>484</v>
       </c>
       <c r="B3" s="77" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="C3" s="76" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="D3" s="70"/>
       <c r="E3" s="70"/>
       <c r="F3" s="71" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G3" s="78">
         <v>45951</v>
@@ -21759,7 +21893,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -21767,15 +21901,15 @@
         <v>488</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="C4" s="82" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="D4" s="83"/>
       <c r="E4" s="70"/>
       <c r="F4" s="84" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G4" s="85">
         <v>45951</v>
@@ -21788,7 +21922,7 @@
         <v>25</v>
       </c>
       <c r="K4" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -21796,15 +21930,15 @@
         <v>491</v>
       </c>
       <c r="B5" s="81" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="C5" s="82" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="D5" s="83"/>
       <c r="E5" s="70"/>
       <c r="F5" s="89" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G5" s="85">
         <v>45954</v>
@@ -21814,10 +21948,10 @@
       </c>
       <c r="I5" s="87"/>
       <c r="J5" s="90" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="K5" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -21825,15 +21959,15 @@
         <v>494</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="C6" s="82" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="D6" s="83"/>
       <c r="E6" s="70"/>
       <c r="F6" s="89" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G6" s="85">
         <v>45897</v>
@@ -21846,7 +21980,7 @@
         <v>74</v>
       </c>
       <c r="K6" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -21854,10 +21988,10 @@
         <v>497</v>
       </c>
       <c r="B7" s="77" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="C7" s="76" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="D7" s="70"/>
       <c r="E7" s="70"/>
@@ -21873,7 +22007,7 @@
         <v>25</v>
       </c>
       <c r="K7" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -21881,10 +22015,10 @@
         <v>500</v>
       </c>
       <c r="B8" s="77" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="D8" s="70"/>
       <c r="E8" s="70"/>
@@ -21902,7 +22036,7 @@
         <v>74</v>
       </c>
       <c r="K8" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -21910,10 +22044,10 @@
         <v>503</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="C9" s="82" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="D9" s="83"/>
       <c r="E9" s="70"/>
@@ -21931,7 +22065,7 @@
         <v>74</v>
       </c>
       <c r="K9" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -21939,10 +22073,10 @@
         <v>506</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="C10" s="76" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
@@ -21960,7 +22094,7 @@
         <v>25</v>
       </c>
       <c r="K10" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -21968,10 +22102,10 @@
         <v>514</v>
       </c>
       <c r="B11" s="81" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="C11" s="82" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="D11" s="83"/>
       <c r="E11" s="70"/>
@@ -21989,7 +22123,7 @@
         <v>74</v>
       </c>
       <c r="K11" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -21997,10 +22131,10 @@
         <v>517</v>
       </c>
       <c r="B12" s="81" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="C12" s="82" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="D12" s="83"/>
       <c r="E12" s="70"/>
@@ -22018,7 +22152,7 @@
         <v>74</v>
       </c>
       <c r="K12" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -22026,10 +22160,10 @@
         <v>520</v>
       </c>
       <c r="B13" s="77" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
@@ -22047,7 +22181,7 @@
         <v>25</v>
       </c>
       <c r="K13" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -22055,10 +22189,10 @@
         <v>523</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="C14" s="82" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="D14" s="83"/>
       <c r="E14" s="70"/>
@@ -22074,7 +22208,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -22082,10 +22216,10 @@
         <v>527</v>
       </c>
       <c r="B15" s="99" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="C15" s="82" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="D15" s="83"/>
       <c r="E15" s="70"/>
@@ -22103,7 +22237,7 @@
         <v>74</v>
       </c>
       <c r="K15" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
@@ -22111,15 +22245,15 @@
         <v>531</v>
       </c>
       <c r="B16" s="77" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="C16" s="76" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
       <c r="F16" s="71" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G16" s="93"/>
       <c r="H16" s="73">
@@ -22130,7 +22264,7 @@
         <v>25</v>
       </c>
       <c r="K16" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
@@ -22138,10 +22272,10 @@
         <v>534</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="C17" s="76" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="D17" s="70"/>
       <c r="E17" s="70"/>
@@ -22161,7 +22295,7 @@
         <v>25</v>
       </c>
       <c r="K17" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="22.5" customHeight="1">
@@ -22169,10 +22303,10 @@
         <v>538</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="70"/>
@@ -22192,7 +22326,7 @@
         <v>74</v>
       </c>
       <c r="K18" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="22.5" customHeight="1">
@@ -22200,10 +22334,10 @@
         <v>541</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="11"/>
@@ -22223,7 +22357,7 @@
         <v>513</v>
       </c>
       <c r="K19" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="22.5" customHeight="1">
@@ -22231,10 +22365,10 @@
         <v>544</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -22252,7 +22386,7 @@
         <v>25</v>
       </c>
       <c r="K20" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="22.5" customHeight="1">
@@ -22260,10 +22394,10 @@
         <v>547</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="C21" s="76" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -22281,7 +22415,7 @@
         <v>745</v>
       </c>
       <c r="K21" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="22.5" customHeight="1">
@@ -22289,10 +22423,10 @@
         <v>552</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="C22" s="76" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="11"/>
@@ -22310,7 +22444,7 @@
         <v>551</v>
       </c>
       <c r="K22" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="22.5" customHeight="1">
@@ -22318,10 +22452,10 @@
         <v>555</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="C23" s="76" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="11"/>
@@ -22339,7 +22473,7 @@
         <v>551</v>
       </c>
       <c r="K23" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="22.5" customHeight="1">
@@ -22347,10 +22481,10 @@
         <v>558</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -22368,7 +22502,7 @@
         <v>551</v>
       </c>
       <c r="K24" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="22.5" customHeight="1">
@@ -22376,15 +22510,15 @@
         <v>558</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="11"/>
       <c r="F25" s="3" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="G25" s="12">
         <v>46068</v>
@@ -22399,7 +22533,7 @@
         <v>513</v>
       </c>
       <c r="K25" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -22407,10 +22541,10 @@
         <v>558</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="11"/>
@@ -22430,7 +22564,7 @@
         <v>551</v>
       </c>
       <c r="K26" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="22.5" customHeight="1">
@@ -22438,10 +22572,10 @@
         <v>562</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -22459,7 +22593,7 @@
         <v>513</v>
       </c>
       <c r="K27" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="22.5" customHeight="1">
@@ -22467,10 +22601,10 @@
         <v>565</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -22488,7 +22622,7 @@
         <v>513</v>
       </c>
       <c r="K28" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="22.5" customHeight="1">
@@ -22496,10 +22630,10 @@
         <v>568</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="11"/>
@@ -22515,7 +22649,7 @@
       <c r="I29" s="45"/>
       <c r="J29" s="14"/>
       <c r="K29" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
   </sheetData>
@@ -22638,17 +22772,17 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="D2" s="101"/>
       <c r="E2" s="101" t="s">
         <v>448</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G2" s="65">
         <v>46083</v>
@@ -22656,10 +22790,10 @@
       <c r="H2" s="66"/>
       <c r="I2" s="67"/>
       <c r="J2" s="64" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -22667,10 +22801,10 @@
         <v>451</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
@@ -22689,10 +22823,10 @@
         <v>0.8</v>
       </c>
       <c r="J3" s="53" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -22700,14 +22834,14 @@
         <v>454</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>449</v>
@@ -22718,10 +22852,10 @@
       <c r="H4" s="61"/>
       <c r="I4" s="56"/>
       <c r="J4" s="53" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -22729,10 +22863,10 @@
         <v>457</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
@@ -22754,18 +22888,18 @@
         <v>688</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
@@ -22783,7 +22917,7 @@
         <v>688</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -22791,10 +22925,10 @@
         <v>459</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
@@ -22809,10 +22943,10 @@
       <c r="H7" s="61"/>
       <c r="I7" s="56"/>
       <c r="J7" s="53" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -22820,10 +22954,10 @@
         <v>462</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
@@ -22841,7 +22975,7 @@
         <v>25</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -22849,14 +22983,14 @@
         <v>465</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="F9" s="53" t="s">
         <v>40</v>
@@ -22870,7 +23004,7 @@
         <v>659</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -22878,10 +23012,10 @@
         <v>468</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
@@ -22899,7 +23033,7 @@
         <v>659</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -22907,14 +23041,14 @@
         <v>471</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="F11" s="53" t="s">
         <v>32</v>
@@ -22928,7 +23062,7 @@
         <v>659</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -22936,10 +23070,10 @@
         <v>474</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
@@ -22955,7 +23089,7 @@
         <v>659</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -22963,10 +23097,10 @@
         <v>477</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
@@ -22988,7 +23122,7 @@
         <v>659</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -22996,10 +23130,10 @@
         <v>481</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10" t="s">
@@ -23016,10 +23150,10 @@
         <v>0.8</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -23027,10 +23161,10 @@
         <v>484</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10" t="s">
@@ -23050,10 +23184,10 @@
         <v>488</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -23073,7 +23207,7 @@
         <v>659</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
@@ -23081,10 +23215,10 @@
         <v>491</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10" t="s">
@@ -23104,10 +23238,10 @@
         <v>494</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10" t="s">
@@ -23127,10 +23261,10 @@
         <v>497</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10" t="s">
@@ -23150,10 +23284,10 @@
         <v>500</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10" t="s">
@@ -23288,13 +23422,13 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="D2" s="62" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="E2" s="63"/>
       <c r="F2" s="64" t="s">
@@ -23310,10 +23444,10 @@
         <v>0.75</v>
       </c>
       <c r="J2" s="64" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="K2" s="104" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -23321,10 +23455,10 @@
         <v>471</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
       <c r="C3" s="82" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
       <c r="D3" s="83"/>
       <c r="E3" s="83"/>
@@ -23340,7 +23474,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -23628,10 +23762,10 @@
         <v>474</v>
       </c>
       <c r="B14" s="107" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
       <c r="C14" s="108" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="D14" s="109"/>
       <c r="E14" s="109"/>
@@ -23649,7 +23783,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -23939,10 +24073,10 @@
         <v>477</v>
       </c>
       <c r="B25" s="117" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
       <c r="C25" s="118" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
       <c r="D25" s="119"/>
       <c r="E25" s="119"/>
@@ -23960,7 +24094,7 @@
         <v>25</v>
       </c>
       <c r="K25" s="125" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -24258,10 +24392,10 @@
         <v>481</v>
       </c>
       <c r="B36" s="126" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
       <c r="C36" s="127" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
       <c r="D36" s="128"/>
       <c r="E36" s="128"/>
@@ -24277,7 +24411,7 @@
         <v>25</v>
       </c>
       <c r="K36" s="134" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="22.5" customHeight="1">
@@ -24409,7 +24543,7 @@
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
       <c r="D42" s="17"/>
       <c r="E42" s="18"/>
@@ -24484,10 +24618,10 @@
         <v>484</v>
       </c>
       <c r="B46" s="107" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="C46" s="108" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="D46" s="109"/>
       <c r="E46" s="109"/>
@@ -24505,7 +24639,7 @@
         <v>74</v>
       </c>
       <c r="K46" s="115" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="22.5" customHeight="1">
@@ -24705,10 +24839,10 @@
         <v>488</v>
       </c>
       <c r="B57" s="135" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="C57" s="136" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="D57" s="137"/>
       <c r="E57" s="137"/>
@@ -24726,7 +24860,7 @@
         <v>25</v>
       </c>
       <c r="K57" s="143" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="22.5" customHeight="1">
@@ -24944,10 +25078,10 @@
         <v>491</v>
       </c>
       <c r="B68" s="107" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="C68" s="108" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="D68" s="109"/>
       <c r="E68" s="109"/>
@@ -24963,7 +25097,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="115" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="22.5" customHeight="1">
@@ -25179,15 +25313,15 @@
         <v>494</v>
       </c>
       <c r="B79" s="126" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="C79" s="127" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="D79" s="128"/>
       <c r="E79" s="128"/>
       <c r="F79" s="146" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G79" s="147">
         <v>45954</v>
@@ -25197,10 +25331,10 @@
       </c>
       <c r="I79" s="132"/>
       <c r="J79" s="148" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="K79" s="134" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="22.5" customHeight="1">
@@ -25250,10 +25384,10 @@
         <v>497</v>
       </c>
       <c r="B82" s="117" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="C82" s="118" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
       <c r="D82" s="119"/>
       <c r="E82" s="119"/>
@@ -25271,7 +25405,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="125" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="22.5" customHeight="1">
@@ -25279,15 +25413,15 @@
         <v>500</v>
       </c>
       <c r="B83" s="126" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="C83" s="127" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="D83" s="128"/>
       <c r="E83" s="128"/>
       <c r="F83" s="146" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G83" s="147">
         <v>45897</v>
@@ -25300,7 +25434,7 @@
         <v>74</v>
       </c>
       <c r="K83" s="134" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22.5" customHeight="1">
@@ -25308,13 +25442,13 @@
         <v>451</v>
       </c>
       <c r="B84" s="151" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
       <c r="C84" s="151" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
       <c r="D84" s="152" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="E84" s="153"/>
       <c r="F84" s="154" t="s">
@@ -25333,7 +25467,7 @@
         <v>25</v>
       </c>
       <c r="K84" s="158" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="22.5" customHeight="1">
@@ -25341,10 +25475,10 @@
         <v>503</v>
       </c>
       <c r="B85" s="107" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
       <c r="C85" s="108" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="D85" s="109"/>
       <c r="E85" s="109"/>
@@ -25362,7 +25496,7 @@
         <v>74</v>
       </c>
       <c r="K85" s="115" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="22.5" customHeight="1">
@@ -25370,10 +25504,10 @@
         <v>506</v>
       </c>
       <c r="B86" s="135" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="C86" s="136" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="D86" s="137"/>
       <c r="E86" s="137"/>
@@ -25391,7 +25525,7 @@
         <v>74</v>
       </c>
       <c r="K86" s="143" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="22.5" customHeight="1">
@@ -25399,10 +25533,10 @@
         <v>510</v>
       </c>
       <c r="B87" s="108" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
       <c r="C87" s="108" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
       <c r="D87" s="109"/>
       <c r="E87" s="109"/>
@@ -25415,10 +25549,10 @@
       </c>
       <c r="I87" s="113"/>
       <c r="J87" s="160" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="K87" s="115" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="22.5" customHeight="1">
@@ -25426,10 +25560,10 @@
         <v>514</v>
       </c>
       <c r="B88" s="135" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
       <c r="C88" s="136" t="s">
-        <v>1350</v>
+        <v>1358</v>
       </c>
       <c r="D88" s="137"/>
       <c r="E88" s="137"/>
@@ -25447,7 +25581,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="143" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="22.5" customHeight="1">
@@ -25455,10 +25589,10 @@
         <v>517</v>
       </c>
       <c r="B89" s="117" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
       <c r="C89" s="118" t="s">
-        <v>1352</v>
+        <v>1360</v>
       </c>
       <c r="D89" s="70"/>
       <c r="E89" s="70"/>
@@ -25476,7 +25610,7 @@
         <v>74</v>
       </c>
       <c r="K89" s="125" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="22.5" customHeight="1">
@@ -25484,10 +25618,10 @@
         <v>520</v>
       </c>
       <c r="B90" s="135" t="s">
-        <v>1353</v>
+        <v>1361</v>
       </c>
       <c r="C90" s="136" t="s">
-        <v>1354</v>
+        <v>1362</v>
       </c>
       <c r="D90" s="83"/>
       <c r="E90" s="83"/>
@@ -25503,7 +25637,7 @@
         <v>74</v>
       </c>
       <c r="K90" s="143" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="22.5" customHeight="1">
@@ -25511,10 +25645,10 @@
         <v>523</v>
       </c>
       <c r="B91" s="77" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="C91" s="76" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="D91" s="70"/>
       <c r="E91" s="70"/>
@@ -25530,7 +25664,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="125" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22.5" customHeight="1">
@@ -25538,10 +25672,10 @@
         <v>527</v>
       </c>
       <c r="B92" s="81" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="C92" s="82" t="s">
-        <v>1356</v>
+        <v>1364</v>
       </c>
       <c r="D92" s="83"/>
       <c r="E92" s="83"/>
@@ -25559,7 +25693,7 @@
         <v>74</v>
       </c>
       <c r="K92" s="143" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="22.5" customHeight="1">
@@ -25567,10 +25701,10 @@
         <v>531</v>
       </c>
       <c r="B93" s="77" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
       <c r="C93" s="76" t="s">
-        <v>1358</v>
+        <v>1366</v>
       </c>
       <c r="D93" s="70"/>
       <c r="E93" s="70"/>
@@ -25586,7 +25720,7 @@
         <v>74</v>
       </c>
       <c r="K93" s="125" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="22.5" customHeight="1">
@@ -25594,10 +25728,10 @@
         <v>534</v>
       </c>
       <c r="B94" s="81" t="s">
-        <v>1359</v>
+        <v>1367</v>
       </c>
       <c r="C94" s="82" t="s">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="D94" s="83"/>
       <c r="E94" s="83"/>
@@ -25613,7 +25747,7 @@
         <v>74</v>
       </c>
       <c r="K94" s="143" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="22.5" customHeight="1">
@@ -25621,13 +25755,13 @@
         <v>454</v>
       </c>
       <c r="B95" s="104" t="s">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="C95" s="104" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
       <c r="D95" s="62" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E95" s="63"/>
       <c r="F95" s="64" t="s">
@@ -25646,7 +25780,7 @@
         <v>16</v>
       </c>
       <c r="K95" s="158" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="22.5" customHeight="1">
@@ -25654,10 +25788,10 @@
         <v>538</v>
       </c>
       <c r="B96" s="77" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="C96" s="76" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="D96" s="70"/>
       <c r="E96" s="70"/>
@@ -25673,7 +25807,7 @@
         <v>74</v>
       </c>
       <c r="K96" s="125" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="22.5" customHeight="1">
@@ -25681,10 +25815,10 @@
         <v>541</v>
       </c>
       <c r="B97" s="81" t="s">
-        <v>1365</v>
+        <v>1373</v>
       </c>
       <c r="C97" s="82" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="D97" s="83"/>
       <c r="E97" s="83"/>
@@ -25700,7 +25834,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="22.5" customHeight="1">
@@ -25708,10 +25842,10 @@
         <v>544</v>
       </c>
       <c r="B98" s="77" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="C98" s="76" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="D98" s="70"/>
       <c r="E98" s="70"/>
@@ -25729,7 +25863,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="22.5" customHeight="1">
@@ -25737,10 +25871,10 @@
         <v>547</v>
       </c>
       <c r="B99" s="81" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="C99" s="82" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="D99" s="83"/>
       <c r="E99" s="83"/>
@@ -25758,7 +25892,7 @@
         <v>74</v>
       </c>
       <c r="K99" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="22.5" customHeight="1">
@@ -25766,10 +25900,10 @@
         <v>552</v>
       </c>
       <c r="B100" s="77" t="s">
-        <v>1366</v>
+        <v>1374</v>
       </c>
       <c r="C100" s="76" t="s">
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="D100" s="70"/>
       <c r="E100" s="70"/>
@@ -25785,7 +25919,7 @@
         <v>74</v>
       </c>
       <c r="K100" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="22.5" customHeight="1">
@@ -25793,10 +25927,10 @@
         <v>555</v>
       </c>
       <c r="B101" s="81" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="C101" s="82" t="s">
-        <v>1369</v>
+        <v>1377</v>
       </c>
       <c r="D101" s="83"/>
       <c r="E101" s="83"/>
@@ -25812,7 +25946,7 @@
         <v>74</v>
       </c>
       <c r="K101" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="22.5" customHeight="1">
@@ -25820,10 +25954,10 @@
         <v>558</v>
       </c>
       <c r="B102" s="77" t="s">
-        <v>1370</v>
+        <v>1378</v>
       </c>
       <c r="C102" s="76" t="s">
-        <v>1371</v>
+        <v>1379</v>
       </c>
       <c r="D102" s="70"/>
       <c r="E102" s="70"/>
@@ -25839,7 +25973,7 @@
         <v>74</v>
       </c>
       <c r="K102" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="22.5" customHeight="1">
@@ -25847,10 +25981,10 @@
         <v>562</v>
       </c>
       <c r="B103" s="81" t="s">
-        <v>1372</v>
+        <v>1380</v>
       </c>
       <c r="C103" s="82" t="s">
-        <v>1373</v>
+        <v>1381</v>
       </c>
       <c r="D103" s="83"/>
       <c r="E103" s="83"/>
@@ -25866,7 +26000,7 @@
         <v>74</v>
       </c>
       <c r="K103" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="22.5" customHeight="1">
@@ -25874,10 +26008,10 @@
         <v>565</v>
       </c>
       <c r="B104" s="76" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="C104" s="76" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="D104" s="70"/>
       <c r="E104" s="70"/>
@@ -25895,7 +26029,7 @@
         <v>25</v>
       </c>
       <c r="K104" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="22.5" customHeight="1">
@@ -25903,10 +26037,10 @@
         <v>568</v>
       </c>
       <c r="B105" s="81" t="s">
-        <v>1374</v>
+        <v>1382</v>
       </c>
       <c r="C105" s="82" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="D105" s="83"/>
       <c r="E105" s="83"/>
@@ -25924,7 +26058,7 @@
         <v>74</v>
       </c>
       <c r="K105" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="22.5" customHeight="1">
@@ -25932,10 +26066,10 @@
         <v>457</v>
       </c>
       <c r="B106" s="104" t="s">
-        <v>1375</v>
+        <v>1383</v>
       </c>
       <c r="C106" s="104" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="D106" s="62" t="s">
         <v>540</v>
@@ -25954,10 +26088,10 @@
         <v>0.9</v>
       </c>
       <c r="J106" s="64" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="K106" s="104" t="s">
-        <v>1377</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="22.5" customHeight="1">
@@ -25965,10 +26099,10 @@
         <v>571</v>
       </c>
       <c r="B107" s="77" t="s">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="C107" s="76" t="s">
-        <v>1379</v>
+        <v>1387</v>
       </c>
       <c r="D107" s="70"/>
       <c r="E107" s="70"/>
@@ -25984,7 +26118,7 @@
         <v>25</v>
       </c>
       <c r="K107" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="22.5" customHeight="1">
@@ -25992,10 +26126,10 @@
         <v>574</v>
       </c>
       <c r="B108" s="81" t="s">
-        <v>1380</v>
+        <v>1388</v>
       </c>
       <c r="C108" s="82" t="s">
-        <v>1381</v>
+        <v>1389</v>
       </c>
       <c r="D108" s="83"/>
       <c r="E108" s="83"/>
@@ -26011,7 +26145,7 @@
         <v>74</v>
       </c>
       <c r="K108" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="22.5" customHeight="1">
@@ -26019,10 +26153,10 @@
         <v>576</v>
       </c>
       <c r="B109" s="77" t="s">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="C109" s="76" t="s">
-        <v>1383</v>
+        <v>1391</v>
       </c>
       <c r="D109" s="70"/>
       <c r="E109" s="70"/>
@@ -26040,7 +26174,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="22.5" customHeight="1">
@@ -26048,10 +26182,10 @@
         <v>579</v>
       </c>
       <c r="B110" s="81" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="C110" s="82" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="D110" s="83"/>
       <c r="E110" s="83"/>
@@ -26067,7 +26201,7 @@
         <v>74</v>
       </c>
       <c r="K110" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="22.5" customHeight="1">
@@ -26075,10 +26209,10 @@
         <v>582</v>
       </c>
       <c r="B111" s="77" t="s">
-        <v>1386</v>
+        <v>1394</v>
       </c>
       <c r="C111" s="76" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="D111" s="70"/>
       <c r="E111" s="70"/>
@@ -26094,7 +26228,7 @@
         <v>74</v>
       </c>
       <c r="K111" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="22.5" customHeight="1">
@@ -26102,10 +26236,10 @@
         <v>585</v>
       </c>
       <c r="B112" s="81" t="s">
-        <v>1388</v>
+        <v>1396</v>
       </c>
       <c r="C112" s="82" t="s">
-        <v>1389</v>
+        <v>1397</v>
       </c>
       <c r="D112" s="83"/>
       <c r="E112" s="83"/>
@@ -26121,7 +26255,7 @@
         <v>74</v>
       </c>
       <c r="K112" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="22.5" customHeight="1">
@@ -26129,10 +26263,10 @@
         <v>588</v>
       </c>
       <c r="B113" s="77" t="s">
-        <v>1390</v>
+        <v>1398</v>
       </c>
       <c r="C113" s="76" t="s">
-        <v>1391</v>
+        <v>1399</v>
       </c>
       <c r="D113" s="70"/>
       <c r="E113" s="70"/>
@@ -26148,7 +26282,7 @@
         <v>74</v>
       </c>
       <c r="K113" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="22.5" customHeight="1">
@@ -26156,10 +26290,10 @@
         <v>591</v>
       </c>
       <c r="B114" s="81" t="s">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="C114" s="82" t="s">
-        <v>1393</v>
+        <v>1401</v>
       </c>
       <c r="D114" s="83"/>
       <c r="E114" s="83"/>
@@ -26175,7 +26309,7 @@
         <v>74</v>
       </c>
       <c r="K114" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="22.5" customHeight="1">
@@ -26183,7 +26317,7 @@
         <v>594</v>
       </c>
       <c r="B115" s="77" t="s">
-        <v>1394</v>
+        <v>1402</v>
       </c>
       <c r="C115" s="76" t="s">
         <v>391</v>
@@ -26202,7 +26336,7 @@
         <v>74</v>
       </c>
       <c r="K115" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="22.5" customHeight="1">
@@ -26210,10 +26344,10 @@
         <v>597</v>
       </c>
       <c r="B116" s="81" t="s">
-        <v>1395</v>
+        <v>1403</v>
       </c>
       <c r="C116" s="82" t="s">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="D116" s="83"/>
       <c r="E116" s="83"/>
@@ -26229,25 +26363,25 @@
         <v>74</v>
       </c>
       <c r="K116" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="22.5" customHeight="1">
       <c r="A117" s="8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B117" s="104" t="s">
-        <v>1397</v>
+        <v>1405</v>
       </c>
       <c r="C117" s="104" t="s">
-        <v>1398</v>
+        <v>1406</v>
       </c>
       <c r="D117" s="62" t="s">
         <v>540</v>
       </c>
       <c r="E117" s="63"/>
       <c r="F117" s="64" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="G117" s="103">
         <v>45976</v>
@@ -26259,10 +26393,10 @@
         <v>0.85</v>
       </c>
       <c r="J117" s="64" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="K117" s="104" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="22.5" customHeight="1">
@@ -26270,10 +26404,10 @@
         <v>600</v>
       </c>
       <c r="B118" s="77" t="s">
-        <v>1399</v>
+        <v>1407</v>
       </c>
       <c r="C118" s="76" t="s">
-        <v>1400</v>
+        <v>1408</v>
       </c>
       <c r="D118" s="70"/>
       <c r="E118" s="70"/>
@@ -26289,7 +26423,7 @@
         <v>74</v>
       </c>
       <c r="K118" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="22.5" customHeight="1">
@@ -26297,10 +26431,10 @@
         <v>603</v>
       </c>
       <c r="B119" s="81" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="C119" s="82" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="D119" s="83"/>
       <c r="E119" s="83"/>
@@ -26318,7 +26452,7 @@
         <v>74</v>
       </c>
       <c r="K119" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="22.5" customHeight="1">
@@ -26326,10 +26460,10 @@
         <v>606</v>
       </c>
       <c r="B120" s="77" t="s">
-        <v>1401</v>
+        <v>1409</v>
       </c>
       <c r="C120" s="76" t="s">
-        <v>1402</v>
+        <v>1410</v>
       </c>
       <c r="D120" s="70"/>
       <c r="E120" s="70"/>
@@ -26347,7 +26481,7 @@
         <v>74</v>
       </c>
       <c r="K120" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="22.5" customHeight="1">
@@ -26355,10 +26489,10 @@
         <v>609</v>
       </c>
       <c r="B121" s="81" t="s">
-        <v>1403</v>
+        <v>1411</v>
       </c>
       <c r="C121" s="82" t="s">
-        <v>1404</v>
+        <v>1412</v>
       </c>
       <c r="D121" s="83"/>
       <c r="E121" s="83"/>
@@ -26374,7 +26508,7 @@
         <v>74</v>
       </c>
       <c r="K121" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="22.5" customHeight="1">
@@ -26382,10 +26516,10 @@
         <v>612</v>
       </c>
       <c r="B122" s="77" t="s">
-        <v>1405</v>
+        <v>1413</v>
       </c>
       <c r="C122" s="76" t="s">
-        <v>1406</v>
+        <v>1414</v>
       </c>
       <c r="D122" s="70"/>
       <c r="E122" s="70"/>
@@ -26401,7 +26535,7 @@
         <v>74</v>
       </c>
       <c r="K122" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="22.5" customHeight="1">
@@ -26409,10 +26543,10 @@
         <v>615</v>
       </c>
       <c r="B123" s="81" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="C123" s="82" t="s">
-        <v>1408</v>
+        <v>1416</v>
       </c>
       <c r="D123" s="83"/>
       <c r="E123" s="83"/>
@@ -26428,7 +26562,7 @@
         <v>74</v>
       </c>
       <c r="K123" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="22.5" customHeight="1">
@@ -26436,10 +26570,10 @@
         <v>618</v>
       </c>
       <c r="B124" s="77" t="s">
-        <v>1409</v>
+        <v>1417</v>
       </c>
       <c r="C124" s="76" t="s">
-        <v>1410</v>
+        <v>1418</v>
       </c>
       <c r="D124" s="70"/>
       <c r="E124" s="70"/>
@@ -26457,7 +26591,7 @@
         <v>25</v>
       </c>
       <c r="K124" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="22.5" customHeight="1">
@@ -26465,10 +26599,10 @@
         <v>621</v>
       </c>
       <c r="B125" s="81" t="s">
-        <v>1411</v>
+        <v>1419</v>
       </c>
       <c r="C125" s="82" t="s">
-        <v>1412</v>
+        <v>1420</v>
       </c>
       <c r="D125" s="83"/>
       <c r="E125" s="83"/>
@@ -26484,7 +26618,7 @@
         <v>25</v>
       </c>
       <c r="K125" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="22.5" customHeight="1">
@@ -26492,10 +26626,10 @@
         <v>624</v>
       </c>
       <c r="B126" s="77" t="s">
-        <v>1413</v>
+        <v>1421</v>
       </c>
       <c r="C126" s="76" t="s">
-        <v>1414</v>
+        <v>1422</v>
       </c>
       <c r="D126" s="70"/>
       <c r="E126" s="70"/>
@@ -26511,7 +26645,7 @@
         <v>74</v>
       </c>
       <c r="K126" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="22.5" customHeight="1">
@@ -26519,10 +26653,10 @@
         <v>627</v>
       </c>
       <c r="B127" s="81" t="s">
-        <v>1415</v>
+        <v>1423</v>
       </c>
       <c r="C127" s="82" t="s">
-        <v>1416</v>
+        <v>1424</v>
       </c>
       <c r="D127" s="83"/>
       <c r="E127" s="83"/>
@@ -26538,7 +26672,7 @@
         <v>74</v>
       </c>
       <c r="K127" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="22.5" customHeight="1">
@@ -26546,10 +26680,10 @@
         <v>459</v>
       </c>
       <c r="B128" s="104" t="s">
-        <v>1417</v>
+        <v>1425</v>
       </c>
       <c r="C128" s="104" t="s">
-        <v>1418</v>
+        <v>1426</v>
       </c>
       <c r="D128" s="62" t="s">
         <v>540</v>
@@ -26568,10 +26702,10 @@
         <v>0.5</v>
       </c>
       <c r="J128" s="64" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="K128" s="104" t="s">
-        <v>1377</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="22.5" customHeight="1">
@@ -26579,10 +26713,10 @@
         <v>630</v>
       </c>
       <c r="B129" s="77" t="s">
-        <v>1419</v>
+        <v>1427</v>
       </c>
       <c r="C129" s="76" t="s">
-        <v>1420</v>
+        <v>1428</v>
       </c>
       <c r="D129" s="70"/>
       <c r="E129" s="70"/>
@@ -26598,7 +26732,7 @@
         <v>74</v>
       </c>
       <c r="K129" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="22.5" customHeight="1">
@@ -26606,10 +26740,10 @@
         <v>633</v>
       </c>
       <c r="B130" s="81" t="s">
-        <v>1421</v>
+        <v>1429</v>
       </c>
       <c r="C130" s="82" t="s">
-        <v>1422</v>
+        <v>1430</v>
       </c>
       <c r="D130" s="83"/>
       <c r="E130" s="83"/>
@@ -26627,7 +26761,7 @@
         <v>74</v>
       </c>
       <c r="K130" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="22.5" customHeight="1">
@@ -26635,10 +26769,10 @@
         <v>636</v>
       </c>
       <c r="B131" s="77" t="s">
-        <v>1423</v>
+        <v>1431</v>
       </c>
       <c r="C131" s="76" t="s">
-        <v>1424</v>
+        <v>1432</v>
       </c>
       <c r="D131" s="70"/>
       <c r="E131" s="70"/>
@@ -26654,7 +26788,7 @@
         <v>74</v>
       </c>
       <c r="K131" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="22.5" customHeight="1">
@@ -26662,10 +26796,10 @@
         <v>637</v>
       </c>
       <c r="B132" s="81" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="C132" s="82" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="D132" s="83"/>
       <c r="E132" s="83"/>
@@ -26683,7 +26817,7 @@
         <v>74</v>
       </c>
       <c r="K132" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="22.5" customHeight="1">
@@ -26691,10 +26825,10 @@
         <v>638</v>
       </c>
       <c r="B133" s="77" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="C133" s="76" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="D133" s="70"/>
       <c r="E133" s="70"/>
@@ -26712,7 +26846,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="22.5" customHeight="1">
@@ -26720,10 +26854,10 @@
         <v>639</v>
       </c>
       <c r="B134" s="81" t="s">
-        <v>1425</v>
+        <v>1433</v>
       </c>
       <c r="C134" s="82" t="s">
-        <v>1426</v>
+        <v>1434</v>
       </c>
       <c r="D134" s="83"/>
       <c r="E134" s="83"/>
@@ -26739,7 +26873,7 @@
         <v>25</v>
       </c>
       <c r="K134" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="22.5" customHeight="1">
@@ -26747,10 +26881,10 @@
         <v>640</v>
       </c>
       <c r="B135" s="77" t="s">
-        <v>1427</v>
+        <v>1435</v>
       </c>
       <c r="C135" s="76" t="s">
-        <v>1428</v>
+        <v>1436</v>
       </c>
       <c r="D135" s="70"/>
       <c r="E135" s="70"/>
@@ -26768,7 +26902,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="22.5" customHeight="1">
@@ -26776,10 +26910,10 @@
         <v>641</v>
       </c>
       <c r="B136" s="81" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="C136" s="82" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="D136" s="83"/>
       <c r="E136" s="83"/>
@@ -26795,7 +26929,7 @@
         <v>74</v>
       </c>
       <c r="K136" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="22.5" customHeight="1">
@@ -26803,10 +26937,10 @@
         <v>642</v>
       </c>
       <c r="B137" s="77" t="s">
-        <v>1429</v>
+        <v>1437</v>
       </c>
       <c r="C137" s="76" t="s">
-        <v>1430</v>
+        <v>1438</v>
       </c>
       <c r="D137" s="70"/>
       <c r="E137" s="70"/>
@@ -26822,7 +26956,7 @@
         <v>74</v>
       </c>
       <c r="K137" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="22.5" customHeight="1">
@@ -26830,10 +26964,10 @@
         <v>643</v>
       </c>
       <c r="B138" s="81" t="s">
-        <v>1431</v>
+        <v>1439</v>
       </c>
       <c r="C138" s="82" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="D138" s="83"/>
       <c r="E138" s="83"/>
@@ -26851,7 +26985,7 @@
         <v>74</v>
       </c>
       <c r="K138" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="22.5" customHeight="1">
@@ -26859,13 +26993,13 @@
         <v>462</v>
       </c>
       <c r="B139" s="104" t="s">
-        <v>1432</v>
+        <v>1440</v>
       </c>
       <c r="C139" s="104" t="s">
-        <v>1433</v>
+        <v>1441</v>
       </c>
       <c r="D139" s="62" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="E139" s="63"/>
       <c r="F139" s="64" t="s">
@@ -26884,7 +27018,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="104" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="22.5" customHeight="1">
@@ -26892,10 +27026,10 @@
         <v>644</v>
       </c>
       <c r="B140" s="81" t="s">
-        <v>1434</v>
+        <v>1442</v>
       </c>
       <c r="C140" s="82" t="s">
-        <v>1435</v>
+        <v>1443</v>
       </c>
       <c r="D140" s="83"/>
       <c r="E140" s="83"/>
@@ -26913,7 +27047,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="22.5" customHeight="1">
@@ -26921,10 +27055,10 @@
         <v>645</v>
       </c>
       <c r="B141" s="77" t="s">
-        <v>1436</v>
+        <v>1444</v>
       </c>
       <c r="C141" s="76" t="s">
-        <v>1437</v>
+        <v>1445</v>
       </c>
       <c r="D141" s="70"/>
       <c r="E141" s="70"/>
@@ -26940,7 +27074,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="22.5" customHeight="1">
@@ -26948,10 +27082,10 @@
         <v>646</v>
       </c>
       <c r="B142" s="81" t="s">
-        <v>1438</v>
+        <v>1446</v>
       </c>
       <c r="C142" s="82" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="D142" s="83"/>
       <c r="E142" s="83"/>
@@ -26967,7 +27101,7 @@
         <v>74</v>
       </c>
       <c r="K142" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="22.5" customHeight="1">
@@ -26975,10 +27109,10 @@
         <v>647</v>
       </c>
       <c r="B143" s="77" t="s">
-        <v>1439</v>
+        <v>1447</v>
       </c>
       <c r="C143" s="76" t="s">
-        <v>1440</v>
+        <v>1448</v>
       </c>
       <c r="D143" s="70"/>
       <c r="E143" s="70"/>
@@ -26994,7 +27128,7 @@
         <v>74</v>
       </c>
       <c r="K143" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="22.5" customHeight="1">
@@ -27002,10 +27136,10 @@
         <v>648</v>
       </c>
       <c r="B144" s="81" t="s">
-        <v>1441</v>
+        <v>1449</v>
       </c>
       <c r="C144" s="82" t="s">
-        <v>1442</v>
+        <v>1450</v>
       </c>
       <c r="D144" s="83"/>
       <c r="E144" s="83"/>
@@ -27021,7 +27155,7 @@
         <v>74</v>
       </c>
       <c r="K144" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="22.5" customHeight="1">
@@ -27029,10 +27163,10 @@
         <v>649</v>
       </c>
       <c r="B145" s="77" t="s">
-        <v>1443</v>
+        <v>1451</v>
       </c>
       <c r="C145" s="76" t="s">
-        <v>1444</v>
+        <v>1452</v>
       </c>
       <c r="D145" s="70"/>
       <c r="E145" s="70"/>
@@ -27048,7 +27182,7 @@
         <v>25</v>
       </c>
       <c r="K145" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="22.5" customHeight="1">
@@ -27056,10 +27190,10 @@
         <v>650</v>
       </c>
       <c r="B146" s="81" t="s">
-        <v>1445</v>
+        <v>1453</v>
       </c>
       <c r="C146" s="82" t="s">
-        <v>1446</v>
+        <v>1454</v>
       </c>
       <c r="D146" s="83"/>
       <c r="E146" s="83"/>
@@ -27075,7 +27209,7 @@
         <v>74</v>
       </c>
       <c r="K146" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="22.5" customHeight="1">
@@ -27083,10 +27217,10 @@
         <v>651</v>
       </c>
       <c r="B147" s="77" t="s">
-        <v>1447</v>
+        <v>1455</v>
       </c>
       <c r="C147" s="76" t="s">
-        <v>1448</v>
+        <v>1456</v>
       </c>
       <c r="D147" s="70"/>
       <c r="E147" s="70"/>
@@ -27102,7 +27236,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="22.5" customHeight="1">
@@ -27110,10 +27244,10 @@
         <v>652</v>
       </c>
       <c r="B148" s="81" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="C148" s="82" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="D148" s="83"/>
       <c r="E148" s="83"/>
@@ -27129,7 +27263,7 @@
         <v>74</v>
       </c>
       <c r="K148" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="22.5" customHeight="1">
@@ -27137,10 +27271,10 @@
         <v>653</v>
       </c>
       <c r="B149" s="77" t="s">
-        <v>1451</v>
+        <v>1459</v>
       </c>
       <c r="C149" s="76" t="s">
-        <v>1452</v>
+        <v>1460</v>
       </c>
       <c r="D149" s="70"/>
       <c r="E149" s="70"/>
@@ -27156,7 +27290,7 @@
         <v>74</v>
       </c>
       <c r="K149" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="22.5" customHeight="1">
@@ -27164,11 +27298,11 @@
         <v>465</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1453</v>
+        <v>1461</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="166" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="E150" s="167"/>
       <c r="F150" s="168"/>
@@ -27183,10 +27317,10 @@
         <v>654</v>
       </c>
       <c r="B151" s="82" t="s">
-        <v>1454</v>
+        <v>1462</v>
       </c>
       <c r="C151" s="82" t="s">
-        <v>1455</v>
+        <v>1463</v>
       </c>
       <c r="D151" s="83"/>
       <c r="E151" s="83"/>
@@ -27199,21 +27333,21 @@
       </c>
       <c r="I151" s="87"/>
       <c r="J151" s="90" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="K151" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="22.5" customHeight="1">
       <c r="A152" s="8" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="B152" s="77" t="s">
-        <v>1456</v>
+        <v>1464</v>
       </c>
       <c r="C152" s="76" t="s">
-        <v>1457</v>
+        <v>1465</v>
       </c>
       <c r="D152" s="70"/>
       <c r="E152" s="70"/>
@@ -27229,18 +27363,18 @@
         <v>25</v>
       </c>
       <c r="K152" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="22.5" customHeight="1">
       <c r="A153" s="8" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="B153" s="81" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="C153" s="82" t="s">
-        <v>1459</v>
+        <v>1467</v>
       </c>
       <c r="D153" s="83"/>
       <c r="E153" s="83"/>
@@ -27256,18 +27390,18 @@
         <v>74</v>
       </c>
       <c r="K153" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="22.5" customHeight="1">
       <c r="A154" s="8" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="B154" s="77" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="C154" s="76" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="D154" s="70"/>
       <c r="E154" s="70"/>
@@ -27283,18 +27417,18 @@
         <v>25</v>
       </c>
       <c r="K154" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="22.5" customHeight="1">
       <c r="A155" s="8" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="B155" s="81" t="s">
-        <v>1460</v>
+        <v>1468</v>
       </c>
       <c r="C155" s="82" t="s">
-        <v>1461</v>
+        <v>1469</v>
       </c>
       <c r="D155" s="83"/>
       <c r="E155" s="83"/>
@@ -27312,18 +27446,18 @@
         <v>25</v>
       </c>
       <c r="K155" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="22.5" customHeight="1">
       <c r="A156" s="8" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="B156" s="76" t="s">
-        <v>1462</v>
+        <v>1470</v>
       </c>
       <c r="C156" s="76" t="s">
-        <v>1463</v>
+        <v>1471</v>
       </c>
       <c r="D156" s="70"/>
       <c r="E156" s="70"/>
@@ -27339,18 +27473,18 @@
         <v>513</v>
       </c>
       <c r="K156" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="22.5" customHeight="1">
       <c r="A157" s="8" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="B157" s="81" t="s">
-        <v>1464</v>
+        <v>1472</v>
       </c>
       <c r="C157" s="82" t="s">
-        <v>1465</v>
+        <v>1473</v>
       </c>
       <c r="D157" s="83"/>
       <c r="E157" s="83"/>
@@ -27368,18 +27502,18 @@
         <v>74</v>
       </c>
       <c r="K157" s="82" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="22.5" customHeight="1">
       <c r="A158" s="8" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="B158" s="76" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="C158" s="76" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="D158" s="70"/>
       <c r="E158" s="70"/>
@@ -27397,18 +27531,18 @@
         <v>25</v>
       </c>
       <c r="K158" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="22.5" customHeight="1">
       <c r="A159" s="8" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="B159" s="77" t="s">
-        <v>1466</v>
+        <v>1474</v>
       </c>
       <c r="C159" s="76" t="s">
-        <v>1467</v>
+        <v>1475</v>
       </c>
       <c r="D159" s="10"/>
       <c r="E159" s="11"/>
@@ -27424,18 +27558,18 @@
         <v>25</v>
       </c>
       <c r="K159" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="22.5" customHeight="1">
       <c r="A160" s="8" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B160" s="77" t="s">
-        <v>1468</v>
+        <v>1476</v>
       </c>
       <c r="C160" s="76" t="s">
-        <v>1469</v>
+        <v>1477</v>
       </c>
       <c r="D160" s="10"/>
       <c r="E160" s="11"/>
@@ -27451,7 +27585,7 @@
         <v>25</v>
       </c>
       <c r="K160" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="22.5" customHeight="1">
@@ -27461,7 +27595,7 @@
       <c r="B161" s="9"/>
       <c r="C161" s="5"/>
       <c r="D161" s="62" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="E161" s="167"/>
       <c r="F161" s="102"/>
@@ -27473,13 +27607,13 @@
     </row>
     <row r="162" spans="1:11" ht="22.5" customHeight="1">
       <c r="A162" s="8" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>1470</v>
+        <v>1478</v>
       </c>
       <c r="D162" s="10"/>
       <c r="E162" s="11"/>
@@ -27497,18 +27631,18 @@
         <v>74</v>
       </c>
       <c r="K162" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="22.5" customHeight="1">
       <c r="A163" s="8" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="D163" s="10"/>
       <c r="E163" s="11"/>
@@ -27526,18 +27660,18 @@
         <v>25</v>
       </c>
       <c r="K163" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="22.5" customHeight="1">
       <c r="A164" s="8" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="D164" s="10"/>
       <c r="E164" s="11"/>
@@ -27555,18 +27689,18 @@
         <v>745</v>
       </c>
       <c r="K164" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="22.5" customHeight="1">
       <c r="A165" s="8" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="D165" s="10"/>
       <c r="E165" s="11"/>
@@ -27584,7 +27718,7 @@
         <v>551</v>
       </c>
       <c r="K165" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="22.5" customHeight="1">
@@ -27621,10 +27755,10 @@
         <v>11</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="D167" s="10"/>
       <c r="E167" s="11"/>
@@ -27642,7 +27776,7 @@
         <v>551</v>
       </c>
       <c r="K167" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="22.5" customHeight="1">
@@ -27679,10 +27813,10 @@
         <v>18</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="D169" s="10"/>
       <c r="E169" s="11"/>
@@ -27700,7 +27834,7 @@
         <v>551</v>
       </c>
       <c r="K169" s="76" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="22.5" customHeight="1">
@@ -29252,10 +29386,10 @@
     <row r="248" spans="1:11" ht="22.5" customHeight="1">
       <c r="A248" s="46"/>
       <c r="B248" s="9" t="s">
-        <v>1471</v>
+        <v>1479</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>1472</v>
+        <v>1480</v>
       </c>
       <c r="D248" s="10"/>
       <c r="E248" s="48" t="s">

--- a/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
+++ b/data/PIPE LINE PROCESO COMERCIAL - Ventas TA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlando.carvajal.DESMEX\Desktop\ClaudeCode\Pipeline1\pipeline-web\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3DDA241-21CC-481C-A298-5112A4DF8A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6760B08E-F35A-44C7-989C-F60843AADA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Josué Morales" sheetId="2" r:id="rId1"/>
@@ -22,11 +22,11 @@
     <sheet name="Copia seguridad 27-01-2026" sheetId="9" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$L$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexandro Carrasco'!$A$1:$L$217</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Copia seguridad 27-01-2026'!$A$1:$K$275</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Daniela Lara'!$A$1:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Josué Morales'!$A$1:$K$148</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Marco Flores'!$A$1:$K$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Marco Flores'!$A$1:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rebeca Ortiz'!$A$1:$K$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Saira Gómez'!$A$1:$K$21</definedName>
   </definedNames>
@@ -50,11 +50,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={9d256fd8-46be-4af9-9b5c-7e04558d4601}</author>
-    <author>tc={c75241ac-b84b-47da-aa2a-6d1cfa1e46ac}</author>
+    <author>tc={468092fc-b411-4a4b-aef0-6c7a29edae13}</author>
+    <author>tc={f80ef82a-da2e-4907-9310-145d24585d0a}</author>
   </authors>
   <commentList>
-    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{9D256FD8-46BE-4AF9-9B5C-7E04558D4601}">
+    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{468092FC-B411-4A4B-AEF0-6C7A29EDAE13}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -62,7 +62,7 @@
     ya lo tiene en seguimiento Josué</t>
       </text>
     </comment>
-    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{C75241AC-B84B-47DA-AA2A-6D1CFA1E46AC}">
+    <comment ref="J62" authorId="1" shapeId="0" xr:uid="{F80EF82A-DA2E-4907-9310-145D24585D0A}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4839" uniqueCount="1481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4843" uniqueCount="1485">
   <si>
     <t>ID de Prospecto</t>
   </si>
@@ -2084,6 +2084,9 @@
     <t>Standard Profil</t>
   </si>
   <si>
+    <t>6. Diseño de Solución / Pre-Ingeniería</t>
+  </si>
+  <si>
     <t>PSP5</t>
   </si>
   <si>
@@ -2180,9 +2183,6 @@
     <t>Pirelli</t>
   </si>
   <si>
-    <t>6. Diseño de Solución / Pre-Ingeniería</t>
-  </si>
-  <si>
     <t>Mantenimiento</t>
   </si>
   <si>
@@ -2858,12 +2858,6 @@
     <t>PICA Ingeniería</t>
   </si>
   <si>
-    <t>Jorge Chahín Jr</t>
-  </si>
-  <si>
-    <t>Grupo Arquitech</t>
-  </si>
-  <si>
     <t>Estefanía Pérez / Ing. Damián</t>
   </si>
   <si>
@@ -3407,6 +3401,9 @@
     <t xml:space="preserve">Jorge Chahín </t>
   </si>
   <si>
+    <t>13. Kickoff / Inicio de Proyecto</t>
+  </si>
+  <si>
     <t>Moisés Gómez (Xóchitl Gálvez)</t>
   </si>
   <si>
@@ -3500,9 +3497,6 @@
     <t>CDMX y Bajío</t>
   </si>
   <si>
-    <t>13. Kickoff / Inicio de Proyecto</t>
-  </si>
-  <si>
     <t>Miguel Martínez</t>
   </si>
   <si>
@@ -3788,6 +3782,9 @@
     <t>Ing. Juan Gasca</t>
   </si>
   <si>
+    <t>Congeladora "La Marina"</t>
+  </si>
+  <si>
     <t>Arq. Alejandra Vergara</t>
   </si>
   <si>
@@ -3801,6 +3798,18 @@
   </si>
   <si>
     <t>Betone SA DE CV</t>
+  </si>
+  <si>
+    <t>Instituto Kanté</t>
+  </si>
+  <si>
+    <t>León, Gto</t>
+  </si>
+  <si>
+    <t>Lic. Christian</t>
+  </si>
+  <si>
+    <t>Carnitas Sapal</t>
   </si>
   <si>
     <r>
@@ -3974,6 +3983,9 @@
   </si>
   <si>
     <t>Rancho la esperanza de Miranda</t>
+  </si>
+  <si>
+    <t>Francisco</t>
   </si>
   <si>
     <t xml:space="preserve">Iriani Ortega </t>
@@ -5799,7 +5811,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Anónimo" id="{45B2083E-4DCC-4231-86BE-3E9E61CFA40D}" userId="" providerId="google-sheets"/>
+  <person displayName="Anónimo" id="{30D01166-BB64-4F6A-A5B1-6891D4898AD8}" userId="" providerId="google-sheets"/>
 </personList>
 </file>
 
@@ -5865,8 +5877,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:L216">
-  <autoFilter ref="A1:L216" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla_3" displayName="Tabla_3" ref="A1:L217">
+  <autoFilter ref="A1:L217" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID de Prospecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Nombre del Prospecto"/>
@@ -5886,8 +5898,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabla_2" displayName="Tabla_2" ref="A1:K29">
-  <autoFilter ref="A1:K29" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabla_2" displayName="Tabla_2" ref="A1:K30">
+  <autoFilter ref="A1:K30" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="ID de Prospecto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Nombre del Prospecto"/>
@@ -6143,10 +6155,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{45B2083E-4DCC-4231-86BE-3E9E61CFA40D}" id="{9D256FD8-46BE-4AF9-9B5C-7E04558D4601}" done="1">
+  <threadedComment ref="J32" dT="2026-02-23T14:39:40.00" personId="{30D01166-BB64-4F6A-A5B1-6891D4898AD8}" id="{468092FC-B411-4A4B-AEF0-6C7A29EDAE13}" done="1">
     <text>ya lo tiene en seguimiento Josué</text>
   </threadedComment>
-  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{45B2083E-4DCC-4231-86BE-3E9E61CFA40D}" id="{C75241AC-B84B-47DA-AA2A-6D1CFA1E46AC}" done="1">
+  <threadedComment ref="J62" dT="2026-02-24T22:06:20.00" personId="{30D01166-BB64-4F6A-A5B1-6891D4898AD8}" id="{F80EF82A-DA2E-4907-9310-145D24585D0A}" done="1">
     <text>Ya tienen contrato con Ammper</text>
   </threadedComment>
 </ThreadedComments>
@@ -12106,7 +12118,7 @@
         <v>448</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>14</v>
+        <v>667</v>
       </c>
       <c r="G5" s="54">
         <v>46076</v>
@@ -12127,13 +12139,13 @@
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
       <c r="A6" s="46" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D6" s="52" t="s">
         <v>540</v>
@@ -12166,19 +12178,19 @@
         <v>459</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G7" s="54">
         <v>46077</v>
@@ -12202,10 +12214,10 @@
         <v>462</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D8" s="52" t="s">
         <v>658</v>
@@ -12238,13 +12250,13 @@
         <v>465</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>448</v>
@@ -12274,10 +12286,10 @@
         <v>468</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D10" s="49" t="s">
         <v>561</v>
@@ -12310,19 +12322,19 @@
         <v>471</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>561</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G11" s="54">
         <v>46083</v>
@@ -12346,19 +12358,19 @@
         <v>474</v>
       </c>
       <c r="B12" s="51" t="s">
+        <v>685</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>686</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>687</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>684</v>
       </c>
-      <c r="C12" s="51" t="s">
-        <v>685</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>686</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>683</v>
-      </c>
       <c r="F12" s="53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G12" s="54">
         <v>46083</v>
@@ -12382,7 +12394,7 @@
         <v>477</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C13" s="51" t="s">
         <v>483</v>
@@ -12394,7 +12406,7 @@
         <v>448</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G13" s="54">
         <v>46085</v>
@@ -12406,7 +12418,7 @@
         <v>0.7</v>
       </c>
       <c r="J13" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K13" s="46" t="s">
         <v>660</v>
@@ -12418,19 +12430,19 @@
         <v>481</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>449</v>
+        <v>32</v>
       </c>
       <c r="G14" s="54">
         <v>46086</v>
@@ -12454,10 +12466,10 @@
         <v>484</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D15" s="49" t="s">
         <v>540</v>
@@ -12490,19 +12502,19 @@
         <v>488</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D16" s="49" t="s">
         <v>561</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G16" s="54">
         <v>46087</v>
@@ -12526,10 +12538,10 @@
         <v>491</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D17" s="49" t="s">
         <v>658</v>
@@ -12538,7 +12550,7 @@
         <v>448</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>699</v>
+        <v>667</v>
       </c>
       <c r="G17" s="54">
         <v>46090</v>
@@ -12571,7 +12583,7 @@
         <v>702</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F18" s="53" t="s">
         <v>24</v>
@@ -12607,7 +12619,7 @@
         <v>561</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F19" s="53" t="s">
         <v>24</v>
@@ -12679,7 +12691,7 @@
         <v>561</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F21" s="53" t="s">
         <v>480</v>
@@ -12823,7 +12835,7 @@
         <v>718</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F25" s="53" t="s">
         <v>449</v>
@@ -12896,7 +12908,7 @@
         <v>448</v>
       </c>
       <c r="F27" s="53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G27" s="54">
         <v>46135</v>
@@ -12932,7 +12944,7 @@
         <v>448</v>
       </c>
       <c r="F28" s="53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G28" s="54">
         <v>46135</v>
@@ -12968,7 +12980,7 @@
         <v>706</v>
       </c>
       <c r="F29" s="53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G29" s="54">
         <v>46140</v>
@@ -13001,7 +13013,7 @@
         <v>728</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F30" s="53" t="s">
         <v>449</v>
@@ -13148,7 +13160,7 @@
         <v>448</v>
       </c>
       <c r="F34" s="53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G34" s="54">
         <v>46148</v>
@@ -13292,7 +13304,7 @@
         <v>448</v>
       </c>
       <c r="F38" s="53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G38" s="54">
         <v>46155</v>
@@ -13328,7 +13340,7 @@
         <v>448</v>
       </c>
       <c r="F39" s="53" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G39" s="54">
         <v>46155</v>
@@ -14786,7 +14798,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC216"/>
+  <dimension ref="A1:AC217"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -15206,7 +15218,7 @@
       <c r="H13" s="55"/>
       <c r="I13" s="56"/>
       <c r="J13" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K13" s="51" t="s">
         <v>769</v>
@@ -15266,7 +15278,7 @@
       <c r="H15" s="55"/>
       <c r="I15" s="56"/>
       <c r="J15" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K15" s="51" t="s">
         <v>769</v>
@@ -15294,7 +15306,7 @@
       <c r="H16" s="55"/>
       <c r="I16" s="56"/>
       <c r="J16" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K16" s="51" t="s">
         <v>769</v>
@@ -15324,7 +15336,7 @@
       <c r="H17" s="55"/>
       <c r="I17" s="56"/>
       <c r="J17" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K17" s="51" t="s">
         <v>769</v>
@@ -15512,7 +15524,7 @@
       <c r="H23" s="55"/>
       <c r="I23" s="56"/>
       <c r="J23" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>769</v>
@@ -15704,7 +15716,7 @@
       <c r="H29" s="55"/>
       <c r="I29" s="56"/>
       <c r="J29" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K29" s="51" t="s">
         <v>769</v>
@@ -15836,7 +15848,7 @@
       <c r="H33" s="55"/>
       <c r="I33" s="56"/>
       <c r="J33" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K33" s="46" t="s">
         <v>769</v>
@@ -15870,7 +15882,7 @@
         <v>839</v>
       </c>
       <c r="J34" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K34" s="51" t="s">
         <v>769</v>
@@ -15900,7 +15912,7 @@
       <c r="H35" s="55"/>
       <c r="I35" s="56"/>
       <c r="J35" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K35" s="51" t="s">
         <v>769</v>
@@ -15962,7 +15974,7 @@
       <c r="H37" s="55"/>
       <c r="I37" s="56"/>
       <c r="J37" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K37" s="51" t="s">
         <v>769</v>
@@ -16118,7 +16130,7 @@
       <c r="H42" s="55"/>
       <c r="I42" s="56"/>
       <c r="J42" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K42" s="46" t="s">
         <v>769</v>
@@ -16150,7 +16162,7 @@
       <c r="H43" s="55"/>
       <c r="I43" s="56"/>
       <c r="J43" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K43" s="51" t="s">
         <v>769</v>
@@ -16248,7 +16260,7 @@
       <c r="H46" s="55"/>
       <c r="I46" s="56"/>
       <c r="J46" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K46" s="51" t="s">
         <v>769</v>
@@ -16408,7 +16420,7 @@
       <c r="H51" s="55"/>
       <c r="I51" s="56"/>
       <c r="J51" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K51" s="51" t="s">
         <v>769</v>
@@ -16470,7 +16482,7 @@
       <c r="H53" s="55"/>
       <c r="I53" s="56"/>
       <c r="J53" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K53" s="46" t="s">
         <v>769</v>
@@ -16502,7 +16514,7 @@
       <c r="H54" s="55"/>
       <c r="I54" s="56"/>
       <c r="J54" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K54" s="51" t="s">
         <v>769</v>
@@ -16566,7 +16578,7 @@
       <c r="H56" s="55"/>
       <c r="I56" s="56"/>
       <c r="J56" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K56" s="51" t="s">
         <v>769</v>
@@ -16788,7 +16800,7 @@
       <c r="H63" s="55"/>
       <c r="I63" s="56"/>
       <c r="J63" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K63" s="51" t="s">
         <v>769</v>
@@ -17012,7 +17024,7 @@
       <c r="H70" s="55"/>
       <c r="I70" s="56"/>
       <c r="J70" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K70" s="51" t="s">
         <v>769</v>
@@ -17053,7 +17065,7 @@
     </row>
     <row r="72" spans="1:12" ht="22.5" customHeight="1">
       <c r="A72" s="8" t="s">
-        <v>520</v>
+        <v>576</v>
       </c>
       <c r="B72" s="51" t="s">
         <v>925</v>
@@ -17061,22 +17073,20 @@
       <c r="C72" s="51" t="s">
         <v>926</v>
       </c>
-      <c r="D72" s="49" t="s">
-        <v>896</v>
-      </c>
+      <c r="D72" s="10"/>
       <c r="E72" s="10" t="s">
-        <v>859</v>
+        <v>448</v>
       </c>
       <c r="F72" s="53" t="s">
         <v>119</v>
       </c>
       <c r="G72" s="54">
-        <v>46052</v>
+        <v>46049</v>
       </c>
       <c r="H72" s="55"/>
       <c r="I72" s="56"/>
       <c r="J72" s="53" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K72" s="51" t="s">
         <v>769</v>
@@ -17085,7 +17095,7 @@
     </row>
     <row r="73" spans="1:12" ht="22.5" customHeight="1">
       <c r="A73" s="8" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B73" s="51" t="s">
         <v>927</v>
@@ -17093,12 +17103,14 @@
       <c r="C73" s="51" t="s">
         <v>928</v>
       </c>
-      <c r="D73" s="10"/>
+      <c r="D73" s="49" t="s">
+        <v>723</v>
+      </c>
       <c r="E73" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F73" s="53" t="s">
-        <v>119</v>
+        <v>449</v>
       </c>
       <c r="G73" s="54">
         <v>46049</v>
@@ -17115,7 +17127,7 @@
     </row>
     <row r="74" spans="1:12" ht="22.5" customHeight="1">
       <c r="A74" s="8" t="s">
-        <v>579</v>
+        <v>650</v>
       </c>
       <c r="B74" s="51" t="s">
         <v>929</v>
@@ -17123,17 +17135,17 @@
       <c r="C74" s="51" t="s">
         <v>930</v>
       </c>
-      <c r="D74" s="49" t="s">
-        <v>723</v>
+      <c r="D74" s="10" t="s">
+        <v>931</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F74" s="53" t="s">
-        <v>449</v>
+        <v>119</v>
       </c>
       <c r="G74" s="54">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="H74" s="55"/>
       <c r="I74" s="56"/>
@@ -17147,61 +17159,61 @@
     </row>
     <row r="75" spans="1:12" ht="22.5" customHeight="1">
       <c r="A75" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="B75" s="51" t="s">
-        <v>931</v>
-      </c>
-      <c r="C75" s="51" t="s">
+        <v>503</v>
+      </c>
+      <c r="B75" s="46" t="s">
         <v>932</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="C75" s="46" t="s">
         <v>933</v>
       </c>
+      <c r="D75" s="49" t="s">
+        <v>934</v>
+      </c>
       <c r="E75" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F75" s="53" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="G75" s="54">
-        <v>46048</v>
-      </c>
-      <c r="H75" s="55"/>
+        <v>46043</v>
+      </c>
+      <c r="H75" s="55">
+        <v>15458</v>
+      </c>
       <c r="I75" s="56"/>
       <c r="J75" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K75" s="51" t="s">
+      <c r="K75" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L75" s="57"/>
     </row>
     <row r="76" spans="1:12" ht="22.5" customHeight="1">
       <c r="A76" s="8" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B76" s="46" t="s">
+        <v>932</v>
+      </c>
+      <c r="C76" s="46" t="s">
+        <v>933</v>
+      </c>
+      <c r="D76" s="49" t="s">
         <v>934</v>
       </c>
-      <c r="C76" s="46" t="s">
+      <c r="E76" s="10" t="s">
         <v>935</v>
       </c>
-      <c r="D76" s="49" t="s">
-        <v>936</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>448</v>
-      </c>
       <c r="F76" s="53" t="s">
-        <v>24</v>
+        <v>667</v>
       </c>
       <c r="G76" s="54">
         <v>46043</v>
       </c>
-      <c r="H76" s="55">
-        <v>15458</v>
-      </c>
+      <c r="H76" s="55"/>
       <c r="I76" s="56"/>
       <c r="J76" s="53" t="s">
         <v>25</v>
@@ -17213,114 +17225,112 @@
     </row>
     <row r="77" spans="1:12" ht="22.5" customHeight="1">
       <c r="A77" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="B77" s="46" t="s">
-        <v>934</v>
-      </c>
-      <c r="C77" s="46" t="s">
-        <v>935</v>
-      </c>
-      <c r="D77" s="49" t="s">
+        <v>488</v>
+      </c>
+      <c r="B77" s="51" t="s">
         <v>936</v>
       </c>
+      <c r="C77" s="51" t="s">
+        <v>937</v>
+      </c>
+      <c r="D77" s="10"/>
       <c r="E77" s="10" t="s">
-        <v>937</v>
+        <v>448</v>
       </c>
       <c r="F77" s="53" t="s">
-        <v>699</v>
+        <v>24</v>
       </c>
       <c r="G77" s="54">
-        <v>46043</v>
-      </c>
-      <c r="H77" s="55"/>
+        <v>46038</v>
+      </c>
+      <c r="H77" s="55">
+        <v>169705</v>
+      </c>
       <c r="I77" s="56"/>
       <c r="J77" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K77" s="46" t="s">
+      <c r="K77" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L77" s="57"/>
     </row>
     <row r="78" spans="1:12" ht="22.5" customHeight="1">
       <c r="A78" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="B78" s="51" t="s">
+        <v>494</v>
+      </c>
+      <c r="B78" s="46" t="s">
         <v>938</v>
       </c>
-      <c r="C78" s="51" t="s">
+      <c r="C78" s="46" t="s">
         <v>939</v>
       </c>
-      <c r="D78" s="10"/>
+      <c r="D78" s="49" t="s">
+        <v>658</v>
+      </c>
       <c r="E78" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F78" s="53" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G78" s="54">
-        <v>46038</v>
+        <v>46035</v>
       </c>
       <c r="H78" s="55">
-        <v>169705</v>
+        <v>592418</v>
       </c>
       <c r="I78" s="56"/>
       <c r="J78" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K78" s="51" t="s">
+      <c r="K78" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L78" s="57"/>
     </row>
     <row r="79" spans="1:12" ht="22.5" customHeight="1">
       <c r="A79" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="B79" s="46" t="s">
+        <v>764</v>
+      </c>
+      <c r="B79" s="51" t="s">
         <v>940</v>
       </c>
-      <c r="C79" s="46" t="s">
+      <c r="C79" s="51" t="s">
         <v>941</v>
       </c>
       <c r="D79" s="49" t="s">
-        <v>658</v>
+        <v>942</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F79" s="53" t="s">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="G79" s="54">
-        <v>46035</v>
-      </c>
-      <c r="H79" s="55">
-        <v>592418</v>
-      </c>
+        <v>46034</v>
+      </c>
+      <c r="H79" s="55"/>
       <c r="I79" s="56"/>
       <c r="J79" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="K79" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="K79" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L79" s="57"/>
     </row>
     <row r="80" spans="1:12" ht="22.5" customHeight="1">
       <c r="A80" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="B80" s="51" t="s">
-        <v>942</v>
-      </c>
-      <c r="C80" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="B80" s="46"/>
+      <c r="C80" s="46" t="s">
         <v>943</v>
       </c>
       <c r="D80" s="49" t="s">
-        <v>944</v>
+        <v>540</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>448</v>
@@ -17334,69 +17344,71 @@
       <c r="H80" s="55"/>
       <c r="I80" s="56"/>
       <c r="J80" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="K80" s="51" t="s">
+        <v>551</v>
+      </c>
+      <c r="K80" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L80" s="57"/>
     </row>
     <row r="81" spans="1:12" ht="22.5" customHeight="1">
       <c r="A81" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B81" s="46"/>
-      <c r="C81" s="46" t="s">
+        <v>582</v>
+      </c>
+      <c r="B81" s="51" t="s">
+        <v>944</v>
+      </c>
+      <c r="C81" s="51" t="s">
         <v>945</v>
       </c>
       <c r="D81" s="49" t="s">
-        <v>540</v>
+        <v>946</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>448</v>
+        <v>859</v>
       </c>
       <c r="F81" s="53" t="s">
         <v>119</v>
       </c>
       <c r="G81" s="54">
-        <v>46034</v>
+        <v>46030</v>
       </c>
       <c r="H81" s="55"/>
       <c r="I81" s="56"/>
       <c r="J81" s="53" t="s">
-        <v>551</v>
-      </c>
-      <c r="K81" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="K81" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L81" s="57"/>
     </row>
     <row r="82" spans="1:12" ht="22.5" customHeight="1">
       <c r="A82" s="8" t="s">
-        <v>582</v>
+        <v>113</v>
       </c>
       <c r="B82" s="51" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C82" s="51" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D82" s="49" t="s">
-        <v>948</v>
+        <v>723</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>859</v>
+        <v>448</v>
       </c>
       <c r="F82" s="53" t="s">
         <v>119</v>
       </c>
       <c r="G82" s="54">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="H82" s="55"/>
       <c r="I82" s="56"/>
       <c r="J82" s="53" t="s">
-        <v>74</v>
+        <v>689</v>
       </c>
       <c r="K82" s="51" t="s">
         <v>769</v>
@@ -17404,18 +17416,14 @@
       <c r="L82" s="57"/>
     </row>
     <row r="83" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A83" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B83" s="51" t="s">
+      <c r="A83" s="46"/>
+      <c r="B83" s="46" t="s">
         <v>949</v>
       </c>
-      <c r="C83" s="51" t="s">
-        <v>950</v>
-      </c>
-      <c r="D83" s="49" t="s">
-        <v>723</v>
-      </c>
+      <c r="C83" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="D83" s="10"/>
       <c r="E83" s="10" t="s">
         <v>448</v>
       </c>
@@ -17428,22 +17436,26 @@
       <c r="H83" s="55"/>
       <c r="I83" s="56"/>
       <c r="J83" s="53" t="s">
-        <v>688</v>
-      </c>
-      <c r="K83" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="K83" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L83" s="57"/>
     </row>
     <row r="84" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A84" s="46"/>
-      <c r="B84" s="46" t="s">
+      <c r="A84" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B84" s="51" t="s">
+        <v>950</v>
+      </c>
+      <c r="C84" s="51" t="s">
         <v>951</v>
       </c>
-      <c r="C84" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="D84" s="10"/>
+      <c r="D84" s="49" t="s">
+        <v>952</v>
+      </c>
       <c r="E84" s="10" t="s">
         <v>448</v>
       </c>
@@ -17451,31 +17463,27 @@
         <v>119</v>
       </c>
       <c r="G84" s="54">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="H84" s="55"/>
       <c r="I84" s="56"/>
       <c r="J84" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="K84" s="46" t="s">
+        <v>689</v>
+      </c>
+      <c r="K84" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L84" s="57"/>
     </row>
     <row r="85" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A85" s="8" t="s">
-        <v>116</v>
-      </c>
+      <c r="A85" s="46"/>
       <c r="B85" s="51" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C85" s="51" t="s">
-        <v>953</v>
-      </c>
-      <c r="D85" s="49" t="s">
         <v>954</v>
       </c>
+      <c r="D85" s="10"/>
       <c r="E85" s="10" t="s">
         <v>448</v>
       </c>
@@ -17483,12 +17491,12 @@
         <v>119</v>
       </c>
       <c r="G85" s="54">
-        <v>46028</v>
+        <v>46018</v>
       </c>
       <c r="H85" s="55"/>
       <c r="I85" s="56"/>
       <c r="J85" s="53" t="s">
-        <v>688</v>
+        <v>25</v>
       </c>
       <c r="K85" s="51" t="s">
         <v>769</v>
@@ -17503,7 +17511,9 @@
       <c r="C86" s="51" t="s">
         <v>956</v>
       </c>
-      <c r="D86" s="10"/>
+      <c r="D86" s="49" t="s">
+        <v>679</v>
+      </c>
       <c r="E86" s="10" t="s">
         <v>448</v>
       </c>
@@ -17516,7 +17526,7 @@
       <c r="H86" s="55"/>
       <c r="I86" s="56"/>
       <c r="J86" s="53" t="s">
-        <v>25</v>
+        <v>957</v>
       </c>
       <c r="K86" s="51" t="s">
         <v>769</v>
@@ -17526,27 +17536,27 @@
     <row r="87" spans="1:12" ht="22.5" customHeight="1">
       <c r="A87" s="46"/>
       <c r="B87" s="51" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C87" s="51" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D87" s="49" t="s">
-        <v>678</v>
+        <v>960</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F87" s="53" t="s">
-        <v>119</v>
+        <v>449</v>
       </c>
       <c r="G87" s="54">
-        <v>46018</v>
+        <v>46010</v>
       </c>
       <c r="H87" s="55"/>
       <c r="I87" s="56"/>
       <c r="J87" s="53" t="s">
-        <v>959</v>
+        <v>74</v>
       </c>
       <c r="K87" s="51" t="s">
         <v>769</v>
@@ -17554,29 +17564,31 @@
       <c r="L87" s="57"/>
     </row>
     <row r="88" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A88" s="46"/>
+      <c r="A88" s="8" t="s">
+        <v>565</v>
+      </c>
       <c r="B88" s="51" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>962</v>
+        <v>922</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F88" s="53" t="s">
-        <v>449</v>
+        <v>119</v>
       </c>
       <c r="G88" s="54">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="H88" s="55"/>
       <c r="I88" s="56"/>
       <c r="J88" s="53" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="K88" s="51" t="s">
         <v>769</v>
@@ -17585,7 +17597,7 @@
     </row>
     <row r="89" spans="1:12" ht="22.5" customHeight="1">
       <c r="A89" s="8" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B89" s="51" t="s">
         <v>963</v>
@@ -17594,7 +17606,7 @@
         <v>964</v>
       </c>
       <c r="D89" s="49" t="s">
-        <v>922</v>
+        <v>723</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>448</v>
@@ -17617,7 +17629,7 @@
     </row>
     <row r="90" spans="1:12" ht="22.5" customHeight="1">
       <c r="A90" s="8" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B90" s="51" t="s">
         <v>965</v>
@@ -17625,9 +17637,7 @@
       <c r="C90" s="51" t="s">
         <v>966</v>
       </c>
-      <c r="D90" s="49" t="s">
-        <v>723</v>
-      </c>
+      <c r="D90" s="10"/>
       <c r="E90" s="10" t="s">
         <v>448</v>
       </c>
@@ -17649,7 +17659,7 @@
     </row>
     <row r="91" spans="1:12" ht="22.5" customHeight="1">
       <c r="A91" s="8" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B91" s="51" t="s">
         <v>967</v>
@@ -17657,12 +17667,14 @@
       <c r="C91" s="51" t="s">
         <v>968</v>
       </c>
-      <c r="D91" s="10"/>
+      <c r="D91" s="49" t="s">
+        <v>896</v>
+      </c>
       <c r="E91" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F91" s="53" t="s">
-        <v>119</v>
+        <v>449</v>
       </c>
       <c r="G91" s="54">
         <v>46009</v>
@@ -17679,7 +17691,7 @@
     </row>
     <row r="92" spans="1:12" ht="22.5" customHeight="1">
       <c r="A92" s="8" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="B92" s="51" t="s">
         <v>969</v>
@@ -17688,16 +17700,16 @@
         <v>970</v>
       </c>
       <c r="D92" s="49" t="s">
-        <v>896</v>
+        <v>540</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F92" s="53" t="s">
-        <v>449</v>
+        <v>119</v>
       </c>
       <c r="G92" s="54">
-        <v>46009</v>
+        <v>46008</v>
       </c>
       <c r="H92" s="55"/>
       <c r="I92" s="56"/>
@@ -17711,7 +17723,7 @@
     </row>
     <row r="93" spans="1:12" ht="22.5" customHeight="1">
       <c r="A93" s="8" t="s">
-        <v>562</v>
+        <v>88</v>
       </c>
       <c r="B93" s="51" t="s">
         <v>971</v>
@@ -17729,12 +17741,12 @@
         <v>119</v>
       </c>
       <c r="G93" s="54">
-        <v>46008</v>
+        <v>46006</v>
       </c>
       <c r="H93" s="55"/>
       <c r="I93" s="56"/>
       <c r="J93" s="53" t="s">
-        <v>25</v>
+        <v>513</v>
       </c>
       <c r="K93" s="51" t="s">
         <v>769</v>
@@ -17743,62 +17755,60 @@
     </row>
     <row r="94" spans="1:12" ht="22.5" customHeight="1">
       <c r="A94" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B94" s="51" t="s">
+        <v>523</v>
+      </c>
+      <c r="B94" s="46" t="s">
         <v>973</v>
       </c>
-      <c r="C94" s="51" t="s">
+      <c r="C94" s="46" t="s">
         <v>974</v>
       </c>
       <c r="D94" s="49" t="s">
-        <v>540</v>
+        <v>723</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>448</v>
+        <v>975</v>
       </c>
       <c r="F94" s="53" t="s">
-        <v>119</v>
+        <v>449</v>
       </c>
       <c r="G94" s="54">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="H94" s="55"/>
       <c r="I94" s="56"/>
       <c r="J94" s="53" t="s">
-        <v>513</v>
-      </c>
-      <c r="K94" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="K94" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L94" s="57"/>
     </row>
     <row r="95" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A95" s="8" t="s">
-        <v>523</v>
-      </c>
+      <c r="A95" s="46"/>
       <c r="B95" s="46" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C95" s="46" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D95" s="49" t="s">
-        <v>723</v>
+        <v>946</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>977</v>
+        <v>448</v>
       </c>
       <c r="F95" s="53" t="s">
-        <v>449</v>
+        <v>119</v>
       </c>
       <c r="G95" s="54">
-        <v>46001</v>
+        <v>45996</v>
       </c>
       <c r="H95" s="55"/>
       <c r="I95" s="56"/>
       <c r="J95" s="53" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="K95" s="46" t="s">
         <v>769</v>
@@ -17806,15 +17816,17 @@
       <c r="L95" s="57"/>
     </row>
     <row r="96" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A96" s="46"/>
-      <c r="B96" s="46" t="s">
+      <c r="A96" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B96" s="51" t="s">
         <v>978</v>
       </c>
-      <c r="C96" s="46" t="s">
+      <c r="C96" s="51" t="s">
         <v>979</v>
       </c>
       <c r="D96" s="49" t="s">
-        <v>948</v>
+        <v>980</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>448</v>
@@ -17823,30 +17835,30 @@
         <v>119</v>
       </c>
       <c r="G96" s="54">
-        <v>45996</v>
+        <v>45992</v>
       </c>
       <c r="H96" s="55"/>
       <c r="I96" s="56"/>
       <c r="J96" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="K96" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="K96" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L96" s="57"/>
     </row>
     <row r="97" spans="1:12" ht="22.5" customHeight="1">
       <c r="A97" s="8" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B97" s="51" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C97" s="51" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D97" s="49" t="s">
-        <v>982</v>
+        <v>526</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>448</v>
@@ -17869,7 +17881,7 @@
     </row>
     <row r="98" spans="1:12" ht="22.5" customHeight="1">
       <c r="A98" s="8" t="s">
-        <v>644</v>
+        <v>132</v>
       </c>
       <c r="B98" s="51" t="s">
         <v>983</v>
@@ -17878,7 +17890,7 @@
         <v>984</v>
       </c>
       <c r="D98" s="49" t="s">
-        <v>526</v>
+        <v>914</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>448</v>
@@ -17892,7 +17904,7 @@
       <c r="H98" s="55"/>
       <c r="I98" s="56"/>
       <c r="J98" s="53" t="s">
-        <v>74</v>
+        <v>513</v>
       </c>
       <c r="K98" s="51" t="s">
         <v>769</v>
@@ -17901,7 +17913,7 @@
     </row>
     <row r="99" spans="1:12" ht="22.5" customHeight="1">
       <c r="A99" s="8" t="s">
-        <v>132</v>
+        <v>606</v>
       </c>
       <c r="B99" s="51" t="s">
         <v>985</v>
@@ -17910,7 +17922,7 @@
         <v>986</v>
       </c>
       <c r="D99" s="49" t="s">
-        <v>914</v>
+        <v>561</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>448</v>
@@ -17919,12 +17931,12 @@
         <v>119</v>
       </c>
       <c r="G99" s="54">
-        <v>45992</v>
+        <v>45982</v>
       </c>
       <c r="H99" s="55"/>
       <c r="I99" s="56"/>
       <c r="J99" s="53" t="s">
-        <v>513</v>
+        <v>25</v>
       </c>
       <c r="K99" s="51" t="s">
         <v>769</v>
@@ -17933,7 +17945,7 @@
     </row>
     <row r="100" spans="1:12" ht="22.5" customHeight="1">
       <c r="A100" s="8" t="s">
-        <v>606</v>
+        <v>538</v>
       </c>
       <c r="B100" s="51" t="s">
         <v>987</v>
@@ -17942,16 +17954,16 @@
         <v>988</v>
       </c>
       <c r="D100" s="49" t="s">
-        <v>561</v>
+        <v>723</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F100" s="53" t="s">
-        <v>119</v>
+        <v>449</v>
       </c>
       <c r="G100" s="54">
-        <v>45982</v>
+        <v>45975</v>
       </c>
       <c r="H100" s="55"/>
       <c r="I100" s="56"/>
@@ -17965,7 +17977,7 @@
     </row>
     <row r="101" spans="1:12" ht="22.5" customHeight="1">
       <c r="A101" s="8" t="s">
-        <v>538</v>
+        <v>645</v>
       </c>
       <c r="B101" s="51" t="s">
         <v>989</v>
@@ -17974,7 +17986,7 @@
         <v>990</v>
       </c>
       <c r="D101" s="49" t="s">
-        <v>723</v>
+        <v>526</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>448</v>
@@ -17983,12 +17995,12 @@
         <v>449</v>
       </c>
       <c r="G101" s="54">
-        <v>45975</v>
+        <v>45972</v>
       </c>
       <c r="H101" s="55"/>
       <c r="I101" s="56"/>
       <c r="J101" s="53" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K101" s="51" t="s">
         <v>769</v>
@@ -17997,7 +18009,7 @@
     </row>
     <row r="102" spans="1:12" ht="22.5" customHeight="1">
       <c r="A102" s="8" t="s">
-        <v>645</v>
+        <v>120</v>
       </c>
       <c r="B102" s="51" t="s">
         <v>991</v>
@@ -18006,16 +18018,16 @@
         <v>992</v>
       </c>
       <c r="D102" s="49" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F102" s="53" t="s">
-        <v>449</v>
+        <v>119</v>
       </c>
       <c r="G102" s="54">
-        <v>45972</v>
+        <v>45968</v>
       </c>
       <c r="H102" s="55"/>
       <c r="I102" s="56"/>
@@ -18029,7 +18041,7 @@
     </row>
     <row r="103" spans="1:12" ht="22.5" customHeight="1">
       <c r="A103" s="8" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B103" s="51" t="s">
         <v>993</v>
@@ -18038,7 +18050,7 @@
         <v>994</v>
       </c>
       <c r="D103" s="49" t="s">
-        <v>540</v>
+        <v>995</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>448</v>
@@ -18047,7 +18059,7 @@
         <v>119</v>
       </c>
       <c r="G103" s="54">
-        <v>45968</v>
+        <v>45967</v>
       </c>
       <c r="H103" s="55"/>
       <c r="I103" s="56"/>
@@ -18061,16 +18073,14 @@
     </row>
     <row r="104" spans="1:12" ht="22.5" customHeight="1">
       <c r="A104" s="8" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>995</v>
-      </c>
-      <c r="C104" s="51" t="s">
         <v>996</v>
       </c>
+      <c r="C104" s="51"/>
       <c r="D104" s="49" t="s">
-        <v>997</v>
+        <v>733</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>448</v>
@@ -18079,7 +18089,7 @@
         <v>119</v>
       </c>
       <c r="G104" s="54">
-        <v>45967</v>
+        <v>45965</v>
       </c>
       <c r="H104" s="55"/>
       <c r="I104" s="56"/>
@@ -18093,14 +18103,16 @@
     </row>
     <row r="105" spans="1:12" ht="22.5" customHeight="1">
       <c r="A105" s="8" t="s">
-        <v>41</v>
+        <v>646</v>
       </c>
       <c r="B105" s="51" t="s">
+        <v>997</v>
+      </c>
+      <c r="C105" s="51" t="s">
         <v>998</v>
       </c>
-      <c r="C105" s="51"/>
       <c r="D105" s="49" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>448</v>
@@ -18109,12 +18121,12 @@
         <v>119</v>
       </c>
       <c r="G105" s="54">
-        <v>45965</v>
+        <v>45964</v>
       </c>
       <c r="H105" s="55"/>
       <c r="I105" s="56"/>
       <c r="J105" s="53" t="s">
-        <v>16</v>
+        <v>999</v>
       </c>
       <c r="K105" s="51" t="s">
         <v>769</v>
@@ -18123,13 +18135,13 @@
     </row>
     <row r="106" spans="1:12" ht="22.5" customHeight="1">
       <c r="A106" s="8" t="s">
-        <v>646</v>
+        <v>757</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C106" s="51" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D106" s="49" t="s">
         <v>723</v>
@@ -18141,12 +18153,12 @@
         <v>119</v>
       </c>
       <c r="G106" s="54">
-        <v>45964</v>
+        <v>45961</v>
       </c>
       <c r="H106" s="55"/>
       <c r="I106" s="56"/>
       <c r="J106" s="53" t="s">
-        <v>1001</v>
+        <v>74</v>
       </c>
       <c r="K106" s="51" t="s">
         <v>769</v>
@@ -18154,9 +18166,7 @@
       <c r="L106" s="57"/>
     </row>
     <row r="107" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A107" s="8" t="s">
-        <v>757</v>
-      </c>
+      <c r="A107" s="46"/>
       <c r="B107" s="51" t="s">
         <v>1002</v>
       </c>
@@ -18164,7 +18174,7 @@
         <v>1003</v>
       </c>
       <c r="D107" s="49" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>448</v>
@@ -18178,7 +18188,7 @@
       <c r="H107" s="55"/>
       <c r="I107" s="56"/>
       <c r="J107" s="53" t="s">
-        <v>74</v>
+        <v>689</v>
       </c>
       <c r="K107" s="51" t="s">
         <v>769</v>
@@ -18186,63 +18196,67 @@
       <c r="L107" s="57"/>
     </row>
     <row r="108" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A108" s="46"/>
-      <c r="B108" s="51" t="s">
+      <c r="A108" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="B108" s="46" t="s">
         <v>1004</v>
       </c>
-      <c r="C108" s="51" t="s">
+      <c r="C108" s="46" t="s">
         <v>1005</v>
       </c>
-      <c r="D108" s="49" t="s">
-        <v>733</v>
+      <c r="D108" s="10" t="s">
+        <v>1006</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F108" s="53" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="G108" s="54">
-        <v>45961</v>
-      </c>
-      <c r="H108" s="55"/>
-      <c r="I108" s="56"/>
+        <v>45958</v>
+      </c>
+      <c r="H108" s="55">
+        <v>327759</v>
+      </c>
+      <c r="I108" s="56">
+        <v>0.7</v>
+      </c>
       <c r="J108" s="53" t="s">
-        <v>688</v>
-      </c>
-      <c r="K108" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K108" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L108" s="57"/>
     </row>
     <row r="109" spans="1:12" ht="22.5" customHeight="1">
       <c r="A109" s="8" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B109" s="46" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C109" s="46" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D109" s="10" t="s">
         <v>1008</v>
       </c>
+      <c r="D109" s="49" t="s">
+        <v>540</v>
+      </c>
       <c r="E109" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F109" s="53" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="G109" s="54">
-        <v>45958</v>
+        <v>45952</v>
       </c>
       <c r="H109" s="55">
-        <v>327759</v>
-      </c>
-      <c r="I109" s="56">
-        <v>0.7</v>
-      </c>
+        <v>85653</v>
+      </c>
+      <c r="I109" s="56"/>
       <c r="J109" s="53" t="s">
         <v>25</v>
       </c>
@@ -18253,7 +18267,7 @@
     </row>
     <row r="110" spans="1:12" ht="22.5" customHeight="1">
       <c r="A110" s="8" t="s">
-        <v>462</v>
+        <v>552</v>
       </c>
       <c r="B110" s="46" t="s">
         <v>1009</v>
@@ -18262,20 +18276,18 @@
         <v>1010</v>
       </c>
       <c r="D110" s="49" t="s">
-        <v>540</v>
+        <v>896</v>
       </c>
       <c r="E110" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F110" s="53" t="s">
-        <v>24</v>
+        <v>744</v>
       </c>
       <c r="G110" s="54">
         <v>45952</v>
       </c>
-      <c r="H110" s="55">
-        <v>85653</v>
-      </c>
+      <c r="H110" s="55"/>
       <c r="I110" s="56"/>
       <c r="J110" s="53" t="s">
         <v>25</v>
@@ -18287,12 +18299,12 @@
     </row>
     <row r="111" spans="1:12" ht="22.5" customHeight="1">
       <c r="A111" s="8" t="s">
-        <v>552</v>
-      </c>
-      <c r="B111" s="46" t="s">
+        <v>534</v>
+      </c>
+      <c r="B111" s="51" t="s">
         <v>1011</v>
       </c>
-      <c r="C111" s="46" t="s">
+      <c r="C111" s="51" t="s">
         <v>1012</v>
       </c>
       <c r="D111" s="49" t="s">
@@ -18302,24 +18314,24 @@
         <v>448</v>
       </c>
       <c r="F111" s="53" t="s">
-        <v>744</v>
+        <v>449</v>
       </c>
       <c r="G111" s="54">
-        <v>45952</v>
+        <v>45947</v>
       </c>
       <c r="H111" s="55"/>
       <c r="I111" s="56"/>
       <c r="J111" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K111" s="46" t="s">
+      <c r="K111" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L111" s="57"/>
     </row>
     <row r="112" spans="1:12" ht="22.5" customHeight="1">
       <c r="A112" s="8" t="s">
-        <v>534</v>
+        <v>594</v>
       </c>
       <c r="B112" s="51" t="s">
         <v>1013</v>
@@ -18328,13 +18340,13 @@
         <v>1014</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>896</v>
+        <v>540</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F112" s="53" t="s">
-        <v>449</v>
+        <v>119</v>
       </c>
       <c r="G112" s="54">
         <v>45947</v>
@@ -18351,7 +18363,7 @@
     </row>
     <row r="113" spans="1:12" ht="22.5" customHeight="1">
       <c r="A113" s="8" t="s">
-        <v>594</v>
+        <v>642</v>
       </c>
       <c r="B113" s="51" t="s">
         <v>1015</v>
@@ -18360,7 +18372,7 @@
         <v>1016</v>
       </c>
       <c r="D113" s="49" t="s">
-        <v>540</v>
+        <v>723</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>448</v>
@@ -18369,7 +18381,7 @@
         <v>119</v>
       </c>
       <c r="G113" s="54">
-        <v>45947</v>
+        <v>45946</v>
       </c>
       <c r="H113" s="55"/>
       <c r="I113" s="56"/>
@@ -18383,51 +18395,51 @@
     </row>
     <row r="114" spans="1:12" ht="22.5" customHeight="1">
       <c r="A114" s="8" t="s">
-        <v>642</v>
-      </c>
-      <c r="B114" s="51" t="s">
+        <v>531</v>
+      </c>
+      <c r="B114" s="46" t="s">
         <v>1017</v>
       </c>
-      <c r="C114" s="51" t="s">
+      <c r="C114" s="46" t="s">
         <v>1018</v>
       </c>
       <c r="D114" s="49" t="s">
-        <v>723</v>
+        <v>896</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>448</v>
+        <v>859</v>
       </c>
       <c r="F114" s="53" t="s">
         <v>119</v>
       </c>
       <c r="G114" s="54">
-        <v>45946</v>
+        <v>45945</v>
       </c>
       <c r="H114" s="55"/>
       <c r="I114" s="56"/>
       <c r="J114" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K114" s="51" t="s">
+      <c r="K114" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L114" s="57"/>
     </row>
     <row r="115" spans="1:12" ht="22.5" customHeight="1">
       <c r="A115" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="B115" s="46" t="s">
+        <v>766</v>
+      </c>
+      <c r="B115" s="51" t="s">
         <v>1019</v>
       </c>
-      <c r="C115" s="46" t="s">
+      <c r="C115" s="51" t="s">
         <v>1020</v>
       </c>
       <c r="D115" s="49" t="s">
-        <v>896</v>
+        <v>960</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>859</v>
+        <v>448</v>
       </c>
       <c r="F115" s="53" t="s">
         <v>119</v>
@@ -18438,16 +18450,16 @@
       <c r="H115" s="55"/>
       <c r="I115" s="56"/>
       <c r="J115" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="K115" s="46" t="s">
+        <v>745</v>
+      </c>
+      <c r="K115" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L115" s="57"/>
     </row>
     <row r="116" spans="1:12" ht="22.5" customHeight="1">
       <c r="A116" s="8" t="s">
-        <v>766</v>
+        <v>94</v>
       </c>
       <c r="B116" s="51" t="s">
         <v>1021</v>
@@ -18456,21 +18468,21 @@
         <v>1022</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>962</v>
+        <v>1023</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>448</v>
+        <v>1024</v>
       </c>
       <c r="F116" s="53" t="s">
         <v>119</v>
       </c>
       <c r="G116" s="54">
-        <v>45945</v>
+        <v>45944</v>
       </c>
       <c r="H116" s="55"/>
       <c r="I116" s="56"/>
       <c r="J116" s="53" t="s">
-        <v>745</v>
+        <v>25</v>
       </c>
       <c r="K116" s="51" t="s">
         <v>769</v>
@@ -18479,88 +18491,88 @@
     </row>
     <row r="117" spans="1:12" ht="22.5" customHeight="1">
       <c r="A117" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B117" s="51" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C117" s="51" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D117" s="49" t="s">
+        <v>454</v>
+      </c>
+      <c r="B117" s="46" t="s">
         <v>1025</v>
       </c>
+      <c r="C117" s="46" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D117" s="10" t="s">
+        <v>1027</v>
+      </c>
       <c r="E117" s="10" t="s">
-        <v>1026</v>
+        <v>448</v>
       </c>
       <c r="F117" s="53" t="s">
-        <v>119</v>
+        <v>744</v>
       </c>
       <c r="G117" s="54">
-        <v>45944</v>
-      </c>
-      <c r="H117" s="55"/>
+        <v>45940</v>
+      </c>
+      <c r="H117" s="55">
+        <v>459065</v>
+      </c>
       <c r="I117" s="56"/>
       <c r="J117" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K117" s="51" t="s">
+      <c r="K117" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L117" s="57"/>
     </row>
     <row r="118" spans="1:12" ht="22.5" customHeight="1">
       <c r="A118" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="B118" s="46" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C118" s="46" t="s">
+        <v>585</v>
+      </c>
+      <c r="B118" s="51" t="s">
         <v>1028</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="C118" s="51" t="s">
         <v>1029</v>
       </c>
+      <c r="D118" s="49" t="s">
+        <v>1030</v>
+      </c>
       <c r="E118" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F118" s="53" t="s">
-        <v>744</v>
+        <v>480</v>
       </c>
       <c r="G118" s="54">
         <v>45940</v>
       </c>
-      <c r="H118" s="55">
-        <v>459065</v>
-      </c>
+      <c r="H118" s="55"/>
       <c r="I118" s="56"/>
       <c r="J118" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K118" s="46" t="s">
+      <c r="K118" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L118" s="57"/>
     </row>
     <row r="119" spans="1:12" ht="22.5" customHeight="1">
       <c r="A119" s="8" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C119" s="51" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D119" s="49" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F119" s="53" t="s">
-        <v>480</v>
+        <v>119</v>
       </c>
       <c r="G119" s="54">
         <v>45940</v>
@@ -18577,30 +18589,30 @@
     </row>
     <row r="120" spans="1:12" ht="22.5" customHeight="1">
       <c r="A120" s="8" t="s">
-        <v>591</v>
+        <v>91</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C120" s="51" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>1035</v>
+        <v>540</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F120" s="53" t="s">
-        <v>119</v>
+        <v>480</v>
       </c>
       <c r="G120" s="54">
-        <v>45940</v>
+        <v>45938</v>
       </c>
       <c r="H120" s="55"/>
       <c r="I120" s="56"/>
       <c r="J120" s="53" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K120" s="51" t="s">
         <v>769</v>
@@ -18609,82 +18621,82 @@
     </row>
     <row r="121" spans="1:12" ht="22.5" customHeight="1">
       <c r="A121" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B121" s="51" t="s">
+        <v>457</v>
+      </c>
+      <c r="B121" s="46" t="s">
         <v>1036</v>
       </c>
-      <c r="C121" s="51" t="s">
+      <c r="C121" s="46" t="s">
         <v>1037</v>
       </c>
       <c r="D121" s="49" t="s">
-        <v>540</v>
+        <v>896</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F121" s="53" t="s">
-        <v>480</v>
+        <v>744</v>
       </c>
       <c r="G121" s="54">
-        <v>45938</v>
-      </c>
-      <c r="H121" s="55"/>
+        <v>45933</v>
+      </c>
+      <c r="H121" s="55">
+        <v>282665</v>
+      </c>
       <c r="I121" s="56"/>
       <c r="J121" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="K121" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K121" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L121" s="57"/>
     </row>
     <row r="122" spans="1:12" ht="22.5" customHeight="1">
       <c r="A122" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="B122" s="46" t="s">
+        <v>652</v>
+      </c>
+      <c r="B122" s="51" t="s">
         <v>1038</v>
       </c>
-      <c r="C122" s="46" t="s">
+      <c r="C122" s="51" t="s">
         <v>1039</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>896</v>
+        <v>733</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F122" s="53" t="s">
-        <v>744</v>
+        <v>119</v>
       </c>
       <c r="G122" s="54">
-        <v>45933</v>
-      </c>
-      <c r="H122" s="55">
-        <v>282665</v>
-      </c>
+        <v>45932</v>
+      </c>
+      <c r="H122" s="55"/>
       <c r="I122" s="56"/>
       <c r="J122" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="K122" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="K122" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L122" s="57"/>
     </row>
     <row r="123" spans="1:12" ht="22.5" customHeight="1">
       <c r="A123" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="B123" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="B123" s="46" t="s">
         <v>1040</v>
       </c>
-      <c r="C123" s="51" t="s">
+      <c r="C123" s="46" t="s">
         <v>1041</v>
       </c>
       <c r="D123" s="49" t="s">
-        <v>733</v>
+        <v>540</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>448</v>
@@ -18693,30 +18705,30 @@
         <v>119</v>
       </c>
       <c r="G123" s="54">
-        <v>45932</v>
+        <v>45931</v>
       </c>
       <c r="H123" s="55"/>
       <c r="I123" s="56"/>
       <c r="J123" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="K123" s="51" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K123" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L123" s="57"/>
     </row>
     <row r="124" spans="1:12" ht="22.5" customHeight="1">
       <c r="A124" s="8" t="s">
-        <v>37</v>
+        <v>765</v>
       </c>
       <c r="B124" s="46" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C124" s="46" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D124" s="49" t="s">
-        <v>540</v>
+        <v>733</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>448</v>
@@ -18725,12 +18737,12 @@
         <v>119</v>
       </c>
       <c r="G124" s="54">
-        <v>45931</v>
+        <v>45929</v>
       </c>
       <c r="H124" s="55"/>
       <c r="I124" s="56"/>
       <c r="J124" s="53" t="s">
-        <v>1044</v>
+        <v>513</v>
       </c>
       <c r="K124" s="46" t="s">
         <v>769</v>
@@ -18739,16 +18751,16 @@
     </row>
     <row r="125" spans="1:12" ht="22.5" customHeight="1">
       <c r="A125" s="8" t="s">
-        <v>765</v>
-      </c>
-      <c r="B125" s="46" t="s">
+        <v>760</v>
+      </c>
+      <c r="B125" s="51" t="s">
         <v>1045</v>
       </c>
-      <c r="C125" s="46" t="s">
+      <c r="C125" s="51" t="s">
         <v>1046</v>
       </c>
       <c r="D125" s="49" t="s">
-        <v>733</v>
+        <v>540</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>448</v>
@@ -18757,21 +18769,21 @@
         <v>119</v>
       </c>
       <c r="G125" s="54">
-        <v>45929</v>
+        <v>45926</v>
       </c>
       <c r="H125" s="55"/>
       <c r="I125" s="56"/>
       <c r="J125" s="53" t="s">
-        <v>513</v>
-      </c>
-      <c r="K125" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="K125" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L125" s="57"/>
     </row>
     <row r="126" spans="1:12" ht="22.5" customHeight="1">
       <c r="A126" s="8" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B126" s="51" t="s">
         <v>1047</v>
@@ -18780,7 +18792,7 @@
         <v>1048</v>
       </c>
       <c r="D126" s="49" t="s">
-        <v>540</v>
+        <v>733</v>
       </c>
       <c r="E126" s="10" t="s">
         <v>448</v>
@@ -18789,7 +18801,7 @@
         <v>119</v>
       </c>
       <c r="G126" s="54">
-        <v>45926</v>
+        <v>45924</v>
       </c>
       <c r="H126" s="55"/>
       <c r="I126" s="56"/>
@@ -18803,7 +18815,7 @@
     </row>
     <row r="127" spans="1:12" ht="22.5" customHeight="1">
       <c r="A127" s="8" t="s">
-        <v>759</v>
+        <v>168</v>
       </c>
       <c r="B127" s="51" t="s">
         <v>1049</v>
@@ -18821,12 +18833,12 @@
         <v>119</v>
       </c>
       <c r="G127" s="54">
-        <v>45924</v>
+        <v>45919</v>
       </c>
       <c r="H127" s="55"/>
       <c r="I127" s="56"/>
       <c r="J127" s="53" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="K127" s="51" t="s">
         <v>769</v>
@@ -18835,7 +18847,7 @@
     </row>
     <row r="128" spans="1:12" ht="22.5" customHeight="1">
       <c r="A128" s="8" t="s">
-        <v>168</v>
+        <v>756</v>
       </c>
       <c r="B128" s="51" t="s">
         <v>1051</v>
@@ -18843,8 +18855,8 @@
       <c r="C128" s="51" t="s">
         <v>1052</v>
       </c>
-      <c r="D128" s="49" t="s">
-        <v>733</v>
+      <c r="D128" s="10" t="s">
+        <v>1053</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>448</v>
@@ -18853,12 +18865,12 @@
         <v>119</v>
       </c>
       <c r="G128" s="54">
-        <v>45919</v>
+        <v>45917</v>
       </c>
       <c r="H128" s="55"/>
       <c r="I128" s="56"/>
       <c r="J128" s="53" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="K128" s="51" t="s">
         <v>769</v>
@@ -18867,16 +18879,16 @@
     </row>
     <row r="129" spans="1:12" ht="22.5" customHeight="1">
       <c r="A129" s="8" t="s">
-        <v>756</v>
+        <v>641</v>
       </c>
       <c r="B129" s="51" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C129" s="51" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>448</v>
@@ -18885,7 +18897,7 @@
         <v>119</v>
       </c>
       <c r="G129" s="54">
-        <v>45917</v>
+        <v>45912</v>
       </c>
       <c r="H129" s="55"/>
       <c r="I129" s="56"/>
@@ -18899,16 +18911,16 @@
     </row>
     <row r="130" spans="1:12" ht="22.5" customHeight="1">
       <c r="A130" s="8" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="B130" s="51" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D130" s="10" t="s">
         <v>1058</v>
+      </c>
+      <c r="D130" s="49" t="s">
+        <v>718</v>
       </c>
       <c r="E130" s="10" t="s">
         <v>448</v>
@@ -18917,7 +18929,7 @@
         <v>119</v>
       </c>
       <c r="G130" s="54">
-        <v>45912</v>
+        <v>45909</v>
       </c>
       <c r="H130" s="55"/>
       <c r="I130" s="56"/>
@@ -18931,7 +18943,7 @@
     </row>
     <row r="131" spans="1:12" ht="22.5" customHeight="1">
       <c r="A131" s="8" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B131" s="51" t="s">
         <v>1059</v>
@@ -18940,7 +18952,7 @@
         <v>1060</v>
       </c>
       <c r="D131" s="49" t="s">
-        <v>718</v>
+        <v>995</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>448</v>
@@ -18949,12 +18961,12 @@
         <v>119</v>
       </c>
       <c r="G131" s="54">
-        <v>45909</v>
+        <v>45897</v>
       </c>
       <c r="H131" s="55"/>
       <c r="I131" s="56"/>
       <c r="J131" s="53" t="s">
-        <v>25</v>
+        <v>513</v>
       </c>
       <c r="K131" s="51" t="s">
         <v>769</v>
@@ -18963,7 +18975,7 @@
     </row>
     <row r="132" spans="1:12" ht="22.5" customHeight="1">
       <c r="A132" s="8" t="s">
-        <v>627</v>
+        <v>555</v>
       </c>
       <c r="B132" s="51" t="s">
         <v>1061</v>
@@ -18972,21 +18984,23 @@
         <v>1062</v>
       </c>
       <c r="D132" s="49" t="s">
-        <v>997</v>
+        <v>540</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F132" s="53" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="G132" s="54">
-        <v>45897</v>
-      </c>
-      <c r="H132" s="55"/>
+        <v>45868</v>
+      </c>
+      <c r="H132" s="55">
+        <v>3560</v>
+      </c>
       <c r="I132" s="56"/>
       <c r="J132" s="53" t="s">
-        <v>513</v>
+        <v>25</v>
       </c>
       <c r="K132" s="51" t="s">
         <v>769</v>
@@ -18995,7 +19009,7 @@
     </row>
     <row r="133" spans="1:12" ht="22.5" customHeight="1">
       <c r="A133" s="8" t="s">
-        <v>555</v>
+        <v>160</v>
       </c>
       <c r="B133" s="51" t="s">
         <v>1063</v>
@@ -19004,23 +19018,21 @@
         <v>1064</v>
       </c>
       <c r="D133" s="49" t="s">
-        <v>540</v>
+        <v>1065</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F133" s="53" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="G133" s="54">
         <v>45868</v>
       </c>
-      <c r="H133" s="55">
-        <v>3560</v>
-      </c>
+      <c r="H133" s="55"/>
       <c r="I133" s="56"/>
       <c r="J133" s="53" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K133" s="51" t="s">
         <v>769</v>
@@ -19029,84 +19041,82 @@
     </row>
     <row r="134" spans="1:12" ht="22.5" customHeight="1">
       <c r="A134" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="B134" s="51" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C134" s="51" t="s">
+        <v>451</v>
+      </c>
+      <c r="B134" s="46" t="s">
         <v>1066</v>
       </c>
+      <c r="C134" s="46" t="s">
+        <v>1067</v>
+      </c>
       <c r="D134" s="49" t="s">
-        <v>1067</v>
+        <v>540</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F134" s="53" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="G134" s="54">
-        <v>45868</v>
-      </c>
-      <c r="H134" s="55"/>
-      <c r="I134" s="56"/>
+        <v>45862</v>
+      </c>
+      <c r="H134" s="61">
+        <v>370375</v>
+      </c>
+      <c r="I134" s="56">
+        <v>0.8</v>
+      </c>
       <c r="J134" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="K134" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K134" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L134" s="57"/>
     </row>
     <row r="135" spans="1:12" ht="22.5" customHeight="1">
       <c r="A135" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="B135" s="46" t="s">
+        <v>547</v>
+      </c>
+      <c r="B135" s="51" t="s">
         <v>1068</v>
       </c>
-      <c r="C135" s="46" t="s">
+      <c r="C135" s="51" t="s">
         <v>1069</v>
       </c>
       <c r="D135" s="49" t="s">
-        <v>540</v>
+        <v>1070</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F135" s="53" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="G135" s="54">
-        <v>45862</v>
-      </c>
-      <c r="H135" s="61">
-        <v>370375</v>
-      </c>
-      <c r="I135" s="56">
-        <v>0.8</v>
-      </c>
+        <v>45855</v>
+      </c>
+      <c r="H135" s="55"/>
+      <c r="I135" s="56"/>
       <c r="J135" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K135" s="46" t="s">
+      <c r="K135" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L135" s="57"/>
     </row>
     <row r="136" spans="1:12" ht="22.5" customHeight="1">
       <c r="A136" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="B136" s="51" t="s">
-        <v>1070</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="B136" s="51"/>
       <c r="C136" s="51" t="s">
         <v>1071</v>
       </c>
       <c r="D136" s="49" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>448</v>
@@ -19129,14 +19139,16 @@
     </row>
     <row r="137" spans="1:12" ht="22.5" customHeight="1">
       <c r="A137" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B137" s="51"/>
+        <v>541</v>
+      </c>
+      <c r="B137" s="51" t="s">
+        <v>1072</v>
+      </c>
       <c r="C137" s="51" t="s">
         <v>1073</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>1067</v>
+        <v>896</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>448</v>
@@ -19145,12 +19157,12 @@
         <v>119</v>
       </c>
       <c r="G137" s="54">
-        <v>45855</v>
+        <v>45824</v>
       </c>
       <c r="H137" s="55"/>
       <c r="I137" s="56"/>
       <c r="J137" s="53" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="K137" s="51" t="s">
         <v>769</v>
@@ -19159,105 +19171,109 @@
     </row>
     <row r="138" spans="1:12" ht="22.5" customHeight="1">
       <c r="A138" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="B138" s="51" t="s">
+        <v>477</v>
+      </c>
+      <c r="B138" s="46" t="s">
         <v>1074</v>
       </c>
-      <c r="C138" s="51" t="s">
+      <c r="C138" s="46" t="s">
         <v>1075</v>
       </c>
       <c r="D138" s="49" t="s">
-        <v>896</v>
+        <v>540</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F138" s="53" t="s">
-        <v>119</v>
+        <v>744</v>
       </c>
       <c r="G138" s="54">
-        <v>45824</v>
-      </c>
-      <c r="H138" s="55"/>
+        <v>45822</v>
+      </c>
+      <c r="H138" s="55">
+        <v>198958</v>
+      </c>
       <c r="I138" s="56"/>
       <c r="J138" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="K138" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K138" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L138" s="57"/>
     </row>
     <row r="139" spans="1:12" ht="22.5" customHeight="1">
       <c r="A139" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="B139" s="46" t="s">
+        <v>654</v>
+      </c>
+      <c r="B139" s="51" t="s">
         <v>1076</v>
       </c>
-      <c r="C139" s="46" t="s">
+      <c r="C139" s="51" t="s">
+        <v>410</v>
+      </c>
+      <c r="D139" s="10" t="s">
         <v>1077</v>
       </c>
-      <c r="D139" s="49" t="s">
-        <v>540</v>
-      </c>
       <c r="E139" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F139" s="53" t="s">
-        <v>744</v>
+        <v>119</v>
       </c>
       <c r="G139" s="54">
-        <v>45822</v>
-      </c>
-      <c r="H139" s="55">
-        <v>198958</v>
-      </c>
+        <v>45814</v>
+      </c>
+      <c r="H139" s="55"/>
       <c r="I139" s="56"/>
       <c r="J139" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="K139" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="K139" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L139" s="57"/>
     </row>
     <row r="140" spans="1:12" ht="22.5" customHeight="1">
       <c r="A140" s="8" t="s">
-        <v>654</v>
-      </c>
-      <c r="B140" s="51" t="s">
+        <v>491</v>
+      </c>
+      <c r="B140" s="46" t="s">
         <v>1078</v>
       </c>
-      <c r="C140" s="51" t="s">
-        <v>410</v>
-      </c>
-      <c r="D140" s="10" t="s">
+      <c r="C140" s="46" t="s">
         <v>1079</v>
       </c>
+      <c r="D140" s="49" t="s">
+        <v>896</v>
+      </c>
       <c r="E140" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F140" s="53" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="G140" s="54">
-        <v>45814</v>
-      </c>
-      <c r="H140" s="55"/>
-      <c r="I140" s="56"/>
+        <v>45791</v>
+      </c>
+      <c r="H140" s="55">
+        <v>24369</v>
+      </c>
+      <c r="I140" s="56">
+        <v>0.8</v>
+      </c>
       <c r="J140" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="K140" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K140" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L140" s="57"/>
     </row>
     <row r="141" spans="1:12" ht="22.5" customHeight="1">
       <c r="A141" s="8" t="s">
-        <v>491</v>
+        <v>471</v>
       </c>
       <c r="B141" s="46" t="s">
         <v>1080</v>
@@ -19265,8 +19281,8 @@
       <c r="C141" s="46" t="s">
         <v>1081</v>
       </c>
-      <c r="D141" s="49" t="s">
-        <v>896</v>
+      <c r="D141" s="10" t="s">
+        <v>1082</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>448</v>
@@ -19275,14 +19291,12 @@
         <v>24</v>
       </c>
       <c r="G141" s="54">
-        <v>45791</v>
+        <v>45784</v>
       </c>
       <c r="H141" s="55">
-        <v>24369</v>
-      </c>
-      <c r="I141" s="56">
-        <v>0.8</v>
-      </c>
+        <v>588274</v>
+      </c>
+      <c r="I141" s="56"/>
       <c r="J141" s="53" t="s">
         <v>25</v>
       </c>
@@ -19293,28 +19307,28 @@
     </row>
     <row r="142" spans="1:12" ht="22.5" customHeight="1">
       <c r="A142" s="8" t="s">
-        <v>471</v>
+        <v>668</v>
       </c>
       <c r="B142" s="46" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C142" s="46" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>1084</v>
+        <v>718</v>
       </c>
       <c r="E142" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F142" s="53" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G142" s="54">
-        <v>45784</v>
+        <v>45775</v>
       </c>
       <c r="H142" s="55">
-        <v>588274</v>
+        <v>117537</v>
       </c>
       <c r="I142" s="56"/>
       <c r="J142" s="53" t="s">
@@ -19327,41 +19341,39 @@
     </row>
     <row r="143" spans="1:12" ht="22.5" customHeight="1">
       <c r="A143" s="8" t="s">
-        <v>667</v>
-      </c>
-      <c r="B143" s="46" t="s">
+        <v>123</v>
+      </c>
+      <c r="B143" s="51" t="s">
         <v>1085</v>
       </c>
-      <c r="C143" s="46" t="s">
+      <c r="C143" s="51" t="s">
         <v>1086</v>
       </c>
-      <c r="D143" s="10" t="s">
-        <v>718</v>
+      <c r="D143" s="49" t="s">
+        <v>540</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F143" s="53" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="G143" s="54">
-        <v>45775</v>
-      </c>
-      <c r="H143" s="55">
-        <v>117537</v>
-      </c>
+        <v>45770</v>
+      </c>
+      <c r="H143" s="55"/>
       <c r="I143" s="56"/>
       <c r="J143" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="K143" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="K143" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L143" s="57"/>
     </row>
     <row r="144" spans="1:12" ht="22.5" customHeight="1">
       <c r="A144" s="8" t="s">
-        <v>123</v>
+        <v>544</v>
       </c>
       <c r="B144" s="51" t="s">
         <v>1087</v>
@@ -19379,12 +19391,12 @@
         <v>119</v>
       </c>
       <c r="G144" s="54">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H144" s="55"/>
       <c r="I144" s="56"/>
       <c r="J144" s="53" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K144" s="51" t="s">
         <v>769</v>
@@ -19392,9 +19404,7 @@
       <c r="L144" s="57"/>
     </row>
     <row r="145" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A145" s="8" t="s">
-        <v>544</v>
-      </c>
+      <c r="A145" s="46"/>
       <c r="B145" s="51" t="s">
         <v>1089</v>
       </c>
@@ -19402,16 +19412,16 @@
         <v>1090</v>
       </c>
       <c r="D145" s="49" t="s">
-        <v>540</v>
+        <v>733</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F145" s="53" t="s">
-        <v>119</v>
+        <v>744</v>
       </c>
       <c r="G145" s="54">
-        <v>45769</v>
+        <v>45736</v>
       </c>
       <c r="H145" s="55"/>
       <c r="I145" s="56"/>
@@ -19424,15 +19434,17 @@
       <c r="L145" s="57"/>
     </row>
     <row r="146" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A146" s="46"/>
-      <c r="B146" s="51" t="s">
+      <c r="A146" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="B146" s="46" t="s">
         <v>1091</v>
       </c>
-      <c r="C146" s="51" t="s">
+      <c r="C146" s="46" t="s">
         <v>1092</v>
       </c>
       <c r="D146" s="49" t="s">
-        <v>733</v>
+        <v>540</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>448</v>
@@ -19441,55 +19453,55 @@
         <v>744</v>
       </c>
       <c r="G146" s="54">
-        <v>45736</v>
-      </c>
-      <c r="H146" s="55"/>
+        <v>45700</v>
+      </c>
+      <c r="H146" s="55">
+        <v>29297</v>
+      </c>
       <c r="I146" s="56"/>
       <c r="J146" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K146" s="51" t="s">
+      <c r="K146" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L146" s="57"/>
     </row>
     <row r="147" spans="1:12" ht="22.5" customHeight="1">
       <c r="A147" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="B147" s="46" t="s">
+        <v>636</v>
+      </c>
+      <c r="B147" s="51" t="s">
         <v>1093</v>
       </c>
-      <c r="C147" s="46" t="s">
+      <c r="C147" s="51" t="s">
         <v>1094</v>
       </c>
       <c r="D147" s="49" t="s">
-        <v>540</v>
+        <v>851</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F147" s="53" t="s">
-        <v>744</v>
+        <v>119</v>
       </c>
       <c r="G147" s="54">
-        <v>45700</v>
-      </c>
-      <c r="H147" s="55">
-        <v>29297</v>
-      </c>
+        <v>45699</v>
+      </c>
+      <c r="H147" s="55"/>
       <c r="I147" s="56"/>
       <c r="J147" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="K147" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="K147" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L147" s="57"/>
     </row>
     <row r="148" spans="1:12" ht="22.5" customHeight="1">
       <c r="A148" s="8" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B148" s="51" t="s">
         <v>1095</v>
@@ -19498,21 +19510,21 @@
         <v>1096</v>
       </c>
       <c r="D148" s="49" t="s">
-        <v>851</v>
+        <v>896</v>
       </c>
       <c r="E148" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F148" s="53" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="G148" s="54">
-        <v>45699</v>
+        <v>45693</v>
       </c>
       <c r="H148" s="55"/>
       <c r="I148" s="56"/>
       <c r="J148" s="53" t="s">
-        <v>16</v>
+        <v>777</v>
       </c>
       <c r="K148" s="51" t="s">
         <v>769</v>
@@ -19521,12 +19533,12 @@
     </row>
     <row r="149" spans="1:12" ht="22.5" customHeight="1">
       <c r="A149" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="B149" s="51" t="s">
+        <v>497</v>
+      </c>
+      <c r="B149" s="46" t="s">
         <v>1097</v>
       </c>
-      <c r="C149" s="51" t="s">
+      <c r="C149" s="46" t="s">
         <v>1098</v>
       </c>
       <c r="D149" s="49" t="s">
@@ -19539,33 +19551,37 @@
         <v>24</v>
       </c>
       <c r="G149" s="54">
-        <v>45693</v>
-      </c>
-      <c r="H149" s="55"/>
-      <c r="I149" s="56"/>
+        <v>45637</v>
+      </c>
+      <c r="H149" s="55">
+        <v>30783</v>
+      </c>
+      <c r="I149" s="56">
+        <v>0.5</v>
+      </c>
       <c r="J149" s="53" t="s">
-        <v>777</v>
-      </c>
-      <c r="K149" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K149" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L149" s="57"/>
     </row>
     <row r="150" spans="1:12" ht="22.5" customHeight="1">
       <c r="A150" s="8" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B150" s="46" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C150" s="46" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="D150" s="49" t="s">
         <v>896</v>
       </c>
       <c r="E150" s="10" t="s">
-        <v>448</v>
+        <v>935</v>
       </c>
       <c r="F150" s="53" t="s">
         <v>24</v>
@@ -19573,9 +19589,7 @@
       <c r="G150" s="54">
         <v>45637</v>
       </c>
-      <c r="H150" s="55">
-        <v>30783</v>
-      </c>
+      <c r="H150" s="55"/>
       <c r="I150" s="56">
         <v>0.5</v>
       </c>
@@ -19589,41 +19603,39 @@
     </row>
     <row r="151" spans="1:12" ht="22.5" customHeight="1">
       <c r="A151" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="B151" s="46" t="s">
+        <v>651</v>
+      </c>
+      <c r="B151" s="51" t="s">
         <v>1099</v>
       </c>
-      <c r="C151" s="46" t="s">
+      <c r="C151" s="51" t="s">
         <v>1100</v>
       </c>
       <c r="D151" s="49" t="s">
-        <v>896</v>
+        <v>952</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>937</v>
+        <v>448</v>
       </c>
       <c r="F151" s="53" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="G151" s="54">
-        <v>45637</v>
+        <v>45560</v>
       </c>
       <c r="H151" s="55"/>
-      <c r="I151" s="56">
-        <v>0.5</v>
-      </c>
+      <c r="I151" s="56"/>
       <c r="J151" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K151" s="46" t="s">
+      <c r="K151" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L151" s="57"/>
     </row>
     <row r="152" spans="1:12" ht="22.5" customHeight="1">
       <c r="A152" s="8" t="s">
-        <v>651</v>
+        <v>588</v>
       </c>
       <c r="B152" s="51" t="s">
         <v>1101</v>
@@ -19632,16 +19644,16 @@
         <v>1102</v>
       </c>
       <c r="D152" s="49" t="s">
-        <v>954</v>
+        <v>526</v>
       </c>
       <c r="E152" s="10" t="s">
-        <v>448</v>
+        <v>859</v>
       </c>
       <c r="F152" s="53" t="s">
         <v>119</v>
       </c>
       <c r="G152" s="54">
-        <v>45560</v>
+        <v>45553</v>
       </c>
       <c r="H152" s="55"/>
       <c r="I152" s="56"/>
@@ -19655,64 +19667,68 @@
     </row>
     <row r="153" spans="1:12" ht="22.5" customHeight="1">
       <c r="A153" s="8" t="s">
-        <v>588</v>
-      </c>
-      <c r="B153" s="51" t="s">
+        <v>481</v>
+      </c>
+      <c r="B153" s="46" t="s">
         <v>1103</v>
       </c>
-      <c r="C153" s="51" t="s">
+      <c r="C153" s="46" t="s">
         <v>1104</v>
       </c>
       <c r="D153" s="49" t="s">
         <v>526</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>859</v>
+        <v>448</v>
       </c>
       <c r="F153" s="53" t="s">
-        <v>119</v>
+        <v>744</v>
       </c>
       <c r="G153" s="54">
-        <v>45553</v>
-      </c>
-      <c r="H153" s="55"/>
+        <v>45519</v>
+      </c>
+      <c r="H153" s="55">
+        <v>466101</v>
+      </c>
       <c r="I153" s="56"/>
       <c r="J153" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K153" s="51" t="s">
+      <c r="K153" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L153" s="57"/>
     </row>
     <row r="154" spans="1:12" ht="22.5" customHeight="1">
       <c r="A154" s="8" t="s">
-        <v>481</v>
+        <v>517</v>
       </c>
       <c r="B154" s="46" t="s">
         <v>1105</v>
       </c>
       <c r="C154" s="46" t="s">
+        <v>483</v>
+      </c>
+      <c r="D154" s="49" t="s">
+        <v>896</v>
+      </c>
+      <c r="E154" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F154" s="53" t="s">
         <v>1106</v>
       </c>
-      <c r="D154" s="49" t="s">
-        <v>526</v>
-      </c>
-      <c r="E154" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="F154" s="53" t="s">
-        <v>744</v>
-      </c>
       <c r="G154" s="54">
-        <v>45519</v>
+        <v>45516</v>
       </c>
       <c r="H154" s="55">
-        <v>466101</v>
-      </c>
-      <c r="I154" s="56"/>
+        <v>8620</v>
+      </c>
+      <c r="I154" s="56">
+        <v>1</v>
+      </c>
       <c r="J154" s="53" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="K154" s="46" t="s">
         <v>769</v>
@@ -19721,118 +19737,114 @@
     </row>
     <row r="155" spans="1:12" ht="22.5" customHeight="1">
       <c r="A155" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="B155" s="46" t="s">
+        <v>761</v>
+      </c>
+      <c r="B155" s="51" t="s">
         <v>1107</v>
       </c>
-      <c r="C155" s="46" t="s">
-        <v>483</v>
+      <c r="C155" s="51" t="s">
+        <v>1108</v>
       </c>
       <c r="D155" s="49" t="s">
-        <v>896</v>
+        <v>1109</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>448</v>
+        <v>852</v>
       </c>
       <c r="F155" s="53" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="G155" s="54">
         <v>45516</v>
       </c>
-      <c r="H155" s="55">
-        <v>8620</v>
-      </c>
-      <c r="I155" s="56">
-        <v>1</v>
-      </c>
+      <c r="H155" s="55"/>
+      <c r="I155" s="56"/>
       <c r="J155" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="K155" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="K155" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L155" s="57"/>
     </row>
     <row r="156" spans="1:12" ht="22.5" customHeight="1">
       <c r="A156" s="8" t="s">
-        <v>761</v>
-      </c>
-      <c r="B156" s="51" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C156" s="51" t="s">
-        <v>1109</v>
+        <v>514</v>
+      </c>
+      <c r="B156" s="46" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C156" s="46" t="s">
+        <v>483</v>
       </c>
       <c r="D156" s="49" t="s">
-        <v>1110</v>
+        <v>896</v>
       </c>
       <c r="E156" s="10" t="s">
-        <v>852</v>
+        <v>448</v>
       </c>
       <c r="F156" s="53" t="s">
-        <v>119</v>
+        <v>744</v>
       </c>
       <c r="G156" s="54">
-        <v>45516</v>
-      </c>
-      <c r="H156" s="55"/>
+        <v>45513</v>
+      </c>
+      <c r="H156" s="55">
+        <v>41051</v>
+      </c>
       <c r="I156" s="56"/>
       <c r="J156" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="K156" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="K156" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L156" s="57"/>
     </row>
     <row r="157" spans="1:12" ht="22.5" customHeight="1">
       <c r="A157" s="8" t="s">
-        <v>514</v>
-      </c>
-      <c r="B157" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="B157" s="51" t="s">
         <v>1111</v>
       </c>
-      <c r="C157" s="46" t="s">
-        <v>483</v>
-      </c>
-      <c r="D157" s="49" t="s">
-        <v>896</v>
+      <c r="C157" s="51" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D157" s="10" t="s">
+        <v>1113</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F157" s="53" t="s">
-        <v>744</v>
+        <v>119</v>
       </c>
       <c r="G157" s="54">
-        <v>45513</v>
-      </c>
-      <c r="H157" s="55">
-        <v>41051</v>
-      </c>
+        <v>45449</v>
+      </c>
+      <c r="H157" s="55"/>
       <c r="I157" s="56"/>
       <c r="J157" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="K157" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="K157" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L157" s="57"/>
     </row>
     <row r="158" spans="1:12" ht="22.5" customHeight="1">
       <c r="A158" s="8" t="s">
-        <v>166</v>
+        <v>618</v>
       </c>
       <c r="B158" s="51" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>1113</v>
-      </c>
-      <c r="D158" s="10" t="s">
-        <v>1114</v>
+        <v>1115</v>
+      </c>
+      <c r="D158" s="49" t="s">
+        <v>896</v>
       </c>
       <c r="E158" s="10" t="s">
         <v>448</v>
@@ -19841,12 +19853,12 @@
         <v>119</v>
       </c>
       <c r="G158" s="54">
-        <v>45449</v>
+        <v>45421</v>
       </c>
       <c r="H158" s="55"/>
       <c r="I158" s="56"/>
       <c r="J158" s="53" t="s">
-        <v>74</v>
+        <v>513</v>
       </c>
       <c r="K158" s="51" t="s">
         <v>769</v>
@@ -19855,30 +19867,30 @@
     </row>
     <row r="159" spans="1:12" ht="22.5" customHeight="1">
       <c r="A159" s="8" t="s">
-        <v>618</v>
+        <v>633</v>
       </c>
       <c r="B159" s="51" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C159" s="51" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D159" s="49" t="s">
-        <v>896</v>
+        <v>526</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F159" s="53" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="G159" s="54">
-        <v>45421</v>
+        <v>45406</v>
       </c>
       <c r="H159" s="55"/>
       <c r="I159" s="56"/>
       <c r="J159" s="53" t="s">
-        <v>513</v>
+        <v>16</v>
       </c>
       <c r="K159" s="51" t="s">
         <v>769</v>
@@ -19887,22 +19899,22 @@
     </row>
     <row r="160" spans="1:12" ht="22.5" customHeight="1">
       <c r="A160" s="8" t="s">
-        <v>633</v>
+        <v>75</v>
       </c>
       <c r="B160" s="51" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C160" s="51" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D160" s="49" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="E160" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F160" s="53" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="G160" s="54">
         <v>45406</v>
@@ -19910,7 +19922,7 @@
       <c r="H160" s="55"/>
       <c r="I160" s="56"/>
       <c r="J160" s="53" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K160" s="51" t="s">
         <v>769</v>
@@ -19919,166 +19931,166 @@
     </row>
     <row r="161" spans="1:12" ht="22.5" customHeight="1">
       <c r="A161" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B161" s="51" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C161" s="51" t="s">
+        <v>465</v>
+      </c>
+      <c r="B161" s="46" t="s">
         <v>1120</v>
       </c>
-      <c r="D161" s="49" t="s">
+      <c r="C161" s="46" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D161" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E161" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F161" s="53" t="s">
+        <v>744</v>
+      </c>
+      <c r="G161" s="54">
+        <v>45384</v>
+      </c>
+      <c r="H161" s="55">
+        <v>92642</v>
+      </c>
+      <c r="I161" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="J161" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="K161" s="46" t="s">
+        <v>769</v>
+      </c>
+      <c r="L161" s="57"/>
+    </row>
+    <row r="162" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A162" s="46"/>
+      <c r="B162" s="51" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C162" s="51" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D162" s="49" t="s">
         <v>540</v>
       </c>
-      <c r="E161" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="F161" s="53" t="s">
+      <c r="E162" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F162" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="G161" s="54">
-        <v>45406</v>
-      </c>
-      <c r="H161" s="55"/>
-      <c r="I161" s="56"/>
-      <c r="J161" s="53" t="s">
+      <c r="G162" s="54">
+        <v>45251</v>
+      </c>
+      <c r="H162" s="55"/>
+      <c r="I162" s="56"/>
+      <c r="J162" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="K162" s="51" t="s">
+        <v>769</v>
+      </c>
+      <c r="L162" s="57"/>
+    </row>
+    <row r="163" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A163" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="B163" s="46" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C163" s="46" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D163" s="10" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E163" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F163" s="53" t="s">
+        <v>744</v>
+      </c>
+      <c r="G163" s="54">
+        <v>45203</v>
+      </c>
+      <c r="H163" s="55">
+        <v>293263</v>
+      </c>
+      <c r="I163" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="J163" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K161" s="51" t="s">
-        <v>769</v>
-      </c>
-      <c r="L161" s="57"/>
-    </row>
-    <row r="162" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A162" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="B162" s="46" t="s">
-        <v>1121</v>
-      </c>
-      <c r="C162" s="46" t="s">
-        <v>1122</v>
-      </c>
-      <c r="D162" s="10" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E162" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="F162" s="53" t="s">
-        <v>744</v>
-      </c>
-      <c r="G162" s="54">
-        <v>45384</v>
-      </c>
-      <c r="H162" s="55">
-        <v>92642</v>
-      </c>
-      <c r="I162" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="J162" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="K162" s="46" t="s">
-        <v>769</v>
-      </c>
-      <c r="L162" s="57"/>
-    </row>
-    <row r="163" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A163" s="46"/>
-      <c r="B163" s="51" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C163" s="51" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D163" s="49" t="s">
-        <v>540</v>
-      </c>
-      <c r="E163" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="F163" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="G163" s="54">
-        <v>45251</v>
-      </c>
-      <c r="H163" s="55"/>
-      <c r="I163" s="56"/>
-      <c r="J163" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="K163" s="51" t="s">
+      <c r="K163" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L163" s="57"/>
     </row>
     <row r="164" spans="1:12" ht="22.5" customHeight="1">
       <c r="A164" s="8" t="s">
-        <v>484</v>
-      </c>
-      <c r="B164" s="46" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C164" s="46" t="s">
+        <v>558</v>
+      </c>
+      <c r="B164" s="51" t="s">
         <v>1127</v>
       </c>
+      <c r="C164" s="51" t="s">
+        <v>1128</v>
+      </c>
       <c r="D164" s="10" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="E164" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F164" s="53" t="s">
-        <v>744</v>
+        <v>24</v>
       </c>
       <c r="G164" s="54">
-        <v>45203</v>
+        <v>45181</v>
       </c>
       <c r="H164" s="55">
-        <v>293263</v>
-      </c>
-      <c r="I164" s="56">
-        <v>0.5</v>
-      </c>
+        <v>110656</v>
+      </c>
+      <c r="I164" s="56"/>
       <c r="J164" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="K164" s="46" t="s">
+      <c r="K164" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L164" s="57"/>
     </row>
     <row r="165" spans="1:12" ht="22.5" customHeight="1">
       <c r="A165" s="8" t="s">
-        <v>558</v>
+        <v>615</v>
       </c>
       <c r="B165" s="51" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>1129</v>
-      </c>
-      <c r="D165" s="10" t="s">
-        <v>1084</v>
+        <v>1130</v>
+      </c>
+      <c r="D165" s="49" t="s">
+        <v>896</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F165" s="53" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="G165" s="54">
-        <v>45181</v>
-      </c>
-      <c r="H165" s="55">
-        <v>110656</v>
-      </c>
+        <v>45008</v>
+      </c>
+      <c r="H165" s="55"/>
       <c r="I165" s="56"/>
       <c r="J165" s="53" t="s">
-        <v>25</v>
+        <v>513</v>
       </c>
       <c r="K165" s="51" t="s">
         <v>769</v>
@@ -20087,15 +20099,15 @@
     </row>
     <row r="166" spans="1:12" ht="22.5" customHeight="1">
       <c r="A166" s="8" t="s">
-        <v>615</v>
+        <v>648</v>
       </c>
       <c r="B166" s="51" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C166" s="51" t="s">
-        <v>1131</v>
-      </c>
-      <c r="D166" s="49" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D166" s="10" t="s">
         <v>896</v>
       </c>
       <c r="E166" s="10" t="s">
@@ -20105,12 +20117,12 @@
         <v>119</v>
       </c>
       <c r="G166" s="54">
-        <v>45008</v>
+        <v>44916</v>
       </c>
       <c r="H166" s="55"/>
       <c r="I166" s="56"/>
       <c r="J166" s="53" t="s">
-        <v>513</v>
+        <v>25</v>
       </c>
       <c r="K166" s="51" t="s">
         <v>769</v>
@@ -20119,16 +20131,16 @@
     </row>
     <row r="167" spans="1:12" ht="22.5" customHeight="1">
       <c r="A167" s="8" t="s">
-        <v>648</v>
+        <v>612</v>
       </c>
       <c r="B167" s="51" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="C167" s="51" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D167" s="10" t="s">
-        <v>896</v>
+        <v>1134</v>
+      </c>
+      <c r="D167" s="49" t="s">
+        <v>1135</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>448</v>
@@ -20137,12 +20149,12 @@
         <v>119</v>
       </c>
       <c r="G167" s="54">
-        <v>44916</v>
+        <v>44744</v>
       </c>
       <c r="H167" s="55"/>
       <c r="I167" s="56"/>
       <c r="J167" s="53" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K167" s="51" t="s">
         <v>769</v>
@@ -20151,30 +20163,30 @@
     </row>
     <row r="168" spans="1:12" ht="22.5" customHeight="1">
       <c r="A168" s="8" t="s">
-        <v>612</v>
+        <v>647</v>
       </c>
       <c r="B168" s="51" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="C168" s="51" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D168" s="49" t="s">
-        <v>1136</v>
+        <v>804</v>
+      </c>
+      <c r="D168" s="10" t="s">
+        <v>1137</v>
       </c>
       <c r="E168" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F168" s="53" t="s">
-        <v>119</v>
+        <v>1106</v>
       </c>
       <c r="G168" s="54">
-        <v>44744</v>
+        <v>44725</v>
       </c>
       <c r="H168" s="55"/>
       <c r="I168" s="56"/>
       <c r="J168" s="53" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K168" s="51" t="s">
         <v>769</v>
@@ -20183,25 +20195,25 @@
     </row>
     <row r="169" spans="1:12" ht="22.5" customHeight="1">
       <c r="A169" s="8" t="s">
-        <v>647</v>
+        <v>51</v>
       </c>
       <c r="B169" s="51" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C169" s="51" t="s">
-        <v>804</v>
-      </c>
-      <c r="D169" s="10" t="s">
-        <v>1138</v>
+        <v>1139</v>
+      </c>
+      <c r="D169" s="49" t="s">
+        <v>733</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F169" s="53" t="s">
-        <v>1139</v>
+        <v>119</v>
       </c>
       <c r="G169" s="54">
-        <v>44725</v>
+        <v>44405</v>
       </c>
       <c r="H169" s="55"/>
       <c r="I169" s="56"/>
@@ -20215,7 +20227,7 @@
     </row>
     <row r="170" spans="1:12" ht="22.5" customHeight="1">
       <c r="A170" s="8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B170" s="51" t="s">
         <v>1140</v>
@@ -20230,15 +20242,15 @@
         <v>448</v>
       </c>
       <c r="F170" s="53" t="s">
-        <v>119</v>
+        <v>449</v>
       </c>
       <c r="G170" s="54">
-        <v>44405</v>
+        <v>44400</v>
       </c>
       <c r="H170" s="55"/>
       <c r="I170" s="56"/>
       <c r="J170" s="53" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="K170" s="51" t="s">
         <v>769</v>
@@ -20247,30 +20259,30 @@
     </row>
     <row r="171" spans="1:12" ht="22.5" customHeight="1">
       <c r="A171" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B171" s="51" t="s">
+        <v>445</v>
+      </c>
+      <c r="B171" s="8" t="s">
         <v>1142</v>
       </c>
-      <c r="C171" s="51" t="s">
+      <c r="C171" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="D171" s="49" t="s">
-        <v>733</v>
-      </c>
-      <c r="E171" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="F171" s="53" t="s">
-        <v>449</v>
-      </c>
-      <c r="G171" s="54">
-        <v>44400</v>
-      </c>
-      <c r="H171" s="55"/>
-      <c r="I171" s="56"/>
-      <c r="J171" s="53" t="s">
-        <v>74</v>
+      <c r="D171" s="62" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E171" s="63"/>
+      <c r="F171" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="G171" s="65">
+        <v>43923</v>
+      </c>
+      <c r="H171" s="66">
+        <v>15000</v>
+      </c>
+      <c r="I171" s="67"/>
+      <c r="J171" s="64" t="s">
+        <v>790</v>
       </c>
       <c r="K171" s="51" t="s">
         <v>769</v>
@@ -20279,98 +20291,98 @@
     </row>
     <row r="172" spans="1:12" ht="22.5" customHeight="1">
       <c r="A172" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="B172" s="8" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C172" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="B172" s="46" t="s">
         <v>1145</v>
       </c>
-      <c r="D172" s="62" t="s">
+      <c r="C172" s="46" t="s">
         <v>1146</v>
       </c>
-      <c r="E172" s="63"/>
-      <c r="F172" s="64" t="s">
-        <v>119</v>
-      </c>
-      <c r="G172" s="65">
+      <c r="D172" s="49" t="s">
+        <v>896</v>
+      </c>
+      <c r="E172" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F172" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="G172" s="54">
         <v>43923</v>
       </c>
-      <c r="H172" s="66">
-        <v>15000</v>
-      </c>
-      <c r="I172" s="67"/>
-      <c r="J172" s="64" t="s">
-        <v>790</v>
-      </c>
-      <c r="K172" s="51" t="s">
+      <c r="H172" s="55">
+        <v>45200</v>
+      </c>
+      <c r="I172" s="56">
+        <v>0.8</v>
+      </c>
+      <c r="J172" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="K172" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L172" s="57"/>
     </row>
     <row r="173" spans="1:12" ht="22.5" customHeight="1">
       <c r="A173" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="B173" s="46" t="s">
+        <v>653</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="C173" s="46" t="s">
+      <c r="C173" s="51" t="s">
         <v>1148</v>
       </c>
       <c r="D173" s="49" t="s">
-        <v>896</v>
+        <v>733</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>448</v>
+        <v>1149</v>
       </c>
       <c r="F173" s="53" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="G173" s="54">
-        <v>43923</v>
-      </c>
-      <c r="H173" s="55">
-        <v>45200</v>
-      </c>
-      <c r="I173" s="56">
-        <v>0.8</v>
-      </c>
+        <v>43018</v>
+      </c>
+      <c r="H173" s="55"/>
+      <c r="I173" s="56"/>
       <c r="J173" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="K173" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="K173" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L173" s="57"/>
     </row>
     <row r="174" spans="1:12" ht="22.5" customHeight="1">
       <c r="A174" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>1149</v>
+        <v>158</v>
+      </c>
+      <c r="B174" s="51" t="s">
+        <v>1150</v>
       </c>
       <c r="C174" s="51" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D174" s="49" t="s">
         <v>733</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>1151</v>
+        <v>448</v>
       </c>
       <c r="F174" s="53" t="s">
         <v>119</v>
       </c>
       <c r="G174" s="54">
-        <v>43018</v>
+        <v>42724</v>
       </c>
       <c r="H174" s="55"/>
       <c r="I174" s="56"/>
       <c r="J174" s="53" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K174" s="51" t="s">
         <v>769</v>
@@ -20378,9 +20390,7 @@
       <c r="L174" s="57"/>
     </row>
     <row r="175" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A175" s="8" t="s">
-        <v>158</v>
-      </c>
+      <c r="A175" s="46"/>
       <c r="B175" s="51" t="s">
         <v>1152</v>
       </c>
@@ -20394,15 +20404,19 @@
         <v>448</v>
       </c>
       <c r="F175" s="53" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="G175" s="54">
-        <v>42724</v>
-      </c>
-      <c r="H175" s="55"/>
-      <c r="I175" s="56"/>
+        <v>42449</v>
+      </c>
+      <c r="H175" s="55">
+        <v>2008.48</v>
+      </c>
+      <c r="I175" s="56">
+        <v>0.9</v>
+      </c>
       <c r="J175" s="53" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="K175" s="51" t="s">
         <v>769</v>
@@ -20410,7 +20424,9 @@
       <c r="L175" s="57"/>
     </row>
     <row r="176" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A176" s="46"/>
+      <c r="A176" s="8" t="s">
+        <v>510</v>
+      </c>
       <c r="B176" s="51" t="s">
         <v>1154</v>
       </c>
@@ -20418,25 +20434,21 @@
         <v>1155</v>
       </c>
       <c r="D176" s="49" t="s">
-        <v>733</v>
+        <v>896</v>
       </c>
       <c r="E176" s="10" t="s">
-        <v>448</v>
+        <v>1156</v>
       </c>
       <c r="F176" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="G176" s="54">
-        <v>42449</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G176" s="54"/>
       <c r="H176" s="55">
-        <v>2008.48</v>
-      </c>
-      <c r="I176" s="56">
-        <v>0.9</v>
-      </c>
+        <v>36383</v>
+      </c>
+      <c r="I176" s="56"/>
       <c r="J176" s="53" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="K176" s="51" t="s">
         <v>769</v>
@@ -20445,30 +20457,28 @@
     </row>
     <row r="177" spans="1:12" ht="22.5" customHeight="1">
       <c r="A177" s="8" t="s">
-        <v>510</v>
+        <v>110</v>
       </c>
       <c r="B177" s="51" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C177" s="51" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D177" s="49" t="s">
-        <v>896</v>
+        <v>1158</v>
+      </c>
+      <c r="D177" s="10" t="s">
+        <v>1159</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>1158</v>
+        <v>738</v>
       </c>
       <c r="F177" s="53" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="G177" s="54"/>
-      <c r="H177" s="55">
-        <v>36383</v>
-      </c>
+      <c r="H177" s="55"/>
       <c r="I177" s="56"/>
       <c r="J177" s="53" t="s">
-        <v>25</v>
+        <v>513</v>
       </c>
       <c r="K177" s="51" t="s">
         <v>769</v>
@@ -20476,27 +20486,31 @@
       <c r="L177" s="57"/>
     </row>
     <row r="178" spans="1:12" ht="22.5" customHeight="1">
-      <c r="A178" s="8" t="s">
-        <v>110</v>
-      </c>
+      <c r="A178" s="46"/>
       <c r="B178" s="51" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="C178" s="51" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="D178" s="10" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E178" s="10" t="s">
-        <v>738</v>
+        <v>448</v>
       </c>
       <c r="F178" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="G178" s="54"/>
-      <c r="H178" s="55"/>
-      <c r="I178" s="56"/>
+        <v>14</v>
+      </c>
+      <c r="G178" s="54">
+        <v>46066</v>
+      </c>
+      <c r="H178" s="55">
+        <v>30320.42</v>
+      </c>
+      <c r="I178" s="56">
+        <v>0.8</v>
+      </c>
       <c r="J178" s="53" t="s">
         <v>513</v>
       </c>
@@ -20508,31 +20522,29 @@
     <row r="179" spans="1:12" ht="22.5" customHeight="1">
       <c r="A179" s="46"/>
       <c r="B179" s="51" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D179" s="10" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F179" s="53" t="s">
-        <v>14</v>
+        <v>480</v>
       </c>
       <c r="G179" s="54">
-        <v>46066</v>
-      </c>
-      <c r="H179" s="55">
-        <v>30320.42</v>
-      </c>
+        <v>45940</v>
+      </c>
+      <c r="H179" s="55"/>
       <c r="I179" s="56">
         <v>0.8</v>
       </c>
       <c r="J179" s="53" t="s">
-        <v>513</v>
+        <v>25</v>
       </c>
       <c r="K179" s="51" t="s">
         <v>769</v>
@@ -20541,32 +20553,26 @@
     </row>
     <row r="180" spans="1:12" ht="22.5" customHeight="1">
       <c r="A180" s="46"/>
-      <c r="B180" s="51" t="s">
+      <c r="B180" s="46" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C180" s="46" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D180" s="10" t="s">
         <v>1165</v>
       </c>
-      <c r="C180" s="51" t="s">
-        <v>1166</v>
-      </c>
-      <c r="D180" s="10" t="s">
-        <v>1167</v>
-      </c>
       <c r="E180" s="10" t="s">
-        <v>448</v>
+        <v>1168</v>
       </c>
       <c r="F180" s="53" t="s">
-        <v>480</v>
-      </c>
-      <c r="G180" s="54">
-        <v>45940</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="G180" s="54"/>
       <c r="H180" s="55"/>
-      <c r="I180" s="56">
-        <v>0.8</v>
-      </c>
-      <c r="J180" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="K180" s="51" t="s">
+      <c r="I180" s="56"/>
+      <c r="J180" s="53"/>
+      <c r="K180" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L180" s="57"/>
@@ -20574,24 +20580,32 @@
     <row r="181" spans="1:12" ht="22.5" customHeight="1">
       <c r="A181" s="46"/>
       <c r="B181" s="46" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C181" s="46" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D181" s="10" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E181" s="10" t="s">
         <v>1168</v>
       </c>
-      <c r="C181" s="46" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D181" s="10" t="s">
-        <v>1167</v>
-      </c>
-      <c r="E181" s="10" t="s">
-        <v>1170</v>
-      </c>
       <c r="F181" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="G181" s="54"/>
-      <c r="H181" s="55"/>
-      <c r="I181" s="56"/>
-      <c r="J181" s="53"/>
+        <v>106</v>
+      </c>
+      <c r="G181" s="54">
+        <v>46086</v>
+      </c>
+      <c r="H181" s="55">
+        <v>55482.84</v>
+      </c>
+      <c r="I181" s="56">
+        <v>0.7</v>
+      </c>
+      <c r="J181" s="53" t="s">
+        <v>74</v>
+      </c>
       <c r="K181" s="46" t="s">
         <v>769</v>
       </c>
@@ -20600,31 +20614,31 @@
     <row r="182" spans="1:12" ht="22.5" customHeight="1">
       <c r="A182" s="46"/>
       <c r="B182" s="46" t="s">
+        <v>767</v>
+      </c>
+      <c r="C182" s="46" t="s">
         <v>1171</v>
       </c>
-      <c r="C182" s="46" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D182" s="10" t="s">
-        <v>1167</v>
+      <c r="D182" s="49" t="s">
+        <v>561</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>1170</v>
+        <v>448</v>
       </c>
       <c r="F182" s="53" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G182" s="54">
-        <v>46086</v>
+        <v>46065</v>
       </c>
       <c r="H182" s="55">
-        <v>55482.84</v>
+        <v>39859.199999999997</v>
       </c>
       <c r="I182" s="56">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J182" s="53" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="K182" s="46" t="s">
         <v>769</v>
@@ -20634,7 +20648,7 @@
     <row r="183" spans="1:12" ht="22.5" customHeight="1">
       <c r="A183" s="46"/>
       <c r="B183" s="46" t="s">
-        <v>767</v>
+        <v>1172</v>
       </c>
       <c r="C183" s="46" t="s">
         <v>1173</v>
@@ -20646,16 +20660,16 @@
         <v>448</v>
       </c>
       <c r="F183" s="53" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G183" s="54">
-        <v>46065</v>
+        <v>46098</v>
       </c>
       <c r="H183" s="55">
-        <v>39859.199999999997</v>
+        <v>68319.759999999995</v>
       </c>
       <c r="I183" s="56">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J183" s="53" t="s">
         <v>25</v>
@@ -20674,22 +20688,22 @@
         <v>1175</v>
       </c>
       <c r="D184" s="49" t="s">
-        <v>561</v>
+        <v>679</v>
       </c>
       <c r="E184" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F184" s="53" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="G184" s="54">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="H184" s="55">
-        <v>68319.759999999995</v>
+        <v>341492.94</v>
       </c>
       <c r="I184" s="56">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J184" s="53" t="s">
         <v>25</v>
@@ -20708,22 +20722,22 @@
         <v>1177</v>
       </c>
       <c r="D185" s="49" t="s">
-        <v>678</v>
+        <v>1178</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F185" s="53" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G185" s="54">
-        <v>46085</v>
+        <v>45175</v>
       </c>
       <c r="H185" s="55">
-        <v>341492.94</v>
+        <v>321911.81</v>
       </c>
       <c r="I185" s="56">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J185" s="53" t="s">
         <v>25</v>
@@ -20736,29 +20750,25 @@
     <row r="186" spans="1:12" ht="22.5" customHeight="1">
       <c r="A186" s="46"/>
       <c r="B186" s="46" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="C186" s="46" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D186" s="49" t="s">
-        <v>1180</v>
+        <v>561</v>
       </c>
       <c r="E186" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F186" s="53" t="s">
-        <v>14</v>
+        <v>449</v>
       </c>
       <c r="G186" s="54">
-        <v>45175</v>
-      </c>
-      <c r="H186" s="55">
-        <v>321911.81</v>
-      </c>
-      <c r="I186" s="56">
-        <v>0.8</v>
-      </c>
+        <v>46074</v>
+      </c>
+      <c r="H186" s="55"/>
+      <c r="I186" s="56"/>
       <c r="J186" s="53" t="s">
         <v>25</v>
       </c>
@@ -20769,7 +20779,7 @@
     </row>
     <row r="187" spans="1:12" ht="22.5" customHeight="1">
       <c r="A187" s="46"/>
-      <c r="B187" s="46" t="s">
+      <c r="B187" s="1" t="s">
         <v>1181</v>
       </c>
       <c r="C187" s="46" t="s">
@@ -20782,15 +20792,15 @@
         <v>448</v>
       </c>
       <c r="F187" s="53" t="s">
-        <v>449</v>
+        <v>119</v>
       </c>
       <c r="G187" s="54">
-        <v>46074</v>
+        <v>46097</v>
       </c>
       <c r="H187" s="55"/>
       <c r="I187" s="56"/>
       <c r="J187" s="53" t="s">
-        <v>25</v>
+        <v>513</v>
       </c>
       <c r="K187" s="46" t="s">
         <v>769</v>
@@ -20799,14 +20809,14 @@
     </row>
     <row r="188" spans="1:12" ht="22.5" customHeight="1">
       <c r="A188" s="46"/>
-      <c r="B188" s="1" t="s">
+      <c r="B188" s="9" t="s">
         <v>1183</v>
       </c>
       <c r="C188" s="46" t="s">
         <v>1184</v>
       </c>
       <c r="D188" s="49" t="s">
-        <v>561</v>
+        <v>1185</v>
       </c>
       <c r="E188" s="10" t="s">
         <v>448</v>
@@ -20815,12 +20825,12 @@
         <v>119</v>
       </c>
       <c r="G188" s="54">
-        <v>46097</v>
+        <v>46140</v>
       </c>
       <c r="H188" s="55"/>
       <c r="I188" s="56"/>
       <c r="J188" s="53" t="s">
-        <v>513</v>
+        <v>74</v>
       </c>
       <c r="K188" s="46" t="s">
         <v>769</v>
@@ -20830,27 +20840,27 @@
     <row r="189" spans="1:12" ht="22.5" customHeight="1">
       <c r="A189" s="46"/>
       <c r="B189" s="9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C189" s="46" t="s">
-        <v>1186</v>
+        <v>1020</v>
       </c>
       <c r="D189" s="49" t="s">
-        <v>1187</v>
+        <v>960</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F189" s="53" t="s">
-        <v>119</v>
+        <v>449</v>
       </c>
       <c r="G189" s="54">
-        <v>46140</v>
+        <v>46010</v>
       </c>
       <c r="H189" s="55"/>
       <c r="I189" s="56"/>
       <c r="J189" s="53" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="K189" s="46" t="s">
         <v>769</v>
@@ -20860,27 +20870,27 @@
     <row r="190" spans="1:12" ht="22.5" customHeight="1">
       <c r="A190" s="46"/>
       <c r="B190" s="9" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C190" s="46" t="s">
         <v>1188</v>
       </c>
-      <c r="C190" s="46" t="s">
-        <v>1022</v>
-      </c>
       <c r="D190" s="49" t="s">
-        <v>962</v>
+        <v>1109</v>
       </c>
       <c r="E190" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F190" s="53" t="s">
-        <v>449</v>
+        <v>119</v>
       </c>
       <c r="G190" s="54">
-        <v>46010</v>
+        <v>46141</v>
       </c>
       <c r="H190" s="55"/>
       <c r="I190" s="56"/>
       <c r="J190" s="53" t="s">
-        <v>25</v>
+        <v>777</v>
       </c>
       <c r="K190" s="46" t="s">
         <v>769</v>
@@ -20893,10 +20903,10 @@
         <v>1189</v>
       </c>
       <c r="C191" s="46" t="s">
-        <v>1190</v>
+        <v>410</v>
       </c>
       <c r="D191" s="49" t="s">
-        <v>1110</v>
+        <v>946</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>448</v>
@@ -20905,12 +20915,12 @@
         <v>119</v>
       </c>
       <c r="G191" s="54">
-        <v>46141</v>
+        <v>46084</v>
       </c>
       <c r="H191" s="55"/>
       <c r="I191" s="56"/>
       <c r="J191" s="53" t="s">
-        <v>777</v>
+        <v>74</v>
       </c>
       <c r="K191" s="46" t="s">
         <v>769</v>
@@ -20920,13 +20930,13 @@
     <row r="192" spans="1:12" ht="22.5" customHeight="1">
       <c r="A192" s="46"/>
       <c r="B192" s="9" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C192" s="46" t="s">
         <v>1191</v>
       </c>
-      <c r="C192" s="46" t="s">
-        <v>410</v>
-      </c>
       <c r="D192" s="49" t="s">
-        <v>948</v>
+        <v>733</v>
       </c>
       <c r="E192" s="10" t="s">
         <v>448</v>
@@ -20935,12 +20945,12 @@
         <v>119</v>
       </c>
       <c r="G192" s="54">
-        <v>46084</v>
+        <v>46141</v>
       </c>
       <c r="H192" s="55"/>
       <c r="I192" s="56"/>
       <c r="J192" s="53" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="K192" s="46" t="s">
         <v>769</v>
@@ -20970,7 +20980,7 @@
       <c r="H193" s="55"/>
       <c r="I193" s="56"/>
       <c r="J193" s="53" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="K193" s="46" t="s">
         <v>769</v>
@@ -20985,9 +20995,7 @@
       <c r="C194" s="46" t="s">
         <v>1195</v>
       </c>
-      <c r="D194" s="49" t="s">
-        <v>733</v>
-      </c>
+      <c r="D194" s="10"/>
       <c r="E194" s="10" t="s">
         <v>448</v>
       </c>
@@ -20995,12 +21003,12 @@
         <v>119</v>
       </c>
       <c r="G194" s="54">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="H194" s="55"/>
       <c r="I194" s="56"/>
       <c r="J194" s="53" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="K194" s="46" t="s">
         <v>769</v>
@@ -21015,7 +21023,9 @@
       <c r="C195" s="46" t="s">
         <v>1197</v>
       </c>
-      <c r="D195" s="10"/>
+      <c r="D195" s="49" t="s">
+        <v>718</v>
+      </c>
       <c r="E195" s="10" t="s">
         <v>448</v>
       </c>
@@ -21028,7 +21038,7 @@
       <c r="H195" s="55"/>
       <c r="I195" s="56"/>
       <c r="J195" s="53" t="s">
-        <v>25</v>
+        <v>1198</v>
       </c>
       <c r="K195" s="46" t="s">
         <v>769</v>
@@ -21038,13 +21048,13 @@
     <row r="196" spans="1:12" ht="22.5" customHeight="1">
       <c r="A196" s="46"/>
       <c r="B196" s="9" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C196" s="46" t="s">
         <v>1199</v>
       </c>
+      <c r="C196" s="51" t="s">
+        <v>1200</v>
+      </c>
       <c r="D196" s="49" t="s">
-        <v>718</v>
+        <v>818</v>
       </c>
       <c r="E196" s="10" t="s">
         <v>448</v>
@@ -21052,15 +21062,11 @@
       <c r="F196" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="G196" s="54">
-        <v>46142</v>
-      </c>
+      <c r="G196" s="54"/>
       <c r="H196" s="55"/>
       <c r="I196" s="56"/>
-      <c r="J196" s="53" t="s">
-        <v>1200</v>
-      </c>
-      <c r="K196" s="46" t="s">
+      <c r="J196" s="68"/>
+      <c r="K196" s="51" t="s">
         <v>769</v>
       </c>
       <c r="L196" s="57"/>
@@ -21070,11 +21076,11 @@
       <c r="B197" s="9" t="s">
         <v>1201</v>
       </c>
-      <c r="C197" s="51" t="s">
+      <c r="C197" s="46" t="s">
         <v>1202</v>
       </c>
       <c r="D197" s="49" t="s">
-        <v>818</v>
+        <v>1203</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>448</v>
@@ -21085,8 +21091,8 @@
       <c r="G197" s="54"/>
       <c r="H197" s="55"/>
       <c r="I197" s="56"/>
-      <c r="J197" s="68"/>
-      <c r="K197" s="51" t="s">
+      <c r="J197" s="53"/>
+      <c r="K197" s="46" t="s">
         <v>769</v>
       </c>
       <c r="L197" s="57"/>
@@ -21094,13 +21100,13 @@
     <row r="198" spans="1:12" ht="22.5" customHeight="1">
       <c r="A198" s="46"/>
       <c r="B198" s="9" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C198" s="46" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="D198" s="49" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="E198" s="10" t="s">
         <v>448</v>
@@ -21115,19 +21121,17 @@
       <c r="K198" s="46" t="s">
         <v>769</v>
       </c>
-      <c r="L198" s="57"/>
+      <c r="L198" s="46"/>
     </row>
     <row r="199" spans="1:12" ht="22.5" customHeight="1">
       <c r="A199" s="46"/>
       <c r="B199" s="9" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C199" s="46" t="s">
-        <v>1207</v>
-      </c>
-      <c r="D199" s="49" t="s">
-        <v>1208</v>
-      </c>
+        <v>1184</v>
+      </c>
+      <c r="D199" s="10"/>
       <c r="E199" s="10" t="s">
         <v>448</v>
       </c>
@@ -21146,17 +21150,15 @@
     <row r="200" spans="1:12" ht="22.5" customHeight="1">
       <c r="A200" s="46"/>
       <c r="B200" s="9" t="s">
-        <v>1209</v>
-      </c>
-      <c r="C200" s="46" t="s">
-        <v>1186</v>
-      </c>
+        <v>1208</v>
+      </c>
+      <c r="C200" s="46"/>
       <c r="D200" s="10"/>
       <c r="E200" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F200" s="53" t="s">
-        <v>119</v>
+        <v>449</v>
       </c>
       <c r="G200" s="54"/>
       <c r="H200" s="55"/>
@@ -21170,15 +21172,19 @@
     <row r="201" spans="1:12" ht="22.5" customHeight="1">
       <c r="A201" s="46"/>
       <c r="B201" s="9" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C201" s="46" t="s">
         <v>1210</v>
       </c>
-      <c r="C201" s="46"/>
-      <c r="D201" s="10"/>
+      <c r="D201" s="10" t="s">
+        <v>537</v>
+      </c>
       <c r="E201" s="10" t="s">
-        <v>448</v>
+        <v>812</v>
       </c>
       <c r="F201" s="53" t="s">
-        <v>449</v>
+        <v>119</v>
       </c>
       <c r="G201" s="54"/>
       <c r="H201" s="55"/>
@@ -21197,11 +21203,11 @@
       <c r="C202" s="46" t="s">
         <v>1212</v>
       </c>
-      <c r="D202" s="10" t="s">
-        <v>537</v>
+      <c r="D202" s="49" t="s">
+        <v>851</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>812</v>
+        <v>448</v>
       </c>
       <c r="F202" s="53" t="s">
         <v>119</v>
@@ -21224,7 +21230,7 @@
         <v>1214</v>
       </c>
       <c r="D203" s="49" t="s">
-        <v>851</v>
+        <v>537</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>448</v>
@@ -21249,9 +21255,7 @@
       <c r="C204" s="46" t="s">
         <v>1216</v>
       </c>
-      <c r="D204" s="49" t="s">
-        <v>537</v>
-      </c>
+      <c r="D204" s="10"/>
       <c r="E204" s="10" t="s">
         <v>448</v>
       </c>
@@ -21275,7 +21279,9 @@
       <c r="C205" s="46" t="s">
         <v>1218</v>
       </c>
-      <c r="D205" s="10"/>
+      <c r="D205" s="49" t="s">
+        <v>733</v>
+      </c>
       <c r="E205" s="10" t="s">
         <v>448</v>
       </c>
@@ -21300,10 +21306,10 @@
         <v>1220</v>
       </c>
       <c r="D206" s="49" t="s">
-        <v>733</v>
+        <v>679</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>448</v>
+        <v>1221</v>
       </c>
       <c r="F206" s="53" t="s">
         <v>119</v>
@@ -21320,20 +21326,18 @@
     <row r="207" spans="1:12" ht="22.5" customHeight="1">
       <c r="A207" s="46"/>
       <c r="B207" s="9" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="C207" s="46" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="D207" s="49" t="s">
-        <v>678</v>
+        <v>561</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>1223</v>
-      </c>
-      <c r="F207" s="53" t="s">
-        <v>119</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="F207" s="53"/>
       <c r="G207" s="54"/>
       <c r="H207" s="55"/>
       <c r="I207" s="56"/>
@@ -21352,7 +21356,7 @@
         <v>1225</v>
       </c>
       <c r="D208" s="49" t="s">
-        <v>561</v>
+        <v>526</v>
       </c>
       <c r="E208" s="10" t="s">
         <v>448</v>
@@ -21376,7 +21380,7 @@
         <v>1227</v>
       </c>
       <c r="D209" s="49" t="s">
-        <v>526</v>
+        <v>723</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>448</v>
@@ -21400,12 +21404,14 @@
         <v>1229</v>
       </c>
       <c r="D210" s="49" t="s">
-        <v>723</v>
+        <v>561</v>
       </c>
       <c r="E210" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="F210" s="53"/>
+        <v>1230</v>
+      </c>
+      <c r="F210" s="53" t="s">
+        <v>449</v>
+      </c>
       <c r="G210" s="54"/>
       <c r="H210" s="55"/>
       <c r="I210" s="56"/>
@@ -21418,20 +21424,16 @@
     <row r="211" spans="1:12" ht="22.5" customHeight="1">
       <c r="A211" s="46"/>
       <c r="B211" s="9" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="C211" s="46" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D211" s="49" t="s">
-        <v>561</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="D211" s="10"/>
       <c r="E211" s="10" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F211" s="53" t="s">
-        <v>449</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="F211" s="53"/>
       <c r="G211" s="54"/>
       <c r="H211" s="55"/>
       <c r="I211" s="56"/>
@@ -21444,17 +21446,23 @@
     <row r="212" spans="1:12" ht="22.5" customHeight="1">
       <c r="A212" s="46"/>
       <c r="B212" s="9" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C212" s="46" t="s">
         <v>1233</v>
       </c>
-      <c r="C212" s="46" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D212" s="10"/>
+      <c r="D212" s="49" t="s">
+        <v>561</v>
+      </c>
       <c r="E212" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="F212" s="53"/>
-      <c r="G212" s="54"/>
+      <c r="F212" s="53" t="s">
+        <v>480</v>
+      </c>
+      <c r="G212" s="54">
+        <v>46100</v>
+      </c>
       <c r="H212" s="55"/>
       <c r="I212" s="56"/>
       <c r="J212" s="53"/>
@@ -21469,18 +21477,12 @@
         <v>1234</v>
       </c>
       <c r="C213" s="46"/>
-      <c r="D213" s="49" t="s">
-        <v>561</v>
-      </c>
+      <c r="D213" s="10"/>
       <c r="E213" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="F213" s="53" t="s">
-        <v>480</v>
-      </c>
-      <c r="G213" s="54">
-        <v>46100</v>
-      </c>
+      <c r="F213" s="53"/>
+      <c r="G213" s="54"/>
       <c r="H213" s="55"/>
       <c r="I213" s="56"/>
       <c r="J213" s="53"/>
@@ -21494,12 +21496,18 @@
       <c r="B214" s="9" t="s">
         <v>1235</v>
       </c>
-      <c r="C214" s="46"/>
-      <c r="D214" s="10"/>
+      <c r="C214" s="46" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D214" s="49" t="s">
+        <v>679</v>
+      </c>
       <c r="E214" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="F214" s="53"/>
+      <c r="F214" s="53" t="s">
+        <v>449</v>
+      </c>
       <c r="G214" s="54"/>
       <c r="H214" s="55"/>
       <c r="I214" s="56"/>
@@ -21512,20 +21520,18 @@
     <row r="215" spans="1:12" ht="22.5" customHeight="1">
       <c r="A215" s="46"/>
       <c r="B215" s="9" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C215" s="46" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D215" s="49" t="s">
-        <v>678</v>
+        <v>823</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="F215" s="53" t="s">
-        <v>449</v>
-      </c>
+      <c r="F215" s="53"/>
       <c r="G215" s="54"/>
       <c r="H215" s="55"/>
       <c r="I215" s="56"/>
@@ -21537,43 +21543,65 @@
     </row>
     <row r="216" spans="1:12" ht="22.5" customHeight="1">
       <c r="A216" s="46"/>
-      <c r="B216" s="9" t="s">
-        <v>1238</v>
-      </c>
+      <c r="B216" s="9"/>
       <c r="C216" s="46" t="s">
         <v>1239</v>
       </c>
-      <c r="D216" s="49" t="s">
-        <v>823</v>
+      <c r="D216" s="10" t="s">
+        <v>1240</v>
       </c>
       <c r="E216" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="F216" s="53"/>
+      <c r="F216" s="53" t="s">
+        <v>119</v>
+      </c>
       <c r="G216" s="54"/>
       <c r="H216" s="55"/>
       <c r="I216" s="56"/>
       <c r="J216" s="53"/>
-      <c r="K216" s="46" t="s">
-        <v>769</v>
-      </c>
+      <c r="K216" s="46"/>
       <c r="L216" s="46"/>
+    </row>
+    <row r="217" spans="1:12" ht="22.5" customHeight="1">
+      <c r="A217" s="46"/>
+      <c r="B217" s="9" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C217" s="46" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D217" s="10" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E217" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F217" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="G217" s="54"/>
+      <c r="H217" s="55"/>
+      <c r="I217" s="56"/>
+      <c r="J217" s="53"/>
+      <c r="K217" s="46"/>
+      <c r="L217" s="46"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="F2:F216" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F217" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"1. Prospección,2. Contacto Inicial,3. Calificación,4. Levantamiento de Requerimientos,5. Visita Técnica / Diagnóstico en Sitio,6. Diseño de Solución / Pre-Ingeniería,7. Estimación / Cotización,8. Propuesta Enviada,9. Aclaraciones / Ajustes de Propuesta,10"&amp;". Negociación,11. Aprobación Interna (Go/No-Go),12. Cierre de Venta (Contrato / OC),13. Kickoff / Inicio de Proyecto,14. Descartado / No Califica,15. En Pausa / Seguimiento Posterior"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G216" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G217" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G2))), AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I216" xr:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I217" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>AND(ISNUMBER(H2),(NOT(OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J216" xr:uid="{00000000-0002-0000-0400-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J217" xr:uid="{00000000-0002-0000-0400-000003000000}">
       <formula1>"Referido (Cliente),Referido (Proveedor/Subcontratista),Referido (Empleado/Interno),Cliente Recurrente (Recompra/Ampliación),Sitio Web (Formulario),Landing Page (Campaña),Chat Web / WhatsApp,SEO (Búsqueda Orgánica),Google Ads (Search),Remarketing (Display/"&amp;"Redes),LinkedIn (Orgánico),Email Outbound (Prospección),Llamada en Frío (Prospección),Visita en Frío (Prospección),Feria / Expo Industrial,Congreso / Cámara / Networking,Webinar / Evento Virtual,Licitación Pública,Licitación Privada (RFP/RFQ),Portal de Co"&amp;"mpras (Cliente),Alianza (Integrador/EPC/Constructor),Partner Tecnológico (Marca/Distribuidor),Directorio B2B / Clúster,Redes Sociales (Facebook/Instagram),YouTube / Contenido Técnico,PR / Medio Especializado,Reactivación de Base de Datos,Otros"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C216 E2:E216 K2:K216" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C217 E2:E217 K2:K217" xr:uid="{00000000-0002-0000-0400-000004000000}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -21637,20 +21665,20 @@
     <hyperlink ref="D69" r:id="rId59" xr:uid="{00000000-0004-0000-0400-00003A000000}"/>
     <hyperlink ref="D70" r:id="rId60" xr:uid="{00000000-0004-0000-0400-00003B000000}"/>
     <hyperlink ref="D71" r:id="rId61" xr:uid="{00000000-0004-0000-0400-00003C000000}"/>
-    <hyperlink ref="D72" r:id="rId62" xr:uid="{00000000-0004-0000-0400-00003D000000}"/>
-    <hyperlink ref="D74" r:id="rId63" xr:uid="{00000000-0004-0000-0400-00003E000000}"/>
+    <hyperlink ref="D73" r:id="rId62" xr:uid="{00000000-0004-0000-0400-00003D000000}"/>
+    <hyperlink ref="D75" r:id="rId63" xr:uid="{00000000-0004-0000-0400-00003E000000}"/>
     <hyperlink ref="D76" r:id="rId64" xr:uid="{00000000-0004-0000-0400-00003F000000}"/>
-    <hyperlink ref="D77" r:id="rId65" xr:uid="{00000000-0004-0000-0400-000040000000}"/>
+    <hyperlink ref="D78" r:id="rId65" xr:uid="{00000000-0004-0000-0400-000040000000}"/>
     <hyperlink ref="D79" r:id="rId66" xr:uid="{00000000-0004-0000-0400-000041000000}"/>
     <hyperlink ref="D80" r:id="rId67" xr:uid="{00000000-0004-0000-0400-000042000000}"/>
     <hyperlink ref="D81" r:id="rId68" xr:uid="{00000000-0004-0000-0400-000043000000}"/>
     <hyperlink ref="D82" r:id="rId69" xr:uid="{00000000-0004-0000-0400-000044000000}"/>
-    <hyperlink ref="D83" r:id="rId70" xr:uid="{00000000-0004-0000-0400-000045000000}"/>
-    <hyperlink ref="D85" r:id="rId71" xr:uid="{00000000-0004-0000-0400-000046000000}"/>
+    <hyperlink ref="D84" r:id="rId70" xr:uid="{00000000-0004-0000-0400-000045000000}"/>
+    <hyperlink ref="D86" r:id="rId71" xr:uid="{00000000-0004-0000-0400-000046000000}"/>
     <hyperlink ref="D87" r:id="rId72" xr:uid="{00000000-0004-0000-0400-000047000000}"/>
     <hyperlink ref="D88" r:id="rId73" xr:uid="{00000000-0004-0000-0400-000048000000}"/>
     <hyperlink ref="D89" r:id="rId74" xr:uid="{00000000-0004-0000-0400-000049000000}"/>
-    <hyperlink ref="D90" r:id="rId75" xr:uid="{00000000-0004-0000-0400-00004A000000}"/>
+    <hyperlink ref="D91" r:id="rId75" xr:uid="{00000000-0004-0000-0400-00004A000000}"/>
     <hyperlink ref="D92" r:id="rId76" xr:uid="{00000000-0004-0000-0400-00004B000000}"/>
     <hyperlink ref="D93" r:id="rId77" xr:uid="{00000000-0004-0000-0400-00004C000000}"/>
     <hyperlink ref="D94" r:id="rId78" xr:uid="{00000000-0004-0000-0400-00004D000000}"/>
@@ -21667,7 +21695,7 @@
     <hyperlink ref="D105" r:id="rId89" xr:uid="{00000000-0004-0000-0400-000058000000}"/>
     <hyperlink ref="D106" r:id="rId90" xr:uid="{00000000-0004-0000-0400-000059000000}"/>
     <hyperlink ref="D107" r:id="rId91" xr:uid="{00000000-0004-0000-0400-00005A000000}"/>
-    <hyperlink ref="D108" r:id="rId92" xr:uid="{00000000-0004-0000-0400-00005B000000}"/>
+    <hyperlink ref="D109" r:id="rId92" xr:uid="{00000000-0004-0000-0400-00005B000000}"/>
     <hyperlink ref="D110" r:id="rId93" xr:uid="{00000000-0004-0000-0400-00005C000000}"/>
     <hyperlink ref="D111" r:id="rId94" xr:uid="{00000000-0004-0000-0400-00005D000000}"/>
     <hyperlink ref="D112" r:id="rId95" xr:uid="{00000000-0004-0000-0400-00005E000000}"/>
@@ -21675,7 +21703,7 @@
     <hyperlink ref="D114" r:id="rId97" xr:uid="{00000000-0004-0000-0400-000060000000}"/>
     <hyperlink ref="D115" r:id="rId98" xr:uid="{00000000-0004-0000-0400-000061000000}"/>
     <hyperlink ref="D116" r:id="rId99" xr:uid="{00000000-0004-0000-0400-000062000000}"/>
-    <hyperlink ref="D117" r:id="rId100" xr:uid="{00000000-0004-0000-0400-000063000000}"/>
+    <hyperlink ref="D118" r:id="rId100" xr:uid="{00000000-0004-0000-0400-000063000000}"/>
     <hyperlink ref="D119" r:id="rId101" xr:uid="{00000000-0004-0000-0400-000064000000}"/>
     <hyperlink ref="D120" r:id="rId102" xr:uid="{00000000-0004-0000-0400-000065000000}"/>
     <hyperlink ref="D121" r:id="rId103" xr:uid="{00000000-0004-0000-0400-000066000000}"/>
@@ -21685,7 +21713,7 @@
     <hyperlink ref="D125" r:id="rId107" xr:uid="{00000000-0004-0000-0400-00006A000000}"/>
     <hyperlink ref="D126" r:id="rId108" xr:uid="{00000000-0004-0000-0400-00006B000000}"/>
     <hyperlink ref="D127" r:id="rId109" xr:uid="{00000000-0004-0000-0400-00006C000000}"/>
-    <hyperlink ref="D128" r:id="rId110" xr:uid="{00000000-0004-0000-0400-00006D000000}"/>
+    <hyperlink ref="D130" r:id="rId110" xr:uid="{00000000-0004-0000-0400-00006D000000}"/>
     <hyperlink ref="D131" r:id="rId111" xr:uid="{00000000-0004-0000-0400-00006E000000}"/>
     <hyperlink ref="D132" r:id="rId112" xr:uid="{00000000-0004-0000-0400-00006F000000}"/>
     <hyperlink ref="D133" r:id="rId113" xr:uid="{00000000-0004-0000-0400-000070000000}"/>
@@ -21694,8 +21722,8 @@
     <hyperlink ref="D136" r:id="rId116" xr:uid="{00000000-0004-0000-0400-000073000000}"/>
     <hyperlink ref="D137" r:id="rId117" xr:uid="{00000000-0004-0000-0400-000074000000}"/>
     <hyperlink ref="D138" r:id="rId118" xr:uid="{00000000-0004-0000-0400-000075000000}"/>
-    <hyperlink ref="D139" r:id="rId119" xr:uid="{00000000-0004-0000-0400-000076000000}"/>
-    <hyperlink ref="D141" r:id="rId120" xr:uid="{00000000-0004-0000-0400-000077000000}"/>
+    <hyperlink ref="D140" r:id="rId119" xr:uid="{00000000-0004-0000-0400-000076000000}"/>
+    <hyperlink ref="D143" r:id="rId120" xr:uid="{00000000-0004-0000-0400-000077000000}"/>
     <hyperlink ref="D144" r:id="rId121" xr:uid="{00000000-0004-0000-0400-000078000000}"/>
     <hyperlink ref="D145" r:id="rId122" xr:uid="{00000000-0004-0000-0400-000079000000}"/>
     <hyperlink ref="D146" r:id="rId123" xr:uid="{00000000-0004-0000-0400-00007A000000}"/>
@@ -21709,13 +21737,13 @@
     <hyperlink ref="D154" r:id="rId131" xr:uid="{00000000-0004-0000-0400-000082000000}"/>
     <hyperlink ref="D155" r:id="rId132" xr:uid="{00000000-0004-0000-0400-000083000000}"/>
     <hyperlink ref="D156" r:id="rId133" xr:uid="{00000000-0004-0000-0400-000084000000}"/>
-    <hyperlink ref="D157" r:id="rId134" xr:uid="{00000000-0004-0000-0400-000085000000}"/>
+    <hyperlink ref="D158" r:id="rId134" xr:uid="{00000000-0004-0000-0400-000085000000}"/>
     <hyperlink ref="D159" r:id="rId135" xr:uid="{00000000-0004-0000-0400-000086000000}"/>
     <hyperlink ref="D160" r:id="rId136" xr:uid="{00000000-0004-0000-0400-000087000000}"/>
-    <hyperlink ref="D161" r:id="rId137" xr:uid="{00000000-0004-0000-0400-000088000000}"/>
-    <hyperlink ref="D163" r:id="rId138" xr:uid="{00000000-0004-0000-0400-000089000000}"/>
-    <hyperlink ref="D166" r:id="rId139" xr:uid="{00000000-0004-0000-0400-00008A000000}"/>
-    <hyperlink ref="D168" r:id="rId140" xr:uid="{00000000-0004-0000-0400-00008B000000}"/>
+    <hyperlink ref="D162" r:id="rId137" xr:uid="{00000000-0004-0000-0400-000088000000}"/>
+    <hyperlink ref="D165" r:id="rId138" xr:uid="{00000000-0004-0000-0400-000089000000}"/>
+    <hyperlink ref="D167" r:id="rId139" xr:uid="{00000000-0004-0000-0400-00008A000000}"/>
+    <hyperlink ref="D169" r:id="rId140" xr:uid="{00000000-0004-0000-0400-00008B000000}"/>
     <hyperlink ref="D170" r:id="rId141" xr:uid="{00000000-0004-0000-0400-00008C000000}"/>
     <hyperlink ref="D171" r:id="rId142" xr:uid="{00000000-0004-0000-0400-00008D000000}"/>
     <hyperlink ref="D172" r:id="rId143" xr:uid="{00000000-0004-0000-0400-00008E000000}"/>
@@ -21723,7 +21751,7 @@
     <hyperlink ref="D174" r:id="rId145" xr:uid="{00000000-0004-0000-0400-000090000000}"/>
     <hyperlink ref="D175" r:id="rId146" xr:uid="{00000000-0004-0000-0400-000091000000}"/>
     <hyperlink ref="D176" r:id="rId147" xr:uid="{00000000-0004-0000-0400-000092000000}"/>
-    <hyperlink ref="D177" r:id="rId148" xr:uid="{00000000-0004-0000-0400-000093000000}"/>
+    <hyperlink ref="D182" r:id="rId148" xr:uid="{00000000-0004-0000-0400-000093000000}"/>
     <hyperlink ref="D183" r:id="rId149" xr:uid="{00000000-0004-0000-0400-000094000000}"/>
     <hyperlink ref="D184" r:id="rId150" xr:uid="{00000000-0004-0000-0400-000095000000}"/>
     <hyperlink ref="D185" r:id="rId151" xr:uid="{00000000-0004-0000-0400-000096000000}"/>
@@ -21735,28 +21763,27 @@
     <hyperlink ref="D191" r:id="rId157" xr:uid="{00000000-0004-0000-0400-00009C000000}"/>
     <hyperlink ref="D192" r:id="rId158" xr:uid="{00000000-0004-0000-0400-00009D000000}"/>
     <hyperlink ref="D193" r:id="rId159" xr:uid="{00000000-0004-0000-0400-00009E000000}"/>
-    <hyperlink ref="D194" r:id="rId160" xr:uid="{00000000-0004-0000-0400-00009F000000}"/>
+    <hyperlink ref="D195" r:id="rId160" xr:uid="{00000000-0004-0000-0400-00009F000000}"/>
     <hyperlink ref="D196" r:id="rId161" xr:uid="{00000000-0004-0000-0400-0000A0000000}"/>
     <hyperlink ref="D197" r:id="rId162" xr:uid="{00000000-0004-0000-0400-0000A1000000}"/>
     <hyperlink ref="D198" r:id="rId163" xr:uid="{00000000-0004-0000-0400-0000A2000000}"/>
-    <hyperlink ref="D199" r:id="rId164" xr:uid="{00000000-0004-0000-0400-0000A3000000}"/>
+    <hyperlink ref="D202" r:id="rId164" xr:uid="{00000000-0004-0000-0400-0000A3000000}"/>
     <hyperlink ref="D203" r:id="rId165" xr:uid="{00000000-0004-0000-0400-0000A4000000}"/>
-    <hyperlink ref="D204" r:id="rId166" xr:uid="{00000000-0004-0000-0400-0000A5000000}"/>
+    <hyperlink ref="D205" r:id="rId166" xr:uid="{00000000-0004-0000-0400-0000A5000000}"/>
     <hyperlink ref="D206" r:id="rId167" xr:uid="{00000000-0004-0000-0400-0000A6000000}"/>
     <hyperlink ref="D207" r:id="rId168" xr:uid="{00000000-0004-0000-0400-0000A7000000}"/>
     <hyperlink ref="D208" r:id="rId169" xr:uid="{00000000-0004-0000-0400-0000A8000000}"/>
     <hyperlink ref="D209" r:id="rId170" xr:uid="{00000000-0004-0000-0400-0000A9000000}"/>
     <hyperlink ref="D210" r:id="rId171" xr:uid="{00000000-0004-0000-0400-0000AA000000}"/>
-    <hyperlink ref="D211" r:id="rId172" xr:uid="{00000000-0004-0000-0400-0000AB000000}"/>
-    <hyperlink ref="D213" r:id="rId173" xr:uid="{00000000-0004-0000-0400-0000AC000000}"/>
+    <hyperlink ref="D212" r:id="rId172" xr:uid="{00000000-0004-0000-0400-0000AB000000}"/>
+    <hyperlink ref="D214" r:id="rId173" xr:uid="{00000000-0004-0000-0400-0000AC000000}"/>
     <hyperlink ref="D215" r:id="rId174" xr:uid="{00000000-0004-0000-0400-0000AD000000}"/>
-    <hyperlink ref="D216" r:id="rId175" xr:uid="{00000000-0004-0000-0400-0000AE000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
   <tableParts count="1">
-    <tablePart r:id="rId176"/>
+    <tablePart r:id="rId175"/>
   </tableParts>
 </worksheet>
 </file>
@@ -21767,7 +21794,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -21841,10 +21868,10 @@
         <v>481</v>
       </c>
       <c r="B2" s="69" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="D2" s="70"/>
       <c r="E2" s="70"/>
@@ -21864,7 +21891,7 @@
         <v>25</v>
       </c>
       <c r="K2" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="21" customHeight="1">
@@ -21872,15 +21899,15 @@
         <v>484</v>
       </c>
       <c r="B3" s="77" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="C3" s="76" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="D3" s="70"/>
       <c r="E3" s="70"/>
       <c r="F3" s="71" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G3" s="78">
         <v>45951</v>
@@ -21893,7 +21920,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -21901,15 +21928,15 @@
         <v>488</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="C4" s="82" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="D4" s="83"/>
       <c r="E4" s="70"/>
       <c r="F4" s="84" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G4" s="85">
         <v>45951</v>
@@ -21922,7 +21949,7 @@
         <v>25</v>
       </c>
       <c r="K4" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -21930,15 +21957,15 @@
         <v>491</v>
       </c>
       <c r="B5" s="81" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C5" s="82" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="D5" s="83"/>
       <c r="E5" s="70"/>
       <c r="F5" s="89" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G5" s="85">
         <v>45954</v>
@@ -21951,7 +21978,7 @@
         <v>790</v>
       </c>
       <c r="K5" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
@@ -21959,15 +21986,15 @@
         <v>494</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="C6" s="82" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="D6" s="83"/>
       <c r="E6" s="70"/>
       <c r="F6" s="89" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G6" s="85">
         <v>45897</v>
@@ -21980,7 +22007,7 @@
         <v>74</v>
       </c>
       <c r="K6" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -21988,10 +22015,10 @@
         <v>497</v>
       </c>
       <c r="B7" s="77" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="C7" s="76" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="D7" s="70"/>
       <c r="E7" s="70"/>
@@ -22007,7 +22034,7 @@
         <v>25</v>
       </c>
       <c r="K7" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -22015,10 +22042,10 @@
         <v>500</v>
       </c>
       <c r="B8" s="77" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="D8" s="70"/>
       <c r="E8" s="70"/>
@@ -22036,7 +22063,7 @@
         <v>74</v>
       </c>
       <c r="K8" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -22044,10 +22071,10 @@
         <v>503</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="C9" s="82" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="D9" s="83"/>
       <c r="E9" s="70"/>
@@ -22065,7 +22092,7 @@
         <v>74</v>
       </c>
       <c r="K9" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -22073,10 +22100,10 @@
         <v>506</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="C10" s="76" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
@@ -22094,7 +22121,7 @@
         <v>25</v>
       </c>
       <c r="K10" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -22102,10 +22129,10 @@
         <v>514</v>
       </c>
       <c r="B11" s="81" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="C11" s="82" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="D11" s="83"/>
       <c r="E11" s="70"/>
@@ -22123,7 +22150,7 @@
         <v>74</v>
       </c>
       <c r="K11" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -22131,10 +22158,10 @@
         <v>517</v>
       </c>
       <c r="B12" s="81" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="C12" s="82" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="D12" s="83"/>
       <c r="E12" s="70"/>
@@ -22152,7 +22179,7 @@
         <v>74</v>
       </c>
       <c r="K12" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -22160,10 +22187,10 @@
         <v>520</v>
       </c>
       <c r="B13" s="77" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
@@ -22181,7 +22208,7 @@
         <v>25</v>
       </c>
       <c r="K13" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -22189,10 +22216,10 @@
         <v>523</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="C14" s="82" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="D14" s="83"/>
       <c r="E14" s="70"/>
@@ -22208,7 +22235,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -22216,10 +22243,10 @@
         <v>527</v>
       </c>
       <c r="B15" s="99" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="C15" s="82" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="D15" s="83"/>
       <c r="E15" s="70"/>
@@ -22237,7 +22264,7 @@
         <v>74</v>
       </c>
       <c r="K15" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="22.5" customHeight="1">
@@ -22245,15 +22272,15 @@
         <v>531</v>
       </c>
       <c r="B16" s="77" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="C16" s="76" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
       <c r="F16" s="71" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G16" s="93"/>
       <c r="H16" s="73">
@@ -22264,7 +22291,7 @@
         <v>25</v>
       </c>
       <c r="K16" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
@@ -22272,10 +22299,10 @@
         <v>534</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="C17" s="76" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="D17" s="70"/>
       <c r="E17" s="70"/>
@@ -22295,7 +22322,7 @@
         <v>25</v>
       </c>
       <c r="K17" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="22.5" customHeight="1">
@@ -22303,10 +22330,10 @@
         <v>538</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="70"/>
@@ -22326,7 +22353,7 @@
         <v>74</v>
       </c>
       <c r="K18" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="22.5" customHeight="1">
@@ -22334,10 +22361,10 @@
         <v>541</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="11"/>
@@ -22357,7 +22384,7 @@
         <v>513</v>
       </c>
       <c r="K19" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="22.5" customHeight="1">
@@ -22365,10 +22392,10 @@
         <v>544</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -22386,7 +22413,7 @@
         <v>25</v>
       </c>
       <c r="K20" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="22.5" customHeight="1">
@@ -22394,10 +22421,10 @@
         <v>547</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="C21" s="76" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -22415,7 +22442,7 @@
         <v>745</v>
       </c>
       <c r="K21" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="22.5" customHeight="1">
@@ -22423,10 +22450,10 @@
         <v>552</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="C22" s="76" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="11"/>
@@ -22444,7 +22471,7 @@
         <v>551</v>
       </c>
       <c r="K22" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="22.5" customHeight="1">
@@ -22452,10 +22479,10 @@
         <v>555</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="C23" s="76" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="11"/>
@@ -22473,7 +22500,7 @@
         <v>551</v>
       </c>
       <c r="K23" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="22.5" customHeight="1">
@@ -22481,10 +22508,10 @@
         <v>558</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -22502,7 +22529,7 @@
         <v>551</v>
       </c>
       <c r="K24" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="22.5" customHeight="1">
@@ -22510,15 +22537,15 @@
         <v>558</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="11"/>
       <c r="F25" s="3" t="s">
-        <v>1139</v>
+        <v>1106</v>
       </c>
       <c r="G25" s="12">
         <v>46068</v>
@@ -22533,7 +22560,7 @@
         <v>513</v>
       </c>
       <c r="K25" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -22541,10 +22568,10 @@
         <v>558</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="11"/>
@@ -22564,7 +22591,7 @@
         <v>551</v>
       </c>
       <c r="K26" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="22.5" customHeight="1">
@@ -22572,10 +22599,10 @@
         <v>562</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -22593,7 +22620,7 @@
         <v>513</v>
       </c>
       <c r="K27" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="22.5" customHeight="1">
@@ -22601,10 +22628,10 @@
         <v>565</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -22622,7 +22649,7 @@
         <v>513</v>
       </c>
       <c r="K28" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="22.5" customHeight="1">
@@ -22630,10 +22657,10 @@
         <v>568</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="11"/>
@@ -22649,24 +22676,41 @@
       <c r="I29" s="45"/>
       <c r="J29" s="14"/>
       <c r="K29" s="76" t="s">
-        <v>1242</v>
-      </c>
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="22.5" customHeight="1">
+      <c r="A30" s="46"/>
+      <c r="B30" s="9" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D30" s="10"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="76"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="F2:F29" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F30" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"1. Prospección,2. Contacto Inicial,3. Calificación,4. Levantamiento de Requerimientos,5. Visita Técnica / Diagnóstico en Sitio,6. Diseño de Solución / Pre-Ingeniería,7. Estimación / Cotización,8. Propuesta Enviada,9. Aclaraciones / Ajustes de Propuesta,10"&amp;". Negociación,11. Aprobación Interna (Go/No-Go),12. Cierre de Venta (Contrato / OC),13. Kickoff / Inicio de Proyecto,14. Descartado / No Califica,15. En Pausa / Seguimiento Posterior"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G29" xr:uid="{00000000-0002-0000-0500-000001000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G30" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(G2))), AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I29" xr:uid="{00000000-0002-0000-0500-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="H2:I30" xr:uid="{00000000-0002-0000-0500-000002000000}">
       <formula1>AND(ISNUMBER(H2),(NOT(OR(NOT(ISERROR(DATEVALUE(H2))), AND(ISNUMBER(H2), LEFT(CELL("format", H2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J29" xr:uid="{00000000-0002-0000-0500-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J30" xr:uid="{00000000-0002-0000-0500-000003000000}">
       <formula1>"Referido (Cliente),Referido (Proveedor/Subcontratista),Referido (Empleado/Interno),Cliente Recurrente (Recompra/Ampliación),Sitio Web (Formulario),Landing Page (Campaña),Chat Web / WhatsApp,SEO (Búsqueda Orgánica),Google Ads (Search),Remarketing (Display/"&amp;"Redes),LinkedIn (Orgánico),Email Outbound (Prospección),Llamada en Frío (Prospección),Visita en Frío (Prospección),Feria / Expo Industrial,Congreso / Cámara / Networking,Webinar / Evento Virtual,Licitación Pública,Licitación Privada (RFP/RFQ),Portal de Co"&amp;"mpras (Cliente),Alianza (Integrador/EPC/Constructor),Partner Tecnológico (Marca/Distribuidor),Directorio B2B / Clúster,Redes Sociales (Facebook/Instagram),YouTube / Contenido Técnico,PR / Medio Especializado,Reactivación de Base de Datos,Otros"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C29 E2:E29 K2:K29" xr:uid="{00000000-0002-0000-0500-000004000000}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="B2:C30 E2:E30 K2:K30" xr:uid="{00000000-0002-0000-0500-000004000000}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -22772,17 +22816,17 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="D2" s="101"/>
       <c r="E2" s="101" t="s">
         <v>448</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G2" s="65">
         <v>46083</v>
@@ -22793,7 +22837,7 @@
         <v>790</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -22801,10 +22845,10 @@
         <v>451</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
@@ -22826,7 +22870,7 @@
         <v>790</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -22834,14 +22878,14 @@
         <v>454</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="F4" s="53" t="s">
         <v>449</v>
@@ -22855,7 +22899,7 @@
         <v>790</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1">
@@ -22863,10 +22907,10 @@
         <v>457</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
@@ -22885,21 +22929,21 @@
         <v>0.8</v>
       </c>
       <c r="J5" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
@@ -22914,10 +22958,10 @@
       <c r="H6" s="61"/>
       <c r="I6" s="56"/>
       <c r="J6" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1">
@@ -22925,10 +22969,10 @@
         <v>459</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
@@ -22946,7 +22990,7 @@
         <v>790</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="22.5" customHeight="1">
@@ -22954,10 +22998,10 @@
         <v>462</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
@@ -22975,7 +23019,7 @@
         <v>25</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="22.5" customHeight="1">
@@ -22983,14 +23027,14 @@
         <v>465</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="F9" s="53" t="s">
         <v>40</v>
@@ -23004,7 +23048,7 @@
         <v>659</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="22.5" customHeight="1">
@@ -23012,17 +23056,17 @@
         <v>468</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>40</v>
+        <v>667</v>
       </c>
       <c r="G10" s="54">
         <v>46085</v>
@@ -23033,7 +23077,7 @@
         <v>659</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="22.5" customHeight="1">
@@ -23041,14 +23085,14 @@
         <v>471</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="F11" s="53" t="s">
         <v>32</v>
@@ -23062,7 +23106,7 @@
         <v>659</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="22.5" customHeight="1">
@@ -23070,10 +23114,10 @@
         <v>474</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
@@ -23089,7 +23133,7 @@
         <v>659</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="22.5" customHeight="1">
@@ -23097,10 +23141,10 @@
         <v>477</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
@@ -23122,7 +23166,7 @@
         <v>659</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="22.5" customHeight="1">
@@ -23130,10 +23174,10 @@
         <v>481</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10" t="s">
@@ -23153,7 +23197,7 @@
         <v>790</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -23161,10 +23205,10 @@
         <v>484</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10" t="s">
@@ -23184,10 +23228,10 @@
         <v>488</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -23207,7 +23251,7 @@
         <v>659</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="22.5" customHeight="1">
@@ -23215,17 +23259,17 @@
         <v>491</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>699</v>
+        <v>667</v>
       </c>
       <c r="G17" s="54"/>
       <c r="H17" s="55"/>
@@ -23238,17 +23282,17 @@
         <v>494</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>699</v>
+        <v>667</v>
       </c>
       <c r="G18" s="54"/>
       <c r="H18" s="55"/>
@@ -23261,17 +23305,17 @@
         <v>497</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10" t="s">
         <v>448</v>
       </c>
       <c r="F19" s="53" t="s">
-        <v>699</v>
+        <v>667</v>
       </c>
       <c r="G19" s="54"/>
       <c r="H19" s="55"/>
@@ -23284,10 +23328,10 @@
         <v>500</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10" t="s">
@@ -23422,13 +23466,13 @@
         <v>445</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D2" s="62" t="s">
         <v>1144</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D2" s="62" t="s">
-        <v>1146</v>
       </c>
       <c r="E2" s="63"/>
       <c r="F2" s="64" t="s">
@@ -23447,7 +23491,7 @@
         <v>790</v>
       </c>
       <c r="K2" s="104" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="22.5" customHeight="1">
@@ -23455,10 +23499,10 @@
         <v>471</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="C3" s="82" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="D3" s="83"/>
       <c r="E3" s="83"/>
@@ -23474,7 +23518,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1">
@@ -23762,10 +23806,10 @@
         <v>474</v>
       </c>
       <c r="B14" s="107" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="C14" s="108" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="D14" s="109"/>
       <c r="E14" s="109"/>
@@ -23783,7 +23827,7 @@
         <v>74</v>
       </c>
       <c r="K14" s="115" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.5" customHeight="1">
@@ -24073,10 +24117,10 @@
         <v>477</v>
       </c>
       <c r="B25" s="117" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="C25" s="118" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="D25" s="119"/>
       <c r="E25" s="119"/>
@@ -24094,7 +24138,7 @@
         <v>25</v>
       </c>
       <c r="K25" s="125" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="22.5" customHeight="1">
@@ -24392,10 +24436,10 @@
         <v>481</v>
       </c>
       <c r="B36" s="126" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="C36" s="127" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="D36" s="128"/>
       <c r="E36" s="128"/>
@@ -24411,7 +24455,7 @@
         <v>25</v>
       </c>
       <c r="K36" s="134" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="22.5" customHeight="1">
@@ -24543,7 +24587,7 @@
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="D42" s="17"/>
       <c r="E42" s="18"/>
@@ -24618,10 +24662,10 @@
         <v>484</v>
       </c>
       <c r="B46" s="107" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="C46" s="108" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="D46" s="109"/>
       <c r="E46" s="109"/>
@@ -24639,7 +24683,7 @@
         <v>74</v>
       </c>
       <c r="K46" s="115" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="22.5" customHeight="1">
@@ -24839,10 +24883,10 @@
         <v>488</v>
       </c>
       <c r="B57" s="135" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="C57" s="136" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="D57" s="137"/>
       <c r="E57" s="137"/>
@@ -24860,7 +24904,7 @@
         <v>25</v>
       </c>
       <c r="K57" s="143" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="22.5" customHeight="1">
@@ -25078,10 +25122,10 @@
         <v>491</v>
       </c>
       <c r="B68" s="107" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="C68" s="108" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="D68" s="109"/>
       <c r="E68" s="109"/>
@@ -25097,7 +25141,7 @@
         <v>74</v>
       </c>
       <c r="K68" s="115" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="22.5" customHeight="1">
@@ -25313,15 +25357,15 @@
         <v>494</v>
       </c>
       <c r="B79" s="126" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="C79" s="127" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="D79" s="128"/>
       <c r="E79" s="128"/>
       <c r="F79" s="146" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G79" s="147">
         <v>45954</v>
@@ -25334,7 +25378,7 @@
         <v>790</v>
       </c>
       <c r="K79" s="134" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="22.5" customHeight="1">
@@ -25384,10 +25428,10 @@
         <v>497</v>
       </c>
       <c r="B82" s="117" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="C82" s="118" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="D82" s="119"/>
       <c r="E82" s="119"/>
@@ -25405,7 +25449,7 @@
         <v>74</v>
       </c>
       <c r="K82" s="125" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="22.5" customHeight="1">
@@ -25413,15 +25457,15 @@
         <v>500</v>
       </c>
       <c r="B83" s="126" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="C83" s="127" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="D83" s="128"/>
       <c r="E83" s="128"/>
       <c r="F83" s="146" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G83" s="147">
         <v>45897</v>
@@ -25434,7 +25478,7 @@
         <v>74</v>
       </c>
       <c r="K83" s="134" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="22.5" customHeight="1">
@@ -25442,10 +25486,10 @@
         <v>451</v>
       </c>
       <c r="B84" s="151" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="C84" s="151" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="D84" s="152" t="s">
         <v>818</v>
@@ -25467,7 +25511,7 @@
         <v>25</v>
       </c>
       <c r="K84" s="158" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="22.5" customHeight="1">
@@ -25475,10 +25519,10 @@
         <v>503</v>
       </c>
       <c r="B85" s="107" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="C85" s="108" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="D85" s="109"/>
       <c r="E85" s="109"/>
@@ -25496,7 +25540,7 @@
         <v>74</v>
       </c>
       <c r="K85" s="115" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="22.5" customHeight="1">
@@ -25504,10 +25548,10 @@
         <v>506</v>
       </c>
       <c r="B86" s="135" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="C86" s="136" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="D86" s="137"/>
       <c r="E86" s="137"/>
@@ -25525,7 +25569,7 @@
         <v>74</v>
       </c>
       <c r="K86" s="143" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="22.5" customHeight="1">
@@ -25533,10 +25577,10 @@
         <v>510</v>
       </c>
       <c r="B87" s="108" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="C87" s="108" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="D87" s="109"/>
       <c r="E87" s="109"/>
@@ -25552,7 +25596,7 @@
         <v>790</v>
       </c>
       <c r="K87" s="115" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="22.5" customHeight="1">
@@ -25560,10 +25604,10 @@
         <v>514</v>
       </c>
       <c r="B88" s="135" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="C88" s="136" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="D88" s="137"/>
       <c r="E88" s="137"/>
@@ -25581,7 +25625,7 @@
         <v>74</v>
       </c>
       <c r="K88" s="143" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="22.5" customHeight="1">
@@ -25589,10 +25633,10 @@
         <v>517</v>
       </c>
       <c r="B89" s="117" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="C89" s="118" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="D89" s="70"/>
       <c r="E89" s="70"/>
@@ -25610,7 +25654,7 @@
         <v>74</v>
       </c>
       <c r="K89" s="125" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="22.5" customHeight="1">
@@ -25618,10 +25662,10 @@
         <v>520</v>
       </c>
       <c r="B90" s="135" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="C90" s="136" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="D90" s="83"/>
       <c r="E90" s="83"/>
@@ -25637,7 +25681,7 @@
         <v>74</v>
       </c>
       <c r="K90" s="143" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="22.5" customHeight="1">
@@ -25645,10 +25689,10 @@
         <v>523</v>
       </c>
       <c r="B91" s="77" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="C91" s="76" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="D91" s="70"/>
       <c r="E91" s="70"/>
@@ -25664,7 +25708,7 @@
         <v>25</v>
       </c>
       <c r="K91" s="125" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="22.5" customHeight="1">
@@ -25672,10 +25716,10 @@
         <v>527</v>
       </c>
       <c r="B92" s="81" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="C92" s="82" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="D92" s="83"/>
       <c r="E92" s="83"/>
@@ -25693,7 +25737,7 @@
         <v>74</v>
       </c>
       <c r="K92" s="143" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="22.5" customHeight="1">
@@ -25701,10 +25745,10 @@
         <v>531</v>
       </c>
       <c r="B93" s="77" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="C93" s="76" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="D93" s="70"/>
       <c r="E93" s="70"/>
@@ -25720,7 +25764,7 @@
         <v>74</v>
       </c>
       <c r="K93" s="125" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="22.5" customHeight="1">
@@ -25728,10 +25772,10 @@
         <v>534</v>
       </c>
       <c r="B94" s="81" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="C94" s="82" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="D94" s="83"/>
       <c r="E94" s="83"/>
@@ -25747,7 +25791,7 @@
         <v>74</v>
       </c>
       <c r="K94" s="143" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="22.5" customHeight="1">
@@ -25755,10 +25799,10 @@
         <v>454</v>
       </c>
       <c r="B95" s="104" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="C95" s="104" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="D95" s="62" t="s">
         <v>896</v>
@@ -25780,7 +25824,7 @@
         <v>16</v>
       </c>
       <c r="K95" s="158" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="22.5" customHeight="1">
@@ -25788,10 +25832,10 @@
         <v>538</v>
       </c>
       <c r="B96" s="77" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="C96" s="76" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D96" s="70"/>
       <c r="E96" s="70"/>
@@ -25807,7 +25851,7 @@
         <v>74</v>
       </c>
       <c r="K96" s="125" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="22.5" customHeight="1">
@@ -25815,10 +25859,10 @@
         <v>541</v>
       </c>
       <c r="B97" s="81" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="C97" s="82" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="D97" s="83"/>
       <c r="E97" s="83"/>
@@ -25834,7 +25878,7 @@
         <v>74</v>
       </c>
       <c r="K97" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="22.5" customHeight="1">
@@ -25842,10 +25886,10 @@
         <v>544</v>
       </c>
       <c r="B98" s="77" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="C98" s="76" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="D98" s="70"/>
       <c r="E98" s="70"/>
@@ -25863,7 +25907,7 @@
         <v>74</v>
       </c>
       <c r="K98" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="22.5" customHeight="1">
@@ -25871,10 +25915,10 @@
         <v>547</v>
       </c>
       <c r="B99" s="81" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="C99" s="82" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="D99" s="83"/>
       <c r="E99" s="83"/>
@@ -25892,7 +25936,7 @@
         <v>74</v>
       </c>
       <c r="K99" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="22.5" customHeight="1">
@@ -25900,10 +25944,10 @@
         <v>552</v>
       </c>
       <c r="B100" s="77" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="C100" s="76" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="D100" s="70"/>
       <c r="E100" s="70"/>
@@ -25919,7 +25963,7 @@
         <v>74</v>
       </c>
       <c r="K100" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="22.5" customHeight="1">
@@ -25927,10 +25971,10 @@
         <v>555</v>
       </c>
       <c r="B101" s="81" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="C101" s="82" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="D101" s="83"/>
       <c r="E101" s="83"/>
@@ -25946,7 +25990,7 @@
         <v>74</v>
       </c>
       <c r="K101" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="22.5" customHeight="1">
@@ -25954,10 +25998,10 @@
         <v>558</v>
       </c>
       <c r="B102" s="77" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="C102" s="76" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="D102" s="70"/>
       <c r="E102" s="70"/>
@@ -25973,7 +26017,7 @@
         <v>74</v>
       </c>
       <c r="K102" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="22.5" customHeight="1">
@@ -25981,10 +26025,10 @@
         <v>562</v>
       </c>
       <c r="B103" s="81" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="C103" s="82" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="D103" s="83"/>
       <c r="E103" s="83"/>
@@ -26000,7 +26044,7 @@
         <v>74</v>
       </c>
       <c r="K103" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="22.5" customHeight="1">
@@ -26008,10 +26052,10 @@
         <v>565</v>
       </c>
       <c r="B104" s="76" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="C104" s="76" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="D104" s="70"/>
       <c r="E104" s="70"/>
@@ -26029,7 +26073,7 @@
         <v>25</v>
       </c>
       <c r="K104" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="22.5" customHeight="1">
@@ -26037,10 +26081,10 @@
         <v>568</v>
       </c>
       <c r="B105" s="81" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="C105" s="82" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="D105" s="83"/>
       <c r="E105" s="83"/>
@@ -26058,7 +26102,7 @@
         <v>74</v>
       </c>
       <c r="K105" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="22.5" customHeight="1">
@@ -26066,10 +26110,10 @@
         <v>457</v>
       </c>
       <c r="B106" s="104" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="C106" s="104" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="D106" s="62" t="s">
         <v>540</v>
@@ -26088,10 +26132,10 @@
         <v>0.9</v>
       </c>
       <c r="J106" s="64" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="K106" s="104" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="22.5" customHeight="1">
@@ -26099,10 +26143,10 @@
         <v>571</v>
       </c>
       <c r="B107" s="77" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="C107" s="76" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="D107" s="70"/>
       <c r="E107" s="70"/>
@@ -26118,7 +26162,7 @@
         <v>25</v>
       </c>
       <c r="K107" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="22.5" customHeight="1">
@@ -26126,10 +26170,10 @@
         <v>574</v>
       </c>
       <c r="B108" s="81" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="C108" s="82" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="D108" s="83"/>
       <c r="E108" s="83"/>
@@ -26145,7 +26189,7 @@
         <v>74</v>
       </c>
       <c r="K108" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="22.5" customHeight="1">
@@ -26153,10 +26197,10 @@
         <v>576</v>
       </c>
       <c r="B109" s="77" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="C109" s="76" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="D109" s="70"/>
       <c r="E109" s="70"/>
@@ -26174,7 +26218,7 @@
         <v>25</v>
       </c>
       <c r="K109" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="22.5" customHeight="1">
@@ -26182,10 +26226,10 @@
         <v>579</v>
       </c>
       <c r="B110" s="81" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="C110" s="82" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="D110" s="83"/>
       <c r="E110" s="83"/>
@@ -26201,7 +26245,7 @@
         <v>74</v>
       </c>
       <c r="K110" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="22.5" customHeight="1">
@@ -26209,10 +26253,10 @@
         <v>582</v>
       </c>
       <c r="B111" s="77" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="C111" s="76" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="D111" s="70"/>
       <c r="E111" s="70"/>
@@ -26228,7 +26272,7 @@
         <v>74</v>
       </c>
       <c r="K111" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="22.5" customHeight="1">
@@ -26236,10 +26280,10 @@
         <v>585</v>
       </c>
       <c r="B112" s="81" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="C112" s="82" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="D112" s="83"/>
       <c r="E112" s="83"/>
@@ -26255,7 +26299,7 @@
         <v>74</v>
       </c>
       <c r="K112" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="22.5" customHeight="1">
@@ -26263,10 +26307,10 @@
         <v>588</v>
       </c>
       <c r="B113" s="77" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="C113" s="76" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="D113" s="70"/>
       <c r="E113" s="70"/>
@@ -26282,7 +26326,7 @@
         <v>74</v>
       </c>
       <c r="K113" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="22.5" customHeight="1">
@@ -26290,10 +26334,10 @@
         <v>591</v>
       </c>
       <c r="B114" s="81" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="C114" s="82" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="D114" s="83"/>
       <c r="E114" s="83"/>
@@ -26309,7 +26353,7 @@
         <v>74</v>
       </c>
       <c r="K114" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="22.5" customHeight="1">
@@ -26317,7 +26361,7 @@
         <v>594</v>
       </c>
       <c r="B115" s="77" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="C115" s="76" t="s">
         <v>391</v>
@@ -26336,7 +26380,7 @@
         <v>74</v>
       </c>
       <c r="K115" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="22.5" customHeight="1">
@@ -26344,10 +26388,10 @@
         <v>597</v>
       </c>
       <c r="B116" s="81" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="C116" s="82" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="D116" s="83"/>
       <c r="E116" s="83"/>
@@ -26363,25 +26407,25 @@
         <v>74</v>
       </c>
       <c r="K116" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="22.5" customHeight="1">
       <c r="A117" s="8" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B117" s="104" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="C117" s="104" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="D117" s="62" t="s">
         <v>540</v>
       </c>
       <c r="E117" s="63"/>
       <c r="F117" s="64" t="s">
-        <v>1139</v>
+        <v>1106</v>
       </c>
       <c r="G117" s="103">
         <v>45976</v>
@@ -26393,10 +26437,10 @@
         <v>0.85</v>
       </c>
       <c r="J117" s="64" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="K117" s="104" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="22.5" customHeight="1">
@@ -26404,10 +26448,10 @@
         <v>600</v>
       </c>
       <c r="B118" s="77" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="C118" s="76" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="D118" s="70"/>
       <c r="E118" s="70"/>
@@ -26423,7 +26467,7 @@
         <v>74</v>
       </c>
       <c r="K118" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="22.5" customHeight="1">
@@ -26431,10 +26475,10 @@
         <v>603</v>
       </c>
       <c r="B119" s="81" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="C119" s="82" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="D119" s="83"/>
       <c r="E119" s="83"/>
@@ -26452,7 +26496,7 @@
         <v>74</v>
       </c>
       <c r="K119" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="22.5" customHeight="1">
@@ -26460,10 +26504,10 @@
         <v>606</v>
       </c>
       <c r="B120" s="77" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="C120" s="76" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="D120" s="70"/>
       <c r="E120" s="70"/>
@@ -26481,7 +26525,7 @@
         <v>74</v>
       </c>
       <c r="K120" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="22.5" customHeight="1">
@@ -26489,10 +26533,10 @@
         <v>609</v>
       </c>
       <c r="B121" s="81" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="C121" s="82" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="D121" s="83"/>
       <c r="E121" s="83"/>
@@ -26508,7 +26552,7 @@
         <v>74</v>
       </c>
       <c r="K121" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="22.5" customHeight="1">
@@ -26516,10 +26560,10 @@
         <v>612</v>
       </c>
       <c r="B122" s="77" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="C122" s="76" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="D122" s="70"/>
       <c r="E122" s="70"/>
@@ -26535,7 +26579,7 @@
         <v>74</v>
       </c>
       <c r="K122" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="22.5" customHeight="1">
@@ -26543,10 +26587,10 @@
         <v>615</v>
       </c>
       <c r="B123" s="81" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="C123" s="82" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="D123" s="83"/>
       <c r="E123" s="83"/>
@@ -26562,7 +26606,7 @@
         <v>74</v>
       </c>
       <c r="K123" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="22.5" customHeight="1">
@@ -26570,10 +26614,10 @@
         <v>618</v>
       </c>
       <c r="B124" s="77" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="C124" s="76" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="D124" s="70"/>
       <c r="E124" s="70"/>
@@ -26591,7 +26635,7 @@
         <v>25</v>
       </c>
       <c r="K124" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="22.5" customHeight="1">
@@ -26599,10 +26643,10 @@
         <v>621</v>
       </c>
       <c r="B125" s="81" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="C125" s="82" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="D125" s="83"/>
       <c r="E125" s="83"/>
@@ -26618,7 +26662,7 @@
         <v>25</v>
       </c>
       <c r="K125" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="22.5" customHeight="1">
@@ -26626,10 +26670,10 @@
         <v>624</v>
       </c>
       <c r="B126" s="77" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="C126" s="76" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="D126" s="70"/>
       <c r="E126" s="70"/>
@@ -26645,7 +26689,7 @@
         <v>74</v>
       </c>
       <c r="K126" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="22.5" customHeight="1">
@@ -26653,10 +26697,10 @@
         <v>627</v>
       </c>
       <c r="B127" s="81" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="C127" s="82" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="D127" s="83"/>
       <c r="E127" s="83"/>
@@ -26672,7 +26716,7 @@
         <v>74</v>
       </c>
       <c r="K127" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="22.5" customHeight="1">
@@ -26680,10 +26724,10 @@
         <v>459</v>
       </c>
       <c r="B128" s="104" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="C128" s="104" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="D128" s="62" t="s">
         <v>540</v>
@@ -26702,10 +26746,10 @@
         <v>0.5</v>
       </c>
       <c r="J128" s="64" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="K128" s="104" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="22.5" customHeight="1">
@@ -26713,10 +26757,10 @@
         <v>630</v>
       </c>
       <c r="B129" s="77" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="C129" s="76" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="D129" s="70"/>
       <c r="E129" s="70"/>
@@ -26732,7 +26776,7 @@
         <v>74</v>
       </c>
       <c r="K129" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="22.5" customHeight="1">
@@ -26740,10 +26784,10 @@
         <v>633</v>
       </c>
       <c r="B130" s="81" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="C130" s="82" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="D130" s="83"/>
       <c r="E130" s="83"/>
@@ -26761,7 +26805,7 @@
         <v>74</v>
       </c>
       <c r="K130" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="22.5" customHeight="1">
@@ -26769,10 +26813,10 @@
         <v>636</v>
       </c>
       <c r="B131" s="77" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="C131" s="76" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="D131" s="70"/>
       <c r="E131" s="70"/>
@@ -26788,7 +26832,7 @@
         <v>74</v>
       </c>
       <c r="K131" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="22.5" customHeight="1">
@@ -26796,10 +26840,10 @@
         <v>637</v>
       </c>
       <c r="B132" s="81" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="C132" s="82" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="D132" s="83"/>
       <c r="E132" s="83"/>
@@ -26817,7 +26861,7 @@
         <v>74</v>
       </c>
       <c r="K132" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="22.5" customHeight="1">
@@ -26825,10 +26869,10 @@
         <v>638</v>
       </c>
       <c r="B133" s="77" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="C133" s="76" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="D133" s="70"/>
       <c r="E133" s="70"/>
@@ -26846,7 +26890,7 @@
         <v>25</v>
       </c>
       <c r="K133" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="22.5" customHeight="1">
@@ -26854,10 +26898,10 @@
         <v>639</v>
       </c>
       <c r="B134" s="81" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="C134" s="82" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="D134" s="83"/>
       <c r="E134" s="83"/>
@@ -26873,7 +26917,7 @@
         <v>25</v>
       </c>
       <c r="K134" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="22.5" customHeight="1">
@@ -26881,10 +26925,10 @@
         <v>640</v>
       </c>
       <c r="B135" s="77" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="C135" s="76" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="D135" s="70"/>
       <c r="E135" s="70"/>
@@ -26902,7 +26946,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="22.5" customHeight="1">
@@ -26910,10 +26954,10 @@
         <v>641</v>
       </c>
       <c r="B136" s="81" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="C136" s="82" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="D136" s="83"/>
       <c r="E136" s="83"/>
@@ -26929,7 +26973,7 @@
         <v>74</v>
       </c>
       <c r="K136" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="22.5" customHeight="1">
@@ -26937,10 +26981,10 @@
         <v>642</v>
       </c>
       <c r="B137" s="77" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="C137" s="76" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="D137" s="70"/>
       <c r="E137" s="70"/>
@@ -26956,7 +27000,7 @@
         <v>74</v>
       </c>
       <c r="K137" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="22.5" customHeight="1">
@@ -26964,10 +27008,10 @@
         <v>643</v>
       </c>
       <c r="B138" s="81" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="C138" s="82" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="D138" s="83"/>
       <c r="E138" s="83"/>
@@ -26985,7 +27029,7 @@
         <v>74</v>
       </c>
       <c r="K138" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="22.5" customHeight="1">
@@ -26993,10 +27037,10 @@
         <v>462</v>
       </c>
       <c r="B139" s="104" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="C139" s="104" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="D139" s="62" t="s">
         <v>818</v>
@@ -27018,7 +27062,7 @@
         <v>25</v>
       </c>
       <c r="K139" s="104" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="22.5" customHeight="1">
@@ -27026,10 +27070,10 @@
         <v>644</v>
       </c>
       <c r="B140" s="81" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="C140" s="82" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D140" s="83"/>
       <c r="E140" s="83"/>
@@ -27047,7 +27091,7 @@
         <v>74</v>
       </c>
       <c r="K140" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="22.5" customHeight="1">
@@ -27055,10 +27099,10 @@
         <v>645</v>
       </c>
       <c r="B141" s="77" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="C141" s="76" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="D141" s="70"/>
       <c r="E141" s="70"/>
@@ -27074,7 +27118,7 @@
         <v>25</v>
       </c>
       <c r="K141" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="22.5" customHeight="1">
@@ -27082,10 +27126,10 @@
         <v>646</v>
       </c>
       <c r="B142" s="81" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="C142" s="82" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="D142" s="83"/>
       <c r="E142" s="83"/>
@@ -27101,7 +27145,7 @@
         <v>74</v>
       </c>
       <c r="K142" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="22.5" customHeight="1">
@@ -27109,10 +27153,10 @@
         <v>647</v>
       </c>
       <c r="B143" s="77" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="C143" s="76" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="D143" s="70"/>
       <c r="E143" s="70"/>
@@ -27128,7 +27172,7 @@
         <v>74</v>
       </c>
       <c r="K143" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="22.5" customHeight="1">
@@ -27136,10 +27180,10 @@
         <v>648</v>
       </c>
       <c r="B144" s="81" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="C144" s="82" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="D144" s="83"/>
       <c r="E144" s="83"/>
@@ -27155,7 +27199,7 @@
         <v>74</v>
       </c>
       <c r="K144" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="22.5" customHeight="1">
@@ -27163,10 +27207,10 @@
         <v>649</v>
       </c>
       <c r="B145" s="77" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="C145" s="76" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="D145" s="70"/>
       <c r="E145" s="70"/>
@@ -27182,7 +27226,7 @@
         <v>25</v>
       </c>
       <c r="K145" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="22.5" customHeight="1">
@@ -27190,10 +27234,10 @@
         <v>650</v>
       </c>
       <c r="B146" s="81" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="C146" s="82" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="D146" s="83"/>
       <c r="E146" s="83"/>
@@ -27209,7 +27253,7 @@
         <v>74</v>
       </c>
       <c r="K146" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="22.5" customHeight="1">
@@ -27217,10 +27261,10 @@
         <v>651</v>
       </c>
       <c r="B147" s="77" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="C147" s="76" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="D147" s="70"/>
       <c r="E147" s="70"/>
@@ -27236,7 +27280,7 @@
         <v>25</v>
       </c>
       <c r="K147" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="22.5" customHeight="1">
@@ -27244,10 +27288,10 @@
         <v>652</v>
       </c>
       <c r="B148" s="81" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="C148" s="82" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="D148" s="83"/>
       <c r="E148" s="83"/>
@@ -27263,7 +27307,7 @@
         <v>74</v>
       </c>
       <c r="K148" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="22.5" customHeight="1">
@@ -27271,10 +27315,10 @@
         <v>653</v>
       </c>
       <c r="B149" s="77" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="C149" s="76" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="D149" s="70"/>
       <c r="E149" s="70"/>
@@ -27290,7 +27334,7 @@
         <v>74</v>
       </c>
       <c r="K149" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="22.5" customHeight="1">
@@ -27298,7 +27342,7 @@
         <v>465</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="166" t="s">
@@ -27317,10 +27361,10 @@
         <v>654</v>
       </c>
       <c r="B151" s="82" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="C151" s="82" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="D151" s="83"/>
       <c r="E151" s="83"/>
@@ -27336,7 +27380,7 @@
         <v>790</v>
       </c>
       <c r="K151" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="22.5" customHeight="1">
@@ -27344,10 +27388,10 @@
         <v>754</v>
       </c>
       <c r="B152" s="77" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="C152" s="76" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="D152" s="70"/>
       <c r="E152" s="70"/>
@@ -27363,7 +27407,7 @@
         <v>25</v>
       </c>
       <c r="K152" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="22.5" customHeight="1">
@@ -27371,10 +27415,10 @@
         <v>755</v>
       </c>
       <c r="B153" s="81" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="C153" s="82" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="D153" s="83"/>
       <c r="E153" s="83"/>
@@ -27390,7 +27434,7 @@
         <v>74</v>
       </c>
       <c r="K153" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="22.5" customHeight="1">
@@ -27398,10 +27442,10 @@
         <v>756</v>
       </c>
       <c r="B154" s="77" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="C154" s="76" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="D154" s="70"/>
       <c r="E154" s="70"/>
@@ -27417,7 +27461,7 @@
         <v>25</v>
       </c>
       <c r="K154" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="22.5" customHeight="1">
@@ -27425,10 +27469,10 @@
         <v>757</v>
       </c>
       <c r="B155" s="81" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="C155" s="82" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="D155" s="83"/>
       <c r="E155" s="83"/>
@@ -27446,7 +27490,7 @@
         <v>25</v>
       </c>
       <c r="K155" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="22.5" customHeight="1">
@@ -27454,10 +27498,10 @@
         <v>758</v>
       </c>
       <c r="B156" s="76" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="C156" s="76" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="D156" s="70"/>
       <c r="E156" s="70"/>
@@ -27473,7 +27517,7 @@
         <v>513</v>
       </c>
       <c r="K156" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="22.5" customHeight="1">
@@ -27481,10 +27525,10 @@
         <v>759</v>
       </c>
       <c r="B157" s="81" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="C157" s="82" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="D157" s="83"/>
       <c r="E157" s="83"/>
@@ -27502,7 +27546,7 @@
         <v>74</v>
       </c>
       <c r="K157" s="82" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="22.5" customHeight="1">
@@ -27510,10 +27554,10 @@
         <v>760</v>
       </c>
       <c r="B158" s="76" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="C158" s="76" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="D158" s="70"/>
       <c r="E158" s="70"/>
@@ -27531,7 +27575,7 @@
         <v>25</v>
       </c>
       <c r="K158" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="22.5" customHeight="1">
@@ -27539,10 +27583,10 @@
         <v>761</v>
       </c>
       <c r="B159" s="77" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="C159" s="76" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="D159" s="10"/>
       <c r="E159" s="11"/>
@@ -27558,7 +27602,7 @@
         <v>25</v>
       </c>
       <c r="K159" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="22.5" customHeight="1">
@@ -27566,10 +27610,10 @@
         <v>762</v>
       </c>
       <c r="B160" s="77" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="C160" s="76" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="D160" s="10"/>
       <c r="E160" s="11"/>
@@ -27585,7 +27629,7 @@
         <v>25</v>
       </c>
       <c r="K160" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="22.5" customHeight="1">
@@ -27610,10 +27654,10 @@
         <v>763</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="D162" s="10"/>
       <c r="E162" s="11"/>
@@ -27631,7 +27675,7 @@
         <v>74</v>
       </c>
       <c r="K162" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="22.5" customHeight="1">
@@ -27639,10 +27683,10 @@
         <v>764</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="D163" s="10"/>
       <c r="E163" s="11"/>
@@ -27660,7 +27704,7 @@
         <v>25</v>
       </c>
       <c r="K163" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="22.5" customHeight="1">
@@ -27668,10 +27712,10 @@
         <v>765</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="D164" s="10"/>
       <c r="E164" s="11"/>
@@ -27689,7 +27733,7 @@
         <v>745</v>
       </c>
       <c r="K164" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="22.5" customHeight="1">
@@ -27697,10 +27741,10 @@
         <v>766</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="D165" s="10"/>
       <c r="E165" s="11"/>
@@ -27718,7 +27762,7 @@
         <v>551</v>
       </c>
       <c r="K165" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="22.5" customHeight="1">
@@ -27755,10 +27799,10 @@
         <v>11</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="D167" s="10"/>
       <c r="E167" s="11"/>
@@ -27776,7 +27820,7 @@
         <v>551</v>
       </c>
       <c r="K167" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="22.5" customHeight="1">
@@ -27813,10 +27857,10 @@
         <v>18</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="D169" s="10"/>
       <c r="E169" s="11"/>
@@ -27834,7 +27878,7 @@
         <v>551</v>
       </c>
       <c r="K169" s="76" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="22.5" customHeight="1">
@@ -29386,10 +29430,10 @@
     <row r="248" spans="1:11" ht="22.5" customHeight="1">
       <c r="A248" s="46"/>
       <c r="B248" s="9" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="D248" s="10"/>
       <c r="E248" s="48" t="s">
